--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$J$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$J$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証60ケース）。上から順に実施する。S-01〜S-11が準備、T-／C-が検証、R-01〜R-06は動作テストでは検出できない実装物のレビュー。S-02（算式の確定）とS-03（サンプルデータ再作成）はゲート。黄色は記入欄。スクショは ID.png で保存。</t>
+          <t>確かめる手順（準備11行＋検証63ケース）。上から順に実施する。S-01〜S-11が準備、T-／C-が検証、R-01〜R-06は動作テストでは検出できない実装物のレビュー。S-02（算式の確定）とS-03（サンプルデータ再作成）はゲート。黄色は記入欄。スクショは ID.png で保存。</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>2つの日時が異なる（例：反映8/1・編集6/25）。手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン) の4種が記録・絞り込みできる</t>
+          <t>①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>未選択の防止と文字化け</t>
+          <t>未選択でのエクスポート防止</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>種別／対象／項目のいずれかを未選択のまま「エクスポート」→ その後T-E04の出力ファイルをExcelで開く</t>
+          <t>種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>警告が出て出力されない（空ファイルが落ちてこない）。日本語が文字化けしない（BOM付きUTF-8）</t>
+          <t>警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>AC-27 AC-28</t>
+          <t>AC-27</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
@@ -2808,42 +2808,42 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>取込データ</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>T-N01</t>
+          <t>T-E08</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>取込元データの確認</t>
+          <t>出力CSVの文字化け</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>T-I03実施済み</t>
+          <t>S-04 ／ T-E04で出力済み</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
+          <t>T-E04で出力したCSVをExcelで開く</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
+          <t>日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>T-N01.png</t>
+          <t>T-E08.png</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>AC-39</t>
+          <t>AC-28</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr"/>
@@ -2857,37 +2857,37 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>T-N02</t>
+          <t>T-N01</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>取込前のプレビューと前回差分</t>
+          <t>取込元データの確認</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>S-06 S-12</t>
+          <t>T-I03実施済み</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す</t>
+          <t>サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回330,000円→新規350,000円」の形式で差だけが表示される。読み込み＝取込中モーダルが出て完了する</t>
+          <t>設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>T-N02.png</t>
+          <t>T-N01.png</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>AC-50</t>
+          <t>AC-39</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
@@ -2901,37 +2901,37 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>T-N03</t>
+          <t>T-N02</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>取込データと人件費実績の相互導線</t>
+          <t>取込前のプレビューと前回差分</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-06 S-12</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
+          <t>設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>2経路とも到達する（不通=0）</t>
+          <t>プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回330,000円→新規350,000円」の形式で差だけが表示される。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>T-N03.png</t>
+          <t>T-N02.png</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>AC-30</t>
+          <t>AC-50</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr"/>
@@ -2940,42 +2940,42 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>T-Z01</t>
+          <t>T-N03</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>移行前後の突合</t>
+          <t>取込データと人件費実績の相互導線</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>S-09 S-11</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>移行を実施し、移行後の従業員一覧・設定履歴・直近3か月の人件費実績を出力して data/15 で突合</t>
+          <t>人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>件数の増減＝0／全項目の差分＝0／適用日付が空の行＝0／3か月とも人件費の差分＝0円</t>
+          <t>2経路とも到達する（不通=0）</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>T-Z01.png</t>
+          <t>T-N03.png</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>AC-01 AC-02 AC-03</t>
+          <t>AC-30</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
@@ -2989,37 +2989,37 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>T-Z04</t>
+          <t>T-Z01</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>サイドバーの構成</t>
+          <t>移行前後の突合（既存データ）</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>S-09 S-11</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
+          <t>移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
+          <t>件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>T-Z04.png</t>
+          <t>T-Z01.png</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>AC-29</t>
+          <t>AC-01</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr"/>
@@ -3033,37 +3033,37 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>T-Z05</t>
+          <t>T-Z02</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>遷移と表示規則の網羅</t>
+          <t>移行後の適用日付の付与</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>S-04 S-05</t>
+          <t>S-09 ／ T-Z01実施済み</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+          <t>移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+          <t>適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>T-Z05.png</t>
+          <t>T-Z02.png</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>AC-30 AC-01</t>
+          <t>AC-02</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr"/>
@@ -3072,42 +3072,42 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>横断</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>C-001</t>
+          <t>T-Z03</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプなし）</t>
+          <t>移行前後の過去月の人件費</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>S-03 S-07</t>
+          <t>S-09 ／ T-Z01実施済み</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>2026-05の EMP-002（概算280,000・深夜2h=2,800）と EMP-007（概算300,000・深夜4h=6,000）を検算</t>
+          <t>移行前に出力しておいた直近3か月の人件費実績と、移行後の同3か月を突合する</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>EMP-002＝282,800／EMP-007＝306,000（差分0円）</t>
+          <t>3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>C-001.png</t>
+          <t>T-Z03.png</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>AC-03</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr"/>
@@ -3116,42 +3116,42 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>横断</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>C-003</t>
+          <t>T-Z04</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプあり）</t>
+          <t>サイドバーの構成</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>S-03 S-07</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>2026-05の EMP-001（概算320,000・ヘルプ34,000・深夜9,000）／EMP-005（350,000・58,000・18,000）／EMP-003（144,000・13,000・0）を検算</t>
+          <t>PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>EMP-001＝338,000（概算320,000＋深夜18,000）／EMP-005＝382,812（350,000＋32,812）／EMP-003＝144,000。ヘルプ人件費は実績給与を労働時間で按分し応援先へ振替（EMP-001=43,232／EMP-003=24,000／EMP-005=72,424）</t>
+          <t>閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>C-003.png</t>
+          <t>T-Z04.png</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-29</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
@@ -3160,42 +3160,42 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>横断</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>C-005</t>
+          <t>T-Z05</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>店舗別合計と全社合計の一致</t>
+          <t>遷移と表示規則の網羅</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>S-03 S-04</t>
+          <t>S-04 S-05</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
+          <t>仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
+          <t>すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>C-005.png</t>
+          <t>T-Z05.png</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>AC-11</t>
+          <t>AC-30 AC-01</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr"/>
@@ -3209,37 +3209,37 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>C-006</t>
+          <t>C-001</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>月中改定と予約の日割り</t>
+          <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>S-07 ／ data/14を投入</t>
+          <t>S-03 S-07</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
+          <t>2026-05の EMP-002（概算280,000・深夜2h=2,800）と EMP-007（概算300,000・深夜4h=6,000）を検算</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+          <t>EMP-002＝282,800／EMP-007＝306,000（差分0円）</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>C-006.png</t>
+          <t>C-001.png</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>AC-12 AC-04</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
@@ -3253,37 +3253,37 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>C-011</t>
+          <t>C-003</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>S-07 ／ data/14を投入</t>
+          <t>S-03 S-07</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
+          <t>2026-05の EMP-001（概算320,000・ヘルプ34,000・深夜9,000）／EMP-005（350,000・58,000・18,000）／EMP-003（144,000・13,000・0）を検算</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
+          <t>EMP-001＝338,000（概算320,000＋深夜18,000）／EMP-005＝382,812（350,000＋32,812）／EMP-003＝144,000。ヘルプ人件費は実績給与を労働時間で按分し応援先へ振替（EMP-001=43,232／EMP-003=24,000／EMP-005=72,424）</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>C-011.png</t>
+          <t>C-003.png</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>AC-13</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
@@ -3297,37 +3297,37 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-005</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>T-S03実施済み S-07</t>
+          <t>S-03 S-04</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>2026-05を締めた状態で EMP-001に2026-05-10適用の改定を保存し、勤怠も再取込する（締め解除後の再計算は T-S05 で確認する）</t>
+          <t>2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）</t>
+          <t>店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>C-008.png</t>
+          <t>C-005.png</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>AC-16</t>
+          <t>AC-11</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
@@ -3341,37 +3341,37 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-006</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>月中改定と予約の日割り</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>S-03 S-07</t>
+          <t>S-07 ／ data/14を投入</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・10h）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>判断7（暫定）＝基礎時給×1.5。ヘルプ人件費＝当日の有効単価×ヘルプ時間（2,000×10＝20,000）。計上先はS02</t>
+          <t>6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>C-013.png</t>
+          <t>C-006.png</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-12 AC-04</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
@@ -3385,169 +3385,169 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-011</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>S-03 S-04</t>
+          <t>S-07 ／ data/14を投入</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
+          <t>5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>C-017.png</t>
+          <t>C-011.png</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-13</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>①履歴テーブルへのUPDATE/DELETEが**0箇所**（INSERTのみ） ②従業員コードに一意制約が**1件**ある ③ヘルプ先交通費が「従業員×店舗」の**多対多**で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
-        </is>
-      </c>
-      <c r="G68" s="8" t="inlineStr">
-        <is>
-          <t>R-01.png</t>
-        </is>
-      </c>
-      <c r="H68" s="9" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47</t>
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>締めの前後で数字が動かないこと</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>T-S03実施済み S-07</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>2026-05を締めた状態で EMP-001に2026-05-10適用の改定を保存し、勤怠も再取込する（締め解除後の再計算は T-S05 で確認する）</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>C-008.png</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>AC-16</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>R-02</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>締めの実装レビュー</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
-        </is>
-      </c>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>①締め状態を保持する項目が**1つ**ある ②締め済み期間で再計算を行う経路が**0箇所**（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が**0箇所**</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>R-02.png</t>
-        </is>
-      </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>AC-16 AC-41</t>
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>C-013</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>S-03 S-07</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・10h）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>判断7（暫定）＝基礎時給×1.5。ヘルプ人件費＝当日の有効単価×ヘルプ時間（2,000×10＝20,000）。計上先はS02</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>C-013.png</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>R-03</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>入力検証とトランザクションのレビュー</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>①必須項目のサーバ側チェックが**全項目**にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の**5種**をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が**1つ**に固定されている）</t>
-        </is>
-      </c>
-      <c r="G70" s="8" t="inlineStr">
-        <is>
-          <t>R-03.png</t>
-        </is>
-      </c>
-      <c r="H70" s="9" t="inlineStr">
-        <is>
-          <t>AC-23 AC-42 AC-43</t>
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>C-017</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>交通費の計上先</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>S-03 S-04</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>C-017.png</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>AC-15</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
@@ -3561,12 +3561,12 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>計算ロジックの共有レビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -3576,22 +3576,22 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+          <t>テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
         </is>
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>同じ集計ロジックを参照している（画面ごとの独自計算が**0箇所**）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も**1箇所**に集約されている</t>
+          <t>①履歴テーブルへのUPDATE/DELETEが**0箇所**（INSERTのみ） ②従業員コードに一意制約が**1件**ある ③ヘルプ先交通費が「従業員×店舗」の**多対多**で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
         </is>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>R-04.png</t>
+          <t>R-01.png</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
-          <t>AC-35 AC-11</t>
+          <t>AC-07 AC-40 AC-47</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr"/>
@@ -3605,12 +3605,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>締めの実装レビュー</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -3620,22 +3620,22 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>取込の列解決の実装を提示してもらう</t>
+          <t>締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>CSVの列名がコードに直接書かれている箇所が**0箇所**。列の対応はマッピング設定から解決している</t>
+          <t>①締め状態を保持する項目が**1つ**ある ②締め済み期間で再計算を行う経路が**0箇所**（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が**0箇所**</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>R-05.png</t>
+          <t>R-02.png</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-16 AC-41</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr"/>
@@ -3649,12 +3649,12 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>設定更新処理の共通化レビュー</t>
+          <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -3664,34 +3664,166 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+          <t>取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>設定更新の処理が**1箇所**に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+          <t>①必須項目のサーバ側チェックが**全項目**にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の**5種**をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が**1つ**に固定されている）</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>R-06.png</t>
+          <t>R-03.png</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="5" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>R-04</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>計算ロジックの共有レビュー</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>同じ集計ロジックを参照している（画面ごとの独自計算が**0箇所**）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も**1箇所**に集約されている</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>R-04.png</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>AC-35 AC-11</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr"/>
+      <c r="J74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>R-05</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>列マッピングの実装レビュー</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>取込の列解決の実装を提示してもらう</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>CSVの列名がコードに直接書かれている箇所が**0箇所**。列の対応はマッピング設定から解決している</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>R-05.png</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>AC-22 AC-24</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr"/>
+      <c r="J75" s="5" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>設定更新の処理が**1箇所**に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>R-06.png</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr"/>
+      <c r="J76" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:J73"/>
+  <autoFilter ref="A2:J76"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J3:J73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J3:J76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$J$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$J$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -505,7 +505,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証63ケース）。上から順に実施する。S-01〜S-11が準備、T-／C-が検証、R-01〜R-06は動作テストでは検出できない実装物のレビュー。S-02（算式の確定）とS-03（サンプルデータ再作成）はゲート。黄色は記入欄。スクショは ID.png で保存。</t>
+          <t>確かめる手順（準備11行＋検証64ケース）。上から順に実施する。S-01〜S-11が準備、T-／C-が検証、R-01〜R-06は動作テストでは検出できない実装物のレビュー。S-02（算式の確定）とS-03（サンプルデータ再作成）はゲート。黄色は記入欄。スクショは ID.png で保存。</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>削除アイコン →（a）キャンセル →（b）実行</t>
+          <t>EMP-012（山田 さくら・実績データに含まれない末尾の従業員）の削除アイコン →（a）キャンセル →（b）実行</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>（a）完了後に一覧へ戻り13名になる （b）一覧へ戻り件数は変わらない （c）従業員一覧／設定インポートへ遷移</t>
+          <t>（a）完了表示のあと一覧へ戻り、**登録前より1名増えている** （b）一覧へ戻り件数は変わらない （c）従業員一覧／設定インポートへ遷移</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻り、C-008で保留されていた5/10からの改定が反映されて再計算される。EMP-001の2026-05の実績給与＝352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
+          <t>「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>AC-17 AC-19</t>
+          <t>AC-19</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
@@ -3209,37 +3209,37 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>C-001</t>
+          <t>C-000</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプなし）</t>
+          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>S-03 S-07</t>
+          <t>S-03 S-05</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>2026-05の EMP-002（概算280,000・深夜2h=2,800）と EMP-007（概算300,000・深夜4h=6,000）を検算</t>
+          <t>操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>EMP-002＝282,800／EMP-007＝306,000（差分0円）</t>
+          <t>従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>C-001.png</t>
+          <t>C-000.png</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
@@ -3253,37 +3253,37 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>C-003</t>
+          <t>C-001</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプあり）</t>
+          <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>S-03 S-07</t>
+          <t>C-000 S-03 S-07</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>2026-05の EMP-001（概算320,000・ヘルプ34,000・深夜9,000）／EMP-005（350,000・58,000・18,000）／EMP-003（144,000・13,000・0）を検算</t>
+          <t>2026-05の EMP-002（概算280,000・深夜2h=2,800）と EMP-007（概算300,000・深夜4h=6,000）を検算</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>EMP-001＝338,000（概算320,000＋深夜18,000）／EMP-005＝382,812（350,000＋32,812）／EMP-003＝144,000。ヘルプ人件費は実績給与を労働時間で按分し応援先へ振替（EMP-001=43,232／EMP-003=24,000／EMP-005=72,424）</t>
+          <t>EMP-002＝282,800／EMP-007＝306,000（差分0円）</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>C-003.png</t>
+          <t>C-001.png</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
@@ -3297,37 +3297,37 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>C-005</t>
+          <t>C-003</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>店舗別合計と全社合計の一致</t>
+          <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>S-03 S-04</t>
+          <t>C-000 S-03 S-07</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
+          <t>2026-05の EMP-001（概算320,000・ヘルプ34,000・深夜9,000）／EMP-005（350,000・58,000・18,000）／EMP-003（144,000・13,000・0）を検算</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
+          <t>EMP-001＝338,000（概算320,000＋深夜18,000）／EMP-005＝382,812（350,000＋32,812）／EMP-003＝144,000。ヘルプ人件費は実績給与を労働時間で按分し応援先へ振替（EMP-001=43,232／EMP-003=24,000／EMP-005=72,424）</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>C-005.png</t>
+          <t>C-003.png</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>AC-11</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
@@ -3341,37 +3341,37 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>C-006</t>
+          <t>C-005</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>月中改定と予約の日割り</t>
+          <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>S-07 ／ data/14を投入</t>
+          <t>C-000 S-03 S-04</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
+          <t>2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+          <t>店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>C-006.png</t>
+          <t>C-005.png</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>AC-12 AC-04</t>
+          <t>AC-11</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
@@ -3385,37 +3385,37 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>C-011</t>
+          <t>C-006</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>月中改定と予約の日割り</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>S-07 ／ data/14を投入</t>
+          <t>C-000 S-07 ／ data/14を投入</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
+          <t>EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
+          <t>6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>C-011.png</t>
+          <t>C-006.png</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>AC-13</t>
+          <t>AC-12 AC-04</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
@@ -3429,37 +3429,37 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-011</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>T-S03実施済み S-07</t>
+          <t>C-000 S-07 ／ data/14を投入</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>2026-05を締めた状態で EMP-001に2026-05-10適用の改定を保存し、勤怠も再取込する（締め解除後の再計算は T-S05 で確認する）</t>
+          <t>EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）</t>
+          <t>5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>C-008.png</t>
+          <t>C-011.png</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>AC-16</t>
+          <t>AC-13</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
@@ -3473,37 +3473,37 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-008</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>締めの前後で数字が動かないこと</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>S-03 S-07</t>
+          <t>C-000 S-07</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・10h）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>判断7（暫定）＝基礎時給×1.5。ヘルプ人件費＝当日の有効単価×ヘルプ時間（2,000×10＝20,000）。計上先はS02</t>
+          <t>（a）5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>C-013.png</t>
+          <t>C-008.png</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-16 AC-17</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
@@ -3517,81 +3517,81 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-013</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>S-03 S-04</t>
+          <t>C-000 S-03 S-07</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・10h）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
+          <t>判断7（暫定）＝基礎時給×1.5。ヘルプ人件費＝当日の有効単価×ヘルプ時間（2,000×10＝20,000）。計上先はS02</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>C-017.png</t>
+          <t>C-013.png</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>①履歴テーブルへのUPDATE/DELETEが**0箇所**（INSERTのみ） ②従業員コードに一意制約が**1件**ある ③ヘルプ先交通費が「従業員×店舗」の**多対多**で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="inlineStr">
-        <is>
-          <t>R-01.png</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47</t>
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>C-017</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>交通費の計上先</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>C-000 S-03 S-04</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>C-017.png</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>AC-15</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr"/>
@@ -3605,12 +3605,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>締めの実装レビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -3620,22 +3620,22 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
+          <t>テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>①締め状態を保持する項目が**1つ**ある ②締め済み期間で再計算を行う経路が**0箇所**（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が**0箇所**</t>
+          <t>①履歴テーブルへのUPDATE/DELETEが**0箇所**（INSERTのみ） ②従業員コードに一意制約が**1件**ある ③ヘルプ先交通費が「従業員×店舗」の**多対多**で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
         </is>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>R-02.png</t>
+          <t>R-01.png</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>AC-16 AC-41</t>
+          <t>AC-07 AC-40 AC-47</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr"/>
@@ -3649,12 +3649,12 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>入力検証とトランザクションのレビュー</t>
+          <t>締めの実装レビュー</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -3664,22 +3664,22 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
+          <t>締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>①必須項目のサーバ側チェックが**全項目**にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の**5種**をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が**1つ**に固定されている）</t>
+          <t>①締め状態を保持する項目が**1つ**ある ②締め済み期間で再計算を行う経路が**0箇所**（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が**0箇所**</t>
         </is>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>R-03.png</t>
+          <t>R-02.png</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>AC-23 AC-42 AC-43</t>
+          <t>AC-16 AC-41</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
@@ -3693,12 +3693,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>計算ロジックの共有レビュー</t>
+          <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+          <t>取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>同じ集計ロジックを参照している（画面ごとの独自計算が**0箇所**）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も**1箇所**に集約されている</t>
+          <t>①必須項目のサーバ側チェックが**全項目**にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の**5種**をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が**1つ**に固定されている）</t>
         </is>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>R-04.png</t>
+          <t>R-03.png</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>AC-35 AC-11</t>
+          <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
@@ -3737,12 +3737,12 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>計算ロジックの共有レビュー</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
@@ -3752,22 +3752,22 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>取込の列解決の実装を提示してもらう</t>
+          <t>人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>CSVの列名がコードに直接書かれている箇所が**0箇所**。列の対応はマッピング設定から解決している</t>
+          <t>同じ集計ロジックを参照している（画面ごとの独自計算が**0箇所**）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も**1箇所**に集約されている</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>R-05.png</t>
+          <t>R-04.png</t>
         </is>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-35 AC-11</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>設定更新処理の共通化レビュー</t>
+          <t>列マッピングの実装レビュー</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -3796,34 +3796,78 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+          <t>取込の列解決の実装を提示してもらう</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>設定更新の処理が**1箇所**に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+          <t>CSVの列名がコードに直接書かれている箇所が**0箇所**。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>R-06.png</t>
+          <t>R-05.png</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-22 AC-24</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="5" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>設定更新の処理が**1箇所**に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>R-06.png</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr"/>
+      <c r="J77" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:J76"/>
+  <autoFilter ref="A2:J77"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J3:J76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J3:J77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>data/07（KOT）・08（ジョブカン）・09（異常系）・10（給与設定）・11（先頭説明行あり）を手元に用意し、data/12（設定未入力のEMP-015）を投入。あわせて data/16・17（前回取込の差分確認用）を用意。data/18（列マッピング表のテンプレ）も用意</t>
+          <t>data/07（KOT）・08（ジョブカン）・09（異常系）・10（給与設定）・11（先頭説明行あり）を手元に用意し、data/12（設定未入力のEMP-015）を投入。あわせて data/16・17（前回取込の差分確認用）を用意。data/18（列マッピング表のテンプレ）・data/19（同じ従業員コードが2行あるCSV）も用意</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>（a）data/07を2回続けて取り込む （b）同じ従業員コードが2行あるCSVを作って取り込む</t>
+          <t>（a）data/07を2回続けて取り込む （b）data/19（EMP-002が2行・単位給与額が異なる）を取り込む</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>S-06 S-12</t>
+          <t>S-05 S-06</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す</t>
+          <t>設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回330,000円→新規350,000円」の形式で差だけが表示される。読み込み＝取込中モーダルが出て完了する</t>
+          <t>プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$J$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$K$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -487,25 +487,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="44" customHeight="1">
+    <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証64ケース）。上から順に実施する。S-01〜S-11が準備、T-／C-が検証、R-01〜R-06は動作テストでは検出できない実装物のレビュー。S-02（算式の確定）とS-03（サンプルデータ再作成）はゲート。黄色は記入欄。スクショは ID.png で保存。</t>
+          <t>確かめる手順（準備11行＋検証64ケース）。上から順に実施する。S-01〜S-11が準備、T-／C-が検証、R-01〜R-06は動作テストでは検出できない実装物のレビュー。「ヘルプ該当箇所」はヘルプページのどの項目を担保する検証かを示す（ヘルプを直したときに影響する検証が逆引きできる）。黄色は記入欄。</t>
         </is>
       </c>
     </row>
@@ -542,20 +543,25 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>ヘルプ該当箇所</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>スクショ</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>対応ID（受入条件）</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>実際の値</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
@@ -592,18 +598,19 @@
           <t>サイドバーに「従業員管理」が表示される／モックのトップが表示される</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>S-01.png</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr"/>
       <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -636,18 +643,19 @@
           <t>6件が確定し文書化されている（仕様書 第5部 11-A・11-C）</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>S-02.png</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-12 AC-15</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -680,18 +688,19 @@
           <t>全行が算式で再現でき、日次合計＝月次・店舗別合計＝全社（差0円）</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>S-03.png</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr"/>
       <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -724,18 +733,19 @@
           <t>従業員一覧に12名が表示される</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>S-04.png</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -768,18 +778,19 @@
           <t>履歴に適用済3・予約中1が入る／人件費実績に5名分が表示される</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>S-05.png</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -812,18 +823,19 @@
           <t>5ファイルがアップロード可能な状態／設定が欠落した従業員が1名いる</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>S-06.png</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -856,18 +868,19 @@
           <t>以降の計算ケースで同じ入力値を使う</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>S-07.png</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -900,18 +913,19 @@
           <t>ボタンが「2026-05 締め」になっている</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>S-08.png</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -944,18 +958,19 @@
           <t>突合シート M-01〜M-06 が埋まった状態</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>S-09.png</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -988,18 +1003,19 @@
           <t>店長でログインでき、従業員管理のメニューが表示される</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>S-10.png</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1032,18 +1048,19 @@
           <t>移行を検証枠内で実行できる段取りができている</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>S-11.png</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1076,18 +1093,23 @@
           <t>12名が表示。12列（名前/従業員コード/所属店舗/ヘルプ先店舗/雇用区分/給与単位/単位給与額/交通費単位/単位交通費/所定労働時間/みなし残業時間/アクション）。雇用区分・給与単位が色分け。EMP-001はヘルプ先2バッジ、EMP-002は空。単位給与額が数値順にソート（1,000→…→410,000）。該当なしで「データはありません。」</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>従業員を探す・削除する</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>T-L01.png</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1120,18 +1142,23 @@
           <t>渋谷店＝3名（EMP-001・002・011）、正社員＝6名、田中＝1名。2段目で対象データが切り替わる</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>従業員を探す・削除する</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>T-L08.png</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>AC-33</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1164,18 +1191,23 @@
           <t>**5経路すべて到達**（従業員登録／設定インポート／設定・実績エクスポート／設定取込データ／従業員詳細）。不通=0</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>従業員を探す・削除する</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>T-L06.png</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>AC-30</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1208,18 +1240,23 @@
           <t>（a）12名のまま削除されない （b）完了表示のあと11名になる</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>従業員を探す・削除する</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>T-L10.png</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>AC-34</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1252,18 +1289,23 @@
           <t>13項目（名前/従業員コード/所属店舗/ヘルプ先店舗/雇用区分/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。¥320,000 と千区切り表示。適用日付は所定労働時間・みなし残業時間の下の行・初期値は当日</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>従業員を登録する</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>T-R02.png</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>AC-06</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1296,18 +1338,23 @@
           <t>選択した2店それぞれに交通費欄が出る／（a）必須バリデーションで登録できない／（b）新宿店の欄だけ消え、青山店の入力値は残る</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>従業員を登録する</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>T-R04.png</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>AC-15 AC-47</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1340,18 +1387,23 @@
           <t>（a）完了表示のあと一覧へ戻り、**登録前より1名増えている** （b）一覧へ戻り件数は変わらない （c）従業員一覧／設定インポートへ遷移</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>従業員を登録する</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>T-R07.png</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>AC-06 AC-30</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1384,18 +1436,23 @@
           <t>いずれの場合も登録できず、画面が遷移しない。どの項目が不足かが分かる表示になる</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>設定が保存できません</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>T-R10.png</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>AC-43</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1428,18 +1485,23 @@
           <t>基本情報／設定変更履歴／給与実績 が表示。基本情報は登録と同項目・同配置。履歴は14列（変更反映日時〜変更ソース の13項目＋操作）。2026-08-01行が「予約中」</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>T-D01.png</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1472,18 +1534,23 @@
           <t>「（日付）からの適用を予約しました」と表示。履歴に「予約中」が1行追加。一覧の単位給与額は320,000のまま</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>給与改定を先の日付で予約する</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>T-D04.png</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>AC-04</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1516,18 +1583,23 @@
           <t>一覧が340,000に変わり、履歴が「適用中」、旧行が「過去」になる</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>給与改定を先の日付で予約する</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>T-D05.png</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>AC-05</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -1560,18 +1632,23 @@
           <t>「即時反映しました」と表示。一覧が290,000になる</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>T-D06.png</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>AC-06</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1604,18 +1681,23 @@
           <t>月次17列（年月〜深夜残業代＋交通費＋総支給額）／日次14列。個人向けに列を絞った構成で、人件費実績（26列/21列）とは別。フィルタで期間が絞られる。表示中の内容がBOM付きCSVで出力される</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>T-D09.png</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>AC-35 AC-36</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1648,18 +1730,23 @@
           <t>（a）削除されず件数が変わらない （b）確認のあと削除される （c）一覧へ戻る（保存されない）</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>従業員を探す・削除する</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>T-D08.png</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>AC-34 AC-30</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1692,18 +1779,23 @@
           <t>履歴が1行増える。既存行の値の差分＝0</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>数字が合わないとき</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>T-H01.png</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -1736,18 +1828,23 @@
           <t>①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>数字が合わないとき</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>T-H02.png</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>AC-08 AC-09</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1780,18 +1877,23 @@
           <t>店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では**2行**（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>数字が合わないとき</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>T-H04.png</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>AC-33 AC-36 AC-30</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -1824,18 +1926,23 @@
           <t>全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>T-A02.png</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>AC-10 AC-31</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -1868,18 +1975,23 @@
           <t>モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。**従業員詳細の履歴が1行増え、変更ソースが記録される**（詳細から編集した場合と同じ形式）</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>T-A09.png</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>AC-49</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -1912,18 +2024,23 @@
           <t>全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>T-A05.png</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -1956,18 +2073,23 @@
           <t>表示中のタブ・モード・フィルタの内容が出力される。日本語が文字化けしない</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>データを出力する</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>T-A07.png</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>AC-36</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -2000,18 +2122,23 @@
           <t>「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>T-A08.png</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>AC-48</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -2044,18 +2171,23 @@
           <t>月別のみ「2026-05 締め」が表示。日別には表示されない</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>T-S01.png</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>AC-18</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -2088,18 +2220,23 @@
           <t>「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>T-S03.png</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>AC-16 AC-19 AC-32</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -2132,18 +2269,23 @@
           <t>編集できない（または反映されない）</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>数字・締めについて</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>T-S04.png</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>AC-16</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -2176,18 +2318,23 @@
           <t>締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>締めたあとに給与改定が決まったとき</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>T-D07.png</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>AC-20</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -2220,18 +2367,23 @@
           <t>「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>数字・締めについて</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>T-S05.png</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>AC-19</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -2264,18 +2416,23 @@
           <t>締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>どなたが操作できますか</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>T-S07.png</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>AC-41</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -2308,18 +2465,23 @@
           <t>従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>はじめて設定する</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>T-I02.png</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>AC-21 AC-30</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -2352,18 +2514,23 @@
           <t>07は3行すべて取り込まれ、EMP-001=340,000・EMP-005=360,000に更新、EMP-013は新規追加。10は給与設定（ヘルプ先交通費 S02:700;S03:900 の記法を含む）が反映される</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>はじめて設定する</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>T-I03.png</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>AC-21</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -2396,18 +2563,23 @@
           <t>3行すべて取り込まれる（EMP-003=1,250・EMP-010=1,300・EMP-014は新規）</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>はじめて設定する</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>T-I04.png</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>AC-22</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -2440,18 +2612,23 @@
           <t>4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーになります</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>T-I05.png</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>AC-23</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -2484,18 +2661,23 @@
           <t>（a）2回目は更新となり件数が増えない （b）重複行がエラーとして検出される（両方が登録されない）</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーになります</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>T-I17.png</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>AC-40</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="5" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -2528,18 +2710,23 @@
           <t>部分的に登録された行が残らない（全体拒否）か、正常行のみ登録され異常行が明示される（行単位）。**どちらであっても、中途半端な状態が残らない**</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>CSVの取り込みでエラーになります</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>T-I18.png</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>AC-42</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -2572,18 +2759,23 @@
           <t>余計な行が無視され、3行が正しく取り込まれる</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>T-I11.png</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>AC-37</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -2616,18 +2808,23 @@
           <t>テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>T-I09.png</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr"/>
+      <c r="K49" s="5" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -2660,18 +2857,23 @@
           <t>テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>T-I19.png</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>AC-51</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr"/>
+      <c r="K50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -2704,18 +2906,23 @@
           <t>専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>データを出力する</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>T-E04.png</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -2748,18 +2955,23 @@
           <t>実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
         </is>
       </c>
-      <c r="G52" s="6" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>データを出力する</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>T-E09.png</t>
         </is>
       </c>
-      <c r="H52" s="7" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>AC-25</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="5" t="inlineStr"/>
+      <c r="K52" s="5" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -2792,18 +3004,23 @@
           <t>警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>データを出力する</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>T-E07.png</t>
         </is>
       </c>
-      <c r="H53" s="7" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>AC-27</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -2836,18 +3053,23 @@
           <t>日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>データを出力する</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>T-E08.png</t>
         </is>
       </c>
-      <c r="H54" s="7" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>AC-28</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="5" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -2880,18 +3102,23 @@
           <t>設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>取り込んだ元データを確認する</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>T-N01.png</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>AC-39</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="5" t="inlineStr"/>
+      <c r="K55" s="5" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -2924,18 +3151,23 @@
           <t>プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>取り込んだ元データを確認する</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>T-N02.png</t>
         </is>
       </c>
-      <c r="H56" s="7" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t>AC-50</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="5" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -2968,18 +3200,23 @@
           <t>2経路とも到達する（不通=0）</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>取り込んだ元データを確認する</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>T-N03.png</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>AC-30</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="5" t="inlineStr"/>
+      <c r="K57" s="5" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -3012,18 +3249,23 @@
           <t>件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
         </is>
       </c>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>すでにご利用中のお客様</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>T-Z01.png</t>
         </is>
       </c>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="I58" s="7" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="5" t="inlineStr"/>
+      <c r="K58" s="5" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -3056,18 +3298,23 @@
           <t>適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている</t>
         </is>
       </c>
-      <c r="G59" s="6" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>すでにご利用中のお客様</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>T-Z02.png</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>AC-02</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="5" t="inlineStr"/>
+      <c r="K59" s="5" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -3100,18 +3347,23 @@
           <t>3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>すでにご利用中のお客様</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>T-Z03.png</t>
         </is>
       </c>
-      <c r="H60" s="7" t="inlineStr">
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>AC-03</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr"/>
+      <c r="K60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -3144,18 +3396,23 @@
           <t>閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>（ヘルプ記載なし・画面構成）</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t>T-Z04.png</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
+      <c r="I61" s="7" t="inlineStr">
         <is>
           <t>AC-29</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr"/>
+      <c r="K61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -3188,18 +3445,23 @@
           <t>すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>（ヘルプ記載なし・遷移網羅）</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>T-Z05.png</t>
         </is>
       </c>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="I62" s="7" t="inlineStr">
         <is>
           <t>AC-30 AC-01</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="5" t="inlineStr"/>
+      <c r="K62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -3232,18 +3494,23 @@
           <t>従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>毎月の人件費を確定する</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>C-000.png</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="5" t="inlineStr"/>
+      <c r="K63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -3276,18 +3543,23 @@
           <t>EMP-002＝282,800／EMP-007＝306,000（差分0円）</t>
         </is>
       </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>人件費の計算方法</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>C-001.png</t>
         </is>
       </c>
-      <c r="H64" s="7" t="inlineStr">
+      <c r="I64" s="7" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr"/>
+      <c r="K64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -3320,18 +3592,23 @@
           <t>EMP-001＝338,000（概算320,000＋深夜18,000）／EMP-005＝382,812（350,000＋32,812）／EMP-003＝144,000。ヘルプ人件費は実績給与を労働時間で按分し応援先へ振替（EMP-001=43,232／EMP-003=24,000／EMP-005=72,424）</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>応援（ヘルプ）勤務がある場合</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>C-003.png</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>AC-10 AC-14</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="5" t="inlineStr"/>
+      <c r="K65" s="5" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -3364,18 +3641,23 @@
           <t>店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
         </is>
       </c>
-      <c r="G66" s="6" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>応援（ヘルプ）勤務がある場合</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>C-005.png</t>
         </is>
       </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="I66" s="7" t="inlineStr">
         <is>
           <t>AC-11</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr"/>
+      <c r="K66" s="5" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -3408,18 +3690,23 @@
           <t>6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>給与改定を先の日付で予約する</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>C-006.png</t>
         </is>
       </c>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>AC-12 AC-04</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr"/>
+      <c r="K67" s="5" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -3452,18 +3739,23 @@
           <t>5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>人件費の計算方法</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>C-011.png</t>
         </is>
       </c>
-      <c r="H68" s="7" t="inlineStr">
+      <c r="I68" s="7" t="inlineStr">
         <is>
           <t>AC-13</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr"/>
+      <c r="K68" s="5" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -3496,18 +3788,23 @@
           <t>（a）5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
         </is>
       </c>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>数字・締めについて</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>C-008.png</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>AC-16 AC-17</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="5" t="inlineStr"/>
+      <c r="K69" s="5" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -3540,18 +3837,23 @@
           <t>判断7（暫定）＝基礎時給×1.5。ヘルプ人件費＝当日の有効単価×ヘルプ時間（2,000×10＝20,000）。計上先はS02</t>
         </is>
       </c>
-      <c r="G70" s="6" t="inlineStr">
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>人件費の計算方法</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>C-013.png</t>
         </is>
       </c>
-      <c r="H70" s="7" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr">
         <is>
           <t>AC-10 AC-14</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="5" t="inlineStr"/>
+      <c r="K70" s="5" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -3584,18 +3886,23 @@
           <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
         </is>
       </c>
-      <c r="G71" s="6" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>応援（ヘルプ）勤務がある場合</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
         <is>
           <t>C-017.png</t>
         </is>
       </c>
-      <c r="H71" s="7" t="inlineStr">
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>AC-15</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="5" t="inlineStr"/>
+      <c r="K71" s="5" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
@@ -3628,18 +3935,23 @@
           <t>①履歴テーブルへのUPDATE/DELETEが**0箇所**（INSERTのみ） ②従業員コードに一意制約が**1件**ある ③ヘルプ先交通費が「従業員×店舗」の**多対多**で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
         </is>
       </c>
-      <c r="G72" s="8" t="inlineStr">
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>数字が合わないとき</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
         <is>
           <t>R-01.png</t>
         </is>
       </c>
-      <c r="H72" s="9" t="inlineStr">
+      <c r="I72" s="9" t="inlineStr">
         <is>
           <t>AC-07 AC-40 AC-47</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="5" t="inlineStr"/>
+      <c r="K72" s="5" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
@@ -3672,18 +3984,23 @@
           <t>①締め状態を保持する項目が**1つ**ある ②締め済み期間で再計算を行う経路が**0箇所**（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が**0箇所**</t>
         </is>
       </c>
-      <c r="G73" s="8" t="inlineStr">
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>どなたが操作できますか</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>R-02.png</t>
         </is>
       </c>
-      <c r="H73" s="9" t="inlineStr">
+      <c r="I73" s="9" t="inlineStr">
         <is>
           <t>AC-16 AC-41</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="5" t="inlineStr"/>
+      <c r="K73" s="5" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
@@ -3716,18 +4033,23 @@
           <t>①必須項目のサーバ側チェックが**全項目**にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の**5種**をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が**1つ**に固定されている）</t>
         </is>
       </c>
-      <c r="G74" s="8" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>設定が保存できません</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
         <is>
           <t>R-03.png</t>
         </is>
       </c>
-      <c r="H74" s="9" t="inlineStr">
+      <c r="I74" s="9" t="inlineStr">
         <is>
           <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="5" t="inlineStr"/>
+      <c r="K74" s="5" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
@@ -3760,18 +4082,23 @@
           <t>同じ集計ロジックを参照している（画面ごとの独自計算が**0箇所**）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も**1箇所**に集約されている</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>人件費の計算方法</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>R-04.png</t>
         </is>
       </c>
-      <c r="H75" s="9" t="inlineStr">
+      <c r="I75" s="9" t="inlineStr">
         <is>
           <t>AC-35 AC-11</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="5" t="inlineStr"/>
+      <c r="K75" s="5" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
@@ -3804,18 +4131,23 @@
           <t>CSVの列名がコードに直接書かれている箇所が**0箇所**。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
-      <c r="G76" s="8" t="inlineStr">
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>R-05.png</t>
         </is>
       </c>
-      <c r="H76" s="9" t="inlineStr">
+      <c r="I76" s="9" t="inlineStr">
         <is>
           <t>AC-22 AC-24</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="5" t="inlineStr"/>
+      <c r="K76" s="5" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
@@ -3848,26 +4180,31 @@
           <t>設定更新の処理が**1箇所**に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
         </is>
       </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>R-06.png</t>
         </is>
       </c>
-      <c r="H77" s="9" t="inlineStr">
+      <c r="I77" s="9" t="inlineStr">
         <is>
           <t>AC-49</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="5" t="inlineStr"/>
+      <c r="K77" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J77"/>
+  <autoFilter ref="A2:K77"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J3:J77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K3:K77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -506,7 +506,7 @@
     <row r="1" ht="50" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証64ケース）。上から順に実施する。S-01〜S-11が準備、T-／C-が検証、R-01〜R-06は動作テストでは検出できない実装物のレビュー。「ヘルプ該当箇所」はヘルプページのどの項目を担保する検証かを示す（ヘルプを直したときに影響する検証が逆引きできる）。黄色は記入欄。</t>
+          <t>確かめる手順（準備11行＋検証64ケース）。上から順に実施する。S-01〜S-11が準備、T-／C-が検証、R-01〜R-06は動作テストでは検出できない実装物のレビュー。「ヘルプ該当箇所」はヘルプページのどの項目を担保する検証かを示す。黄色は記入欄。</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>data/04（履歴5行）・data/05（月次5行）・data/06（日次5行）・data/13（2026-05の全稼働日54行）を投入</t>
+          <t>data/04（履歴5行）・data/05（月次5行）・data/06（日次95行）・data/13（2026-05の全稼働日95行）を投入</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -3535,12 +3535,12 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>2026-05の EMP-002（概算280,000・深夜2h=2,800）と EMP-007（概算300,000・深夜4h=6,000）を検算</t>
+          <t>2026-05の EMP-002（概算280,000・基礎時給1,750＝280,000÷160・深夜2h）と EMP-007（概算300,000・基礎時給1,875＝300,000÷160・深夜4h）を検算</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>EMP-002＝282,800／EMP-007＝306,000（差分0円）</t>
+          <t>EMP-002＝285,250（概算280,000＋深夜残業代5,250＝1,750×1.5×2h）／EMP-007＝311,250（概算300,000＋深夜残業代11,250＝1,875×1.5×4h）。いずれも差分0円</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>2026-05の EMP-001（概算320,000・ヘルプ34,000・深夜9,000）／EMP-005（350,000・58,000・18,000）／EMP-003（144,000・13,000・0）を検算</t>
+          <t>2026-05の EMP-001（概算320,000・基礎時給2,000・深夜6h・ヘルプ22h／総労働172h）／EMP-005（概算350,000・基礎時給2,187・深夜10h・ヘルプ35h／総労働185h）／EMP-003（概算144,000・時給1,200・深夜0h・ヘルプ20h／総労働120h）を検算</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>EMP-001＝338,000（概算320,000＋深夜18,000）／EMP-005＝382,812（350,000＋32,812）／EMP-003＝144,000。ヘルプ人件費は実績給与を労働時間で按分し応援先へ振替（EMP-001=43,232／EMP-003=24,000／EMP-005=72,424）</t>
+          <t>EMP-001＝338,000（概算320,000＋深夜18,000＝2,000×1.5×6h）／EMP-005＝382,812（概算350,000＋深夜32,812＝2,187×1.5×10h）／EMP-003＝144,000（深夜なし）。ヘルプ人件費は実績給与×ヘルプ時間÷総労働時間で按分し応援先へ振替（EMP-001＝43,232／EMP-003＝24,000／EMP-005＝72,424）</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・10h）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>判断7（暫定）＝基礎時給×1.5。ヘルプ人件費＝当日の有効単価×ヘルプ時間（2,000×10＝20,000）。計上先はS02</t>
+          <t>判断7（暫定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。5/8のヘルプ人件費＝実績給与338,000×11h÷総労働172h＝21,616円で、計上先はS02。みなし労働時間差分＝172−(160＋20)＝−8h（未達はマイナス表示・減額なし＝判断8）</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -502,28 +502,28 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>画面を操作して確かめるケース。「画面」列にサイドバーからの経路・タブ・ボタン名まで書いてあるので、その順に開いて操作する。青＝どこを開くか、橙＝何を証拠に残すか、紫＝ヘルプ／受入条件との対応、黄＝当日の記入欄。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
+          <t>画面を操作して確かめるケース。「画面」列にサイドバーからの経路・タブ・ボタン名・モーダル名まで書いてあるので、その順に開いて操作する。青＝どこを開くか、橙＝何を証拠に残すか、紫＝ヘルプ／受入条件との対応、黄＝当日の記入欄。判定はOK／NG／対象外から選ぶ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>検証ID</t>
@@ -590,7 +590,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="78" customHeight="1">
+    <row r="3" ht="94" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>T-L01</t>
@@ -650,7 +650,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="39" customHeight="1">
+    <row r="4" ht="49" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>T-L08</t>
@@ -710,7 +710,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="39" customHeight="1">
+    <row r="5" ht="64" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>T-L06</t>
@@ -770,7 +770,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="39" customHeight="1">
+    <row r="6" ht="49" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>T-L10</t>
@@ -830,7 +830,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="52" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>T-R02</t>
@@ -890,7 +890,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="49" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>T-R04</t>
@@ -950,7 +950,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="39" customHeight="1">
+    <row r="9" ht="64" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>T-R07</t>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="49" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>T-R10</t>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="39" customHeight="1">
+    <row r="11" ht="49" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>T-D01</t>
@@ -1130,7 +1130,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="49" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>T-D04</t>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
+    <row r="13" ht="79" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>T-D05</t>
@@ -1250,7 +1250,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="34" customHeight="1">
+    <row r="14" ht="49" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>T-D06</t>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="39" customHeight="1">
+    <row r="15" ht="49" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>T-D09</t>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="34" customHeight="1">
+    <row r="16" ht="49" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>T-D08</t>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="39" customHeight="1">
+    <row r="18" ht="49" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>T-H02</t>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
+    <row r="19" ht="64" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>T-H04</t>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="91" customHeight="1">
+    <row r="20" ht="109" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>T-A02</t>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="39" customHeight="1">
+    <row r="21" ht="49" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>T-A09</t>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="78" customHeight="1">
+    <row r="22" ht="94" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>T-A05</t>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="34" customHeight="1">
+    <row r="23" ht="49" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>T-A07</t>
@@ -1850,7 +1850,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="39" customHeight="1">
+    <row r="24" ht="49" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>T-A08</t>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="39" customHeight="1">
+    <row r="26" ht="49" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>T-S03</t>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="39" customHeight="1">
+    <row r="29" ht="49" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>T-S05</t>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="34" customHeight="1">
+    <row r="30" ht="49" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>T-S07</t>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="52" customHeight="1">
+    <row r="31" ht="64" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
           <t>T-I02</t>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="52" customHeight="1">
+    <row r="32" ht="49" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
           <t>T-I03</t>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="34" customHeight="1">
+    <row r="33" ht="49" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
           <t>T-I04</t>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="39" customHeight="1">
+    <row r="35" ht="49" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
           <t>T-I17</t>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="39" customHeight="1">
+    <row r="36" ht="49" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
           <t>T-I18</t>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="39" customHeight="1">
+    <row r="37" ht="49" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
           <t>T-I11</t>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="52" customHeight="1">
+    <row r="38" ht="79" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
           <t>T-I09</t>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="52" customHeight="1">
+    <row r="39" ht="79" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
           <t>T-I19</t>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="52" customHeight="1">
+    <row r="40" ht="79" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
           <t>T-E04</t>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="39" customHeight="1">
+    <row r="41" ht="64" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
           <t>T-E09</t>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="34" customHeight="1">
+    <row r="42" ht="49" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
           <t>T-E07</t>
@@ -3050,7 +3050,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="39" customHeight="1">
+    <row r="44" ht="49" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
           <t>T-N01</t>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="52" customHeight="1">
+    <row r="45" ht="64" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
           <t>T-N02</t>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="34" customHeight="1">
+    <row r="46" ht="49" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
           <t>T-N03</t>
@@ -3230,7 +3230,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="34" customHeight="1">
+    <row r="47" ht="49" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
           <t>T-Z01</t>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="34" customHeight="1">
+    <row r="48" ht="49" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
           <t>T-Z02</t>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="34" customHeight="1">
+    <row r="49" ht="49" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
           <t>T-Z03</t>
@@ -3410,7 +3410,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="34" customHeight="1">
+    <row r="50" ht="49" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
           <t>T-Z04</t>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="39" customHeight="1">
+    <row r="51" ht="49" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
           <t>T-Z05</t>
@@ -3554,28 +3554,28 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>金額の算式を検算するケース。先に「準備」シートのC-000（データの初期化）を実施する。計算根拠の列に算式と、その根拠となる判断を記載している。</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>検証ID</t>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="52" customHeight="1">
+    <row r="3" ht="64" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>C-000</t>
@@ -3702,7 +3702,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="52" customHeight="1">
+    <row r="4" ht="64" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>C-001</t>
@@ -3762,7 +3762,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="78" customHeight="1">
+    <row r="5" ht="79" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>C-003</t>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="49" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>C-005</t>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="52" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>C-006</t>
@@ -3942,7 +3942,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="52" customHeight="1">
+    <row r="8" ht="49" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>C-011</t>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="52" customHeight="1">
+    <row r="9" ht="64" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>C-008</t>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
+    <row r="10" ht="64" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>C-013</t>
@@ -4122,7 +4122,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="39" customHeight="1">
+    <row r="11" ht="49" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>C-017</t>
@@ -4206,28 +4206,28 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>検証を始める前の準備。上から順に実施する。★S-02（算式の確定）とS-03（サンプルデータの再作成）はゲート。</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>検証ID</t>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="39" customHeight="1">
+    <row r="3" ht="49" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>S-01</t>
@@ -4345,7 +4345,7 @@
       <c r="L3" s="9" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr"/>
     </row>
-    <row r="4" ht="52" customHeight="1">
+    <row r="4" ht="79" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>S-02</t>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="49" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>S-03</t>
@@ -4448,7 +4448,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="49" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>S-04</t>
@@ -4500,7 +4500,7 @@
       <c r="L6" s="9" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr"/>
     </row>
-    <row r="7" ht="39" customHeight="1">
+    <row r="7" ht="49" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>S-05</t>
@@ -4552,7 +4552,7 @@
       <c r="L7" s="9" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr"/>
     </row>
-    <row r="8" ht="78" customHeight="1">
+    <row r="8" ht="94" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>S-06</t>
@@ -4600,7 +4600,7 @@
       <c r="L8" s="9" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr"/>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="49" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>S-07</t>
@@ -4700,7 +4700,7 @@
       <c r="L10" s="9" t="inlineStr"/>
       <c r="M10" s="4" t="inlineStr"/>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="49" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>S-09</t>
@@ -4752,7 +4752,7 @@
       <c r="L11" s="9" t="inlineStr"/>
       <c r="M11" s="4" t="inlineStr"/>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="49" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>S-10</t>
@@ -4800,7 +4800,7 @@
       <c r="L12" s="9" t="inlineStr"/>
       <c r="M12" s="4" t="inlineStr"/>
     </row>
-    <row r="13" ht="34" customHeight="1">
+    <row r="13" ht="49" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>S-11</t>
@@ -4872,28 +4872,28 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>画面を操作しても判別できない条件。実装物（スキーマ・API・コード）を提示してもらって確認する。エンジニアの同席が必要。</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>検証ID</t>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="52" customHeight="1">
+    <row r="3" ht="64" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>R-01</t>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="39" customHeight="1">
+    <row r="4" ht="49" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>R-02</t>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="52" customHeight="1">
+    <row r="5" ht="64" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>R-03</t>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="49" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>R-04</t>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="49" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>R-06</t>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -69,7 +69,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F0FF"/>
+        <fgColor rgb="00EDE7FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -509,8 +509,8 @@
     <col width="54" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
@@ -519,7 +519,7 @@
     <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>画面を操作して確かめるケース。「画面」列にサイドバーからの経路・タブ・ボタン名・モーダル名まで書いてあるので、その順に開いて操作する。青＝どこを開くか、橙＝何を証拠に残すか、紫＝ヘルプ／受入条件との対応、黄＝当日の記入欄。判定はOK／NG／対象外から選ぶ。</t>
+          <t>画面を操作して確かめるケース。「画面」列にサイドバーからの経路・タブ・ボタン名・モーダル名まで書いてあるので、その順に開いて操作する。紫の2列で、この検証がヘルプページのどの記述と受入条件のどのIDを担保するかが分かる。青＝どこを開くか、橙＝何を証拠に残すか、黄＝当日の記入欄。</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>従業員を探す・削除する</t>
+          <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>従業員を探す・削除する</t>
+          <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>従業員を探す・削除する</t>
+          <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>従業員を探す・削除する</t>
+          <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>従業員を登録する</t>
+          <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>従業員を登録する</t>
+          <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>従業員を登録する</t>
+          <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>設定が保存できません</t>
+          <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>従業員の設定を変更する</t>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>給与改定を先の日付で予約する</t>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>給与改定を先の日付で予約する</t>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>従業員の設定を変更する</t>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>従業員を探す・削除する</t>
+          <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>数字が合わないとき</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>数字が合わないとき</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>数字が合わないとき</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>従業員の設定を変更する</t>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>データを出力する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>数字・締めについて</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>締めたあとに給与改定が決まったとき</t>
+          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>数字・締めについて</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>どなたが操作できますか</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>はじめて設定する</t>
+          <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>はじめて設定する</t>
+          <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>はじめて設定する</t>
+          <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>CSVの取り込みでエラーになります</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>CSVの取り込みでエラーになります</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>CSVの取り込みでエラーになります</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>CSVの列名がラクミーと違うとき</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>CSVの列名がラクミーと違うとき</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>CSVの列名がラクミーと違うとき</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>データを出力する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>データを出力する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>データを出力する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="I43" s="8" t="inlineStr">
         <is>
-          <t>データを出力する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>取り込んだ元データを確認する</t>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>取り込んだ元データを確認する</t>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>取り込んだ元データを確認する</t>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>すでにご利用中のお客様</t>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>すでにご利用中のお客様</t>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="I49" s="8" t="inlineStr">
         <is>
-          <t>すでにご利用中のお客様</t>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
       <c r="J49" s="8" t="inlineStr">
@@ -3561,8 +3561,8 @@
     <col width="54" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>毎月の人件費を確定する</t>
+          <t>（初期化のため対応なし）</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>人件費の計算方法</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>応援（ヘルプ）勤務がある場合</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>応援（ヘルプ）勤務がある場合</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>給与改定を先の日付で予約する</t>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>人件費の計算方法</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>数字・締めについて</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>人件費の計算方法</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>応援（ヘルプ）勤務がある場合</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -4213,8 +4213,8 @@
     <col width="54" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
@@ -4223,7 +4223,7 @@
     <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>検証を始める前の準備。上から順に実施する。★S-02（算式の確定）とS-03（サンプルデータの再作成）はゲート。</t>
+          <t>検証を始める前の準備。上から順に実施する。★S-02（算式の確定）とS-03（サンプルデータの再作成）はゲート。準備行のため受入条件・ヘルプページとの対応はない。</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,11 @@
           <t>メニューが出るか／モックが開くか</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>（準備のため対応なし）</t>
+        </is>
+      </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4382,7 +4386,11 @@
           <t>6件の算式が確定・文書化されているか</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>（準備のため対応なし）</t>
+        </is>
+      </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-12 AC-15</t>
@@ -4434,7 +4442,11 @@
           <t>算式で全行が再現できるか</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>（準備のため対応なし）</t>
+        </is>
+      </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
           <t>AC-10</t>
@@ -4490,7 +4502,11 @@
           <t>12名が一覧に出るか</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>（準備のため対応なし）</t>
+        </is>
+      </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4542,7 +4558,11 @@
           <t>履歴に予約中1件・実績5名が出るか</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>（準備のため対応なし）</t>
+        </is>
+      </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4590,7 +4610,11 @@
           <t>5ファイルがアップロードできる状態か</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>（準備のため対応なし）</t>
+        </is>
+      </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4638,7 +4662,11 @@
           <t>基礎時給と所定労働日数が確定しているか</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>（準備のため対応なし）</t>
+        </is>
+      </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4690,7 +4718,11 @@
           <t>2026-05が未締めか</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>（準備のため対応なし）</t>
+        </is>
+      </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4742,7 +4774,11 @@
           <t>移行前の値を控えたか</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>（準備のため対応なし）</t>
+        </is>
+      </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4790,7 +4826,11 @@
           <t>店長アカウントでログインできるか</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>（準備のため対応なし）</t>
+        </is>
+      </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4838,7 +4878,11 @@
           <t>移行を実行できる状態か</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>（準備のため対応なし）</t>
+        </is>
+      </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
           <t>-</t>
@@ -4879,8 +4923,8 @@
     <col width="54" customWidth="1" min="6" max="6"/>
     <col width="58" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
@@ -5004,7 +5048,7 @@
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>数字が合わないとき</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
@@ -5064,7 +5108,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>どなたが操作できますか</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
@@ -5124,7 +5168,7 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>設定が保存できません</t>
+          <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -5184,7 +5228,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>人件費の計算方法</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -5244,7 +5288,7 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>CSVの列名がラクミーと違うとき</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -5304,7 +5348,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>従業員の設定を変更する</t>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -7,16 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作系検証" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="計算系検証" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="準備" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="実装レビュー" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_使い方" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="操作系検証" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="計算系検証" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="準備" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="実装レビュー" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'操作系検証'!$A$2:$M$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'計算系検証'!$A$2:$M$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'準備'!$A$2:$M$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'実装レビュー'!$A$2:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'操作系検証'!$A$2:$M$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'計算系検証'!$A$2:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'準備'!$A$2:$M$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'実装レビュー'!$A$2:$M$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +35,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="0057606A"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11.5"/>
     </font>
     <font>
       <b val="1"/>
@@ -44,13 +49,22 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <color rgb="0057606A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDE7F5"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -104,33 +118,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -498,6 +517,524 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>検証プランの使い方</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>■ 1. 進め方</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="19" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>やること</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>使うシート</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>準備を上から実施する（★S-02・S-03はゲート）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>準備</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>操作系検証を上から実施し、実際の値と判定を記入する</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>操作系検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>C-000でデータを初期化してから計算系検証を実施する</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>計算系検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>エンジニア同席で実装レビューを実施する</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>検証IDごとの判定を、受入条件IDごとに集約する</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>（別ファイル）01_確認表.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>L0・L1の合否からリリース判断を出す</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>（別ファイル）01_確認表.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>■ 2. 1件をどう進めるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>列</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>見るタイミング</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>使い方</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>操作の前</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>サイドバーからの経路・タブ・ボタン名・モーダル名まで書いてある。この順に開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>操作・前提条件（入力値）</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>操作するとき</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>【前提】の準備行が済んでいるか確認してから【操作】を行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>確認ポイント</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>操作の直後</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>何を見るかの一言。まずここを見る</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>判定するとき</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>この内容と実際の画面を突き合わせる。数値で書いてあるものは数値で比べる</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>スクショ（撮るもの）</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>判定した後</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>ここに書いてある内容が写るように撮り、ファイル名の列の名前で保存する</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>実際の値・判定</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>最後</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>測った値を書き、OK／NG／対象外を選ぶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>■ 3. 紐付けの2列をどう使うか</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>受入条件は「リリースしてよいか」、ヘルプページは「顧客に案内したとおりか」を見るためのものです。役割が違うので、両方を確認します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>列</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>何が書いてあるか</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>検証中にどう使うか</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="94" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>対応受入条件</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>この検証が担保する受入条件のID（AC-16 など）</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>①判定に迷ったら、そのIDを受入条件表で引くと「合格基準（定量）」が書いてある（例 AC-16＝実績給与の差分0円）。②検証が終わったら、IDごとに判定を確認表へ集約する。ひとつのIDに複数の検証が紐づく場合は、すべてOKで初めてその条件が合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ヘルプページ該当箇所</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>この検証が担保するヘルプページの記述（大項目 ＞ 中項目）</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>ヘルプページは顧客への約束。NGだった場合、実装を直すのか、ヘルプの記述を直すのかを必ず決める。ヘルプ側を直す判断をしたときは、この列から該当箇所を開いて修正する</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>■ 4. 判定の入れ方</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>その後</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>期待値を満たした</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>次へ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>操作できたが期待値を満たさない</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>実装の修正か、期待値・ヘルプ記述の見直しかを決める。所見に実測値を残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>対象外</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>その環境では実施できない（機能が未実装など）</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>なぜ実施できないかを所見に残す。未実施のまま合格にはしない</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>■ 5. 色の意味</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>色</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>列</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>青</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>画面</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>どこを開くか</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>橙</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>スクショファイル名／スクショ（撮るもの）</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>何を証拠に残すか</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>ヘルプページ該当箇所／対応受入条件</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>何を担保する検証か</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>黄</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>実際の値／判定</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>当日の記入欄</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A12:C12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -517,81 +1054,81 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>画面を操作して確かめるケース。「画面」列にサイドバーからの経路・タブ・ボタン名・モーダル名まで書いてあるので、その順に開いて操作する。紫の2列で、この検証がヘルプページのどの記述と受入条件のどのIDを担保するかが分かる。青＝どこを開くか、橙＝何を証拠に残すか、黄＝当日の記入欄。</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>画面を操作して確かめるケース。使い方は「00_使い方」シートを参照。紫の2列で、この検証がヘルプページのどの記述と受入条件のどのIDを担保するかが分かる。</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>検証ID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>検証内容</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>操作・前提条件</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>スクショファイル名</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>スクショ（撮るもの）</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>確認ポイント</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>ヘルプページ該当箇所</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>対応受入条件</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>実際の値</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>計算根拠</t>
         </is>
       </c>
     </row>
     <row r="3" ht="94" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>T-L01</t>
         </is>
@@ -612,17 +1149,17 @@
           <t>12名が表示。12列（名前/従業員コード/所属店舗/ヘルプ先店舗/雇用区分/給与単位/単位給与額/交通費単位/単位交通費/所定労働時間/みなし残業時間/アクション）。雇用区分・給与単位が色分け。EMP-001はヘルプ先2バッジ、EMP-002は空。単位給与額が数値順にソート（1,000→…→410,000）。該当なしで「データはありません。」</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>T-L01.png</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>一覧全体（12行・12列・バッジの色・ソート矢印）と、フィルタで0件にしたときの「データはありません。」</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>従業員一覧 … 表の12列・雇用区分/給与単位のバッジ・列ヘッダーのソート・0件表示</t>
         </is>
@@ -632,18 +1169,18 @@
           <t>12列・バッジ・ソート・0件表示</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr"/>
+      <c r="K3" s="12" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr">
         <is>
           <t>移行：既存顧客が壊れない</t>
@@ -651,7 +1188,7 @@
       </c>
     </row>
     <row r="4" ht="49" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>T-L08</t>
         </is>
@@ -672,17 +1209,17 @@
           <t>渋谷店＝3名（EMP-001・002・011）、正社員＝6名、田中＝1名。2段目で対象データが切り替わる</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>T-L08.png</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>1段目と2段目の両方を適用した状態（絞り込み条件と結果件数が同時に写ること）</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>従業員一覧 … 1段目フィルタ（店舗/雇用区分/名前検索）と2段目フィルタ（月/取込データ）</t>
         </is>
@@ -692,18 +1229,18 @@
           <t>2段フィルタが効くか</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>AC-33</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr"/>
+      <c r="K4" s="12" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
           <t>画面：対象を探せる</t>
@@ -711,7 +1248,7 @@
       </c>
     </row>
     <row r="5" ht="64" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>T-L06</t>
         </is>
@@ -732,17 +1269,17 @@
           <t>5経路すべて到達（従業員登録／設定インポート／設定・実績エクスポート／設定取込データ／従業員詳細）。不通=0</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>T-L06.png</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>遷移先5画面の到達直後（従業員登録・設定インポート・エクスポート・設定取込データ・従業員詳細）</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>従業員一覧 … 右上ツールバー「従業員登録」「CSVインポート」「設定・実績エクスポート」／2段目「設定取込データへ」／行末の詳細アイコン</t>
         </is>
@@ -752,18 +1289,18 @@
           <t>5経路すべて到達するか</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>AC-30</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr">
         <is>
           <t>画面：操作が最後まで通る</t>
@@ -771,7 +1308,7 @@
       </c>
     </row>
     <row r="6" ht="49" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>T-L10</t>
         </is>
@@ -792,17 +1329,17 @@
           <t>（a）12名のまま削除されない （b）完了表示のあと11名になる</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>T-L10.png</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>削除の確認ダイアログ／キャンセル後の一覧／実行後の一覧（行が消えたこと）</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>従業員一覧 … 行末の削除アイコン → 確認ダイアログ</t>
         </is>
@@ -812,18 +1349,18 @@
           <t>キャンセルで消えない／実行で消えるか</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>AC-34</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr">
         <is>
           <t>データ保全：消える操作は確認を経る</t>
@@ -831,7 +1368,7 @@
       </c>
     </row>
     <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>T-R02</t>
         </is>
@@ -852,17 +1389,17 @@
           <t>13項目（名前/従業員コード/所属店舗/ヘルプ先店舗/雇用区分/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。¥320,000 と千区切り表示。適用日付は所定労働時間・みなし残業時間の下の行・初期値は当日</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>T-R02.png</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>登録フォーム全体（単位給与額に320,000と入れ、桁区切りが効いている状態）</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>従業員登録（従業員一覧 右上「従業員登録」から遷移）… 入力フォーム全体と通貨の桁区切り表示</t>
         </is>
@@ -872,18 +1409,18 @@
           <t>項目の過不足と桁区切り表示</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>AC-06</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr"/>
-      <c r="L7" s="9" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr"/>
+      <c r="L7" s="12" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr">
         <is>
           <t>原則①：当日・過去日は即時</t>
@@ -891,7 +1428,7 @@
       </c>
     </row>
     <row r="8" ht="49" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>T-R04</t>
         </is>
@@ -912,17 +1449,17 @@
           <t>選択した2店それぞれに交通費欄が出る／（a）必須バリデーションで登録できない／（b）新宿店の欄だけ消え、青山店の入力値は残る</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>T-R04.png</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>ヘルプ先2店選択でヘルプ先交通費欄が出た状態／1店外して欄が消えた状態の2枚</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>従業員登録 … ヘルプ先店舗の複数選択と、その下に自動表示されるヘルプ先交通費の入力欄</t>
         </is>
@@ -932,18 +1469,18 @@
           <t>交通費欄が自動で出る／消えるか</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>AC-15 AC-47</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr"/>
-      <c r="L8" s="9" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr"/>
+      <c r="L8" s="12" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr">
         <is>
           <t>原則③：交通費の帰属／原則③：交通費も働いた店舗の実費で</t>
@@ -951,7 +1488,7 @@
       </c>
     </row>
     <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>T-R07</t>
         </is>
@@ -972,17 +1509,17 @@
           <t>（a）完了表示のあと一覧へ戻り、登録前より1名増えている （b）一覧へ戻り件数は変わらない （c）従業員一覧／設定インポートへ遷移</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>T-R07.png</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>登録成功後の従業員一覧（新規行が見えること）とキャンセル後の一覧</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>従業員登録 … 下部「登録」「キャンセル」／ツールバー「従業員一覧へ」「CSVインポート」→ 従業員一覧</t>
         </is>
@@ -992,18 +1529,18 @@
           <t>登録される／されないの分岐</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>AC-06 AC-30</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr"/>
-      <c r="L9" s="9" t="inlineStr"/>
+      <c r="K9" s="12" t="inlineStr"/>
+      <c r="L9" s="12" t="inlineStr"/>
       <c r="M9" s="4" t="inlineStr">
         <is>
           <t>原則①：当日・過去日は即時／画面：操作が最後まで通る</t>
@@ -1011,7 +1548,7 @@
       </c>
     </row>
     <row r="10" ht="49" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>T-R10</t>
         </is>
@@ -1029,20 +1566,20 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>いずれの場合も登録できず、画面が遷移しない。どの項目が不足かが分かる表示になる</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+          <t>6項目それぞれで 登録=0件・画面遷移=0件（6回とも同じ）。不足している項目名が画面上に表示される</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>T-R10.png</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>必須未入力で「登録」を押した直後（エラー表示と、画面が遷移していないこと）</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>従業員登録 … 必須項目のバリデーション表示（画面に留まること）</t>
         </is>
@@ -1052,18 +1589,18 @@
           <t>必須未入力で保存も遷移もしないか</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>AC-43</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr"/>
-      <c r="L10" s="9" t="inlineStr"/>
+      <c r="K10" s="12" t="inlineStr"/>
+      <c r="L10" s="12" t="inlineStr"/>
       <c r="M10" s="4" t="inlineStr">
         <is>
           <t>データ保全：不完全な登録を作らない</t>
@@ -1071,7 +1608,7 @@
       </c>
     </row>
     <row r="11" ht="49" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>T-D01</t>
         </is>
@@ -1092,17 +1629,17 @@
           <t>基本情報／設定変更履歴／給与実績 が表示。基本情報は登録と同項目・同配置。履歴は14列（変更反映日時〜変更ソース の13項目＋操作）。2026-08-01行が「予約中」</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>T-D01.png</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>従業員詳細の全体（基本情報・設定変更履歴・給与実績の3セクションが分かる範囲）</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>従業員詳細（従業員一覧の詳細アイコンから遷移）… 基本情報／設定変更履歴／給与実績の3セクション</t>
         </is>
@@ -1112,18 +1649,18 @@
           <t>3セクションと履歴14列</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr"/>
-      <c r="L11" s="9" t="inlineStr"/>
+      <c r="K11" s="12" t="inlineStr"/>
+      <c r="L11" s="12" t="inlineStr"/>
       <c r="M11" s="4" t="inlineStr">
         <is>
           <t>原則①：過去は不変</t>
@@ -1131,7 +1668,7 @@
       </c>
     </row>
     <row r="12" ht="49" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>T-D04</t>
         </is>
@@ -1152,17 +1689,17 @@
           <t>「（日付）からの適用を予約しました」と表示。履歴に「予約中」が1行追加。一覧の単位給与額は320,000のまま</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>T-D04.png</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>保存直後のトースト「◯月◯日からの適用を予約しました」／履歴の「予約中」行／一覧の値が未変更であること の3枚</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>従業員詳細 … 基本情報の単位給与額と適用日付 → 下部「保存」→ 従業員一覧のトーストと一覧値</t>
         </is>
@@ -1172,18 +1709,18 @@
           <t>予約になり一覧の値が変わらないか</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>AC-04</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr"/>
-      <c r="L12" s="9" t="inlineStr"/>
+      <c r="K12" s="12" t="inlineStr"/>
+      <c r="L12" s="12" t="inlineStr"/>
       <c r="M12" s="4" t="inlineStr">
         <is>
           <t>原則①：未来日は予約になる</t>
@@ -1191,7 +1728,7 @@
       </c>
     </row>
     <row r="13" ht="79" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>T-D05</t>
         </is>
@@ -1212,17 +1749,17 @@
           <t>一覧が340,000に変わり、履歴が「適用中」、旧行が「過去」になる</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>T-D05.png</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>適用日を迎えた後の一覧の値と、履歴のステータスが「適用中」に変わった行</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>従業員詳細（予約を仕込む）→ 翌日の従業員一覧と設定変更履歴のステータス</t>
         </is>
@@ -1232,18 +1769,18 @@
           <t>適用日に自動で切り替わるか</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>AC-05</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr"/>
-      <c r="L13" s="9" t="inlineStr"/>
+      <c r="K13" s="12" t="inlineStr"/>
+      <c r="L13" s="12" t="inlineStr"/>
       <c r="M13" s="4" t="inlineStr">
         <is>
           <t>原則①：予約が自動で効く</t>
@@ -1251,7 +1788,7 @@
       </c>
     </row>
     <row r="14" ht="49" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>T-D06</t>
         </is>
@@ -1272,17 +1809,17 @@
           <t>「即時反映しました」と表示。一覧が290,000になる</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>T-D06.png</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>トースト「即時反映しました」と、一覧の値が290,000になった状態</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>従業員詳細 … 適用日付＝当日で「保存」→ 従業員一覧の値</t>
         </is>
@@ -1292,18 +1829,18 @@
           <t>即時反映され一覧の値が変わるか</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>AC-06</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr"/>
-      <c r="L14" s="9" t="inlineStr"/>
+      <c r="K14" s="12" t="inlineStr"/>
+      <c r="L14" s="12" t="inlineStr"/>
       <c r="M14" s="4" t="inlineStr">
         <is>
           <t>原則①：当日・過去日は即時</t>
@@ -1311,7 +1848,7 @@
       </c>
     </row>
     <row r="15" ht="49" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>T-D09</t>
         </is>
@@ -1332,17 +1869,17 @@
           <t>月次17列（年月〜深夜残業代＋交通費＋総支給額）／日次14列。個人向けに列を絞った構成で、人件費実績（26列/21列）とは別。フィルタで期間が絞られる。表示中の内容がBOM付きCSVで出力される</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>T-D09.png</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>月次タブ（概算／実績の両方）と日次タブ／出力したCSVをExcelで開いた画面</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>従業員詳細 → 給与実績セクション … 月次タブ（概算⇄実績の切替・年フィルタ）／日次タブ（月フィルタ）／各タブのCSVエクスポート</t>
         </is>
@@ -1352,18 +1889,18 @@
           <t>タブ切替とCSVの中身が変わるか</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>AC-35 AC-36</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr"/>
+      <c r="K15" s="12" t="inlineStr"/>
+      <c r="L15" s="12" t="inlineStr"/>
       <c r="M15" s="4" t="inlineStr">
         <is>
           <t>計算：個人単位でも同じ数字／入出力：画面の内容と一致</t>
@@ -1371,7 +1908,7 @@
       </c>
     </row>
     <row r="16" ht="49" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>T-D08</t>
         </is>
@@ -1392,17 +1929,17 @@
           <t>（a）削除されず件数が変わらない （b）確認のあと削除される （c）一覧へ戻る（保存されない）</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>T-D08.png</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>削除の確認モーダル／実行後の一覧（行が消えたこと）</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>従業員詳細 … 下部「従業員削除」→ 確認モーダル／「一覧へ戻る」→ 従業員一覧</t>
         </is>
@@ -1412,18 +1949,18 @@
           <t>キャンセルで消えない／実行で消えるか</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>AC-34 AC-30</t>
         </is>
       </c>
-      <c r="K16" s="9" t="inlineStr"/>
-      <c r="L16" s="9" t="inlineStr"/>
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="12" t="inlineStr"/>
       <c r="M16" s="4" t="inlineStr">
         <is>
           <t>データ保全：消える操作は確認を経る／画面：操作が最後まで通る</t>
@@ -1431,7 +1968,7 @@
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>T-H01</t>
         </is>
@@ -1452,17 +1989,17 @@
           <t>履歴が1行増える。既存行の値の差分＝0</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>T-H01.png</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>従業員設定履歴 … 変更前後の行（既存行が書き換わらないこと）</t>
         </is>
@@ -1472,18 +2009,18 @@
           <t>既存行が書き換わらないか</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr"/>
-      <c r="L17" s="9" t="inlineStr"/>
+      <c r="K17" s="12" t="inlineStr"/>
+      <c r="L17" s="12" t="inlineStr"/>
       <c r="M17" s="4" t="inlineStr">
         <is>
           <t>原則①：過去は不変</t>
@@ -1491,7 +2028,7 @@
       </c>
     </row>
     <row r="18" ht="49" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>T-H02</t>
         </is>
@@ -1512,17 +2049,17 @@
           <t>①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>T-H02.png</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>従業員設定履歴 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
         </is>
@@ -1532,18 +2069,18 @@
           <t>2つの日時が別で記録されるか</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>AC-08 AC-09</t>
         </is>
       </c>
-      <c r="K18" s="9" t="inlineStr"/>
-      <c r="L18" s="9" t="inlineStr"/>
+      <c r="K18" s="12" t="inlineStr"/>
+      <c r="L18" s="12" t="inlineStr"/>
       <c r="M18" s="4" t="inlineStr">
         <is>
           <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
@@ -1551,7 +2088,7 @@
       </c>
     </row>
     <row r="19" ht="64" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>T-H04</t>
         </is>
@@ -1572,17 +2109,17 @@
           <t>店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>T-H04.png</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>従業員設定履歴 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
         </is>
@@ -1592,18 +2129,18 @@
           <t>絞り込み後の行だけ出力されるか</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>AC-33 AC-36 AC-30</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr"/>
-      <c r="L19" s="9" t="inlineStr"/>
+      <c r="K19" s="12" t="inlineStr"/>
+      <c r="L19" s="12" t="inlineStr"/>
       <c r="M19" s="4" t="inlineStr">
         <is>
           <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
@@ -1611,7 +2148,7 @@
       </c>
     </row>
     <row r="20" ht="109" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>T-A02</t>
         </is>
@@ -1632,17 +2169,17 @@
           <t>全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>T-A02.png</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
         </is>
@@ -1652,18 +2189,18 @@
           <t>モード切替で列が増減するか</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>AC-10 AC-31</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr"/>
-      <c r="L20" s="9" t="inlineStr"/>
+      <c r="K20" s="12" t="inlineStr"/>
+      <c r="L20" s="12" t="inlineStr"/>
       <c r="M20" s="4" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額／画面：状態が漏れない</t>
@@ -1671,7 +2208,7 @@
       </c>
     </row>
     <row r="21" ht="49" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>T-A09</t>
         </is>
@@ -1692,17 +2229,17 @@
           <t>モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>T-A09.png</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>設定編集モーダル（項目が見える状態）／更新保存後の人件費実績／従業員詳細の設定変更履歴に行が増えたこと</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 人件費実績／確認は従業員詳細の設定変更履歴</t>
         </is>
@@ -1712,18 +2249,18 @@
           <t>モーダル編集でも履歴が残るか</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>AC-49</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr"/>
-      <c r="L21" s="9" t="inlineStr"/>
+      <c r="K21" s="12" t="inlineStr"/>
+      <c r="L21" s="12" t="inlineStr"/>
       <c r="M21" s="4" t="inlineStr">
         <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
@@ -1731,7 +2268,7 @@
       </c>
     </row>
     <row r="22" ht="94" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>T-A05</t>
         </is>
@@ -1752,17 +2289,17 @@
           <t>全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>T-A05.png</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
         </is>
@@ -1772,18 +2309,18 @@
           <t>日別に概算モードが無いか</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr"/>
-      <c r="L22" s="9" t="inlineStr"/>
+      <c r="K22" s="12" t="inlineStr"/>
+      <c r="L22" s="12" t="inlineStr"/>
       <c r="M22" s="4" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額</t>
@@ -1791,7 +2328,7 @@
       </c>
     </row>
     <row r="23" ht="49" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>T-A07</t>
         </is>
@@ -1809,20 +2346,20 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>表示中のタブ・モード・フィルタの内容が出力される。日本語が文字化けしない</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
+          <t>出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>T-A07.png</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>人件費実績 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
         </is>
@@ -1832,18 +2369,18 @@
           <t>表示中の内容が出力されるか</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>AC-36</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr"/>
-      <c r="L23" s="9" t="inlineStr"/>
+      <c r="K23" s="12" t="inlineStr"/>
+      <c r="L23" s="12" t="inlineStr"/>
       <c r="M23" s="4" t="inlineStr">
         <is>
           <t>入出力：画面の内容と一致</t>
@@ -1851,7 +2388,7 @@
       </c>
     </row>
     <row r="24" ht="49" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>T-A08</t>
         </is>
@@ -1872,17 +2409,17 @@
           <t>「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>T-A08.png</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
         </is>
@@ -1892,18 +2429,18 @@
           <t>進捗が出て他操作を受け付けないか</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>AC-48</t>
         </is>
       </c>
-      <c r="K24" s="9" t="inlineStr"/>
-      <c r="L24" s="9" t="inlineStr"/>
+      <c r="K24" s="12" t="inlineStr"/>
+      <c r="L24" s="12" t="inlineStr"/>
       <c r="M24" s="4" t="inlineStr">
         <is>
           <t>入出力：勤怠実績を取り込める</t>
@@ -1911,7 +2448,7 @@
       </c>
     </row>
     <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>T-S01</t>
         </is>
@@ -1932,17 +2469,17 @@
           <t>月別のみ「2026-05 締め」が表示。日別には表示されない</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>T-S01.png</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>人件費実績 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
         </is>
@@ -1952,18 +2489,18 @@
           <t>締めが月別タブにだけ出るか</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>AC-18</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr"/>
-      <c r="L25" s="9" t="inlineStr"/>
+      <c r="K25" s="12" t="inlineStr"/>
+      <c r="L25" s="12" t="inlineStr"/>
       <c r="M25" s="4" t="inlineStr">
         <is>
           <t>原則②：締めの単位は月</t>
@@ -1971,7 +2508,7 @@
       </c>
     </row>
     <row r="26" ht="49" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>T-S03</t>
         </is>
@@ -1992,17 +2529,17 @@
           <t>「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>T-S03.png</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
         </is>
@@ -2012,18 +2549,18 @@
           <t>確認モーダルを経て締まるか</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>AC-16 AC-19 AC-32</t>
         </is>
       </c>
-      <c r="K26" s="9" t="inlineStr"/>
-      <c r="L26" s="9" t="inlineStr"/>
+      <c r="K26" s="12" t="inlineStr"/>
+      <c r="L26" s="12" t="inlineStr"/>
       <c r="M26" s="4" t="inlineStr">
         <is>
           <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
@@ -2031,7 +2568,7 @@
       </c>
     </row>
     <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>T-S04</t>
         </is>
@@ -2052,17 +2589,17 @@
           <t>編集できない（または反映されない）</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>T-S04.png</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
         </is>
@@ -2072,18 +2609,18 @@
           <t>締め後に金額が動かないか</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="11" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr">
         <is>
           <t>AC-16</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr"/>
-      <c r="L27" s="9" t="inlineStr"/>
+      <c r="K27" s="12" t="inlineStr"/>
+      <c r="L27" s="12" t="inlineStr"/>
       <c r="M27" s="4" t="inlineStr">
         <is>
           <t>原則②：締めたら動かない</t>
@@ -2091,7 +2628,7 @@
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>T-D07</t>
         </is>
@@ -2112,17 +2649,17 @@
           <t>締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>T-D07.png</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
         </is>
@@ -2132,18 +2669,18 @@
           <t>警告が出て反映されないか</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="J28" s="11" t="inlineStr">
         <is>
           <t>AC-20</t>
         </is>
       </c>
-      <c r="K28" s="9" t="inlineStr"/>
-      <c r="L28" s="9" t="inlineStr"/>
+      <c r="K28" s="12" t="inlineStr"/>
+      <c r="L28" s="12" t="inlineStr"/>
       <c r="M28" s="4" t="inlineStr">
         <is>
           <t>原則②：遡及は黙って捨てない</t>
@@ -2151,7 +2688,7 @@
       </c>
     </row>
     <row r="29" ht="49" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>T-S05</t>
         </is>
@@ -2172,17 +2709,17 @@
           <t>「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>T-S05.png</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
         <is>
           <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
         </is>
@@ -2192,18 +2729,18 @@
           <t>解除で再計算されるか</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
-      <c r="J29" s="8" t="inlineStr">
+      <c r="J29" s="11" t="inlineStr">
         <is>
           <t>AC-19</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr"/>
-      <c r="L29" s="9" t="inlineStr"/>
+      <c r="K29" s="12" t="inlineStr"/>
+      <c r="L29" s="12" t="inlineStr"/>
       <c r="M29" s="4" t="inlineStr">
         <is>
           <t>原則②：確定操作は確認を経る</t>
@@ -2211,7 +2748,7 @@
       </c>
     </row>
     <row r="30" ht="49" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>T-S07</t>
         </is>
@@ -2232,17 +2769,17 @@
           <t>締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>T-S07.png</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>店長スコープでの人件費実績（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
         </is>
@@ -2252,18 +2789,18 @@
           <t>店長が締められないか</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
-      <c r="J30" s="8" t="inlineStr">
+      <c r="J30" s="11" t="inlineStr">
         <is>
           <t>AC-41</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr"/>
-      <c r="L30" s="9" t="inlineStr"/>
+      <c r="K30" s="12" t="inlineStr"/>
+      <c r="L30" s="12" t="inlineStr"/>
       <c r="M30" s="4" t="inlineStr">
         <is>
           <t>原則②：締めは会社スコープのみ</t>
@@ -2271,7 +2808,7 @@
       </c>
     </row>
     <row r="31" ht="64" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>T-I02</t>
         </is>
@@ -2292,17 +2829,17 @@
           <t>従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>T-I02.png</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
         <is>
           <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
         </is>
@@ -2312,18 +2849,18 @@
           <t>テンプレートの列とBOM</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr">
+      <c r="J31" s="11" t="inlineStr">
         <is>
           <t>AC-21 AC-30</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr"/>
-      <c r="L31" s="9" t="inlineStr"/>
+      <c r="K31" s="12" t="inlineStr"/>
+      <c r="L31" s="12" t="inlineStr"/>
       <c r="M31" s="4" t="inlineStr">
         <is>
           <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
@@ -2331,7 +2868,7 @@
       </c>
     </row>
     <row r="32" ht="49" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>T-I03</t>
         </is>
@@ -2352,17 +2889,17 @@
           <t>07は3行すべて取り込まれ、EMP-001=340,000・EMP-005=360,000に更新、EMP-013は新規追加。10は給与設定（ヘルプ先交通費 S02:700;S03:900 の記法を含む）が反映される</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>T-I03.png</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
         <is>
           <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
         </is>
@@ -2372,18 +2909,18 @@
           <t>3行が更新・追加されるか</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
-      <c r="J32" s="8" t="inlineStr">
+      <c r="J32" s="11" t="inlineStr">
         <is>
           <t>AC-21</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr"/>
-      <c r="L32" s="9" t="inlineStr"/>
+      <c r="K32" s="12" t="inlineStr"/>
+      <c r="L32" s="12" t="inlineStr"/>
       <c r="M32" s="4" t="inlineStr">
         <is>
           <t>入出力：導入を止めない</t>
@@ -2391,7 +2928,7 @@
       </c>
     </row>
     <row r="33" ht="49" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>T-I04</t>
         </is>
@@ -2412,17 +2949,17 @@
           <t>3行すべて取り込まれる（EMP-003=1,250・EMP-010=1,300・EMP-014は新規）</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>T-I04.png</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
         </is>
@@ -2432,18 +2969,18 @@
           <t>表記ゆれを吸収できるか</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="J33" s="11" t="inlineStr">
         <is>
           <t>AC-22</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr"/>
-      <c r="L33" s="9" t="inlineStr"/>
+      <c r="K33" s="12" t="inlineStr"/>
+      <c r="L33" s="12" t="inlineStr"/>
       <c r="M33" s="4" t="inlineStr">
         <is>
           <t>入出力：表記ゆれを吸収</t>
@@ -2451,7 +2988,7 @@
       </c>
     </row>
     <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>T-I05</t>
         </is>
@@ -2472,17 +3009,17 @@
           <t>4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>T-I05.png</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
         <is>
           <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
         </is>
@@ -2492,18 +3029,18 @@
           <t>4種の異常を行ごとに検出するか</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="11" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
-      <c r="J34" s="8" t="inlineStr">
+      <c r="J34" s="11" t="inlineStr">
         <is>
           <t>AC-23</t>
         </is>
       </c>
-      <c r="K34" s="9" t="inlineStr"/>
-      <c r="L34" s="9" t="inlineStr"/>
+      <c r="K34" s="12" t="inlineStr"/>
+      <c r="L34" s="12" t="inlineStr"/>
       <c r="M34" s="4" t="inlineStr">
         <is>
           <t>データ保全：不正値を入れない</t>
@@ -2511,7 +3048,7 @@
       </c>
     </row>
     <row r="35" ht="49" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>T-I17</t>
         </is>
@@ -2532,17 +3069,17 @@
           <t>（a）2回目は更新となり件数が増えない （b）重複行がエラーとして検出される（両方が登録されない）</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>T-I17.png</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
         </is>
@@ -2552,26 +3089,26 @@
           <t>二重登録されないか</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
-      <c r="J35" s="8" t="inlineStr">
+      <c r="J35" s="11" t="inlineStr">
         <is>
           <t>AC-40</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr"/>
-      <c r="L35" s="9" t="inlineStr"/>
+      <c r="K35" s="12" t="inlineStr"/>
+      <c r="L35" s="12" t="inlineStr"/>
       <c r="M35" s="4" t="inlineStr">
         <is>
           <t>データ保全：二重登録を防ぐ</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="49" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>T-I18</t>
         </is>
@@ -2589,20 +3126,20 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>部分的に登録された行が残らない（全体拒否）か、正常行のみ登録され異常行が明示される（行単位）。どちらであっても、中途半端な状態が残らない</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
+          <t>中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>T-I18.png</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録されていないこと）</t>
         </is>
@@ -2612,18 +3149,18 @@
           <t>部分登録が残らないか</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="I36" s="11" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
-      <c r="J36" s="8" t="inlineStr">
+      <c r="J36" s="11" t="inlineStr">
         <is>
           <t>AC-42</t>
         </is>
       </c>
-      <c r="K36" s="9" t="inlineStr"/>
-      <c r="L36" s="9" t="inlineStr"/>
+      <c r="K36" s="12" t="inlineStr"/>
+      <c r="L36" s="12" t="inlineStr"/>
       <c r="M36" s="4" t="inlineStr">
         <is>
           <t>データ保全：中途半端に残さない</t>
@@ -2631,7 +3168,7 @@
       </c>
     </row>
     <row r="37" ht="49" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>T-I11</t>
         </is>
@@ -2652,17 +3189,17 @@
           <t>余計な行が無視され、3行が正しく取り込まれる</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>T-I11.png</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
         </is>
@@ -2672,18 +3209,18 @@
           <t>説明行を飛ばして取り込めるか</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="I37" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="J37" s="8" t="inlineStr">
+      <c r="J37" s="11" t="inlineStr">
         <is>
           <t>AC-37</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr"/>
-      <c r="L37" s="9" t="inlineStr"/>
+      <c r="K37" s="12" t="inlineStr"/>
+      <c r="L37" s="12" t="inlineStr"/>
       <c r="M37" s="4" t="inlineStr">
         <is>
           <t>入出力：現場のCSVをそのまま使える</t>
@@ -2691,7 +3228,7 @@
       </c>
     </row>
     <row r="38" ht="79" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>T-I09</t>
         </is>
@@ -2712,17 +3249,17 @@
           <t>テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>T-I09.png</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>設定インポート → ツールバー「列マッピングテンプレート管理」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
         </is>
@@ -2732,18 +3269,18 @@
           <t>テンプレの登録・編集・削除と往復</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="J38" s="8" t="inlineStr">
+      <c r="J38" s="11" t="inlineStr">
         <is>
           <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
-      <c r="K38" s="9" t="inlineStr"/>
-      <c r="L38" s="9" t="inlineStr"/>
+      <c r="K38" s="12" t="inlineStr"/>
+      <c r="L38" s="12" t="inlineStr"/>
       <c r="M38" s="4" t="inlineStr">
         <is>
           <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
@@ -2751,7 +3288,7 @@
       </c>
     </row>
     <row r="39" ht="79" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>T-I19</t>
         </is>
@@ -2772,17 +3309,17 @@
           <t>テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>T-I19.png</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
         <is>
           <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
         </is>
@@ -2792,18 +3329,18 @@
           <t>一括登録と10MB超の扱い</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="J39" s="8" t="inlineStr">
+      <c r="J39" s="11" t="inlineStr">
         <is>
           <t>AC-51</t>
         </is>
       </c>
-      <c r="K39" s="9" t="inlineStr"/>
-      <c r="L39" s="9" t="inlineStr"/>
+      <c r="K39" s="12" t="inlineStr"/>
+      <c r="L39" s="12" t="inlineStr"/>
       <c r="M39" s="4" t="inlineStr">
         <is>
           <t>入出力：マッピングの一括運用</t>
@@ -2811,7 +3348,7 @@
       </c>
     </row>
     <row r="40" ht="79" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>T-E04</t>
         </is>
@@ -2832,17 +3369,17 @@
           <t>専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>T-E04.png</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F40" s="9" t="inlineStr">
         <is>
           <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
         </is>
@@ -2852,18 +3389,18 @@
           <t>選んだ項目だけ・対象数だけ出るか</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="I40" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="J40" s="8" t="inlineStr">
+      <c r="J40" s="11" t="inlineStr">
         <is>
           <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
-      <c r="K40" s="9" t="inlineStr"/>
-      <c r="L40" s="9" t="inlineStr"/>
+      <c r="K40" s="12" t="inlineStr"/>
+      <c r="L40" s="12" t="inlineStr"/>
       <c r="M40" s="4" t="inlineStr">
         <is>
           <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
@@ -2871,7 +3408,7 @@
       </c>
     </row>
     <row r="41" ht="64" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>T-E09</t>
         </is>
@@ -2892,17 +3429,17 @@
           <t>実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>T-E09.png</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
         </is>
@@ -2912,18 +3449,18 @@
           <t>実績と同時選択のファイル数</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="I41" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="J41" s="11" t="inlineStr">
         <is>
           <t>AC-25</t>
         </is>
       </c>
-      <c r="K41" s="9" t="inlineStr"/>
-      <c r="L41" s="9" t="inlineStr"/>
+      <c r="K41" s="12" t="inlineStr"/>
+      <c r="L41" s="12" t="inlineStr"/>
       <c r="M41" s="4" t="inlineStr">
         <is>
           <t>入出力：渡し先に合わせて出せる</t>
@@ -2931,7 +3468,7 @@
       </c>
     </row>
     <row r="42" ht="49" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>T-E07</t>
         </is>
@@ -2952,17 +3489,17 @@
           <t>警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>T-E07.png</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
         <is>
           <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
         </is>
@@ -2972,18 +3509,18 @@
           <t>未選択で出力されないか</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="I42" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
+      <c r="J42" s="11" t="inlineStr">
         <is>
           <t>AC-27</t>
         </is>
       </c>
-      <c r="K42" s="9" t="inlineStr"/>
-      <c r="L42" s="9" t="inlineStr"/>
+      <c r="K42" s="12" t="inlineStr"/>
+      <c r="L42" s="12" t="inlineStr"/>
       <c r="M42" s="4" t="inlineStr">
         <is>
           <t>入出力：空振りを防ぐ</t>
@@ -2991,7 +3528,7 @@
       </c>
     </row>
     <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>T-E08</t>
         </is>
@@ -3012,17 +3549,17 @@
           <t>日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>T-E08.png</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr">
         <is>
           <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G43" s="10" t="inlineStr">
         <is>
           <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
         </is>
@@ -3032,18 +3569,18 @@
           <t>Excelで文字化けしないか</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I43" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="J43" s="8" t="inlineStr">
+      <c r="J43" s="11" t="inlineStr">
         <is>
           <t>AC-28</t>
         </is>
       </c>
-      <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr"/>
+      <c r="K43" s="12" t="inlineStr"/>
+      <c r="L43" s="12" t="inlineStr"/>
       <c r="M43" s="4" t="inlineStr">
         <is>
           <t>入出力：そのまま提出できる</t>
@@ -3051,7 +3588,7 @@
       </c>
     </row>
     <row r="44" ht="49" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>T-N01</t>
         </is>
@@ -3072,17 +3609,17 @@
           <t>設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>T-N01.png</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F44" s="9" t="inlineStr">
         <is>
           <t>設定取込データと実績取込データの一覧＋各タブ（計4枚）</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>設定取込データ（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績取込データ … 月別データ／日別データタブ</t>
         </is>
@@ -3092,18 +3629,18 @@
           <t>元データとタブの構成</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="I44" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
-      <c r="J44" s="8" t="inlineStr">
+      <c r="J44" s="11" t="inlineStr">
         <is>
           <t>AC-39</t>
         </is>
       </c>
-      <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
+      <c r="K44" s="12" t="inlineStr"/>
+      <c r="L44" s="12" t="inlineStr"/>
       <c r="M44" s="4" t="inlineStr">
         <is>
           <t>入出力：原因を追える</t>
@@ -3111,7 +3648,7 @@
       </c>
     </row>
     <row r="45" ht="64" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>T-N02</t>
         </is>
@@ -3132,17 +3669,17 @@
           <t>プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>T-N02.png</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" s="9" t="inlineStr">
         <is>
           <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>設定取込データ／実績取込データ … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
         </is>
@@ -3152,18 +3689,18 @@
           <t>差分がdata/16・17と一致するか</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="I45" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="J45" s="11" t="inlineStr">
         <is>
           <t>AC-50</t>
         </is>
       </c>
-      <c r="K45" s="9" t="inlineStr"/>
-      <c r="L45" s="9" t="inlineStr"/>
+      <c r="K45" s="12" t="inlineStr"/>
+      <c r="L45" s="12" t="inlineStr"/>
       <c r="M45" s="4" t="inlineStr">
         <is>
           <t>データ保全：取り込む前に気づける</t>
@@ -3171,7 +3708,7 @@
       </c>
     </row>
     <row r="46" ht="49" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>T-N03</t>
         </is>
@@ -3192,17 +3729,17 @@
           <t>2経路とも到達する（不通=0）</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>T-N03.png</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F46" s="9" t="inlineStr">
         <is>
           <t>人件費実績→実績取込データ／実績取込データ→人件費実績 の到達直後（2枚）</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 「実績取込データへ」／実績取込データ → 「人件費実績へ」（相互導線）</t>
         </is>
@@ -3212,18 +3749,18 @@
           <t>2経路とも到達するか</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="I46" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
-      <c r="J46" s="8" t="inlineStr">
+      <c r="J46" s="11" t="inlineStr">
         <is>
           <t>AC-30</t>
         </is>
       </c>
-      <c r="K46" s="9" t="inlineStr"/>
-      <c r="L46" s="9" t="inlineStr"/>
+      <c r="K46" s="12" t="inlineStr"/>
+      <c r="L46" s="12" t="inlineStr"/>
       <c r="M46" s="4" t="inlineStr">
         <is>
           <t>画面：操作が最後まで通る</t>
@@ -3231,7 +3768,7 @@
       </c>
     </row>
     <row r="47" ht="49" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>T-Z01</t>
         </is>
@@ -3252,17 +3789,17 @@
           <t>件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>T-Z01.png</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
         </is>
@@ -3272,18 +3809,18 @@
           <t>移行前後で差分0件か</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="I47" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="J47" s="11" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
-      <c r="K47" s="9" t="inlineStr"/>
-      <c r="L47" s="9" t="inlineStr"/>
+      <c r="K47" s="12" t="inlineStr"/>
+      <c r="L47" s="12" t="inlineStr"/>
       <c r="M47" s="4" t="inlineStr">
         <is>
           <t>移行：既存顧客が壊れない</t>
@@ -3291,7 +3828,7 @@
       </c>
     </row>
     <row r="48" ht="49" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>T-Z02</t>
         </is>
@@ -3312,17 +3849,17 @@
           <t>適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>T-Z02.png</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F48" s="9" t="inlineStr">
         <is>
           <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>従業員詳細 → 設定変更履歴／従業員設定履歴 … 適用日付の空欄</t>
         </is>
@@ -3332,18 +3869,18 @@
           <t>適用日付の空欄が0件か</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="I48" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
-      <c r="J48" s="8" t="inlineStr">
+      <c r="J48" s="11" t="inlineStr">
         <is>
           <t>AC-02</t>
         </is>
       </c>
-      <c r="K48" s="9" t="inlineStr"/>
-      <c r="L48" s="9" t="inlineStr"/>
+      <c r="K48" s="12" t="inlineStr"/>
+      <c r="L48" s="12" t="inlineStr"/>
       <c r="M48" s="4" t="inlineStr">
         <is>
           <t>移行：履歴の起点を作る</t>
@@ -3351,7 +3888,7 @@
       </c>
     </row>
     <row r="49" ht="49" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>T-Z03</t>
         </is>
@@ -3372,17 +3909,17 @@
           <t>3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>T-Z03.png</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F49" s="9" t="inlineStr">
         <is>
           <t>移行前後の人件費実績 月別実績（直近3か月・金額が同じであること）</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G49" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ … 移行前後の直近3か月</t>
         </is>
@@ -3392,18 +3929,18 @@
           <t>過去3か月の金額が変わらないか</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="I49" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
-      <c r="J49" s="8" t="inlineStr">
+      <c r="J49" s="11" t="inlineStr">
         <is>
           <t>AC-03</t>
         </is>
       </c>
-      <c r="K49" s="9" t="inlineStr"/>
-      <c r="L49" s="9" t="inlineStr"/>
+      <c r="K49" s="12" t="inlineStr"/>
+      <c r="L49" s="12" t="inlineStr"/>
       <c r="M49" s="4" t="inlineStr">
         <is>
           <t>移行：過去が動かない</t>
@@ -3411,7 +3948,7 @@
       </c>
     </row>
     <row r="50" ht="49" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>T-Z04</t>
         </is>
@@ -3432,17 +3969,17 @@
           <t>閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>T-Z04.png</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F50" s="9" t="inlineStr">
         <is>
           <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
         </is>
       </c>
-      <c r="G50" s="7" t="inlineStr">
+      <c r="G50" s="10" t="inlineStr">
         <is>
           <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
         </is>
@@ -3452,18 +3989,18 @@
           <t>PC・モバイルとも開くか</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
+      <c r="I50" s="11" t="inlineStr">
         <is>
           <t>（ヘルプ記載なし・画面構成）</t>
         </is>
       </c>
-      <c r="J50" s="8" t="inlineStr">
+      <c r="J50" s="11" t="inlineStr">
         <is>
           <t>AC-29</t>
         </is>
       </c>
-      <c r="K50" s="9" t="inlineStr"/>
-      <c r="L50" s="9" t="inlineStr"/>
+      <c r="K50" s="12" t="inlineStr"/>
+      <c r="L50" s="12" t="inlineStr"/>
       <c r="M50" s="4" t="inlineStr">
         <is>
           <t>画面：たどり着ける</t>
@@ -3471,7 +4008,7 @@
       </c>
     </row>
     <row r="51" ht="49" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>T-Z05</t>
         </is>
@@ -3492,17 +4029,17 @@
           <t>すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>T-Z05.png</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G51" s="10" t="inlineStr">
         <is>
           <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
         </is>
@@ -3512,18 +4049,18 @@
           <t>75本の遷移と表示規則</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="I51" s="11" t="inlineStr">
         <is>
           <t>（ヘルプ記載なし・遷移網羅）</t>
         </is>
       </c>
-      <c r="J51" s="8" t="inlineStr">
+      <c r="J51" s="11" t="inlineStr">
         <is>
           <t>AC-30 AC-01</t>
         </is>
       </c>
-      <c r="K51" s="9" t="inlineStr"/>
-      <c r="L51" s="9" t="inlineStr"/>
+      <c r="K51" s="12" t="inlineStr"/>
+      <c r="L51" s="12" t="inlineStr"/>
       <c r="M51" s="4" t="inlineStr">
         <is>
           <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
@@ -3544,7 +4081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3569,81 +4106,81 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>金額の算式を検算するケース。先に「準備」シートのC-000（データの初期化）を実施する。計算根拠の列に算式と、その根拠となる判断を記載している。</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>検証ID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>検証内容</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>入力値</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>スクショファイル名</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>スクショ（撮るもの）</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>確認ポイント</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>ヘルプページ該当箇所</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>対応受入条件</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>実際の値</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>計算根拠</t>
         </is>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>C-000</t>
         </is>
@@ -3664,17 +4201,17 @@
           <t>従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>C-000.png</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>初期化後の従業員一覧（12名）と人件費実績（未締め・S-05時点の金額）</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未締めに戻す）</t>
         </is>
@@ -3684,18 +4221,18 @@
           <t>S-05時点の値に戻ったか</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>（初期化のため対応なし）</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr"/>
+      <c r="K3" s="12" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr">
         <is>
           <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
@@ -3703,7 +4240,7 @@
       </c>
     </row>
     <row r="4" ht="64" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>C-001</t>
         </is>
@@ -3724,17 +4261,17 @@
           <t>EMP-002＝285,250（概算280,000＋深夜残業代5,250＝1,750×1.5×2h）／EMP-007＝311,250（概算300,000＋深夜残業代11,250＝1,875×1.5×4h）。いずれも差分0円</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>C-001.png</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
         </is>
@@ -3744,18 +4281,18 @@
           <t>概算＋深夜＝実績給与か</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr"/>
+      <c r="K4" s="12" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
           <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・暫定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
@@ -3763,7 +4300,7 @@
       </c>
     </row>
     <row r="5" ht="79" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>C-003</t>
         </is>
@@ -3784,17 +4321,17 @@
           <t>EMP-001＝338,000（概算320,000＋深夜18,000＝2,000×1.5×6h）／EMP-005＝382,812（概算350,000＋深夜32,812＝2,187×1.5×10h）／EMP-003＝144,000（深夜なし）。ヘルプ人件費は実績給与×ヘルプ時間÷総労働時間で按分し応援先へ振替（EMP-001＝43,232／EMP-003＝24,000／EMP-005＝72,424）</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>C-003.png</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
         </is>
@@ -3804,18 +4341,18 @@
           <t>ヘルプ人件費が按分で振替されるか</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>AC-10 AC-14</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr">
         <is>
           <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
@@ -3823,7 +4360,7 @@
       </c>
     </row>
     <row r="6" ht="49" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>C-005</t>
         </is>
@@ -3844,17 +4381,17 @@
           <t>店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>C-005.png</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
         </is>
@@ -3864,18 +4401,18 @@
           <t>店舗別合計＝全社（差0円）か</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>AC-11</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr">
         <is>
           <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
@@ -3883,7 +4420,7 @@
       </c>
     </row>
     <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>C-006</t>
         </is>
@@ -3904,17 +4441,17 @@
           <t>6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>C-006.png</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
         </is>
@@ -3924,18 +4461,18 @@
           <t>所定労働日割になっているか</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>AC-12 AC-04</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr"/>
-      <c r="L7" s="9" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr"/>
+      <c r="L7" s="12" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr">
         <is>
           <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
@@ -3943,7 +4480,7 @@
       </c>
     </row>
     <row r="8" ht="49" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>C-011</t>
         </is>
@@ -3964,17 +4501,17 @@
           <t>5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>C-011.png</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
         </is>
@@ -3984,18 +4521,18 @@
           <t>時給者の概算と月中改定</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>AC-13</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr"/>
-      <c r="L8" s="9" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr"/>
+      <c r="L8" s="12" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr">
         <is>
           <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
@@ -4003,7 +4540,7 @@
       </c>
     </row>
     <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>C-008</t>
         </is>
@@ -4024,17 +4561,17 @@
           <t>（a）5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>C-008.png</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
         </is>
@@ -4044,18 +4581,18 @@
           <t>締め前後で差0円・解除後に再計算</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>AC-16 AC-17</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr"/>
-      <c r="L9" s="9" t="inlineStr"/>
+      <c r="K9" s="12" t="inlineStr"/>
+      <c r="L9" s="12" t="inlineStr"/>
       <c r="M9" s="4" t="inlineStr">
         <is>
           <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
@@ -4063,7 +4600,7 @@
       </c>
     </row>
     <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>C-013</t>
         </is>
@@ -4084,17 +4621,17 @@
           <t>判断7（暫定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。5/8のヘルプ人件費＝実績給与338,000×11h÷総労働172h＝21,616円で、計上先はS02。みなし労働時間差分＝172−(160＋20)＝−8h（未達はマイナス表示・減額なし＝判断8）</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>C-013.png</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
         </is>
@@ -4104,18 +4641,18 @@
           <t>深夜1.5倍とヘルプの按分単価</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>AC-10 AC-14</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr"/>
-      <c r="L10" s="9" t="inlineStr"/>
+      <c r="K10" s="12" t="inlineStr"/>
+      <c r="L10" s="12" t="inlineStr"/>
       <c r="M10" s="4" t="inlineStr">
         <is>
           <t>深夜残業代＝基礎時給×1.5（判断7・暫定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・暫定）</t>
@@ -4123,7 +4660,7 @@
       </c>
     </row>
     <row r="11" ht="49" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>C-017</t>
         </is>
@@ -4144,17 +4681,17 @@
           <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>C-017.png</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
         </is>
@@ -4164,18 +4701,18 @@
           <t>交通費が給与と別費目か</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>AC-15</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr"/>
-      <c r="L11" s="9" t="inlineStr"/>
+      <c r="K11" s="12" t="inlineStr"/>
+      <c r="L11" s="12" t="inlineStr"/>
       <c r="M11" s="4" t="inlineStr">
         <is>
           <t>交通費は給与と別の独立費目（判断6・確定）。通勤交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
@@ -4196,7 +4733,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4221,81 +4758,81 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>検証を始める前の準備。上から順に実施する。★S-02（算式の確定）とS-03（サンプルデータの再作成）はゲート。準備行のため受入条件・ヘルプページとの対応はない。</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>検証ID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>検証内容</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>操作・前提条件</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>スクショファイル名</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>スクショ（撮るもの）</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>確認ポイント</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>ヘルプページ該当箇所</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>対応受入条件</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>実際の値</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>計算根拠</t>
         </is>
       </c>
     </row>
     <row r="3" ht="49" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
@@ -4315,17 +4852,17 @@
           <t>サイドバーに「従業員管理」が表示される／モックのトップが表示される</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>S-01.png</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>サイドバーに「従業員管理」が展開された状態</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>サイドバー「従業員管理」（PCはホバー展開）／仕様モックのトップ</t>
         </is>
@@ -4335,22 +4872,22 @@
           <t>メニューが出るか／モックが開くか</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr"/>
+      <c r="K3" s="12" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="79" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>S-02</t>
         </is>
@@ -4370,13 +4907,13 @@
           <t>6件が確定し文書化されている（仕様書 第5部 11-A・11-C）</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>不要（文書で確認）</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>（画面操作なし・仕様書 第5部 11-A/11-C の確認）</t>
         </is>
@@ -4386,18 +4923,18 @@
           <t>6件の算式が確定・文書化されているか</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-12 AC-15</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr"/>
+      <c r="K4" s="12" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額／原則③：人件費は働いた店舗に付ける／計算：月中改定の日割り／原則③：交通費の帰属</t>
@@ -4405,7 +4942,7 @@
       </c>
     </row>
     <row r="5" ht="49" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>S-03</t>
         </is>
@@ -4426,13 +4963,13 @@
           <t>全行が算式で再現でき、日次合計＝月次・店舗別合計＝全社（差0円）</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>不要（データで確認）</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>（画面操作なし・data/05・06 の確認）</t>
         </is>
@@ -4442,18 +4979,18 @@
           <t>算式で全行が再現できるか</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額</t>
@@ -4461,7 +4998,7 @@
       </c>
     </row>
     <row r="6" ht="49" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>S-04</t>
         </is>
@@ -4482,17 +5019,17 @@
           <t>従業員一覧に12名が表示される</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>S-04.png</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>従業員一覧に12名が表示された全体</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>従業員一覧（サイドバー → 従業員管理 → 従業員一覧）</t>
         </is>
@@ -4502,22 +5039,22 @@
           <t>12名が一覧に出るか</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="49" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
@@ -4538,17 +5075,17 @@
           <t>履歴に適用済3・予約中1が入る／人件費実績に5名分が表示される</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>S-05.png</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>設定変更履歴（予約中の行が見える）／人件費実績 月別実績の5行</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>従業員設定履歴／人件費実績（月別実績タブ）</t>
         </is>
@@ -4558,22 +5095,22 @@
           <t>履歴に予約中1件・実績5名が出るか</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr"/>
-      <c r="L7" s="9" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr"/>
+      <c r="L7" s="12" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="94" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>S-06</t>
         </is>
@@ -4594,13 +5131,13 @@
           <t>5ファイルがアップロード可能な状態／設定が欠落した従業員が1名いる</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>不要（ファイル準備のみ）</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>（画面操作なし・取込ファイルの用意）</t>
         </is>
@@ -4610,22 +5147,22 @@
           <t>5ファイルがアップロードできる状態か</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr"/>
-      <c r="L8" s="9" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr"/>
+      <c r="L8" s="12" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="49" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>S-07</t>
         </is>
@@ -4646,13 +5183,13 @@
           <t>以降の計算ケースで同じ入力値を使う</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>不要（値の確定のみ）</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>（画面操作なし・基礎時給と所定労働日数の確定）</t>
         </is>
@@ -4662,22 +5199,22 @@
           <t>基礎時給と所定労働日数が確定しているか</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr"/>
-      <c r="L9" s="9" t="inlineStr"/>
+      <c r="K9" s="12" t="inlineStr"/>
+      <c r="L9" s="12" t="inlineStr"/>
       <c r="M9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>S-08</t>
         </is>
@@ -4698,17 +5235,17 @@
           <t>ボタンが「2026-05 締め」になっている</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>S-08.png</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>人件費実績 月別実績（ボタンが「2026-05 締め」＝未締め）</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 年月2026-05（締め状態の確認）</t>
         </is>
@@ -4718,22 +5255,22 @@
           <t>2026-05が未締めか</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr"/>
-      <c r="L10" s="9" t="inlineStr"/>
+      <c r="K10" s="12" t="inlineStr"/>
+      <c r="L10" s="12" t="inlineStr"/>
       <c r="M10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="49" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>S-09</t>
         </is>
@@ -4754,17 +5291,17 @@
           <t>突合シート M-01〜M-06 が埋まった状態</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>S-09.png</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>移行前の従業員一覧と人件費実績（比較の元になるため必須）</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>従業員一覧（CSVエクスポート）／人件費実績 月別実績（直近3か月）</t>
         </is>
@@ -4774,22 +5311,22 @@
           <t>移行前の値を控えたか</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr"/>
-      <c r="L11" s="9" t="inlineStr"/>
+      <c r="K11" s="12" t="inlineStr"/>
+      <c r="L11" s="12" t="inlineStr"/>
       <c r="M11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="49" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>S-10</t>
         </is>
@@ -4810,13 +5347,13 @@
           <t>店長でログインでき、従業員管理のメニューが表示される</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>（画面操作なし・店長スコープのアカウント用意）</t>
         </is>
@@ -4826,22 +5363,22 @@
           <t>店長アカウントでログインできるか</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr"/>
-      <c r="L12" s="9" t="inlineStr"/>
+      <c r="K12" s="12" t="inlineStr"/>
+      <c r="L12" s="12" t="inlineStr"/>
       <c r="M12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="49" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>S-11</t>
         </is>
@@ -4862,13 +5399,13 @@
           <t>移行を検証枠内で実行できる段取りができている</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>（画面操作なし・移行スクリプトの段取り）</t>
         </is>
@@ -4878,18 +5415,18 @@
           <t>移行を実行できる状態か</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr"/>
-      <c r="L13" s="9" t="inlineStr"/>
+      <c r="K13" s="12" t="inlineStr"/>
+      <c r="L13" s="12" t="inlineStr"/>
       <c r="M13" s="4" t="inlineStr"/>
     </row>
   </sheetData>
@@ -4906,7 +5443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4931,81 +5468,81 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>画面を操作しても判別できない条件。実装物（スキーマ・API・コード）を提示してもらって確認する。エンジニアの同席が必要。</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>検証ID</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>検証内容</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>操作・前提条件</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>スクショファイル名</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>スクショ（撮るもの）</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>確認ポイント</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>ヘルプページ該当箇所</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>対応受入条件</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>実際の値</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>計算根拠</t>
         </is>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>R-01</t>
         </is>
@@ -5026,17 +5563,17 @@
           <t>①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>R-01.png</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
@@ -5046,18 +5583,18 @@
           <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>AC-07 AC-40 AC-47</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr"/>
+      <c r="K3" s="12" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr">
         <is>
           <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
@@ -5065,7 +5602,7 @@
       </c>
     </row>
     <row r="4" ht="49" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>R-02</t>
         </is>
@@ -5086,17 +5623,17 @@
           <t>①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>R-02.png</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
@@ -5106,18 +5643,18 @@
           <t>APIでも店長が締められないか</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="11" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>AC-16 AC-41</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr"/>
+      <c r="K4" s="12" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
           <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
@@ -5125,7 +5662,7 @@
       </c>
     </row>
     <row r="5" ht="64" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>R-03</t>
         </is>
@@ -5146,17 +5683,17 @@
           <t>①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>R-03.png</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
@@ -5166,18 +5703,18 @@
           <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr"/>
+      <c r="K5" s="12" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr">
         <is>
           <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
@@ -5185,7 +5722,7 @@
       </c>
     </row>
     <row r="6" ht="49" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>R-04</t>
         </is>
@@ -5206,17 +5743,17 @@
           <t>同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>R-04.png</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
         </is>
@@ -5226,18 +5763,18 @@
           <t>計算ロジックが1箇所か</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J6" s="11" t="inlineStr">
         <is>
           <t>AC-35 AC-11</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr"/>
+      <c r="K6" s="12" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr">
         <is>
           <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
@@ -5245,7 +5782,7 @@
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
@@ -5266,17 +5803,17 @@
           <t>CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>R-05.png</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>列名の対応づけを保持している箇所（DBかコードか）</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
         </is>
@@ -5286,18 +5823,18 @@
           <t>列名がコードに埋まっていないか</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>AC-22 AC-24</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr"/>
-      <c r="L7" s="9" t="inlineStr"/>
+      <c r="K7" s="12" t="inlineStr"/>
+      <c r="L7" s="12" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr">
         <is>
           <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
@@ -5305,7 +5842,7 @@
       </c>
     </row>
     <row r="8" ht="49" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
@@ -5326,17 +5863,17 @@
           <t>設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>R-06.png</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
         </is>
@@ -5346,18 +5883,18 @@
           <t>2つの入口で更新処理が共通か</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>AC-49</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr"/>
-      <c r="L8" s="9" t="inlineStr"/>
+      <c r="K8" s="12" t="inlineStr"/>
+      <c r="L8" s="12" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr">
         <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -54,7 +54,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F1F3F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEBE9"/>
       </patternFill>
     </fill>
     <fill>
@@ -118,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,6 +133,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -137,11 +143,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -150,6 +153,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -517,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -659,142 +665,142 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>■ 2. 1件をどう進めるか</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>■ 2. 実施順を変えてはいけない箇所</t>
         </is>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>列</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>見るタイミング</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>使い方</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>画面</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>操作の前</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>サイドバーからの経路・タブ・ボタン名・モーダル名まで書いてある。この順に開く</t>
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>上から順に実施すれば成立するように並べてあります。順番を入れ替える場合は、下記の依存に注意してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>守らないとどうなるか</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>操作・前提条件（入力値）</t>
+          <t>T-A08（勤怠取込）→ T-S03（締め）</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>操作するとき</t>
+          <t>締めた後は取込が効かないため</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>【前提】の準備行が済んでいるか確認してから【操作】を行う</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1">
+          <t>締め後に取り込むと反映されず、T-A08が判定できない</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="49" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>確認ポイント</t>
+          <t>T-S03（締め）→ T-S04・T-D07 → T-S05（締め解除）</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>操作の直後</t>
+          <t>この3件は締め済みの状態でしか確認できない</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>何を見るかの一言。まずここを見る</t>
+          <t>解除してから実施すると、締めの効果を確認できない</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>期待値</t>
+          <t>C-000（初期化）を計算系の先頭で実施</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>判定するとき</t>
+          <t>操作系でデータが変わっているため</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>この内容と実際の画面を突き合わせる。数値で書いてあるものは数値で比べる</t>
+          <t>EMP-001が340,000のままなど、計算系の期待値と合わなくなる</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>スクショ（撮るもの）</t>
+          <t>C-008は計算系の最後</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>判定した後</t>
+          <t>2026-05のEMP-001を352,286円に変えるため</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>ここに書いてある内容が写るように撮り、ファイル名の列の名前で保存する</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19" customHeight="1">
+          <t>先に実施するとC-013・C-017の期待値（338,000円が前提）と合わなくなる</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>実際の値・判定</t>
+          <t>T-N02の前にdata/02を再投入</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>最後</t>
+          <t>T-I03でEMP-001が340,000になっているため</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>測った値を書き、OK／NG／対象外を選ぶ</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>■ 3. 紐付けの2列をどう使うか</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>受入条件は「リリースしてよいか」、ヘルプページは「顧客に案内したとおりか」を見るためのものです。役割が違うので、両方を確認します。</t>
+          <t>前回差分が0件になり、差分表示の検証にならない</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>削除はEMP-012（T-L10）とEMP-004（T-D08）だけ</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>この2名はマスタにしか出てこない</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>実績や取込CSVに出てくる従業員を消すと、以降の検証と計算が成立しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>■ 3. 1件をどう進めるか</t>
         </is>
       </c>
     </row>
@@ -806,224 +812,359 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>何が書いてあるか</t>
+          <t>見るタイミング</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>検証中にどう使うか</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="94" customHeight="1">
+          <t>使い方</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>対応受入条件</t>
+          <t>画面</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>この検証が担保する受入条件のID（AC-16 など）</t>
+          <t>操作の前</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>①判定に迷ったら、そのIDを受入条件表で引くと「合格基準（定量）」が書いてある（例 AC-16＝実績給与の差分0円）。②検証が終わったら、IDごとに判定を確認表へ集約する。ひとつのIDに複数の検証が紐づく場合は、すべてOKで初めてその条件が合格</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="64" customHeight="1">
+          <t>サイドバーからの経路・タブ・ボタン名・モーダル名まで書いてある。この順に開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>ヘルプページ該当箇所</t>
+          <t>操作・前提条件（入力値）</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>この検証が担保するヘルプページの記述（大項目 ＞ 中項目）</t>
+          <t>操作するとき</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>ヘルプページは顧客への約束。NGだった場合、実装を直すのか、ヘルプの記述を直すのかを必ず決める。ヘルプ側を直す判断をしたときは、この列から該当箇所を開いて修正する</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>■ 4. 判定の入れ方</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>意味</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>その後</t>
+          <t>【前提】の準備行が済んでいるか確認してから【操作】を行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>確認ポイント</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>操作の直後</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>何を見るかの一言。まずここを見る</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>期待値</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>判定するとき</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>この内容と実際の画面を突き合わせる。数値で書いてあるものは数値で比べる</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>スクショ（撮るもの）</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>判定した後</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>ここに書いてある内容が写るように撮り、ファイル名の列の名前で保存する</t>
         </is>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>実際の値・判定</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>最後</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>測った値を書き、OK／NG／対象外を選ぶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>■ 4. 紐付けの2列をどう使うか</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>受入条件は「リリースしてよいか」、ヘルプページは「顧客に案内したとおりか」を見るためのものです。役割が違うので、両方を確認します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>列</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>何が書いてあるか</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>検証中にどう使うか</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="94" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>対応受入条件</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>この検証が担保する受入条件のID（AC-16 など）</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>①判定に迷ったら、そのIDを受入条件表で引くと「合格基準（定量）」が書いてある（例 AC-16＝実績給与の差分0円）。②検証が終わったら、IDごとに判定を確認表へ集約する。ひとつのIDに複数の検証が紐づく場合は、すべてOKで初めてその条件が合格</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ヘルプページ該当箇所</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>この検証が担保するヘルプページの記述（大項目 ＞ 中項目）</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>ヘルプページは顧客への約束。NGだった場合、実装を直すのか、ヘルプの記述を直すのかを必ず決める。ヘルプ側を直す判断をしたときは、この列から該当箇所を開いて修正する</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>■ 5. 判定の入れ方</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>その後</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>期待値を満たした</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>次へ</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>NG</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>操作できたが期待値を満たさない</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>実装の修正か、期待値・ヘルプ記述の見直しかを決める。所見に実測値を残す</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>対象外</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>その環境では実施できない（機能が未実装など）</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>なぜ実施できないかを所見に残す。未実施のまま合格にはしない</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>■ 5. 色の意味</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>■ 6. 色の意味</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>色</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>列</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>意味</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>青</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>どこを開くか</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>橙</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>スクショファイル名／スクショ（撮るもの）</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>何を証拠に残すか</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>紫</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>ヘルプページ該当箇所／対応受入条件</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>何を担保する検証か</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>黄</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>実際の値／判定</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>当日の記入欄</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A33:C33"/>
+  <mergeCells count="8">
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A27:C27"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1054,81 +1195,81 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>画面を操作して確かめるケース。使い方は「00_使い方」シートを参照。紫の2列で、この検証がヘルプページのどの記述と受入条件のどのIDを担保するかが分かる。</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>画面を操作して確かめるケース。上から順に実施する（実施順の依存は「00_使い方」の2番を参照）。紫の2列で、この検証がヘルプページのどの記述と受入条件のどのIDを担保するかが分かる。</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>検証ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>検証内容</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>操作・前提条件</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>スクショファイル名</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>スクショ（撮るもの）</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>確認ポイント</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>ヘルプページ該当箇所</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>対応受入条件</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>実際の値</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>計算根拠</t>
         </is>
       </c>
     </row>
     <row r="3" ht="94" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>T-L01</t>
         </is>
@@ -1149,17 +1290,17 @@
           <t>12名が表示。12列（名前/従業員コード/所属店舗/ヘルプ先店舗/雇用区分/給与単位/単位給与額/交通費単位/単位交通費/所定労働時間/みなし残業時間/アクション）。雇用区分・給与単位が色分け。EMP-001はヘルプ先2バッジ、EMP-002は空。単位給与額が数値順にソート（1,000→…→410,000）。該当なしで「データはありません。」</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>T-L01.png</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>一覧全体（12行・12列・バッジの色・ソート矢印）と、フィルタで0件にしたときの「データはありません。」</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>従業員一覧 … 表の12列・雇用区分/給与単位のバッジ・列ヘッダーのソート・0件表示</t>
         </is>
@@ -1169,18 +1310,18 @@
           <t>12列・バッジ・ソート・0件表示</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
-      <c r="K3" s="12" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr"/>
+      <c r="K3" s="13" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr">
         <is>
           <t>移行：既存顧客が壊れない</t>
@@ -1188,7 +1329,7 @@
       </c>
     </row>
     <row r="4" ht="49" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>T-L08</t>
         </is>
@@ -1209,17 +1350,17 @@
           <t>渋谷店＝3名（EMP-001・002・011）、正社員＝6名、田中＝1名。2段目で対象データが切り替わる</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>T-L08.png</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>1段目と2段目の両方を適用した状態（絞り込み条件と結果件数が同時に写ること）</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>従業員一覧 … 1段目フィルタ（店舗/雇用区分/名前検索）と2段目フィルタ（月/取込データ）</t>
         </is>
@@ -1229,18 +1370,18 @@
           <t>2段フィルタが効くか</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>AC-33</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr"/>
+      <c r="K4" s="13" t="inlineStr"/>
+      <c r="L4" s="13" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
           <t>画面：対象を探せる</t>
@@ -1248,7 +1389,7 @@
       </c>
     </row>
     <row r="5" ht="64" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>T-L06</t>
         </is>
@@ -1269,17 +1410,17 @@
           <t>5経路すべて到達（従業員登録／設定インポート／設定・実績エクスポート／設定取込データ／従業員詳細）。不通=0</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>T-L06.png</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>遷移先5画面の到達直後（従業員登録・設定インポート・エクスポート・設定取込データ・従業員詳細）</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>従業員一覧 … 右上ツールバー「従業員登録」「CSVインポート」「設定・実績エクスポート」／2段目「設定取込データへ」／行末の詳細アイコン</t>
         </is>
@@ -1289,18 +1430,18 @@
           <t>5経路すべて到達するか</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>AC-30</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr"/>
+      <c r="K5" s="13" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr">
         <is>
           <t>画面：操作が最後まで通る</t>
@@ -1308,7 +1449,7 @@
       </c>
     </row>
     <row r="6" ht="49" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>T-L10</t>
         </is>
@@ -1329,17 +1470,17 @@
           <t>（a）12名のまま削除されない （b）完了表示のあと11名になる</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>T-L10.png</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>削除の確認ダイアログ／キャンセル後の一覧／実行後の一覧（行が消えたこと）</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>従業員一覧 … 行末の削除アイコン → 確認ダイアログ</t>
         </is>
@@ -1349,18 +1490,18 @@
           <t>キャンセルで消えない／実行で消えるか</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>AC-34</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr"/>
+      <c r="K6" s="13" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr">
         <is>
           <t>データ保全：消える操作は確認を経る</t>
@@ -1368,7 +1509,7 @@
       </c>
     </row>
     <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>T-R02</t>
         </is>
@@ -1389,17 +1530,17 @@
           <t>13項目（名前/従業員コード/所属店舗/ヘルプ先店舗/雇用区分/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。¥320,000 と千区切り表示。適用日付は所定労働時間・みなし残業時間の下の行・初期値は当日</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>T-R02.png</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>登録フォーム全体（単位給与額に320,000と入れ、桁区切りが効いている状態）</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>従業員登録（従業員一覧 右上「従業員登録」から遷移）… 入力フォーム全体と通貨の桁区切り表示</t>
         </is>
@@ -1409,18 +1550,18 @@
           <t>項目の過不足と桁区切り表示</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>AC-06</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr"/>
-      <c r="L7" s="12" t="inlineStr"/>
+      <c r="K7" s="13" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr">
         <is>
           <t>原則①：当日・過去日は即時</t>
@@ -1428,7 +1569,7 @@
       </c>
     </row>
     <row r="8" ht="49" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>T-R04</t>
         </is>
@@ -1449,17 +1590,17 @@
           <t>選択した2店それぞれに交通費欄が出る／（a）必須バリデーションで登録できない／（b）新宿店の欄だけ消え、青山店の入力値は残る</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>T-R04.png</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>ヘルプ先2店選択でヘルプ先交通費欄が出た状態／1店外して欄が消えた状態の2枚</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>従業員登録 … ヘルプ先店舗の複数選択と、その下に自動表示されるヘルプ先交通費の入力欄</t>
         </is>
@@ -1469,18 +1610,18 @@
           <t>交通費欄が自動で出る／消えるか</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>AC-15 AC-47</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr"/>
-      <c r="L8" s="12" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr">
         <is>
           <t>原則③：交通費の帰属／原則③：交通費も働いた店舗の実費で</t>
@@ -1488,7 +1629,7 @@
       </c>
     </row>
     <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>T-R07</t>
         </is>
@@ -1509,17 +1650,17 @@
           <t>（a）完了表示のあと一覧へ戻り、登録前より1名増えている （b）一覧へ戻り件数は変わらない （c）従業員一覧／設定インポートへ遷移</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>T-R07.png</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>登録成功後の従業員一覧（新規行が見えること）とキャンセル後の一覧</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>従業員登録 … 下部「登録」「キャンセル」／ツールバー「従業員一覧へ」「CSVインポート」→ 従業員一覧</t>
         </is>
@@ -1529,18 +1670,18 @@
           <t>登録される／されないの分岐</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>AC-06 AC-30</t>
         </is>
       </c>
-      <c r="K9" s="12" t="inlineStr"/>
-      <c r="L9" s="12" t="inlineStr"/>
+      <c r="K9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr"/>
       <c r="M9" s="4" t="inlineStr">
         <is>
           <t>原則①：当日・過去日は即時／画面：操作が最後まで通る</t>
@@ -1548,7 +1689,7 @@
       </c>
     </row>
     <row r="10" ht="49" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>T-R10</t>
         </is>
@@ -1569,17 +1710,17 @@
           <t>6項目それぞれで 登録=0件・画面遷移=0件（6回とも同じ）。不足している項目名が画面上に表示される</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>T-R10.png</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>必須未入力で「登録」を押した直後（エラー表示と、画面が遷移していないこと）</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>従業員登録 … 必須項目のバリデーション表示（画面に留まること）</t>
         </is>
@@ -1589,18 +1730,18 @@
           <t>必須未入力で保存も遷移もしないか</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>AC-43</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr"/>
-      <c r="L10" s="12" t="inlineStr"/>
+      <c r="K10" s="13" t="inlineStr"/>
+      <c r="L10" s="13" t="inlineStr"/>
       <c r="M10" s="4" t="inlineStr">
         <is>
           <t>データ保全：不完全な登録を作らない</t>
@@ -1608,7 +1749,7 @@
       </c>
     </row>
     <row r="11" ht="49" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>T-D01</t>
         </is>
@@ -1629,17 +1770,17 @@
           <t>基本情報／設定変更履歴／給与実績 が表示。基本情報は登録と同項目・同配置。履歴は14列（変更反映日時〜変更ソース の13項目＋操作）。2026-08-01行が「予約中」</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>T-D01.png</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>従業員詳細の全体（基本情報・設定変更履歴・給与実績の3セクションが分かる範囲）</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>従業員詳細（従業員一覧の詳細アイコンから遷移）… 基本情報／設定変更履歴／給与実績の3セクション</t>
         </is>
@@ -1649,18 +1790,18 @@
           <t>3セクションと履歴14列</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr"/>
-      <c r="L11" s="12" t="inlineStr"/>
+      <c r="K11" s="13" t="inlineStr"/>
+      <c r="L11" s="13" t="inlineStr"/>
       <c r="M11" s="4" t="inlineStr">
         <is>
           <t>原則①：過去は不変</t>
@@ -1668,7 +1809,7 @@
       </c>
     </row>
     <row r="12" ht="49" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>T-D04</t>
         </is>
@@ -1689,17 +1830,17 @@
           <t>「（日付）からの適用を予約しました」と表示。履歴に「予約中」が1行追加。一覧の単位給与額は320,000のまま</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>T-D04.png</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>保存直後のトースト「◯月◯日からの適用を予約しました」／履歴の「予約中」行／一覧の値が未変更であること の3枚</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>従業員詳細 … 基本情報の単位給与額と適用日付 → 下部「保存」→ 従業員一覧のトーストと一覧値</t>
         </is>
@@ -1709,18 +1850,18 @@
           <t>予約になり一覧の値が変わらないか</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>AC-04</t>
         </is>
       </c>
-      <c r="K12" s="12" t="inlineStr"/>
-      <c r="L12" s="12" t="inlineStr"/>
+      <c r="K12" s="13" t="inlineStr"/>
+      <c r="L12" s="13" t="inlineStr"/>
       <c r="M12" s="4" t="inlineStr">
         <is>
           <t>原則①：未来日は予約になる</t>
@@ -1728,7 +1869,7 @@
       </c>
     </row>
     <row r="13" ht="79" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>T-D05</t>
         </is>
@@ -1749,17 +1890,17 @@
           <t>一覧が340,000に変わり、履歴が「適用中」、旧行が「過去」になる</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>T-D05.png</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>適用日を迎えた後の一覧の値と、履歴のステータスが「適用中」に変わった行</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>従業員詳細（予約を仕込む）→ 翌日の従業員一覧と設定変更履歴のステータス</t>
         </is>
@@ -1769,18 +1910,18 @@
           <t>適用日に自動で切り替わるか</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>AC-05</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr"/>
-      <c r="L13" s="12" t="inlineStr"/>
+      <c r="K13" s="13" t="inlineStr"/>
+      <c r="L13" s="13" t="inlineStr"/>
       <c r="M13" s="4" t="inlineStr">
         <is>
           <t>原則①：予約が自動で効く</t>
@@ -1788,7 +1929,7 @@
       </c>
     </row>
     <row r="14" ht="49" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>T-D06</t>
         </is>
@@ -1809,17 +1950,17 @@
           <t>「即時反映しました」と表示。一覧が290,000になる</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>T-D06.png</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>トースト「即時反映しました」と、一覧の値が290,000になった状態</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>従業員詳細 … 適用日付＝当日で「保存」→ 従業員一覧の値</t>
         </is>
@@ -1829,18 +1970,18 @@
           <t>即時反映され一覧の値が変わるか</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>AC-06</t>
         </is>
       </c>
-      <c r="K14" s="12" t="inlineStr"/>
-      <c r="L14" s="12" t="inlineStr"/>
+      <c r="K14" s="13" t="inlineStr"/>
+      <c r="L14" s="13" t="inlineStr"/>
       <c r="M14" s="4" t="inlineStr">
         <is>
           <t>原則①：当日・過去日は即時</t>
@@ -1848,7 +1989,7 @@
       </c>
     </row>
     <row r="15" ht="49" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>T-D09</t>
         </is>
@@ -1869,17 +2010,17 @@
           <t>月次17列（年月〜深夜残業代＋交通費＋総支給額）／日次14列。個人向けに列を絞った構成で、人件費実績（26列/21列）とは別。フィルタで期間が絞られる。表示中の内容がBOM付きCSVで出力される</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>T-D09.png</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>月次タブ（概算／実績の両方）と日次タブ／出力したCSVをExcelで開いた画面</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>従業員詳細 → 給与実績セクション … 月次タブ（概算⇄実績の切替・年フィルタ）／日次タブ（月フィルタ）／各タブのCSVエクスポート</t>
         </is>
@@ -1889,26 +2030,26 @@
           <t>タブ切替とCSVの中身が変わるか</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>AC-35 AC-36</t>
         </is>
       </c>
-      <c r="K15" s="12" t="inlineStr"/>
-      <c r="L15" s="12" t="inlineStr"/>
+      <c r="K15" s="13" t="inlineStr"/>
+      <c r="L15" s="13" t="inlineStr"/>
       <c r="M15" s="4" t="inlineStr">
         <is>
           <t>計算：個人単位でも同じ数字／入出力：画面の内容と一致</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="49" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>T-D08</t>
         </is>
@@ -1921,7 +2062,7 @@
       <c r="C16" s="4" t="inlineStr">
         <is>
           <t>【前提】S-04
-【操作】「従業員削除」→（a）キャンセル →（b）実行、（c）「一覧へ戻る」</t>
+【操作】EMP-004（山本 健／実績データにも取込CSVにも含まれない）の詳細を開き「従業員削除」→（a）キャンセル →（b）実行、（c）別の従業員で「一覧へ戻る」</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1929,17 +2070,17 @@
           <t>（a）削除されず件数が変わらない （b）確認のあと削除される （c）一覧へ戻る（保存されない）</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>T-D08.png</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>削除の確認モーダル／実行後の一覧（行が消えたこと）</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>従業員詳細 … 下部「従業員削除」→ 確認モーダル／「一覧へ戻る」→ 従業員一覧</t>
         </is>
@@ -1949,18 +2090,18 @@
           <t>キャンセルで消えない／実行で消えるか</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>AC-34 AC-30</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="12" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr"/>
+      <c r="L16" s="13" t="inlineStr"/>
       <c r="M16" s="4" t="inlineStr">
         <is>
           <t>データ保全：消える操作は確認を経る／画面：操作が最後まで通る</t>
@@ -1968,7 +2109,7 @@
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>T-H01</t>
         </is>
@@ -1989,17 +2130,17 @@
           <t>履歴が1行増える。既存行の値の差分＝0</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>T-H01.png</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>従業員設定履歴 … 変更前後の行（既存行が書き換わらないこと）</t>
         </is>
@@ -2009,18 +2150,18 @@
           <t>既存行が書き換わらないか</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr"/>
-      <c r="L17" s="12" t="inlineStr"/>
+      <c r="K17" s="13" t="inlineStr"/>
+      <c r="L17" s="13" t="inlineStr"/>
       <c r="M17" s="4" t="inlineStr">
         <is>
           <t>原則①：過去は不変</t>
@@ -2028,7 +2169,7 @@
       </c>
     </row>
     <row r="18" ht="49" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>T-H02</t>
         </is>
@@ -2049,17 +2190,17 @@
           <t>①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>T-H02.png</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>従業員設定履歴 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
         </is>
@@ -2069,18 +2210,18 @@
           <t>2つの日時が別で記録されるか</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>AC-08 AC-09</t>
         </is>
       </c>
-      <c r="K18" s="12" t="inlineStr"/>
-      <c r="L18" s="12" t="inlineStr"/>
+      <c r="K18" s="13" t="inlineStr"/>
+      <c r="L18" s="13" t="inlineStr"/>
       <c r="M18" s="4" t="inlineStr">
         <is>
           <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
@@ -2088,7 +2229,7 @@
       </c>
     </row>
     <row r="19" ht="64" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>T-H04</t>
         </is>
@@ -2109,17 +2250,17 @@
           <t>店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>T-H04.png</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>従業員設定履歴 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
         </is>
@@ -2129,18 +2270,18 @@
           <t>絞り込み後の行だけ出力されるか</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>AC-33 AC-36 AC-30</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr"/>
-      <c r="L19" s="12" t="inlineStr"/>
+      <c r="K19" s="13" t="inlineStr"/>
+      <c r="L19" s="13" t="inlineStr"/>
       <c r="M19" s="4" t="inlineStr">
         <is>
           <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
@@ -2148,7 +2289,7 @@
       </c>
     </row>
     <row r="20" ht="109" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>T-A02</t>
         </is>
@@ -2169,17 +2310,17 @@
           <t>全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>T-A02.png</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
         </is>
@@ -2189,18 +2330,18 @@
           <t>モード切替で列が増減するか</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>AC-10 AC-31</t>
         </is>
       </c>
-      <c r="K20" s="12" t="inlineStr"/>
-      <c r="L20" s="12" t="inlineStr"/>
+      <c r="K20" s="13" t="inlineStr"/>
+      <c r="L20" s="13" t="inlineStr"/>
       <c r="M20" s="4" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額／画面：状態が漏れない</t>
@@ -2208,7 +2349,7 @@
       </c>
     </row>
     <row r="21" ht="49" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>T-A09</t>
         </is>
@@ -2229,17 +2370,17 @@
           <t>モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>T-A09.png</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>設定編集モーダル（項目が見える状態）／更新保存後の人件費実績／従業員詳細の設定変更履歴に行が増えたこと</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 人件費実績／確認は従業員詳細の設定変更履歴</t>
         </is>
@@ -2249,18 +2390,18 @@
           <t>モーダル編集でも履歴が残るか</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>AC-49</t>
         </is>
       </c>
-      <c r="K21" s="12" t="inlineStr"/>
-      <c r="L21" s="12" t="inlineStr"/>
+      <c r="K21" s="13" t="inlineStr"/>
+      <c r="L21" s="13" t="inlineStr"/>
       <c r="M21" s="4" t="inlineStr">
         <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
@@ -2268,7 +2409,7 @@
       </c>
     </row>
     <row r="22" ht="94" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>T-A05</t>
         </is>
@@ -2289,17 +2430,17 @@
           <t>全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>T-A05.png</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
         </is>
@@ -2309,18 +2450,18 @@
           <t>日別に概算モードが無いか</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="K22" s="12" t="inlineStr"/>
-      <c r="L22" s="12" t="inlineStr"/>
+      <c r="K22" s="13" t="inlineStr"/>
+      <c r="L22" s="13" t="inlineStr"/>
       <c r="M22" s="4" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額</t>
@@ -2328,7 +2469,7 @@
       </c>
     </row>
     <row r="23" ht="49" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>T-A07</t>
         </is>
@@ -2349,17 +2490,17 @@
           <t>出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>T-A07.png</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>人件費実績 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
         </is>
@@ -2369,18 +2510,18 @@
           <t>表示中の内容が出力されるか</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I23" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J23" s="12" t="inlineStr">
         <is>
           <t>AC-36</t>
         </is>
       </c>
-      <c r="K23" s="12" t="inlineStr"/>
-      <c r="L23" s="12" t="inlineStr"/>
+      <c r="K23" s="13" t="inlineStr"/>
+      <c r="L23" s="13" t="inlineStr"/>
       <c r="M23" s="4" t="inlineStr">
         <is>
           <t>入出力：画面の内容と一致</t>
@@ -2388,7 +2529,7 @@
       </c>
     </row>
     <row r="24" ht="49" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>T-A08</t>
         </is>
@@ -2409,17 +2550,17 @@
           <t>「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>T-A08.png</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
         </is>
@@ -2429,18 +2570,18 @@
           <t>進捗が出て他操作を受け付けないか</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>AC-48</t>
         </is>
       </c>
-      <c r="K24" s="12" t="inlineStr"/>
-      <c r="L24" s="12" t="inlineStr"/>
+      <c r="K24" s="13" t="inlineStr"/>
+      <c r="L24" s="13" t="inlineStr"/>
       <c r="M24" s="4" t="inlineStr">
         <is>
           <t>入出力：勤怠実績を取り込める</t>
@@ -2448,7 +2589,7 @@
       </c>
     </row>
     <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>T-S01</t>
         </is>
@@ -2469,17 +2610,17 @@
           <t>月別のみ「2026-05 締め」が表示。日別には表示されない</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>T-S01.png</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>人件費実績 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
         </is>
@@ -2489,18 +2630,18 @@
           <t>締めが月別タブにだけ出るか</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="J25" s="12" t="inlineStr">
         <is>
           <t>AC-18</t>
         </is>
       </c>
-      <c r="K25" s="12" t="inlineStr"/>
-      <c r="L25" s="12" t="inlineStr"/>
+      <c r="K25" s="13" t="inlineStr"/>
+      <c r="L25" s="13" t="inlineStr"/>
       <c r="M25" s="4" t="inlineStr">
         <is>
           <t>原則②：締めの単位は月</t>
@@ -2508,7 +2649,7 @@
       </c>
     </row>
     <row r="26" ht="49" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>T-S03</t>
         </is>
@@ -2529,17 +2670,17 @@
           <t>「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>T-S03.png</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
         </is>
@@ -2549,18 +2690,18 @@
           <t>確認モーダルを経て締まるか</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="I26" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J26" s="12" t="inlineStr">
         <is>
           <t>AC-16 AC-19 AC-32</t>
         </is>
       </c>
-      <c r="K26" s="12" t="inlineStr"/>
-      <c r="L26" s="12" t="inlineStr"/>
+      <c r="K26" s="13" t="inlineStr"/>
+      <c r="L26" s="13" t="inlineStr"/>
       <c r="M26" s="4" t="inlineStr">
         <is>
           <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
@@ -2568,7 +2709,7 @@
       </c>
     </row>
     <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>T-S04</t>
         </is>
@@ -2589,17 +2730,17 @@
           <t>編集できない（または反映されない）</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>T-S04.png</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
         </is>
@@ -2609,18 +2750,18 @@
           <t>締め後に金額が動かないか</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="J27" s="12" t="inlineStr">
         <is>
           <t>AC-16</t>
         </is>
       </c>
-      <c r="K27" s="12" t="inlineStr"/>
-      <c r="L27" s="12" t="inlineStr"/>
+      <c r="K27" s="13" t="inlineStr"/>
+      <c r="L27" s="13" t="inlineStr"/>
       <c r="M27" s="4" t="inlineStr">
         <is>
           <t>原則②：締めたら動かない</t>
@@ -2628,7 +2769,7 @@
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>T-D07</t>
         </is>
@@ -2649,17 +2790,17 @@
           <t>締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>T-D07.png</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
         </is>
@@ -2669,18 +2810,18 @@
           <t>警告が出て反映されないか</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="I28" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J28" s="12" t="inlineStr">
         <is>
           <t>AC-20</t>
         </is>
       </c>
-      <c r="K28" s="12" t="inlineStr"/>
-      <c r="L28" s="12" t="inlineStr"/>
+      <c r="K28" s="13" t="inlineStr"/>
+      <c r="L28" s="13" t="inlineStr"/>
       <c r="M28" s="4" t="inlineStr">
         <is>
           <t>原則②：遡及は黙って捨てない</t>
@@ -2688,7 +2829,7 @@
       </c>
     </row>
     <row r="29" ht="49" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>T-S05</t>
         </is>
@@ -2709,17 +2850,17 @@
           <t>「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>T-S05.png</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
         </is>
@@ -2729,18 +2870,18 @@
           <t>解除で再計算されるか</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>AC-19</t>
         </is>
       </c>
-      <c r="K29" s="12" t="inlineStr"/>
-      <c r="L29" s="12" t="inlineStr"/>
+      <c r="K29" s="13" t="inlineStr"/>
+      <c r="L29" s="13" t="inlineStr"/>
       <c r="M29" s="4" t="inlineStr">
         <is>
           <t>原則②：確定操作は確認を経る</t>
@@ -2748,7 +2889,7 @@
       </c>
     </row>
     <row r="30" ht="49" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>T-S07</t>
         </is>
@@ -2769,17 +2910,17 @@
           <t>締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>T-S07.png</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>店長スコープでの人件費実績（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
         </is>
@@ -2789,18 +2930,18 @@
           <t>店長が締められないか</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr">
+      <c r="I30" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="J30" s="12" t="inlineStr">
         <is>
           <t>AC-41</t>
         </is>
       </c>
-      <c r="K30" s="12" t="inlineStr"/>
-      <c r="L30" s="12" t="inlineStr"/>
+      <c r="K30" s="13" t="inlineStr"/>
+      <c r="L30" s="13" t="inlineStr"/>
       <c r="M30" s="4" t="inlineStr">
         <is>
           <t>原則②：締めは会社スコープのみ</t>
@@ -2808,7 +2949,7 @@
       </c>
     </row>
     <row r="31" ht="64" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>T-I02</t>
         </is>
@@ -2829,17 +2970,17 @@
           <t>従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>T-I02.png</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
         </is>
@@ -2849,18 +2990,18 @@
           <t>テンプレートの列とBOM</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="I31" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr">
+      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>AC-21 AC-30</t>
         </is>
       </c>
-      <c r="K31" s="12" t="inlineStr"/>
-      <c r="L31" s="12" t="inlineStr"/>
+      <c r="K31" s="13" t="inlineStr"/>
+      <c r="L31" s="13" t="inlineStr"/>
       <c r="M31" s="4" t="inlineStr">
         <is>
           <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
@@ -2868,7 +3009,7 @@
       </c>
     </row>
     <row r="32" ht="49" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>T-I03</t>
         </is>
@@ -2889,17 +3030,17 @@
           <t>07は3行すべて取り込まれ、EMP-001=340,000・EMP-005=360,000に更新、EMP-013は新規追加。10は給与設定（ヘルプ先交通費 S02:700;S03:900 の記法を含む）が反映される</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>T-I03.png</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
         </is>
@@ -2909,18 +3050,18 @@
           <t>3行が更新・追加されるか</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr">
+      <c r="I32" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>AC-21</t>
         </is>
       </c>
-      <c r="K32" s="12" t="inlineStr"/>
-      <c r="L32" s="12" t="inlineStr"/>
+      <c r="K32" s="13" t="inlineStr"/>
+      <c r="L32" s="13" t="inlineStr"/>
       <c r="M32" s="4" t="inlineStr">
         <is>
           <t>入出力：導入を止めない</t>
@@ -2928,7 +3069,7 @@
       </c>
     </row>
     <row r="33" ht="49" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>T-I04</t>
         </is>
@@ -2949,17 +3090,17 @@
           <t>3行すべて取り込まれる（EMP-003=1,250・EMP-010=1,300・EMP-014は新規）</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>T-I04.png</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
         </is>
@@ -2969,18 +3110,18 @@
           <t>表記ゆれを吸収できるか</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr">
+      <c r="J33" s="12" t="inlineStr">
         <is>
           <t>AC-22</t>
         </is>
       </c>
-      <c r="K33" s="12" t="inlineStr"/>
-      <c r="L33" s="12" t="inlineStr"/>
+      <c r="K33" s="13" t="inlineStr"/>
+      <c r="L33" s="13" t="inlineStr"/>
       <c r="M33" s="4" t="inlineStr">
         <is>
           <t>入出力：表記ゆれを吸収</t>
@@ -2988,7 +3129,7 @@
       </c>
     </row>
     <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>T-I05</t>
         </is>
@@ -3009,17 +3150,17 @@
           <t>4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>T-I05.png</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
         </is>
@@ -3029,18 +3170,18 @@
           <t>4種の異常を行ごとに検出するか</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="I34" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>AC-23</t>
         </is>
       </c>
-      <c r="K34" s="12" t="inlineStr"/>
-      <c r="L34" s="12" t="inlineStr"/>
+      <c r="K34" s="13" t="inlineStr"/>
+      <c r="L34" s="13" t="inlineStr"/>
       <c r="M34" s="4" t="inlineStr">
         <is>
           <t>データ保全：不正値を入れない</t>
@@ -3048,7 +3189,7 @@
       </c>
     </row>
     <row r="35" ht="49" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>T-I17</t>
         </is>
@@ -3069,17 +3210,17 @@
           <t>（a）2回目は更新となり件数が増えない （b）重複行がエラーとして検出される（両方が登録されない）</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>T-I17.png</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
         </is>
@@ -3089,18 +3230,18 @@
           <t>二重登録されないか</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr">
+      <c r="I35" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr">
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>AC-40</t>
         </is>
       </c>
-      <c r="K35" s="12" t="inlineStr"/>
-      <c r="L35" s="12" t="inlineStr"/>
+      <c r="K35" s="13" t="inlineStr"/>
+      <c r="L35" s="13" t="inlineStr"/>
       <c r="M35" s="4" t="inlineStr">
         <is>
           <t>データ保全：二重登録を防ぐ</t>
@@ -3108,7 +3249,7 @@
       </c>
     </row>
     <row r="36" ht="64" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>T-I18</t>
         </is>
@@ -3129,17 +3270,17 @@
           <t>中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>T-I18.png</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録されていないこと）</t>
         </is>
@@ -3149,18 +3290,18 @@
           <t>部分登録が残らないか</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="I36" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>AC-42</t>
         </is>
       </c>
-      <c r="K36" s="12" t="inlineStr"/>
-      <c r="L36" s="12" t="inlineStr"/>
+      <c r="K36" s="13" t="inlineStr"/>
+      <c r="L36" s="13" t="inlineStr"/>
       <c r="M36" s="4" t="inlineStr">
         <is>
           <t>データ保全：中途半端に残さない</t>
@@ -3168,7 +3309,7 @@
       </c>
     </row>
     <row r="37" ht="49" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>T-I11</t>
         </is>
@@ -3189,17 +3330,17 @@
           <t>余計な行が無視され、3行が正しく取り込まれる</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>T-I11.png</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
         </is>
@@ -3209,18 +3350,18 @@
           <t>説明行を飛ばして取り込めるか</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="I37" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr">
+      <c r="J37" s="12" t="inlineStr">
         <is>
           <t>AC-37</t>
         </is>
       </c>
-      <c r="K37" s="12" t="inlineStr"/>
-      <c r="L37" s="12" t="inlineStr"/>
+      <c r="K37" s="13" t="inlineStr"/>
+      <c r="L37" s="13" t="inlineStr"/>
       <c r="M37" s="4" t="inlineStr">
         <is>
           <t>入出力：現場のCSVをそのまま使える</t>
@@ -3228,7 +3369,7 @@
       </c>
     </row>
     <row r="38" ht="79" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>T-I09</t>
         </is>
@@ -3249,17 +3390,17 @@
           <t>テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>T-I09.png</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
         </is>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G38" s="11" t="inlineStr">
         <is>
           <t>設定インポート → ツールバー「列マッピングテンプレート管理」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
         </is>
@@ -3269,18 +3410,18 @@
           <t>テンプレの登録・編集・削除と往復</t>
         </is>
       </c>
-      <c r="I38" s="11" t="inlineStr">
+      <c r="I38" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr">
+      <c r="J38" s="12" t="inlineStr">
         <is>
           <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
-      <c r="K38" s="12" t="inlineStr"/>
-      <c r="L38" s="12" t="inlineStr"/>
+      <c r="K38" s="13" t="inlineStr"/>
+      <c r="L38" s="13" t="inlineStr"/>
       <c r="M38" s="4" t="inlineStr">
         <is>
           <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
@@ -3288,7 +3429,7 @@
       </c>
     </row>
     <row r="39" ht="79" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>T-I19</t>
         </is>
@@ -3309,17 +3450,17 @@
           <t>テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>T-I19.png</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
         </is>
@@ -3329,18 +3470,18 @@
           <t>一括登録と10MB超の扱い</t>
         </is>
       </c>
-      <c r="I39" s="11" t="inlineStr">
+      <c r="I39" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr">
+      <c r="J39" s="12" t="inlineStr">
         <is>
           <t>AC-51</t>
         </is>
       </c>
-      <c r="K39" s="12" t="inlineStr"/>
-      <c r="L39" s="12" t="inlineStr"/>
+      <c r="K39" s="13" t="inlineStr"/>
+      <c r="L39" s="13" t="inlineStr"/>
       <c r="M39" s="4" t="inlineStr">
         <is>
           <t>入出力：マッピングの一括運用</t>
@@ -3348,7 +3489,7 @@
       </c>
     </row>
     <row r="40" ht="79" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>T-E04</t>
         </is>
@@ -3369,17 +3510,17 @@
           <t>専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>T-E04.png</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
         </is>
       </c>
-      <c r="G40" s="10" t="inlineStr">
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
         </is>
@@ -3389,18 +3530,18 @@
           <t>選んだ項目だけ・対象数だけ出るか</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="I40" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="J40" s="12" t="inlineStr">
         <is>
           <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
-      <c r="K40" s="12" t="inlineStr"/>
-      <c r="L40" s="12" t="inlineStr"/>
+      <c r="K40" s="13" t="inlineStr"/>
+      <c r="L40" s="13" t="inlineStr"/>
       <c r="M40" s="4" t="inlineStr">
         <is>
           <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
@@ -3408,7 +3549,7 @@
       </c>
     </row>
     <row r="41" ht="64" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>T-E09</t>
         </is>
@@ -3429,17 +3570,17 @@
           <t>実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>T-E09.png</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
         </is>
       </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
         </is>
@@ -3449,18 +3590,18 @@
           <t>実績と同時選択のファイル数</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr">
+      <c r="I41" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr">
+      <c r="J41" s="12" t="inlineStr">
         <is>
           <t>AC-25</t>
         </is>
       </c>
-      <c r="K41" s="12" t="inlineStr"/>
-      <c r="L41" s="12" t="inlineStr"/>
+      <c r="K41" s="13" t="inlineStr"/>
+      <c r="L41" s="13" t="inlineStr"/>
       <c r="M41" s="4" t="inlineStr">
         <is>
           <t>入出力：渡し先に合わせて出せる</t>
@@ -3468,7 +3609,7 @@
       </c>
     </row>
     <row r="42" ht="49" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>T-E07</t>
         </is>
@@ -3489,17 +3630,17 @@
           <t>警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>T-E07.png</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
         </is>
       </c>
-      <c r="G42" s="10" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
         </is>
@@ -3509,18 +3650,18 @@
           <t>未選択で出力されないか</t>
         </is>
       </c>
-      <c r="I42" s="11" t="inlineStr">
+      <c r="I42" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr">
+      <c r="J42" s="12" t="inlineStr">
         <is>
           <t>AC-27</t>
         </is>
       </c>
-      <c r="K42" s="12" t="inlineStr"/>
-      <c r="L42" s="12" t="inlineStr"/>
+      <c r="K42" s="13" t="inlineStr"/>
+      <c r="L42" s="13" t="inlineStr"/>
       <c r="M42" s="4" t="inlineStr">
         <is>
           <t>入出力：空振りを防ぐ</t>
@@ -3528,7 +3669,7 @@
       </c>
     </row>
     <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>T-E08</t>
         </is>
@@ -3549,17 +3690,17 @@
           <t>日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>T-E08.png</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
         </is>
       </c>
-      <c r="G43" s="10" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
         </is>
@@ -3569,18 +3710,18 @@
           <t>Excelで文字化けしないか</t>
         </is>
       </c>
-      <c r="I43" s="11" t="inlineStr">
+      <c r="I43" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr">
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>AC-28</t>
         </is>
       </c>
-      <c r="K43" s="12" t="inlineStr"/>
-      <c r="L43" s="12" t="inlineStr"/>
+      <c r="K43" s="13" t="inlineStr"/>
+      <c r="L43" s="13" t="inlineStr"/>
       <c r="M43" s="4" t="inlineStr">
         <is>
           <t>入出力：そのまま提出できる</t>
@@ -3588,7 +3729,7 @@
       </c>
     </row>
     <row r="44" ht="49" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>T-N01</t>
         </is>
@@ -3609,17 +3750,17 @@
           <t>設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>T-N01.png</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>設定取込データと実績取込データの一覧＋各タブ（計4枚）</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="G44" s="11" t="inlineStr">
         <is>
           <t>設定取込データ（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績取込データ … 月別データ／日別データタブ</t>
         </is>
@@ -3629,26 +3770,26 @@
           <t>元データとタブの構成</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
+      <c r="I44" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="J44" s="12" t="inlineStr">
         <is>
           <t>AC-39</t>
         </is>
       </c>
-      <c r="K44" s="12" t="inlineStr"/>
-      <c r="L44" s="12" t="inlineStr"/>
+      <c r="K44" s="13" t="inlineStr"/>
+      <c r="L44" s="13" t="inlineStr"/>
       <c r="M44" s="4" t="inlineStr">
         <is>
           <t>入出力：原因を追える</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="64" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="45" ht="79" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>T-N02</t>
         </is>
@@ -3661,7 +3802,7 @@
       <c r="C45" s="4" t="inlineStr">
         <is>
           <t>【前提】S-05 S-06
-【操作】設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
+【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3669,17 +3810,17 @@
           <t>プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>T-N02.png</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
         </is>
       </c>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>設定取込データ／実績取込データ … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
         </is>
@@ -3689,18 +3830,18 @@
           <t>差分がdata/16・17と一致するか</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>AC-50</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr"/>
-      <c r="L45" s="12" t="inlineStr"/>
+      <c r="K45" s="13" t="inlineStr"/>
+      <c r="L45" s="13" t="inlineStr"/>
       <c r="M45" s="4" t="inlineStr">
         <is>
           <t>データ保全：取り込む前に気づける</t>
@@ -3708,7 +3849,7 @@
       </c>
     </row>
     <row r="46" ht="49" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>T-N03</t>
         </is>
@@ -3729,17 +3870,17 @@
           <t>2経路とも到達する（不通=0）</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>T-N03.png</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>人件費実績→実績取込データ／実績取込データ→人件費実績 の到達直後（2枚）</t>
         </is>
       </c>
-      <c r="G46" s="10" t="inlineStr">
+      <c r="G46" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 「実績取込データへ」／実績取込データ → 「人件費実績へ」（相互導線）</t>
         </is>
@@ -3749,18 +3890,18 @@
           <t>2経路とも到達するか</t>
         </is>
       </c>
-      <c r="I46" s="11" t="inlineStr">
+      <c r="I46" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr">
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>AC-30</t>
         </is>
       </c>
-      <c r="K46" s="12" t="inlineStr"/>
-      <c r="L46" s="12" t="inlineStr"/>
+      <c r="K46" s="13" t="inlineStr"/>
+      <c r="L46" s="13" t="inlineStr"/>
       <c r="M46" s="4" t="inlineStr">
         <is>
           <t>画面：操作が最後まで通る</t>
@@ -3768,7 +3909,7 @@
       </c>
     </row>
     <row r="47" ht="49" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>T-Z01</t>
         </is>
@@ -3789,17 +3930,17 @@
           <t>件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>T-Z01.png</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
         </is>
       </c>
-      <c r="G47" s="10" t="inlineStr">
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
         </is>
@@ -3809,18 +3950,18 @@
           <t>移行前後で差分0件か</t>
         </is>
       </c>
-      <c r="I47" s="11" t="inlineStr">
+      <c r="I47" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr">
+      <c r="J47" s="12" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
-      <c r="K47" s="12" t="inlineStr"/>
-      <c r="L47" s="12" t="inlineStr"/>
+      <c r="K47" s="13" t="inlineStr"/>
+      <c r="L47" s="13" t="inlineStr"/>
       <c r="M47" s="4" t="inlineStr">
         <is>
           <t>移行：既存顧客が壊れない</t>
@@ -3828,7 +3969,7 @@
       </c>
     </row>
     <row r="48" ht="49" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>T-Z02</t>
         </is>
@@ -3849,17 +3990,17 @@
           <t>適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>T-Z02.png</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
         </is>
       </c>
-      <c r="G48" s="10" t="inlineStr">
+      <c r="G48" s="11" t="inlineStr">
         <is>
           <t>従業員詳細 → 設定変更履歴／従業員設定履歴 … 適用日付の空欄</t>
         </is>
@@ -3869,18 +4010,18 @@
           <t>適用日付の空欄が0件か</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr">
+      <c r="I48" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr">
+      <c r="J48" s="12" t="inlineStr">
         <is>
           <t>AC-02</t>
         </is>
       </c>
-      <c r="K48" s="12" t="inlineStr"/>
-      <c r="L48" s="12" t="inlineStr"/>
+      <c r="K48" s="13" t="inlineStr"/>
+      <c r="L48" s="13" t="inlineStr"/>
       <c r="M48" s="4" t="inlineStr">
         <is>
           <t>移行：履歴の起点を作る</t>
@@ -3888,7 +4029,7 @@
       </c>
     </row>
     <row r="49" ht="49" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>T-Z03</t>
         </is>
@@ -3909,17 +4050,17 @@
           <t>3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>T-Z03.png</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>移行前後の人件費実績 月別実績（直近3か月・金額が同じであること）</t>
         </is>
       </c>
-      <c r="G49" s="10" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ … 移行前後の直近3か月</t>
         </is>
@@ -3929,18 +4070,18 @@
           <t>過去3か月の金額が変わらないか</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr">
+      <c r="I49" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr">
+      <c r="J49" s="12" t="inlineStr">
         <is>
           <t>AC-03</t>
         </is>
       </c>
-      <c r="K49" s="12" t="inlineStr"/>
-      <c r="L49" s="12" t="inlineStr"/>
+      <c r="K49" s="13" t="inlineStr"/>
+      <c r="L49" s="13" t="inlineStr"/>
       <c r="M49" s="4" t="inlineStr">
         <is>
           <t>移行：過去が動かない</t>
@@ -3948,7 +4089,7 @@
       </c>
     </row>
     <row r="50" ht="49" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>T-Z04</t>
         </is>
@@ -3969,17 +4110,17 @@
           <t>閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>T-Z04.png</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="F50" s="10" t="inlineStr">
         <is>
           <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
         </is>
       </c>
-      <c r="G50" s="10" t="inlineStr">
+      <c r="G50" s="11" t="inlineStr">
         <is>
           <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
         </is>
@@ -3989,18 +4130,18 @@
           <t>PC・モバイルとも開くか</t>
         </is>
       </c>
-      <c r="I50" s="11" t="inlineStr">
+      <c r="I50" s="12" t="inlineStr">
         <is>
           <t>（ヘルプ記載なし・画面構成）</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr">
+      <c r="J50" s="12" t="inlineStr">
         <is>
           <t>AC-29</t>
         </is>
       </c>
-      <c r="K50" s="12" t="inlineStr"/>
-      <c r="L50" s="12" t="inlineStr"/>
+      <c r="K50" s="13" t="inlineStr"/>
+      <c r="L50" s="13" t="inlineStr"/>
       <c r="M50" s="4" t="inlineStr">
         <is>
           <t>画面：たどり着ける</t>
@@ -4008,7 +4149,7 @@
       </c>
     </row>
     <row r="51" ht="49" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>T-Z05</t>
         </is>
@@ -4029,17 +4170,17 @@
           <t>すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>T-Z05.png</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
         </is>
       </c>
-      <c r="G51" s="10" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
         </is>
@@ -4049,18 +4190,18 @@
           <t>75本の遷移と表示規則</t>
         </is>
       </c>
-      <c r="I51" s="11" t="inlineStr">
+      <c r="I51" s="12" t="inlineStr">
         <is>
           <t>（ヘルプ記載なし・遷移網羅）</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr">
+      <c r="J51" s="12" t="inlineStr">
         <is>
           <t>AC-30 AC-01</t>
         </is>
       </c>
-      <c r="K51" s="12" t="inlineStr"/>
-      <c r="L51" s="12" t="inlineStr"/>
+      <c r="K51" s="13" t="inlineStr"/>
+      <c r="L51" s="13" t="inlineStr"/>
       <c r="M51" s="4" t="inlineStr">
         <is>
           <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
@@ -4106,81 +4247,81 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>金額の算式を検算するケース。先に「準備」シートのC-000（データの初期化）を実施する。計算根拠の列に算式と、その根拠となる判断を記載している。</t>
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>金額の算式を検算するケース。先頭のC-000（データの初期化）を必ず実施してから始める。最後のC-008は2026-05の金額を変えるため、順番を入れ替えないこと。</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>検証ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>検証内容</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>入力値</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>スクショファイル名</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>スクショ（撮るもの）</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>確認ポイント</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>ヘルプページ該当箇所</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>対応受入条件</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>実際の値</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>計算根拠</t>
         </is>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>C-000</t>
         </is>
@@ -4201,17 +4342,17 @@
           <t>従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>C-000.png</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>初期化後の従業員一覧（12名）と人件費実績（未締め・S-05時点の金額）</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未締めに戻す）</t>
         </is>
@@ -4221,18 +4362,18 @@
           <t>S-05時点の値に戻ったか</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>（初期化のため対応なし）</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K3" s="12" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr"/>
+      <c r="K3" s="13" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr">
         <is>
           <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
@@ -4240,7 +4381,7 @@
       </c>
     </row>
     <row r="4" ht="64" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>C-001</t>
         </is>
@@ -4261,17 +4402,17 @@
           <t>EMP-002＝285,250（概算280,000＋深夜残業代5,250＝1,750×1.5×2h）／EMP-007＝311,250（概算300,000＋深夜残業代11,250＝1,875×1.5×4h）。いずれも差分0円</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>C-001.png</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
         </is>
@@ -4281,18 +4422,18 @@
           <t>概算＋深夜＝実績給与か</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr"/>
+      <c r="K4" s="13" t="inlineStr"/>
+      <c r="L4" s="13" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
           <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・暫定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
@@ -4300,7 +4441,7 @@
       </c>
     </row>
     <row r="5" ht="79" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>C-003</t>
         </is>
@@ -4321,17 +4462,17 @@
           <t>EMP-001＝338,000（概算320,000＋深夜18,000＝2,000×1.5×6h）／EMP-005＝382,812（概算350,000＋深夜32,812＝2,187×1.5×10h）／EMP-003＝144,000（深夜なし）。ヘルプ人件費は実績給与×ヘルプ時間÷総労働時間で按分し応援先へ振替（EMP-001＝43,232／EMP-003＝24,000／EMP-005＝72,424）</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>C-003.png</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
         </is>
@@ -4341,18 +4482,18 @@
           <t>ヘルプ人件費が按分で振替されるか</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>AC-10 AC-14</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr"/>
+      <c r="K5" s="13" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr">
         <is>
           <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
@@ -4360,7 +4501,7 @@
       </c>
     </row>
     <row r="6" ht="49" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>C-005</t>
         </is>
@@ -4381,17 +4522,17 @@
           <t>店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>C-005.png</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
         </is>
@@ -4401,18 +4542,18 @@
           <t>店舗別合計＝全社（差0円）か</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>AC-11</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr"/>
+      <c r="K6" s="13" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr">
         <is>
           <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
@@ -4420,7 +4561,7 @@
       </c>
     </row>
     <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>C-006</t>
         </is>
@@ -4441,17 +4582,17 @@
           <t>6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>C-006.png</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
         </is>
@@ -4461,18 +4602,18 @@
           <t>所定労働日割になっているか</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>AC-12 AC-04</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr"/>
-      <c r="L7" s="12" t="inlineStr"/>
+      <c r="K7" s="13" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr">
         <is>
           <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
@@ -4480,7 +4621,7 @@
       </c>
     </row>
     <row r="8" ht="49" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>C-011</t>
         </is>
@@ -4501,17 +4642,17 @@
           <t>5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>C-011.png</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
         </is>
@@ -4521,18 +4662,18 @@
           <t>時給者の概算と月中改定</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>AC-13</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr"/>
-      <c r="L8" s="12" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr">
         <is>
           <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
@@ -4540,182 +4681,182 @@
       </c>
     </row>
     <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>C-013</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-03 S-07
+【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>判断7（暫定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。5/8のヘルプ人件費＝実績給与338,000×11h÷総労働172h＝21,616円で、計上先はS02。みなし労働時間差分＝172−(160＋20)＝−8h（未達はマイナス表示・減額なし＝判断8）</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>C-013.png</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>深夜1.5倍とヘルプの按分単価</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 人件費の計算方法</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>AC-10 AC-14</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>深夜残業代＝基礎時給×1.5（判断7・暫定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・暫定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="49" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>C-017</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>交通費の計上先</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-03 S-04
+【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>C-017.png</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>交通費が給与と別費目か</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>AC-15</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr"/>
+      <c r="L10" s="13" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>交通費は給与と別の独立費目（判断6・確定）。通勤交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>C-008</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>締めの前後で数字が動かないこと</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>【前提】C-000 S-07
 【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>（a）5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>C-008.png</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>締め前後で差0円・解除後に再計算</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>AC-16 AC-17</t>
         </is>
       </c>
-      <c r="K9" s="12" t="inlineStr"/>
-      <c r="L9" s="12" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="K11" s="13" t="inlineStr"/>
+      <c r="L11" s="13" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>C-013</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>判断7（暫定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。5/8のヘルプ人件費＝実績給与338,000×11h÷総労働172h＝21,616円で、計上先はS02。みなし労働時間差分＝172−(160＋20)＝−8h（未達はマイナス表示・減額なし＝判断8）</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>C-013.png</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>深夜1.5倍とヘルプの按分単価</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>AC-10 AC-14</t>
-        </is>
-      </c>
-      <c r="K10" s="12" t="inlineStr"/>
-      <c r="L10" s="12" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>深夜残業代＝基礎時給×1.5（判断7・暫定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・暫定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="49" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>C-017</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>交通費の計上先</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>C-017.png</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>交通費が給与と別費目か</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>AC-15</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="inlineStr"/>
-      <c r="L11" s="12" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>交通費は給与と別の独立費目（判断6・確定）。通勤交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
         </is>
       </c>
     </row>
@@ -4758,81 +4899,81 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>検証を始める前の準備。上から順に実施する。★S-02（算式の確定）とS-03（サンプルデータの再作成）はゲート。準備行のため受入条件・ヘルプページとの対応はない。</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>検証ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>検証内容</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>操作・前提条件</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>スクショファイル名</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>スクショ（撮るもの）</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>確認ポイント</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>ヘルプページ該当箇所</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>対応受入条件</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>実際の値</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>計算根拠</t>
         </is>
       </c>
     </row>
     <row r="3" ht="49" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>S-01</t>
         </is>
@@ -4852,17 +4993,17 @@
           <t>サイドバーに「従業員管理」が表示される／モックのトップが表示される</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>S-01.png</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>サイドバーに「従業員管理」が展開された状態</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>サイドバー「従業員管理」（PCはホバー展開）／仕様モックのトップ</t>
         </is>
@@ -4872,22 +5013,22 @@
           <t>メニューが出るか／モックが開くか</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K3" s="12" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr"/>
+      <c r="K3" s="13" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="79" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>S-02</t>
         </is>
@@ -4907,13 +5048,13 @@
           <t>6件が確定し文書化されている（仕様書 第5部 11-A・11-C）</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr"/>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>不要（文書で確認）</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>（画面操作なし・仕様書 第5部 11-A/11-C の確認）</t>
         </is>
@@ -4923,18 +5064,18 @@
           <t>6件の算式が確定・文書化されているか</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-12 AC-15</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr"/>
+      <c r="K4" s="13" t="inlineStr"/>
+      <c r="L4" s="13" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額／原則③：人件費は働いた店舗に付ける／計算：月中改定の日割り／原則③：交通費の帰属</t>
@@ -4942,7 +5083,7 @@
       </c>
     </row>
     <row r="5" ht="49" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>S-03</t>
         </is>
@@ -4963,13 +5104,13 @@
           <t>全行が算式で再現でき、日次合計＝月次・店舗別合計＝全社（差0円）</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr"/>
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>不要（データで確認）</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>（画面操作なし・data/05・06 の確認）</t>
         </is>
@@ -4979,18 +5120,18 @@
           <t>算式で全行が再現できるか</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr"/>
+      <c r="K5" s="13" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額</t>
@@ -4998,7 +5139,7 @@
       </c>
     </row>
     <row r="6" ht="49" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>S-04</t>
         </is>
@@ -5019,17 +5160,17 @@
           <t>従業員一覧に12名が表示される</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>S-04.png</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>従業員一覧に12名が表示された全体</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>従業員一覧（サイドバー → 従業員管理 → 従業員一覧）</t>
         </is>
@@ -5039,22 +5180,22 @@
           <t>12名が一覧に出るか</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr"/>
+      <c r="K6" s="13" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="49" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>S-05</t>
         </is>
@@ -5075,17 +5216,17 @@
           <t>履歴に適用済3・予約中1が入る／人件費実績に5名分が表示される</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>S-05.png</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>設定変更履歴（予約中の行が見える）／人件費実績 月別実績の5行</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>従業員設定履歴／人件費実績（月別実績タブ）</t>
         </is>
@@ -5095,22 +5236,22 @@
           <t>履歴に予約中1件・実績5名が出るか</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr"/>
-      <c r="L7" s="12" t="inlineStr"/>
+      <c r="K7" s="13" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="94" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>S-06</t>
         </is>
@@ -5131,13 +5272,13 @@
           <t>5ファイルがアップロード可能な状態／設定が欠落した従業員が1名いる</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr"/>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>不要（ファイル準備のみ）</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>（画面操作なし・取込ファイルの用意）</t>
         </is>
@@ -5147,22 +5288,22 @@
           <t>5ファイルがアップロードできる状態か</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr"/>
-      <c r="L8" s="12" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="49" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>S-07</t>
         </is>
@@ -5183,13 +5324,13 @@
           <t>以降の計算ケースで同じ入力値を使う</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>不要（値の確定のみ）</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>（画面操作なし・基礎時給と所定労働日数の確定）</t>
         </is>
@@ -5199,22 +5340,22 @@
           <t>基礎時給と所定労働日数が確定しているか</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K9" s="12" t="inlineStr"/>
-      <c r="L9" s="12" t="inlineStr"/>
+      <c r="K9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr"/>
       <c r="M9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>S-08</t>
         </is>
@@ -5235,17 +5376,17 @@
           <t>ボタンが「2026-05 締め」になっている</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>S-08.png</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>人件費実績 月別実績（ボタンが「2026-05 締め」＝未締め）</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 年月2026-05（締め状態の確認）</t>
         </is>
@@ -5255,22 +5396,22 @@
           <t>2026-05が未締めか</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr"/>
-      <c r="L10" s="12" t="inlineStr"/>
+      <c r="K10" s="13" t="inlineStr"/>
+      <c r="L10" s="13" t="inlineStr"/>
       <c r="M10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="49" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>S-09</t>
         </is>
@@ -5291,17 +5432,17 @@
           <t>突合シート M-01〜M-06 が埋まった状態</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>S-09.png</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>移行前の従業員一覧と人件費実績（比較の元になるため必須）</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>従業員一覧（CSVエクスポート）／人件費実績 月別実績（直近3か月）</t>
         </is>
@@ -5311,22 +5452,22 @@
           <t>移行前の値を控えたか</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr"/>
-      <c r="L11" s="12" t="inlineStr"/>
+      <c r="K11" s="13" t="inlineStr"/>
+      <c r="L11" s="13" t="inlineStr"/>
       <c r="M11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="49" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>S-10</t>
         </is>
@@ -5347,13 +5488,13 @@
           <t>店長でログインでき、従業員管理のメニューが表示される</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>（画面操作なし・店長スコープのアカウント用意）</t>
         </is>
@@ -5363,22 +5504,22 @@
           <t>店長アカウントでログインできるか</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="12" t="inlineStr"/>
-      <c r="L12" s="12" t="inlineStr"/>
+      <c r="K12" s="13" t="inlineStr"/>
+      <c r="L12" s="13" t="inlineStr"/>
       <c r="M12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="49" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>S-11</t>
         </is>
@@ -5399,13 +5540,13 @@
           <t>移行を検証枠内で実行できる段取りができている</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>（画面操作なし・移行スクリプトの段取り）</t>
         </is>
@@ -5415,18 +5556,18 @@
           <t>移行を実行できる状態か</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K13" s="12" t="inlineStr"/>
-      <c r="L13" s="12" t="inlineStr"/>
+      <c r="K13" s="13" t="inlineStr"/>
+      <c r="L13" s="13" t="inlineStr"/>
       <c r="M13" s="4" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5468,81 +5609,81 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>画面を操作しても判別できない条件。実装物（スキーマ・API・コード）を提示してもらって確認する。エンジニアの同席が必要。</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>検証ID</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>検証内容</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>操作・前提条件</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>スクショファイル名</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>スクショ（撮るもの）</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>確認ポイント</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>ヘルプページ該当箇所</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>対応受入条件</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>実際の値</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>計算根拠</t>
         </is>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>R-01</t>
         </is>
@@ -5563,17 +5704,17 @@
           <t>①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>R-01.png</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="11" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
@@ -5583,18 +5724,18 @@
           <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>AC-07 AC-40 AC-47</t>
         </is>
       </c>
-      <c r="K3" s="12" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr"/>
+      <c r="K3" s="13" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr"/>
       <c r="M3" s="4" t="inlineStr">
         <is>
           <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
@@ -5602,7 +5743,7 @@
       </c>
     </row>
     <row r="4" ht="49" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>R-02</t>
         </is>
@@ -5623,17 +5764,17 @@
           <t>①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>R-02.png</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
@@ -5643,18 +5784,18 @@
           <t>APIでも店長が締められないか</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>AC-16 AC-41</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr"/>
+      <c r="K4" s="13" t="inlineStr"/>
+      <c r="L4" s="13" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
           <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
@@ -5662,7 +5803,7 @@
       </c>
     </row>
     <row r="5" ht="64" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>R-03</t>
         </is>
@@ -5683,17 +5824,17 @@
           <t>①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>R-03.png</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
@@ -5703,18 +5844,18 @@
           <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr"/>
+      <c r="K5" s="13" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr"/>
       <c r="M5" s="4" t="inlineStr">
         <is>
           <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
@@ -5722,7 +5863,7 @@
       </c>
     </row>
     <row r="6" ht="49" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>R-04</t>
         </is>
@@ -5743,17 +5884,17 @@
           <t>同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R-04.png</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
         </is>
@@ -5763,18 +5904,18 @@
           <t>計算ロジックが1箇所か</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>AC-35 AC-11</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr"/>
+      <c r="K6" s="13" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr">
         <is>
           <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
@@ -5782,7 +5923,7 @@
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
@@ -5803,17 +5944,17 @@
           <t>CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>R-05.png</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>列名の対応づけを保持している箇所（DBかコードか）</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
         </is>
@@ -5823,18 +5964,18 @@
           <t>列名がコードに埋まっていないか</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>AC-22 AC-24</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr"/>
-      <c r="L7" s="12" t="inlineStr"/>
+      <c r="K7" s="13" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr">
         <is>
           <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
@@ -5842,7 +5983,7 @@
       </c>
     </row>
     <row r="8" ht="49" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
@@ -5863,17 +6004,17 @@
           <t>設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>R-06.png</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
         </is>
@@ -5883,18 +6024,18 @@
           <t>2つの入口で更新処理が共通か</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>AC-49</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr"/>
-      <c r="L8" s="12" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr">
         <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$N$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$P$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39,7 +39,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF9DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -113,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -137,10 +142,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -149,15 +154,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -525,32 +533,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:P77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="64" customWidth="1" min="4" max="4"/>
-    <col width="62" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="54" customWidth="1" min="7" max="7"/>
-    <col width="58" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="54" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="44" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="68" customHeight="1">
+    <row r="1" ht="83" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>確かめる手順（準備11行＋検証64ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
-実施順を変えてはいけない箇所：①T-A08（勤怠取込）→T-S03（締め）　②T-S03→T-S04・T-D07→T-S05（この3件は締め済みでしか確認できない）　③C-000（初期化）は計算の先頭　④C-008は計算の最後（2026-05のEMP-001を352,286円に変えるためC-013・C-017が合わなくなる）　⑤T-N02の前にdata/02を再投入（T-I03で340,000になっているため差分が0件になる）　⑥削除はEMP-012（T-L10）とEMP-004（T-D08）だけ（この2名のみマスタにしか出てこない）
-列の使い方：画面＝どこを開くか（サイドバーからの経路・タブ・ボタン・モーダル）／確認ポイント＝何を見るか／期待値＝合否の基準／スクショ（撮るもの）＝何が写っていれば証拠になるか／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めてその条件が合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを必ず決める
-色：青＝画面　橙＝スクショ　紫＝ヘルプ・受入条件との対応　黄＝当日の記入欄（実際の値・判定）。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
+実施順を変えてはいけない箇所：①T-A08（勤怠取込）→T-S03（締め）　②T-S03→T-S04・T-D07→T-S05（この3件は締め済みでしか確認できない）　③C-000（初期化）は計算の先頭　④C-008は計算の最後（2026-05のEMP-001を352,286円に変えるためC-013・C-017が合わなくなる）　⑤T-N02の前にdata/02を再投入　⑥削除はEMP-012（T-L10）とEMP-004（T-D08）だけ
+列の使い方：使用する検証データ＝この検証で投入・使用するdataファイル（（投入済み）は準備行で入れたものを見るだけ）／画面＝どこを開くか（サイドバーからの経路・タブ・ボタン・モーダル）／確認ポイント＝何を見るか／期待値＝合否の基準／スクショ（撮るもの）＝何が写っていれば証拠になるか／スクショ貼付欄＝撮った画像をこの列に貼る／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めて合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを決める
+色：緑＝使う検証データ　青＝画面　橙＝スクショ　紫＝ヘルプ・受入条件　黄＝当日の記入欄。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
         </is>
       </c>
     </row>
@@ -577,56 +587,66 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>使用する検証データ</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>期待値</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>スクショファイル名</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>スクショ（撮るもの）</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>スクショ貼付欄</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>確認ポイント</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>ヘルプページ該当箇所</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>対応受入条件</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>実際の値</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>計算根拠</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="49" customHeight="1">
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -649,42 +669,48 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
           <t>サイドバーに「従業員管理」が表示される／モックのトップが表示される</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>S-01.png</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>サイドバーに「従業員管理」が展開された状態</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>サイドバー「従業員管理」（PCはホバー展開）／仕様モックのトップ</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>メニューが出るか／モックが開くか</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="79" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -709,44 +735,50 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
           <t>6件が確定し文書化されている（仕様書 第5部 11-A・11-C）</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>不要（文書で確認）</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>（画面操作なし・仕様書 第5部 11-A/11-C の確認）</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>6件の算式が確定・文書化されているか</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>AC-10 AC-11 AC-12 AC-15</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額／原則③：人件費は働いた店舗に付ける／計算：月中改定の日割り／原則③：交通費の帰属</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="49" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -770,44 +802,50 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>投入する：05・06</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>全行が算式で再現でき、日次合計＝月次・店舗別合計＝全社（差0円）</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>不要（データで確認）</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>（画面操作なし・data/05・06 の確認）</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>算式で全行が再現できるか</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr"/>
-      <c r="M5" s="5" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="49" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -831,44 +869,50 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
+          <t>投入する：01・02・03</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
           <t>従業員一覧に12名が表示される</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>S-04.png</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>従業員一覧に12名が表示された全体</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>従業員一覧（サイドバー → 従業員管理 → 従業員一覧）</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>12名が一覧に出るか</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="49" customHeight="1">
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -892,42 +936,48 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
+          <t>投入する：04・05・06・13</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>履歴に適用済3・予約中1が入る／人件費実績に5名分が表示される</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>S-05.png</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>設定変更履歴（予約中の行が見える）／人件費実績 月別実績の5行</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>従業員設定履歴／人件費実績（月別実績タブ）</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>履歴に予約中1件・実績5名が出るか</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="94" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -953,40 +1003,46 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
+          <t>投入する：取込CSV一式（07〜12・16〜19）</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
           <t>5ファイルがアップロード可能な状態／設定が欠落した従業員が1名いる</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>不要（ファイル準備のみ）</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>（画面操作なし・取込ファイルの用意）</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>5ファイルがアップロードできる状態か</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9" ht="49" customHeight="1">
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -1010,40 +1066,46 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
+          <t>14 勤務データ 2026-06 月中改定</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
           <t>以降の計算ケースで同じ入力値を使う</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>不要（値の確定のみ）</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>（画面操作なし・基礎時給と所定労働日数の確定）</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>基礎時給と所定労働日数が確定しているか</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="34" customHeight="1">
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -1067,44 +1129,50 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
           <t>ボタンが「2026-05 締め」になっている</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>S-08.png</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>人件費実績 月別実績（ボタンが「2026-05 締め」＝未締め）</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 年月2026-05（締め状態の確認）</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>2026-05が未締めか</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11" ht="49" customHeight="1">
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -1128,44 +1196,50 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
+          <t>投入する：15</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>突合シート M-01〜M-06 が埋まった状態</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>S-09.png</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>移行前の従業員一覧と人件費実績（比較の元になるため必須）</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>従業員一覧（CSVエクスポート）／人件費実績 月別実績（直近3か月）</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>移行前の値を控えたか</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="49" customHeight="1">
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -1189,40 +1263,46 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
           <t>店長でログインでき、従業員管理のメニューが表示される</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>（画面操作なし・店長スコープのアカウント用意）</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>店長アカウントでログインできるか</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13" ht="49" customHeight="1">
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -1246,38 +1326,44 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
           <t>移行を検証枠内で実行できる段取りができている</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>（画面操作なし・移行スクリプトの段取り）</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>移行を実行できる状態か</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>（準備のため対応なし）</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr"/>
-      <c r="M13" s="5" t="inlineStr"/>
-      <c r="N13" s="4" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="94" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
@@ -1301,50 +1387,56 @@
 【操作】従業員一覧を開き、列・バッジ・ソート・0件表示を確認</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>12名が表示。12列（名前/従業員コード/所属店舗/ヘルプ先店舗/雇用区分/給与単位/単位給与額/交通費単位/単位交通費/所定労働時間/みなし残業時間/アクション）。雇用区分・給与単位が色分け。EMP-001はヘルプ先2バッジ、EMP-002は空。単位給与額が数値順にソート（1,000→…→410,000）。該当なしで「データはありません。」</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>T-L01.png</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>一覧全体（12行・12列・バッジの色・ソート矢印）と、フィルタで0件にしたときの「データはありません。」</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>従業員一覧 … 表の12列・雇用区分/給与単位のバッジ・列ヘッダーのソート・0件表示</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>12列・バッジ・ソート・0件表示</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="M14" s="12" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr"/>
-      <c r="M14" s="5" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>移行：既存顧客が壊れない</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="49" customHeight="1">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t>一覧</t>
@@ -1366,44 +1458,50 @@
 【操作】1段目＝店舗「渋谷店」／雇用区分「正社員」／名前「田中」、2段目＝月「2026-05」／取込データ を順に適用</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>渋谷店＝3名（EMP-001・002・011）、正社員＝6名、田中＝1名。2段目で対象データが切り替わる</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>T-L08.png</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>1段目と2段目の両方を適用した状態（絞り込み条件と結果件数が同時に写ること）</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr">
         <is>
           <t>従業員一覧 … 1段目フィルタ（店舗/雇用区分/名前検索）と2段目フィルタ（月/取込データ）</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>2段フィルタが効くか</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="L15" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="M15" s="12" t="inlineStr">
         <is>
           <t>AC-33</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr"/>
-      <c r="M15" s="5" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>画面：対象を探せる</t>
         </is>
@@ -1431,50 +1529,56 @@
 【操作】右上「従業員登録」「CSVインポート」「設定・実績エクスポート」、2段目「設定取込データへ」、行の詳細アイコン を順に押す</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>5経路すべて到達（従業員登録／設定インポート／設定・実績エクスポート／設定取込データ／従業員詳細）。不通=0</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>T-L06.png</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>遷移先5画面の到達直後（従業員登録・設定インポート・エクスポート・設定取込データ・従業員詳細）</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="11" t="inlineStr">
         <is>
           <t>従業員一覧 … 右上ツールバー「従業員登録」「CSVインポート」「設定・実績エクスポート」／2段目「設定取込データへ」／行末の詳細アイコン</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>5経路すべて到達するか</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="M16" s="12" t="inlineStr">
         <is>
           <t>AC-30</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="49" customHeight="1">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>一覧</t>
@@ -1496,50 +1600,56 @@
 【操作】EMP-012（山田 さくら・実績データに含まれない末尾の従業員）の削除アイコン →（a）キャンセル →（b）実行</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>05 月次給与実績</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>（a）12名のまま削除されない （b）完了表示のあと11名になる</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>T-L10.png</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>削除の確認ダイアログ／キャンセル後の一覧／実行後の一覧（行が消えたこと）</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="11" t="inlineStr">
         <is>
           <t>従業員一覧 … 行末の削除アイコン → 確認ダイアログ</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>キャンセルで消えない／実行で消えるか</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="L17" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="M17" s="12" t="inlineStr">
         <is>
           <t>AC-34</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr"/>
-      <c r="M17" s="5" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>データ保全：消える操作は確認を経る</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="64" customHeight="1">
+    <row r="18" ht="79" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t>登録</t>
@@ -1561,50 +1671,56 @@
 【操作】従業員登録を開き、項目と通貨表示を確認（単位給与額に 320000 と入力）</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>13項目（名前/従業員コード/所属店舗/ヘルプ先店舗/雇用区分/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。¥320,000 と千区切り表示。適用日付は所定労働時間・みなし残業時間の下の行・初期値は当日</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>T-R02.png</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>登録フォーム全体（単位給与額に320,000と入れ、桁区切りが効いている状態）</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>従業員登録（従業員一覧 右上「従業員登録」から遷移）… 入力フォーム全体と通貨の桁区切り表示</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>項目の過不足と桁区切り表示</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="L18" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="M18" s="12" t="inlineStr">
         <is>
           <t>AC-06</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr"/>
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>原則①：当日・過去日は即時</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="49" customHeight="1">
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t>登録</t>
@@ -1626,44 +1742,50 @@
 【操作】ヘルプ先店舗で青山店＋新宿店を選択 →（a）空のまま登録 →（b）新宿店の選択を外す</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>選択した2店それぞれに交通費欄が出る／（a）必須バリデーションで登録できない／（b）新宿店の欄だけ消え、青山店の入力値は残る</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>T-R04.png</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>ヘルプ先2店選択でヘルプ先交通費欄が出た状態／1店外して欄が消えた状態の2枚</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>従業員登録 … ヘルプ先店舗の複数選択と、その下に自動表示されるヘルプ先交通費の入力欄</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>交通費欄が自動で出る／消えるか</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="L19" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="M19" s="12" t="inlineStr">
         <is>
           <t>AC-15 AC-47</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr"/>
-      <c r="M19" s="5" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>原則③：交通費の帰属／原則③：交通費も働いた店舗の実費で</t>
         </is>
@@ -1691,50 +1813,56 @@
 【操作】（a）必須を埋めて「登録」（適用日付＝当日）（b）入力途中で「キャンセル」（c）ツールバー「従業員一覧へ」「CSVインポート」</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>（a）完了表示のあと一覧へ戻り、登録前より1名増えている （b）一覧へ戻り件数は変わらない （c）従業員一覧／設定インポートへ遷移</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>T-R07.png</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>登録成功後の従業員一覧（新規行が見えること）とキャンセル後の一覧</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>従業員登録 … 下部「登録」「キャンセル」／ツールバー「従業員一覧へ」「CSVインポート」→ 従業員一覧</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>登録される／されないの分岐</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="L20" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="M20" s="12" t="inlineStr">
         <is>
           <t>AC-06 AC-30</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="5" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="5" t="inlineStr"/>
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>原則①：当日・過去日は即時／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="49" customHeight="1">
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t>登録</t>
@@ -1756,50 +1884,56 @@
 【操作】名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額 をそれぞれ空にして「登録」を押す</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>6項目それぞれで 登録=0件・画面遷移=0件（6回とも同じ）。不足している項目名が画面上に表示される</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>T-R10.png</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>必須未入力で「登録」を押した直後（エラー表示と、画面が遷移していないこと）</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>従業員登録 … 必須項目のバリデーション表示（画面に留まること）</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>必須未入力で保存も遷移もしないか</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="L21" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="M21" s="12" t="inlineStr">
         <is>
           <t>AC-43</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr"/>
-      <c r="M21" s="5" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>データ保全：不完全な登録を作らない</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="49" customHeight="1">
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t>詳細</t>
@@ -1821,50 +1955,56 @@
 【操作】EMP-001の詳細を開き、3セクションと履歴の列を確認</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>基本情報／設定変更履歴／給与実績 が表示。基本情報は登録と同項目・同配置。履歴は14列（変更反映日時〜変更ソース の13項目＋操作）。2026-08-01行が「予約中」</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>T-D01.png</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>従業員詳細の全体（基本情報・設定変更履歴・給与実績の3セクションが分かる範囲）</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t>従業員詳細（従業員一覧の詳細アイコンから遷移）… 基本情報／設定変更履歴／給与実績の3セクション</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>3セクションと履歴14列</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="L22" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="M22" s="12" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr"/>
-      <c r="M22" s="5" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="5" t="inlineStr"/>
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>原則①：過去は不変</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="49" customHeight="1">
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t>詳細</t>
@@ -1886,44 +2026,50 @@
 【操作】単位給与額を340,000に変更し、適用日付＝翌月1日で「保存」</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>「（日付）からの適用を予約しました」と表示。履歴に「予約中」が1行追加。一覧の単位給与額は320,000のまま</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>T-D04.png</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>保存直後のトースト「◯月◯日からの適用を予約しました」／履歴の「予約中」行／一覧の値が未変更であること の3枚</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>従業員詳細 … 基本情報の単位給与額と適用日付 → 下部「保存」→ 従業員一覧のトーストと一覧値</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>予約になり一覧の値が変わらないか</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="L23" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="M23" s="12" t="inlineStr">
         <is>
           <t>AC-04</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>原則①：未来日は予約になる</t>
         </is>
@@ -1951,50 +2097,56 @@
 【操作】適用日を迎えた状態を作って、一覧と履歴を再表示する。次の3通りから検証環境で可能な方法を選ぶ：①前日に予約を仕込み翌日に確認（8/12仕込み→8/13確認）②システム日付を進める ③予約適用のバッチを手動実行する</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>一覧が340,000に変わり、履歴が「適用中」、旧行が「過去」になる</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>T-D05.png</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>適用日を迎えた後の一覧の値と、履歴のステータスが「適用中」に変わった行</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>従業員詳細（予約を仕込む）→ 翌日の従業員一覧と設定変更履歴のステータス</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>適用日に自動で切り替わるか</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="L24" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr">
+      <c r="M24" s="12" t="inlineStr">
         <is>
           <t>AC-05</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr"/>
-      <c r="N24" s="7" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr"/>
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>原則①：予約が自動で効く</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="49" customHeight="1">
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
           <t>詳細</t>
@@ -2016,50 +2168,56 @@
 【操作】EMP-002の単位給与額を290,000に変更し、適用日付＝当日で「保存」</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>「即時反映しました」と表示。一覧が290,000になる</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>T-D06.png</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>トースト「即時反映しました」と、一覧の値が290,000になった状態</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="11" t="inlineStr">
         <is>
           <t>従業員詳細 … 適用日付＝当日で「保存」→ 従業員一覧の値</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>即時反映され一覧の値が変わるか</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="L25" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="M25" s="12" t="inlineStr">
         <is>
           <t>AC-06</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>原則①：当日・過去日は即時</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="49" customHeight="1">
+    <row r="26" ht="64" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t>詳細</t>
@@ -2081,44 +2239,50 @@
 【操作】給与実績セクションで 月次タブ（概算⇄実績・年フィルタ）→ 日次タブ（月フィルタ）→ 各タブでCSVエクスポート</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>月次17列（年月〜深夜残業代＋交通費＋総支給額）／日次14列。個人向けに列を絞った構成で、人件費実績（26列/21列）とは別。フィルタで期間が絞られる。表示中の内容がBOM付きCSVで出力される</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>T-D09.png</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>月次タブ（概算／実績の両方）と日次タブ／出力したCSVをExcelで開いた画面</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>従業員詳細 → 給与実績セクション … 月次タブ（概算⇄実績の切替・年フィルタ）／日次タブ（月フィルタ）／各タブのCSVエクスポート</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>タブ切替とCSVの中身が変わるか</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="L26" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr">
+      <c r="M26" s="12" t="inlineStr">
         <is>
           <t>AC-35 AC-36</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr"/>
-      <c r="N26" s="7" t="inlineStr">
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="5" t="inlineStr"/>
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>計算：個人単位でも同じ数字／入出力：画面の内容と一致</t>
         </is>
@@ -2146,50 +2310,56 @@
 【操作】EMP-004（山本 健／実績データにも取込CSVにも含まれない）の詳細を開き「従業員削除」→（a）キャンセル →（b）実行、（c）別の従業員で「一覧へ戻る」</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>（a）削除されず件数が変わらない （b）確認のあと削除される （c）一覧へ戻る（保存されない）</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>T-D08.png</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>削除の確認モーダル／実行後の一覧（行が消えたこと）</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="11" t="inlineStr">
         <is>
           <t>従業員詳細 … 下部「従業員削除」→ 確認モーダル／「一覧へ戻る」→ 従業員一覧</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>キャンセルで消えない／実行で消えるか</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="L27" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="M27" s="12" t="inlineStr">
         <is>
           <t>AC-34 AC-30</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="7" t="inlineStr">
         <is>
           <t>データ保全：消える操作は確認を経る／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="34" customHeight="1">
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2211,50 +2381,56 @@
 【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>履歴が1行増える。既存行の値の差分＝0</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>T-H01.png</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="11" t="inlineStr">
         <is>
           <t>従業員設定履歴 … 変更前後の行（既存行が書き換わらないこと）</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>既存行が書き換わらないか</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="L28" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="K28" s="11" t="inlineStr">
+      <c r="M28" s="12" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr"/>
-      <c r="M28" s="5" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr">
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="7" t="inlineStr">
         <is>
           <t>原則①：過去は不変</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="49" customHeight="1">
+    <row r="29" ht="64" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2276,50 +2452,56 @@
 【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>T-H02.png</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="11" t="inlineStr">
         <is>
           <t>従業員設定履歴 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>2つの日時が別で記録されるか</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="L29" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="M29" s="12" t="inlineStr">
         <is>
           <t>AC-08 AC-09</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="7" t="inlineStr">
         <is>
           <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="64" customHeight="1">
+    <row r="30" ht="79" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2341,44 +2523,50 @@
 【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>T-H04.png</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="11" t="inlineStr">
         <is>
           <t>従業員設定履歴 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>絞り込み後の行だけ出力されるか</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="L30" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr">
+      <c r="M30" s="12" t="inlineStr">
         <is>
           <t>AC-33 AC-36 AC-30</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr"/>
-      <c r="M30" s="5" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="5" t="inlineStr"/>
+      <c r="P30" s="7" t="inlineStr">
         <is>
           <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
         </is>
@@ -2406,50 +2594,56 @@
 【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>T-A02.png</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>モード切替で列が増減するか</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr">
+      <c r="L31" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="K31" s="11" t="inlineStr">
+      <c r="M31" s="12" t="inlineStr">
         <is>
           <t>AC-10 AC-31</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr"/>
-      <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr">
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="7" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額／画面：状態が漏れない</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="49" customHeight="1">
+    <row r="32" ht="64" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
           <t>実績</t>
@@ -2471,44 +2665,50 @@
 【操作】人件費実績で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>T-A09.png</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>設定編集モーダル（項目が見える状態）／更新保存後の人件費実績／従業員詳細の設定変更履歴に行が増えたこと</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 人件費実績／確認は従業員詳細の設定変更履歴</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>モーダル編集でも履歴が残るか</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="L32" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="K32" s="11" t="inlineStr">
+      <c r="M32" s="12" t="inlineStr">
         <is>
           <t>AC-49</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr"/>
-      <c r="M32" s="5" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="5" t="inlineStr"/>
+      <c r="P32" s="7" t="inlineStr">
         <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
@@ -2536,50 +2736,56 @@
 【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>T-A05.png</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>日別に概算モードが無いか</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr">
+      <c r="L33" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="K33" s="11" t="inlineStr">
+      <c r="M33" s="12" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr"/>
-      <c r="M33" s="5" t="inlineStr"/>
-      <c r="N33" s="7" t="inlineStr">
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="7" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="49" customHeight="1">
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
           <t>実績</t>
@@ -2601,50 +2807,56 @@
 【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t>T-A07.png</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="11" t="inlineStr">
         <is>
           <t>人件費実績 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="K34" s="7" t="inlineStr">
         <is>
           <t>表示中の内容が出力されるか</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="L34" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="K34" s="11" t="inlineStr">
+      <c r="M34" s="12" t="inlineStr">
         <is>
           <t>AC-36</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="5" t="inlineStr"/>
+      <c r="P34" s="7" t="inlineStr">
         <is>
           <t>入出力：画面の内容と一致</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="49" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
           <t>実績</t>
@@ -2666,50 +2878,56 @@
 【操作】人件費実績の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>T-A08.png</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>進捗が出て他操作を受け付けないか</t>
         </is>
       </c>
-      <c r="J35" s="11" t="inlineStr">
+      <c r="L35" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="K35" s="11" t="inlineStr">
+      <c r="M35" s="12" t="inlineStr">
         <is>
           <t>AC-48</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr"/>
-      <c r="N35" s="7" t="inlineStr">
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="7" t="inlineStr">
         <is>
           <t>入出力：勤怠実績を取り込める</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="34" customHeight="1">
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t>締め</t>
@@ -2731,50 +2949,56 @@
 【操作】月別実績タブと日別実績タブを順に開く</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>月別のみ「2026-05 締め」が表示。日別には表示されない</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>T-S01.png</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="11" t="inlineStr">
         <is>
           <t>人件費実績 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>締めが月別タブにだけ出るか</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="L36" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="K36" s="11" t="inlineStr">
+      <c r="M36" s="12" t="inlineStr">
         <is>
           <t>AC-18</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr"/>
-      <c r="M36" s="5" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr">
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="5" t="inlineStr"/>
+      <c r="P36" s="7" t="inlineStr">
         <is>
           <t>原則②：締めの単位は月</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="49" customHeight="1">
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t>締め</t>
@@ -2796,50 +3020,56 @@
 【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>T-S03.png</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
         </is>
       </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>確認モーダルを経て締まるか</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr">
+      <c r="L37" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="K37" s="11" t="inlineStr">
+      <c r="M37" s="12" t="inlineStr">
         <is>
           <t>AC-16 AC-19 AC-32</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr"/>
-      <c r="M37" s="5" t="inlineStr"/>
-      <c r="N37" s="7" t="inlineStr">
+      <c r="N37" s="5" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr"/>
+      <c r="P37" s="7" t="inlineStr">
         <is>
           <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="34" customHeight="1">
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
           <t>締め</t>
@@ -2861,50 +3091,56 @@
 【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>編集できない（または反映されない）</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>T-S04.png</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="11" t="inlineStr">
         <is>
           <t>人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>締め後に金額が動かないか</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr">
+      <c r="L38" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
-      <c r="K38" s="11" t="inlineStr">
+      <c r="M38" s="12" t="inlineStr">
         <is>
           <t>AC-16</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr">
+      <c r="N38" s="5" t="inlineStr"/>
+      <c r="O38" s="5" t="inlineStr"/>
+      <c r="P38" s="7" t="inlineStr">
         <is>
           <t>原則②：締めたら動かない</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="34" customHeight="1">
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
           <t>締め</t>
@@ -2926,50 +3162,56 @@
 【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>T-D07.png</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="11" t="inlineStr">
         <is>
           <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>警告が出て反映されないか</t>
         </is>
       </c>
-      <c r="J39" s="11" t="inlineStr">
+      <c r="L39" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
-      <c r="K39" s="11" t="inlineStr">
+      <c r="M39" s="12" t="inlineStr">
         <is>
           <t>AC-20</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr"/>
-      <c r="M39" s="5" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr">
+      <c r="N39" s="5" t="inlineStr"/>
+      <c r="O39" s="5" t="inlineStr"/>
+      <c r="P39" s="7" t="inlineStr">
         <is>
           <t>原則②：遡及は黙って捨てない</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="49" customHeight="1">
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
           <t>締め</t>
@@ -2991,50 +3233,56 @@
 【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>T-S05.png</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>解除で再計算されるか</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="L40" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
-      <c r="K40" s="11" t="inlineStr">
+      <c r="M40" s="12" t="inlineStr">
         <is>
           <t>AC-19</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr">
+      <c r="N40" s="5" t="inlineStr"/>
+      <c r="O40" s="5" t="inlineStr"/>
+      <c r="P40" s="7" t="inlineStr">
         <is>
           <t>原則②：確定操作は確認を経る</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="49" customHeight="1">
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3056,44 +3304,50 @@
 【操作】店長スコープのアカウントでログインし、人件費実績を開いて締めを試みる</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>T-S07.png</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>店長スコープでの人件費実績（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>店長が締められないか</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr">
+      <c r="L41" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
-      <c r="K41" s="11" t="inlineStr">
+      <c r="M41" s="12" t="inlineStr">
         <is>
           <t>AC-41</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr"/>
-      <c r="M41" s="5" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr">
+      <c r="N41" s="5" t="inlineStr"/>
+      <c r="O41" s="5" t="inlineStr"/>
+      <c r="P41" s="7" t="inlineStr">
         <is>
           <t>原則②：締めは会社スコープのみ</t>
         </is>
@@ -3121,50 +3375,56 @@
 【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>T-I02.png</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="11" t="inlineStr">
         <is>
           <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="K42" s="7" t="inlineStr">
         <is>
           <t>テンプレートの列とBOM</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr">
+      <c r="L42" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
-      <c r="K42" s="11" t="inlineStr">
+      <c r="M42" s="12" t="inlineStr">
         <is>
           <t>AC-21 AC-30</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr">
+      <c r="N42" s="5" t="inlineStr"/>
+      <c r="O42" s="5" t="inlineStr"/>
+      <c r="P42" s="7" t="inlineStr">
         <is>
           <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="49" customHeight="1">
+    <row r="43" ht="64" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3186,50 +3446,56 @@
 【操作】データ種類＝King of Time を選び data/07（従業員設定・3行）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>07は3行すべて取り込まれ、EMP-001=340,000・EMP-005=360,000に更新、EMP-013は新規追加。10は給与設定（ヘルプ先交通費 S02:700;S03:900 の記法を含む）が反映される</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>T-I03.png</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="11" t="inlineStr">
         <is>
           <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>3行が更新・追加されるか</t>
         </is>
       </c>
-      <c r="J43" s="11" t="inlineStr">
+      <c r="L43" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
-      <c r="K43" s="11" t="inlineStr">
+      <c r="M43" s="12" t="inlineStr">
         <is>
           <t>AC-21</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr"/>
-      <c r="M43" s="5" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr">
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr"/>
+      <c r="P43" s="7" t="inlineStr">
         <is>
           <t>入出力：導入を止めない</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="49" customHeight="1">
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3251,50 +3517,56 @@
 【操作】データ種類＝ジョブカン を選び data/08（3行）をD&amp;D → 登録</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>08 取込CSV ジョブカン</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>3行すべて取り込まれる（EMP-003=1,250・EMP-010=1,300・EMP-014は新規）</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="G44" s="9" t="inlineStr">
         <is>
           <t>T-I04.png</t>
         </is>
       </c>
-      <c r="G44" s="9" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="11" t="inlineStr">
         <is>
           <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>表記ゆれを吸収できるか</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="L44" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
-      <c r="K44" s="11" t="inlineStr">
+      <c r="M44" s="12" t="inlineStr">
         <is>
           <t>AC-22</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr"/>
-      <c r="M44" s="5" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr">
+      <c r="N44" s="5" t="inlineStr"/>
+      <c r="O44" s="5" t="inlineStr"/>
+      <c r="P44" s="7" t="inlineStr">
         <is>
           <t>入出力：表記ゆれを吸収</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="34" customHeight="1">
+    <row r="45" ht="60" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3316,50 +3588,56 @@
 【操作】data/09（4行）をD&amp;D → 登録</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>09 取込CSV 異常系</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>T-I05.png</t>
         </is>
       </c>
-      <c r="G45" s="9" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="11" t="inlineStr">
         <is>
           <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>4種の異常を行ごとに検出するか</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="L45" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
-      <c r="K45" s="11" t="inlineStr">
+      <c r="M45" s="12" t="inlineStr">
         <is>
           <t>AC-23</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr"/>
-      <c r="M45" s="5" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr">
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="5" t="inlineStr"/>
+      <c r="P45" s="7" t="inlineStr">
         <is>
           <t>データ保全：不正値を入れない</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="49" customHeight="1">
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3381,44 +3659,50 @@
 【操作】（a）data/07を2回続けて取り込む （b）data/19（EMP-002が2行・単位給与額が異なる）を取り込む</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>（a）2回目は更新となり件数が増えない （b）重複行がエラーとして検出される（両方が登録されない）</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="G46" s="9" t="inlineStr">
         <is>
           <t>T-I17.png</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="11" t="inlineStr">
         <is>
           <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="K46" s="7" t="inlineStr">
         <is>
           <t>二重登録されないか</t>
         </is>
       </c>
-      <c r="J46" s="11" t="inlineStr">
+      <c r="L46" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
-      <c r="K46" s="11" t="inlineStr">
+      <c r="M46" s="12" t="inlineStr">
         <is>
           <t>AC-40</t>
         </is>
       </c>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr">
+      <c r="N46" s="5" t="inlineStr"/>
+      <c r="O46" s="5" t="inlineStr"/>
+      <c r="P46" s="7" t="inlineStr">
         <is>
           <t>データ保全：二重登録を防ぐ</t>
         </is>
@@ -3446,50 +3730,56 @@
 【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>09 取込CSV 異常系</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr">
         <is>
           <t>T-I18.png</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="11" t="inlineStr">
         <is>
           <t>設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録されていないこと）</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>部分登録が残らないか</t>
         </is>
       </c>
-      <c r="J47" s="11" t="inlineStr">
+      <c r="L47" s="12" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
-      <c r="K47" s="11" t="inlineStr">
+      <c r="M47" s="12" t="inlineStr">
         <is>
           <t>AC-42</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr"/>
-      <c r="N47" s="7" t="inlineStr">
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="5" t="inlineStr"/>
+      <c r="P47" s="7" t="inlineStr">
         <is>
           <t>データ保全：中途半端に残さない</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="49" customHeight="1">
+    <row r="48" ht="60" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3511,44 +3801,50 @@
 【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>11 取込CSV 説明行あり</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>余計な行が無視され、3行が正しく取り込まれる</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="G48" s="9" t="inlineStr">
         <is>
           <t>T-I11.png</t>
         </is>
       </c>
-      <c r="G48" s="9" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="11" t="inlineStr">
         <is>
           <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>説明行を飛ばして取り込めるか</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr">
+      <c r="L48" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="K48" s="11" t="inlineStr">
+      <c r="M48" s="12" t="inlineStr">
         <is>
           <t>AC-37</t>
         </is>
       </c>
-      <c r="L48" s="5" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr"/>
-      <c r="N48" s="7" t="inlineStr">
+      <c r="N48" s="5" t="inlineStr"/>
+      <c r="O48" s="5" t="inlineStr"/>
+      <c r="P48" s="7" t="inlineStr">
         <is>
           <t>入出力：現場のCSVをそのまま使える</t>
         </is>
@@ -3576,44 +3872,50 @@
 【操作】「列マッピングテンプレート管理」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="G49" s="9" t="inlineStr">
         <is>
           <t>T-I09.png</t>
         </is>
       </c>
-      <c r="G49" s="9" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="11" t="inlineStr">
         <is>
           <t>設定インポート → ツールバー「列マッピングテンプレート管理」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>テンプレの登録・編集・削除と往復</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr">
+      <c r="L49" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="K49" s="11" t="inlineStr">
+      <c r="M49" s="12" t="inlineStr">
         <is>
           <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr">
+      <c r="N49" s="5" t="inlineStr"/>
+      <c r="O49" s="5" t="inlineStr"/>
+      <c r="P49" s="7" t="inlineStr">
         <is>
           <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
         </is>
@@ -3641,44 +3943,50 @@
 【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>18 列マッピング表テンプレ</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="G50" s="9" t="inlineStr">
         <is>
           <t>T-I19.png</t>
         </is>
       </c>
-      <c r="G50" s="9" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="11" t="inlineStr">
         <is>
           <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>一括登録と10MB超の扱い</t>
         </is>
       </c>
-      <c r="J50" s="11" t="inlineStr">
+      <c r="L50" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="K50" s="11" t="inlineStr">
+      <c r="M50" s="12" t="inlineStr">
         <is>
           <t>AC-51</t>
         </is>
       </c>
-      <c r="L50" s="5" t="inlineStr"/>
-      <c r="M50" s="5" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr">
+      <c r="N50" s="5" t="inlineStr"/>
+      <c r="O50" s="5" t="inlineStr"/>
+      <c r="P50" s="7" t="inlineStr">
         <is>
           <t>入出力：マッピングの一括運用</t>
         </is>
@@ -3706,44 +4014,50 @@
 【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr">
         <is>
           <t>T-E04.png</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="11" t="inlineStr">
         <is>
           <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>選んだ項目だけ・対象数だけ出るか</t>
         </is>
       </c>
-      <c r="J51" s="11" t="inlineStr">
+      <c r="L51" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="K51" s="11" t="inlineStr">
+      <c r="M51" s="12" t="inlineStr">
         <is>
           <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr"/>
-      <c r="M51" s="5" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr">
+      <c r="N51" s="5" t="inlineStr"/>
+      <c r="O51" s="5" t="inlineStr"/>
+      <c r="P51" s="7" t="inlineStr">
         <is>
           <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
         </is>
@@ -3771,50 +4085,56 @@
 【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="G52" s="9" t="inlineStr">
         <is>
           <t>T-E09.png</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="11" t="inlineStr">
         <is>
           <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="K52" s="7" t="inlineStr">
         <is>
           <t>実績と同時選択のファイル数</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr">
+      <c r="L52" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="K52" s="11" t="inlineStr">
+      <c r="M52" s="12" t="inlineStr">
         <is>
           <t>AC-25</t>
         </is>
       </c>
-      <c r="L52" s="5" t="inlineStr"/>
-      <c r="M52" s="5" t="inlineStr"/>
-      <c r="N52" s="7" t="inlineStr">
+      <c r="N52" s="5" t="inlineStr"/>
+      <c r="O52" s="5" t="inlineStr"/>
+      <c r="P52" s="7" t="inlineStr">
         <is>
           <t>入出力：渡し先に合わせて出せる</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="49" customHeight="1">
+    <row r="53" ht="60" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
           <t>出力</t>
@@ -3836,50 +4156,56 @@
 【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr">
         <is>
           <t>T-E07.png</t>
         </is>
       </c>
-      <c r="G53" s="9" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="11" t="inlineStr">
         <is>
           <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>未選択で出力されないか</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr">
+      <c r="L53" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="K53" s="11" t="inlineStr">
+      <c r="M53" s="12" t="inlineStr">
         <is>
           <t>AC-27</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr"/>
-      <c r="M53" s="5" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr">
+      <c r="N53" s="5" t="inlineStr"/>
+      <c r="O53" s="5" t="inlineStr"/>
+      <c r="P53" s="7" t="inlineStr">
         <is>
           <t>入出力：空振りを防ぐ</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="34" customHeight="1">
+    <row r="54" ht="60" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
           <t>出力</t>
@@ -3901,50 +4227,56 @@
 【操作】T-E04で出力したCSVをExcelで開く</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
         </is>
       </c>
-      <c r="F54" s="8" t="inlineStr">
+      <c r="G54" s="9" t="inlineStr">
         <is>
           <t>T-E08.png</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="11" t="inlineStr">
         <is>
           <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="K54" s="7" t="inlineStr">
         <is>
           <t>Excelで文字化けしないか</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr">
+      <c r="L54" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="K54" s="11" t="inlineStr">
+      <c r="M54" s="12" t="inlineStr">
         <is>
           <t>AC-28</t>
         </is>
       </c>
-      <c r="L54" s="5" t="inlineStr"/>
-      <c r="M54" s="5" t="inlineStr"/>
-      <c r="N54" s="7" t="inlineStr">
+      <c r="N54" s="5" t="inlineStr"/>
+      <c r="O54" s="5" t="inlineStr"/>
+      <c r="P54" s="7" t="inlineStr">
         <is>
           <t>入出力：そのまま提出できる</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="49" customHeight="1">
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -3966,50 +4298,56 @@
 【操作】サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
         </is>
       </c>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr">
         <is>
           <t>T-N01.png</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>設定取込データと実績取込データの一覧＋各タブ（計4枚）</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="11" t="inlineStr">
         <is>
           <t>設定取込データ（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績取込データ … 月別データ／日別データタブ</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>元データとタブの構成</t>
         </is>
       </c>
-      <c r="J55" s="11" t="inlineStr">
+      <c r="L55" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
-      <c r="K55" s="11" t="inlineStr">
+      <c r="M55" s="12" t="inlineStr">
         <is>
           <t>AC-39</t>
         </is>
       </c>
-      <c r="L55" s="5" t="inlineStr"/>
-      <c r="M55" s="5" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr">
+      <c r="N55" s="5" t="inlineStr"/>
+      <c r="O55" s="5" t="inlineStr"/>
+      <c r="P55" s="7" t="inlineStr">
         <is>
           <t>入出力：原因を追える</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="79" customHeight="1">
+    <row r="56" ht="94" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -4031,50 +4369,56 @@
 【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="G56" s="9" t="inlineStr">
         <is>
           <t>T-N02.png</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="11" t="inlineStr">
         <is>
           <t>設定取込データ／実績取込データ … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>差分がdata/16・17と一致するか</t>
         </is>
       </c>
-      <c r="J56" s="11" t="inlineStr">
+      <c r="L56" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
-      <c r="K56" s="11" t="inlineStr">
+      <c r="M56" s="12" t="inlineStr">
         <is>
           <t>AC-50</t>
         </is>
       </c>
-      <c r="L56" s="5" t="inlineStr"/>
-      <c r="M56" s="5" t="inlineStr"/>
-      <c r="N56" s="7" t="inlineStr">
+      <c r="N56" s="5" t="inlineStr"/>
+      <c r="O56" s="5" t="inlineStr"/>
+      <c r="P56" s="7" t="inlineStr">
         <is>
           <t>データ保全：取り込む前に気づける</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="49" customHeight="1">
+    <row r="57" ht="60" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -4096,50 +4440,56 @@
 【操作】人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>2経路とも到達する（不通=0）</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="G57" s="9" t="inlineStr">
         <is>
           <t>T-N03.png</t>
         </is>
       </c>
-      <c r="G57" s="9" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>人件費実績→実績取込データ／実績取込データ→人件費実績 の到達直後（2枚）</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 「実績取込データへ」／実績取込データ → 「人件費実績へ」（相互導線）</t>
         </is>
       </c>
-      <c r="I57" s="7" t="inlineStr">
+      <c r="K57" s="7" t="inlineStr">
         <is>
           <t>2経路とも到達するか</t>
         </is>
       </c>
-      <c r="J57" s="11" t="inlineStr">
+      <c r="L57" s="12" t="inlineStr">
         <is>
           <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
-      <c r="K57" s="11" t="inlineStr">
+      <c r="M57" s="12" t="inlineStr">
         <is>
           <t>AC-30</t>
         </is>
       </c>
-      <c r="L57" s="5" t="inlineStr"/>
-      <c r="M57" s="5" t="inlineStr"/>
-      <c r="N57" s="7" t="inlineStr">
+      <c r="N57" s="5" t="inlineStr"/>
+      <c r="O57" s="5" t="inlineStr"/>
+      <c r="P57" s="7" t="inlineStr">
         <is>
           <t>画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="49" customHeight="1">
+    <row r="58" ht="60" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
           <t>横断</t>
@@ -4161,50 +4511,56 @@
 【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>15 移行前後 突合テンプレ</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="G58" s="9" t="inlineStr">
         <is>
           <t>T-Z01.png</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="11" t="inlineStr">
         <is>
           <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="K58" s="7" t="inlineStr">
         <is>
           <t>移行前後で差分0件か</t>
         </is>
       </c>
-      <c r="J58" s="11" t="inlineStr">
+      <c r="L58" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
-      <c r="K58" s="11" t="inlineStr">
+      <c r="M58" s="12" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
-      <c r="L58" s="5" t="inlineStr"/>
-      <c r="M58" s="5" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr">
+      <c r="N58" s="5" t="inlineStr"/>
+      <c r="O58" s="5" t="inlineStr"/>
+      <c r="P58" s="7" t="inlineStr">
         <is>
           <t>移行：既存顧客が壊れない</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="49" customHeight="1">
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
           <t>横断</t>
@@ -4226,50 +4582,56 @@
 【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr">
         <is>
           <t>T-Z02.png</t>
         </is>
       </c>
-      <c r="G59" s="9" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="11" t="inlineStr">
         <is>
           <t>従業員詳細 → 設定変更履歴／従業員設定履歴 … 適用日付の空欄</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
+      <c r="K59" s="7" t="inlineStr">
         <is>
           <t>適用日付の空欄が0件か</t>
         </is>
       </c>
-      <c r="J59" s="11" t="inlineStr">
+      <c r="L59" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
-      <c r="K59" s="11" t="inlineStr">
+      <c r="M59" s="12" t="inlineStr">
         <is>
           <t>AC-02</t>
         </is>
       </c>
-      <c r="L59" s="5" t="inlineStr"/>
-      <c r="M59" s="5" t="inlineStr"/>
-      <c r="N59" s="7" t="inlineStr">
+      <c r="N59" s="5" t="inlineStr"/>
+      <c r="O59" s="5" t="inlineStr"/>
+      <c r="P59" s="7" t="inlineStr">
         <is>
           <t>移行：履歴の起点を作る</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="49" customHeight="1">
+    <row r="60" ht="60" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
           <t>横断</t>
@@ -4291,50 +4653,56 @@
 【操作】移行前に出力しておいた直近3か月の人件費実績と、移行後の同3か月を突合する</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>15 移行前後 突合テンプレ</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="G60" s="9" t="inlineStr">
         <is>
           <t>T-Z03.png</t>
         </is>
       </c>
-      <c r="G60" s="9" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>移行前後の人件費実績 月別実績（直近3か月・金額が同じであること）</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="11" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ … 移行前後の直近3か月</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
+      <c r="K60" s="7" t="inlineStr">
         <is>
           <t>過去3か月の金額が変わらないか</t>
         </is>
       </c>
-      <c r="J60" s="11" t="inlineStr">
+      <c r="L60" s="12" t="inlineStr">
         <is>
           <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
-      <c r="K60" s="11" t="inlineStr">
+      <c r="M60" s="12" t="inlineStr">
         <is>
           <t>AC-03</t>
         </is>
       </c>
-      <c r="L60" s="5" t="inlineStr"/>
-      <c r="M60" s="5" t="inlineStr"/>
-      <c r="N60" s="7" t="inlineStr">
+      <c r="N60" s="5" t="inlineStr"/>
+      <c r="O60" s="5" t="inlineStr"/>
+      <c r="P60" s="7" t="inlineStr">
         <is>
           <t>移行：過去が動かない</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="49" customHeight="1">
+    <row r="61" ht="60" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
           <t>横断</t>
@@ -4356,50 +4724,56 @@
 【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr">
         <is>
           <t>T-Z04.png</t>
         </is>
       </c>
-      <c r="G61" s="9" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
         </is>
       </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="11" t="inlineStr">
         <is>
           <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
+      <c r="K61" s="7" t="inlineStr">
         <is>
           <t>PC・モバイルとも開くか</t>
         </is>
       </c>
-      <c r="J61" s="11" t="inlineStr">
+      <c r="L61" s="12" t="inlineStr">
         <is>
           <t>（ヘルプ記載なし・画面構成）</t>
         </is>
       </c>
-      <c r="K61" s="11" t="inlineStr">
+      <c r="M61" s="12" t="inlineStr">
         <is>
           <t>AC-29</t>
         </is>
       </c>
-      <c r="L61" s="5" t="inlineStr"/>
-      <c r="M61" s="5" t="inlineStr"/>
-      <c r="N61" s="7" t="inlineStr">
+      <c r="N61" s="5" t="inlineStr"/>
+      <c r="O61" s="5" t="inlineStr"/>
+      <c r="P61" s="7" t="inlineStr">
         <is>
           <t>画面：たどり着ける</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="49" customHeight="1">
+    <row r="62" ht="60" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
           <t>横断</t>
@@ -4421,1031 +4795,1127 @@
 【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="G62" s="9" t="inlineStr">
         <is>
           <t>T-Z05.png</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="11" t="inlineStr">
         <is>
           <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr">
+      <c r="K62" s="7" t="inlineStr">
         <is>
           <t>75本の遷移と表示規則</t>
         </is>
       </c>
-      <c r="J62" s="11" t="inlineStr">
+      <c r="L62" s="12" t="inlineStr">
         <is>
           <t>（ヘルプ記載なし・遷移網羅）</t>
         </is>
       </c>
-      <c r="K62" s="11" t="inlineStr">
+      <c r="M62" s="12" t="inlineStr">
         <is>
           <t>AC-30 AC-01</t>
         </is>
       </c>
-      <c r="L62" s="5" t="inlineStr"/>
-      <c r="M62" s="5" t="inlineStr"/>
-      <c r="N62" s="7" t="inlineStr">
+      <c r="N62" s="5" t="inlineStr"/>
+      <c r="O62" s="5" t="inlineStr"/>
+      <c r="P62" s="7" t="inlineStr">
         <is>
           <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
         </is>
       </c>
     </row>
     <row r="63" ht="64" customHeight="1">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>C-000</t>
         </is>
       </c>
-      <c r="C63" s="13" t="inlineStr">
+      <c r="C63" s="14" t="inlineStr">
         <is>
           <t>データの初期化（計算の検証に入る前に必ず実施）</t>
         </is>
       </c>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>【前提】S-03 S-05
 【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>02〜06・13を再投入（初期化）</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
         <is>
           <t>従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
-      <c r="F63" s="12" t="inlineStr">
+      <c r="G63" s="13" t="inlineStr">
         <is>
           <t>C-000.png</t>
         </is>
       </c>
-      <c r="G63" s="13" t="inlineStr">
+      <c r="H63" s="14" t="inlineStr">
         <is>
           <t>初期化後の従業員一覧（12名）と人件費実績（未締め・S-05時点の金額）</t>
         </is>
       </c>
-      <c r="H63" s="13" t="inlineStr">
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="14" t="inlineStr">
         <is>
           <t>従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未締めに戻す）</t>
         </is>
       </c>
-      <c r="I63" s="13" t="inlineStr">
+      <c r="K63" s="14" t="inlineStr">
         <is>
           <t>S-05時点の値に戻ったか</t>
         </is>
       </c>
-      <c r="J63" s="13" t="inlineStr">
+      <c r="L63" s="14" t="inlineStr">
         <is>
           <t>（初期化のため対応なし）</t>
         </is>
       </c>
-      <c r="K63" s="13" t="inlineStr">
+      <c r="M63" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr"/>
-      <c r="M63" s="5" t="inlineStr"/>
-      <c r="N63" s="13" t="inlineStr">
+      <c r="N63" s="5" t="inlineStr"/>
+      <c r="O63" s="5" t="inlineStr"/>
+      <c r="P63" s="14" t="inlineStr">
         <is>
           <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
         </is>
       </c>
     </row>
     <row r="64" ht="64" customHeight="1">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>C-001</t>
         </is>
       </c>
-      <c r="C64" s="13" t="inlineStr">
+      <c r="C64" s="14" t="inlineStr">
         <is>
           <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D64" s="14" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
 【操作】2026-05の EMP-002（概算280,000・基礎時給1,750＝280,000÷160・深夜2h）と EMP-007（概算300,000・基礎時給1,875＝300,000÷160・深夜4h）を検算</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>05 月次給与実績</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
         <is>
           <t>EMP-002＝285,250（概算280,000＋深夜残業代5,250＝1,750×1.5×2h）／EMP-007＝311,250（概算300,000＋深夜残業代11,250＝1,875×1.5×4h）。いずれも差分0円</t>
         </is>
       </c>
-      <c r="F64" s="12" t="inlineStr">
+      <c r="G64" s="13" t="inlineStr">
         <is>
           <t>C-001.png</t>
         </is>
       </c>
-      <c r="G64" s="13" t="inlineStr">
+      <c r="H64" s="14" t="inlineStr">
         <is>
           <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
         </is>
       </c>
-      <c r="H64" s="13" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="14" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
         </is>
       </c>
-      <c r="I64" s="13" t="inlineStr">
+      <c r="K64" s="14" t="inlineStr">
         <is>
           <t>概算＋深夜＝実績給与か</t>
         </is>
       </c>
-      <c r="J64" s="13" t="inlineStr">
+      <c r="L64" s="14" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="K64" s="13" t="inlineStr">
+      <c r="M64" s="14" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
-      <c r="L64" s="5" t="inlineStr"/>
-      <c r="M64" s="5" t="inlineStr"/>
-      <c r="N64" s="13" t="inlineStr">
+      <c r="N64" s="5" t="inlineStr"/>
+      <c r="O64" s="5" t="inlineStr"/>
+      <c r="P64" s="14" t="inlineStr">
         <is>
           <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・暫定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
         </is>
       </c>
     </row>
     <row r="65" ht="79" customHeight="1">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>C-003</t>
         </is>
       </c>
-      <c r="C65" s="13" t="inlineStr">
+      <c r="C65" s="14" t="inlineStr">
         <is>
           <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
-      <c r="D65" s="13" t="inlineStr">
+      <c r="D65" s="14" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
 【操作】2026-05の EMP-001（概算320,000・基礎時給2,000・深夜6h・ヘルプ22h／総労働172h）／EMP-005（概算350,000・基礎時給2,187・深夜10h・ヘルプ35h／総労働185h）／EMP-003（概算144,000・時給1,200・深夜0h・ヘルプ20h／総労働120h）を検算</t>
         </is>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="E65" s="14" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
         <is>
           <t>EMP-001＝338,000（概算320,000＋深夜18,000＝2,000×1.5×6h）／EMP-005＝382,812（概算350,000＋深夜32,812＝2,187×1.5×10h）／EMP-003＝144,000（深夜なし）。ヘルプ人件費は実績給与×ヘルプ時間÷総労働時間で按分し応援先へ振替（EMP-001＝43,232／EMP-003＝24,000／EMP-005＝72,424）</t>
         </is>
       </c>
-      <c r="F65" s="12" t="inlineStr">
+      <c r="G65" s="13" t="inlineStr">
         <is>
           <t>C-003.png</t>
         </is>
       </c>
-      <c r="G65" s="13" t="inlineStr">
+      <c r="H65" s="14" t="inlineStr">
         <is>
           <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
         </is>
       </c>
-      <c r="H65" s="13" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr"/>
+      <c r="J65" s="14" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
         </is>
       </c>
-      <c r="I65" s="13" t="inlineStr">
+      <c r="K65" s="14" t="inlineStr">
         <is>
           <t>ヘルプ人件費が按分で振替されるか</t>
         </is>
       </c>
-      <c r="J65" s="13" t="inlineStr">
+      <c r="L65" s="14" t="inlineStr">
         <is>
           <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
-      <c r="K65" s="13" t="inlineStr">
+      <c r="M65" s="14" t="inlineStr">
         <is>
           <t>AC-10 AC-14</t>
         </is>
       </c>
-      <c r="L65" s="5" t="inlineStr"/>
-      <c r="M65" s="5" t="inlineStr"/>
-      <c r="N65" s="13" t="inlineStr">
+      <c r="N65" s="5" t="inlineStr"/>
+      <c r="O65" s="5" t="inlineStr"/>
+      <c r="P65" s="14" t="inlineStr">
         <is>
           <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="49" customHeight="1">
-      <c r="A66" s="12" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>C-005</t>
         </is>
       </c>
-      <c r="C66" s="13" t="inlineStr">
+      <c r="C66" s="14" t="inlineStr">
         <is>
           <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D66" s="14" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-04
 【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
-      <c r="E66" s="13" t="inlineStr">
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>05 月次給与実績</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
         <is>
           <t>店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
         </is>
       </c>
-      <c r="F66" s="12" t="inlineStr">
+      <c r="G66" s="13" t="inlineStr">
         <is>
           <t>C-005.png</t>
         </is>
       </c>
-      <c r="G66" s="13" t="inlineStr">
+      <c r="H66" s="14" t="inlineStr">
         <is>
           <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
         </is>
       </c>
-      <c r="H66" s="13" t="inlineStr">
+      <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="14" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
         </is>
       </c>
-      <c r="I66" s="13" t="inlineStr">
+      <c r="K66" s="14" t="inlineStr">
         <is>
           <t>店舗別合計＝全社（差0円）か</t>
         </is>
       </c>
-      <c r="J66" s="13" t="inlineStr">
+      <c r="L66" s="14" t="inlineStr">
         <is>
           <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
-      <c r="K66" s="13" t="inlineStr">
+      <c r="M66" s="14" t="inlineStr">
         <is>
           <t>AC-11</t>
         </is>
       </c>
-      <c r="L66" s="5" t="inlineStr"/>
-      <c r="M66" s="5" t="inlineStr"/>
-      <c r="N66" s="13" t="inlineStr">
+      <c r="N66" s="5" t="inlineStr"/>
+      <c r="O66" s="5" t="inlineStr"/>
+      <c r="P66" s="14" t="inlineStr">
         <is>
           <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
         </is>
       </c>
     </row>
     <row r="67" ht="64" customHeight="1">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B67" s="13" t="inlineStr">
         <is>
           <t>C-006</t>
         </is>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C67" s="14" t="inlineStr">
         <is>
           <t>月中改定と予約の日割り</t>
         </is>
       </c>
-      <c r="D67" s="13" t="inlineStr">
+      <c r="D67" s="14" t="inlineStr">
         <is>
           <t>【前提】C-000 S-07 ／ data/14を投入
 【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
-      <c r="E67" s="13" t="inlineStr">
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>14 勤務データ 2026-06</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
         <is>
           <t>6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
-      <c r="F67" s="12" t="inlineStr">
+      <c r="G67" s="13" t="inlineStr">
         <is>
           <t>C-006.png</t>
         </is>
       </c>
-      <c r="G67" s="13" t="inlineStr">
+      <c r="H67" s="14" t="inlineStr">
         <is>
           <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
         </is>
       </c>
-      <c r="H67" s="13" t="inlineStr">
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="14" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
         </is>
       </c>
-      <c r="I67" s="13" t="inlineStr">
+      <c r="K67" s="14" t="inlineStr">
         <is>
           <t>所定労働日割になっているか</t>
         </is>
       </c>
-      <c r="J67" s="13" t="inlineStr">
+      <c r="L67" s="14" t="inlineStr">
         <is>
           <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
-      <c r="K67" s="13" t="inlineStr">
+      <c r="M67" s="14" t="inlineStr">
         <is>
           <t>AC-12 AC-04</t>
         </is>
       </c>
-      <c r="L67" s="5" t="inlineStr"/>
-      <c r="M67" s="5" t="inlineStr"/>
-      <c r="N67" s="13" t="inlineStr">
+      <c r="N67" s="5" t="inlineStr"/>
+      <c r="O67" s="5" t="inlineStr"/>
+      <c r="P67" s="14" t="inlineStr">
         <is>
           <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="49" customHeight="1">
-      <c r="A68" s="12" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="13" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>C-011</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C68" s="14" t="inlineStr">
         <is>
           <t>時給者の概算と月中改定</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D68" s="14" t="inlineStr">
         <is>
           <t>【前提】C-000 S-07 ／ data/14を投入
 【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
         </is>
       </c>
-      <c r="E68" s="13" t="inlineStr">
+      <c r="E68" s="14" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・14 勤務データ 2026-06</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
         <is>
           <t>5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
-      <c r="F68" s="12" t="inlineStr">
+      <c r="G68" s="13" t="inlineStr">
         <is>
           <t>C-011.png</t>
         </is>
       </c>
-      <c r="G68" s="13" t="inlineStr">
+      <c r="H68" s="14" t="inlineStr">
         <is>
           <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
         </is>
       </c>
-      <c r="H68" s="13" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr"/>
+      <c r="J68" s="14" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
         </is>
       </c>
-      <c r="I68" s="13" t="inlineStr">
+      <c r="K68" s="14" t="inlineStr">
         <is>
           <t>時給者の概算と月中改定</t>
         </is>
       </c>
-      <c r="J68" s="13" t="inlineStr">
+      <c r="L68" s="14" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="K68" s="13" t="inlineStr">
+      <c r="M68" s="14" t="inlineStr">
         <is>
           <t>AC-13</t>
         </is>
       </c>
-      <c r="L68" s="5" t="inlineStr"/>
-      <c r="M68" s="5" t="inlineStr"/>
-      <c r="N68" s="13" t="inlineStr">
+      <c r="N68" s="5" t="inlineStr"/>
+      <c r="O68" s="5" t="inlineStr"/>
+      <c r="P68" s="14" t="inlineStr">
         <is>
           <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="64" customHeight="1">
-      <c r="A69" s="12" t="inlineStr">
+    <row r="69" ht="79" customHeight="1">
+      <c r="A69" s="13" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B69" s="13" t="inlineStr">
         <is>
           <t>C-013</t>
         </is>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C69" s="14" t="inlineStr">
         <is>
           <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D69" s="14" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
 【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
-      <c r="E69" s="13" t="inlineStr">
+      <c r="E69" s="14" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
         <is>
           <t>判断7（暫定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。5/8のヘルプ人件費＝実績給与338,000×11h÷総労働172h＝21,616円で、計上先はS02。みなし労働時間差分＝172−(160＋20)＝−8h（未達はマイナス表示・減額なし＝判断8）</t>
         </is>
       </c>
-      <c r="F69" s="12" t="inlineStr">
+      <c r="G69" s="13" t="inlineStr">
         <is>
           <t>C-013.png</t>
         </is>
       </c>
-      <c r="G69" s="13" t="inlineStr">
+      <c r="H69" s="14" t="inlineStr">
         <is>
           <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
         </is>
       </c>
-      <c r="H69" s="13" t="inlineStr">
+      <c r="I69" s="5" t="inlineStr"/>
+      <c r="J69" s="14" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
         </is>
       </c>
-      <c r="I69" s="13" t="inlineStr">
+      <c r="K69" s="14" t="inlineStr">
         <is>
           <t>深夜1.5倍とヘルプの按分単価</t>
         </is>
       </c>
-      <c r="J69" s="13" t="inlineStr">
+      <c r="L69" s="14" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="K69" s="13" t="inlineStr">
+      <c r="M69" s="14" t="inlineStr">
         <is>
           <t>AC-10 AC-14</t>
         </is>
       </c>
-      <c r="L69" s="5" t="inlineStr"/>
-      <c r="M69" s="5" t="inlineStr"/>
-      <c r="N69" s="13" t="inlineStr">
+      <c r="N69" s="5" t="inlineStr"/>
+      <c r="O69" s="5" t="inlineStr"/>
+      <c r="P69" s="14" t="inlineStr">
         <is>
           <t>深夜残業代＝基礎時給×1.5（判断7・暫定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・暫定）</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="49" customHeight="1">
-      <c r="A70" s="12" t="inlineStr">
+    <row r="70" ht="64" customHeight="1">
+      <c r="A70" s="13" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B70" s="13" t="inlineStr">
         <is>
           <t>C-017</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C70" s="14" t="inlineStr">
         <is>
           <t>交通費の計上先</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D70" s="14" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-04
 【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
         </is>
       </c>
-      <c r="E70" s="13" t="inlineStr">
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
         <is>
           <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
         </is>
       </c>
-      <c r="F70" s="12" t="inlineStr">
+      <c r="G70" s="13" t="inlineStr">
         <is>
           <t>C-017.png</t>
         </is>
       </c>
-      <c r="G70" s="13" t="inlineStr">
+      <c r="H70" s="14" t="inlineStr">
         <is>
           <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
         </is>
       </c>
-      <c r="H70" s="13" t="inlineStr">
+      <c r="I70" s="5" t="inlineStr"/>
+      <c r="J70" s="14" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
         </is>
       </c>
-      <c r="I70" s="13" t="inlineStr">
+      <c r="K70" s="14" t="inlineStr">
         <is>
           <t>交通費が給与と別費目か</t>
         </is>
       </c>
-      <c r="J70" s="13" t="inlineStr">
+      <c r="L70" s="14" t="inlineStr">
         <is>
           <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
-      <c r="K70" s="13" t="inlineStr">
+      <c r="M70" s="14" t="inlineStr">
         <is>
           <t>AC-15</t>
         </is>
       </c>
-      <c r="L70" s="5" t="inlineStr"/>
-      <c r="M70" s="5" t="inlineStr"/>
-      <c r="N70" s="13" t="inlineStr">
+      <c r="N70" s="5" t="inlineStr"/>
+      <c r="O70" s="5" t="inlineStr"/>
+      <c r="P70" s="14" t="inlineStr">
         <is>
           <t>交通費は給与と別の独立費目（判断6・確定）。通勤交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
         </is>
       </c>
     </row>
     <row r="71" ht="64" customHeight="1">
-      <c r="A71" s="12" t="inlineStr">
+      <c r="A71" s="13" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B71" s="13" t="inlineStr">
         <is>
           <t>C-008</t>
         </is>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C71" s="14" t="inlineStr">
         <is>
           <t>締めの前後で数字が動かないこと</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D71" s="14" t="inlineStr">
         <is>
           <t>【前提】C-000 S-07
 【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
         </is>
       </c>
-      <c r="E71" s="13" t="inlineStr">
+      <c r="E71" s="14" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
         <is>
           <t>（a）5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
         </is>
       </c>
-      <c r="F71" s="12" t="inlineStr">
+      <c r="G71" s="13" t="inlineStr">
         <is>
           <t>C-008.png</t>
         </is>
       </c>
-      <c r="G71" s="13" t="inlineStr">
+      <c r="H71" s="14" t="inlineStr">
         <is>
           <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
-      <c r="H71" s="13" t="inlineStr">
+      <c r="I71" s="5" t="inlineStr"/>
+      <c r="J71" s="14" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
         </is>
       </c>
-      <c r="I71" s="13" t="inlineStr">
+      <c r="K71" s="14" t="inlineStr">
         <is>
           <t>締め前後で差0円・解除後に再計算</t>
         </is>
       </c>
-      <c r="J71" s="13" t="inlineStr">
+      <c r="L71" s="14" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
-      <c r="K71" s="13" t="inlineStr">
+      <c r="M71" s="14" t="inlineStr">
         <is>
           <t>AC-16 AC-17</t>
         </is>
       </c>
-      <c r="L71" s="5" t="inlineStr"/>
-      <c r="M71" s="5" t="inlineStr"/>
-      <c r="N71" s="13" t="inlineStr">
+      <c r="N71" s="5" t="inlineStr"/>
+      <c r="O71" s="5" t="inlineStr"/>
+      <c r="P71" s="14" t="inlineStr">
         <is>
           <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
         </is>
       </c>
     </row>
     <row r="72" ht="64" customHeight="1">
-      <c r="A72" s="14" t="inlineStr">
+      <c r="A72" s="15" t="inlineStr">
         <is>
           <t>実装レビュー</t>
         </is>
       </c>
-      <c r="B72" s="14" t="inlineStr">
+      <c r="B72" s="15" t="inlineStr">
         <is>
           <t>R-01</t>
         </is>
       </c>
-      <c r="C72" s="15" t="inlineStr">
+      <c r="C72" s="16" t="inlineStr">
         <is>
           <t>データ構造のレビュー</t>
         </is>
       </c>
-      <c r="D72" s="15" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
         </is>
       </c>
-      <c r="E72" s="15" t="inlineStr">
+      <c r="E72" s="16" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F72" s="16" t="inlineStr">
         <is>
           <t>①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
         </is>
       </c>
-      <c r="F72" s="14" t="inlineStr">
+      <c r="G72" s="15" t="inlineStr">
         <is>
           <t>R-01.png</t>
         </is>
       </c>
-      <c r="G72" s="15" t="inlineStr">
+      <c r="H72" s="16" t="inlineStr">
         <is>
           <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
-      <c r="H72" s="15" t="inlineStr">
+      <c r="I72" s="5" t="inlineStr"/>
+      <c r="J72" s="16" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
       </c>
-      <c r="I72" s="15" t="inlineStr">
+      <c r="K72" s="16" t="inlineStr">
         <is>
           <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
-      <c r="J72" s="15" t="inlineStr">
+      <c r="L72" s="16" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="K72" s="15" t="inlineStr">
+      <c r="M72" s="16" t="inlineStr">
         <is>
           <t>AC-07 AC-40 AC-47</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr"/>
-      <c r="M72" s="5" t="inlineStr"/>
-      <c r="N72" s="15" t="inlineStr">
+      <c r="N72" s="5" t="inlineStr"/>
+      <c r="O72" s="5" t="inlineStr"/>
+      <c r="P72" s="16" t="inlineStr">
         <is>
           <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="49" customHeight="1">
-      <c r="A73" s="14" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" s="15" t="inlineStr">
         <is>
           <t>実装レビュー</t>
         </is>
       </c>
-      <c r="B73" s="14" t="inlineStr">
+      <c r="B73" s="15" t="inlineStr">
         <is>
           <t>R-02</t>
         </is>
       </c>
-      <c r="C73" s="15" t="inlineStr">
+      <c r="C73" s="16" t="inlineStr">
         <is>
           <t>締めの実装レビュー</t>
         </is>
       </c>
-      <c r="D73" s="15" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
-      <c r="E73" s="15" t="inlineStr">
+      <c r="E73" s="16" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F73" s="16" t="inlineStr">
         <is>
           <t>①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
         </is>
       </c>
-      <c r="F73" s="14" t="inlineStr">
+      <c r="G73" s="15" t="inlineStr">
         <is>
           <t>R-02.png</t>
         </is>
       </c>
-      <c r="G73" s="15" t="inlineStr">
+      <c r="H73" s="16" t="inlineStr">
         <is>
           <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
-      <c r="H73" s="15" t="inlineStr">
+      <c r="I73" s="5" t="inlineStr"/>
+      <c r="J73" s="16" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
       </c>
-      <c r="I73" s="15" t="inlineStr">
+      <c r="K73" s="16" t="inlineStr">
         <is>
           <t>APIでも店長が締められないか</t>
         </is>
       </c>
-      <c r="J73" s="15" t="inlineStr">
+      <c r="L73" s="16" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
-      <c r="K73" s="15" t="inlineStr">
+      <c r="M73" s="16" t="inlineStr">
         <is>
           <t>AC-16 AC-41</t>
         </is>
       </c>
-      <c r="L73" s="5" t="inlineStr"/>
-      <c r="M73" s="5" t="inlineStr"/>
-      <c r="N73" s="15" t="inlineStr">
+      <c r="N73" s="5" t="inlineStr"/>
+      <c r="O73" s="5" t="inlineStr"/>
+      <c r="P73" s="16" t="inlineStr">
         <is>
           <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="64" customHeight="1">
-      <c r="A74" s="14" t="inlineStr">
+    <row r="74" ht="79" customHeight="1">
+      <c r="A74" s="15" t="inlineStr">
         <is>
           <t>実装レビュー</t>
         </is>
       </c>
-      <c r="B74" s="14" t="inlineStr">
+      <c r="B74" s="15" t="inlineStr">
         <is>
           <t>R-03</t>
         </is>
       </c>
-      <c r="C74" s="15" t="inlineStr">
+      <c r="C74" s="16" t="inlineStr">
         <is>
           <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
-      <c r="D74" s="15" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
-      <c r="E74" s="15" t="inlineStr">
+      <c r="E74" s="16" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
         <is>
           <t>①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
         </is>
       </c>
-      <c r="F74" s="14" t="inlineStr">
+      <c r="G74" s="15" t="inlineStr">
         <is>
           <t>R-03.png</t>
         </is>
       </c>
-      <c r="G74" s="15" t="inlineStr">
+      <c r="H74" s="16" t="inlineStr">
         <is>
           <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
-      <c r="H74" s="15" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr"/>
+      <c r="J74" s="16" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
       </c>
-      <c r="I74" s="15" t="inlineStr">
+      <c r="K74" s="16" t="inlineStr">
         <is>
           <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
-      <c r="J74" s="15" t="inlineStr">
+      <c r="L74" s="16" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
-      <c r="K74" s="15" t="inlineStr">
+      <c r="M74" s="16" t="inlineStr">
         <is>
           <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
-      <c r="L74" s="5" t="inlineStr"/>
-      <c r="M74" s="5" t="inlineStr"/>
-      <c r="N74" s="15" t="inlineStr">
+      <c r="N74" s="5" t="inlineStr"/>
+      <c r="O74" s="5" t="inlineStr"/>
+      <c r="P74" s="16" t="inlineStr">
         <is>
           <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="49" customHeight="1">
-      <c r="A75" s="14" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" s="15" t="inlineStr">
         <is>
           <t>実装レビュー</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B75" s="15" t="inlineStr">
         <is>
           <t>R-04</t>
         </is>
       </c>
-      <c r="C75" s="15" t="inlineStr">
+      <c r="C75" s="16" t="inlineStr">
         <is>
           <t>計算ロジックの共有レビュー</t>
         </is>
       </c>
-      <c r="D75" s="15" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
-      <c r="E75" s="15" t="inlineStr">
+      <c r="E75" s="16" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F75" s="16" t="inlineStr">
         <is>
           <t>同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
         </is>
       </c>
-      <c r="F75" s="14" t="inlineStr">
+      <c r="G75" s="15" t="inlineStr">
         <is>
           <t>R-04.png</t>
         </is>
       </c>
-      <c r="G75" s="15" t="inlineStr">
+      <c r="H75" s="16" t="inlineStr">
         <is>
           <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
         </is>
       </c>
-      <c r="H75" s="15" t="inlineStr">
+      <c r="I75" s="5" t="inlineStr"/>
+      <c r="J75" s="16" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
         </is>
       </c>
-      <c r="I75" s="15" t="inlineStr">
+      <c r="K75" s="16" t="inlineStr">
         <is>
           <t>計算ロジックが1箇所か</t>
         </is>
       </c>
-      <c r="J75" s="15" t="inlineStr">
+      <c r="L75" s="16" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="K75" s="15" t="inlineStr">
+      <c r="M75" s="16" t="inlineStr">
         <is>
           <t>AC-35 AC-11</t>
         </is>
       </c>
-      <c r="L75" s="5" t="inlineStr"/>
-      <c r="M75" s="5" t="inlineStr"/>
-      <c r="N75" s="15" t="inlineStr">
+      <c r="N75" s="5" t="inlineStr"/>
+      <c r="O75" s="5" t="inlineStr"/>
+      <c r="P75" s="16" t="inlineStr">
         <is>
           <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="34" customHeight="1">
-      <c r="A76" s="14" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="15" t="inlineStr">
         <is>
           <t>実装レビュー</t>
         </is>
       </c>
-      <c r="B76" s="14" t="inlineStr">
+      <c r="B76" s="15" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
       </c>
-      <c r="C76" s="15" t="inlineStr">
+      <c r="C76" s="16" t="inlineStr">
         <is>
           <t>列マッピングの実装レビュー</t>
         </is>
       </c>
-      <c r="D76" s="15" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】取込の列解決の実装を提示してもらう</t>
         </is>
       </c>
-      <c r="E76" s="15" t="inlineStr">
+      <c r="E76" s="16" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F76" s="16" t="inlineStr">
         <is>
           <t>CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
-      <c r="F76" s="14" t="inlineStr">
+      <c r="G76" s="15" t="inlineStr">
         <is>
           <t>R-05.png</t>
         </is>
       </c>
-      <c r="G76" s="15" t="inlineStr">
+      <c r="H76" s="16" t="inlineStr">
         <is>
           <t>列名の対応づけを保持している箇所（DBかコードか）</t>
         </is>
       </c>
-      <c r="H76" s="15" t="inlineStr">
+      <c r="I76" s="5" t="inlineStr"/>
+      <c r="J76" s="16" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
         </is>
       </c>
-      <c r="I76" s="15" t="inlineStr">
+      <c r="K76" s="16" t="inlineStr">
         <is>
           <t>列名がコードに埋まっていないか</t>
         </is>
       </c>
-      <c r="J76" s="15" t="inlineStr">
+      <c r="L76" s="16" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="K76" s="15" t="inlineStr">
+      <c r="M76" s="16" t="inlineStr">
         <is>
           <t>AC-22 AC-24</t>
         </is>
       </c>
-      <c r="L76" s="5" t="inlineStr"/>
-      <c r="M76" s="5" t="inlineStr"/>
-      <c r="N76" s="15" t="inlineStr">
+      <c r="N76" s="5" t="inlineStr"/>
+      <c r="O76" s="5" t="inlineStr"/>
+      <c r="P76" s="16" t="inlineStr">
         <is>
           <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="49" customHeight="1">
-      <c r="A77" s="14" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" s="15" t="inlineStr">
         <is>
           <t>実装レビュー</t>
         </is>
       </c>
-      <c r="B77" s="14" t="inlineStr">
+      <c r="B77" s="15" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
       </c>
-      <c r="C77" s="15" t="inlineStr">
+      <c r="C77" s="16" t="inlineStr">
         <is>
           <t>設定更新処理の共通化レビュー</t>
         </is>
       </c>
-      <c r="D77" s="15" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
         </is>
       </c>
-      <c r="E77" s="15" t="inlineStr">
+      <c r="E77" s="16" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F77" s="16" t="inlineStr">
         <is>
           <t>設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
         </is>
       </c>
-      <c r="F77" s="14" t="inlineStr">
+      <c r="G77" s="15" t="inlineStr">
         <is>
           <t>R-06.png</t>
         </is>
       </c>
-      <c r="G77" s="15" t="inlineStr">
+      <c r="H77" s="16" t="inlineStr">
         <is>
           <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
         </is>
       </c>
-      <c r="H77" s="15" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr"/>
+      <c r="J77" s="16" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
         </is>
       </c>
-      <c r="I77" s="15" t="inlineStr">
+      <c r="K77" s="16" t="inlineStr">
         <is>
           <t>2つの入口で更新処理が共通か</t>
         </is>
       </c>
-      <c r="J77" s="15" t="inlineStr">
+      <c r="L77" s="16" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="K77" s="15" t="inlineStr">
+      <c r="M77" s="16" t="inlineStr">
         <is>
           <t>AC-49</t>
         </is>
       </c>
-      <c r="L77" s="5" t="inlineStr"/>
-      <c r="M77" s="5" t="inlineStr"/>
-      <c r="N77" s="15" t="inlineStr">
+      <c r="N77" s="5" t="inlineStr"/>
+      <c r="O77" s="5" t="inlineStr"/>
+      <c r="P77" s="16" t="inlineStr">
         <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N77"/>
+  <autoFilter ref="A2:P77"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="M3:M77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$P$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -134,6 +134,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -533,34 +536,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P77"/>
+  <dimension ref="A1:S77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="58" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="54" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="44" customWidth="1" min="16" max="16"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="83" customHeight="1">
+    <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>確かめる手順（準備11行＋検証64ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
 実施順を変えてはいけない箇所：①T-A08（勤怠取込）→T-S03（締め）　②T-S03→T-S04・T-D07→T-S05（この3件は締め済みでしか確認できない）　③C-000（初期化）は計算の先頭　④C-008は計算の最後（2026-05のEMP-001を352,286円に変えるためC-013・C-017が合わなくなる）　⑤T-N02の前にdata/02を再投入　⑥削除はEMP-012（T-L10）とEMP-004（T-D08）だけ
-列の使い方：使用する検証データ＝この検証で投入・使用するdataファイル（（投入済み）は準備行で入れたものを見るだけ）／画面＝どこを開くか（サイドバーからの経路・タブ・ボタン・モーダル）／確認ポイント＝何を見るか／期待値＝合否の基準／スクショ（撮るもの）＝何が写っていれば証拠になるか／スクショ貼付欄＝撮った画像をこの列に貼る／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めて合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを決める
-色：緑＝使う検証データ　青＝画面　橙＝スクショ　紫＝ヘルプ・受入条件　黄＝当日の記入欄。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
+列の使い方：使用する検証データ＝この検証で投入・使用するdataファイル／期待値＝先頭の【確認場所】でどの画面を見て合否を出すかを示し、続けて合格の基準を書いている／スクショ（撮るもの）＝何が写っていれば証拠になるか／スクショ貼付欄＝撮った画像をこの列に貼る／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めて合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを決める
+色：緑＝使う検証データ　青＝画面　橙＝スクショの指示　紫＝ヘルプ・受入条件との対応　黄＝当日の記入欄（スクショ貼付欄・実際の値・判定・所見・実施日・実施者）。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
         </is>
       </c>
     </row>
@@ -642,11 +648,26 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
+          <t>所見・気づき</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>実施日</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>実施者</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
           <t>計算根拠</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
+    <row r="3" ht="64" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -674,7 +695,8 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>サイドバーに「従業員管理」が表示される／モックのトップが表示される</t>
+          <t>【確認場所：サイドバー「従業員管理」（PCはホバー展開）／仕様モックのトップ】
+サイドバーに「従業員管理」が表示される／モックのトップが表示される</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -710,7 +732,10 @@
       </c>
       <c r="N3" s="5" t="inlineStr"/>
       <c r="O3" s="5" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr"/>
+      <c r="P3" s="6" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr"/>
     </row>
     <row r="4" ht="79" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -740,7 +765,8 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>6件が確定し文書化されている（仕様書 第5部 11-A・11-C）</t>
+          <t>【確認場所：画面操作なし】
+6件が確定し文書化されている（仕様書 第5部 11-A・11-C）</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -772,7 +798,10 @@
       </c>
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額／原則③：人件費は働いた店舗に付ける／計算：月中改定の日割り／原則③：交通費の帰属</t>
         </is>
@@ -807,7 +836,8 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>全行が算式で再現でき、日次合計＝月次・店舗別合計＝全社（差0円）</t>
+          <t>【確認場所：画面操作なし】
+全行が算式で再現でき、日次合計＝月次・店舗別合計＝全社（差0円）</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -839,7 +869,10 @@
       </c>
       <c r="N5" s="5" t="inlineStr"/>
       <c r="O5" s="5" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="P5" s="6" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額</t>
         </is>
@@ -874,7 +907,8 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>従業員一覧に12名が表示される</t>
+          <t>【確認場所：従業員一覧（サイドバー → 従業員管理 → 従業員一覧）】
+従業員一覧に12名が表示される</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -910,7 +944,10 @@
       </c>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -941,7 +978,8 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>履歴に適用済3・予約中1が入る／人件費実績に5名分が表示される</t>
+          <t>【確認場所：従業員設定履歴／人件費実績（月別実績タブ）】
+履歴に適用済3・予約中1が入る／人件費実績に5名分が表示される</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -977,7 +1015,10 @@
       </c>
       <c r="N7" s="5" t="inlineStr"/>
       <c r="O7" s="5" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr"/>
+      <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="94" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -1008,7 +1049,8 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>5ファイルがアップロード可能な状態／設定が欠落した従業員が1名いる</t>
+          <t>【確認場所：画面操作なし】
+5ファイルがアップロード可能な状態／設定が欠落した従業員が1名いる</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -1040,7 +1082,10 @@
       </c>
       <c r="N8" s="5" t="inlineStr"/>
       <c r="O8" s="5" t="inlineStr"/>
-      <c r="P8" s="4" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1071,7 +1116,8 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>以降の計算ケースで同じ入力値を使う</t>
+          <t>【確認場所：画面操作なし】
+以降の計算ケースで同じ入力値を使う</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1103,7 +1149,10 @@
       </c>
       <c r="N9" s="5" t="inlineStr"/>
       <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="4" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -1134,7 +1183,8 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>ボタンが「2026-05 締め」になっている</t>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+ボタンが「2026-05 締め」になっている</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1170,7 +1220,10 @@
       </c>
       <c r="N10" s="5" t="inlineStr"/>
       <c r="O10" s="5" t="inlineStr"/>
-      <c r="P10" s="4" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1201,7 +1254,8 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>突合シート M-01〜M-06 が埋まった状態</t>
+          <t>【確認場所：従業員一覧（CSVエクスポート）／人件費実績 月別実績（直近3か月）】
+突合シート M-01〜M-06 が埋まった状態</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1237,7 +1291,10 @@
       </c>
       <c r="N11" s="5" t="inlineStr"/>
       <c r="O11" s="5" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
+      <c r="P11" s="6" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -1268,7 +1325,8 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>店長でログインでき、従業員管理のメニューが表示される</t>
+          <t>【確認場所：画面操作なし】
+店長でログインでき、従業員管理のメニューが表示される</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -1300,7 +1358,10 @@
       </c>
       <c r="N12" s="5" t="inlineStr"/>
       <c r="O12" s="5" t="inlineStr"/>
-      <c r="P12" s="4" t="inlineStr"/>
+      <c r="P12" s="6" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -1331,7 +1392,8 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>移行を検証枠内で実行できる段取りができている</t>
+          <t>【確認場所：画面操作なし】
+移行を検証枠内で実行できる段取りができている</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -1363,4556 +1425,4815 @@
       </c>
       <c r="N13" s="5" t="inlineStr"/>
       <c r="O13" s="5" t="inlineStr"/>
-      <c r="P13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14" ht="94" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="P13" s="6" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="109" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>一覧</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>T-L01</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>一覧の表示</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
 【操作】従業員一覧を開き、列・バッジ・ソート・0件表示を確認</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>12名が表示。12列（名前/従業員コード/所属店舗/ヘルプ先店舗/雇用区分/給与単位/単位給与額/交通費単位/単位交通費/所定労働時間/みなし残業時間/アクション）。雇用区分・給与単位が色分け。EMP-001はヘルプ先2バッジ、EMP-002は空。単位給与額が数値順にソート（1,000→…→410,000）。該当なしで「データはありません。」</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員一覧】
+12名が表示。12列（名前/従業員コード/所属店舗/ヘルプ先店舗/雇用区分/給与単位/単位給与額/交通費単位/単位交通費/所定労働時間/みなし残業時間/アクション）。雇用区分・給与単位が色分け。EMP-001はヘルプ先2バッジ、EMP-002は空。単位給与額が数値順にソート（1,000→…→410,000）。該当なしで「データはありません。」</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>T-L01.png</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>一覧全体（12行・12列・バッジの色・ソート矢印）と、フィルタで0件にしたときの「データはありません。」</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>従業員一覧 … 表の12列・雇用区分/給与単位のバッジ・列ヘッダーのソート・0件表示</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>12列・バッジ・ソート・0件表示</t>
         </is>
       </c>
-      <c r="L14" s="12" t="inlineStr">
+      <c r="L14" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="M14" s="12" t="inlineStr">
+      <c r="M14" s="13" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr"/>
       <c r="O14" s="5" t="inlineStr"/>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr"/>
+      <c r="S14" s="8" t="inlineStr">
         <is>
           <t>移行：既存顧客が壊れない</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>一覧</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>T-L08</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>一覧のフィルタ</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-05
 【操作】1段目＝店舗「渋谷店」／雇用区分「正社員」／名前「田中」、2段目＝月「2026-05」／取込データ を順に適用</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>渋谷店＝3名（EMP-001・002・011）、正社員＝6名、田中＝1名。2段目で対象データが切り替わる</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員一覧】
+渋谷店＝3名（EMP-001・002・011）、正社員＝6名、田中＝1名。2段目で対象データが切り替わる</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>T-L08.png</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>1段目と2段目の両方を適用した状態（絞り込み条件と結果件数が同時に写ること）</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>従業員一覧 … 1段目フィルタ（店舗/雇用区分/名前検索）と2段目フィルタ（月/取込データ）</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>2段フィルタが効くか</t>
         </is>
       </c>
-      <c r="L15" s="12" t="inlineStr">
+      <c r="L15" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="M15" s="12" t="inlineStr">
+      <c r="M15" s="13" t="inlineStr">
         <is>
           <t>AC-33</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr"/>
       <c r="O15" s="5" t="inlineStr"/>
-      <c r="P15" s="7" t="inlineStr">
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="8" t="inlineStr">
         <is>
           <t>画面：対象を探せる</t>
         </is>
       </c>
     </row>
     <row r="16" ht="64" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>一覧</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>T-L06</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>一覧からの遷移</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
 【操作】右上「従業員登録」「CSVインポート」「設定・実績エクスポート」、2段目「設定取込データへ」、行の詳細アイコン を順に押す</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>5経路すべて到達（従業員登録／設定インポート／設定・実績エクスポート／設定取込データ／従業員詳細）。不通=0</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員一覧】
+5経路すべて到達（従業員登録／設定インポート／設定・実績エクスポート／設定取込データ／従業員詳細）。不通=0</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>T-L06.png</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>遷移先5画面の到達直後（従業員登録・設定インポート・エクスポート・設定取込データ・従業員詳細）</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>従業員一覧 … 右上ツールバー「従業員登録」「CSVインポート」「設定・実績エクスポート」／2段目「設定取込データへ」／行末の詳細アイコン</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>5経路すべて到達するか</t>
         </is>
       </c>
-      <c r="L16" s="12" t="inlineStr">
+      <c r="L16" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="M16" s="12" t="inlineStr">
+      <c r="M16" s="13" t="inlineStr">
         <is>
           <t>AC-30</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr"/>
       <c r="O16" s="5" t="inlineStr"/>
-      <c r="P16" s="7" t="inlineStr">
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr"/>
+      <c r="S16" s="8" t="inlineStr">
         <is>
           <t>画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>一覧</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>T-L10</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>一覧の削除</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
 【操作】EMP-012（山田 さくら・実績データに含まれない末尾の従業員）の削除アイコン →（a）キャンセル →（b）実行</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>05 月次給与実績</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>（a）12名のまま削除されない （b）完了表示のあと11名になる</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員一覧】
+（a）12名のまま削除されない （b）完了表示のあと11名になる</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>T-L10.png</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>削除の確認ダイアログ／キャンセル後の一覧／実行後の一覧（行が消えたこと）</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t>従業員一覧 … 行末の削除アイコン → 確認ダイアログ</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="K17" s="8" t="inlineStr">
         <is>
           <t>キャンセルで消えない／実行で消えるか</t>
         </is>
       </c>
-      <c r="L17" s="12" t="inlineStr">
+      <c r="L17" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="M17" s="12" t="inlineStr">
+      <c r="M17" s="13" t="inlineStr">
         <is>
           <t>AC-34</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr"/>
       <c r="O17" s="5" t="inlineStr"/>
-      <c r="P17" s="7" t="inlineStr">
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="8" t="inlineStr">
         <is>
           <t>データ保全：消える操作は確認を経る</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="79" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="18" ht="109" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>登録</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>T-R02</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>登録フォームの項目</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
 【操作】従業員登録を開き、項目と通貨表示を確認（単位給与額に 320000 と入力）</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>13項目（名前/従業員コード/所属店舗/ヘルプ先店舗/雇用区分/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。¥320,000 と千区切り表示。適用日付は所定労働時間・みなし残業時間の下の行・初期値は当日</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員登録（従業員一覧 右上「従業員登録」から遷移）】
+13項目（名前/従業員コード/所属店舗/ヘルプ先店舗/雇用区分/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。¥320,000 と千区切り表示。適用日付は所定労働時間・みなし残業時間の下の行・初期値は当日</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>T-R02.png</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>登録フォーム全体（単位給与額に320,000と入れ、桁区切りが効いている状態）</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>従業員登録（従業員一覧 右上「従業員登録」から遷移）… 入力フォーム全体と通貨の桁区切り表示</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>項目の過不足と桁区切り表示</t>
         </is>
       </c>
-      <c r="L18" s="12" t="inlineStr">
+      <c r="L18" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
-      <c r="M18" s="12" t="inlineStr">
+      <c r="M18" s="13" t="inlineStr">
         <is>
           <t>AC-06</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr"/>
       <c r="O18" s="5" t="inlineStr"/>
-      <c r="P18" s="7" t="inlineStr">
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+      <c r="S18" s="8" t="inlineStr">
         <is>
           <t>原則①：当日・過去日は即時</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>登録</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>T-R04</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>ヘルプ先交通費の連動</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
 【操作】ヘルプ先店舗で青山店＋新宿店を選択 →（a）空のまま登録 →（b）新宿店の選択を外す</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>選択した2店それぞれに交通費欄が出る／（a）必須バリデーションで登録できない／（b）新宿店の欄だけ消え、青山店の入力値は残る</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員登録】
+選択した2店それぞれに交通費欄が出る／（a）必須バリデーションで登録できない／（b）新宿店の欄だけ消え、青山店の入力値は残る</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>T-R04.png</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>ヘルプ先2店選択でヘルプ先交通費欄が出た状態／1店外して欄が消えた状態の2枚</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>従業員登録 … ヘルプ先店舗の複数選択と、その下に自動表示されるヘルプ先交通費の入力欄</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>交通費欄が自動で出る／消えるか</t>
         </is>
       </c>
-      <c r="L19" s="12" t="inlineStr">
+      <c r="L19" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
-      <c r="M19" s="12" t="inlineStr">
+      <c r="M19" s="13" t="inlineStr">
         <is>
           <t>AC-15 AC-47</t>
         </is>
       </c>
       <c r="N19" s="5" t="inlineStr"/>
       <c r="O19" s="5" t="inlineStr"/>
-      <c r="P19" s="7" t="inlineStr">
+      <c r="P19" s="6" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="8" t="inlineStr">
         <is>
           <t>原則③：交通費の帰属／原則③：交通費も働いた店舗の実費で</t>
         </is>
       </c>
     </row>
     <row r="20" ht="64" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>登録</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>T-R07</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>登録の実行・中断</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
 【操作】（a）必須を埋めて「登録」（適用日付＝当日）（b）入力途中で「キャンセル」（c）ツールバー「従業員一覧へ」「CSVインポート」</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>（a）完了表示のあと一覧へ戻り、登録前より1名増えている （b）一覧へ戻り件数は変わらない （c）従業員一覧／設定インポートへ遷移</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員登録】
+（a）完了表示のあと一覧へ戻り、登録前より1名増えている （b）一覧へ戻り件数は変わらない （c）従業員一覧／設定インポートへ遷移</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>T-R07.png</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>登録成功後の従業員一覧（新規行が見えること）とキャンセル後の一覧</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>従業員登録 … 下部「登録」「キャンセル」／ツールバー「従業員一覧へ」「CSVインポート」→ 従業員一覧</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>登録される／されないの分岐</t>
         </is>
       </c>
-      <c r="L20" s="12" t="inlineStr">
+      <c r="L20" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を登録する</t>
         </is>
       </c>
-      <c r="M20" s="12" t="inlineStr">
+      <c r="M20" s="13" t="inlineStr">
         <is>
           <t>AC-06 AC-30</t>
         </is>
       </c>
       <c r="N20" s="5" t="inlineStr"/>
       <c r="O20" s="5" t="inlineStr"/>
-      <c r="P20" s="7" t="inlineStr">
+      <c r="P20" s="6" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+      <c r="S20" s="8" t="inlineStr">
         <is>
           <t>原則①：当日・過去日は即時／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>登録</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>T-R10</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>必須未入力では保存も遷移もしないこと</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
 【操作】名前・従業員コード・所属店舗・雇用区分・給与単位・単位給与額 をそれぞれ空にして「登録」を押す</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>6項目それぞれで 登録=0件・画面遷移=0件（6回とも同じ）。不足している項目名が画面上に表示される</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員登録】
+6項目それぞれで 登録=0件・画面遷移=0件（6回とも同じ）。不足している項目名が画面上に表示される</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>T-R10.png</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>必須未入力で「登録」を押した直後（エラー表示と、画面が遷移していないこと）</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>従業員登録 … 必須項目のバリデーション表示（画面に留まること）</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>必須未入力で保存も遷移もしないか</t>
         </is>
       </c>
-      <c r="L21" s="12" t="inlineStr">
+      <c r="L21" s="13" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
-      <c r="M21" s="12" t="inlineStr">
+      <c r="M21" s="13" t="inlineStr">
         <is>
           <t>AC-43</t>
         </is>
       </c>
       <c r="N21" s="5" t="inlineStr"/>
       <c r="O21" s="5" t="inlineStr"/>
-      <c r="P21" s="7" t="inlineStr">
+      <c r="P21" s="6" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="8" t="inlineStr">
         <is>
           <t>データ保全：不完全な登録を作らない</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22" ht="79" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>詳細</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>T-D01</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>詳細の表示</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-05
 【操作】EMP-001の詳細を開き、3セクションと履歴の列を確認</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>基本情報／設定変更履歴／給与実績 が表示。基本情報は登録と同項目・同配置。履歴は14列（変更反映日時〜変更ソース の13項目＋操作）。2026-08-01行が「予約中」</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員詳細（従業員一覧の詳細アイコンから遷移）】
+基本情報／設定変更履歴／給与実績 が表示。基本情報は登録と同項目・同配置。履歴は14列（変更反映日時〜変更ソース の13項目＋操作）。2026-08-01行が「予約中」</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>T-D01.png</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>従業員詳細の全体（基本情報・設定変更履歴・給与実績の3セクションが分かる範囲）</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>従業員詳細（従業員一覧の詳細アイコンから遷移）… 基本情報／設定変更履歴／給与実績の3セクション</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>3セクションと履歴14列</t>
         </is>
       </c>
-      <c r="L22" s="12" t="inlineStr">
+      <c r="L22" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="M22" s="12" t="inlineStr">
+      <c r="M22" s="13" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
       <c r="N22" s="5" t="inlineStr"/>
       <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="7" t="inlineStr">
+      <c r="P22" s="6" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
+      <c r="S22" s="8" t="inlineStr">
         <is>
           <t>原則①：過去は不変</t>
         </is>
       </c>
     </row>
     <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>詳細</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>T-D04</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>未来日＝予約になる</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-05 S-07
 【操作】単位給与額を340,000に変更し、適用日付＝翌月1日で「保存」</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>「（日付）からの適用を予約しました」と表示。履歴に「予約中」が1行追加。一覧の単位給与額は320,000のまま</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員詳細】
+「（日付）からの適用を予約しました」と表示。履歴に「予約中」が1行追加。一覧の単位給与額は320,000のまま</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>T-D04.png</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>保存直後のトースト「◯月◯日からの適用を予約しました」／履歴の「予約中」行／一覧の値が未変更であること の3枚</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J23" s="12" t="inlineStr">
         <is>
           <t>従業員詳細 … 基本情報の単位給与額と適用日付 → 下部「保存」→ 従業員一覧のトーストと一覧値</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr">
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>予約になり一覧の値が変わらないか</t>
         </is>
       </c>
-      <c r="L23" s="12" t="inlineStr">
+      <c r="L23" s="13" t="inlineStr">
         <is>
           <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
-      <c r="M23" s="12" t="inlineStr">
+      <c r="M23" s="13" t="inlineStr">
         <is>
           <t>AC-04</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr"/>
       <c r="O23" s="5" t="inlineStr"/>
-      <c r="P23" s="7" t="inlineStr">
+      <c r="P23" s="6" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="8" t="inlineStr">
         <is>
           <t>原則①：未来日は予約になる</t>
         </is>
       </c>
     </row>
     <row r="24" ht="79" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>詳細</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>T-D05</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>予約の自動適用</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>【前提】T-D04実施済み
 【操作】適用日を迎えた状態を作って、一覧と履歴を再表示する。次の3通りから検証環境で可能な方法を選ぶ：①前日に予約を仕込み翌日に確認（8/12仕込み→8/13確認）②システム日付を進める ③予約適用のバッチを手動実行する</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>一覧が340,000に変わり、履歴が「適用中」、旧行が「過去」になる</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員詳細（予約を仕込む）→ 翌日の従業員一覧と設定変更履歴のステー】
+一覧が340,000に変わり、履歴が「適用中」、旧行が「過去」になる</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>T-D05.png</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>適用日を迎えた後の一覧の値と、履歴のステータスが「適用中」に変わった行</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>従業員詳細（予約を仕込む）→ 翌日の従業員一覧と設定変更履歴のステータス</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr">
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t>適用日に自動で切り替わるか</t>
         </is>
       </c>
-      <c r="L24" s="12" t="inlineStr">
+      <c r="L24" s="13" t="inlineStr">
         <is>
           <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
-      <c r="M24" s="12" t="inlineStr">
+      <c r="M24" s="13" t="inlineStr">
         <is>
           <t>AC-05</t>
         </is>
       </c>
       <c r="N24" s="5" t="inlineStr"/>
       <c r="O24" s="5" t="inlineStr"/>
-      <c r="P24" s="7" t="inlineStr">
+      <c r="P24" s="6" t="inlineStr"/>
+      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr"/>
+      <c r="S24" s="8" t="inlineStr">
         <is>
           <t>原則①：予約が自動で効く</t>
         </is>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>詳細</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>T-D06</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>当日適用＝即時反映</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
 【操作】EMP-002の単位給与額を290,000に変更し、適用日付＝当日で「保存」</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>「即時反映しました」と表示。一覧が290,000になる</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員詳細】
+「即時反映しました」と表示。一覧が290,000になる</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>T-D06.png</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>トースト「即時反映しました」と、一覧の値が290,000になった状態</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="J25" s="12" t="inlineStr">
         <is>
           <t>従業員詳細 … 適用日付＝当日で「保存」→ 従業員一覧の値</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr">
+      <c r="K25" s="8" t="inlineStr">
         <is>
           <t>即時反映され一覧の値が変わるか</t>
         </is>
       </c>
-      <c r="L25" s="12" t="inlineStr">
+      <c r="L25" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="M25" s="12" t="inlineStr">
+      <c r="M25" s="13" t="inlineStr">
         <is>
           <t>AC-06</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr"/>
       <c r="O25" s="5" t="inlineStr"/>
-      <c r="P25" s="7" t="inlineStr">
+      <c r="P25" s="6" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="8" t="inlineStr">
         <is>
           <t>原則①：当日・過去日は即時</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="64" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="26" ht="79" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>詳細</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>T-D09</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>詳細の給与実績</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
 【操作】給与実績セクションで 月次タブ（概算⇄実績・年フィルタ）→ 日次タブ（月フィルタ）→ 各タブでCSVエクスポート</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>月次17列（年月〜深夜残業代＋交通費＋総支給額）／日次14列。個人向けに列を絞った構成で、人件費実績（26列/21列）とは別。フィルタで期間が絞られる。表示中の内容がBOM付きCSVで出力される</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員詳細 → 給与実績セクション】
+月次17列（年月〜深夜残業代＋交通費＋総支給額）／日次14列。個人向けに列を絞った構成で、人件費実績（26列/21列）とは別。フィルタで期間が絞られる。表示中の内容がBOM付きCSVで出力される</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>T-D09.png</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>月次タブ（概算／実績の両方）と日次タブ／出力したCSVをExcelで開いた画面</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J26" s="12" t="inlineStr">
         <is>
           <t>従業員詳細 → 給与実績セクション … 月次タブ（概算⇄実績の切替・年フィルタ）／日次タブ（月フィルタ）／各タブのCSVエクスポート</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>タブ切替とCSVの中身が変わるか</t>
         </is>
       </c>
-      <c r="L26" s="12" t="inlineStr">
+      <c r="L26" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="M26" s="12" t="inlineStr">
+      <c r="M26" s="13" t="inlineStr">
         <is>
           <t>AC-35 AC-36</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr"/>
       <c r="O26" s="5" t="inlineStr"/>
-      <c r="P26" s="7" t="inlineStr">
+      <c r="P26" s="6" t="inlineStr"/>
+      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr"/>
+      <c r="S26" s="8" t="inlineStr">
         <is>
           <t>計算：個人単位でも同じ数字／入出力：画面の内容と一致</t>
         </is>
       </c>
     </row>
     <row r="27" ht="64" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>詳細</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>T-D08</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>詳細の削除・戻る</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
 【操作】EMP-004（山本 健／実績データにも取込CSVにも含まれない）の詳細を開き「従業員削除」→（a）キャンセル →（b）実行、（c）別の従業員で「一覧へ戻る」</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>（a）削除されず件数が変わらない （b）確認のあと削除される （c）一覧へ戻る（保存されない）</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員詳細】
+（a）削除されず件数が変わらない （b）確認のあと削除される （c）一覧へ戻る（保存されない）</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>T-D08.png</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>削除の確認モーダル／実行後の一覧（行が消えたこと）</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="J27" s="12" t="inlineStr">
         <is>
           <t>従業員詳細 … 下部「従業員削除」→ 確認モーダル／「一覧へ戻る」→ 従業員一覧</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>キャンセルで消えない／実行で消えるか</t>
         </is>
       </c>
-      <c r="L27" s="12" t="inlineStr">
+      <c r="L27" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
-      <c r="M27" s="12" t="inlineStr">
+      <c r="M27" s="13" t="inlineStr">
         <is>
           <t>AC-34 AC-30</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr"/>
       <c r="O27" s="5" t="inlineStr"/>
-      <c r="P27" s="7" t="inlineStr">
+      <c r="P27" s="6" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="8" t="inlineStr">
         <is>
           <t>データ保全：消える操作は確認を経る／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>T-H01</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>履歴の追記と過去行の不変</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05 ／ 変更前の履歴をCSV出力しておく
 【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>履歴が1行増える。既存行の値の差分＝0</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員設定履歴】
+履歴が1行増える。既存行の値の差分＝0</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>T-H01.png</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J28" s="12" t="inlineStr">
         <is>
           <t>従業員設定履歴 … 変更前後の行（既存行が書き換わらないこと）</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr">
+      <c r="K28" s="8" t="inlineStr">
         <is>
           <t>既存行が書き換わらないか</t>
         </is>
       </c>
-      <c r="L28" s="12" t="inlineStr">
+      <c r="L28" s="13" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="M28" s="12" t="inlineStr">
+      <c r="M28" s="13" t="inlineStr">
         <is>
           <t>AC-07</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr"/>
       <c r="O28" s="5" t="inlineStr"/>
-      <c r="P28" s="7" t="inlineStr">
+      <c r="P28" s="6" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr"/>
+      <c r="S28" s="8" t="inlineStr">
         <is>
           <t>原則①：過去は不変</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="64" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29" ht="79" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>T-H02</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>記録の内容</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05 T-D04実施済み
 【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員設定履歴】
+①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>T-H02.png</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
         <is>
           <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>従業員設定履歴 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>2つの日時が別で記録されるか</t>
         </is>
       </c>
-      <c r="L29" s="12" t="inlineStr">
+      <c r="L29" s="13" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="M29" s="12" t="inlineStr">
+      <c r="M29" s="13" t="inlineStr">
         <is>
           <t>AC-08 AC-09</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr"/>
       <c r="O29" s="5" t="inlineStr"/>
-      <c r="P29" s="7" t="inlineStr">
+      <c r="P29" s="6" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="8" t="inlineStr">
         <is>
           <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="79" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="30" ht="94" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>T-H04</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>履歴の絞り込み・出力・遷移</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
 【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員設定履歴】
+店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>T-H04.png</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H30" s="11" t="inlineStr">
         <is>
           <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="J30" s="12" t="inlineStr">
         <is>
           <t>従業員設定履歴 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
         </is>
       </c>
-      <c r="K30" s="7" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>絞り込み後の行だけ出力されるか</t>
         </is>
       </c>
-      <c r="L30" s="12" t="inlineStr">
+      <c r="L30" s="13" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="M30" s="12" t="inlineStr">
+      <c r="M30" s="13" t="inlineStr">
         <is>
           <t>AC-33 AC-36 AC-30</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr"/>
       <c r="O30" s="5" t="inlineStr"/>
-      <c r="P30" s="7" t="inlineStr">
+      <c r="P30" s="6" t="inlineStr"/>
+      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr"/>
+      <c r="S30" s="8" t="inlineStr">
         <is>
           <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="109" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="31" ht="124" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>T-A02</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>月別実績の表示と切替</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
 【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>T-A02.png</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H31" s="11" t="inlineStr">
         <is>
           <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="11" t="inlineStr">
+      <c r="J31" s="12" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr">
+      <c r="K31" s="8" t="inlineStr">
         <is>
           <t>モード切替で列が増減するか</t>
         </is>
       </c>
-      <c r="L31" s="12" t="inlineStr">
+      <c r="L31" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="M31" s="12" t="inlineStr">
+      <c r="M31" s="13" t="inlineStr">
         <is>
           <t>AC-10 AC-31</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr"/>
       <c r="O31" s="5" t="inlineStr"/>
-      <c r="P31" s="7" t="inlineStr">
+      <c r="P31" s="6" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr"/>
+      <c r="S31" s="8" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額／画面：状態が漏れない</t>
         </is>
       </c>
     </row>
     <row r="32" ht="64" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>T-A09</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>人件費実績からの設定編集</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
 【操作】人件費実績で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績　→　行の「従業員設定」】
+モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>T-A09.png</t>
         </is>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>設定編集モーダル（項目が見える状態）／更新保存後の人件費実績／従業員詳細の設定変更履歴に行が増えたこと</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>人件費実績 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 人件費実績／確認は従業員詳細の設定変更履歴</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t>モーダル編集でも履歴が残るか</t>
         </is>
       </c>
-      <c r="L32" s="12" t="inlineStr">
+      <c r="L32" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="M32" s="12" t="inlineStr">
+      <c r="M32" s="13" t="inlineStr">
         <is>
           <t>AC-49</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr"/>
       <c r="O32" s="5" t="inlineStr"/>
-      <c r="P32" s="7" t="inlineStr">
+      <c r="P32" s="6" t="inlineStr"/>
+      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="R32" s="5" t="inlineStr"/>
+      <c r="S32" s="8" t="inlineStr">
         <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="94" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="33" ht="109" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>T-A05</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>日別実績の表示</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
 【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 日別実績タブ】
+全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>T-A05.png</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="11" t="inlineStr">
+      <c r="J33" s="12" t="inlineStr">
         <is>
           <t>人件費実績 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>日別に概算モードが無いか</t>
         </is>
       </c>
-      <c r="L33" s="12" t="inlineStr">
+      <c r="L33" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="M33" s="12" t="inlineStr">
+      <c r="M33" s="13" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
       <c r="O33" s="5" t="inlineStr"/>
-      <c r="P33" s="7" t="inlineStr">
+      <c r="P33" s="6" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+      <c r="R33" s="5" t="inlineStr"/>
+      <c r="S33" s="8" t="inlineStr">
         <is>
           <t>計算：算式どおりの金額</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>T-A07</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>実績のCSVエクスポート</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
 【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績】
+出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>T-A07.png</t>
         </is>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H34" s="11" t="inlineStr">
         <is>
           <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>人件費実績 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr">
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>表示中の内容が出力されるか</t>
         </is>
       </c>
-      <c r="L34" s="12" t="inlineStr">
+      <c r="L34" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="M34" s="12" t="inlineStr">
+      <c r="M34" s="13" t="inlineStr">
         <is>
           <t>AC-36</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr"/>
       <c r="O34" s="5" t="inlineStr"/>
-      <c r="P34" s="7" t="inlineStr">
+      <c r="P34" s="6" t="inlineStr"/>
+      <c r="Q34" s="5" t="inlineStr"/>
+      <c r="R34" s="5" t="inlineStr"/>
+      <c r="S34" s="8" t="inlineStr">
         <is>
           <t>入出力：画面の内容と一致</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>実績</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>T-A08</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>勤怠実績の取込</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05 S-08
 【操作】人件費実績の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>T-A08.png</t>
         </is>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="11" t="inlineStr">
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr">
+      <c r="K35" s="8" t="inlineStr">
         <is>
           <t>進捗が出て他操作を受け付けないか</t>
         </is>
       </c>
-      <c r="L35" s="12" t="inlineStr">
+      <c r="L35" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="M35" s="12" t="inlineStr">
+      <c r="M35" s="13" t="inlineStr">
         <is>
           <t>AC-48</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr"/>
       <c r="O35" s="5" t="inlineStr"/>
-      <c r="P35" s="7" t="inlineStr">
+      <c r="P35" s="6" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+      <c r="R35" s="5" t="inlineStr"/>
+      <c r="S35" s="8" t="inlineStr">
         <is>
           <t>入出力：勤怠実績を取り込める</t>
         </is>
       </c>
     </row>
     <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>締め</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>T-S01</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>締めボタンの表示条件</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>【前提】S-08
 【操作】月別実績タブと日別実績タブを順に開く</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>月別のみ「2026-05 締め」が表示。日別には表示されない</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績】
+月別のみ「2026-05 締め」が表示。日別には表示されない</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>T-S01.png</t>
         </is>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>人件費実績 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr">
+      <c r="K36" s="8" t="inlineStr">
         <is>
           <t>締めが月別タブにだけ出るか</t>
         </is>
       </c>
-      <c r="L36" s="12" t="inlineStr">
+      <c r="L36" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="M36" s="12" t="inlineStr">
+      <c r="M36" s="13" t="inlineStr">
         <is>
           <t>AC-18</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr"/>
       <c r="O36" s="5" t="inlineStr"/>
-      <c r="P36" s="7" t="inlineStr">
+      <c r="P36" s="6" t="inlineStr"/>
+      <c r="Q36" s="5" t="inlineStr"/>
+      <c r="R36" s="5" t="inlineStr"/>
+      <c r="S36" s="8" t="inlineStr">
         <is>
           <t>原則②：締めの単位は月</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>締め</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>T-S03</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>締めの実行</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06 S-08
 【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>T-S03.png</t>
         </is>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="11" t="inlineStr">
+      <c r="J37" s="12" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr">
+      <c r="K37" s="8" t="inlineStr">
         <is>
           <t>確認モーダルを経て締まるか</t>
         </is>
       </c>
-      <c r="L37" s="12" t="inlineStr">
+      <c r="L37" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
-      <c r="M37" s="12" t="inlineStr">
+      <c r="M37" s="13" t="inlineStr">
         <is>
           <t>AC-16 AC-19 AC-32</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr"/>
       <c r="O37" s="5" t="inlineStr"/>
-      <c r="P37" s="7" t="inlineStr">
+      <c r="P37" s="6" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr"/>
+      <c r="R37" s="5" t="inlineStr"/>
+      <c r="S37" s="8" t="inlineStr">
         <is>
           <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
         </is>
       </c>
     </row>
     <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>締め</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>T-S04</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>締め後は編集できない</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>【前提】T-S03実施済み
 【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>編集できない（または反映されない）</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績】
+編集できない（または反映されない）</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>T-S04.png</t>
         </is>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="11" t="inlineStr">
+      <c r="J38" s="12" t="inlineStr">
         <is>
           <t>人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
         </is>
       </c>
-      <c r="K38" s="7" t="inlineStr">
+      <c r="K38" s="8" t="inlineStr">
         <is>
           <t>締め後に金額が動かないか</t>
         </is>
       </c>
-      <c r="L38" s="12" t="inlineStr">
+      <c r="L38" s="13" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
-      <c r="M38" s="12" t="inlineStr">
+      <c r="M38" s="13" t="inlineStr">
         <is>
           <t>AC-16</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr"/>
       <c r="O38" s="5" t="inlineStr"/>
-      <c r="P38" s="7" t="inlineStr">
+      <c r="P38" s="6" t="inlineStr"/>
+      <c r="Q38" s="5" t="inlineStr"/>
+      <c r="R38" s="5" t="inlineStr"/>
+      <c r="S38" s="8" t="inlineStr">
         <is>
           <t>原則②：締めたら動かない</t>
         </is>
       </c>
     </row>
     <row r="39" ht="60" customHeight="1">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>締め</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>T-D07</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>締め済み期間への遡及</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>【前提】T-S03実施済み S-07
 【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員詳細】
+締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>T-D07.png</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr"/>
-      <c r="J39" s="11" t="inlineStr">
+      <c r="J39" s="12" t="inlineStr">
         <is>
           <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr">
+      <c r="K39" s="8" t="inlineStr">
         <is>
           <t>警告が出て反映されないか</t>
         </is>
       </c>
-      <c r="L39" s="12" t="inlineStr">
+      <c r="L39" s="13" t="inlineStr">
         <is>
           <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
-      <c r="M39" s="12" t="inlineStr">
+      <c r="M39" s="13" t="inlineStr">
         <is>
           <t>AC-20</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr"/>
       <c r="O39" s="5" t="inlineStr"/>
-      <c r="P39" s="7" t="inlineStr">
+      <c r="P39" s="6" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr"/>
+      <c r="R39" s="5" t="inlineStr"/>
+      <c r="S39" s="8" t="inlineStr">
         <is>
           <t>原則②：遡及は黙って捨てない</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>締め</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>T-S05</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>締めの解除</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>【前提】T-S03実施済み
 【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>T-S05.png</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr">
         <is>
           <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="J40" s="12" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
         </is>
       </c>
-      <c r="K40" s="7" t="inlineStr">
+      <c r="K40" s="8" t="inlineStr">
         <is>
           <t>解除で再計算されるか</t>
         </is>
       </c>
-      <c r="L40" s="12" t="inlineStr">
+      <c r="L40" s="13" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
-      <c r="M40" s="12" t="inlineStr">
+      <c r="M40" s="13" t="inlineStr">
         <is>
           <t>AC-19</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr"/>
       <c r="O40" s="5" t="inlineStr"/>
-      <c r="P40" s="7" t="inlineStr">
+      <c r="P40" s="6" t="inlineStr"/>
+      <c r="Q40" s="5" t="inlineStr"/>
+      <c r="R40" s="5" t="inlineStr"/>
+      <c r="S40" s="8" t="inlineStr">
         <is>
           <t>原則②：確定操作は確認を経る</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>締め</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>T-S07</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>締めの実行権限</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>【前提】S-10 S-08
 【操作】店長スコープのアカウントでログインし、人件費実績を開いて締めを試みる</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績タブ（店長スコープでログイン）】
+締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>T-S07.png</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr">
         <is>
           <t>店長スコープでの人件費実績（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
-      <c r="J41" s="11" t="inlineStr">
+      <c r="J41" s="12" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
         </is>
       </c>
-      <c r="K41" s="7" t="inlineStr">
+      <c r="K41" s="8" t="inlineStr">
         <is>
           <t>店長が締められないか</t>
         </is>
       </c>
-      <c r="L41" s="12" t="inlineStr">
+      <c r="L41" s="13" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
-      <c r="M41" s="12" t="inlineStr">
+      <c r="M41" s="13" t="inlineStr">
         <is>
           <t>AC-41</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr"/>
       <c r="O41" s="5" t="inlineStr"/>
-      <c r="P41" s="7" t="inlineStr">
+      <c r="P41" s="6" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr"/>
+      <c r="R41" s="5" t="inlineStr"/>
+      <c r="S41" s="8" t="inlineStr">
         <is>
           <t>原則②：締めは会社スコープのみ</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="64" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="42" ht="79" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>取込</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>T-I02</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>テンプレートのDLと画面</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定インポート】
+従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>T-I02.png</t>
         </is>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="H42" s="11" t="inlineStr">
         <is>
           <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="11" t="inlineStr">
+      <c r="J42" s="12" t="inlineStr">
         <is>
           <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
         </is>
       </c>
-      <c r="K42" s="7" t="inlineStr">
+      <c r="K42" s="8" t="inlineStr">
         <is>
           <t>テンプレートの列とBOM</t>
         </is>
       </c>
-      <c r="L42" s="12" t="inlineStr">
+      <c r="L42" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
-      <c r="M42" s="12" t="inlineStr">
+      <c r="M42" s="13" t="inlineStr">
         <is>
           <t>AC-21 AC-30</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr"/>
       <c r="O42" s="5" t="inlineStr"/>
-      <c r="P42" s="7" t="inlineStr">
+      <c r="P42" s="6" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr"/>
+      <c r="R42" s="5" t="inlineStr"/>
+      <c r="S42" s="8" t="inlineStr">
         <is>
           <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="43" ht="64" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>取込</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>T-I03</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>King of Time形式の取込</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
 【操作】データ種類＝King of Time を選び data/07（従業員設定・3行）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>07は3行すべて取り込まれ、EMP-001=340,000・EMP-005=360,000に更新、EMP-013は新規追加。10は給与設定（ヘルプ先交通費 S02:700;S03:900 の記法を含む）が反映される</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定インポート】
+07は3行すべて取り込まれ、EMP-001=340,000・EMP-005=360,000に更新、EMP-013は新規追加。10は給与設定（ヘルプ先交通費 S02:700;S03:900 の記法を含む）が反映される</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
         <is>
           <t>T-I03.png</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="H43" s="11" t="inlineStr">
         <is>
           <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="11" t="inlineStr">
+      <c r="J43" s="12" t="inlineStr">
         <is>
           <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="K43" s="8" t="inlineStr">
         <is>
           <t>3行が更新・追加されるか</t>
         </is>
       </c>
-      <c r="L43" s="12" t="inlineStr">
+      <c r="L43" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
-      <c r="M43" s="12" t="inlineStr">
+      <c r="M43" s="13" t="inlineStr">
         <is>
           <t>AC-21</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr"/>
       <c r="O43" s="5" t="inlineStr"/>
-      <c r="P43" s="7" t="inlineStr">
+      <c r="P43" s="6" t="inlineStr"/>
+      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="R43" s="5" t="inlineStr"/>
+      <c r="S43" s="8" t="inlineStr">
         <is>
           <t>入出力：導入を止めない</t>
         </is>
       </c>
     </row>
     <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>取込</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>T-I04</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>ジョブカン形式（表記ゆれ）の取込</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
 【操作】データ種類＝ジョブカン を選び data/08（3行）をD&amp;D → 登録</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>08 取込CSV ジョブカン</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>3行すべて取り込まれる（EMP-003=1,250・EMP-010=1,300・EMP-014は新規）</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定インポート】
+3行すべて取り込まれる（EMP-003=1,250・EMP-010=1,300・EMP-014は新規）</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>T-I04.png</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H44" s="11" t="inlineStr">
         <is>
           <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="J44" s="12" t="inlineStr">
         <is>
           <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
         </is>
       </c>
-      <c r="K44" s="7" t="inlineStr">
+      <c r="K44" s="8" t="inlineStr">
         <is>
           <t>表記ゆれを吸収できるか</t>
         </is>
       </c>
-      <c r="L44" s="12" t="inlineStr">
+      <c r="L44" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
-      <c r="M44" s="12" t="inlineStr">
+      <c r="M44" s="13" t="inlineStr">
         <is>
           <t>AC-22</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr"/>
       <c r="O44" s="5" t="inlineStr"/>
-      <c r="P44" s="7" t="inlineStr">
+      <c r="P44" s="6" t="inlineStr"/>
+      <c r="Q44" s="5" t="inlineStr"/>
+      <c r="R44" s="5" t="inlineStr"/>
+      <c r="S44" s="8" t="inlineStr">
         <is>
           <t>入出力：表記ゆれを吸収</t>
         </is>
       </c>
     </row>
     <row r="45" ht="60" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>取込</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>T-I05</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>異常系データの検出</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
 【操作】data/09（4行）をD&amp;D → 登録</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>09 取込CSV 異常系</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
-        </is>
-      </c>
-      <c r="G45" s="9" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定インポート】
+4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>T-I05.png</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H45" s="11" t="inlineStr">
         <is>
           <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
         </is>
       </c>
-      <c r="K45" s="7" t="inlineStr">
+      <c r="K45" s="8" t="inlineStr">
         <is>
           <t>4種の異常を行ごとに検出するか</t>
         </is>
       </c>
-      <c r="L45" s="12" t="inlineStr">
+      <c r="L45" s="13" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
-      <c r="M45" s="12" t="inlineStr">
+      <c r="M45" s="13" t="inlineStr">
         <is>
           <t>AC-23</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr"/>
       <c r="O45" s="5" t="inlineStr"/>
-      <c r="P45" s="7" t="inlineStr">
+      <c r="P45" s="6" t="inlineStr"/>
+      <c r="Q45" s="5" t="inlineStr"/>
+      <c r="R45" s="5" t="inlineStr"/>
+      <c r="S45" s="8" t="inlineStr">
         <is>
           <t>データ保全：不正値を入れない</t>
         </is>
       </c>
     </row>
     <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>取込</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>T-I17</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>二重登録の防止</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
 【操作】（a）data/07を2回続けて取り込む （b）data/19（EMP-002が2行・単位給与額が異なる）を取り込む</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>（a）2回目は更新となり件数が増えない （b）重複行がエラーとして検出される（両方が登録されない）</t>
-        </is>
-      </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定インポート】
+（a）2回目は更新となり件数が増えない （b）重複行がエラーとして検出される（両方が登録されない）</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>T-I17.png</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="H46" s="11" t="inlineStr">
         <is>
           <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="11" t="inlineStr">
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
         </is>
       </c>
-      <c r="K46" s="7" t="inlineStr">
+      <c r="K46" s="8" t="inlineStr">
         <is>
           <t>二重登録されないか</t>
         </is>
       </c>
-      <c r="L46" s="12" t="inlineStr">
+      <c r="L46" s="13" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
-      <c r="M46" s="12" t="inlineStr">
+      <c r="M46" s="13" t="inlineStr">
         <is>
           <t>AC-40</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr"/>
       <c r="O46" s="5" t="inlineStr"/>
-      <c r="P46" s="7" t="inlineStr">
+      <c r="P46" s="6" t="inlineStr"/>
+      <c r="Q46" s="5" t="inlineStr"/>
+      <c r="R46" s="5" t="inlineStr"/>
+      <c r="S46" s="8" t="inlineStr">
         <is>
           <t>データ保全：二重登録を防ぐ</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="64" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
+    <row r="47" ht="94" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>取込</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>T-I18</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>取込が途中で失敗したときの扱い</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
 【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>09 取込CSV 異常系</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録】
+中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>T-I18.png</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H47" s="11" t="inlineStr">
         <is>
           <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="11" t="inlineStr">
+      <c r="J47" s="12" t="inlineStr">
         <is>
           <t>設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録されていないこと）</t>
         </is>
       </c>
-      <c r="K47" s="7" t="inlineStr">
+      <c r="K47" s="8" t="inlineStr">
         <is>
           <t>部分登録が残らないか</t>
         </is>
       </c>
-      <c r="L47" s="12" t="inlineStr">
+      <c r="L47" s="13" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr">
+      <c r="M47" s="13" t="inlineStr">
         <is>
           <t>AC-42</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr"/>
       <c r="O47" s="5" t="inlineStr"/>
-      <c r="P47" s="7" t="inlineStr">
+      <c r="P47" s="6" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr"/>
+      <c r="R47" s="5" t="inlineStr"/>
+      <c r="S47" s="8" t="inlineStr">
         <is>
           <t>データ保全：中途半端に残さない</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
+    <row r="48" ht="64" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>取込</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>T-I11</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>CSV位置合わせ設定</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
 【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>11 取込CSV 説明行あり</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>余計な行が無視され、3行が正しく取り込まれる</t>
-        </is>
-      </c>
-      <c r="G48" s="9" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定インポート】
+余計な行が無視され、3行が正しく取り込まれる</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>T-I11.png</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="H48" s="11" t="inlineStr">
         <is>
           <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="11" t="inlineStr">
+      <c r="J48" s="12" t="inlineStr">
         <is>
           <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
         </is>
       </c>
-      <c r="K48" s="7" t="inlineStr">
+      <c r="K48" s="8" t="inlineStr">
         <is>
           <t>説明行を飛ばして取り込めるか</t>
         </is>
       </c>
-      <c r="L48" s="12" t="inlineStr">
+      <c r="L48" s="13" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="M48" s="12" t="inlineStr">
+      <c r="M48" s="13" t="inlineStr">
         <is>
           <t>AC-37</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr"/>
       <c r="O48" s="5" t="inlineStr"/>
-      <c r="P48" s="7" t="inlineStr">
+      <c r="P48" s="6" t="inlineStr"/>
+      <c r="Q48" s="5" t="inlineStr"/>
+      <c r="R48" s="5" t="inlineStr"/>
+      <c r="S48" s="8" t="inlineStr">
         <is>
           <t>入出力：現場のCSVをそのまま使える</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="79" customHeight="1">
-      <c r="A49" s="6" t="inlineStr">
+    <row r="49" ht="94" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>取込</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>T-I09</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>列マッピングテンプレート</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
 【操作】「列マッピングテンプレート管理」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート管理」】
+テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
         <is>
           <t>T-I09.png</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H49" s="11" t="inlineStr">
         <is>
           <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="11" t="inlineStr">
+      <c r="J49" s="12" t="inlineStr">
         <is>
           <t>設定インポート → ツールバー「列マッピングテンプレート管理」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr">
+      <c r="K49" s="8" t="inlineStr">
         <is>
           <t>テンプレの登録・編集・削除と往復</t>
         </is>
       </c>
-      <c r="L49" s="12" t="inlineStr">
+      <c r="L49" s="13" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="M49" s="12" t="inlineStr">
+      <c r="M49" s="13" t="inlineStr">
         <is>
           <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
       <c r="O49" s="5" t="inlineStr"/>
-      <c r="P49" s="7" t="inlineStr">
+      <c r="P49" s="6" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr"/>
+      <c r="R49" s="5" t="inlineStr"/>
+      <c r="S49" s="8" t="inlineStr">
         <is>
           <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="50" ht="79" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>取込</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>T-I19</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>マッピング表の一括登録</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
 【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>18 列マッピング表テンプレ</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：列マッピングテンプレート】
+テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
         <is>
           <t>T-I19.png</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="H50" s="11" t="inlineStr">
         <is>
           <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="11" t="inlineStr">
+      <c r="J50" s="12" t="inlineStr">
         <is>
           <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
         </is>
       </c>
-      <c r="K50" s="7" t="inlineStr">
+      <c r="K50" s="8" t="inlineStr">
         <is>
           <t>一括登録と10MB超の扱い</t>
         </is>
       </c>
-      <c r="L50" s="12" t="inlineStr">
+      <c r="L50" s="13" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="M50" s="12" t="inlineStr">
+      <c r="M50" s="13" t="inlineStr">
         <is>
           <t>AC-51</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr"/>
       <c r="O50" s="5" t="inlineStr"/>
-      <c r="P50" s="7" t="inlineStr">
+      <c r="P50" s="6" t="inlineStr"/>
+      <c r="Q50" s="5" t="inlineStr"/>
+      <c r="R50" s="5" t="inlineStr"/>
+      <c r="S50" s="8" t="inlineStr">
         <is>
           <t>入出力：マッピングの一括運用</t>
         </is>
       </c>
     </row>
     <row r="51" ht="79" customHeight="1">
-      <c r="A51" s="6" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>出力</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>T-E04</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>設定のエクスポート</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
 【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
+専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
         <is>
           <t>T-E04.png</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H51" s="11" t="inlineStr">
         <is>
           <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr"/>
-      <c r="J51" s="11" t="inlineStr">
+      <c r="J51" s="12" t="inlineStr">
         <is>
           <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="K51" s="8" t="inlineStr">
         <is>
           <t>選んだ項目だけ・対象数だけ出るか</t>
         </is>
       </c>
-      <c r="L51" s="12" t="inlineStr">
+      <c r="L51" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="M51" s="12" t="inlineStr">
+      <c r="M51" s="13" t="inlineStr">
         <is>
           <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr"/>
       <c r="O51" s="5" t="inlineStr"/>
-      <c r="P51" s="7" t="inlineStr">
+      <c r="P51" s="6" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr"/>
+      <c r="R51" s="5" t="inlineStr"/>
+      <c r="S51" s="8" t="inlineStr">
         <is>
           <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="52" ht="64" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>出力</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>T-E09</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>実績・同時のエクスポート</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
 【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定・実績エクスポート】
+実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
         <is>
           <t>T-E09.png</t>
         </is>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="H52" s="11" t="inlineStr">
         <is>
           <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr"/>
-      <c r="J52" s="11" t="inlineStr">
+      <c r="J52" s="12" t="inlineStr">
         <is>
           <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
         </is>
       </c>
-      <c r="K52" s="7" t="inlineStr">
+      <c r="K52" s="8" t="inlineStr">
         <is>
           <t>実績と同時選択のファイル数</t>
         </is>
       </c>
-      <c r="L52" s="12" t="inlineStr">
+      <c r="L52" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="M52" s="12" t="inlineStr">
+      <c r="M52" s="13" t="inlineStr">
         <is>
           <t>AC-25</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr"/>
       <c r="O52" s="5" t="inlineStr"/>
-      <c r="P52" s="7" t="inlineStr">
+      <c r="P52" s="6" t="inlineStr"/>
+      <c r="Q52" s="5" t="inlineStr"/>
+      <c r="R52" s="5" t="inlineStr"/>
+      <c r="S52" s="8" t="inlineStr">
         <is>
           <t>入出力：渡し先に合わせて出せる</t>
         </is>
       </c>
     </row>
     <row r="53" ht="60" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>出力</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>T-E07</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>未選択でのエクスポート防止</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
 【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定・実績エクスポート】
+警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
         <is>
           <t>T-E07.png</t>
         </is>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="H53" s="11" t="inlineStr">
         <is>
           <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
-      <c r="J53" s="11" t="inlineStr">
+      <c r="J53" s="12" t="inlineStr">
         <is>
           <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr">
+      <c r="K53" s="8" t="inlineStr">
         <is>
           <t>未選択で出力されないか</t>
         </is>
       </c>
-      <c r="L53" s="12" t="inlineStr">
+      <c r="L53" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="M53" s="12" t="inlineStr">
+      <c r="M53" s="13" t="inlineStr">
         <is>
           <t>AC-27</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr"/>
       <c r="O53" s="5" t="inlineStr"/>
-      <c r="P53" s="7" t="inlineStr">
+      <c r="P53" s="6" t="inlineStr"/>
+      <c r="Q53" s="5" t="inlineStr"/>
+      <c r="R53" s="5" t="inlineStr"/>
+      <c r="S53" s="8" t="inlineStr">
         <is>
           <t>入出力：空振りを防ぐ</t>
         </is>
       </c>
     </row>
     <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>出力</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>T-E08</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>出力CSVの文字化け</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 ／ T-E04で出力済み
 【操作】T-E04で出力したCSVをExcelで開く</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
-        </is>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定・実績エクスポート】
+日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
         <is>
           <t>T-E08.png</t>
         </is>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="H54" s="11" t="inlineStr">
         <is>
           <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="11" t="inlineStr">
+      <c r="J54" s="12" t="inlineStr">
         <is>
           <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
         </is>
       </c>
-      <c r="K54" s="7" t="inlineStr">
+      <c r="K54" s="8" t="inlineStr">
         <is>
           <t>Excelで文字化けしないか</t>
         </is>
       </c>
-      <c r="L54" s="12" t="inlineStr">
+      <c r="L54" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
-      <c r="M54" s="12" t="inlineStr">
+      <c r="M54" s="13" t="inlineStr">
         <is>
           <t>AC-28</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr"/>
       <c r="O54" s="5" t="inlineStr"/>
-      <c r="P54" s="7" t="inlineStr">
+      <c r="P54" s="6" t="inlineStr"/>
+      <c r="Q54" s="5" t="inlineStr"/>
+      <c r="R54" s="5" t="inlineStr"/>
+      <c r="S54" s="8" t="inlineStr">
         <is>
           <t>入出力：そのまま提出できる</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
+    <row r="55" ht="64" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>T-N01</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>取込元データの確認</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>【前提】T-I03実施済み
 【操作】サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定取込データ（サイドバー）】
+設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
         <is>
           <t>T-N01.png</t>
         </is>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="H55" s="11" t="inlineStr">
         <is>
           <t>設定取込データと実績取込データの一覧＋各タブ（計4枚）</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="11" t="inlineStr">
+      <c r="J55" s="12" t="inlineStr">
         <is>
           <t>設定取込データ（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績取込データ … 月別データ／日別データタブ</t>
         </is>
       </c>
-      <c r="K55" s="7" t="inlineStr">
+      <c r="K55" s="8" t="inlineStr">
         <is>
           <t>元データとタブの構成</t>
         </is>
       </c>
-      <c r="L55" s="12" t="inlineStr">
+      <c r="L55" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
-      <c r="M55" s="12" t="inlineStr">
+      <c r="M55" s="13" t="inlineStr">
         <is>
           <t>AC-39</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
       <c r="O55" s="5" t="inlineStr"/>
-      <c r="P55" s="7" t="inlineStr">
+      <c r="P55" s="6" t="inlineStr"/>
+      <c r="Q55" s="5" t="inlineStr"/>
+      <c r="R55" s="5" t="inlineStr"/>
+      <c r="S55" s="8" t="inlineStr">
         <is>
           <t>入出力：原因を追える</t>
         </is>
       </c>
     </row>
     <row r="56" ht="94" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>T-N02</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>取込前のプレビューと前回差分</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05 S-06
 【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：設定取込データ／実績取込データ】
+プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>T-N02.png</t>
         </is>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="H56" s="11" t="inlineStr">
         <is>
           <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="11" t="inlineStr">
+      <c r="J56" s="12" t="inlineStr">
         <is>
           <t>設定取込データ／実績取込データ … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
         </is>
       </c>
-      <c r="K56" s="7" t="inlineStr">
+      <c r="K56" s="8" t="inlineStr">
         <is>
           <t>差分がdata/16・17と一致するか</t>
         </is>
       </c>
-      <c r="L56" s="12" t="inlineStr">
+      <c r="L56" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
-      <c r="M56" s="12" t="inlineStr">
+      <c r="M56" s="13" t="inlineStr">
         <is>
           <t>AC-50</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr"/>
       <c r="O56" s="5" t="inlineStr"/>
-      <c r="P56" s="7" t="inlineStr">
+      <c r="P56" s="6" t="inlineStr"/>
+      <c r="Q56" s="5" t="inlineStr"/>
+      <c r="R56" s="5" t="inlineStr"/>
+      <c r="S56" s="8" t="inlineStr">
         <is>
           <t>データ保全：取り込む前に気づける</t>
         </is>
       </c>
     </row>
     <row r="57" ht="60" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>T-N03</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>取込データと人件費実績の相互導線</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
 【操作】人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>2経路とも到達する（不通=0）</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績　→　「実績取込データへ」／実績取込データ】
+2経路とも到達する（不通=0）</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
         <is>
           <t>T-N03.png</t>
         </is>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="H57" s="11" t="inlineStr">
         <is>
           <t>人件費実績→実績取込データ／実績取込データ→人件費実績 の到達直後（2枚）</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="11" t="inlineStr">
+      <c r="J57" s="12" t="inlineStr">
         <is>
           <t>人件費実績 → 「実績取込データへ」／実績取込データ → 「人件費実績へ」（相互導線）</t>
         </is>
       </c>
-      <c r="K57" s="7" t="inlineStr">
+      <c r="K57" s="8" t="inlineStr">
         <is>
           <t>2経路とも到達するか</t>
         </is>
       </c>
-      <c r="L57" s="12" t="inlineStr">
+      <c r="L57" s="13" t="inlineStr">
         <is>
           <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
-      <c r="M57" s="12" t="inlineStr">
+      <c r="M57" s="13" t="inlineStr">
         <is>
           <t>AC-30</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr"/>
       <c r="O57" s="5" t="inlineStr"/>
-      <c r="P57" s="7" t="inlineStr">
+      <c r="P57" s="6" t="inlineStr"/>
+      <c r="Q57" s="5" t="inlineStr"/>
+      <c r="R57" s="5" t="inlineStr"/>
+      <c r="S57" s="8" t="inlineStr">
         <is>
           <t>画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="58" ht="60" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>横断</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>T-Z01</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>移行前後の突合（既存データ）</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>【前提】S-09 S-11
 【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
-        </is>
-      </c>
-      <c r="G58" s="9" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員一覧】
+件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
         <is>
           <t>T-Z01.png</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="H58" s="11" t="inlineStr">
         <is>
           <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="11" t="inlineStr">
+      <c r="J58" s="12" t="inlineStr">
         <is>
           <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
         </is>
       </c>
-      <c r="K58" s="7" t="inlineStr">
+      <c r="K58" s="8" t="inlineStr">
         <is>
           <t>移行前後で差分0件か</t>
         </is>
       </c>
-      <c r="L58" s="12" t="inlineStr">
+      <c r="L58" s="13" t="inlineStr">
         <is>
           <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
-      <c r="M58" s="12" t="inlineStr">
+      <c r="M58" s="13" t="inlineStr">
         <is>
           <t>AC-01</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr"/>
       <c r="O58" s="5" t="inlineStr"/>
-      <c r="P58" s="7" t="inlineStr">
+      <c r="P58" s="6" t="inlineStr"/>
+      <c r="Q58" s="5" t="inlineStr"/>
+      <c r="R58" s="5" t="inlineStr"/>
+      <c r="S58" s="8" t="inlineStr">
         <is>
           <t>移行：既存顧客が壊れない</t>
         </is>
       </c>
     </row>
     <row r="59" ht="60" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>横断</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>T-Z02</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>移行後の適用日付の付与</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>【前提】S-09 ／ T-Z01実施済み
 【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員詳細 → 設定変更履歴／従業員設定履歴】
+適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
         <is>
           <t>T-Z02.png</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="H59" s="11" t="inlineStr">
         <is>
           <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="11" t="inlineStr">
+      <c r="J59" s="12" t="inlineStr">
         <is>
           <t>従業員詳細 → 設定変更履歴／従業員設定履歴 … 適用日付の空欄</t>
         </is>
       </c>
-      <c r="K59" s="7" t="inlineStr">
+      <c r="K59" s="8" t="inlineStr">
         <is>
           <t>適用日付の空欄が0件か</t>
         </is>
       </c>
-      <c r="L59" s="12" t="inlineStr">
+      <c r="L59" s="13" t="inlineStr">
         <is>
           <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
-      <c r="M59" s="12" t="inlineStr">
+      <c r="M59" s="13" t="inlineStr">
         <is>
           <t>AC-02</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr"/>
       <c r="O59" s="5" t="inlineStr"/>
-      <c r="P59" s="7" t="inlineStr">
+      <c r="P59" s="6" t="inlineStr"/>
+      <c r="Q59" s="5" t="inlineStr"/>
+      <c r="R59" s="5" t="inlineStr"/>
+      <c r="S59" s="8" t="inlineStr">
         <is>
           <t>移行：履歴の起点を作る</t>
         </is>
       </c>
     </row>
     <row r="60" ht="60" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>横断</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>T-Z03</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>移行前後の過去月の人件費</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>【前提】S-09 ／ T-Z01実施済み
 【操作】移行前に出力しておいた直近3か月の人件費実績と、移行後の同3か月を突合する</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
         <is>
           <t>T-Z03.png</t>
         </is>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="H60" s="11" t="inlineStr">
         <is>
           <t>移行前後の人件費実績 月別実績（直近3か月・金額が同じであること）</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="11" t="inlineStr">
+      <c r="J60" s="12" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ … 移行前後の直近3か月</t>
         </is>
       </c>
-      <c r="K60" s="7" t="inlineStr">
+      <c r="K60" s="8" t="inlineStr">
         <is>
           <t>過去3か月の金額が変わらないか</t>
         </is>
       </c>
-      <c r="L60" s="12" t="inlineStr">
+      <c r="L60" s="13" t="inlineStr">
         <is>
           <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
-      <c r="M60" s="12" t="inlineStr">
+      <c r="M60" s="13" t="inlineStr">
         <is>
           <t>AC-03</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr"/>
       <c r="O60" s="5" t="inlineStr"/>
-      <c r="P60" s="7" t="inlineStr">
+      <c r="P60" s="6" t="inlineStr"/>
+      <c r="Q60" s="5" t="inlineStr"/>
+      <c r="R60" s="5" t="inlineStr"/>
+      <c r="S60" s="8" t="inlineStr">
         <is>
           <t>移行：過去が動かない</t>
         </is>
       </c>
     </row>
     <row r="61" ht="60" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>横断</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>T-Z04</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>サイドバーの構成</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：サイドバー「従業員管理」】
+閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
         <is>
           <t>T-Z04.png</t>
         </is>
       </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="H61" s="11" t="inlineStr">
         <is>
           <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="11" t="inlineStr">
+      <c r="J61" s="12" t="inlineStr">
         <is>
           <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
         </is>
       </c>
-      <c r="K61" s="7" t="inlineStr">
+      <c r="K61" s="8" t="inlineStr">
         <is>
           <t>PC・モバイルとも開くか</t>
         </is>
       </c>
-      <c r="L61" s="12" t="inlineStr">
+      <c r="L61" s="13" t="inlineStr">
         <is>
           <t>（ヘルプ記載なし・画面構成）</t>
         </is>
       </c>
-      <c r="M61" s="12" t="inlineStr">
+      <c r="M61" s="13" t="inlineStr">
         <is>
           <t>AC-29</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr"/>
       <c r="O61" s="5" t="inlineStr"/>
-      <c r="P61" s="7" t="inlineStr">
+      <c r="P61" s="6" t="inlineStr"/>
+      <c r="Q61" s="5" t="inlineStr"/>
+      <c r="R61" s="5" t="inlineStr"/>
+      <c r="S61" s="8" t="inlineStr">
         <is>
           <t>画面：たどり着ける</t>
         </is>
       </c>
     </row>
     <row r="62" ht="60" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>横断</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>T-Z05</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>遷移と表示規則の網羅</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-05
 【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
-        </is>
-      </c>
-      <c r="G62" s="9" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
+すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
         <is>
           <t>T-Z05.png</t>
         </is>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="H62" s="11" t="inlineStr">
         <is>
           <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="11" t="inlineStr">
+      <c r="J62" s="12" t="inlineStr">
         <is>
           <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
         </is>
       </c>
-      <c r="K62" s="7" t="inlineStr">
+      <c r="K62" s="8" t="inlineStr">
         <is>
           <t>75本の遷移と表示規則</t>
         </is>
       </c>
-      <c r="L62" s="12" t="inlineStr">
+      <c r="L62" s="13" t="inlineStr">
         <is>
           <t>（ヘルプ記載なし・遷移網羅）</t>
         </is>
       </c>
-      <c r="M62" s="12" t="inlineStr">
+      <c r="M62" s="13" t="inlineStr">
         <is>
           <t>AC-30 AC-01</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr"/>
       <c r="O62" s="5" t="inlineStr"/>
-      <c r="P62" s="7" t="inlineStr">
+      <c r="P62" s="6" t="inlineStr"/>
+      <c r="Q62" s="5" t="inlineStr"/>
+      <c r="R62" s="5" t="inlineStr"/>
+      <c r="S62" s="8" t="inlineStr">
         <is>
           <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="64" customHeight="1">
-      <c r="A63" s="13" t="inlineStr">
+    <row r="63" ht="79" customHeight="1">
+      <c r="A63" s="14" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>C-000</t>
         </is>
       </c>
-      <c r="C63" s="14" t="inlineStr">
+      <c r="C63" s="15" t="inlineStr">
         <is>
           <t>データの初期化（計算の検証に入る前に必ず実施）</t>
         </is>
       </c>
-      <c r="D63" s="14" t="inlineStr">
+      <c r="D63" s="15" t="inlineStr">
         <is>
           <t>【前提】S-03 S-05
 【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
         </is>
       </c>
-      <c r="E63" s="14" t="inlineStr">
+      <c r="E63" s="15" t="inlineStr">
         <is>
           <t>02〜06・13を再投入（初期化）</t>
         </is>
       </c>
-      <c r="F63" s="14" t="inlineStr">
-        <is>
-          <t>従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
-        </is>
-      </c>
-      <c r="G63" s="13" t="inlineStr">
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未】
+従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
         <is>
           <t>C-000.png</t>
         </is>
       </c>
-      <c r="H63" s="14" t="inlineStr">
+      <c r="H63" s="15" t="inlineStr">
         <is>
           <t>初期化後の従業員一覧（12名）と人件費実績（未締め・S-05時点の金額）</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="14" t="inlineStr">
+      <c r="J63" s="15" t="inlineStr">
         <is>
           <t>従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未締めに戻す）</t>
         </is>
       </c>
-      <c r="K63" s="14" t="inlineStr">
+      <c r="K63" s="15" t="inlineStr">
         <is>
           <t>S-05時点の値に戻ったか</t>
         </is>
       </c>
-      <c r="L63" s="14" t="inlineStr">
+      <c r="L63" s="15" t="inlineStr">
         <is>
           <t>（初期化のため対応なし）</t>
         </is>
       </c>
-      <c r="M63" s="14" t="inlineStr">
+      <c r="M63" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr"/>
       <c r="O63" s="5" t="inlineStr"/>
-      <c r="P63" s="14" t="inlineStr">
+      <c r="P63" s="6" t="inlineStr"/>
+      <c r="Q63" s="5" t="inlineStr"/>
+      <c r="R63" s="5" t="inlineStr"/>
+      <c r="S63" s="15" t="inlineStr">
         <is>
           <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
         </is>
       </c>
     </row>
     <row r="64" ht="64" customHeight="1">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A64" s="14" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
+      <c r="B64" s="14" t="inlineStr">
         <is>
           <t>C-001</t>
         </is>
       </c>
-      <c r="C64" s="14" t="inlineStr">
+      <c r="C64" s="15" t="inlineStr">
         <is>
           <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
-      <c r="D64" s="14" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
 【操作】2026-05の EMP-002（概算280,000・基礎時給1,750＝280,000÷160・深夜2h）と EMP-007（概算300,000・基礎時給1,875＝300,000÷160・深夜4h）を検算</t>
         </is>
       </c>
-      <c r="E64" s="14" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr">
         <is>
           <t>05 月次給与実績</t>
         </is>
       </c>
-      <c r="F64" s="14" t="inlineStr">
-        <is>
-          <t>EMP-002＝285,250（概算280,000＋深夜残業代5,250＝1,750×1.5×2h）／EMP-007＝311,250（概算300,000＋深夜残業代11,250＝1,875×1.5×4h）。いずれも差分0円</t>
-        </is>
-      </c>
-      <c r="G64" s="13" t="inlineStr">
+      <c r="F64" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
+EMP-002＝285,250（概算280,000＋深夜残業代5,250＝1,750×1.5×2h）／EMP-007＝311,250（概算300,000＋深夜残業代11,250＝1,875×1.5×4h）。いずれも差分0円</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
         <is>
           <t>C-001.png</t>
         </is>
       </c>
-      <c r="H64" s="14" t="inlineStr">
+      <c r="H64" s="15" t="inlineStr">
         <is>
           <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="14" t="inlineStr">
+      <c r="J64" s="15" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
         </is>
       </c>
-      <c r="K64" s="14" t="inlineStr">
+      <c r="K64" s="15" t="inlineStr">
         <is>
           <t>概算＋深夜＝実績給与か</t>
         </is>
       </c>
-      <c r="L64" s="14" t="inlineStr">
+      <c r="L64" s="15" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="M64" s="14" t="inlineStr">
+      <c r="M64" s="15" t="inlineStr">
         <is>
           <t>AC-10</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr"/>
       <c r="O64" s="5" t="inlineStr"/>
-      <c r="P64" s="14" t="inlineStr">
+      <c r="P64" s="6" t="inlineStr"/>
+      <c r="Q64" s="5" t="inlineStr"/>
+      <c r="R64" s="5" t="inlineStr"/>
+      <c r="S64" s="15" t="inlineStr">
         <is>
           <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・暫定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="79" customHeight="1">
-      <c r="A65" s="13" t="inlineStr">
+    <row r="65" ht="94" customHeight="1">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>C-003</t>
         </is>
       </c>
-      <c r="C65" s="14" t="inlineStr">
+      <c r="C65" s="15" t="inlineStr">
         <is>
           <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
-      <c r="D65" s="14" t="inlineStr">
+      <c r="D65" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
 【操作】2026-05の EMP-001（概算320,000・基礎時給2,000・深夜6h・ヘルプ22h／総労働172h）／EMP-005（概算350,000・基礎時給2,187・深夜10h・ヘルプ35h／総労働185h）／EMP-003（概算144,000・時給1,200・深夜0h・ヘルプ20h／総労働120h）を検算</t>
         </is>
       </c>
-      <c r="E65" s="14" t="inlineStr">
+      <c r="E65" s="15" t="inlineStr">
         <is>
           <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F65" s="14" t="inlineStr">
-        <is>
-          <t>EMP-001＝338,000（概算320,000＋深夜18,000＝2,000×1.5×6h）／EMP-005＝382,812（概算350,000＋深夜32,812＝2,187×1.5×10h）／EMP-003＝144,000（深夜なし）。ヘルプ人件費は実績給与×ヘルプ時間÷総労働時間で按分し応援先へ振替（EMP-001＝43,232／EMP-003＝24,000／EMP-005＝72,424）</t>
-        </is>
-      </c>
-      <c r="G65" s="13" t="inlineStr">
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
+EMP-001＝338,000（概算320,000＋深夜18,000＝2,000×1.5×6h）／EMP-005＝382,812（概算350,000＋深夜32,812＝2,187×1.5×10h）／EMP-003＝144,000（深夜なし）。ヘルプ人件費は実績給与×ヘルプ時間÷総労働時間で按分し応援先へ振替（EMP-001＝43,232／EMP-003＝24,000／EMP-005＝72,424）</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
         <is>
           <t>C-003.png</t>
         </is>
       </c>
-      <c r="H65" s="14" t="inlineStr">
+      <c r="H65" s="15" t="inlineStr">
         <is>
           <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="14" t="inlineStr">
+      <c r="J65" s="15" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
         </is>
       </c>
-      <c r="K65" s="14" t="inlineStr">
+      <c r="K65" s="15" t="inlineStr">
         <is>
           <t>ヘルプ人件費が按分で振替されるか</t>
         </is>
       </c>
-      <c r="L65" s="14" t="inlineStr">
+      <c r="L65" s="15" t="inlineStr">
         <is>
           <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
-      <c r="M65" s="14" t="inlineStr">
+      <c r="M65" s="15" t="inlineStr">
         <is>
           <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr"/>
       <c r="O65" s="5" t="inlineStr"/>
-      <c r="P65" s="14" t="inlineStr">
+      <c r="P65" s="6" t="inlineStr"/>
+      <c r="Q65" s="5" t="inlineStr"/>
+      <c r="R65" s="5" t="inlineStr"/>
+      <c r="S65" s="15" t="inlineStr">
         <is>
           <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
         </is>
       </c>
     </row>
     <row r="66" ht="60" customHeight="1">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="A66" s="14" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>C-005</t>
         </is>
       </c>
-      <c r="C66" s="14" t="inlineStr">
+      <c r="C66" s="15" t="inlineStr">
         <is>
           <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
-      <c r="D66" s="14" t="inlineStr">
+      <c r="D66" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-04
 【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
-      <c r="E66" s="14" t="inlineStr">
+      <c r="E66" s="15" t="inlineStr">
         <is>
           <t>05 月次給与実績</t>
         </is>
       </c>
-      <c r="F66" s="14" t="inlineStr">
-        <is>
-          <t>店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
-        </is>
-      </c>
-      <c r="G66" s="13" t="inlineStr">
+      <c r="F66" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
+店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
         <is>
           <t>C-005.png</t>
         </is>
       </c>
-      <c r="H66" s="14" t="inlineStr">
+      <c r="H66" s="15" t="inlineStr">
         <is>
           <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="14" t="inlineStr">
+      <c r="J66" s="15" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
         </is>
       </c>
-      <c r="K66" s="14" t="inlineStr">
+      <c r="K66" s="15" t="inlineStr">
         <is>
           <t>店舗別合計＝全社（差0円）か</t>
         </is>
       </c>
-      <c r="L66" s="14" t="inlineStr">
+      <c r="L66" s="15" t="inlineStr">
         <is>
           <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
-      <c r="M66" s="14" t="inlineStr">
+      <c r="M66" s="15" t="inlineStr">
         <is>
           <t>AC-11</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr"/>
       <c r="O66" s="5" t="inlineStr"/>
-      <c r="P66" s="14" t="inlineStr">
+      <c r="P66" s="6" t="inlineStr"/>
+      <c r="Q66" s="5" t="inlineStr"/>
+      <c r="R66" s="5" t="inlineStr"/>
+      <c r="S66" s="15" t="inlineStr">
         <is>
           <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="64" customHeight="1">
-      <c r="A67" s="13" t="inlineStr">
+    <row r="67" ht="79" customHeight="1">
+      <c r="A67" s="14" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B67" s="14" t="inlineStr">
         <is>
           <t>C-006</t>
         </is>
       </c>
-      <c r="C67" s="14" t="inlineStr">
+      <c r="C67" s="15" t="inlineStr">
         <is>
           <t>月中改定と予約の日割り</t>
         </is>
       </c>
-      <c r="D67" s="14" t="inlineStr">
+      <c r="D67" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-07 ／ data/14を投入
 【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
-      <c r="E67" s="14" t="inlineStr">
+      <c r="E67" s="15" t="inlineStr">
         <is>
           <t>14 勤務データ 2026-06</t>
         </is>
       </c>
-      <c r="F67" s="14" t="inlineStr">
-        <is>
-          <t>6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
-        </is>
-      </c>
-      <c r="G67" s="13" t="inlineStr">
+      <c r="F67" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従】
+6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
         <is>
           <t>C-006.png</t>
         </is>
       </c>
-      <c r="H67" s="14" t="inlineStr">
+      <c r="H67" s="15" t="inlineStr">
         <is>
           <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="14" t="inlineStr">
+      <c r="J67" s="15" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
         </is>
       </c>
-      <c r="K67" s="14" t="inlineStr">
+      <c r="K67" s="15" t="inlineStr">
         <is>
           <t>所定労働日割になっているか</t>
         </is>
       </c>
-      <c r="L67" s="14" t="inlineStr">
+      <c r="L67" s="15" t="inlineStr">
         <is>
           <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
-      <c r="M67" s="14" t="inlineStr">
+      <c r="M67" s="15" t="inlineStr">
         <is>
           <t>AC-12 AC-04</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr"/>
       <c r="O67" s="5" t="inlineStr"/>
-      <c r="P67" s="14" t="inlineStr">
+      <c r="P67" s="6" t="inlineStr"/>
+      <c r="Q67" s="5" t="inlineStr"/>
+      <c r="R67" s="5" t="inlineStr"/>
+      <c r="S67" s="15" t="inlineStr">
         <is>
           <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" s="13" t="inlineStr">
+    <row r="68" ht="64" customHeight="1">
+      <c r="A68" s="14" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B68" s="14" t="inlineStr">
         <is>
           <t>C-011</t>
         </is>
       </c>
-      <c r="C68" s="14" t="inlineStr">
+      <c r="C68" s="15" t="inlineStr">
         <is>
           <t>時給者の概算と月中改定</t>
         </is>
       </c>
-      <c r="D68" s="14" t="inlineStr">
+      <c r="D68" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-07 ／ data/14を投入
 【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
         </is>
       </c>
-      <c r="E68" s="14" t="inlineStr">
+      <c r="E68" s="15" t="inlineStr">
         <is>
           <t>05 月次給与実績・14 勤務データ 2026-06</t>
         </is>
       </c>
-      <c r="F68" s="14" t="inlineStr">
-        <is>
-          <t>5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
-        </is>
-      </c>
-      <c r="G68" s="13" t="inlineStr">
+      <c r="F68" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
         <is>
           <t>C-011.png</t>
         </is>
       </c>
-      <c r="H68" s="14" t="inlineStr">
+      <c r="H68" s="15" t="inlineStr">
         <is>
           <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
-      <c r="J68" s="14" t="inlineStr">
+      <c r="J68" s="15" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
         </is>
       </c>
-      <c r="K68" s="14" t="inlineStr">
+      <c r="K68" s="15" t="inlineStr">
         <is>
           <t>時給者の概算と月中改定</t>
         </is>
       </c>
-      <c r="L68" s="14" t="inlineStr">
+      <c r="L68" s="15" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="M68" s="14" t="inlineStr">
+      <c r="M68" s="15" t="inlineStr">
         <is>
           <t>AC-13</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr"/>
       <c r="O68" s="5" t="inlineStr"/>
-      <c r="P68" s="14" t="inlineStr">
+      <c r="P68" s="6" t="inlineStr"/>
+      <c r="Q68" s="5" t="inlineStr"/>
+      <c r="R68" s="5" t="inlineStr"/>
+      <c r="S68" s="15" t="inlineStr">
         <is>
           <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="79" customHeight="1">
-      <c r="A69" s="13" t="inlineStr">
+    <row r="69" ht="94" customHeight="1">
+      <c r="A69" s="14" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr">
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>C-013</t>
         </is>
       </c>
-      <c r="C69" s="14" t="inlineStr">
+      <c r="C69" s="15" t="inlineStr">
         <is>
           <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
         </is>
       </c>
-      <c r="D69" s="14" t="inlineStr">
+      <c r="D69" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
 【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
-      <c r="E69" s="14" t="inlineStr">
+      <c r="E69" s="15" t="inlineStr">
         <is>
           <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
-      <c r="F69" s="14" t="inlineStr">
-        <is>
-          <t>判断7（暫定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。5/8のヘルプ人件費＝実績給与338,000×11h÷総労働172h＝21,616円で、計上先はS02。みなし労働時間差分＝172−(160＋20)＝−8h（未達はマイナス表示・減額なし＝判断8）</t>
-        </is>
-      </c>
-      <c r="G69" s="13" t="inlineStr">
+      <c r="F69" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績】
+判断7（暫定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。5/8のヘルプ人件費＝実績給与338,000×11h÷総労働172h＝21,616円で、計上先はS02。みなし労働時間差分＝172−(160＋20)＝−8h（未達はマイナス表示・減額なし＝判断8）</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
         <is>
           <t>C-013.png</t>
         </is>
       </c>
-      <c r="H69" s="14" t="inlineStr">
+      <c r="H69" s="15" t="inlineStr">
         <is>
           <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="14" t="inlineStr">
+      <c r="J69" s="15" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
         </is>
       </c>
-      <c r="K69" s="14" t="inlineStr">
+      <c r="K69" s="15" t="inlineStr">
         <is>
           <t>深夜1.5倍とヘルプの按分単価</t>
         </is>
       </c>
-      <c r="L69" s="14" t="inlineStr">
+      <c r="L69" s="15" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="M69" s="14" t="inlineStr">
+      <c r="M69" s="15" t="inlineStr">
         <is>
           <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr"/>
       <c r="O69" s="5" t="inlineStr"/>
-      <c r="P69" s="14" t="inlineStr">
+      <c r="P69" s="6" t="inlineStr"/>
+      <c r="Q69" s="5" t="inlineStr"/>
+      <c r="R69" s="5" t="inlineStr"/>
+      <c r="S69" s="15" t="inlineStr">
         <is>
           <t>深夜残業代＝基礎時給×1.5（判断7・暫定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・暫定）</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="64" customHeight="1">
-      <c r="A70" s="13" t="inlineStr">
+    <row r="70" ht="79" customHeight="1">
+      <c r="A70" s="14" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="B70" s="14" t="inlineStr">
         <is>
           <t>C-017</t>
         </is>
       </c>
-      <c r="C70" s="14" t="inlineStr">
+      <c r="C70" s="15" t="inlineStr">
         <is>
           <t>交通費の計上先</t>
         </is>
       </c>
-      <c r="D70" s="14" t="inlineStr">
+      <c r="D70" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-04
 【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
         </is>
       </c>
-      <c r="E70" s="14" t="inlineStr">
+      <c r="E70" s="15" t="inlineStr">
         <is>
           <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
         </is>
       </c>
-      <c r="F70" s="14" t="inlineStr">
-        <is>
-          <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
-        </is>
-      </c>
-      <c r="G70" s="13" t="inlineStr">
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8の】
+交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
         <is>
           <t>C-017.png</t>
         </is>
       </c>
-      <c r="H70" s="14" t="inlineStr">
+      <c r="H70" s="15" t="inlineStr">
         <is>
           <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
-      <c r="J70" s="14" t="inlineStr">
+      <c r="J70" s="15" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
         </is>
       </c>
-      <c r="K70" s="14" t="inlineStr">
+      <c r="K70" s="15" t="inlineStr">
         <is>
           <t>交通費が給与と別費目か</t>
         </is>
       </c>
-      <c r="L70" s="14" t="inlineStr">
+      <c r="L70" s="15" t="inlineStr">
         <is>
           <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
-      <c r="M70" s="14" t="inlineStr">
+      <c r="M70" s="15" t="inlineStr">
         <is>
           <t>AC-15</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr"/>
       <c r="O70" s="5" t="inlineStr"/>
-      <c r="P70" s="14" t="inlineStr">
+      <c r="P70" s="6" t="inlineStr"/>
+      <c r="Q70" s="5" t="inlineStr"/>
+      <c r="R70" s="5" t="inlineStr"/>
+      <c r="S70" s="15" t="inlineStr">
         <is>
           <t>交通費は給与と別の独立費目（判断6・確定）。通勤交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="64" customHeight="1">
-      <c r="A71" s="13" t="inlineStr">
+    <row r="71" ht="94" customHeight="1">
+      <c r="A71" s="14" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>C-008</t>
         </is>
       </c>
-      <c r="C71" s="14" t="inlineStr">
+      <c r="C71" s="15" t="inlineStr">
         <is>
           <t>締めの前後で数字が動かないこと</t>
         </is>
       </c>
-      <c r="D71" s="14" t="inlineStr">
+      <c r="D71" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-07
 【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
         </is>
       </c>
-      <c r="E71" s="14" t="inlineStr">
+      <c r="E71" s="15" t="inlineStr">
         <is>
           <t>05 月次給与実績・13 勤務データ 2026-05</t>
         </is>
       </c>
-      <c r="F71" s="14" t="inlineStr">
-        <is>
-          <t>（a）5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
-        </is>
-      </c>
-      <c r="G71" s="13" t="inlineStr">
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解】
+（a）5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
         <is>
           <t>C-008.png</t>
         </is>
       </c>
-      <c r="H71" s="14" t="inlineStr">
+      <c r="H71" s="15" t="inlineStr">
         <is>
           <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="14" t="inlineStr">
+      <c r="J71" s="15" t="inlineStr">
         <is>
           <t>人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
         </is>
       </c>
-      <c r="K71" s="14" t="inlineStr">
+      <c r="K71" s="15" t="inlineStr">
         <is>
           <t>締め前後で差0円・解除後に再計算</t>
         </is>
       </c>
-      <c r="L71" s="14" t="inlineStr">
+      <c r="L71" s="15" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
-      <c r="M71" s="14" t="inlineStr">
+      <c r="M71" s="15" t="inlineStr">
         <is>
           <t>AC-16 AC-17</t>
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr"/>
       <c r="O71" s="5" t="inlineStr"/>
-      <c r="P71" s="14" t="inlineStr">
+      <c r="P71" s="6" t="inlineStr"/>
+      <c r="Q71" s="5" t="inlineStr"/>
+      <c r="R71" s="5" t="inlineStr"/>
+      <c r="S71" s="15" t="inlineStr">
         <is>
           <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="64" customHeight="1">
-      <c r="A72" s="15" t="inlineStr">
+    <row r="72" ht="94" customHeight="1">
+      <c r="A72" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
         </is>
       </c>
-      <c r="B72" s="15" t="inlineStr">
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>R-01</t>
         </is>
       </c>
-      <c r="C72" s="16" t="inlineStr">
+      <c r="C72" s="17" t="inlineStr">
         <is>
           <t>データ構造のレビュー</t>
         </is>
       </c>
-      <c r="D72" s="16" t="inlineStr">
+      <c r="D72" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
         </is>
       </c>
-      <c r="E72" s="16" t="inlineStr">
+      <c r="E72" s="17" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F72" s="16" t="inlineStr">
-        <is>
-          <t>①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
-        </is>
-      </c>
-      <c r="G72" s="15" t="inlineStr">
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
+①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
+        </is>
+      </c>
+      <c r="G72" s="16" t="inlineStr">
         <is>
           <t>R-01.png</t>
         </is>
       </c>
-      <c r="H72" s="16" t="inlineStr">
+      <c r="H72" s="17" t="inlineStr">
         <is>
           <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="16" t="inlineStr">
+      <c r="J72" s="17" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
       </c>
-      <c r="K72" s="16" t="inlineStr">
+      <c r="K72" s="17" t="inlineStr">
         <is>
           <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
-      <c r="L72" s="16" t="inlineStr">
+      <c r="L72" s="17" t="inlineStr">
         <is>
           <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
-      <c r="M72" s="16" t="inlineStr">
+      <c r="M72" s="17" t="inlineStr">
         <is>
           <t>AC-07 AC-40 AC-47</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr"/>
       <c r="O72" s="5" t="inlineStr"/>
-      <c r="P72" s="16" t="inlineStr">
+      <c r="P72" s="6" t="inlineStr"/>
+      <c r="Q72" s="5" t="inlineStr"/>
+      <c r="R72" s="5" t="inlineStr"/>
+      <c r="S72" s="17" t="inlineStr">
         <is>
           <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" s="15" t="inlineStr">
+    <row r="73" ht="79" customHeight="1">
+      <c r="A73" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
         </is>
       </c>
-      <c r="B73" s="15" t="inlineStr">
+      <c r="B73" s="16" t="inlineStr">
         <is>
           <t>R-02</t>
         </is>
       </c>
-      <c r="C73" s="16" t="inlineStr">
+      <c r="C73" s="17" t="inlineStr">
         <is>
           <t>締めの実装レビュー</t>
         </is>
       </c>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="D73" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
-      <c r="E73" s="16" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F73" s="16" t="inlineStr">
-        <is>
-          <t>①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
-        </is>
-      </c>
-      <c r="G73" s="15" t="inlineStr">
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
+①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
+        </is>
+      </c>
+      <c r="G73" s="16" t="inlineStr">
         <is>
           <t>R-02.png</t>
         </is>
       </c>
-      <c r="H73" s="16" t="inlineStr">
+      <c r="H73" s="17" t="inlineStr">
         <is>
           <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
-      <c r="J73" s="16" t="inlineStr">
+      <c r="J73" s="17" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
       </c>
-      <c r="K73" s="16" t="inlineStr">
+      <c r="K73" s="17" t="inlineStr">
         <is>
           <t>APIでも店長が締められないか</t>
         </is>
       </c>
-      <c r="L73" s="16" t="inlineStr">
+      <c r="L73" s="17" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
-      <c r="M73" s="16" t="inlineStr">
+      <c r="M73" s="17" t="inlineStr">
         <is>
           <t>AC-16 AC-41</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr"/>
       <c r="O73" s="5" t="inlineStr"/>
-      <c r="P73" s="16" t="inlineStr">
+      <c r="P73" s="6" t="inlineStr"/>
+      <c r="Q73" s="5" t="inlineStr"/>
+      <c r="R73" s="5" t="inlineStr"/>
+      <c r="S73" s="17" t="inlineStr">
         <is>
           <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="79" customHeight="1">
-      <c r="A74" s="15" t="inlineStr">
+    <row r="74" ht="109" customHeight="1">
+      <c r="A74" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
         </is>
       </c>
-      <c r="B74" s="15" t="inlineStr">
+      <c r="B74" s="16" t="inlineStr">
         <is>
           <t>R-03</t>
         </is>
       </c>
-      <c r="C74" s="16" t="inlineStr">
+      <c r="C74" s="17" t="inlineStr">
         <is>
           <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="D74" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="E74" s="17" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F74" s="16" t="inlineStr">
-        <is>
-          <t>①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
-        </is>
-      </c>
-      <c r="G74" s="15" t="inlineStr">
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
+①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
+        </is>
+      </c>
+      <c r="G74" s="16" t="inlineStr">
         <is>
           <t>R-03.png</t>
         </is>
       </c>
-      <c r="H74" s="16" t="inlineStr">
+      <c r="H74" s="17" t="inlineStr">
         <is>
           <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
-      <c r="J74" s="16" t="inlineStr">
+      <c r="J74" s="17" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
       </c>
-      <c r="K74" s="16" t="inlineStr">
+      <c r="K74" s="17" t="inlineStr">
         <is>
           <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
-      <c r="L74" s="16" t="inlineStr">
+      <c r="L74" s="17" t="inlineStr">
         <is>
           <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
-      <c r="M74" s="16" t="inlineStr">
+      <c r="M74" s="17" t="inlineStr">
         <is>
           <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr"/>
       <c r="O74" s="5" t="inlineStr"/>
-      <c r="P74" s="16" t="inlineStr">
+      <c r="P74" s="6" t="inlineStr"/>
+      <c r="Q74" s="5" t="inlineStr"/>
+      <c r="R74" s="5" t="inlineStr"/>
+      <c r="S74" s="17" t="inlineStr">
         <is>
           <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" s="15" t="inlineStr">
+    <row r="75" ht="79" customHeight="1">
+      <c r="A75" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
         </is>
       </c>
-      <c r="B75" s="15" t="inlineStr">
+      <c r="B75" s="16" t="inlineStr">
         <is>
           <t>R-04</t>
         </is>
       </c>
-      <c r="C75" s="16" t="inlineStr">
+      <c r="C75" s="17" t="inlineStr">
         <is>
           <t>計算ロジックの共有レビュー</t>
         </is>
       </c>
-      <c r="D75" s="16" t="inlineStr">
+      <c r="D75" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
-      <c r="E75" s="16" t="inlineStr">
+      <c r="E75" s="17" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F75" s="16" t="inlineStr">
-        <is>
-          <t>同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
-        </is>
-      </c>
-      <c r="G75" s="15" t="inlineStr">
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
+同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="inlineStr">
         <is>
           <t>R-04.png</t>
         </is>
       </c>
-      <c r="H75" s="16" t="inlineStr">
+      <c r="H75" s="17" t="inlineStr">
         <is>
           <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="16" t="inlineStr">
+      <c r="J75" s="17" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
         </is>
       </c>
-      <c r="K75" s="16" t="inlineStr">
+      <c r="K75" s="17" t="inlineStr">
         <is>
           <t>計算ロジックが1箇所か</t>
         </is>
       </c>
-      <c r="L75" s="16" t="inlineStr">
+      <c r="L75" s="17" t="inlineStr">
         <is>
           <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
-      <c r="M75" s="16" t="inlineStr">
+      <c r="M75" s="17" t="inlineStr">
         <is>
           <t>AC-35 AC-11</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
       <c r="O75" s="5" t="inlineStr"/>
-      <c r="P75" s="16" t="inlineStr">
+      <c r="P75" s="6" t="inlineStr"/>
+      <c r="Q75" s="5" t="inlineStr"/>
+      <c r="R75" s="5" t="inlineStr"/>
+      <c r="S75" s="17" t="inlineStr">
         <is>
           <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" s="15" t="inlineStr">
+    <row r="76" ht="64" customHeight="1">
+      <c r="A76" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
         </is>
       </c>
-      <c r="B76" s="15" t="inlineStr">
+      <c r="B76" s="16" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
       </c>
-      <c r="C76" s="16" t="inlineStr">
+      <c r="C76" s="17" t="inlineStr">
         <is>
           <t>列マッピングの実装レビュー</t>
         </is>
       </c>
-      <c r="D76" s="16" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】取込の列解決の実装を提示してもらう</t>
         </is>
       </c>
-      <c r="E76" s="16" t="inlineStr">
+      <c r="E76" s="17" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F76" s="16" t="inlineStr">
-        <is>
-          <t>CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
-        </is>
-      </c>
-      <c r="G76" s="15" t="inlineStr">
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
+CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
+        </is>
+      </c>
+      <c r="G76" s="16" t="inlineStr">
         <is>
           <t>R-05.png</t>
         </is>
       </c>
-      <c r="H76" s="16" t="inlineStr">
+      <c r="H76" s="17" t="inlineStr">
         <is>
           <t>列名の対応づけを保持している箇所（DBかコードか）</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
-      <c r="J76" s="16" t="inlineStr">
+      <c r="J76" s="17" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
         </is>
       </c>
-      <c r="K76" s="16" t="inlineStr">
+      <c r="K76" s="17" t="inlineStr">
         <is>
           <t>列名がコードに埋まっていないか</t>
         </is>
       </c>
-      <c r="L76" s="16" t="inlineStr">
+      <c r="L76" s="17" t="inlineStr">
         <is>
           <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
-      <c r="M76" s="16" t="inlineStr">
+      <c r="M76" s="17" t="inlineStr">
         <is>
           <t>AC-22 AC-24</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr"/>
       <c r="O76" s="5" t="inlineStr"/>
-      <c r="P76" s="16" t="inlineStr">
+      <c r="P76" s="6" t="inlineStr"/>
+      <c r="Q76" s="5" t="inlineStr"/>
+      <c r="R76" s="5" t="inlineStr"/>
+      <c r="S76" s="17" t="inlineStr">
         <is>
           <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" s="15" t="inlineStr">
+    <row r="77" ht="79" customHeight="1">
+      <c r="A77" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
         </is>
       </c>
-      <c r="B77" s="15" t="inlineStr">
+      <c r="B77" s="16" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
       </c>
-      <c r="C77" s="16" t="inlineStr">
+      <c r="C77" s="17" t="inlineStr">
         <is>
           <t>設定更新処理の共通化レビュー</t>
         </is>
       </c>
-      <c r="D77" s="16" t="inlineStr">
+      <c r="D77" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
 【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
         </is>
       </c>
-      <c r="E77" s="16" t="inlineStr">
+      <c r="E77" s="17" t="inlineStr">
         <is>
           <t>（追加のデータ投入なし）</t>
         </is>
       </c>
-      <c r="F77" s="16" t="inlineStr">
-        <is>
-          <t>設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
-        </is>
-      </c>
-      <c r="G77" s="15" t="inlineStr">
+      <c r="F77" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
+設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="G77" s="16" t="inlineStr">
         <is>
           <t>R-06.png</t>
         </is>
       </c>
-      <c r="H77" s="16" t="inlineStr">
+      <c r="H77" s="17" t="inlineStr">
         <is>
           <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
-      <c r="J77" s="16" t="inlineStr">
+      <c r="J77" s="17" t="inlineStr">
         <is>
           <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
         </is>
       </c>
-      <c r="K77" s="16" t="inlineStr">
+      <c r="K77" s="17" t="inlineStr">
         <is>
           <t>2つの入口で更新処理が共通か</t>
         </is>
       </c>
-      <c r="L77" s="16" t="inlineStr">
+      <c r="L77" s="17" t="inlineStr">
         <is>
           <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
-      <c r="M77" s="16" t="inlineStr">
+      <c r="M77" s="17" t="inlineStr">
         <is>
           <t>AC-49</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
       <c r="O77" s="5" t="inlineStr"/>
-      <c r="P77" s="16" t="inlineStr">
+      <c r="P77" s="6" t="inlineStr"/>
+      <c r="Q77" s="5" t="inlineStr"/>
+      <c r="R77" s="5" t="inlineStr"/>
+      <c r="S77" s="17" t="inlineStr">
         <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:P77"/>
+  <autoFilter ref="A2:S77"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="O3:O77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S77"/>
+  <dimension ref="A1:S78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -563,10 +563,10 @@
     <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証64ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
+          <t>確かめる手順（準備11行＋検証65ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
 実施順を変えてはいけない箇所：①T-A08（勤怠取込）→T-S03（締め）　②T-S03→T-S04・T-D07→T-S05（この3件は締め済みでしか確認できない）　③C-000（初期化）は計算の先頭　④C-008は計算の最後（2026-05のEMP-001を352,286円に変えるためC-013・C-017が合わなくなる）　⑤T-N02の前にdata/02を再投入　⑥削除はEMP-012（T-L10）とEMP-004（T-D08）だけ
 列の使い方：使用する検証データ＝この検証で投入・使用するdataファイル／期待値＝先頭の【確認場所】でどの画面を見て合否を出すかを示し、続けて合格の基準を書いている／スクショ（撮るもの）＝何が写っていれば証拠になるか／スクショ貼付欄＝撮った画像をこの列に貼る／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めて合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを決める
-色：緑＝使う検証データ　青＝画面　橙＝スクショの指示　紫＝ヘルプ・受入条件との対応　黄＝当日の記入欄（スクショ貼付欄・実際の値・判定・所見・実施日・実施者）。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
+色：緑＝使う検証データ　青＝画面　橙＝スクショの指示　紫＝ヘルプ・受入条件との対応　黄＝当日の記入欄。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       <c r="R3" s="5" t="inlineStr"/>
       <c r="S3" s="4" t="inlineStr"/>
     </row>
-    <row r="4" ht="79" customHeight="1">
+    <row r="4" ht="94" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -755,7 +755,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>確定内容を確認：判断1＝所定労働日割／判断5＝振替（応援先に加算し所属店舗から差引）／判断6＝交通費は独立費目（通勤=所属店舗・ヘルプ先=応援先）。あわせて暫定適用中の判断7（深夜割増1.5）・8（みなし超過1.25・未達は減額なし）・9（端数は所属店舗に寄せる）を確認</t>
+          <t>確定内容を確認（判断1・5・6＝2026-08-03、判断7・8・9＝2026-08-07）：判断1＝所定労働日割／判断5＝振替（応援先に加算し所属店舗から差引）／判断6＝交通費は独立費目（通勤=所属店舗・ヘルプ先=応援先）。あわせて確定中の判断7（深夜割増1.5）・8（みなし超過1.25・未達は減額なし）・9（端数は所属店舗に寄せる）を確認</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -2480,68 +2480,68 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
+    <row r="28" ht="109" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>詳細</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>T-H01</t>
+          <t>T-D11</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>履歴の追記と過去行の不変</t>
+          <t>設定変更履歴の表示ルール</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 ／ 変更前の履歴をCSV出力しておく
-【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
+          <t>【前提】S-04 S-05
+【操作】EMP-001の詳細を開き、（a）並び順とステータス列の位置を確認 →（b）単位給与額を380,000に変更し適用日付＝翌々月1日で保存 →（c）保存後の履歴の最上部と強調を確認 →（d）右上「すべての履歴」を押す</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）04 設定変更履歴</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員設定履歴】
-履歴が1行増える。既存行の値の差分＝0</t>
+          <t>【確認場所：従業員詳細 → 設定変更履歴】
+（a）並びは変更反映日時の降順で、予約中が最上部。ステータスは変更反映日時の次（2列目）にあり横スクロールなしで見える。表示は直近3件（b・c）保存した行が最上部に増え、1つ古い行と値が違う項目（単位給与額）だけが強調される。強調の過不足=0件（d）従業員設定履歴が開き、EMP-001で絞り込まれた状態になる（絞り込みなしでの遷移=0件）</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>T-H01.png</t>
+          <t>T-D11.png</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
+          <t>保存前後の履歴セクション2枚（並び順とステータス列の位置が分かる範囲）／強調された項目／「すべての履歴」で開いた従業員設定履歴（絞り込み条件が見える状態）</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>従業員設定履歴 … 変更前後の行（既存行が書き換わらないこと）</t>
+          <t>従業員詳細 → 設定変更履歴セクション … 右上「すべての履歴」→ 従業員設定履歴（EMP-001で絞り込み済み）</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>既存行が書き換わらないか</t>
+          <t>保存した行が最上部に来るか／変更点だけ強調されるか</t>
         </is>
       </c>
       <c r="L28" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
       <c r="M28" s="13" t="inlineStr">
         <is>
-          <t>AC-07</t>
+          <t>AC-52 AC-53</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr"/>
@@ -2551,11 +2551,11 @@
       <c r="R28" s="5" t="inlineStr"/>
       <c r="S28" s="8" t="inlineStr">
         <is>
-          <t>原則①：過去は不変</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="79" customHeight="1">
+          <t>画面：保存できたか確かめられる／画面：変更点が読み取れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2563,18 +2563,18 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>T-H02</t>
+          <t>T-H01</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>記録の内容</t>
+          <t>履歴の追記と過去行の不変</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 T-D04実施済み
-【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
+          <t>【前提】S-05 ／ 変更前の履歴をCSV出力しておく
+【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -2585,28 +2585,28 @@
       <c r="F29" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員設定履歴】
-①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
+履歴が1行増える。既存行の値の差分＝0</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>T-H02.png</t>
+          <t>T-H01.png</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
+          <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>従業員設定履歴 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
+          <t>従業員設定履歴 … 変更前後の行（既存行が書き換わらないこと）</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>2つの日時が別で記録されるか</t>
+          <t>既存行が書き換わらないか</t>
         </is>
       </c>
       <c r="L29" s="13" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="M29" s="13" t="inlineStr">
         <is>
-          <t>AC-08 AC-09</t>
+          <t>AC-07</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr"/>
@@ -2626,11 +2626,11 @@
       <c r="R29" s="5" t="inlineStr"/>
       <c r="S29" s="8" t="inlineStr">
         <is>
-          <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="94" customHeight="1">
+          <t>原則①：過去は不変</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="79" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2638,18 +2638,18 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>T-H04</t>
+          <t>T-H02</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>履歴の絞り込み・出力・遷移</t>
+          <t>記録の内容</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
+          <t>【前提】S-05 T-D04実施済み
+【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -2660,28 +2660,28 @@
       <c r="F30" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員設定履歴】
-店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
+①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>T-H04.png</t>
+          <t>T-H02.png</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
+          <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>従業員設定履歴 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
+          <t>従業員設定履歴 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>絞り込み後の行だけ出力されるか</t>
+          <t>2つの日時が別で記録されるか</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="M30" s="13" t="inlineStr">
         <is>
-          <t>AC-33 AC-36 AC-30</t>
+          <t>AC-08 AC-09</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr"/>
@@ -2701,30 +2701,30 @@
       <c r="R30" s="5" t="inlineStr"/>
       <c r="S30" s="8" t="inlineStr">
         <is>
-          <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="124" customHeight="1">
+          <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="94" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>履歴</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>T-A02</t>
+          <t>T-H04</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>月別実績の表示と切替</t>
+          <t>履歴の絞り込み・出力・遷移</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
+【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -2734,39 +2734,39 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
-全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない</t>
+          <t>【確認場所：従業員設定履歴】
+店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>T-A02.png</t>
+          <t>T-H04.png</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
+          <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
+          <t>従業員設定履歴 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>モード切替で列が増減するか</t>
+          <t>絞り込み後の行だけ出力されるか</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>AC-10 AC-31</t>
+          <t>AC-33 AC-36 AC-30</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr"/>
@@ -2776,11 +2776,11 @@
       <c r="R31" s="5" t="inlineStr"/>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>計算：算式どおりの金額／画面：状態が漏れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="64" customHeight="1">
+          <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="124" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -2788,18 +2788,18 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>T-A09</t>
+          <t>T-A02</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>人件費実績からの設定編集</t>
+          <t>月別実績の表示と切替</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】人件費実績で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
+【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2809,39 +2809,39 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　行の「従業員設定」】
-モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>T-A09.png</t>
+          <t>T-A02.png</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>設定編集モーダル（項目が見える状態）／更新保存後の人件費実績／従業員詳細の設定変更履歴に行が増えたこと</t>
+          <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 人件費実績／確認は従業員詳細の設定変更履歴</t>
+          <t>人件費実績 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>モーダル編集でも履歴が残るか</t>
+          <t>モード切替で列が増減するか</t>
         </is>
       </c>
       <c r="L32" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M32" s="13" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-10 AC-31</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr"/>
@@ -2851,11 +2851,11 @@
       <c r="R32" s="5" t="inlineStr"/>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>原則①：どの入口から編集しても履歴が残る</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="109" customHeight="1">
+          <t>計算：算式どおりの金額／画面：状態が漏れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="64" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -2863,18 +2863,18 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>T-A05</t>
+          <t>T-A09</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>日別実績の表示</t>
+          <t>人件費実績からの設定編集</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
+【操作】人件費実績で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2884,39 +2884,39 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 日別実績タブ】
-全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
+          <t>【確認場所：人件費実績　→　行の「従業員設定」】
+モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>T-A05.png</t>
+          <t>T-A09.png</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
+          <t>設定編集モーダル（項目が見える状態）／更新保存後の人件費実績／従業員詳細の設定変更履歴に行が増えたこと</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
+          <t>人件費実績 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 人件費実績／確認は従業員詳細の設定変更履歴</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>日別に概算モードが無いか</t>
+          <t>モーダル編集でも履歴が残るか</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>AC-49</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
@@ -2926,11 +2926,11 @@
       <c r="R33" s="5" t="inlineStr"/>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>計算：算式どおりの金額</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="64" customHeight="1">
+          <t>原則①：どの入口から編集しても履歴が残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="109" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -2938,18 +2938,18 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>T-A07</t>
+          <t>T-A05</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>実績のCSVエクスポート</t>
+          <t>日別実績の表示</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
+【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2959,39 +2959,39 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績】
-出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
+          <t>【確認場所：人件費実績 → 日別実績タブ】
+全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>T-A07.png</t>
+          <t>T-A05.png</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
+          <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
+          <t>人件費実績 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>表示中の内容が出力されるか</t>
+          <t>日別に概算モードが無いか</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M34" s="13" t="inlineStr">
         <is>
-          <t>AC-36</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr"/>
@@ -3001,7 +3001,7 @@
       <c r="R34" s="5" t="inlineStr"/>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>入出力：画面の内容と一致</t>
+          <t>計算：算式どおりの金額</t>
         </is>
       </c>
     </row>
@@ -3013,18 +3013,18 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>T-A08</t>
+          <t>T-A07</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>勤怠実績の取込</t>
+          <t>実績のCSVエクスポート</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-08
-【操作】人件費実績の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
+          <t>【前提】S-05
+【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -3034,39 +3034,39 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
-「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
+          <t>【確認場所：人件費実績】
+出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>T-A08.png</t>
+          <t>T-A07.png</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
+          <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
+          <t>人件費実績 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>進捗が出て他操作を受け付けないか</t>
+          <t>表示中の内容が出力されるか</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>AC-48</t>
+          <t>AC-36</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr"/>
@@ -3076,62 +3076,62 @@
       <c r="R35" s="5" t="inlineStr"/>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>入出力：勤怠実績を取り込める</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="60" customHeight="1">
+          <t>入出力：画面の内容と一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="64" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>締め</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>T-S01</t>
+          <t>T-A08</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>締めボタンの表示条件</t>
+          <t>勤怠実績の取込</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-08
-【操作】月別実績タブと日別実績タブを順に開く</t>
+          <t>【前提】S-05 S-08
+【操作】人件費実績の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績】
-月別のみ「2026-05 締め」が表示。日別には表示されない</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>T-S01.png</t>
+          <t>T-A08.png</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
+          <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
+          <t>人件費実績 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>締めが月別タブにだけ出るか</t>
+          <t>進捗が出て他操作を受け付けないか</t>
         </is>
       </c>
       <c r="L36" s="13" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="M36" s="13" t="inlineStr">
         <is>
-          <t>AC-18</t>
+          <t>AC-48</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr"/>
@@ -3151,11 +3151,11 @@
       <c r="R36" s="5" t="inlineStr"/>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めの単位は月</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="64" customHeight="1">
+          <t>入出力：勤怠実績を取り込める</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3163,18 +3163,18 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>T-S03</t>
+          <t>T-S01</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>締めの実行</t>
+          <t>締めボタンの表示条件</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06 S-08
-【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
+          <t>【前提】S-08
+【操作】月別実績タブと日別実績タブを順に開く</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -3184,29 +3184,29 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
-「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
+          <t>【確認場所：人件費実績】
+月別のみ「2026-05 締め」が表示。日別には表示されない</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>T-S03.png</t>
+          <t>T-S01.png</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
+          <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
+          <t>人件費実績 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>確認モーダルを経て締まるか</t>
+          <t>締めが月別タブにだけ出るか</t>
         </is>
       </c>
       <c r="L37" s="13" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="M37" s="13" t="inlineStr">
         <is>
-          <t>AC-16 AC-19 AC-32</t>
+          <t>AC-18</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr"/>
@@ -3226,11 +3226,11 @@
       <c r="R37" s="5" t="inlineStr"/>
       <c r="S37" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1">
+          <t>原則②：締めの単位は月</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="64" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3238,18 +3238,18 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>T-S04</t>
+          <t>T-S03</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>締め後は編集できない</t>
+          <t>締めの実行</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み
-【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
+          <t>【前提】S-06 S-08
+【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -3259,39 +3259,39 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績】
-編集できない（または反映されない）</t>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>T-S04.png</t>
+          <t>T-S03.png</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
+          <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
+          <t>人件費実績 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>締め後に金額が動かないか</t>
+          <t>確認モーダルを経て締まるか</t>
         </is>
       </c>
       <c r="L38" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M38" s="13" t="inlineStr">
         <is>
-          <t>AC-16</t>
+          <t>AC-16 AC-19 AC-32</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr"/>
@@ -3301,7 +3301,7 @@
       <c r="R38" s="5" t="inlineStr"/>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない</t>
+          <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
         </is>
       </c>
     </row>
@@ -3313,18 +3313,18 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>T-D07</t>
+          <t>T-S04</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>締め済み期間への遡及</t>
+          <t>締め後は編集できない</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み S-07
-【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
+          <t>【前提】T-S03実施済み
+【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -3334,39 +3334,39 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細】
-締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
+          <t>【確認場所：人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績】
+編集できない（または反映されない）</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>T-D07.png</t>
+          <t>T-S04.png</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
+          <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
+          <t>人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>警告が出て反映されないか</t>
+          <t>締め後に金額が動かないか</t>
         </is>
       </c>
       <c r="L39" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="M39" s="13" t="inlineStr">
         <is>
-          <t>AC-20</t>
+          <t>AC-16</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr"/>
@@ -3376,11 +3376,11 @@
       <c r="R39" s="5" t="inlineStr"/>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t>原則②：遡及は黙って捨てない</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="64" customHeight="1">
+          <t>原則②：締めたら動かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3388,18 +3388,18 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>T-S05</t>
+          <t>T-D07</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>締めの解除</t>
+          <t>締め済み期間への遡及</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み
-【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
+          <t>【前提】T-S03実施済み S-07
+【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -3409,39 +3409,39 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
-「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
+          <t>【確認場所：従業員詳細】
+締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>T-S05.png</t>
+          <t>T-D07.png</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
+          <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
+          <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>解除で再計算されるか</t>
+          <t>警告が出て反映されないか</t>
         </is>
       </c>
       <c r="L40" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
       <c r="M40" s="13" t="inlineStr">
         <is>
-          <t>AC-19</t>
+          <t>AC-20</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr"/>
@@ -3451,7 +3451,7 @@
       <c r="R40" s="5" t="inlineStr"/>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>原則②：確定操作は確認を経る</t>
+          <t>原則②：遡及は黙って捨てない</t>
         </is>
       </c>
     </row>
@@ -3463,18 +3463,18 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>T-S07</t>
+          <t>T-S05</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>締めの実行権限</t>
+          <t>締めの解除</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-10 S-08
-【操作】店長スコープのアカウントでログインし、人件費実績を開いて締めを試みる</t>
+          <t>【前提】T-S03実施済み
+【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -3484,39 +3484,39 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ（店長スコープでログイン）】
-締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>T-S07.png</t>
+          <t>T-S05.png</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>店長スコープでの人件費実績（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
+          <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
+          <t>人件費実績 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>店長が締められないか</t>
+          <t>解除で再計算されるか</t>
         </is>
       </c>
       <c r="L41" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="M41" s="13" t="inlineStr">
         <is>
-          <t>AC-41</t>
+          <t>AC-19</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr"/>
@@ -3526,30 +3526,30 @@
       <c r="R41" s="5" t="inlineStr"/>
       <c r="S41" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="79" customHeight="1">
+          <t>原則②：確定操作は確認を経る</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="64" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>取込</t>
+          <t>締め</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>T-I02</t>
+          <t>T-S07</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>テンプレートのDLと画面</t>
+          <t>締めの実行権限</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
+          <t>【前提】S-10 S-08
+【操作】店長スコープのアカウントでログインし、人件費実績を開いて締めを試みる</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -3559,39 +3559,39 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ（店長スコープでログイン）】
+締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>T-I02.png</t>
+          <t>T-S07.png</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
+          <t>店長スコープでの人件費実績（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
+          <t>人件費実績 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
         </is>
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>テンプレートの列とBOM</t>
+          <t>店長が締められないか</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ はじめて設定する</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M42" s="13" t="inlineStr">
         <is>
-          <t>AC-21 AC-30</t>
+          <t>AC-41</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr"/>
@@ -3601,11 +3601,11 @@
       <c r="R42" s="5" t="inlineStr"/>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="64" customHeight="1">
+          <t>原則②：締めは会社スコープのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="79" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3613,50 +3613,50 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>T-I03</t>
+          <t>T-I02</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>King of Time形式の取込</t>
+          <t>テンプレートのDLと画面</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-06
-【操作】データ種類＝King of Time を選び data/07（従業員設定・3行）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
+          <t>【前提】S-01
+【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート】
-07は3行すべて取り込まれ、EMP-001=340,000・EMP-005=360,000に更新、EMP-013は新規追加。10は給与設定（ヘルプ先交通費 S02:700;S03:900 の記法を含む）が反映される</t>
+従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>T-I03.png</t>
+          <t>T-I02.png</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
+          <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
+          <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>3行が更新・追加されるか</t>
+          <t>テンプレートの列とBOM</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="M43" s="13" t="inlineStr">
         <is>
-          <t>AC-21</t>
+          <t>AC-21 AC-30</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr"/>
@@ -3676,11 +3676,11 @@
       <c r="R43" s="5" t="inlineStr"/>
       <c r="S43" s="8" t="inlineStr">
         <is>
-          <t>入出力：導入を止めない</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="60" customHeight="1">
+          <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="64" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3688,50 +3688,50 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>T-I04</t>
+          <t>T-I03</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>ジョブカン形式（表記ゆれ）の取込</t>
+          <t>King of Time形式の取込</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】データ種類＝ジョブカン を選び data/08（3行）をD&amp;D → 登録</t>
+【操作】データ種類＝King of Time を選び data/07（従業員設定・3行）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>08 取込CSV ジョブカン</t>
+          <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート】
-3行すべて取り込まれる（EMP-003=1,250・EMP-010=1,300・EMP-014は新規）</t>
+07は3行すべて取り込まれ、EMP-001=340,000・EMP-005=360,000に更新、EMP-013は新規追加。10は給与設定（ヘルプ先交通費 S02:700;S03:900 の記法を含む）が反映される</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>T-I04.png</t>
+          <t>T-I03.png</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
+          <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
+          <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>表記ゆれを吸収できるか</t>
+          <t>3行が更新・追加されるか</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>AC-22</t>
+          <t>AC-21</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr"/>
@@ -3751,7 +3751,7 @@
       <c r="R44" s="5" t="inlineStr"/>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収</t>
+          <t>入出力：導入を止めない</t>
         </is>
       </c>
     </row>
@@ -3763,60 +3763,60 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>T-I05</t>
+          <t>T-I04</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>異常系データの検出</t>
+          <t>ジョブカン形式（表記ゆれ）の取込</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】data/09（4行）をD&amp;D → 登録</t>
+【操作】データ種類＝ジョブカン を選び data/08（3行）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>08 取込CSV ジョブカン</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート】
-4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
+3行すべて取り込まれる（EMP-003=1,250・EMP-010=1,300・EMP-014は新規）</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>T-I05.png</t>
+          <t>T-I04.png</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
+          <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
+          <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>4種の異常を行ごとに検出するか</t>
+          <t>表記ゆれを吸収できるか</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
+          <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
       <c r="M45" s="13" t="inlineStr">
         <is>
-          <t>AC-23</t>
+          <t>AC-22</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr"/>
@@ -3826,7 +3826,7 @@
       <c r="R45" s="5" t="inlineStr"/>
       <c r="S45" s="8" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない</t>
+          <t>入出力：表記ゆれを吸収</t>
         </is>
       </c>
     </row>
@@ -3838,50 +3838,50 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>T-I17</t>
+          <t>T-I05</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>二重登録の防止</t>
+          <t>異常系データの検出</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】（a）data/07を2回続けて取り込む （b）data/19（EMP-002が2行・単位給与額が異なる）を取り込む</t>
+【操作】data/09（4行）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート】
-（a）2回目は更新となり件数が増えない （b）重複行がエラーとして検出される（両方が登録されない）</t>
+4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>T-I17.png</t>
+          <t>T-I05.png</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
+          <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
+          <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>二重登録されないか</t>
+          <t>4種の異常を行ごとに検出するか</t>
         </is>
       </c>
       <c r="L46" s="13" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="M46" s="13" t="inlineStr">
         <is>
-          <t>AC-40</t>
+          <t>AC-23</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr"/>
@@ -3901,11 +3901,11 @@
       <c r="R46" s="5" t="inlineStr"/>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>データ保全：二重登録を防ぐ</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="94" customHeight="1">
+          <t>データ保全：不正値を入れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3913,50 +3913,50 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>T-I18</t>
+          <t>T-I17</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>取込が途中で失敗したときの扱い</t>
+          <t>二重登録の防止</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
+【操作】（a）data/07を2回続けて取り込む （b）data/19（EMP-002が2行・単位給与額が異なる）を取り込む</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録】
-中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
+          <t>【確認場所：設定インポート】
+（a）2回目は更新となり件数が増えない （b）重複行がエラーとして検出される（両方が登録されない）</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>T-I18.png</t>
+          <t>T-I17.png</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
+          <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録されていないこと）</t>
+          <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>部分登録が残らないか</t>
+          <t>二重登録されないか</t>
         </is>
       </c>
       <c r="L47" s="13" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="M47" s="13" t="inlineStr">
         <is>
-          <t>AC-42</t>
+          <t>AC-40</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr"/>
@@ -3976,11 +3976,11 @@
       <c r="R47" s="5" t="inlineStr"/>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>データ保全：中途半端に残さない</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="64" customHeight="1">
+          <t>データ保全：二重登録を防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="94" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3988,60 +3988,60 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>T-I11</t>
+          <t>T-I18</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>CSV位置合わせ設定</t>
+          <t>取込が途中で失敗したときの扱い</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06
-【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
+          <t>【前提】S-04 S-06
+【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>11 取込CSV 説明行あり</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-余計な行が無視され、3行が正しく取り込まれる</t>
+          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録】
+中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>T-I11.png</t>
+          <t>T-I18.png</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
+          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
+          <t>設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録されていないこと）</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>説明行を飛ばして取り込めるか</t>
+          <t>部分登録が残らないか</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="M48" s="13" t="inlineStr">
         <is>
-          <t>AC-37</t>
+          <t>AC-42</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr"/>
@@ -4051,11 +4051,11 @@
       <c r="R48" s="5" t="inlineStr"/>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>入出力：現場のCSVをそのまま使える</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="94" customHeight="1">
+          <t>データ保全：中途半端に残さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="64" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4063,50 +4063,50 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>T-I09</t>
+          <t>T-I11</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>CSV位置合わせ設定</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】「列マッピングテンプレート管理」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
+【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>11 取込CSV 説明行あり</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート管理」】
-テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
+          <t>【確認場所：設定インポート】
+余計な行が無視され、3行が正しく取り込まれる</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>T-I09.png</t>
+          <t>T-I11.png</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
+          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>設定インポート → ツールバー「列マッピングテンプレート管理」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
+          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>テンプレの登録・編集・削除と往復</t>
+          <t>説明行を飛ばして取り込めるか</t>
         </is>
       </c>
       <c r="L49" s="13" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>AC-24 AC-38 AC-30</t>
+          <t>AC-37</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
@@ -4126,11 +4126,11 @@
       <c r="R49" s="5" t="inlineStr"/>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="79" customHeight="1">
+          <t>入出力：現場のCSVをそのまま使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="94" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4138,50 +4138,50 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>T-I19</t>
+          <t>T-I09</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>マッピング表の一括登録</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
+【操作】「列マッピングテンプレート管理」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>18 列マッピング表テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：列マッピングテンプレート】
-テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
+          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート管理」】
+テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>T-I19.png</t>
+          <t>T-I09.png</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
+          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
+          <t>設定インポート → ツールバー「列マッピングテンプレート管理」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>一括登録と10MB超の扱い</t>
+          <t>テンプレの登録・編集・削除と往復</t>
         </is>
       </c>
       <c r="L50" s="13" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="M50" s="13" t="inlineStr">
         <is>
-          <t>AC-51</t>
+          <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr"/>
@@ -4201,72 +4201,72 @@
       <c r="R50" s="5" t="inlineStr"/>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>入出力：マッピングの一括運用</t>
+          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="51" ht="79" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>取込</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>T-E04</t>
+          <t>T-I19</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>設定のエクスポート</t>
+          <t>マッピング表の一括登録</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
+          <t>【前提】S-06
+【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>18 列マッピング表テンプレ</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
-専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
+          <t>【確認場所：列マッピングテンプレート】
+テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>T-E04.png</t>
+          <t>T-I19.png</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
+          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
+          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>選んだ項目だけ・対象数だけ出るか</t>
+          <t>一括登録と10MB超の扱い</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M51" s="13" t="inlineStr">
         <is>
-          <t>AC-25 AC-26 AC-30</t>
+          <t>AC-51</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr"/>
@@ -4276,11 +4276,11 @@
       <c r="R51" s="5" t="inlineStr"/>
       <c r="S51" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="64" customHeight="1">
+          <t>入出力：マッピングの一括運用</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="79" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4288,50 +4288,50 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>T-E09</t>
+          <t>T-E04</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>実績・同時のエクスポート</t>
+          <t>設定のエクスポート</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
+          <t>【前提】S-04
+【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート】
-実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
+          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
+専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>T-E09.png</t>
+          <t>T-E04.png</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
+          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
+          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
         </is>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>実績と同時選択のファイル数</t>
+          <t>選んだ項目だけ・対象数だけ出るか</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="M52" s="13" t="inlineStr">
         <is>
-          <t>AC-25</t>
+          <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr"/>
@@ -4351,11 +4351,11 @@
       <c r="R52" s="5" t="inlineStr"/>
       <c r="S52" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="60" customHeight="1">
+          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="64" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4363,50 +4363,50 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>T-E07</t>
+          <t>T-E09</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>未選択でのエクスポート防止</t>
+          <t>実績・同時のエクスポート</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
+          <t>【前提】S-05
+【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
+実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>T-E07.png</t>
+          <t>T-E09.png</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
+          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
+          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>未選択で出力されないか</t>
+          <t>実績と同時選択のファイル数</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>AC-27</t>
+          <t>AC-25</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr"/>
@@ -4426,7 +4426,7 @@
       <c r="R53" s="5" t="inlineStr"/>
       <c r="S53" s="8" t="inlineStr">
         <is>
-          <t>入出力：空振りを防ぐ</t>
+          <t>入出力：渡し先に合わせて出せる</t>
         </is>
       </c>
     </row>
@@ -4438,18 +4438,18 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>T-E08</t>
+          <t>T-E07</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>出力CSVの文字化け</t>
+          <t>未選択でのエクスポート防止</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 ／ T-E04で出力済み
-【操作】T-E04で出力したCSVをExcelで開く</t>
+          <t>【前提】S-04
+【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -4460,28 +4460,28 @@
       <c r="F54" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
+警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>T-E08.png</t>
+          <t>T-E07.png</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
+          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
+          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>Excelで文字化けしないか</t>
+          <t>未選択で出力されないか</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="M54" s="13" t="inlineStr">
         <is>
-          <t>AC-28</t>
+          <t>AC-27</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr"/>
@@ -4501,72 +4501,72 @@
       <c r="R54" s="5" t="inlineStr"/>
       <c r="S54" s="8" t="inlineStr">
         <is>
-          <t>入出力：そのまま提出できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="64" customHeight="1">
+          <t>入出力：空振りを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>取込データ</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>T-N01</t>
+          <t>T-E08</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>取込元データの確認</t>
+          <t>出力CSVの文字化け</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-I03実施済み
-【操作】サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
+          <t>【前提】S-04 ／ T-E04で出力済み
+【操作】T-E04で出力したCSVをExcelで開く</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定取込データ（サイドバー）】
-設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
+          <t>【確認場所：設定・実績エクスポート】
+日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>T-N01.png</t>
+          <t>T-E08.png</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>設定取込データと実績取込データの一覧＋各タブ（計4枚）</t>
+          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>設定取込データ（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績取込データ … 月別データ／日別データタブ</t>
+          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>元データとタブの構成</t>
+          <t>Excelで文字化けしないか</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M55" s="13" t="inlineStr">
         <is>
-          <t>AC-39</t>
+          <t>AC-28</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
@@ -4576,11 +4576,11 @@
       <c r="R55" s="5" t="inlineStr"/>
       <c r="S55" s="8" t="inlineStr">
         <is>
-          <t>入出力：原因を追える</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="94" customHeight="1">
+          <t>入出力：そのまま提出できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="64" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -4588,50 +4588,50 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>T-N02</t>
+          <t>T-N01</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>取込前のプレビューと前回差分</t>
+          <t>取込元データの確認</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-06
-【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
+          <t>【前提】T-I03実施済み
+【操作】サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定取込データ／実績取込データ】
-プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
+          <t>【確認場所：設定取込データ（サイドバー）】
+設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>T-N02.png</t>
+          <t>T-N01.png</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
+          <t>設定取込データと実績取込データの一覧＋各タブ（計4枚）</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>設定取込データ／実績取込データ … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
+          <t>設定取込データ（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績取込データ … 月別データ／日別データタブ</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>差分がdata/16・17と一致するか</t>
+          <t>元データとタブの構成</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="M56" s="13" t="inlineStr">
         <is>
-          <t>AC-50</t>
+          <t>AC-39</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr"/>
@@ -4651,11 +4651,11 @@
       <c r="R56" s="5" t="inlineStr"/>
       <c r="S56" s="8" t="inlineStr">
         <is>
-          <t>データ保全：取り込む前に気づける</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="60" customHeight="1">
+          <t>入出力：原因を追える</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="94" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -4663,50 +4663,50 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>T-N03</t>
+          <t>T-N02</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>取込データと人件費実績の相互導線</t>
+          <t>取込前のプレビューと前回差分</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
+          <t>【前提】S-05 S-06
+【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　「実績取込データへ」／実績取込データ】
-2経路とも到達する（不通=0）</t>
+          <t>【確認場所：設定取込データ／実績取込データ】
+プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>T-N03.png</t>
+          <t>T-N02.png</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>人件費実績→実績取込データ／実績取込データ→人件費実績 の到達直後（2枚）</t>
+          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 「実績取込データへ」／実績取込データ → 「人件費実績へ」（相互導線）</t>
+          <t>設定取込データ／実績取込データ … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>2経路とも到達するか</t>
+          <t>差分がdata/16・17と一致するか</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="M57" s="13" t="inlineStr">
         <is>
-          <t>AC-30</t>
+          <t>AC-50</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr"/>
@@ -4726,72 +4726,72 @@
       <c r="R57" s="5" t="inlineStr"/>
       <c r="S57" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る</t>
+          <t>データ保全：取り込む前に気づける</t>
         </is>
       </c>
     </row>
     <row r="58" ht="60" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>T-Z01</t>
+          <t>T-N03</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>移行前後の突合（既存データ）</t>
+          <t>取込データと人件費実績の相互導線</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 S-11
-【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
+          <t>【前提】S-05
+【操作】人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員一覧】
-件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
+          <t>【確認場所：人件費実績　→　「実績取込データへ」／実績取込データ】
+2経路とも到達する（不通=0）</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>T-Z01.png</t>
+          <t>T-N03.png</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
+          <t>人件費実績→実績取込データ／実績取込データ→人件費実績 の到達直後（2枚）</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
+          <t>人件費実績 → 「実績取込データへ」／実績取込データ → 「人件費実績へ」（相互導線）</t>
         </is>
       </c>
       <c r="K58" s="8" t="inlineStr">
         <is>
-          <t>移行前後で差分0件か</t>
+          <t>2経路とも到達するか</t>
         </is>
       </c>
       <c r="L58" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ すでにご利用中のお客様</t>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>AC-01</t>
+          <t>AC-30</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr"/>
@@ -4801,7 +4801,7 @@
       <c r="R58" s="5" t="inlineStr"/>
       <c r="S58" s="8" t="inlineStr">
         <is>
-          <t>移行：既存顧客が壊れない</t>
+          <t>画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
@@ -4813,50 +4813,50 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>T-Z02</t>
+          <t>T-Z01</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>移行後の適用日付の付与</t>
+          <t>移行前後の突合（既存データ）</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
+          <t>【前提】S-09 S-11
+【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細 → 設定変更履歴／従業員設定履歴】
-適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている</t>
+          <t>【確認場所：従業員一覧】
+件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>T-Z02.png</t>
+          <t>T-Z01.png</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
+          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 設定変更履歴／従業員設定履歴 … 適用日付の空欄</t>
+          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>適用日付の空欄が0件か</t>
+          <t>移行前後で差分0件か</t>
         </is>
       </c>
       <c r="L59" s="13" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M59" s="13" t="inlineStr">
         <is>
-          <t>AC-02</t>
+          <t>AC-01</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr"/>
@@ -4876,7 +4876,7 @@
       <c r="R59" s="5" t="inlineStr"/>
       <c r="S59" s="8" t="inlineStr">
         <is>
-          <t>移行：履歴の起点を作る</t>
+          <t>移行：既存顧客が壊れない</t>
         </is>
       </c>
     </row>
@@ -4888,50 +4888,50 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>T-Z03</t>
+          <t>T-Z02</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>移行前後の過去月の人件費</t>
+          <t>移行後の適用日付の付与</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
           <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行前に出力しておいた直近3か月の人件費実績と、移行後の同3か月を突合する</t>
+【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
-3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
+          <t>【確認場所：従業員詳細 → 設定変更履歴／従業員設定履歴】
+適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>T-Z03.png</t>
+          <t>T-Z02.png</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>移行前後の人件費実績 月別実績（直近3か月・金額が同じであること）</t>
+          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ … 移行前後の直近3か月</t>
+          <t>従業員詳細 → 設定変更履歴／従業員設定履歴 … 適用日付の空欄</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>過去3か月の金額が変わらないか</t>
+          <t>適用日付の空欄が0件か</t>
         </is>
       </c>
       <c r="L60" s="13" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="M60" s="13" t="inlineStr">
         <is>
-          <t>AC-03</t>
+          <t>AC-02</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr"/>
@@ -4951,7 +4951,7 @@
       <c r="R60" s="5" t="inlineStr"/>
       <c r="S60" s="8" t="inlineStr">
         <is>
-          <t>移行：過去が動かない</t>
+          <t>移行：履歴の起点を作る</t>
         </is>
       </c>
     </row>
@@ -4963,60 +4963,60 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>T-Z04</t>
+          <t>T-Z03</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>サイドバーの構成</t>
+          <t>移行前後の過去月の人件費</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
+          <t>【前提】S-09 ／ T-Z01実施済み
+【操作】移行前に出力しておいた直近3か月の人件費実績と、移行後の同3か月を突合する</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：サイドバー「従業員管理」】
-閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>T-Z04.png</t>
+          <t>T-Z03.png</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
+          <t>移行前後の人件費実績 月別実績（直近3か月・金額が同じであること）</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
+          <t>人件費実績 → 月別実績タブ … 移行前後の直近3か月</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>PC・モバイルとも開くか</t>
+          <t>過去3か月の金額が変わらないか</t>
         </is>
       </c>
       <c r="L61" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・画面構成）</t>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>AC-29</t>
+          <t>AC-03</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr"/>
@@ -5026,7 +5026,7 @@
       <c r="R61" s="5" t="inlineStr"/>
       <c r="S61" s="8" t="inlineStr">
         <is>
-          <t>画面：たどり着ける</t>
+          <t>移行：過去が動かない</t>
         </is>
       </c>
     </row>
@@ -5038,60 +5038,60 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>T-Z05</t>
+          <t>T-Z04</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>遷移と表示規則の網羅</t>
+          <t>サイドバーの構成</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-05
-【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+          <t>【前提】S-01
+【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
-すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+          <t>【確認場所：サイドバー「従業員管理」】
+閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>T-Z05.png</t>
+          <t>T-Z04.png</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
+          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
         </is>
       </c>
       <c r="K62" s="8" t="inlineStr">
         <is>
-          <t>75本の遷移と表示規則</t>
+          <t>PC・モバイルとも開くか</t>
         </is>
       </c>
       <c r="L62" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・遷移網羅）</t>
+          <t>（ヘルプ記載なし・画面構成）</t>
         </is>
       </c>
       <c r="M62" s="13" t="inlineStr">
         <is>
-          <t>AC-30 AC-01</t>
+          <t>AC-29</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr"/>
@@ -5101,72 +5101,72 @@
       <c r="R62" s="5" t="inlineStr"/>
       <c r="S62" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="79" customHeight="1">
-      <c r="A63" s="14" t="inlineStr">
-        <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>C-000</t>
-        </is>
-      </c>
-      <c r="C63" s="15" t="inlineStr">
-        <is>
-          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
-        </is>
-      </c>
-      <c r="D63" s="15" t="inlineStr">
-        <is>
-          <t>【前提】S-03 S-05
-【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
-        </is>
-      </c>
-      <c r="E63" s="15" t="inlineStr">
-        <is>
-          <t>02〜06・13を再投入（初期化）</t>
-        </is>
-      </c>
-      <c r="F63" s="15" t="inlineStr">
-        <is>
-          <t>【確認場所：従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未】
-従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
-        </is>
-      </c>
-      <c r="G63" s="14" t="inlineStr">
-        <is>
-          <t>C-000.png</t>
-        </is>
-      </c>
-      <c r="H63" s="15" t="inlineStr">
-        <is>
-          <t>初期化後の従業員一覧（12名）と人件費実績（未締め・S-05時点の金額）</t>
+          <t>画面：たどり着ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>T-Z05</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>遷移と表示規則の網羅</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>【前提】S-04 S-05
+【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
+すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>T-Z05.png</t>
+        </is>
+      </c>
+      <c r="H63" s="11" t="inlineStr">
+        <is>
+          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="15" t="inlineStr">
-        <is>
-          <t>従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未締めに戻す）</t>
-        </is>
-      </c>
-      <c r="K63" s="15" t="inlineStr">
-        <is>
-          <t>S-05時点の値に戻ったか</t>
-        </is>
-      </c>
-      <c r="L63" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため対応なし）</t>
-        </is>
-      </c>
-      <c r="M63" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J63" s="12" t="inlineStr">
+        <is>
+          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+        </is>
+      </c>
+      <c r="K63" s="8" t="inlineStr">
+        <is>
+          <t>75本の遷移と表示規則</t>
+        </is>
+      </c>
+      <c r="L63" s="13" t="inlineStr">
+        <is>
+          <t>（ヘルプ記載なし・遷移網羅）</t>
+        </is>
+      </c>
+      <c r="M63" s="13" t="inlineStr">
+        <is>
+          <t>AC-30 AC-01</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr"/>
@@ -5174,13 +5174,13 @@
       <c r="P63" s="6" t="inlineStr"/>
       <c r="Q63" s="5" t="inlineStr"/>
       <c r="R63" s="5" t="inlineStr"/>
-      <c r="S63" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="64" customHeight="1">
+      <c r="S63" s="8" t="inlineStr">
+        <is>
+          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="79" customHeight="1">
       <c r="A64" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5188,60 +5188,60 @@
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>C-001</t>
+          <t>C-000</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプなし）</t>
+          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-002（概算280,000・基礎時給1,750＝280,000÷160・深夜2h）と EMP-007（概算300,000・基礎時給1,875＝300,000÷160・深夜4h）を検算</t>
+          <t>【前提】S-03 S-05
+【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>02〜06・13を再投入（初期化）</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-EMP-002＝285,250（概算280,000＋深夜残業代5,250＝1,750×1.5×2h）／EMP-007＝311,250（概算300,000＋深夜残業代11,250＝1,875×1.5×4h）。いずれも差分0円</t>
+          <t>【確認場所：従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未】
+従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>C-001.png</t>
+          <t>C-000.png</t>
         </is>
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
+          <t>初期化後の従業員一覧（12名）と人件費実績（未締め・S-05時点の金額）</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
+          <t>従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未締めに戻す）</t>
         </is>
       </c>
       <c r="K64" s="15" t="inlineStr">
         <is>
-          <t>概算＋深夜＝実績給与か</t>
+          <t>S-05時点の値に戻ったか</t>
         </is>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>（初期化のため対応なし）</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr"/>
@@ -5251,11 +5251,11 @@
       <c r="R64" s="5" t="inlineStr"/>
       <c r="S64" s="15" t="inlineStr">
         <is>
-          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・暫定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="94" customHeight="1">
+          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="64" customHeight="1">
       <c r="A65" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5263,60 +5263,60 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>C-003</t>
+          <t>C-001</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプあり）</t>
+          <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-001（概算320,000・基礎時給2,000・深夜6h・ヘルプ22h／総労働172h）／EMP-005（概算350,000・基礎時給2,187・深夜10h・ヘルプ35h／総労働185h）／EMP-003（概算144,000・時給1,200・深夜0h・ヘルプ20h／総労働120h）を検算</t>
+【操作】2026-05の EMP-002（概算280,000・基礎時給1,750＝280,000÷160・深夜2h）と EMP-007（概算300,000・基礎時給1,875＝300,000÷160・深夜4h）を検算</t>
         </is>
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F65" s="15" t="inlineStr">
         <is>
           <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-EMP-001＝338,000（概算320,000＋深夜18,000＝2,000×1.5×6h）／EMP-005＝382,812（概算350,000＋深夜32,812＝2,187×1.5×10h）／EMP-003＝144,000（深夜なし）。ヘルプ人件費は実績給与×ヘルプ時間÷総労働時間で按分し応援先へ振替（EMP-001＝43,232／EMP-003＝24,000／EMP-005＝72,424）</t>
+EMP-002＝285,250（概算280,000＋深夜残業代5,250＝1,750×1.5×2h）／EMP-007＝311,250（概算300,000＋深夜残業代11,250＝1,875×1.5×4h）。いずれも差分0円</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>C-003.png</t>
+          <t>C-001.png</t>
         </is>
       </c>
       <c r="H65" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
+          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
+          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
         </is>
       </c>
       <c r="K65" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費が按分で振替されるか</t>
+          <t>概算＋深夜＝実績給与か</t>
         </is>
       </c>
       <c r="L65" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M65" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr"/>
@@ -5326,11 +5326,11 @@
       <c r="R65" s="5" t="inlineStr"/>
       <c r="S65" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="60" customHeight="1">
+          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="109" customHeight="1">
       <c r="A66" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5338,50 +5338,50 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>C-005</t>
+          <t>C-003</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計と全社合計の一致</t>
+          <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】2026-05の EMP-001（概算320,000・基礎時給2,000・深夜6h・ヘルプ22h／総労働172h）／EMP-005（概算350,000・基礎時給2,187.5・深夜10h・ヘルプ35h／総労働185h）／EMP-003（概算144,000・時給1,200・深夜0h・ヘルプ20h／総労働120h）を検算</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
           <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
+EMP-001＝338,000（概算320,000＋深夜18,000＝2,000×1.5×6h）／EMP-005＝382,812（概算350,000＋深夜32,812＝2,187.5×1.5×10h＝32,812.5→32,812）／EMP-003＝144,000（深夜なし）。ヘルプ人件費は実績給与×ヘルプ時間÷総労働時間で按分し応援先へ振替（EMP-001＝43,232／EMP-003＝24,000／EMP-005＝72,424）</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>C-005.png</t>
+          <t>C-003.png</t>
         </is>
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
+          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
+          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
         </is>
       </c>
       <c r="K66" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計＝全社（差0円）か</t>
+          <t>ヘルプ人件費が按分で振替されるか</t>
         </is>
       </c>
       <c r="L66" s="15" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>AC-11</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr"/>
@@ -5401,11 +5401,11 @@
       <c r="R66" s="5" t="inlineStr"/>
       <c r="S66" s="15" t="inlineStr">
         <is>
-          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="79" customHeight="1">
+          <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="60" customHeight="1">
       <c r="A67" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5413,60 +5413,60 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>C-006</t>
+          <t>C-005</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>月中改定と予約の日割り</t>
+          <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>14 勤務データ 2026-06</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従】
-6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
+店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>C-006.png</t>
+          <t>C-005.png</t>
         </is>
       </c>
       <c r="H67" s="15" t="inlineStr">
         <is>
-          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
+          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
+          <t>人件費実績 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
         </is>
       </c>
       <c r="K67" s="15" t="inlineStr">
         <is>
-          <t>所定労働日割になっているか</t>
+          <t>店舗別合計＝全社（差0円）か</t>
         </is>
       </c>
       <c r="L67" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M67" s="15" t="inlineStr">
         <is>
-          <t>AC-12 AC-04</t>
+          <t>AC-11</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr"/>
@@ -5476,11 +5476,11 @@
       <c r="R67" s="5" t="inlineStr"/>
       <c r="S67" s="15" t="inlineStr">
         <is>
-          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="64" customHeight="1">
+          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="79" customHeight="1">
       <c r="A68" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5488,60 +5488,60 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>C-011</t>
+          <t>C-006</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>月中改定と予約の日割り</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
+【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・14 勤務データ 2026-06</t>
+          <t>14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
-5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従】
+6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>C-011.png</t>
+          <t>C-006.png</t>
         </is>
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
+          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
+          <t>人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
         </is>
       </c>
       <c r="K68" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>所定労働日割になっているか</t>
         </is>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>AC-13</t>
+          <t>AC-12 AC-04</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr"/>
@@ -5551,11 +5551,11 @@
       <c r="R68" s="5" t="inlineStr"/>
       <c r="S68" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="94" customHeight="1">
+          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="64" customHeight="1">
       <c r="A69" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5563,50 +5563,50 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-011</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>【前提】C-000 S-07 ／ data/14を投入
+【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績・14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F69" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績】
-判断7（暫定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。5/8のヘルプ人件費＝実績給与338,000×11h÷総労働172h＝21,616円で、計上先はS02。みなし労働時間差分＝172−(160＋20)＝−8h（未達はマイナス表示・減額なし＝判断8）</t>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>C-013.png</t>
+          <t>C-011.png</t>
         </is>
       </c>
       <c r="H69" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
+          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
+          <t>人件費実績 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
         </is>
       </c>
       <c r="K69" s="15" t="inlineStr">
         <is>
-          <t>深夜1.5倍とヘルプの按分単価</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="L69" s="15" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="M69" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-13</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr"/>
@@ -5626,11 +5626,11 @@
       <c r="R69" s="5" t="inlineStr"/>
       <c r="S69" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代＝基礎時給×1.5（判断7・暫定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・暫定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="79" customHeight="1">
+          <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="109" customHeight="1">
       <c r="A70" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5638,60 +5638,60 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-013</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8の】
-交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
+          <t>【確認場所：人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績】
+判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。5/8のヘルプ人件費＝実績給与338,000×11h÷総労働172h＝21,616円で、計上先はS02。みなし労働時間差分＝172−(160＋20)＝−8h（未達はマイナス表示・減額なし＝判断8）</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>C-017.png</t>
+          <t>C-013.png</t>
         </is>
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
+          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+          <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
         </is>
       </c>
       <c r="K70" s="15" t="inlineStr">
         <is>
-          <t>交通費が給与と別費目か</t>
+          <t>深夜1.5倍とヘルプの按分単価</t>
         </is>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr"/>
@@ -5701,11 +5701,11 @@
       <c r="R70" s="5" t="inlineStr"/>
       <c r="S70" s="15" t="inlineStr">
         <is>
-          <t>交通費は給与と別の独立費目（判断6・確定）。通勤交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="94" customHeight="1">
+          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="79" customHeight="1">
       <c r="A71" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5713,60 +5713,60 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-017</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>交通費の計上先</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07
-【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解】
-（a）5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
+          <t>【確認場所：人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8の】
+交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>C-008.png</t>
+          <t>C-017.png</t>
         </is>
       </c>
       <c r="H71" s="15" t="inlineStr">
         <is>
-          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
+          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+          <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
         <is>
-          <t>締め前後で差0円・解除後に再計算</t>
+          <t>交通費が給与と別費目か</t>
         </is>
       </c>
       <c r="L71" s="15" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>AC-16 AC-17</t>
+          <t>AC-15</t>
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr"/>
@@ -5776,72 +5776,72 @@
       <c r="R71" s="5" t="inlineStr"/>
       <c r="S71" s="15" t="inlineStr">
         <is>
-          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
+          <t>交通費は給与と別の独立費目（判断6・確定）。通勤交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
         </is>
       </c>
     </row>
     <row r="72" ht="94" customHeight="1">
-      <c r="A72" s="16" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C72" s="17" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="D72" s="17" t="inlineStr">
-        <is>
-          <t>【前提】S-01
-【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
-        </is>
-      </c>
-      <c r="E72" s="17" t="inlineStr">
-        <is>
-          <t>（追加のデータ投入なし）</t>
-        </is>
-      </c>
-      <c r="F72" s="17" t="inlineStr">
-        <is>
-          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
-①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
-        </is>
-      </c>
-      <c r="G72" s="16" t="inlineStr">
-        <is>
-          <t>R-01.png</t>
-        </is>
-      </c>
-      <c r="H72" s="17" t="inlineStr">
-        <is>
-          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>締めの前後で数字が動かないこと</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-07
+【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解】
+（a）5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>C-008.png</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="inlineStr">
+        <is>
+          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="17" t="inlineStr">
-        <is>
-          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
-        </is>
-      </c>
-      <c r="K72" s="17" t="inlineStr">
-        <is>
-          <t>適用日付と履歴がテーブルにあるか</t>
-        </is>
-      </c>
-      <c r="L72" s="17" t="inlineStr">
-        <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
-        </is>
-      </c>
-      <c r="M72" s="17" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47</t>
+      <c r="J72" s="15" t="inlineStr">
+        <is>
+          <t>人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+        </is>
+      </c>
+      <c r="K72" s="15" t="inlineStr">
+        <is>
+          <t>締め前後で差0円・解除後に再計算</t>
+        </is>
+      </c>
+      <c r="L72" s="15" t="inlineStr">
+        <is>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
+        </is>
+      </c>
+      <c r="M72" s="15" t="inlineStr">
+        <is>
+          <t>AC-16 AC-17</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr"/>
@@ -5849,13 +5849,13 @@
       <c r="P72" s="6" t="inlineStr"/>
       <c r="Q72" s="5" t="inlineStr"/>
       <c r="R72" s="5" t="inlineStr"/>
-      <c r="S72" s="17" t="inlineStr">
-        <is>
-          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="79" customHeight="1">
+      <c r="S72" s="15" t="inlineStr">
+        <is>
+          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="94" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -5863,18 +5863,18 @@
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>締めの実装レビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="D73" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
+【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
         </is>
       </c>
       <c r="E73" s="17" t="inlineStr">
@@ -5884,39 +5884,39 @@
       </c>
       <c r="F73" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
-①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
+          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
+①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
         </is>
       </c>
       <c r="G73" s="16" t="inlineStr">
         <is>
-          <t>R-02.png</t>
+          <t>R-01.png</t>
         </is>
       </c>
       <c r="H73" s="17" t="inlineStr">
         <is>
-          <t>締めAPIのコードとスコープ判定箇所</t>
+          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
+          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
       </c>
       <c r="K73" s="17" t="inlineStr">
         <is>
-          <t>APIでも店長が締められないか</t>
+          <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
       <c r="L73" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M73" s="17" t="inlineStr">
         <is>
-          <t>AC-16 AC-41</t>
+          <t>AC-07 AC-40 AC-47</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr"/>
@@ -5926,11 +5926,11 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="17" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="109" customHeight="1">
+          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="79" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -5938,18 +5938,18 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>入力検証とトランザクションのレビュー</t>
+          <t>締めの実装レビュー</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
+【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
@@ -5959,39 +5959,39 @@
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
-①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
+          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
+①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
         </is>
       </c>
       <c r="G74" s="16" t="inlineStr">
         <is>
-          <t>R-03.png</t>
+          <t>R-02.png</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
+          <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
+          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
       </c>
       <c r="K74" s="17" t="inlineStr">
         <is>
-          <t>APIを直接呼んでも弾かれるか</t>
+          <t>APIでも店長が締められないか</t>
         </is>
       </c>
       <c r="L74" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 設定が保存できません</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M74" s="17" t="inlineStr">
         <is>
-          <t>AC-23 AC-42 AC-43</t>
+          <t>AC-16 AC-41</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr"/>
@@ -6001,11 +6001,11 @@
       <c r="R74" s="5" t="inlineStr"/>
       <c r="S74" s="17" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="79" customHeight="1">
+          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="109" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6013,18 +6013,18 @@
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの共有レビュー</t>
+          <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
       <c r="D75" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
       <c r="E75" s="17" t="inlineStr">
@@ -6034,39 +6034,39 @@
       </c>
       <c r="F75" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
-同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
+          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
+①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
         </is>
       </c>
       <c r="G75" s="16" t="inlineStr">
         <is>
-          <t>R-04.png</t>
+          <t>R-03.png</t>
         </is>
       </c>
       <c r="H75" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
+          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
+          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
       </c>
       <c r="K75" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックが1箇所か</t>
+          <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
       <c r="L75" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
       <c r="M75" s="17" t="inlineStr">
         <is>
-          <t>AC-35 AC-11</t>
+          <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
@@ -6076,11 +6076,11 @@
       <c r="R75" s="5" t="inlineStr"/>
       <c r="S75" s="17" t="inlineStr">
         <is>
-          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="64" customHeight="1">
+          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="79" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6088,18 +6088,18 @@
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>計算ロジックの共有レビュー</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込の列解決の実装を提示してもらう</t>
+【操作】人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -6109,39 +6109,39 @@
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
-CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
+          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
+同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
         </is>
       </c>
       <c r="G76" s="16" t="inlineStr">
         <is>
-          <t>R-05.png</t>
+          <t>R-04.png</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
+          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
+          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
         </is>
       </c>
       <c r="K76" s="17" t="inlineStr">
         <is>
-          <t>列名がコードに埋まっていないか</t>
+          <t>計算ロジックが1箇所か</t>
         </is>
       </c>
       <c r="L76" s="17" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M76" s="17" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-35 AC-11</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr"/>
@@ -6151,11 +6151,11 @@
       <c r="R76" s="5" t="inlineStr"/>
       <c r="S76" s="17" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="79" customHeight="1">
+          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="64" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6163,18 +6163,18 @@
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>設定更新処理の共通化レビュー</t>
+          <t>列マッピングの実装レビュー</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+【操作】取込の列解決の実装を提示してもらう</t>
         </is>
       </c>
       <c r="E77" s="17" t="inlineStr">
@@ -6184,39 +6184,39 @@
       </c>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
-設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
+CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
       <c r="G77" s="16" t="inlineStr">
         <is>
-          <t>R-06.png</t>
+          <t>R-05.png</t>
         </is>
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
         </is>
       </c>
       <c r="K77" s="17" t="inlineStr">
         <is>
-          <t>2つの入口で更新処理が共通か</t>
+          <t>列名がコードに埋まっていないか</t>
         </is>
       </c>
       <c r="L77" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M77" s="17" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-22 AC-24</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
@@ -6226,17 +6226,92 @@
       <c r="R77" s="5" t="inlineStr"/>
       <c r="S77" s="17" t="inlineStr">
         <is>
+          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="79" customHeight="1">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
+設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="G78" s="16" t="inlineStr">
+        <is>
+          <t>R-06.png</t>
+        </is>
+      </c>
+      <c r="H78" s="17" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr"/>
+      <c r="J78" s="17" t="inlineStr">
+        <is>
+          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+        </is>
+      </c>
+      <c r="K78" s="17" t="inlineStr">
+        <is>
+          <t>2つの入口で更新処理が共通か</t>
+        </is>
+      </c>
+      <c r="L78" s="17" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="M78" s="17" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="N78" s="5" t="inlineStr"/>
+      <c r="O78" s="5" t="inlineStr"/>
+      <c r="P78" s="6" t="inlineStr"/>
+      <c r="Q78" s="5" t="inlineStr"/>
+      <c r="R78" s="5" t="inlineStr"/>
+      <c r="S78" s="17" t="inlineStr">
+        <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S77"/>
+  <autoFilter ref="A2:S78"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3:O77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S78"/>
+  <dimension ref="A1:S79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証65ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
+          <t>確かめる手順（準備11行＋検証66ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
 実施順を変えてはいけない箇所：①T-A08（勤怠取込）→T-S03（締め）　②T-S03→T-S04・T-D07→T-S05（この3件は締め済みでしか確認できない）　③C-000（初期化）は計算の先頭　④C-008は計算の最後（2026-05のEMP-001を352,286円に変えるためC-013・C-017が合わなくなる）　⑤T-N02の前にdata/02を再投入　⑥削除はEMP-012（T-L10）とEMP-004（T-D08）だけ
 列の使い方：使用する検証データ＝この検証で投入・使用するdataファイル／期待値＝先頭の【確認場所】でどの画面を見て合否を出すかを示し、続けて合格の基準を書いている／スクショ（撮るもの）＝何が写っていれば証拠になるか／スクショ貼付欄＝撮った画像をこの列に貼る／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めて合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを決める
 色：緑＝使う検証データ　青＝画面　橙＝スクショの指示　紫＝ヘルプ・受入条件との対応　黄＝当日の記入欄。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
@@ -2343,13 +2343,13 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>詳細の給与実績</t>
+          <t>詳細の給与実績（ダイジェスト）</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】給与実績セクションで 月次タブ（概算⇄実績・年フィルタ）→ 日次タブ（月フィルタ）→ 各タブでCSVエクスポート</t>
+【操作】従業員詳細の給与実績セクションを開き、月次実績・日次実績のタブを切り替える。年フィルタ・給与計算モード・CSVエクスポートが無いことを確認し、右上「すべての実績」を押す</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -2359,8 +2359,8 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細 → 給与実績セクション】
-月次17列（年月〜深夜残業代＋交通費＋総支給額）／日次14列。個人向けに列を絞った構成で、人件費実績（26列/21列）とは別。フィルタで期間が絞られる。表示中の内容がBOM付きCSVで出力される</t>
+          <t>【確認場所：従業員詳細 → 給与実績】
+月次は直近3か月が実績モードで表示される。絞り込みとCSVエクスポートは無い（詳細に残っている数=0件）。「すべての実績」で給与実績一覧が開き、EMP-001で絞り込まれている</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -2370,18 +2370,18 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>月次タブ（概算／実績の両方）と日次タブ／出力したCSVをExcelで開いた画面</t>
+          <t>給与実績セクション（月次・日次の両タブ／絞り込みとCSVボタンが無いこと）／「すべての実績」で開いた給与実績一覧</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 給与実績セクション … 月次タブ（概算⇄実績の切替・年フィルタ）／日次タブ（月フィルタ）／各タブのCSVエクスポート</t>
+          <t>従業員詳細 → 給与実績セクション … 右上「すべての実績」→ 給与実績一覧</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>タブ切替とCSVの中身が変わるか</t>
+          <t>詳細がダイジェストに絞られているか</t>
         </is>
       </c>
       <c r="L26" s="13" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="M26" s="13" t="inlineStr">
         <is>
-          <t>AC-35 AC-36</t>
+          <t>AC-54</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr"/>
@@ -2401,72 +2401,72 @@
       <c r="R26" s="5" t="inlineStr"/>
       <c r="S26" s="8" t="inlineStr">
         <is>
-          <t>計算：個人単位でも同じ数字／入出力：画面の内容と一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="64" customHeight="1">
+          <t>画面：通して見る場所がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="79" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>詳細</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>T-D08</t>
+          <t>T-P01</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>詳細の削除・戻る</t>
+          <t>給与実績一覧の絞り込みと出力</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】EMP-004（山本 健／実績データにも取込CSVにも含まれない）の詳細を開き「従業員削除」→（a）キャンセル →（b）実行、（c）別の従業員で「一覧へ戻る」</t>
+          <t>【前提】S-05
+【操作】給与実績一覧で（a）年月を2024-10〜2024-12に指定 →（b）年をまたぐ範囲（2024-10〜2025-01）に変更 →（c）給与計算モードを概算⇄実績で切替 →（d）日次実績タブに切り替え →（e）CSVエクスポート</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細】
-（a）削除されず件数が変わらない （b）確認のあと削除される （c）一覧へ戻る（保存されない）</t>
+          <t>【確認場所：給与実績一覧】
+（a・b）指定した期間の行だけが表示され、年をまたいでも表示される（またげない=0件）（c）月次では列が増減する（d）日次タブでは給与計算モードが表示されない（e）出力した行数＝画面の行数（差0件）。Excelで開いて文字化け=0件</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>T-D08.png</t>
+          <t>T-P01.png</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>削除の確認モーダル／実行後の一覧（行が消えたこと）</t>
+          <t>年またぎの期間で表示した一覧／概算と実績の両モード／日次タブ（モードが無いこと）／出力したCSVをExcelで開いた画面</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 … 下部「従業員削除」→ 確認モーダル／「一覧へ戻る」→ 従業員一覧</t>
+          <t>給与実績一覧（従業員詳細 →「すべての実績」）… 年月の開始・終了、給与計算モード、月次実績／日次実績タブ、右上CSVエクスポート</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>キャンセルで消えない／実行で消えるか</t>
+          <t>年をまたいで通して見られるか／表示どおり出力されるか</t>
         </is>
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員を探す・削除する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M27" s="13" t="inlineStr">
         <is>
-          <t>AC-34 AC-30</t>
+          <t>AC-54 AC-36</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr"/>
@@ -2476,11 +2476,11 @@
       <c r="R27" s="5" t="inlineStr"/>
       <c r="S27" s="8" t="inlineStr">
         <is>
-          <t>データ保全：消える操作は確認を経る／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="109" customHeight="1">
+          <t>画面：通して見る場所がある／入出力：画面の内容と一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="64" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
           <t>詳細</t>
@@ -2488,60 +2488,60 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>T-D11</t>
+          <t>T-D08</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>設定変更履歴の表示ルール</t>
+          <t>詳細の削除・戻る</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-05
-【操作】EMP-001の詳細を開き、（a）並び順とステータス列の位置を確認 →（b）単位給与額を380,000に変更し適用日付＝翌々月1日で保存 →（c）保存後の履歴の最上部と強調を確認 →（d）右上「すべての履歴」を押す</t>
+          <t>【前提】S-04
+【操作】EMP-004（山本 健／実績データにも取込CSVにも含まれない）の詳細を開き「従業員削除」→（a）キャンセル →（b）実行、（c）別の従業員で「一覧へ戻る」</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）04 設定変更履歴</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細 → 設定変更履歴】
-（a）並びは変更反映日時の降順で、予約中が最上部。ステータスは変更反映日時の次（2列目）にあり横スクロールなしで見える。表示は直近3件（b・c）保存した行が最上部に増え、1つ古い行と値が違う項目（単位給与額）だけが強調される。強調の過不足=0件（d）従業員設定履歴が開き、EMP-001で絞り込まれた状態になる（絞り込みなしでの遷移=0件）</t>
+          <t>【確認場所：従業員詳細】
+（a）削除されず件数が変わらない （b）確認のあと削除される （c）一覧へ戻る（保存されない）</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>T-D11.png</t>
+          <t>T-D08.png</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>保存前後の履歴セクション2枚（並び順とステータス列の位置が分かる範囲）／強調された項目／「すべての履歴」で開いた従業員設定履歴（絞り込み条件が見える状態）</t>
+          <t>削除の確認モーダル／実行後の一覧（行が消えたこと）</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 設定変更履歴セクション … 右上「すべての履歴」→ 従業員設定履歴（EMP-001で絞り込み済み）</t>
+          <t>従業員詳細 … 下部「従業員削除」→ 確認モーダル／「一覧へ戻る」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>保存した行が最上部に来るか／変更点だけ強調されるか</t>
+          <t>キャンセルで消えない／実行で消えるか</t>
         </is>
       </c>
       <c r="L28" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
       <c r="M28" s="13" t="inlineStr">
         <is>
-          <t>AC-52 AC-53</t>
+          <t>AC-34 AC-30</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr"/>
@@ -2551,72 +2551,72 @@
       <c r="R28" s="5" t="inlineStr"/>
       <c r="S28" s="8" t="inlineStr">
         <is>
-          <t>画面：保存できたか確かめられる／画面：変更点が読み取れる</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
+          <t>データ保全：消える操作は確認を経る／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="109" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>詳細</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>T-H01</t>
+          <t>T-D11</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>履歴の追記と過去行の不変</t>
+          <t>設定変更履歴の表示ルール</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 ／ 変更前の履歴をCSV出力しておく
-【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
+          <t>【前提】S-04 S-05
+【操作】EMP-001の詳細を開き、（a）並び順とステータス列の位置を確認 →（b）単位給与額を380,000に変更し適用日付＝翌々月1日で保存 →（c）保存後の履歴の最上部と強調を確認 →（d）右上「すべての履歴」を押す</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）04 設定変更履歴</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員設定履歴】
-履歴が1行増える。既存行の値の差分＝0</t>
+          <t>【確認場所：従業員詳細 → 設定変更履歴】
+（a）並びは変更反映日時の降順で、予約中が最上部。ステータスは変更反映日時の次（2列目）にあり横スクロールなしで見える。表示は直近3件（b・c）保存した行が最上部に増え、1つ古い行と値が違う項目（単位給与額）だけが強調される。強調の過不足=0件（d）従業員設定履歴が開き、EMP-001で絞り込まれた状態になる（絞り込みなしでの遷移=0件）</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>T-H01.png</t>
+          <t>T-D11.png</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
+          <t>保存前後の履歴セクション2枚（並び順とステータス列の位置が分かる範囲）／強調された項目／「すべての履歴」で開いた従業員設定履歴（絞り込み条件が見える状態）</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>従業員設定履歴 … 変更前後の行（既存行が書き換わらないこと）</t>
+          <t>従業員詳細 → 設定変更履歴セクション … 右上「すべての履歴」→ 従業員設定履歴（EMP-001で絞り込み済み）</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>既存行が書き換わらないか</t>
+          <t>保存した行が最上部に来るか／変更点だけ強調されるか</t>
         </is>
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
       <c r="M29" s="13" t="inlineStr">
         <is>
-          <t>AC-07</t>
+          <t>AC-52 AC-53</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr"/>
@@ -2626,11 +2626,11 @@
       <c r="R29" s="5" t="inlineStr"/>
       <c r="S29" s="8" t="inlineStr">
         <is>
-          <t>原則①：過去は不変</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="79" customHeight="1">
+          <t>画面：保存できたか確かめられる／画面：変更点が読み取れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2638,18 +2638,18 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>T-H02</t>
+          <t>T-H01</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>記録の内容</t>
+          <t>履歴の追記と過去行の不変</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 T-D04実施済み
-【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
+          <t>【前提】S-05 ／ 変更前の履歴をCSV出力しておく
+【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -2660,28 +2660,28 @@
       <c r="F30" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員設定履歴】
-①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
+履歴が1行増える。既存行の値の差分＝0</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>T-H02.png</t>
+          <t>T-H01.png</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
+          <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>従業員設定履歴 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
+          <t>従業員設定履歴 … 変更前後の行（既存行が書き換わらないこと）</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>2つの日時が別で記録されるか</t>
+          <t>既存行が書き換わらないか</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="M30" s="13" t="inlineStr">
         <is>
-          <t>AC-08 AC-09</t>
+          <t>AC-07</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr"/>
@@ -2701,11 +2701,11 @@
       <c r="R30" s="5" t="inlineStr"/>
       <c r="S30" s="8" t="inlineStr">
         <is>
-          <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="94" customHeight="1">
+          <t>原則①：過去は不変</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="79" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2713,18 +2713,18 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>T-H04</t>
+          <t>T-H02</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>履歴の絞り込み・出力・遷移</t>
+          <t>記録の内容</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
+          <t>【前提】S-05 T-D04実施済み
+【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -2735,28 +2735,28 @@
       <c r="F31" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員設定履歴】
-店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
+①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>T-H04.png</t>
+          <t>T-H02.png</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
+          <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>従業員設定履歴 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
+          <t>従業員設定履歴 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>絞り込み後の行だけ出力されるか</t>
+          <t>2つの日時が別で記録されるか</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>AC-33 AC-36 AC-30</t>
+          <t>AC-08 AC-09</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr"/>
@@ -2776,30 +2776,30 @@
       <c r="R31" s="5" t="inlineStr"/>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="124" customHeight="1">
+          <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="94" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>履歴</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>T-A02</t>
+          <t>T-H04</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>月別実績の表示と切替</t>
+          <t>履歴の絞り込み・出力・遷移</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
+【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2809,39 +2809,39 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
-全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない</t>
+          <t>【確認場所：従業員設定履歴】
+店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>T-A02.png</t>
+          <t>T-H04.png</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
+          <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
+          <t>従業員設定履歴 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>モード切替で列が増減するか</t>
+          <t>絞り込み後の行だけ出力されるか</t>
         </is>
       </c>
       <c r="L32" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M32" s="13" t="inlineStr">
         <is>
-          <t>AC-10 AC-31</t>
+          <t>AC-33 AC-36 AC-30</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr"/>
@@ -2851,11 +2851,11 @@
       <c r="R32" s="5" t="inlineStr"/>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>計算：算式どおりの金額／画面：状態が漏れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="64" customHeight="1">
+          <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="124" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -2863,18 +2863,18 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>T-A09</t>
+          <t>T-A02</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>人件費実績からの設定編集</t>
+          <t>月別実績の表示と切替</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】人件費実績で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
+【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2884,39 +2884,39 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　行の「従業員設定」】
-モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>T-A09.png</t>
+          <t>T-A02.png</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>設定編集モーダル（項目が見える状態）／更新保存後の人件費実績／従業員詳細の設定変更履歴に行が増えたこと</t>
+          <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 人件費実績／確認は従業員詳細の設定変更履歴</t>
+          <t>人件費実績 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>モーダル編集でも履歴が残るか</t>
+          <t>モード切替で列が増減するか</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-10 AC-31</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
@@ -2926,11 +2926,11 @@
       <c r="R33" s="5" t="inlineStr"/>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>原則①：どの入口から編集しても履歴が残る</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="109" customHeight="1">
+          <t>計算：算式どおりの金額／画面：状態が漏れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="64" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -2938,18 +2938,18 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>T-A05</t>
+          <t>T-A09</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>日別実績の表示</t>
+          <t>人件費実績からの設定編集</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
+【操作】人件費実績で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2959,39 +2959,39 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 日別実績タブ】
-全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
+          <t>【確認場所：人件費実績　→　行の「従業員設定」】
+モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>T-A05.png</t>
+          <t>T-A09.png</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
+          <t>設定編集モーダル（項目が見える状態）／更新保存後の人件費実績／従業員詳細の設定変更履歴に行が増えたこと</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
+          <t>人件費実績 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 人件費実績／確認は従業員詳細の設定変更履歴</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>日別に概算モードが無いか</t>
+          <t>モーダル編集でも履歴が残るか</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
       <c r="M34" s="13" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>AC-49</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr"/>
@@ -3001,11 +3001,11 @@
       <c r="R34" s="5" t="inlineStr"/>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>計算：算式どおりの金額</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="64" customHeight="1">
+          <t>原則①：どの入口から編集しても履歴が残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="109" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -3013,18 +3013,18 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>T-A07</t>
+          <t>T-A05</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>実績のCSVエクスポート</t>
+          <t>日別実績の表示</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
+【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -3034,39 +3034,39 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績】
-出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
+          <t>【確認場所：人件費実績 → 日別実績タブ】
+全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>T-A07.png</t>
+          <t>T-A05.png</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
+          <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
+          <t>人件費実績 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>表示中の内容が出力されるか</t>
+          <t>日別に概算モードが無いか</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>AC-36</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
       <c r="R35" s="5" t="inlineStr"/>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>入出力：画面の内容と一致</t>
+          <t>計算：算式どおりの金額</t>
         </is>
       </c>
     </row>
@@ -3088,18 +3088,18 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>T-A08</t>
+          <t>T-A07</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>勤怠実績の取込</t>
+          <t>実績のCSVエクスポート</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-08
-【操作】人件費実績の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
+          <t>【前提】S-05
+【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -3109,39 +3109,39 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
-「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
+          <t>【確認場所：人件費実績】
+出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>T-A08.png</t>
+          <t>T-A07.png</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
+          <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
+          <t>人件費実績 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>進捗が出て他操作を受け付けないか</t>
+          <t>表示中の内容が出力されるか</t>
         </is>
       </c>
       <c r="L36" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M36" s="13" t="inlineStr">
         <is>
-          <t>AC-48</t>
+          <t>AC-36</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr"/>
@@ -3151,62 +3151,62 @@
       <c r="R36" s="5" t="inlineStr"/>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>入出力：勤怠実績を取り込める</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="60" customHeight="1">
+          <t>入出力：画面の内容と一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="64" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>締め</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>T-S01</t>
+          <t>T-A08</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>締めボタンの表示条件</t>
+          <t>勤怠実績の取込</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-08
-【操作】月別実績タブと日別実績タブを順に開く</t>
+          <t>【前提】S-05 S-08
+【操作】人件費実績の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績】
-月別のみ「2026-05 締め」が表示。日別には表示されない</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>T-S01.png</t>
+          <t>T-A08.png</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
+          <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
+          <t>人件費実績 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>締めが月別タブにだけ出るか</t>
+          <t>進捗が出て他操作を受け付けないか</t>
         </is>
       </c>
       <c r="L37" s="13" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="M37" s="13" t="inlineStr">
         <is>
-          <t>AC-18</t>
+          <t>AC-48</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr"/>
@@ -3226,11 +3226,11 @@
       <c r="R37" s="5" t="inlineStr"/>
       <c r="S37" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めの単位は月</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="64" customHeight="1">
+          <t>入出力：勤怠実績を取り込める</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3238,18 +3238,18 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>T-S03</t>
+          <t>T-S01</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>締めの実行</t>
+          <t>締めボタンの表示条件</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06 S-08
-【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
+          <t>【前提】S-08
+【操作】月別実績タブと日別実績タブを順に開く</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -3259,29 +3259,29 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
-「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
+          <t>【確認場所：人件費実績】
+月別のみ「2026-05 締め」が表示。日別には表示されない</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>T-S03.png</t>
+          <t>T-S01.png</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
+          <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
+          <t>人件費実績 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>確認モーダルを経て締まるか</t>
+          <t>締めが月別タブにだけ出るか</t>
         </is>
       </c>
       <c r="L38" s="13" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="M38" s="13" t="inlineStr">
         <is>
-          <t>AC-16 AC-19 AC-32</t>
+          <t>AC-18</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr"/>
@@ -3301,11 +3301,11 @@
       <c r="R38" s="5" t="inlineStr"/>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="60" customHeight="1">
+          <t>原則②：締めの単位は月</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="64" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3313,18 +3313,18 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>T-S04</t>
+          <t>T-S03</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>締め後は編集できない</t>
+          <t>締めの実行</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み
-【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
+          <t>【前提】S-06 S-08
+【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -3334,39 +3334,39 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績】
-編集できない（または反映されない）</t>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>T-S04.png</t>
+          <t>T-S03.png</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
+          <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
+          <t>人件費実績 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>締め後に金額が動かないか</t>
+          <t>確認モーダルを経て締まるか</t>
         </is>
       </c>
       <c r="L39" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M39" s="13" t="inlineStr">
         <is>
-          <t>AC-16</t>
+          <t>AC-16 AC-19 AC-32</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr"/>
@@ -3376,7 +3376,7 @@
       <c r="R39" s="5" t="inlineStr"/>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない</t>
+          <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
         </is>
       </c>
     </row>
@@ -3388,18 +3388,18 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>T-D07</t>
+          <t>T-S04</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>締め済み期間への遡及</t>
+          <t>締め後は編集できない</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み S-07
-【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
+          <t>【前提】T-S03実施済み
+【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -3409,39 +3409,39 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細】
-締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
+          <t>【確認場所：人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績】
+編集できない（または反映されない）</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>T-D07.png</t>
+          <t>T-S04.png</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
+          <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
+          <t>人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>警告が出て反映されないか</t>
+          <t>締め後に金額が動かないか</t>
         </is>
       </c>
       <c r="L40" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="M40" s="13" t="inlineStr">
         <is>
-          <t>AC-20</t>
+          <t>AC-16</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr"/>
@@ -3451,11 +3451,11 @@
       <c r="R40" s="5" t="inlineStr"/>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>原則②：遡及は黙って捨てない</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="64" customHeight="1">
+          <t>原則②：締めたら動かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3463,18 +3463,18 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>T-S05</t>
+          <t>T-D07</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>締めの解除</t>
+          <t>締め済み期間への遡及</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み
-【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
+          <t>【前提】T-S03実施済み S-07
+【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -3484,39 +3484,39 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
-「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
+          <t>【確認場所：従業員詳細】
+締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>T-S05.png</t>
+          <t>T-D07.png</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
+          <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
+          <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>解除で再計算されるか</t>
+          <t>警告が出て反映されないか</t>
         </is>
       </c>
       <c r="L41" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
       <c r="M41" s="13" t="inlineStr">
         <is>
-          <t>AC-19</t>
+          <t>AC-20</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr"/>
@@ -3526,7 +3526,7 @@
       <c r="R41" s="5" t="inlineStr"/>
       <c r="S41" s="8" t="inlineStr">
         <is>
-          <t>原則②：確定操作は確認を経る</t>
+          <t>原則②：遡及は黙って捨てない</t>
         </is>
       </c>
     </row>
@@ -3538,18 +3538,18 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>T-S07</t>
+          <t>T-S05</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>締めの実行権限</t>
+          <t>締めの解除</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-10 S-08
-【操作】店長スコープのアカウントでログインし、人件費実績を開いて締めを試みる</t>
+          <t>【前提】T-S03実施済み
+【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -3559,39 +3559,39 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ（店長スコープでログイン）】
-締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>T-S07.png</t>
+          <t>T-S05.png</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>店長スコープでの人件費実績（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
+          <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
+          <t>人件費実績 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
         </is>
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>店長が締められないか</t>
+          <t>解除で再計算されるか</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="M42" s="13" t="inlineStr">
         <is>
-          <t>AC-41</t>
+          <t>AC-19</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr"/>
@@ -3601,30 +3601,30 @@
       <c r="R42" s="5" t="inlineStr"/>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="79" customHeight="1">
+          <t>原則②：確定操作は確認を経る</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="64" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>取込</t>
+          <t>締め</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>T-I02</t>
+          <t>T-S07</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>テンプレートのDLと画面</t>
+          <t>締めの実行権限</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
+          <t>【前提】S-10 S-08
+【操作】店長スコープのアカウントでログインし、人件費実績を開いて締めを試みる</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -3634,39 +3634,39 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ（店長スコープでログイン）】
+締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>T-I02.png</t>
+          <t>T-S07.png</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
+          <t>店長スコープでの人件費実績（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
+          <t>人件費実績 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>テンプレートの列とBOM</t>
+          <t>店長が締められないか</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ はじめて設定する</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M43" s="13" t="inlineStr">
         <is>
-          <t>AC-21 AC-30</t>
+          <t>AC-41</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr"/>
@@ -3676,11 +3676,11 @@
       <c r="R43" s="5" t="inlineStr"/>
       <c r="S43" s="8" t="inlineStr">
         <is>
-          <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="64" customHeight="1">
+          <t>原則②：締めは会社スコープのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="79" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3688,50 +3688,50 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>T-I03</t>
+          <t>T-I02</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>King of Time形式の取込</t>
+          <t>テンプレートのDLと画面</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-06
-【操作】データ種類＝King of Time を選び data/07（従業員設定・3行）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
+          <t>【前提】S-01
+【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート】
-07は3行すべて取り込まれ、EMP-001=340,000・EMP-005=360,000に更新、EMP-013は新規追加。10は給与設定（ヘルプ先交通費 S02:700;S03:900 の記法を含む）が反映される</t>
+従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>T-I03.png</t>
+          <t>T-I02.png</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
+          <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
+          <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>3行が更新・追加されるか</t>
+          <t>テンプレートの列とBOM</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>AC-21</t>
+          <t>AC-21 AC-30</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr"/>
@@ -3751,11 +3751,11 @@
       <c r="R44" s="5" t="inlineStr"/>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t>入出力：導入を止めない</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="60" customHeight="1">
+          <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="64" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3763,50 +3763,50 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>T-I04</t>
+          <t>T-I03</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>ジョブカン形式（表記ゆれ）の取込</t>
+          <t>King of Time形式の取込</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】データ種類＝ジョブカン を選び data/08（3行）をD&amp;D → 登録</t>
+【操作】データ種類＝King of Time を選び data/07（従業員設定・3行）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>08 取込CSV ジョブカン</t>
+          <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート】
-3行すべて取り込まれる（EMP-003=1,250・EMP-010=1,300・EMP-014は新規）</t>
+07は3行すべて取り込まれ、EMP-001=340,000・EMP-005=360,000に更新、EMP-013は新規追加。10は給与設定（ヘルプ先交通費 S02:700;S03:900 の記法を含む）が反映される</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>T-I04.png</t>
+          <t>T-I03.png</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
+          <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
+          <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>表記ゆれを吸収できるか</t>
+          <t>3行が更新・追加されるか</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="M45" s="13" t="inlineStr">
         <is>
-          <t>AC-22</t>
+          <t>AC-21</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr"/>
@@ -3826,7 +3826,7 @@
       <c r="R45" s="5" t="inlineStr"/>
       <c r="S45" s="8" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収</t>
+          <t>入出力：導入を止めない</t>
         </is>
       </c>
     </row>
@@ -3838,60 +3838,60 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>T-I05</t>
+          <t>T-I04</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>異常系データの検出</t>
+          <t>ジョブカン形式（表記ゆれ）の取込</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】data/09（4行）をD&amp;D → 登録</t>
+【操作】データ種類＝ジョブカン を選び data/08（3行）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>08 取込CSV ジョブカン</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート】
-4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
+3行すべて取り込まれる（EMP-003=1,250・EMP-010=1,300・EMP-014は新規）</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>T-I05.png</t>
+          <t>T-I04.png</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
+          <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
+          <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>4種の異常を行ごとに検出するか</t>
+          <t>表記ゆれを吸収できるか</t>
         </is>
       </c>
       <c r="L46" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
+          <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
       <c r="M46" s="13" t="inlineStr">
         <is>
-          <t>AC-23</t>
+          <t>AC-22</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr"/>
@@ -3901,7 +3901,7 @@
       <c r="R46" s="5" t="inlineStr"/>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない</t>
+          <t>入出力：表記ゆれを吸収</t>
         </is>
       </c>
     </row>
@@ -3913,50 +3913,50 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>T-I17</t>
+          <t>T-I05</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>二重登録の防止</t>
+          <t>異常系データの検出</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】（a）data/07を2回続けて取り込む （b）data/19（EMP-002が2行・単位給与額が異なる）を取り込む</t>
+【操作】data/09（4行）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート】
-（a）2回目は更新となり件数が増えない （b）重複行がエラーとして検出される（両方が登録されない）</t>
+4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>T-I17.png</t>
+          <t>T-I05.png</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
+          <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
+          <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>二重登録されないか</t>
+          <t>4種の異常を行ごとに検出するか</t>
         </is>
       </c>
       <c r="L47" s="13" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="M47" s="13" t="inlineStr">
         <is>
-          <t>AC-40</t>
+          <t>AC-23</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr"/>
@@ -3976,11 +3976,11 @@
       <c r="R47" s="5" t="inlineStr"/>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>データ保全：二重登録を防ぐ</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="94" customHeight="1">
+          <t>データ保全：不正値を入れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3988,50 +3988,50 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>T-I18</t>
+          <t>T-I17</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>取込が途中で失敗したときの扱い</t>
+          <t>二重登録の防止</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
+【操作】（a）data/07を2回続けて取り込む （b）data/19（EMP-002が2行・単位給与額が異なる）を取り込む</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録】
-中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
+          <t>【確認場所：設定インポート】
+（a）2回目は更新となり件数が増えない （b）重複行がエラーとして検出される（両方が登録されない）</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>T-I18.png</t>
+          <t>T-I17.png</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
+          <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録されていないこと）</t>
+          <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>部分登録が残らないか</t>
+          <t>二重登録されないか</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="M48" s="13" t="inlineStr">
         <is>
-          <t>AC-42</t>
+          <t>AC-40</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr"/>
@@ -4051,11 +4051,11 @@
       <c r="R48" s="5" t="inlineStr"/>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>データ保全：中途半端に残さない</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="64" customHeight="1">
+          <t>データ保全：二重登録を防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="94" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4063,60 +4063,60 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>T-I11</t>
+          <t>T-I18</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>CSV位置合わせ設定</t>
+          <t>取込が途中で失敗したときの扱い</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06
-【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
+          <t>【前提】S-04 S-06
+【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>11 取込CSV 説明行あり</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-余計な行が無視され、3行が正しく取り込まれる</t>
+          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録】
+中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>T-I11.png</t>
+          <t>T-I18.png</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
+          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
+          <t>設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録されていないこと）</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>説明行を飛ばして取り込めるか</t>
+          <t>部分登録が残らないか</t>
         </is>
       </c>
       <c r="L49" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>AC-37</t>
+          <t>AC-42</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
@@ -4126,11 +4126,11 @@
       <c r="R49" s="5" t="inlineStr"/>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>入出力：現場のCSVをそのまま使える</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="94" customHeight="1">
+          <t>データ保全：中途半端に残さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="64" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4138,50 +4138,50 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>T-I09</t>
+          <t>T-I11</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>CSV位置合わせ設定</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】「列マッピングテンプレート管理」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
+【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>11 取込CSV 説明行あり</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート管理」】
-テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
+          <t>【確認場所：設定インポート】
+余計な行が無視され、3行が正しく取り込まれる</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>T-I09.png</t>
+          <t>T-I11.png</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
+          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>設定インポート → ツールバー「列マッピングテンプレート管理」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
+          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>テンプレの登録・編集・削除と往復</t>
+          <t>説明行を飛ばして取り込めるか</t>
         </is>
       </c>
       <c r="L50" s="13" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="M50" s="13" t="inlineStr">
         <is>
-          <t>AC-24 AC-38 AC-30</t>
+          <t>AC-37</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr"/>
@@ -4201,11 +4201,11 @@
       <c r="R50" s="5" t="inlineStr"/>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="79" customHeight="1">
+          <t>入出力：現場のCSVをそのまま使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="94" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4213,50 +4213,50 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>T-I19</t>
+          <t>T-I09</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>マッピング表の一括登録</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
+【操作】「列マッピングテンプレート管理」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>18 列マッピング表テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：列マッピングテンプレート】
-テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
+          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート管理」】
+テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>T-I19.png</t>
+          <t>T-I09.png</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
+          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
+          <t>設定インポート → ツールバー「列マッピングテンプレート管理」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>一括登録と10MB超の扱い</t>
+          <t>テンプレの登録・編集・削除と往復</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="M51" s="13" t="inlineStr">
         <is>
-          <t>AC-51</t>
+          <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr"/>
@@ -4276,72 +4276,72 @@
       <c r="R51" s="5" t="inlineStr"/>
       <c r="S51" s="8" t="inlineStr">
         <is>
-          <t>入出力：マッピングの一括運用</t>
+          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="52" ht="79" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>取込</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>T-E04</t>
+          <t>T-I19</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>設定のエクスポート</t>
+          <t>マッピング表の一括登録</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
+          <t>【前提】S-06
+【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>18 列マッピング表テンプレ</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
-専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
+          <t>【確認場所：列マッピングテンプレート】
+テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>T-E04.png</t>
+          <t>T-I19.png</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
+          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
+          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
         </is>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>選んだ項目だけ・対象数だけ出るか</t>
+          <t>一括登録と10MB超の扱い</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M52" s="13" t="inlineStr">
         <is>
-          <t>AC-25 AC-26 AC-30</t>
+          <t>AC-51</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr"/>
@@ -4351,11 +4351,11 @@
       <c r="R52" s="5" t="inlineStr"/>
       <c r="S52" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="64" customHeight="1">
+          <t>入出力：マッピングの一括運用</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="79" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4363,50 +4363,50 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>T-E09</t>
+          <t>T-E04</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>実績・同時のエクスポート</t>
+          <t>設定のエクスポート</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
+          <t>【前提】S-04
+【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート】
-実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
+          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
+専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>T-E09.png</t>
+          <t>T-E04.png</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
+          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
+          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>実績と同時選択のファイル数</t>
+          <t>選んだ項目だけ・対象数だけ出るか</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>AC-25</t>
+          <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr"/>
@@ -4426,11 +4426,11 @@
       <c r="R53" s="5" t="inlineStr"/>
       <c r="S53" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="60" customHeight="1">
+          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="64" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4438,50 +4438,50 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>T-E07</t>
+          <t>T-E09</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>未選択でのエクスポート防止</t>
+          <t>実績・同時のエクスポート</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
+          <t>【前提】S-05
+【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
+実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>T-E07.png</t>
+          <t>T-E09.png</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
+          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
+          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>未選択で出力されないか</t>
+          <t>実績と同時選択のファイル数</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="M54" s="13" t="inlineStr">
         <is>
-          <t>AC-27</t>
+          <t>AC-25</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr"/>
@@ -4501,7 +4501,7 @@
       <c r="R54" s="5" t="inlineStr"/>
       <c r="S54" s="8" t="inlineStr">
         <is>
-          <t>入出力：空振りを防ぐ</t>
+          <t>入出力：渡し先に合わせて出せる</t>
         </is>
       </c>
     </row>
@@ -4513,18 +4513,18 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>T-E08</t>
+          <t>T-E07</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>出力CSVの文字化け</t>
+          <t>未選択でのエクスポート防止</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 ／ T-E04で出力済み
-【操作】T-E04で出力したCSVをExcelで開く</t>
+          <t>【前提】S-04
+【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -4535,28 +4535,28 @@
       <c r="F55" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
+警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>T-E08.png</t>
+          <t>T-E07.png</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
+          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
+          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>Excelで文字化けしないか</t>
+          <t>未選択で出力されないか</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="M55" s="13" t="inlineStr">
         <is>
-          <t>AC-28</t>
+          <t>AC-27</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
@@ -4576,72 +4576,72 @@
       <c r="R55" s="5" t="inlineStr"/>
       <c r="S55" s="8" t="inlineStr">
         <is>
-          <t>入出力：そのまま提出できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="64" customHeight="1">
+          <t>入出力：空振りを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>取込データ</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>T-N01</t>
+          <t>T-E08</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>取込元データの確認</t>
+          <t>出力CSVの文字化け</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-I03実施済み
-【操作】サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
+          <t>【前提】S-04 ／ T-E04で出力済み
+【操作】T-E04で出力したCSVをExcelで開く</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定取込データ（サイドバー）】
-設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
+          <t>【確認場所：設定・実績エクスポート】
+日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>T-N01.png</t>
+          <t>T-E08.png</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>設定取込データと実績取込データの一覧＋各タブ（計4枚）</t>
+          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>設定取込データ（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績取込データ … 月別データ／日別データタブ</t>
+          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>元データとタブの構成</t>
+          <t>Excelで文字化けしないか</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M56" s="13" t="inlineStr">
         <is>
-          <t>AC-39</t>
+          <t>AC-28</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr"/>
@@ -4651,11 +4651,11 @@
       <c r="R56" s="5" t="inlineStr"/>
       <c r="S56" s="8" t="inlineStr">
         <is>
-          <t>入出力：原因を追える</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="94" customHeight="1">
+          <t>入出力：そのまま提出できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="64" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -4663,50 +4663,50 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>T-N02</t>
+          <t>T-N01</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>取込前のプレビューと前回差分</t>
+          <t>取込元データの確認</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-06
-【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
+          <t>【前提】T-I03実施済み
+【操作】サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定取込データ／実績取込データ】
-プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
+          <t>【確認場所：設定取込データ（サイドバー）】
+設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>T-N02.png</t>
+          <t>T-N01.png</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
+          <t>設定取込データと実績取込データの一覧＋各タブ（計4枚）</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>設定取込データ／実績取込データ … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
+          <t>設定取込データ（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績取込データ … 月別データ／日別データタブ</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>差分がdata/16・17と一致するか</t>
+          <t>元データとタブの構成</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="M57" s="13" t="inlineStr">
         <is>
-          <t>AC-50</t>
+          <t>AC-39</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr"/>
@@ -4726,11 +4726,11 @@
       <c r="R57" s="5" t="inlineStr"/>
       <c r="S57" s="8" t="inlineStr">
         <is>
-          <t>データ保全：取り込む前に気づける</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="60" customHeight="1">
+          <t>入出力：原因を追える</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="94" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -4738,50 +4738,50 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>T-N03</t>
+          <t>T-N02</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>取込データと人件費実績の相互導線</t>
+          <t>取込前のプレビューと前回差分</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
+          <t>【前提】S-05 S-06
+【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　「実績取込データへ」／実績取込データ】
-2経路とも到達する（不通=0）</t>
+          <t>【確認場所：設定取込データ／実績取込データ】
+プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>T-N03.png</t>
+          <t>T-N02.png</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>人件費実績→実績取込データ／実績取込データ→人件費実績 の到達直後（2枚）</t>
+          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 「実績取込データへ」／実績取込データ → 「人件費実績へ」（相互導線）</t>
+          <t>設定取込データ／実績取込データ … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
         </is>
       </c>
       <c r="K58" s="8" t="inlineStr">
         <is>
-          <t>2経路とも到達するか</t>
+          <t>差分がdata/16・17と一致するか</t>
         </is>
       </c>
       <c r="L58" s="13" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>AC-30</t>
+          <t>AC-50</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr"/>
@@ -4801,72 +4801,72 @@
       <c r="R58" s="5" t="inlineStr"/>
       <c r="S58" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る</t>
+          <t>データ保全：取り込む前に気づける</t>
         </is>
       </c>
     </row>
     <row r="59" ht="60" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>T-Z01</t>
+          <t>T-N03</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>移行前後の突合（既存データ）</t>
+          <t>取込データと人件費実績の相互導線</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 S-11
-【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
+          <t>【前提】S-05
+【操作】人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員一覧】
-件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
+          <t>【確認場所：人件費実績　→　「実績取込データへ」／実績取込データ】
+2経路とも到達する（不通=0）</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>T-Z01.png</t>
+          <t>T-N03.png</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
+          <t>人件費実績→実績取込データ／実績取込データ→人件費実績 の到達直後（2枚）</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
+          <t>人件費実績 → 「実績取込データへ」／実績取込データ → 「人件費実績へ」（相互導線）</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>移行前後で差分0件か</t>
+          <t>2経路とも到達するか</t>
         </is>
       </c>
       <c r="L59" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ すでにご利用中のお客様</t>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
       <c r="M59" s="13" t="inlineStr">
         <is>
-          <t>AC-01</t>
+          <t>AC-30</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr"/>
@@ -4876,7 +4876,7 @@
       <c r="R59" s="5" t="inlineStr"/>
       <c r="S59" s="8" t="inlineStr">
         <is>
-          <t>移行：既存顧客が壊れない</t>
+          <t>画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
@@ -4888,50 +4888,50 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>T-Z02</t>
+          <t>T-Z01</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>移行後の適用日付の付与</t>
+          <t>移行前後の突合（既存データ）</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
+          <t>【前提】S-09 S-11
+【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細 → 設定変更履歴／従業員設定履歴】
-適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている</t>
+          <t>【確認場所：従業員一覧】
+件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>T-Z02.png</t>
+          <t>T-Z01.png</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
+          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 設定変更履歴／従業員設定履歴 … 適用日付の空欄</t>
+          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>適用日付の空欄が0件か</t>
+          <t>移行前後で差分0件か</t>
         </is>
       </c>
       <c r="L60" s="13" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="M60" s="13" t="inlineStr">
         <is>
-          <t>AC-02</t>
+          <t>AC-01</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr"/>
@@ -4951,7 +4951,7 @@
       <c r="R60" s="5" t="inlineStr"/>
       <c r="S60" s="8" t="inlineStr">
         <is>
-          <t>移行：履歴の起点を作る</t>
+          <t>移行：既存顧客が壊れない</t>
         </is>
       </c>
     </row>
@@ -4963,50 +4963,50 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>T-Z03</t>
+          <t>T-Z02</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>移行前後の過去月の人件費</t>
+          <t>移行後の適用日付の付与</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
           <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行前に出力しておいた直近3か月の人件費実績と、移行後の同3か月を突合する</t>
+【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
-3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
+          <t>【確認場所：従業員詳細 → 設定変更履歴／従業員設定履歴】
+適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>T-Z03.png</t>
+          <t>T-Z02.png</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>移行前後の人件費実績 月別実績（直近3か月・金額が同じであること）</t>
+          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ … 移行前後の直近3か月</t>
+          <t>従業員詳細 → 設定変更履歴／従業員設定履歴 … 適用日付の空欄</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>過去3か月の金額が変わらないか</t>
+          <t>適用日付の空欄が0件か</t>
         </is>
       </c>
       <c r="L61" s="13" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>AC-03</t>
+          <t>AC-02</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr"/>
@@ -5026,7 +5026,7 @@
       <c r="R61" s="5" t="inlineStr"/>
       <c r="S61" s="8" t="inlineStr">
         <is>
-          <t>移行：過去が動かない</t>
+          <t>移行：履歴の起点を作る</t>
         </is>
       </c>
     </row>
@@ -5038,60 +5038,60 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>T-Z04</t>
+          <t>T-Z03</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>サイドバーの構成</t>
+          <t>移行前後の過去月の人件費</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
+          <t>【前提】S-09 ／ T-Z01実施済み
+【操作】移行前に出力しておいた直近3か月の人件費実績と、移行後の同3か月を突合する</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：サイドバー「従業員管理」】
-閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>T-Z04.png</t>
+          <t>T-Z03.png</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
+          <t>移行前後の人件費実績 月別実績（直近3か月・金額が同じであること）</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
+          <t>人件費実績 → 月別実績タブ … 移行前後の直近3か月</t>
         </is>
       </c>
       <c r="K62" s="8" t="inlineStr">
         <is>
-          <t>PC・モバイルとも開くか</t>
+          <t>過去3か月の金額が変わらないか</t>
         </is>
       </c>
       <c r="L62" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・画面構成）</t>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
       <c r="M62" s="13" t="inlineStr">
         <is>
-          <t>AC-29</t>
+          <t>AC-03</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr"/>
@@ -5101,7 +5101,7 @@
       <c r="R62" s="5" t="inlineStr"/>
       <c r="S62" s="8" t="inlineStr">
         <is>
-          <t>画面：たどり着ける</t>
+          <t>移行：過去が動かない</t>
         </is>
       </c>
     </row>
@@ -5113,60 +5113,60 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>T-Z05</t>
+          <t>T-Z04</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>遷移と表示規則の網羅</t>
+          <t>サイドバーの構成</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-05
-【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+          <t>【前提】S-01
+【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
-すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+          <t>【確認場所：サイドバー「従業員管理」】
+閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>T-Z05.png</t>
+          <t>T-Z04.png</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
+          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr">
         <is>
-          <t>75本の遷移と表示規則</t>
+          <t>PC・モバイルとも開くか</t>
         </is>
       </c>
       <c r="L63" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・遷移網羅）</t>
+          <t>（ヘルプ記載なし・画面構成）</t>
         </is>
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>AC-30 AC-01</t>
+          <t>AC-29</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr"/>
@@ -5176,72 +5176,72 @@
       <c r="R63" s="5" t="inlineStr"/>
       <c r="S63" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="79" customHeight="1">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>C-000</t>
-        </is>
-      </c>
-      <c r="C64" s="15" t="inlineStr">
-        <is>
-          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
-        </is>
-      </c>
-      <c r="D64" s="15" t="inlineStr">
-        <is>
-          <t>【前提】S-03 S-05
-【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
-        </is>
-      </c>
-      <c r="E64" s="15" t="inlineStr">
-        <is>
-          <t>02〜06・13を再投入（初期化）</t>
-        </is>
-      </c>
-      <c r="F64" s="15" t="inlineStr">
-        <is>
-          <t>【確認場所：従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未】
-従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
-        </is>
-      </c>
-      <c r="G64" s="14" t="inlineStr">
-        <is>
-          <t>C-000.png</t>
-        </is>
-      </c>
-      <c r="H64" s="15" t="inlineStr">
-        <is>
-          <t>初期化後の従業員一覧（12名）と人件費実績（未締め・S-05時点の金額）</t>
+          <t>画面：たどり着ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>T-Z05</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>遷移と表示規則の網羅</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>【前提】S-04 S-05
+【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
+すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>T-Z05.png</t>
+        </is>
+      </c>
+      <c r="H64" s="11" t="inlineStr">
+        <is>
+          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="15" t="inlineStr">
-        <is>
-          <t>従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未締めに戻す）</t>
-        </is>
-      </c>
-      <c r="K64" s="15" t="inlineStr">
-        <is>
-          <t>S-05時点の値に戻ったか</t>
-        </is>
-      </c>
-      <c r="L64" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため対応なし）</t>
-        </is>
-      </c>
-      <c r="M64" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J64" s="12" t="inlineStr">
+        <is>
+          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+        </is>
+      </c>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>75本の遷移と表示規則</t>
+        </is>
+      </c>
+      <c r="L64" s="13" t="inlineStr">
+        <is>
+          <t>（ヘルプ記載なし・遷移網羅）</t>
+        </is>
+      </c>
+      <c r="M64" s="13" t="inlineStr">
+        <is>
+          <t>AC-30 AC-01</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr"/>
@@ -5249,13 +5249,13 @@
       <c r="P64" s="6" t="inlineStr"/>
       <c r="Q64" s="5" t="inlineStr"/>
       <c r="R64" s="5" t="inlineStr"/>
-      <c r="S64" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="64" customHeight="1">
+      <c r="S64" s="8" t="inlineStr">
+        <is>
+          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="79" customHeight="1">
       <c r="A65" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5263,60 +5263,60 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>C-001</t>
+          <t>C-000</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプなし）</t>
+          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-002（概算280,000・基礎時給1,750＝280,000÷160・深夜2h）と EMP-007（概算300,000・基礎時給1,875＝300,000÷160・深夜4h）を検算</t>
+          <t>【前提】S-03 S-05
+【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
         </is>
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>02〜06・13を再投入（初期化）</t>
         </is>
       </c>
       <c r="F65" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-EMP-002＝285,250（概算280,000＋深夜残業代5,250＝1,750×1.5×2h）／EMP-007＝311,250（概算300,000＋深夜残業代11,250＝1,875×1.5×4h）。いずれも差分0円</t>
+          <t>【確認場所：従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未】
+従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>C-001.png</t>
+          <t>C-000.png</t>
         </is>
       </c>
       <c r="H65" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
+          <t>初期化後の従業員一覧（12名）と人件費実績（未締め・S-05時点の金額）</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
+          <t>従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未締めに戻す）</t>
         </is>
       </c>
       <c r="K65" s="15" t="inlineStr">
         <is>
-          <t>概算＋深夜＝実績給与か</t>
+          <t>S-05時点の値に戻ったか</t>
         </is>
       </c>
       <c r="L65" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>（初期化のため対応なし）</t>
         </is>
       </c>
       <c r="M65" s="15" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr"/>
@@ -5326,11 +5326,11 @@
       <c r="R65" s="5" t="inlineStr"/>
       <c r="S65" s="15" t="inlineStr">
         <is>
-          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="109" customHeight="1">
+          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="64" customHeight="1">
       <c r="A66" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5338,60 +5338,60 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>C-003</t>
+          <t>C-001</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプあり）</t>
+          <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-001（概算320,000・基礎時給2,000・深夜6h・ヘルプ22h／総労働172h）／EMP-005（概算350,000・基礎時給2,187.5・深夜10h・ヘルプ35h／総労働185h）／EMP-003（概算144,000・時給1,200・深夜0h・ヘルプ20h／総労働120h）を検算</t>
+【操作】2026-05の EMP-002（概算280,000・基礎時給1,750＝280,000÷160・深夜2h）と EMP-007（概算300,000・基礎時給1,875＝300,000÷160・深夜4h）を検算</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
           <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-EMP-001＝338,000（概算320,000＋深夜18,000＝2,000×1.5×6h）／EMP-005＝382,812（概算350,000＋深夜32,812＝2,187.5×1.5×10h＝32,812.5→32,812）／EMP-003＝144,000（深夜なし）。ヘルプ人件費は実績給与×ヘルプ時間÷総労働時間で按分し応援先へ振替（EMP-001＝43,232／EMP-003＝24,000／EMP-005＝72,424）</t>
+EMP-002＝285,250（概算280,000＋深夜残業代5,250＝1,750×1.5×2h）／EMP-007＝311,250（概算300,000＋深夜残業代11,250＝1,875×1.5×4h）。いずれも差分0円</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>C-003.png</t>
+          <t>C-001.png</t>
         </is>
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
+          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
+          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
         </is>
       </c>
       <c r="K66" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費が按分で振替されるか</t>
+          <t>概算＋深夜＝実績給与か</t>
         </is>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr"/>
@@ -5401,11 +5401,11 @@
       <c r="R66" s="5" t="inlineStr"/>
       <c r="S66" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="60" customHeight="1">
+          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="109" customHeight="1">
       <c r="A67" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5413,50 +5413,50 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>C-005</t>
+          <t>C-003</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計と全社合計の一致</t>
+          <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】2026-05の EMP-001（概算320,000・基礎時給2,000・深夜6h・ヘルプ22h／総労働172h）／EMP-005（概算350,000・基礎時給2,187.5・深夜10h・ヘルプ35h／総労働185h）／EMP-003（概算144,000・時給1,200・深夜0h・ヘルプ20h／総労働120h）を検算</t>
         </is>
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
           <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
+EMP-001＝338,000（概算320,000＋深夜18,000＝2,000×1.5×6h）／EMP-005＝382,812（概算350,000＋深夜32,812＝2,187.5×1.5×10h＝32,812.5→32,812）／EMP-003＝144,000（深夜なし）。ヘルプ人件費は実績給与×ヘルプ時間÷総労働時間で按分し応援先へ振替（EMP-001＝43,232／EMP-003＝24,000／EMP-005＝72,424）</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>C-005.png</t>
+          <t>C-003.png</t>
         </is>
       </c>
       <c r="H67" s="15" t="inlineStr">
         <is>
-          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
+          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
+          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
         </is>
       </c>
       <c r="K67" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計＝全社（差0円）か</t>
+          <t>ヘルプ人件費が按分で振替されるか</t>
         </is>
       </c>
       <c r="L67" s="15" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="M67" s="15" t="inlineStr">
         <is>
-          <t>AC-11</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr"/>
@@ -5476,11 +5476,11 @@
       <c r="R67" s="5" t="inlineStr"/>
       <c r="S67" s="15" t="inlineStr">
         <is>
-          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="79" customHeight="1">
+          <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1">
       <c r="A68" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5488,60 +5488,60 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>C-006</t>
+          <t>C-005</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>月中改定と予約の日割り</t>
+          <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>14 勤務データ 2026-06</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従】
-6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
+店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>C-006.png</t>
+          <t>C-005.png</t>
         </is>
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
+          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
+          <t>人件費実績 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
         </is>
       </c>
       <c r="K68" s="15" t="inlineStr">
         <is>
-          <t>所定労働日割になっているか</t>
+          <t>店舗別合計＝全社（差0円）か</t>
         </is>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>AC-12 AC-04</t>
+          <t>AC-11</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr"/>
@@ -5551,11 +5551,11 @@
       <c r="R68" s="5" t="inlineStr"/>
       <c r="S68" s="15" t="inlineStr">
         <is>
-          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="64" customHeight="1">
+          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="79" customHeight="1">
       <c r="A69" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5563,60 +5563,60 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>C-011</t>
+          <t>C-006</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>月中改定と予約の日割り</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
+【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・14 勤務データ 2026-06</t>
+          <t>14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F69" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
-5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従】
+6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>C-011.png</t>
+          <t>C-006.png</t>
         </is>
       </c>
       <c r="H69" s="15" t="inlineStr">
         <is>
-          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
+          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
+          <t>人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
         </is>
       </c>
       <c r="K69" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>所定労働日割になっているか</t>
         </is>
       </c>
       <c r="L69" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="M69" s="15" t="inlineStr">
         <is>
-          <t>AC-13</t>
+          <t>AC-12 AC-04</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr"/>
@@ -5626,11 +5626,11 @@
       <c r="R69" s="5" t="inlineStr"/>
       <c r="S69" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="109" customHeight="1">
+          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="64" customHeight="1">
       <c r="A70" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5638,50 +5638,50 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-011</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>【前提】C-000 S-07 ／ data/14を投入
+【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績・14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績】
-判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。5/8のヘルプ人件費＝実績給与338,000×11h÷総労働172h＝21,616円で、計上先はS02。みなし労働時間差分＝172−(160＋20)＝−8h（未達はマイナス表示・減額なし＝判断8）</t>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>C-013.png</t>
+          <t>C-011.png</t>
         </is>
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
+          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
+          <t>人件費実績 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
         </is>
       </c>
       <c r="K70" s="15" t="inlineStr">
         <is>
-          <t>深夜1.5倍とヘルプの按分単価</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="L70" s="15" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-13</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr"/>
@@ -5701,11 +5701,11 @@
       <c r="R70" s="5" t="inlineStr"/>
       <c r="S70" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="79" customHeight="1">
+          <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="109" customHeight="1">
       <c r="A71" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5713,60 +5713,60 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-013</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8の】
-交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
+          <t>【確認場所：人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績】
+判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。5/8のヘルプ人件費＝実績給与338,000×11h÷総労働172h＝21,616円で、計上先はS02。みなし労働時間差分＝172−(160＋20)＝−8h（未達はマイナス表示・減額なし＝判断8）</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>C-017.png</t>
+          <t>C-013.png</t>
         </is>
       </c>
       <c r="H71" s="15" t="inlineStr">
         <is>
-          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
+          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+          <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
         <is>
-          <t>交通費が給与と別費目か</t>
+          <t>深夜1.5倍とヘルプの按分単価</t>
         </is>
       </c>
       <c r="L71" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr"/>
@@ -5776,11 +5776,11 @@
       <c r="R71" s="5" t="inlineStr"/>
       <c r="S71" s="15" t="inlineStr">
         <is>
-          <t>交通費は給与と別の独立費目（判断6・確定）。通勤交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="94" customHeight="1">
+          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="79" customHeight="1">
       <c r="A72" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5788,60 +5788,60 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-017</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>交通費の計上先</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07
-【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解】
-（a）5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
+          <t>【確認場所：人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8の】
+交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>C-008.png</t>
+          <t>C-017.png</t>
         </is>
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
+          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+          <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
         </is>
       </c>
       <c r="K72" s="15" t="inlineStr">
         <is>
-          <t>締め前後で差0円・解除後に再計算</t>
+          <t>交通費が給与と別費目か</t>
         </is>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>AC-16 AC-17</t>
+          <t>AC-15</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr"/>
@@ -5851,72 +5851,72 @@
       <c r="R72" s="5" t="inlineStr"/>
       <c r="S72" s="15" t="inlineStr">
         <is>
-          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
+          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
         </is>
       </c>
     </row>
     <row r="73" ht="94" customHeight="1">
-      <c r="A73" s="16" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B73" s="16" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="D73" s="17" t="inlineStr">
-        <is>
-          <t>【前提】S-01
-【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
-        </is>
-      </c>
-      <c r="E73" s="17" t="inlineStr">
-        <is>
-          <t>（追加のデータ投入なし）</t>
-        </is>
-      </c>
-      <c r="F73" s="17" t="inlineStr">
-        <is>
-          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
-①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
-        </is>
-      </c>
-      <c r="G73" s="16" t="inlineStr">
-        <is>
-          <t>R-01.png</t>
-        </is>
-      </c>
-      <c r="H73" s="17" t="inlineStr">
-        <is>
-          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>締めの前後で数字が動かないこと</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-07
+【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解】
+（a）5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>C-008.png</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="inlineStr">
+        <is>
+          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
-      <c r="J73" s="17" t="inlineStr">
-        <is>
-          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
-        </is>
-      </c>
-      <c r="K73" s="17" t="inlineStr">
-        <is>
-          <t>適用日付と履歴がテーブルにあるか</t>
-        </is>
-      </c>
-      <c r="L73" s="17" t="inlineStr">
-        <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
-        </is>
-      </c>
-      <c r="M73" s="17" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47</t>
+      <c r="J73" s="15" t="inlineStr">
+        <is>
+          <t>人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+        </is>
+      </c>
+      <c r="K73" s="15" t="inlineStr">
+        <is>
+          <t>締め前後で差0円・解除後に再計算</t>
+        </is>
+      </c>
+      <c r="L73" s="15" t="inlineStr">
+        <is>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
+        </is>
+      </c>
+      <c r="M73" s="15" t="inlineStr">
+        <is>
+          <t>AC-16 AC-17</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr"/>
@@ -5924,13 +5924,13 @@
       <c r="P73" s="6" t="inlineStr"/>
       <c r="Q73" s="5" t="inlineStr"/>
       <c r="R73" s="5" t="inlineStr"/>
-      <c r="S73" s="17" t="inlineStr">
-        <is>
-          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="79" customHeight="1">
+      <c r="S73" s="15" t="inlineStr">
+        <is>
+          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="94" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -5938,18 +5938,18 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>締めの実装レビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="D74" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
+【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
         </is>
       </c>
       <c r="E74" s="17" t="inlineStr">
@@ -5959,39 +5959,39 @@
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
-①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
+          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
+①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
         </is>
       </c>
       <c r="G74" s="16" t="inlineStr">
         <is>
-          <t>R-02.png</t>
+          <t>R-01.png</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>締めAPIのコードとスコープ判定箇所</t>
+          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
+          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
       </c>
       <c r="K74" s="17" t="inlineStr">
         <is>
-          <t>APIでも店長が締められないか</t>
+          <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
       <c r="L74" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M74" s="17" t="inlineStr">
         <is>
-          <t>AC-16 AC-41</t>
+          <t>AC-07 AC-40 AC-47</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr"/>
@@ -6001,11 +6001,11 @@
       <c r="R74" s="5" t="inlineStr"/>
       <c r="S74" s="17" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="109" customHeight="1">
+          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="79" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6013,18 +6013,18 @@
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>入力検証とトランザクションのレビュー</t>
+          <t>締めの実装レビュー</t>
         </is>
       </c>
       <c r="D75" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
+【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
       <c r="E75" s="17" t="inlineStr">
@@ -6034,39 +6034,39 @@
       </c>
       <c r="F75" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
-①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
+          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
+①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
         </is>
       </c>
       <c r="G75" s="16" t="inlineStr">
         <is>
-          <t>R-03.png</t>
+          <t>R-02.png</t>
         </is>
       </c>
       <c r="H75" s="17" t="inlineStr">
         <is>
-          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
+          <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
+          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
       </c>
       <c r="K75" s="17" t="inlineStr">
         <is>
-          <t>APIを直接呼んでも弾かれるか</t>
+          <t>APIでも店長が締められないか</t>
         </is>
       </c>
       <c r="L75" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 設定が保存できません</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M75" s="17" t="inlineStr">
         <is>
-          <t>AC-23 AC-42 AC-43</t>
+          <t>AC-16 AC-41</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
@@ -6076,11 +6076,11 @@
       <c r="R75" s="5" t="inlineStr"/>
       <c r="S75" s="17" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="79" customHeight="1">
+          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="109" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6088,18 +6088,18 @@
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの共有レビュー</t>
+          <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -6109,39 +6109,39 @@
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
-同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
+          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
+①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
         </is>
       </c>
       <c r="G76" s="16" t="inlineStr">
         <is>
-          <t>R-04.png</t>
+          <t>R-03.png</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
+          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
+          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
       </c>
       <c r="K76" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックが1箇所か</t>
+          <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
       <c r="L76" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
       <c r="M76" s="17" t="inlineStr">
         <is>
-          <t>AC-35 AC-11</t>
+          <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr"/>
@@ -6151,11 +6151,11 @@
       <c r="R76" s="5" t="inlineStr"/>
       <c r="S76" s="17" t="inlineStr">
         <is>
-          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="64" customHeight="1">
+          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="79" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6163,18 +6163,18 @@
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>計算ロジックの共有レビュー</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込の列解決の実装を提示してもらう</t>
+【操作】人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
       <c r="E77" s="17" t="inlineStr">
@@ -6184,39 +6184,39 @@
       </c>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
-CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
+          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
+同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
         </is>
       </c>
       <c r="G77" s="16" t="inlineStr">
         <is>
-          <t>R-05.png</t>
+          <t>R-04.png</t>
         </is>
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
+          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
+          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
         </is>
       </c>
       <c r="K77" s="17" t="inlineStr">
         <is>
-          <t>列名がコードに埋まっていないか</t>
+          <t>計算ロジックが1箇所か</t>
         </is>
       </c>
       <c r="L77" s="17" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M77" s="17" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-35 AC-11</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
@@ -6226,11 +6226,11 @@
       <c r="R77" s="5" t="inlineStr"/>
       <c r="S77" s="17" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="79" customHeight="1">
+          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="64" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6238,18 +6238,18 @@
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>設定更新処理の共通化レビュー</t>
+          <t>列マッピングの実装レビュー</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+【操作】取込の列解決の実装を提示してもらう</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
@@ -6259,39 +6259,39 @@
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
-設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
+CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
       <c r="G78" s="16" t="inlineStr">
         <is>
-          <t>R-06.png</t>
+          <t>R-05.png</t>
         </is>
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
         </is>
       </c>
       <c r="K78" s="17" t="inlineStr">
         <is>
-          <t>2つの入口で更新処理が共通か</t>
+          <t>列名がコードに埋まっていないか</t>
         </is>
       </c>
       <c r="L78" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-22 AC-24</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
@@ -6301,17 +6301,92 @@
       <c r="R78" s="5" t="inlineStr"/>
       <c r="S78" s="17" t="inlineStr">
         <is>
+          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="79" customHeight="1">
+      <c r="A79" s="16" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B79" s="16" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="E79" s="17" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F79" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
+設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="G79" s="16" t="inlineStr">
+        <is>
+          <t>R-06.png</t>
+        </is>
+      </c>
+      <c r="H79" s="17" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr"/>
+      <c r="J79" s="17" t="inlineStr">
+        <is>
+          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+        </is>
+      </c>
+      <c r="K79" s="17" t="inlineStr">
+        <is>
+          <t>2つの入口で更新処理が共通か</t>
+        </is>
+      </c>
+      <c r="L79" s="17" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="M79" s="17" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="N79" s="5" t="inlineStr"/>
+      <c r="O79" s="5" t="inlineStr"/>
+      <c r="P79" s="6" t="inlineStr"/>
+      <c r="Q79" s="5" t="inlineStr"/>
+      <c r="R79" s="5" t="inlineStr"/>
+      <c r="S79" s="17" t="inlineStr">
+        <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S78"/>
+  <autoFilter ref="A2:S79"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3:O78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -5349,7 +5349,7 @@
       <c r="D66" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-002（概算280,000・基礎時給1,750＝280,000÷160・深夜2h）と EMP-007（概算300,000・基礎時給1,875＝300,000÷160・深夜4h）を検算</t>
+【操作】2026-05の EMP-002（概算280,000・基礎時給1,750・深夜2h・所属店舗の交通費15,000）と EMP-007（概算300,000・基礎時給1,875・深夜4h・交通費30,000）を検算</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
@@ -5360,7 +5360,7 @@
       <c r="F66" s="15" t="inlineStr">
         <is>
           <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-EMP-002＝285,250（概算280,000＋深夜残業代5,250＝1,750×1.5×2h）／EMP-007＝311,250（概算300,000＋深夜残業代11,250＝1,875×1.5×4h）。いずれも差分0円</t>
+EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -5405,7 +5405,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="109" customHeight="1">
+    <row r="67" ht="79" customHeight="1">
       <c r="A67" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5424,7 +5424,7 @@
       <c r="D67" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-001（概算320,000・基礎時給2,000・深夜6h・ヘルプ22h／総労働172h）／EMP-005（概算350,000・基礎時給2,187.5・深夜10h・ヘルプ35h／総労働185h）／EMP-003（概算144,000・時給1,200・深夜0h・ヘルプ20h／総労働120h）を検算</t>
+【操作】2026-05の EMP-001（概算320,000・深夜6h・ヘルプ22h／所属店舗の交通費18,000・ヘルプ先の交通費1,600）／EMP-005（概算350,000・深夜10h・ヘルプ35h／22,000・3,100）／EMP-003（概算144,000・ヘルプ20h／9,000・1,300）を検算</t>
         </is>
       </c>
       <c r="E67" s="15" t="inlineStr">
@@ -5435,7 +5435,7 @@
       <c r="F67" s="15" t="inlineStr">
         <is>
           <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-EMP-001＝338,000（概算320,000＋深夜18,000＝2,000×1.5×6h）／EMP-005＝382,812（概算350,000＋深夜32,812＝2,187.5×1.5×10h＝32,812.5→32,812）／EMP-003＝144,000（深夜なし）。ヘルプ人件費は実績給与×ヘルプ時間÷総労働時間で按分し応援先へ振替（EMP-001＝43,232／EMP-003＝24,000／EMP-005＝72,424）</t>
+EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算＋深夜＋みなし超過＋交通費）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -5510,7 +5510,7 @@
       <c r="F68" s="15" t="inlineStr">
         <is>
           <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
+店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="109" customHeight="1">
+    <row r="71" ht="94" customHeight="1">
       <c r="A71" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5734,8 +5734,8 @@
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績】
-判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。5/8のヘルプ人件費＝実績給与338,000×11h÷総労働172h＝21,616円で、計上先はS02。みなし労働時間差分＝172−(160＋20)＝−8h（未達はマイナス表示・減額なし＝判断8）</t>
+          <t>【確認場所：人件費実績 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
+判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
@@ -5809,8 +5809,8 @@
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8の】
-交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
+          <t>【確認場所：人件費実績 → 月別実績・日別実績】
+交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -5884,8 +5884,8 @@
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解】
-（a）5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:S80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証66ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
+          <t>確かめる手順（準備11行＋検証67ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
 実施順を変えてはいけない箇所：①T-A08（勤怠取込）→T-S03（締め）　②T-S03→T-S04・T-D07→T-S05（この3件は締め済みでしか確認できない）　③C-000（初期化）は計算の先頭　④C-008は計算の最後（2026-05のEMP-001を352,286円に変えるためC-013・C-017が合わなくなる）　⑤T-N02の前にdata/02を再投入　⑥削除はEMP-012（T-L10）とEMP-004（T-D08）だけ
 列の使い方：使用する検証データ＝この検証で投入・使用するdataファイル／期待値＝先頭の【確認場所】でどの画面を見て合否を出すかを示し、続けて合格の基準を書いている／スクショ（撮るもの）＝何が写っていれば証拠になるか／スクショ貼付欄＝撮った画像をこの列に貼る／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めて合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを決める
 色：緑＝使う検証データ　青＝画面　橙＝スクショの指示　紫＝ヘルプ・受入条件との対応　黄＝当日の記入欄。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
@@ -878,7 +878,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -897,12 +897,12 @@
       <c r="D6" s="4" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】data/01（店舗5）→ data/02（従業員12）→ data/03（ヘルプ先交通費8行）の順に投入</t>
+【操作】data/01（店舗5）→ data/02（従業員12・従業員IDが付番済み）→ data/03（ヘルプ先交通費8行）→ data/20（外部ID対応表13行）の順に投入</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>投入する：01・02・03</t>
+          <t>投入する：01・02・03・20</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="64" customHeight="1">
+    <row r="45" ht="79" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3774,7 +3774,7 @@
       <c r="D45" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】データ種類＝King of Time を選び data/07（従業員設定・3行）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
+【操作】データ種類＝King of Time を選び data/07（従業員設定・3行／外部ID 1001・1005・1013）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -3784,8 +3784,8 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-07は3行すべて取り込まれ、EMP-001=340,000・EMP-005=360,000に更新、EMP-013は新規追加。10は給与設定（ヘルプ先交通費 S02:700;S03:900 の記法を含む）が反映される</t>
+          <t>【確認場所：設定インポート → 従業員一覧】
+外部ID 1001・1005 は対応表で E0001・E0005 に解決され、既存の従業員が更新される（単位給与額 340,000／360,000）。対応表に無い 1013 は新規として扱われ、従業員IDが自動で付番される。件数は3行</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -3849,7 +3849,7 @@
       <c r="D46" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】データ種類＝ジョブカン を選び data/08（3行）をD&amp;D → 登録</t>
+【操作】データ種類＝ジョブカン を選び data/08（3行／外部ID JB-003・JB-010・JB-014）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -3859,8 +3859,8 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-3行すべて取り込まれる（EMP-003=1,250・EMP-010=1,300・EMP-014は新規）</t>
+          <t>【確認場所：設定インポート → 従業員一覧】
+スタッフコード等の表記ゆれを吸収し、外部ID JB-003・JB-010 が E0003・E0010 に解決される。取込成功=3行</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
+    <row r="48" ht="64" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3999,7 +3999,7 @@
       <c r="D48" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】（a）data/07を2回続けて取り込む （b）data/19（EMP-002が2行・単位給与額が異なる）を取り込む</t>
+【操作】（a）data/07を2回続けて取り込む （b）data/19（外部ID 1002 が2行・単位給与額が異なる）を取り込む</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -4010,7 +4010,7 @@
       <c r="F48" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート】
-（a）2回目は更新となり件数が増えない （b）重複行がエラーとして検出される（両方が登録されない）</t>
+（a）2回目は更新となり件数が増えない（二重登録=0件）（b）同じ外部IDが2行あるためエラーとして検出され、両方とも登録されない。1つの外部IDが2つの従業員IDに紐づく=0件</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="M48" s="13" t="inlineStr">
         <is>
-          <t>AC-40</t>
+          <t>AC-40 AC-56</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr"/>
@@ -4063,60 +4063,60 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>T-I18</t>
+          <t>T-I20</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>取込が途中で失敗したときの扱い</t>
+          <t>外部IDの対応と付番</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
+【操作】（a）data/20 の対応表を開き、EMP-001 が King of Time 1001 とジョブカン JB-001 の2件を持つことを確認 →（b）対応表に無い外部ID（例 9999）を含むCSVを取り込む →（c）取り込んだ従業員の従業員IDを従業員一覧で確認する</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>20 外部ID対応表／07 取込CSV KingOfTime</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録】
-中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
+          <t>【確認場所：列マッピングテンプレート（外部ID対応）→ 設定インポート → 従業員一覧】
+（a）1名が複数の勤怠システムの外部IDを持てる（E0001＝1001／JB-001）（b）対応表に無い外部IDは取り込まれず、件数と理由が表示される（黙って登録=0件）（c）すべての従業員に従業員IDが付いている（未付番=0件）</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>T-I18.png</t>
+          <t>T-I20.png</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
+          <t>外部ID対応表（EMP-001が2システム分ある状態）／対応表に無い外部IDのエラー表示／従業員一覧の従業員ID列</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録されていないこと）</t>
+          <t>列マッピングテンプレート（外部IDの対応）→ 設定インポート → 従業員一覧</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>部分登録が残らないか</t>
+          <t>外部IDが従業員IDに解決されるか／未登録は弾かれるか</t>
         </is>
       </c>
       <c r="L49" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>AC-42</t>
+          <t>AC-55 AC-56</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
@@ -4126,11 +4126,11 @@
       <c r="R49" s="5" t="inlineStr"/>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>データ保全：中途半端に残さない</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="64" customHeight="1">
+          <t>データ保全：従業員の同一性を保つ／入出力：ID体系の違いを吸収</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="94" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4138,60 +4138,60 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>T-I11</t>
+          <t>T-I18</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>CSV位置合わせ設定</t>
+          <t>取込が途中で失敗したときの扱い</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06
-【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
+          <t>【前提】S-04 S-06
+【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>11 取込CSV 説明行あり</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-余計な行が無視され、3行が正しく取り込まれる</t>
+          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録】
+中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>T-I11.png</t>
+          <t>T-I18.png</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
+          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
+          <t>設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録されていないこと）</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>説明行を飛ばして取り込めるか</t>
+          <t>部分登録が残らないか</t>
         </is>
       </c>
       <c r="L50" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="M50" s="13" t="inlineStr">
         <is>
-          <t>AC-37</t>
+          <t>AC-42</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr"/>
@@ -4201,11 +4201,11 @@
       <c r="R50" s="5" t="inlineStr"/>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>入出力：現場のCSVをそのまま使える</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="94" customHeight="1">
+          <t>データ保全：中途半端に残さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="64" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4213,50 +4213,50 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>T-I09</t>
+          <t>T-I11</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>CSV位置合わせ設定</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】「列マッピングテンプレート管理」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
+【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>11 取込CSV 説明行あり</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート管理」】
-テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
+          <t>【確認場所：設定インポート】
+余計な行が無視され、3行が正しく取り込まれる</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>T-I09.png</t>
+          <t>T-I11.png</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
+          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>設定インポート → ツールバー「列マッピングテンプレート管理」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
+          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>テンプレの登録・編集・削除と往復</t>
+          <t>説明行を飛ばして取り込めるか</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="M51" s="13" t="inlineStr">
         <is>
-          <t>AC-24 AC-38 AC-30</t>
+          <t>AC-37</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr"/>
@@ -4276,11 +4276,11 @@
       <c r="R51" s="5" t="inlineStr"/>
       <c r="S51" s="8" t="inlineStr">
         <is>
-          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="79" customHeight="1">
+          <t>入出力：現場のCSVをそのまま使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="94" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4288,50 +4288,50 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>T-I19</t>
+          <t>T-I09</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>マッピング表の一括登録</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
+【操作】「列マッピングテンプレート管理」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>18 列マッピング表テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：列マッピングテンプレート】
-テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
+          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート管理」】
+テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>T-I19.png</t>
+          <t>T-I09.png</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
+          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
+          <t>設定インポート → ツールバー「列マッピングテンプレート管理」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
         </is>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>一括登録と10MB超の扱い</t>
+          <t>テンプレの登録・編集・削除と往復</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="M52" s="13" t="inlineStr">
         <is>
-          <t>AC-51</t>
+          <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr"/>
@@ -4351,72 +4351,72 @@
       <c r="R52" s="5" t="inlineStr"/>
       <c r="S52" s="8" t="inlineStr">
         <is>
-          <t>入出力：マッピングの一括運用</t>
+          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="53" ht="79" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>取込</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>T-E04</t>
+          <t>T-I19</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>設定のエクスポート</t>
+          <t>マッピング表の一括登録</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
+          <t>【前提】S-06
+【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>18 列マッピング表テンプレ</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
-専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
+          <t>【確認場所：列マッピングテンプレート】
+テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>T-E04.png</t>
+          <t>T-I19.png</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
+          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
+          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>選んだ項目だけ・対象数だけ出るか</t>
+          <t>一括登録と10MB超の扱い</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>AC-25 AC-26 AC-30</t>
+          <t>AC-51</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr"/>
@@ -4426,11 +4426,11 @@
       <c r="R53" s="5" t="inlineStr"/>
       <c r="S53" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="64" customHeight="1">
+          <t>入出力：マッピングの一括運用</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="79" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4438,50 +4438,50 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>T-E09</t>
+          <t>T-E04</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>実績・同時のエクスポート</t>
+          <t>設定のエクスポート</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
+          <t>【前提】S-04
+【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート】
-実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
+          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
+専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>T-E09.png</t>
+          <t>T-E04.png</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
+          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
+          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>実績と同時選択のファイル数</t>
+          <t>選んだ項目だけ・対象数だけ出るか</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="M54" s="13" t="inlineStr">
         <is>
-          <t>AC-25</t>
+          <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr"/>
@@ -4501,11 +4501,11 @@
       <c r="R54" s="5" t="inlineStr"/>
       <c r="S54" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="60" customHeight="1">
+          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="64" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4513,50 +4513,50 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>T-E07</t>
+          <t>T-E09</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>未選択でのエクスポート防止</t>
+          <t>実績・同時のエクスポート</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
+          <t>【前提】S-05
+【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
+実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>T-E07.png</t>
+          <t>T-E09.png</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
+          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
+          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>未選択で出力されないか</t>
+          <t>実績と同時選択のファイル数</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="M55" s="13" t="inlineStr">
         <is>
-          <t>AC-27</t>
+          <t>AC-25</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
@@ -4576,7 +4576,7 @@
       <c r="R55" s="5" t="inlineStr"/>
       <c r="S55" s="8" t="inlineStr">
         <is>
-          <t>入出力：空振りを防ぐ</t>
+          <t>入出力：渡し先に合わせて出せる</t>
         </is>
       </c>
     </row>
@@ -4588,18 +4588,18 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>T-E08</t>
+          <t>T-E07</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>出力CSVの文字化け</t>
+          <t>未選択でのエクスポート防止</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 ／ T-E04で出力済み
-【操作】T-E04で出力したCSVをExcelで開く</t>
+          <t>【前提】S-04
+【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -4610,28 +4610,28 @@
       <c r="F56" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
+警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>T-E08.png</t>
+          <t>T-E07.png</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
+          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
+          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>Excelで文字化けしないか</t>
+          <t>未選択で出力されないか</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="M56" s="13" t="inlineStr">
         <is>
-          <t>AC-28</t>
+          <t>AC-27</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr"/>
@@ -4651,72 +4651,72 @@
       <c r="R56" s="5" t="inlineStr"/>
       <c r="S56" s="8" t="inlineStr">
         <is>
-          <t>入出力：そのまま提出できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="64" customHeight="1">
+          <t>入出力：空振りを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>取込データ</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>T-N01</t>
+          <t>T-E08</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>取込元データの確認</t>
+          <t>出力CSVの文字化け</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-I03実施済み
-【操作】サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
+          <t>【前提】S-04 ／ T-E04で出力済み
+【操作】T-E04で出力したCSVをExcelで開く</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定取込データ（サイドバー）】
-設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
+          <t>【確認場所：設定・実績エクスポート】
+日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>T-N01.png</t>
+          <t>T-E08.png</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>設定取込データと実績取込データの一覧＋各タブ（計4枚）</t>
+          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>設定取込データ（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績取込データ … 月別データ／日別データタブ</t>
+          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>元データとタブの構成</t>
+          <t>Excelで文字化けしないか</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M57" s="13" t="inlineStr">
         <is>
-          <t>AC-39</t>
+          <t>AC-28</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr"/>
@@ -4726,11 +4726,11 @@
       <c r="R57" s="5" t="inlineStr"/>
       <c r="S57" s="8" t="inlineStr">
         <is>
-          <t>入出力：原因を追える</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="94" customHeight="1">
+          <t>入出力：そのまま提出できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="79" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -4738,50 +4738,50 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>T-N02</t>
+          <t>T-N01</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>取込前のプレビューと前回差分</t>
+          <t>取込元データの確認</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-06
-【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
+          <t>【前提】T-I03実施済み
+【操作】サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定取込データ／実績取込データ】
-プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
+          <t>【確認場所：設定取込データ（サイドバー）】
+設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ10列／日別データ10列。交通費・総支給額は表示しない（判断14））</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>T-N02.png</t>
+          <t>T-N01.png</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
+          <t>設定取込データと実績取込データの一覧＋各タブ（計4枚）</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>設定取込データ／実績取込データ … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
+          <t>設定取込データ（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績取込データ … 月別データ／日別データタブ</t>
         </is>
       </c>
       <c r="K58" s="8" t="inlineStr">
         <is>
-          <t>差分がdata/16・17と一致するか</t>
+          <t>元データとタブの構成</t>
         </is>
       </c>
       <c r="L58" s="13" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>AC-50</t>
+          <t>AC-39</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr"/>
@@ -4801,11 +4801,11 @@
       <c r="R58" s="5" t="inlineStr"/>
       <c r="S58" s="8" t="inlineStr">
         <is>
-          <t>データ保全：取り込む前に気づける</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="60" customHeight="1">
+          <t>入出力：原因を追える</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="94" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -4813,50 +4813,50 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>T-N03</t>
+          <t>T-N02</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>取込データと人件費実績の相互導線</t>
+          <t>取込前のプレビューと前回差分</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
+          <t>【前提】S-05 S-06
+【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　「実績取込データへ」／実績取込データ】
-2経路とも到達する（不通=0）</t>
+          <t>【確認場所：設定取込データ／実績取込データ】
+プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>T-N03.png</t>
+          <t>T-N02.png</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>人件費実績→実績取込データ／実績取込データ→人件費実績 の到達直後（2枚）</t>
+          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 「実績取込データへ」／実績取込データ → 「人件費実績へ」（相互導線）</t>
+          <t>設定取込データ／実績取込データ … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>2経路とも到達するか</t>
+          <t>差分がdata/16・17と一致するか</t>
         </is>
       </c>
       <c r="L59" s="13" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M59" s="13" t="inlineStr">
         <is>
-          <t>AC-30</t>
+          <t>AC-50</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr"/>
@@ -4876,72 +4876,72 @@
       <c r="R59" s="5" t="inlineStr"/>
       <c r="S59" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る</t>
+          <t>データ保全：取り込む前に気づける</t>
         </is>
       </c>
     </row>
     <row r="60" ht="60" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>T-Z01</t>
+          <t>T-N03</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>移行前後の突合（既存データ）</t>
+          <t>取込データと人件費実績の相互導線</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 S-11
-【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
+          <t>【前提】S-05
+【操作】人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員一覧】
-件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
+          <t>【確認場所：人件費実績　→　「実績取込データへ」／実績取込データ】
+2経路とも到達する（不通=0）</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>T-Z01.png</t>
+          <t>T-N03.png</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
+          <t>人件費実績→実績取込データ／実績取込データ→人件費実績 の到達直後（2枚）</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
+          <t>人件費実績 → 「実績取込データへ」／実績取込データ → 「人件費実績へ」（相互導線）</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>移行前後で差分0件か</t>
+          <t>2経路とも到達するか</t>
         </is>
       </c>
       <c r="L60" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ すでにご利用中のお客様</t>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
       <c r="M60" s="13" t="inlineStr">
         <is>
-          <t>AC-01</t>
+          <t>AC-30</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr"/>
@@ -4951,7 +4951,7 @@
       <c r="R60" s="5" t="inlineStr"/>
       <c r="S60" s="8" t="inlineStr">
         <is>
-          <t>移行：既存顧客が壊れない</t>
+          <t>画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
@@ -4963,50 +4963,50 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>T-Z02</t>
+          <t>T-Z01</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>移行後の適用日付の付与</t>
+          <t>移行前後の突合（既存データ）</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
+          <t>【前提】S-09 S-11
+【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細 → 設定変更履歴／従業員設定履歴】
-適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている</t>
+          <t>【確認場所：従業員一覧】
+件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>T-Z02.png</t>
+          <t>T-Z01.png</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
+          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 設定変更履歴／従業員設定履歴 … 適用日付の空欄</t>
+          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>適用日付の空欄が0件か</t>
+          <t>移行前後で差分0件か</t>
         </is>
       </c>
       <c r="L61" s="13" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>AC-02</t>
+          <t>AC-01</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr"/>
@@ -5026,11 +5026,11 @@
       <c r="R61" s="5" t="inlineStr"/>
       <c r="S61" s="8" t="inlineStr">
         <is>
-          <t>移行：履歴の起点を作る</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="60" customHeight="1">
+          <t>移行：既存顧客が壊れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="79" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
           <t>横断</t>
@@ -5038,50 +5038,51 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>T-Z03</t>
+          <t>T-Z02</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>移行前後の過去月の人件費</t>
+          <t>移行後の適用日付の付与</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
           <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行前に出力しておいた直近3か月の人件費実績と、移行後の同3か月を突合する</t>
+【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
-3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
+          <t>【確認場所：従業員詳細 → 設定変更履歴／従業員設定履歴】
+適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている
+あわせて、すべての従業員に従業員IDが付番されている（未付番=0件）。外部IDは対応表に移されている</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>T-Z03.png</t>
+          <t>T-Z02.png</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>移行前後の人件費実績 月別実績（直近3か月・金額が同じであること）</t>
+          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ … 移行前後の直近3か月</t>
+          <t>従業員詳細 → 設定変更履歴／従業員設定履歴 … 適用日付の空欄</t>
         </is>
       </c>
       <c r="K62" s="8" t="inlineStr">
         <is>
-          <t>過去3か月の金額が変わらないか</t>
+          <t>適用日付の空欄が0件か</t>
         </is>
       </c>
       <c r="L62" s="13" t="inlineStr">
@@ -5091,7 +5092,7 @@
       </c>
       <c r="M62" s="13" t="inlineStr">
         <is>
-          <t>AC-03</t>
+          <t>AC-02 AC-55</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr"/>
@@ -5101,7 +5102,7 @@
       <c r="R62" s="5" t="inlineStr"/>
       <c r="S62" s="8" t="inlineStr">
         <is>
-          <t>移行：過去が動かない</t>
+          <t>移行：履歴の起点を作る</t>
         </is>
       </c>
     </row>
@@ -5113,60 +5114,60 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>T-Z04</t>
+          <t>T-Z03</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>サイドバーの構成</t>
+          <t>移行前後の過去月の人件費</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
+          <t>【前提】S-09 ／ T-Z01実施済み
+【操作】移行前に出力しておいた直近3か月の人件費実績と、移行後の同3か月を突合する</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：サイドバー「従業員管理」】
-閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>T-Z04.png</t>
+          <t>T-Z03.png</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
+          <t>移行前後の人件費実績 月別実績（直近3か月・金額が同じであること）</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
+          <t>人件費実績 → 月別実績タブ … 移行前後の直近3か月</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr">
         <is>
-          <t>PC・モバイルとも開くか</t>
+          <t>過去3か月の金額が変わらないか</t>
         </is>
       </c>
       <c r="L63" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・画面構成）</t>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>AC-29</t>
+          <t>AC-03</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr"/>
@@ -5176,7 +5177,7 @@
       <c r="R63" s="5" t="inlineStr"/>
       <c r="S63" s="8" t="inlineStr">
         <is>
-          <t>画面：たどり着ける</t>
+          <t>移行：過去が動かない</t>
         </is>
       </c>
     </row>
@@ -5188,60 +5189,60 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>T-Z05</t>
+          <t>T-Z04</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>遷移と表示規則の網羅</t>
+          <t>サイドバーの構成</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-05
-【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+          <t>【前提】S-01
+【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
-すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+          <t>【確認場所：サイドバー「従業員管理」】
+閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>T-Z05.png</t>
+          <t>T-Z04.png</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
+          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
         </is>
       </c>
       <c r="K64" s="8" t="inlineStr">
         <is>
-          <t>75本の遷移と表示規則</t>
+          <t>PC・モバイルとも開くか</t>
         </is>
       </c>
       <c r="L64" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・遷移網羅）</t>
+          <t>（ヘルプ記載なし・画面構成）</t>
         </is>
       </c>
       <c r="M64" s="13" t="inlineStr">
         <is>
-          <t>AC-30 AC-01</t>
+          <t>AC-29</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr"/>
@@ -5251,72 +5252,72 @@
       <c r="R64" s="5" t="inlineStr"/>
       <c r="S64" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="79" customHeight="1">
-      <c r="A65" s="14" t="inlineStr">
-        <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>C-000</t>
-        </is>
-      </c>
-      <c r="C65" s="15" t="inlineStr">
-        <is>
-          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
-        </is>
-      </c>
-      <c r="D65" s="15" t="inlineStr">
-        <is>
-          <t>【前提】S-03 S-05
-【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
-        </is>
-      </c>
-      <c r="E65" s="15" t="inlineStr">
-        <is>
-          <t>02〜06・13を再投入（初期化）</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="inlineStr">
-        <is>
-          <t>【確認場所：従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未】
-従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
-        </is>
-      </c>
-      <c r="G65" s="14" t="inlineStr">
-        <is>
-          <t>C-000.png</t>
-        </is>
-      </c>
-      <c r="H65" s="15" t="inlineStr">
-        <is>
-          <t>初期化後の従業員一覧（12名）と人件費実績（未締め・S-05時点の金額）</t>
+          <t>画面：たどり着ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>T-Z05</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>遷移と表示規則の網羅</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>【前提】S-04 S-05
+【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
+すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>T-Z05.png</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
-      <c r="J65" s="15" t="inlineStr">
-        <is>
-          <t>従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未締めに戻す）</t>
-        </is>
-      </c>
-      <c r="K65" s="15" t="inlineStr">
-        <is>
-          <t>S-05時点の値に戻ったか</t>
-        </is>
-      </c>
-      <c r="L65" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため対応なし）</t>
-        </is>
-      </c>
-      <c r="M65" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J65" s="12" t="inlineStr">
+        <is>
+          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+        </is>
+      </c>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>75本の遷移と表示規則</t>
+        </is>
+      </c>
+      <c r="L65" s="13" t="inlineStr">
+        <is>
+          <t>（ヘルプ記載なし・遷移網羅）</t>
+        </is>
+      </c>
+      <c r="M65" s="13" t="inlineStr">
+        <is>
+          <t>AC-30 AC-01</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr"/>
@@ -5324,13 +5325,13 @@
       <c r="P65" s="6" t="inlineStr"/>
       <c r="Q65" s="5" t="inlineStr"/>
       <c r="R65" s="5" t="inlineStr"/>
-      <c r="S65" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="64" customHeight="1">
+      <c r="S65" s="8" t="inlineStr">
+        <is>
+          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="79" customHeight="1">
       <c r="A66" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5338,60 +5339,60 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>C-001</t>
+          <t>C-000</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプなし）</t>
+          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-002（概算280,000・基礎時給1,750・深夜2h・所属店舗の交通費15,000）と EMP-007（概算300,000・基礎時給1,875・深夜4h・交通費30,000）を検算</t>
+          <t>【前提】S-03 S-05
+【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>02〜06・13を再投入（初期化）</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
+          <t>【確認場所：従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未】
+従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>C-001.png</t>
+          <t>C-000.png</t>
         </is>
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
+          <t>初期化後の従業員一覧（12名）と人件費実績（未締め・S-05時点の金額）</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
+          <t>従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未締めに戻す）</t>
         </is>
       </c>
       <c r="K66" s="15" t="inlineStr">
         <is>
-          <t>概算＋深夜＝実績給与か</t>
+          <t>S-05時点の値に戻ったか</t>
         </is>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>（初期化のため対応なし）</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr"/>
@@ -5401,11 +5402,11 @@
       <c r="R66" s="5" t="inlineStr"/>
       <c r="S66" s="15" t="inlineStr">
         <is>
-          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="79" customHeight="1">
+          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="64" customHeight="1">
       <c r="A67" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5413,60 +5414,60 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>C-003</t>
+          <t>C-001</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプあり）</t>
+          <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-001（概算320,000・深夜6h・ヘルプ22h／所属店舗の交通費18,000・ヘルプ先の交通費1,600）／EMP-005（概算350,000・深夜10h・ヘルプ35h／22,000・3,100）／EMP-003（概算144,000・ヘルプ20h／9,000・1,300）を検算</t>
+【操作】2026-05の EMP-002（概算280,000・基礎時給1,750・深夜2h・所属店舗の交通費15,000）と EMP-007（概算300,000・基礎時給1,875・深夜4h・交通費30,000）を検算</t>
         </is>
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
           <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算＋深夜＋みなし超過＋交通費）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
+EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>C-003.png</t>
+          <t>C-001.png</t>
         </is>
       </c>
       <c r="H67" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
+          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
+          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
         </is>
       </c>
       <c r="K67" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費が按分で振替されるか</t>
+          <t>概算＋深夜＝実績給与か</t>
         </is>
       </c>
       <c r="L67" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M67" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr"/>
@@ -5476,11 +5477,11 @@
       <c r="R67" s="5" t="inlineStr"/>
       <c r="S67" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="60" customHeight="1">
+          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="79" customHeight="1">
       <c r="A68" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5488,50 +5489,50 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>C-005</t>
+          <t>C-003</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計と全社合計の一致</t>
+          <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】2026-05の EMP-001（概算320,000・深夜6h・ヘルプ22h／所属店舗の交通費18,000・ヘルプ先の交通費1,600）／EMP-005（概算350,000・深夜10h・ヘルプ35h／22,000・3,100）／EMP-003（概算144,000・ヘルプ20h／9,000・1,300）を検算</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
           <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
+EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算＋深夜＋みなし超過＋交通費）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>C-005.png</t>
+          <t>C-003.png</t>
         </is>
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
+          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
+          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
         </is>
       </c>
       <c r="K68" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計＝全社（差0円）か</t>
+          <t>ヘルプ人件費が按分で振替されるか</t>
         </is>
       </c>
       <c r="L68" s="15" t="inlineStr">
@@ -5541,7 +5542,7 @@
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>AC-11</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr"/>
@@ -5551,11 +5552,11 @@
       <c r="R68" s="5" t="inlineStr"/>
       <c r="S68" s="15" t="inlineStr">
         <is>
-          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="79" customHeight="1">
+          <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="60" customHeight="1">
       <c r="A69" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5563,60 +5564,60 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>C-006</t>
+          <t>C-005</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>月中改定と予約の日割り</t>
+          <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>14 勤務データ 2026-06</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F69" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従】
-6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
+店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>C-006.png</t>
+          <t>C-005.png</t>
         </is>
       </c>
       <c r="H69" s="15" t="inlineStr">
         <is>
-          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
+          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
+          <t>人件費実績 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
         </is>
       </c>
       <c r="K69" s="15" t="inlineStr">
         <is>
-          <t>所定労働日割になっているか</t>
+          <t>店舗別合計＝全社（差0円）か</t>
         </is>
       </c>
       <c r="L69" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M69" s="15" t="inlineStr">
         <is>
-          <t>AC-12 AC-04</t>
+          <t>AC-11</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr"/>
@@ -5626,11 +5627,11 @@
       <c r="R69" s="5" t="inlineStr"/>
       <c r="S69" s="15" t="inlineStr">
         <is>
-          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="64" customHeight="1">
+          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="79" customHeight="1">
       <c r="A70" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5638,60 +5639,60 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>C-011</t>
+          <t>C-006</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>月中改定と予約の日割り</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
+【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・14 勤務データ 2026-06</t>
+          <t>14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
-5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従】
+6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>C-011.png</t>
+          <t>C-006.png</t>
         </is>
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
+          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
+          <t>人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
         </is>
       </c>
       <c r="K70" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>所定労働日割になっているか</t>
         </is>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>AC-13</t>
+          <t>AC-12 AC-04</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr"/>
@@ -5701,11 +5702,11 @@
       <c r="R70" s="5" t="inlineStr"/>
       <c r="S70" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="94" customHeight="1">
+          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="64" customHeight="1">
       <c r="A71" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5713,50 +5714,50 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-011</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>【前提】C-000 S-07 ／ data/14を投入
+【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績・14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
-判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>C-013.png</t>
+          <t>C-011.png</t>
         </is>
       </c>
       <c r="H71" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
+          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
+          <t>人件費実績 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
         <is>
-          <t>深夜1.5倍とヘルプの按分単価</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="L71" s="15" t="inlineStr">
@@ -5766,7 +5767,7 @@
       </c>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-13</t>
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr"/>
@@ -5776,11 +5777,11 @@
       <c r="R71" s="5" t="inlineStr"/>
       <c r="S71" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="79" customHeight="1">
+          <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="94" customHeight="1">
       <c r="A72" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5788,60 +5789,60 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-013</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績・日別実績】
-交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
+          <t>【確認場所：人件費実績 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
+判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>C-017.png</t>
+          <t>C-013.png</t>
         </is>
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
+          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+          <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
         </is>
       </c>
       <c r="K72" s="15" t="inlineStr">
         <is>
-          <t>交通費が給与と別費目か</t>
+          <t>深夜1.5倍とヘルプの按分単価</t>
         </is>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr"/>
@@ -5851,11 +5852,11 @@
       <c r="R72" s="5" t="inlineStr"/>
       <c r="S72" s="15" t="inlineStr">
         <is>
-          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="94" customHeight="1">
+          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="79" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5863,60 +5864,60 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-017</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>交通費の計上先</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07
-【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
-（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+          <t>【確認場所：人件費実績 → 月別実績・日別実績】
+交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>C-008.png</t>
+          <t>C-017.png</t>
         </is>
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
+          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+          <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>締め前後で差0円・解除後に再計算</t>
+          <t>交通費が給与と別費目か</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M73" s="15" t="inlineStr">
         <is>
-          <t>AC-16 AC-17</t>
+          <t>AC-15</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr"/>
@@ -5926,72 +5927,72 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
+          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
         </is>
       </c>
     </row>
     <row r="74" ht="94" customHeight="1">
-      <c r="A74" s="16" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B74" s="16" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C74" s="17" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="D74" s="17" t="inlineStr">
-        <is>
-          <t>【前提】S-01
-【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
-        </is>
-      </c>
-      <c r="E74" s="17" t="inlineStr">
-        <is>
-          <t>（追加のデータ投入なし）</t>
-        </is>
-      </c>
-      <c r="F74" s="17" t="inlineStr">
-        <is>
-          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
-①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
-        </is>
-      </c>
-      <c r="G74" s="16" t="inlineStr">
-        <is>
-          <t>R-01.png</t>
-        </is>
-      </c>
-      <c r="H74" s="17" t="inlineStr">
-        <is>
-          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>締めの前後で数字が動かないこと</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-07
+【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>C-008.png</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="inlineStr">
+        <is>
+          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
-      <c r="J74" s="17" t="inlineStr">
-        <is>
-          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
-        </is>
-      </c>
-      <c r="K74" s="17" t="inlineStr">
-        <is>
-          <t>適用日付と履歴がテーブルにあるか</t>
-        </is>
-      </c>
-      <c r="L74" s="17" t="inlineStr">
-        <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
-        </is>
-      </c>
-      <c r="M74" s="17" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47</t>
+      <c r="J74" s="15" t="inlineStr">
+        <is>
+          <t>人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+        </is>
+      </c>
+      <c r="K74" s="15" t="inlineStr">
+        <is>
+          <t>締め前後で差0円・解除後に再計算</t>
+        </is>
+      </c>
+      <c r="L74" s="15" t="inlineStr">
+        <is>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
+        </is>
+      </c>
+      <c r="M74" s="15" t="inlineStr">
+        <is>
+          <t>AC-16 AC-17</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr"/>
@@ -5999,13 +6000,13 @@
       <c r="P74" s="6" t="inlineStr"/>
       <c r="Q74" s="5" t="inlineStr"/>
       <c r="R74" s="5" t="inlineStr"/>
-      <c r="S74" s="17" t="inlineStr">
-        <is>
-          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="79" customHeight="1">
+      <c r="S74" s="15" t="inlineStr">
+        <is>
+          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="124" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6013,18 +6014,18 @@
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>締めの実装レビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="D75" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
+【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
         </is>
       </c>
       <c r="E75" s="17" t="inlineStr">
@@ -6034,39 +6035,39 @@
       </c>
       <c r="F75" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
-①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
+          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
+①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）</t>
         </is>
       </c>
       <c r="G75" s="16" t="inlineStr">
         <is>
-          <t>R-02.png</t>
+          <t>R-01.png</t>
         </is>
       </c>
       <c r="H75" s="17" t="inlineStr">
         <is>
-          <t>締めAPIのコードとスコープ判定箇所</t>
+          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
+          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
       </c>
       <c r="K75" s="17" t="inlineStr">
         <is>
-          <t>APIでも店長が締められないか</t>
+          <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
       <c r="L75" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M75" s="17" t="inlineStr">
         <is>
-          <t>AC-16 AC-41</t>
+          <t>AC-07 AC-40 AC-47 AC-55</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
@@ -6076,11 +6077,11 @@
       <c r="R75" s="5" t="inlineStr"/>
       <c r="S75" s="17" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="109" customHeight="1">
+          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="79" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6088,18 +6089,18 @@
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>入力検証とトランザクションのレビュー</t>
+          <t>締めの実装レビュー</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
+【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -6109,39 +6110,39 @@
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
-①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
+          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
+①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
         </is>
       </c>
       <c r="G76" s="16" t="inlineStr">
         <is>
-          <t>R-03.png</t>
+          <t>R-02.png</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
+          <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
+          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
       </c>
       <c r="K76" s="17" t="inlineStr">
         <is>
-          <t>APIを直接呼んでも弾かれるか</t>
+          <t>APIでも店長が締められないか</t>
         </is>
       </c>
       <c r="L76" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 設定が保存できません</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M76" s="17" t="inlineStr">
         <is>
-          <t>AC-23 AC-42 AC-43</t>
+          <t>AC-16 AC-41</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr"/>
@@ -6151,11 +6152,11 @@
       <c r="R76" s="5" t="inlineStr"/>
       <c r="S76" s="17" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="79" customHeight="1">
+          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="109" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6163,18 +6164,18 @@
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの共有レビュー</t>
+          <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
       <c r="E77" s="17" t="inlineStr">
@@ -6184,39 +6185,39 @@
       </c>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
-同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
+          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
+①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
         </is>
       </c>
       <c r="G77" s="16" t="inlineStr">
         <is>
-          <t>R-04.png</t>
+          <t>R-03.png</t>
         </is>
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
+          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
+          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
       </c>
       <c r="K77" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックが1箇所か</t>
+          <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
       <c r="L77" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
       <c r="M77" s="17" t="inlineStr">
         <is>
-          <t>AC-35 AC-11</t>
+          <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
@@ -6226,11 +6227,11 @@
       <c r="R77" s="5" t="inlineStr"/>
       <c r="S77" s="17" t="inlineStr">
         <is>
-          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="64" customHeight="1">
+          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="79" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6238,18 +6239,18 @@
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>計算ロジックの共有レビュー</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込の列解決の実装を提示してもらう</t>
+【操作】人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
@@ -6259,39 +6260,39 @@
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
-CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
+          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
+同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
         </is>
       </c>
       <c r="G78" s="16" t="inlineStr">
         <is>
-          <t>R-05.png</t>
+          <t>R-04.png</t>
         </is>
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
+          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
+          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
         </is>
       </c>
       <c r="K78" s="17" t="inlineStr">
         <is>
-          <t>列名がコードに埋まっていないか</t>
+          <t>計算ロジックが1箇所か</t>
         </is>
       </c>
       <c r="L78" s="17" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-35 AC-11</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
@@ -6301,11 +6302,11 @@
       <c r="R78" s="5" t="inlineStr"/>
       <c r="S78" s="17" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="79" customHeight="1">
+          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="64" customHeight="1">
       <c r="A79" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6313,18 +6314,18 @@
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>設定更新処理の共通化レビュー</t>
+          <t>列マッピングの実装レビュー</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+【操作】取込の列解決の実装を提示してもらう</t>
         </is>
       </c>
       <c r="E79" s="17" t="inlineStr">
@@ -6334,39 +6335,39 @@
       </c>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
-設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
+CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
       <c r="G79" s="16" t="inlineStr">
         <is>
-          <t>R-06.png</t>
+          <t>R-05.png</t>
         </is>
       </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
-          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
         </is>
       </c>
       <c r="K79" s="17" t="inlineStr">
         <is>
-          <t>2つの入口で更新処理が共通か</t>
+          <t>列名がコードに埋まっていないか</t>
         </is>
       </c>
       <c r="L79" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M79" s="17" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-22 AC-24</t>
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr"/>
@@ -6376,17 +6377,92 @@
       <c r="R79" s="5" t="inlineStr"/>
       <c r="S79" s="17" t="inlineStr">
         <is>
+          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="79" customHeight="1">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
+設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="G80" s="16" t="inlineStr">
+        <is>
+          <t>R-06.png</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr"/>
+      <c r="J80" s="17" t="inlineStr">
+        <is>
+          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+        </is>
+      </c>
+      <c r="K80" s="17" t="inlineStr">
+        <is>
+          <t>2つの入口で更新処理が共通か</t>
+        </is>
+      </c>
+      <c r="L80" s="17" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="M80" s="17" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="N80" s="5" t="inlineStr"/>
+      <c r="O80" s="5" t="inlineStr"/>
+      <c r="P80" s="6" t="inlineStr"/>
+      <c r="Q80" s="5" t="inlineStr"/>
+      <c r="R80" s="5" t="inlineStr"/>
+      <c r="S80" s="17" t="inlineStr">
+        <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S79"/>
+  <autoFilter ref="A2:S80"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3:O79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S80"/>
+  <dimension ref="A1:S81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証67ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
+          <t>確かめる手順（準備11行＋検証68ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
 実施順を変えてはいけない箇所：①T-A08（勤怠取込）→T-S03（締め）　②T-S03→T-S04・T-D07→T-S05（この3件は締め済みでしか確認できない）　③C-000（初期化）は計算の先頭　④C-008は計算の最後（2026-05のEMP-001を352,286円に変えるためC-013・C-017が合わなくなる）　⑤T-N02の前にdata/02を再投入　⑥削除はEMP-012（T-L10）とEMP-004（T-D08）だけ
 列の使い方：使用する検証データ＝この検証で投入・使用するdataファイル／期待値＝先頭の【確認場所】でどの画面を見て合否を出すかを示し、続けて合格の基準を書いている／スクショ（撮るもの）＝何が写っていれば証拠になるか／スクショ貼付欄＝撮った画像をこの列に貼る／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めて合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを決める
 色：緑＝使う検証データ　青＝画面　橙＝スクショの指示　紫＝ヘルプ・受入条件との対応　黄＝当日の記入欄。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="79" customHeight="1">
+    <row r="26" ht="94" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
           <t>詳細</t>
@@ -2349,7 +2349,7 @@
       <c r="D26" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】従業員詳細の給与実績セクションを開き、月次実績・日次実績のタブを切り替える。年フィルタ・給与計算モード・CSVエクスポートが無いことを確認し、右上「すべての実績」を押す</t>
+【操作】従業員詳細の給与実績で、見出し右の「概算モード」「実績モード」を切り替える。月次実績・日次実績のタブも切り替える。絞り込みとCSVエクスポートが無いことを確認し、右上「すべての実績」を押す</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -2360,7 +2360,7 @@
       <c r="F26" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員詳細 → 給与実績】
-月次は直近3か月が実績モードで表示される。絞り込みとCSVエクスポートは無い（詳細に残っている数=0件）。「すべての実績」で給与実績一覧が開き、EMP-001で絞り込まれている</t>
+概算⇄実績で表示列が増減する。直近3か月が表示され、実績データ取込の前でも概算モードで金額が出る（空欄=0件）。絞り込みとCSVエクスポートは無い（残っている数=0件）。「すべての実績」で給与実績一覧が開き、EMP-001で絞り込まれている</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="M26" s="13" t="inlineStr">
         <is>
-          <t>AC-54</t>
+          <t>AC-54 AC-57</t>
         </is>
       </c>
       <c r="N26" s="5" t="inlineStr"/>
@@ -2480,68 +2480,68 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="64" customHeight="1">
+    <row r="28" ht="79" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>詳細</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>T-D08</t>
+          <t>T-P02</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>詳細の削除・戻る</t>
+          <t>概算モードと差分の表示</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】EMP-004（山本 健／実績データにも取込CSVにも含まれない）の詳細を開き「従業員削除」→（a）キャンセル →（b）実行、（c）別の従業員で「一覧へ戻る」</t>
+          <t>【前提】S-05
+【操作】（a）給与実績一覧で給与計算モードを 概算 → 実績 に切り替える →（b）実績モードで 想定給与・給与実績差分 を確認する →（c）実績データ取込を行っていない月（当月）を範囲に含めて概算モードで表示する</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>（投入済み）05 月次給与実績</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細】
-（a）削除されず件数が変わらない （b）確認のあと削除される （c）一覧へ戻る（保存されない）</t>
+          <t>【確認場所：給与実績一覧 → 月次実績】
+（a）概算モードでは基本列のみ、実績モードで実績列が追加される（b）給与実績差分＝給与−想定給与（計算違い0件）（c）実績がまだ無い月でも概算モードで金額が表示される（空欄=0件）</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>T-D08.png</t>
+          <t>T-P02.png</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>削除の確認モーダル／実行後の一覧（行が消えたこと）</t>
+          <t>概算モードと実績モードの両方（列の増減が比較できること）／想定給与と給与実績差分が読める範囲／実績がまだ無い月を概算モードで表示した状態</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 … 下部「従業員削除」→ 確認モーダル／「一覧へ戻る」→ 従業員一覧</t>
+          <t>給与実績一覧 → 月次実績タブ … 給与計算モード（概算／実績）</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>キャンセルで消えない／実行で消えるか</t>
+          <t>モードで列が増減するか／差分が正しいか</t>
         </is>
       </c>
       <c r="L28" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員を探す・削除する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M28" s="13" t="inlineStr">
         <is>
-          <t>AC-34 AC-30</t>
+          <t>AC-57</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr"/>
@@ -2551,11 +2551,11 @@
       <c r="R28" s="5" t="inlineStr"/>
       <c r="S28" s="8" t="inlineStr">
         <is>
-          <t>データ保全：消える操作は確認を経る／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="109" customHeight="1">
+          <t>画面：実績が出る前も金額が見える</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="64" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
           <t>詳細</t>
@@ -2563,60 +2563,60 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>T-D11</t>
+          <t>T-D08</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>設定変更履歴の表示ルール</t>
+          <t>詳細の削除・戻る</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-05
-【操作】EMP-001の詳細を開き、（a）並び順とステータス列の位置を確認 →（b）単位給与額を380,000に変更し適用日付＝翌々月1日で保存 →（c）保存後の履歴の最上部と強調を確認 →（d）右上「すべての履歴」を押す</t>
+          <t>【前提】S-04
+【操作】EMP-004（山本 健／実績データにも取込CSVにも含まれない）の詳細を開き「従業員削除」→（a）キャンセル →（b）実行、（c）別の従業員で「一覧へ戻る」</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）04 設定変更履歴</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細 → 設定変更履歴】
-（a）並びは変更反映日時の降順で、予約中が最上部。ステータスは変更反映日時の次（2列目）にあり横スクロールなしで見える。表示は直近3件（b・c）保存した行が最上部に増え、1つ古い行と値が違う項目（単位給与額）だけが強調される。強調の過不足=0件（d）従業員設定履歴が開き、EMP-001で絞り込まれた状態になる（絞り込みなしでの遷移=0件）</t>
+          <t>【確認場所：従業員詳細】
+（a）削除されず件数が変わらない （b）確認のあと削除される （c）一覧へ戻る（保存されない）</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>T-D11.png</t>
+          <t>T-D08.png</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>保存前後の履歴セクション2枚（並び順とステータス列の位置が分かる範囲）／強調された項目／「すべての履歴」で開いた従業員設定履歴（絞り込み条件が見える状態）</t>
+          <t>削除の確認モーダル／実行後の一覧（行が消えたこと）</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 設定変更履歴セクション … 右上「すべての履歴」→ 従業員設定履歴（EMP-001で絞り込み済み）</t>
+          <t>従業員詳細 … 下部「従業員削除」→ 確認モーダル／「一覧へ戻る」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>保存した行が最上部に来るか／変更点だけ強調されるか</t>
+          <t>キャンセルで消えない／実行で消えるか</t>
         </is>
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
       <c r="M29" s="13" t="inlineStr">
         <is>
-          <t>AC-52 AC-53</t>
+          <t>AC-34 AC-30</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr"/>
@@ -2626,72 +2626,72 @@
       <c r="R29" s="5" t="inlineStr"/>
       <c r="S29" s="8" t="inlineStr">
         <is>
-          <t>画面：保存できたか確かめられる／画面：変更点が読み取れる</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
+          <t>データ保全：消える操作は確認を経る／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="109" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>詳細</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>T-H01</t>
+          <t>T-D11</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>履歴の追記と過去行の不変</t>
+          <t>設定変更履歴の表示ルール</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 ／ 変更前の履歴をCSV出力しておく
-【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
+          <t>【前提】S-04 S-05
+【操作】EMP-001の詳細を開き、（a）並び順とステータス列の位置を確認 →（b）単位給与額を380,000に変更し適用日付＝翌々月1日で保存 →（c）保存後の履歴の最上部と強調を確認 →（d）右上「すべての履歴」を押す</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）04 設定変更履歴</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員設定履歴】
-履歴が1行増える。既存行の値の差分＝0</t>
+          <t>【確認場所：従業員詳細 → 設定変更履歴】
+（a）並びは変更反映日時の降順で、予約中が最上部。ステータスは変更反映日時の次（2列目）にあり横スクロールなしで見える。表示は直近3件（b・c）保存した行が最上部に増え、1つ古い行と値が違う項目（単位給与額）だけが強調される。強調の過不足=0件（d）従業員設定履歴が開き、EMP-001で絞り込まれた状態になる（絞り込みなしでの遷移=0件）</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>T-H01.png</t>
+          <t>T-D11.png</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
+          <t>保存前後の履歴セクション2枚（並び順とステータス列の位置が分かる範囲）／強調された項目／「すべての履歴」で開いた従業員設定履歴（絞り込み条件が見える状態）</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>従業員設定履歴 … 変更前後の行（既存行が書き換わらないこと）</t>
+          <t>従業員詳細 → 設定変更履歴セクション … 右上「すべての履歴」→ 従業員設定履歴（EMP-001で絞り込み済み）</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>既存行が書き換わらないか</t>
+          <t>保存した行が最上部に来るか／変更点だけ強調されるか</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
       <c r="M30" s="13" t="inlineStr">
         <is>
-          <t>AC-07</t>
+          <t>AC-52 AC-53</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr"/>
@@ -2701,11 +2701,11 @@
       <c r="R30" s="5" t="inlineStr"/>
       <c r="S30" s="8" t="inlineStr">
         <is>
-          <t>原則①：過去は不変</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="79" customHeight="1">
+          <t>画面：保存できたか確かめられる／画面：変更点が読み取れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2713,18 +2713,18 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>T-H02</t>
+          <t>T-H01</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>記録の内容</t>
+          <t>履歴の追記と過去行の不変</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 T-D04実施済み
-【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
+          <t>【前提】S-05 ／ 変更前の履歴をCSV出力しておく
+【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -2735,28 +2735,28 @@
       <c r="F31" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員設定履歴】
-①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
+履歴が1行増える。既存行の値の差分＝0</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>T-H02.png</t>
+          <t>T-H01.png</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
+          <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>従業員設定履歴 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
+          <t>従業員設定履歴 … 変更前後の行（既存行が書き換わらないこと）</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>2つの日時が別で記録されるか</t>
+          <t>既存行が書き換わらないか</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>AC-08 AC-09</t>
+          <t>AC-07</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr"/>
@@ -2776,11 +2776,11 @@
       <c r="R31" s="5" t="inlineStr"/>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="94" customHeight="1">
+          <t>原則①：過去は不変</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="79" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2788,18 +2788,18 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>T-H04</t>
+          <t>T-H02</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>履歴の絞り込み・出力・遷移</t>
+          <t>記録の内容</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
+          <t>【前提】S-05 T-D04実施済み
+【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2810,28 +2810,28 @@
       <c r="F32" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員設定履歴】
-店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
+①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>T-H04.png</t>
+          <t>T-H02.png</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
+          <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>従業員設定履歴 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
+          <t>従業員設定履歴 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>絞り込み後の行だけ出力されるか</t>
+          <t>2つの日時が別で記録されるか</t>
         </is>
       </c>
       <c r="L32" s="13" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="M32" s="13" t="inlineStr">
         <is>
-          <t>AC-33 AC-36 AC-30</t>
+          <t>AC-08 AC-09</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr"/>
@@ -2851,30 +2851,30 @@
       <c r="R32" s="5" t="inlineStr"/>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="124" customHeight="1">
+          <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="94" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>履歴</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>T-A02</t>
+          <t>T-H04</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>月別実績の表示と切替</t>
+          <t>履歴の絞り込み・出力・遷移</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
+【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2884,39 +2884,39 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
-全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない</t>
+          <t>【確認場所：従業員設定履歴】
+店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>T-A02.png</t>
+          <t>T-H04.png</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
+          <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
+          <t>従業員設定履歴 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>モード切替で列が増減するか</t>
+          <t>絞り込み後の行だけ出力されるか</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr">
         <is>
-          <t>AC-10 AC-31</t>
+          <t>AC-33 AC-36 AC-30</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
@@ -2926,11 +2926,11 @@
       <c r="R33" s="5" t="inlineStr"/>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>計算：算式どおりの金額／画面：状態が漏れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="64" customHeight="1">
+          <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="154" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -2938,18 +2938,18 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>T-A09</t>
+          <t>T-A02</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>人件費実績からの設定編集</t>
+          <t>月別実績の表示と切替</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】人件費実績で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
+【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2959,39 +2959,40 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　行の「従業員設定」】
-モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない
+実績モードでは 想定給与・給与・給与実績差分 が表示され、差分＝給与−想定給与 と一致する</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>T-A09.png</t>
+          <t>T-A02.png</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>設定編集モーダル（項目が見える状態）／更新保存後の人件費実績／従業員詳細の設定変更履歴に行が増えたこと</t>
+          <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 人件費実績／確認は従業員詳細の設定変更履歴</t>
+          <t>人件費実績 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>モーダル編集でも履歴が残るか</t>
+          <t>モード切替で列が増減するか</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M34" s="13" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-10 AC-31 AC-57</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr"/>
@@ -3001,11 +3002,11 @@
       <c r="R34" s="5" t="inlineStr"/>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>原則①：どの入口から編集しても履歴が残る</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="109" customHeight="1">
+          <t>計算：算式どおりの金額／画面：状態が漏れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="64" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -3013,18 +3014,18 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>T-A05</t>
+          <t>T-A09</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>日別実績の表示</t>
+          <t>人件費実績からの設定編集</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
+【操作】人件費実績で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -3034,39 +3035,39 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 日別実績タブ】
-全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
+          <t>【確認場所：人件費実績　→　行の「従業員設定」】
+モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>T-A05.png</t>
+          <t>T-A09.png</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
+          <t>設定編集モーダル（項目が見える状態）／更新保存後の人件費実績／従業員詳細の設定変更履歴に行が増えたこと</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
+          <t>人件費実績 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 人件費実績／確認は従業員詳細の設定変更履歴</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>日別に概算モードが無いか</t>
+          <t>モーダル編集でも履歴が残るか</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>AC-49</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr"/>
@@ -3076,11 +3077,11 @@
       <c r="R35" s="5" t="inlineStr"/>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>計算：算式どおりの金額</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="64" customHeight="1">
+          <t>原則①：どの入口から編集しても履歴が残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="109" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -3088,18 +3089,18 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>T-A07</t>
+          <t>T-A05</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>実績のCSVエクスポート</t>
+          <t>日別実績の表示</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
+【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -3109,39 +3110,39 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績】
-出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
+          <t>【確認場所：人件費実績 → 日別実績タブ】
+全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>T-A07.png</t>
+          <t>T-A05.png</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
+          <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
+          <t>人件費実績 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>表示中の内容が出力されるか</t>
+          <t>日別に概算モードが無いか</t>
         </is>
       </c>
       <c r="L36" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M36" s="13" t="inlineStr">
         <is>
-          <t>AC-36</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr"/>
@@ -3151,7 +3152,7 @@
       <c r="R36" s="5" t="inlineStr"/>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>入出力：画面の内容と一致</t>
+          <t>計算：算式どおりの金額</t>
         </is>
       </c>
     </row>
@@ -3163,18 +3164,18 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>T-A08</t>
+          <t>T-A07</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>勤怠実績の取込</t>
+          <t>実績のCSVエクスポート</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-08
-【操作】人件費実績の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
+          <t>【前提】S-05
+【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -3184,39 +3185,39 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
-「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
+          <t>【確認場所：人件費実績】
+出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>T-A08.png</t>
+          <t>T-A07.png</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
+          <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
+          <t>人件費実績 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>進捗が出て他操作を受け付けないか</t>
+          <t>表示中の内容が出力されるか</t>
         </is>
       </c>
       <c r="L37" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M37" s="13" t="inlineStr">
         <is>
-          <t>AC-48</t>
+          <t>AC-36</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr"/>
@@ -3226,62 +3227,62 @@
       <c r="R37" s="5" t="inlineStr"/>
       <c r="S37" s="8" t="inlineStr">
         <is>
-          <t>入出力：勤怠実績を取り込める</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1">
+          <t>入出力：画面の内容と一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="64" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>締め</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>T-S01</t>
+          <t>T-A08</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>締めボタンの表示条件</t>
+          <t>勤怠実績の取込</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-08
-【操作】月別実績タブと日別実績タブを順に開く</t>
+          <t>【前提】S-05 S-08
+【操作】人件費実績の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績】
-月別のみ「2026-05 締め」が表示。日別には表示されない</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>T-S01.png</t>
+          <t>T-A08.png</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
+          <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
+          <t>人件費実績 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>締めが月別タブにだけ出るか</t>
+          <t>進捗が出て他操作を受け付けないか</t>
         </is>
       </c>
       <c r="L38" s="13" t="inlineStr">
@@ -3291,7 +3292,7 @@
       </c>
       <c r="M38" s="13" t="inlineStr">
         <is>
-          <t>AC-18</t>
+          <t>AC-48</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr"/>
@@ -3301,11 +3302,11 @@
       <c r="R38" s="5" t="inlineStr"/>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めの単位は月</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="64" customHeight="1">
+          <t>入出力：勤怠実績を取り込める</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3313,18 +3314,18 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>T-S03</t>
+          <t>T-S01</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>締めの実行</t>
+          <t>締めボタンの表示条件</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06 S-08
-【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
+          <t>【前提】S-08
+【操作】月別実績タブと日別実績タブを順に開く</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -3334,29 +3335,29 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
-「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
+          <t>【確認場所：人件費実績】
+月別のみ「2026-05 締め」が表示。日別には表示されない</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>T-S03.png</t>
+          <t>T-S01.png</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
+          <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
+          <t>人件費実績 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>確認モーダルを経て締まるか</t>
+          <t>締めが月別タブにだけ出るか</t>
         </is>
       </c>
       <c r="L39" s="13" t="inlineStr">
@@ -3366,7 +3367,7 @@
       </c>
       <c r="M39" s="13" t="inlineStr">
         <is>
-          <t>AC-16 AC-19 AC-32</t>
+          <t>AC-18</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr"/>
@@ -3376,11 +3377,11 @@
       <c r="R39" s="5" t="inlineStr"/>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1">
+          <t>原則②：締めの単位は月</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="64" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3388,18 +3389,18 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>T-S04</t>
+          <t>T-S03</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>締め後は編集できない</t>
+          <t>締めの実行</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み
-【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
+          <t>【前提】S-06 S-08
+【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -3409,39 +3410,39 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績】
-編集できない（または反映されない）</t>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>T-S04.png</t>
+          <t>T-S03.png</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
+          <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
+          <t>人件費実績 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>締め後に金額が動かないか</t>
+          <t>確認モーダルを経て締まるか</t>
         </is>
       </c>
       <c r="L40" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M40" s="13" t="inlineStr">
         <is>
-          <t>AC-16</t>
+          <t>AC-16 AC-19 AC-32</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr"/>
@@ -3451,7 +3452,7 @@
       <c r="R40" s="5" t="inlineStr"/>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない</t>
+          <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
         </is>
       </c>
     </row>
@@ -3463,18 +3464,18 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>T-D07</t>
+          <t>T-S04</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>締め済み期間への遡及</t>
+          <t>締め後は編集できない</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み S-07
-【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
+          <t>【前提】T-S03実施済み
+【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -3484,39 +3485,39 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細】
-締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
+          <t>【確認場所：人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績】
+編集できない（または反映されない）</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>T-D07.png</t>
+          <t>T-S04.png</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
+          <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
+          <t>人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>警告が出て反映されないか</t>
+          <t>締め後に金額が動かないか</t>
         </is>
       </c>
       <c r="L41" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="M41" s="13" t="inlineStr">
         <is>
-          <t>AC-20</t>
+          <t>AC-16</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr"/>
@@ -3526,11 +3527,11 @@
       <c r="R41" s="5" t="inlineStr"/>
       <c r="S41" s="8" t="inlineStr">
         <is>
-          <t>原則②：遡及は黙って捨てない</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="64" customHeight="1">
+          <t>原則②：締めたら動かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3538,18 +3539,18 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>T-S05</t>
+          <t>T-D07</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>締めの解除</t>
+          <t>締め済み期間への遡及</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み
-【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
+          <t>【前提】T-S03実施済み S-07
+【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -3559,39 +3560,39 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
-「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
+          <t>【確認場所：従業員詳細】
+締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>T-S05.png</t>
+          <t>T-D07.png</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
+          <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
+          <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
         </is>
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>解除で再計算されるか</t>
+          <t>警告が出て反映されないか</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
       <c r="M42" s="13" t="inlineStr">
         <is>
-          <t>AC-19</t>
+          <t>AC-20</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr"/>
@@ -3601,7 +3602,7 @@
       <c r="R42" s="5" t="inlineStr"/>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t>原則②：確定操作は確認を経る</t>
+          <t>原則②：遡及は黙って捨てない</t>
         </is>
       </c>
     </row>
@@ -3613,18 +3614,18 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>T-S07</t>
+          <t>T-S05</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>締めの実行権限</t>
+          <t>締めの解除</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-10 S-08
-【操作】店長スコープのアカウントでログインし、人件費実績を開いて締めを試みる</t>
+          <t>【前提】T-S03実施済み
+【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -3634,39 +3635,39 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ（店長スコープでログイン）】
-締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>T-S07.png</t>
+          <t>T-S05.png</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>店長スコープでの人件費実績（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
+          <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
+          <t>人件費実績 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>店長が締められないか</t>
+          <t>解除で再計算されるか</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="M43" s="13" t="inlineStr">
         <is>
-          <t>AC-41</t>
+          <t>AC-19</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr"/>
@@ -3676,30 +3677,30 @@
       <c r="R43" s="5" t="inlineStr"/>
       <c r="S43" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="79" customHeight="1">
+          <t>原則②：確定操作は確認を経る</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="64" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>取込</t>
+          <t>締め</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>T-I02</t>
+          <t>T-S07</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>テンプレートのDLと画面</t>
+          <t>締めの実行権限</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
+          <t>【前提】S-10 S-08
+【操作】店長スコープのアカウントでログインし、人件費実績を開いて締めを試みる</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -3709,39 +3710,39 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ（店長スコープでログイン）】
+締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>T-I02.png</t>
+          <t>T-S07.png</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
+          <t>店長スコープでの人件費実績（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
+          <t>人件費実績 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>テンプレートの列とBOM</t>
+          <t>店長が締められないか</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ はじめて設定する</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>AC-21 AC-30</t>
+          <t>AC-41</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr"/>
@@ -3751,7 +3752,7 @@
       <c r="R44" s="5" t="inlineStr"/>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
+          <t>原則②：締めは会社スコープのみ</t>
         </is>
       </c>
     </row>
@@ -3763,50 +3764,50 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>T-I03</t>
+          <t>T-I02</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>King of Time形式の取込</t>
+          <t>テンプレートのDLと画面</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-06
-【操作】データ種類＝King of Time を選び data/07（従業員設定・3行／外部ID 1001・1005・1013）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
+          <t>【前提】S-01
+【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート → 従業員一覧】
-外部ID 1001・1005 は対応表で E0001・E0005 に解決され、既存の従業員が更新される（単位給与額 340,000／360,000）。対応表に無い 1013 は新規として扱われ、従業員IDが自動で付番される。件数は3行</t>
+          <t>【確認場所：設定インポート】
+従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>T-I03.png</t>
+          <t>T-I02.png</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
+          <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
+          <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>3行が更新・追加されるか</t>
+          <t>テンプレートの列とBOM</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
@@ -3816,7 +3817,7 @@
       </c>
       <c r="M45" s="13" t="inlineStr">
         <is>
-          <t>AC-21</t>
+          <t>AC-21 AC-30</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr"/>
@@ -3826,11 +3827,11 @@
       <c r="R45" s="5" t="inlineStr"/>
       <c r="S45" s="8" t="inlineStr">
         <is>
-          <t>入出力：導入を止めない</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="60" customHeight="1">
+          <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="79" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3838,50 +3839,50 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>T-I04</t>
+          <t>T-I03</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>ジョブカン形式（表記ゆれ）の取込</t>
+          <t>King of Time形式の取込</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】データ種類＝ジョブカン を選び data/08（3行／外部ID JB-003・JB-010・JB-014）をD&amp;D → 登録</t>
+【操作】データ種類＝King of Time を選び data/07（従業員設定・3行／外部ID 1001・1005・1013）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>08 取込CSV ジョブカン</t>
+          <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート → 従業員一覧】
-スタッフコード等の表記ゆれを吸収し、外部ID JB-003・JB-010 が E0003・E0010 に解決される。取込成功=3行</t>
+外部ID 1001・1005 は対応表で E0001・E0005 に解決され、既存の従業員が更新される（単位給与額 340,000／360,000）。対応表に無い 1013 は新規として扱われ、従業員IDが自動で付番される。件数は3行</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>T-I04.png</t>
+          <t>T-I03.png</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
+          <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
+          <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>表記ゆれを吸収できるか</t>
+          <t>3行が更新・追加されるか</t>
         </is>
       </c>
       <c r="L46" s="13" t="inlineStr">
@@ -3891,7 +3892,7 @@
       </c>
       <c r="M46" s="13" t="inlineStr">
         <is>
-          <t>AC-22</t>
+          <t>AC-21</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr"/>
@@ -3901,7 +3902,7 @@
       <c r="R46" s="5" t="inlineStr"/>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収</t>
+          <t>入出力：導入を止めない</t>
         </is>
       </c>
     </row>
@@ -3913,60 +3914,60 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>T-I05</t>
+          <t>T-I04</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>異常系データの検出</t>
+          <t>ジョブカン形式（表記ゆれ）の取込</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】data/09（4行）をD&amp;D → 登録</t>
+【操作】データ種類＝ジョブカン を選び data/08（3行／外部ID JB-003・JB-010・JB-014）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>08 取込CSV ジョブカン</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
+          <t>【確認場所：設定インポート → 従業員一覧】
+スタッフコード等の表記ゆれを吸収し、外部ID JB-003・JB-010 が E0003・E0010 に解決される。取込成功=3行</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>T-I05.png</t>
+          <t>T-I04.png</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
+          <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
+          <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>4種の異常を行ごとに検出するか</t>
+          <t>表記ゆれを吸収できるか</t>
         </is>
       </c>
       <c r="L47" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
+          <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
       <c r="M47" s="13" t="inlineStr">
         <is>
-          <t>AC-23</t>
+          <t>AC-22</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr"/>
@@ -3976,11 +3977,11 @@
       <c r="R47" s="5" t="inlineStr"/>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="64" customHeight="1">
+          <t>入出力：表記ゆれを吸収</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3988,50 +3989,50 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>T-I17</t>
+          <t>T-I05</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>二重登録の防止</t>
+          <t>異常系データの検出</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】（a）data/07を2回続けて取り込む （b）data/19（外部ID 1002 が2行・単位給与額が異なる）を取り込む</t>
+【操作】data/09（4行）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート】
-（a）2回目は更新となり件数が増えない（二重登録=0件）（b）同じ外部IDが2行あるためエラーとして検出され、両方とも登録されない。1つの外部IDが2つの従業員IDに紐づく=0件</t>
+4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>T-I17.png</t>
+          <t>T-I05.png</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
+          <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
+          <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>二重登録されないか</t>
+          <t>4種の異常を行ごとに検出するか</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
@@ -4041,7 +4042,7 @@
       </c>
       <c r="M48" s="13" t="inlineStr">
         <is>
-          <t>AC-40 AC-56</t>
+          <t>AC-23</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr"/>
@@ -4051,11 +4052,11 @@
       <c r="R48" s="5" t="inlineStr"/>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>データ保全：二重登録を防ぐ</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="94" customHeight="1">
+          <t>データ保全：不正値を入れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="64" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4063,60 +4064,60 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>T-I20</t>
+          <t>T-I17</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>外部IDの対応と付番</t>
+          <t>二重登録の防止</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】（a）data/20 の対応表を開き、EMP-001 が King of Time 1001 とジョブカン JB-001 の2件を持つことを確認 →（b）対応表に無い外部ID（例 9999）を含むCSVを取り込む →（c）取り込んだ従業員の従業員IDを従業員一覧で確認する</t>
+【操作】（a）data/07を2回続けて取り込む （b）data/19（外部ID 1002 が2行・単位給与額が異なる）を取り込む</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>20 外部ID対応表／07 取込CSV KingOfTime</t>
+          <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：列マッピングテンプレート（外部ID対応）→ 設定インポート → 従業員一覧】
-（a）1名が複数の勤怠システムの外部IDを持てる（E0001＝1001／JB-001）（b）対応表に無い外部IDは取り込まれず、件数と理由が表示される（黙って登録=0件）（c）すべての従業員に従業員IDが付いている（未付番=0件）</t>
+          <t>【確認場所：設定インポート】
+（a）2回目は更新となり件数が増えない（二重登録=0件）（b）同じ外部IDが2行あるためエラーとして検出され、両方とも登録されない。1つの外部IDが2つの従業員IDに紐づく=0件</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>T-I20.png</t>
+          <t>T-I17.png</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>外部ID対応表（EMP-001が2システム分ある状態）／対応表に無い外部IDのエラー表示／従業員一覧の従業員ID列</t>
+          <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート（外部IDの対応）→ 設定インポート → 従業員一覧</t>
+          <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>外部IDが従業員IDに解決されるか／未登録は弾かれるか</t>
+          <t>二重登録されないか</t>
         </is>
       </c>
       <c r="L49" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>AC-55 AC-56</t>
+          <t>AC-40 AC-56</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
@@ -4126,7 +4127,7 @@
       <c r="R49" s="5" t="inlineStr"/>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>データ保全：従業員の同一性を保つ／入出力：ID体系の違いを吸収</t>
+          <t>データ保全：二重登録を防ぐ</t>
         </is>
       </c>
     </row>
@@ -4138,60 +4139,60 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>T-I18</t>
+          <t>T-I20</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>取込が途中で失敗したときの扱い</t>
+          <t>外部IDの対応と付番</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
+【操作】（a）data/20 の対応表を開き、EMP-001 が King of Time 1001 とジョブカン JB-001 の2件を持つことを確認 →（b）対応表に無い外部ID（例 9999）を含むCSVを取り込む →（c）取り込んだ従業員の従業員IDを従業員一覧で確認する</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>20 外部ID対応表／07 取込CSV KingOfTime</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録】
-中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
+          <t>【確認場所：列マッピングテンプレート（外部ID対応）→ 設定インポート → 従業員一覧】
+（a）1名が複数の勤怠システムの外部IDを持てる（E0001＝1001／JB-001）（b）対応表に無い外部IDは取り込まれず、件数と理由が表示される（黙って登録=0件）（c）すべての従業員に従業員IDが付いている（未付番=0件）</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>T-I18.png</t>
+          <t>T-I20.png</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
+          <t>外部ID対応表（EMP-001が2システム分ある状態）／対応表に無い外部IDのエラー表示／従業員一覧の従業員ID列</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録されていないこと）</t>
+          <t>列マッピングテンプレート（外部IDの対応）→ 設定インポート → 従業員一覧</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>部分登録が残らないか</t>
+          <t>外部IDが従業員IDに解決されるか／未登録は弾かれるか</t>
         </is>
       </c>
       <c r="L50" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M50" s="13" t="inlineStr">
         <is>
-          <t>AC-42</t>
+          <t>AC-55 AC-56</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr"/>
@@ -4201,11 +4202,11 @@
       <c r="R50" s="5" t="inlineStr"/>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>データ保全：中途半端に残さない</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="64" customHeight="1">
+          <t>データ保全：従業員の同一性を保つ／入出力：ID体系の違いを吸収</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="94" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4213,60 +4214,60 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>T-I11</t>
+          <t>T-I18</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>CSV位置合わせ設定</t>
+          <t>取込が途中で失敗したときの扱い</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06
-【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
+          <t>【前提】S-04 S-06
+【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>11 取込CSV 説明行あり</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-余計な行が無視され、3行が正しく取り込まれる</t>
+          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録】
+中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>T-I11.png</t>
+          <t>T-I18.png</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
+          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
+          <t>設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録されていないこと）</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>説明行を飛ばして取り込めるか</t>
+          <t>部分登録が残らないか</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="M51" s="13" t="inlineStr">
         <is>
-          <t>AC-37</t>
+          <t>AC-42</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr"/>
@@ -4276,11 +4277,11 @@
       <c r="R51" s="5" t="inlineStr"/>
       <c r="S51" s="8" t="inlineStr">
         <is>
-          <t>入出力：現場のCSVをそのまま使える</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="94" customHeight="1">
+          <t>データ保全：中途半端に残さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="64" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4288,50 +4289,50 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>T-I09</t>
+          <t>T-I11</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>CSV位置合わせ設定</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】「列マッピングテンプレート管理」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
+【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>11 取込CSV 説明行あり</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート管理」】
-テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
+          <t>【確認場所：設定インポート】
+余計な行が無視され、3行が正しく取り込まれる</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>T-I09.png</t>
+          <t>T-I11.png</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
+          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>設定インポート → ツールバー「列マッピングテンプレート管理」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
+          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
         </is>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>テンプレの登録・編集・削除と往復</t>
+          <t>説明行を飛ばして取り込めるか</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -4341,7 +4342,7 @@
       </c>
       <c r="M52" s="13" t="inlineStr">
         <is>
-          <t>AC-24 AC-38 AC-30</t>
+          <t>AC-37</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr"/>
@@ -4351,11 +4352,11 @@
       <c r="R52" s="5" t="inlineStr"/>
       <c r="S52" s="8" t="inlineStr">
         <is>
-          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="79" customHeight="1">
+          <t>入出力：現場のCSVをそのまま使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="94" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4363,50 +4364,50 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>T-I19</t>
+          <t>T-I09</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>マッピング表の一括登録</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
+【操作】「列マッピングテンプレート管理」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>18 列マッピング表テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：列マッピングテンプレート】
-テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
+          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート管理」】
+テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>T-I19.png</t>
+          <t>T-I09.png</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
+          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
+          <t>設定インポート → ツールバー「列マッピングテンプレート管理」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>一括登録と10MB超の扱い</t>
+          <t>テンプレの登録・編集・削除と往復</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
@@ -4416,7 +4417,7 @@
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>AC-51</t>
+          <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr"/>
@@ -4426,72 +4427,72 @@
       <c r="R53" s="5" t="inlineStr"/>
       <c r="S53" s="8" t="inlineStr">
         <is>
-          <t>入出力：マッピングの一括運用</t>
+          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="54" ht="79" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>取込</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>T-E04</t>
+          <t>T-I19</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>設定のエクスポート</t>
+          <t>マッピング表の一括登録</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
+          <t>【前提】S-06
+【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>18 列マッピング表テンプレ</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
-専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
+          <t>【確認場所：列マッピングテンプレート】
+テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>T-E04.png</t>
+          <t>T-I19.png</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
+          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
+          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>選んだ項目だけ・対象数だけ出るか</t>
+          <t>一括登録と10MB超の扱い</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M54" s="13" t="inlineStr">
         <is>
-          <t>AC-25 AC-26 AC-30</t>
+          <t>AC-51</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr"/>
@@ -4501,11 +4502,11 @@
       <c r="R54" s="5" t="inlineStr"/>
       <c r="S54" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="64" customHeight="1">
+          <t>入出力：マッピングの一括運用</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="79" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4513,50 +4514,50 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>T-E09</t>
+          <t>T-E04</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>実績・同時のエクスポート</t>
+          <t>設定のエクスポート</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
+          <t>【前提】S-04
+【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート】
-実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
+          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
+専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>T-E09.png</t>
+          <t>T-E04.png</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
+          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
+          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>実績と同時選択のファイル数</t>
+          <t>選んだ項目だけ・対象数だけ出るか</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
@@ -4566,7 +4567,7 @@
       </c>
       <c r="M55" s="13" t="inlineStr">
         <is>
-          <t>AC-25</t>
+          <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
@@ -4576,11 +4577,11 @@
       <c r="R55" s="5" t="inlineStr"/>
       <c r="S55" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="60" customHeight="1">
+          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="64" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4588,50 +4589,50 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>T-E07</t>
+          <t>T-E09</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>未選択でのエクスポート防止</t>
+          <t>実績・同時のエクスポート</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
+          <t>【前提】S-05
+【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
+実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>T-E07.png</t>
+          <t>T-E09.png</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
+          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
+          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>未選択で出力されないか</t>
+          <t>実績と同時選択のファイル数</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
@@ -4641,7 +4642,7 @@
       </c>
       <c r="M56" s="13" t="inlineStr">
         <is>
-          <t>AC-27</t>
+          <t>AC-25</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr"/>
@@ -4651,7 +4652,7 @@
       <c r="R56" s="5" t="inlineStr"/>
       <c r="S56" s="8" t="inlineStr">
         <is>
-          <t>入出力：空振りを防ぐ</t>
+          <t>入出力：渡し先に合わせて出せる</t>
         </is>
       </c>
     </row>
@@ -4663,18 +4664,18 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>T-E08</t>
+          <t>T-E07</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>出力CSVの文字化け</t>
+          <t>未選択でのエクスポート防止</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 ／ T-E04で出力済み
-【操作】T-E04で出力したCSVをExcelで開く</t>
+          <t>【前提】S-04
+【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -4685,28 +4686,28 @@
       <c r="F57" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
+警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>T-E08.png</t>
+          <t>T-E07.png</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
+          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
+          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>Excelで文字化けしないか</t>
+          <t>未選択で出力されないか</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
@@ -4716,7 +4717,7 @@
       </c>
       <c r="M57" s="13" t="inlineStr">
         <is>
-          <t>AC-28</t>
+          <t>AC-27</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr"/>
@@ -4726,72 +4727,72 @@
       <c r="R57" s="5" t="inlineStr"/>
       <c r="S57" s="8" t="inlineStr">
         <is>
-          <t>入出力：そのまま提出できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="79" customHeight="1">
+          <t>入出力：空振りを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="60" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>取込データ</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>T-N01</t>
+          <t>T-E08</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>取込元データの確認</t>
+          <t>出力CSVの文字化け</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-I03実施済み
-【操作】サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
+          <t>【前提】S-04 ／ T-E04で出力済み
+【操作】T-E04で出力したCSVをExcelで開く</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定取込データ（サイドバー）】
-設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ10列／日別データ10列。交通費・総支給額は表示しない（判断14））</t>
+          <t>【確認場所：設定・実績エクスポート】
+日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>T-N01.png</t>
+          <t>T-E08.png</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>設定取込データと実績取込データの一覧＋各タブ（計4枚）</t>
+          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>設定取込データ（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績取込データ … 月別データ／日別データタブ</t>
+          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
         </is>
       </c>
       <c r="K58" s="8" t="inlineStr">
         <is>
-          <t>元データとタブの構成</t>
+          <t>Excelで文字化けしないか</t>
         </is>
       </c>
       <c r="L58" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>AC-39</t>
+          <t>AC-28</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr"/>
@@ -4801,11 +4802,11 @@
       <c r="R58" s="5" t="inlineStr"/>
       <c r="S58" s="8" t="inlineStr">
         <is>
-          <t>入出力：原因を追える</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="94" customHeight="1">
+          <t>入出力：そのまま提出できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="79" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -4813,50 +4814,50 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>T-N02</t>
+          <t>T-N01</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>取込前のプレビューと前回差分</t>
+          <t>取込元データの確認</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-06
-【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
+          <t>【前提】T-I03実施済み
+【操作】サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定取込データ／実績取込データ】
-プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
+          <t>【確認場所：設定取込データ（サイドバー）】
+設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ10列／日別データ10列。交通費・総支給額は表示しない（判断14））</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>T-N02.png</t>
+          <t>T-N01.png</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
+          <t>設定取込データと実績取込データの一覧＋各タブ（計4枚）</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>設定取込データ／実績取込データ … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
+          <t>設定取込データ（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績取込データ … 月別データ／日別データタブ</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>差分がdata/16・17と一致するか</t>
+          <t>元データとタブの構成</t>
         </is>
       </c>
       <c r="L59" s="13" t="inlineStr">
@@ -4866,7 +4867,7 @@
       </c>
       <c r="M59" s="13" t="inlineStr">
         <is>
-          <t>AC-50</t>
+          <t>AC-39</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr"/>
@@ -4876,11 +4877,11 @@
       <c r="R59" s="5" t="inlineStr"/>
       <c r="S59" s="8" t="inlineStr">
         <is>
-          <t>データ保全：取り込む前に気づける</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="60" customHeight="1">
+          <t>入出力：原因を追える</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="94" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -4888,50 +4889,50 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>T-N03</t>
+          <t>T-N02</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>取込データと人件費実績の相互導線</t>
+          <t>取込前のプレビューと前回差分</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
+          <t>【前提】S-05 S-06
+【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　「実績取込データへ」／実績取込データ】
-2経路とも到達する（不通=0）</t>
+          <t>【確認場所：設定取込データ／実績取込データ】
+プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>T-N03.png</t>
+          <t>T-N02.png</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>人件費実績→実績取込データ／実績取込データ→人件費実績 の到達直後（2枚）</t>
+          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 「実績取込データへ」／実績取込データ → 「人件費実績へ」（相互導線）</t>
+          <t>設定取込データ／実績取込データ … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>2経路とも到達するか</t>
+          <t>差分がdata/16・17と一致するか</t>
         </is>
       </c>
       <c r="L60" s="13" t="inlineStr">
@@ -4941,7 +4942,7 @@
       </c>
       <c r="M60" s="13" t="inlineStr">
         <is>
-          <t>AC-30</t>
+          <t>AC-50</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr"/>
@@ -4951,72 +4952,72 @@
       <c r="R60" s="5" t="inlineStr"/>
       <c r="S60" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る</t>
+          <t>データ保全：取り込む前に気づける</t>
         </is>
       </c>
     </row>
     <row r="61" ht="60" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>T-Z01</t>
+          <t>T-N03</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>移行前後の突合（既存データ）</t>
+          <t>取込データと人件費実績の相互導線</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 S-11
-【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
+          <t>【前提】S-05
+【操作】人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員一覧】
-件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
+          <t>【確認場所：人件費実績　→　「実績取込データへ」／実績取込データ】
+2経路とも到達する（不通=0）</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>T-Z01.png</t>
+          <t>T-N03.png</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
+          <t>人件費実績→実績取込データ／実績取込データ→人件費実績 の到達直後（2枚）</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
+          <t>人件費実績 → 「実績取込データへ」／実績取込データ → 「人件費実績へ」（相互導線）</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>移行前後で差分0件か</t>
+          <t>2経路とも到達するか</t>
         </is>
       </c>
       <c r="L61" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ すでにご利用中のお客様</t>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>AC-01</t>
+          <t>AC-30</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr"/>
@@ -5026,11 +5027,11 @@
       <c r="R61" s="5" t="inlineStr"/>
       <c r="S61" s="8" t="inlineStr">
         <is>
-          <t>移行：既存顧客が壊れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="79" customHeight="1">
+          <t>画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="60" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
           <t>横断</t>
@@ -5038,51 +5039,50 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>T-Z02</t>
+          <t>T-Z01</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>移行後の適用日付の付与</t>
+          <t>移行前後の突合（既存データ）</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
+          <t>【前提】S-09 S-11
+【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細 → 設定変更履歴／従業員設定履歴】
-適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている
-あわせて、すべての従業員に従業員IDが付番されている（未付番=0件）。外部IDは対応表に移されている</t>
+          <t>【確認場所：従業員一覧】
+件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>T-Z02.png</t>
+          <t>T-Z01.png</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
+          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 設定変更履歴／従業員設定履歴 … 適用日付の空欄</t>
+          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
         </is>
       </c>
       <c r="K62" s="8" t="inlineStr">
         <is>
-          <t>適用日付の空欄が0件か</t>
+          <t>移行前後で差分0件か</t>
         </is>
       </c>
       <c r="L62" s="13" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="M62" s="13" t="inlineStr">
         <is>
-          <t>AC-02 AC-55</t>
+          <t>AC-01</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr"/>
@@ -5102,11 +5102,11 @@
       <c r="R62" s="5" t="inlineStr"/>
       <c r="S62" s="8" t="inlineStr">
         <is>
-          <t>移行：履歴の起点を作る</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="60" customHeight="1">
+          <t>移行：既存顧客が壊れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="79" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
           <t>横断</t>
@@ -5114,50 +5114,51 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>T-Z03</t>
+          <t>T-Z02</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>移行前後の過去月の人件費</t>
+          <t>移行後の適用日付の付与</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
           <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行前に出力しておいた直近3か月の人件費実績と、移行後の同3か月を突合する</t>
+【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
-3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
+          <t>【確認場所：従業員詳細 → 設定変更履歴／従業員設定履歴】
+適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている
+あわせて、すべての従業員に従業員IDが付番されている（未付番=0件）。外部IDは対応表に移されている</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>T-Z03.png</t>
+          <t>T-Z02.png</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>移行前後の人件費実績 月別実績（直近3か月・金額が同じであること）</t>
+          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ … 移行前後の直近3か月</t>
+          <t>従業員詳細 → 設定変更履歴／従業員設定履歴 … 適用日付の空欄</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr">
         <is>
-          <t>過去3か月の金額が変わらないか</t>
+          <t>適用日付の空欄が0件か</t>
         </is>
       </c>
       <c r="L63" s="13" t="inlineStr">
@@ -5167,7 +5168,7 @@
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>AC-03</t>
+          <t>AC-02 AC-55</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr"/>
@@ -5177,7 +5178,7 @@
       <c r="R63" s="5" t="inlineStr"/>
       <c r="S63" s="8" t="inlineStr">
         <is>
-          <t>移行：過去が動かない</t>
+          <t>移行：履歴の起点を作る</t>
         </is>
       </c>
     </row>
@@ -5189,60 +5190,60 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>T-Z04</t>
+          <t>T-Z03</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>サイドバーの構成</t>
+          <t>移行前後の過去月の人件費</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
+          <t>【前提】S-09 ／ T-Z01実施済み
+【操作】移行前に出力しておいた直近3か月の人件費実績と、移行後の同3か月を突合する</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：サイドバー「従業員管理」】
-閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>T-Z04.png</t>
+          <t>T-Z03.png</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
+          <t>移行前後の人件費実績 月別実績（直近3か月・金額が同じであること）</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
+          <t>人件費実績 → 月別実績タブ … 移行前後の直近3か月</t>
         </is>
       </c>
       <c r="K64" s="8" t="inlineStr">
         <is>
-          <t>PC・モバイルとも開くか</t>
+          <t>過去3か月の金額が変わらないか</t>
         </is>
       </c>
       <c r="L64" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・画面構成）</t>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
       <c r="M64" s="13" t="inlineStr">
         <is>
-          <t>AC-29</t>
+          <t>AC-03</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr"/>
@@ -5252,7 +5253,7 @@
       <c r="R64" s="5" t="inlineStr"/>
       <c r="S64" s="8" t="inlineStr">
         <is>
-          <t>画面：たどり着ける</t>
+          <t>移行：過去が動かない</t>
         </is>
       </c>
     </row>
@@ -5264,60 +5265,60 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>T-Z05</t>
+          <t>T-Z04</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>遷移と表示規則の網羅</t>
+          <t>サイドバーの構成</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-05
-【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+          <t>【前提】S-01
+【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
-すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+          <t>【確認場所：サイドバー「従業員管理」】
+閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>T-Z05.png</t>
+          <t>T-Z04.png</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
+          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="12" t="inlineStr">
         <is>
-          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>75本の遷移と表示規則</t>
+          <t>PC・モバイルとも開くか</t>
         </is>
       </c>
       <c r="L65" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・遷移網羅）</t>
+          <t>（ヘルプ記載なし・画面構成）</t>
         </is>
       </c>
       <c r="M65" s="13" t="inlineStr">
         <is>
-          <t>AC-30 AC-01</t>
+          <t>AC-29</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr"/>
@@ -5327,72 +5328,72 @@
       <c r="R65" s="5" t="inlineStr"/>
       <c r="S65" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="79" customHeight="1">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>C-000</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
-        <is>
-          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
-        </is>
-      </c>
-      <c r="D66" s="15" t="inlineStr">
-        <is>
-          <t>【前提】S-03 S-05
-【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
-        </is>
-      </c>
-      <c r="E66" s="15" t="inlineStr">
-        <is>
-          <t>02〜06・13を再投入（初期化）</t>
-        </is>
-      </c>
-      <c r="F66" s="15" t="inlineStr">
-        <is>
-          <t>【確認場所：従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未】
-従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
-        </is>
-      </c>
-      <c r="G66" s="14" t="inlineStr">
-        <is>
-          <t>C-000.png</t>
-        </is>
-      </c>
-      <c r="H66" s="15" t="inlineStr">
-        <is>
-          <t>初期化後の従業員一覧（12名）と人件費実績（未締め・S-05時点の金額）</t>
+          <t>画面：たどり着ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>T-Z05</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>遷移と表示規則の網羅</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>【前提】S-04 S-05
+【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
+すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>T-Z05.png</t>
+        </is>
+      </c>
+      <c r="H66" s="11" t="inlineStr">
+        <is>
+          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
-      <c r="J66" s="15" t="inlineStr">
-        <is>
-          <t>従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未締めに戻す）</t>
-        </is>
-      </c>
-      <c r="K66" s="15" t="inlineStr">
-        <is>
-          <t>S-05時点の値に戻ったか</t>
-        </is>
-      </c>
-      <c r="L66" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため対応なし）</t>
-        </is>
-      </c>
-      <c r="M66" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J66" s="12" t="inlineStr">
+        <is>
+          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>75本の遷移と表示規則</t>
+        </is>
+      </c>
+      <c r="L66" s="13" t="inlineStr">
+        <is>
+          <t>（ヘルプ記載なし・遷移網羅）</t>
+        </is>
+      </c>
+      <c r="M66" s="13" t="inlineStr">
+        <is>
+          <t>AC-30 AC-01</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr"/>
@@ -5400,13 +5401,13 @@
       <c r="P66" s="6" t="inlineStr"/>
       <c r="Q66" s="5" t="inlineStr"/>
       <c r="R66" s="5" t="inlineStr"/>
-      <c r="S66" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="64" customHeight="1">
+      <c r="S66" s="8" t="inlineStr">
+        <is>
+          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="79" customHeight="1">
       <c r="A67" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5414,60 +5415,60 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>C-001</t>
+          <t>C-000</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプなし）</t>
+          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-002（概算280,000・基礎時給1,750・深夜2h・所属店舗の交通費15,000）と EMP-007（概算300,000・基礎時給1,875・深夜4h・交通費30,000）を検算</t>
+          <t>【前提】S-03 S-05
+【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
         </is>
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>02〜06・13を再投入（初期化）</t>
         </is>
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
+          <t>【確認場所：従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未】
+従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>C-001.png</t>
+          <t>C-000.png</t>
         </is>
       </c>
       <c r="H67" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
+          <t>初期化後の従業員一覧（12名）と人件費実績（未締め・S-05時点の金額）</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
+          <t>従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未締めに戻す）</t>
         </is>
       </c>
       <c r="K67" s="15" t="inlineStr">
         <is>
-          <t>概算＋深夜＝実績給与か</t>
+          <t>S-05時点の値に戻ったか</t>
         </is>
       </c>
       <c r="L67" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>（初期化のため対応なし）</t>
         </is>
       </c>
       <c r="M67" s="15" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr"/>
@@ -5477,11 +5478,11 @@
       <c r="R67" s="5" t="inlineStr"/>
       <c r="S67" s="15" t="inlineStr">
         <is>
-          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="79" customHeight="1">
+          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="64" customHeight="1">
       <c r="A68" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5489,60 +5490,60 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>C-003</t>
+          <t>C-001</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプあり）</t>
+          <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-001（概算320,000・深夜6h・ヘルプ22h／所属店舗の交通費18,000・ヘルプ先の交通費1,600）／EMP-005（概算350,000・深夜10h・ヘルプ35h／22,000・3,100）／EMP-003（概算144,000・ヘルプ20h／9,000・1,300）を検算</t>
+【操作】2026-05の EMP-002（概算280,000・基礎時給1,750・深夜2h・所属店舗の交通費15,000）と EMP-007（概算300,000・基礎時給1,875・深夜4h・交通費30,000）を検算</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
           <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算＋深夜＋みなし超過＋交通費）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
+EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>C-003.png</t>
+          <t>C-001.png</t>
         </is>
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
+          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
+          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
         </is>
       </c>
       <c r="K68" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費が按分で振替されるか</t>
+          <t>概算＋深夜＝実績給与か</t>
         </is>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr"/>
@@ -5552,11 +5553,11 @@
       <c r="R68" s="5" t="inlineStr"/>
       <c r="S68" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="60" customHeight="1">
+          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="79" customHeight="1">
       <c r="A69" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5564,50 +5565,50 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>C-005</t>
+          <t>C-003</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計と全社合計の一致</t>
+          <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】2026-05の EMP-001（概算320,000・深夜6h・ヘルプ22h／所属店舗の交通費18,000・ヘルプ先の交通費1,600）／EMP-005（概算350,000・深夜10h・ヘルプ35h／22,000・3,100）／EMP-003（概算144,000・ヘルプ20h／9,000・1,300）を検算</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F69" s="15" t="inlineStr">
         <is>
           <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
-店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
+EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算＋深夜＋みなし超過＋交通費）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>C-005.png</t>
+          <t>C-003.png</t>
         </is>
       </c>
       <c r="H69" s="15" t="inlineStr">
         <is>
-          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
+          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
+          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
         </is>
       </c>
       <c r="K69" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計＝全社（差0円）か</t>
+          <t>ヘルプ人件費が按分で振替されるか</t>
         </is>
       </c>
       <c r="L69" s="15" t="inlineStr">
@@ -5617,7 +5618,7 @@
       </c>
       <c r="M69" s="15" t="inlineStr">
         <is>
-          <t>AC-11</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr"/>
@@ -5627,11 +5628,11 @@
       <c r="R69" s="5" t="inlineStr"/>
       <c r="S69" s="15" t="inlineStr">
         <is>
-          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="79" customHeight="1">
+          <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="60" customHeight="1">
       <c r="A70" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5639,60 +5640,60 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>C-006</t>
+          <t>C-005</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>月中改定と予約の日割り</t>
+          <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>14 勤務データ 2026-06</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従】
-6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
+店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>C-006.png</t>
+          <t>C-005.png</t>
         </is>
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
+          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
+          <t>人件費実績 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
         </is>
       </c>
       <c r="K70" s="15" t="inlineStr">
         <is>
-          <t>所定労働日割になっているか</t>
+          <t>店舗別合計＝全社（差0円）か</t>
         </is>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>AC-12 AC-04</t>
+          <t>AC-11</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr"/>
@@ -5702,11 +5703,11 @@
       <c r="R70" s="5" t="inlineStr"/>
       <c r="S70" s="15" t="inlineStr">
         <is>
-          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="64" customHeight="1">
+          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="79" customHeight="1">
       <c r="A71" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5714,60 +5715,60 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>C-011</t>
+          <t>C-006</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>月中改定と予約の日割り</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
+【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・14 勤務データ 2026-06</t>
+          <t>14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
-5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
+          <t>【確認場所：人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従】
+6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>C-011.png</t>
+          <t>C-006.png</t>
         </is>
       </c>
       <c r="H71" s="15" t="inlineStr">
         <is>
-          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
+          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
+          <t>人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>所定労働日割になっているか</t>
         </is>
       </c>
       <c r="L71" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>AC-13</t>
+          <t>AC-12 AC-04</t>
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr"/>
@@ -5777,11 +5778,11 @@
       <c r="R71" s="5" t="inlineStr"/>
       <c r="S71" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="94" customHeight="1">
+          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="64" customHeight="1">
       <c r="A72" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5789,50 +5790,50 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-011</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>【前提】C-000 S-07 ／ data/14を投入
+【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績・14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
-判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
+          <t>【確認場所：人件費実績　→　月別実績タブ】
+5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>C-013.png</t>
+          <t>C-011.png</t>
         </is>
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
+          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
+          <t>人件費実績 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
         </is>
       </c>
       <c r="K72" s="15" t="inlineStr">
         <is>
-          <t>深夜1.5倍とヘルプの按分単価</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="L72" s="15" t="inlineStr">
@@ -5842,7 +5843,7 @@
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-13</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr"/>
@@ -5852,11 +5853,11 @@
       <c r="R72" s="5" t="inlineStr"/>
       <c r="S72" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="79" customHeight="1">
+          <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="94" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5864,60 +5865,60 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-013</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績・日別実績】
-交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
+          <t>【確認場所：人件費実績 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
+判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>C-017.png</t>
+          <t>C-013.png</t>
         </is>
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
+          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+          <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>交通費が給与と別費目か</t>
+          <t>深夜1.5倍とヘルプの按分単価</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M73" s="15" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr"/>
@@ -5927,11 +5928,11 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="94" customHeight="1">
+          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="79" customHeight="1">
       <c r="A74" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5939,60 +5940,60 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-017</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>交通費の計上先</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07
-【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
-（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+          <t>【確認場所：人件費実績 → 月別実績・日別実績】
+交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>C-008.png</t>
+          <t>C-017.png</t>
         </is>
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
+          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+          <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
         </is>
       </c>
       <c r="K74" s="15" t="inlineStr">
         <is>
-          <t>締め前後で差0円・解除後に再計算</t>
+          <t>交通費が給与と別費目か</t>
         </is>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>AC-16 AC-17</t>
+          <t>AC-15</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr"/>
@@ -6002,72 +6003,72 @@
       <c r="R74" s="5" t="inlineStr"/>
       <c r="S74" s="15" t="inlineStr">
         <is>
-          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="124" customHeight="1">
-      <c r="A75" s="16" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B75" s="16" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C75" s="17" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="D75" s="17" t="inlineStr">
-        <is>
-          <t>【前提】S-01
-【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
-        </is>
-      </c>
-      <c r="E75" s="17" t="inlineStr">
-        <is>
-          <t>（追加のデータ投入なし）</t>
-        </is>
-      </c>
-      <c r="F75" s="17" t="inlineStr">
-        <is>
-          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
-①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）</t>
-        </is>
-      </c>
-      <c r="G75" s="16" t="inlineStr">
-        <is>
-          <t>R-01.png</t>
-        </is>
-      </c>
-      <c r="H75" s="17" t="inlineStr">
-        <is>
-          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
+          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="94" customHeight="1">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>締めの前後で数字が動かないこと</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-07
+【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+        </is>
+      </c>
+      <c r="F75" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：人件費実績 → 月別実績タブ】
+（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>C-008.png</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="inlineStr">
+        <is>
+          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
-      <c r="J75" s="17" t="inlineStr">
-        <is>
-          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
-        </is>
-      </c>
-      <c r="K75" s="17" t="inlineStr">
-        <is>
-          <t>適用日付と履歴がテーブルにあるか</t>
-        </is>
-      </c>
-      <c r="L75" s="17" t="inlineStr">
-        <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
-        </is>
-      </c>
-      <c r="M75" s="17" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47 AC-55</t>
+      <c r="J75" s="15" t="inlineStr">
+        <is>
+          <t>人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+        </is>
+      </c>
+      <c r="K75" s="15" t="inlineStr">
+        <is>
+          <t>締め前後で差0円・解除後に再計算</t>
+        </is>
+      </c>
+      <c r="L75" s="15" t="inlineStr">
+        <is>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
+        </is>
+      </c>
+      <c r="M75" s="15" t="inlineStr">
+        <is>
+          <t>AC-16 AC-17</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
@@ -6075,13 +6076,13 @@
       <c r="P75" s="6" t="inlineStr"/>
       <c r="Q75" s="5" t="inlineStr"/>
       <c r="R75" s="5" t="inlineStr"/>
-      <c r="S75" s="17" t="inlineStr">
-        <is>
-          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="79" customHeight="1">
+      <c r="S75" s="15" t="inlineStr">
+        <is>
+          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="124" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6089,18 +6090,18 @@
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>締めの実装レビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
+【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
         </is>
       </c>
       <c r="E76" s="17" t="inlineStr">
@@ -6110,39 +6111,39 @@
       </c>
       <c r="F76" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
-①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
+          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
+①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）</t>
         </is>
       </c>
       <c r="G76" s="16" t="inlineStr">
         <is>
-          <t>R-02.png</t>
+          <t>R-01.png</t>
         </is>
       </c>
       <c r="H76" s="17" t="inlineStr">
         <is>
-          <t>締めAPIのコードとスコープ判定箇所</t>
+          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
+          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
       </c>
       <c r="K76" s="17" t="inlineStr">
         <is>
-          <t>APIでも店長が締められないか</t>
+          <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
       <c r="L76" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M76" s="17" t="inlineStr">
         <is>
-          <t>AC-16 AC-41</t>
+          <t>AC-07 AC-40 AC-47 AC-55</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr"/>
@@ -6152,11 +6153,11 @@
       <c r="R76" s="5" t="inlineStr"/>
       <c r="S76" s="17" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="109" customHeight="1">
+          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="79" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6164,18 +6165,18 @@
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>入力検証とトランザクションのレビュー</t>
+          <t>締めの実装レビュー</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
+【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
       <c r="E77" s="17" t="inlineStr">
@@ -6185,39 +6186,39 @@
       </c>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
-①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
+          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
+①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
         </is>
       </c>
       <c r="G77" s="16" t="inlineStr">
         <is>
-          <t>R-03.png</t>
+          <t>R-02.png</t>
         </is>
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
+          <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
+          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
       </c>
       <c r="K77" s="17" t="inlineStr">
         <is>
-          <t>APIを直接呼んでも弾かれるか</t>
+          <t>APIでも店長が締められないか</t>
         </is>
       </c>
       <c r="L77" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 設定が保存できません</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M77" s="17" t="inlineStr">
         <is>
-          <t>AC-23 AC-42 AC-43</t>
+          <t>AC-16 AC-41</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
@@ -6227,11 +6228,11 @@
       <c r="R77" s="5" t="inlineStr"/>
       <c r="S77" s="17" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="79" customHeight="1">
+          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="109" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6239,18 +6240,18 @@
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの共有レビュー</t>
+          <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
@@ -6260,39 +6261,39 @@
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
-同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
+          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
+①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
         </is>
       </c>
       <c r="G78" s="16" t="inlineStr">
         <is>
-          <t>R-04.png</t>
+          <t>R-03.png</t>
         </is>
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
+          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
+          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
       </c>
       <c r="K78" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックが1箇所か</t>
+          <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
       <c r="L78" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>AC-35 AC-11</t>
+          <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
@@ -6302,11 +6303,11 @@
       <c r="R78" s="5" t="inlineStr"/>
       <c r="S78" s="17" t="inlineStr">
         <is>
-          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="64" customHeight="1">
+          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="79" customHeight="1">
       <c r="A79" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6314,18 +6315,18 @@
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>計算ロジックの共有レビュー</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込の列解決の実装を提示してもらう</t>
+【操作】人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
       <c r="E79" s="17" t="inlineStr">
@@ -6335,39 +6336,39 @@
       </c>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
-CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
+          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
+同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
         </is>
       </c>
       <c r="G79" s="16" t="inlineStr">
         <is>
-          <t>R-05.png</t>
+          <t>R-04.png</t>
         </is>
       </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
-          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
+          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
+          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
         </is>
       </c>
       <c r="K79" s="17" t="inlineStr">
         <is>
-          <t>列名がコードに埋まっていないか</t>
+          <t>計算ロジックが1箇所か</t>
         </is>
       </c>
       <c r="L79" s="17" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M79" s="17" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-35 AC-11</t>
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr"/>
@@ -6377,11 +6378,11 @@
       <c r="R79" s="5" t="inlineStr"/>
       <c r="S79" s="17" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="79" customHeight="1">
+          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="64" customHeight="1">
       <c r="A80" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6389,18 +6390,18 @@
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>設定更新処理の共通化レビュー</t>
+          <t>列マッピングの実装レビュー</t>
         </is>
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+【操作】取込の列解決の実装を提示してもらう</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
@@ -6410,39 +6411,39 @@
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
-設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
+CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
       <c r="G80" s="16" t="inlineStr">
         <is>
-          <t>R-06.png</t>
+          <t>R-05.png</t>
         </is>
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
         </is>
       </c>
       <c r="K80" s="17" t="inlineStr">
         <is>
-          <t>2つの入口で更新処理が共通か</t>
+          <t>列名がコードに埋まっていないか</t>
         </is>
       </c>
       <c r="L80" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M80" s="17" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-22 AC-24</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr"/>
@@ -6452,17 +6453,92 @@
       <c r="R80" s="5" t="inlineStr"/>
       <c r="S80" s="17" t="inlineStr">
         <is>
+          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="79" customHeight="1">
+      <c r="A81" s="16" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B81" s="16" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C81" s="17" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="D81" s="17" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="E81" s="17" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F81" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
+設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="G81" s="16" t="inlineStr">
+        <is>
+          <t>R-06.png</t>
+        </is>
+      </c>
+      <c r="H81" s="17" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="17" t="inlineStr">
+        <is>
+          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+        </is>
+      </c>
+      <c r="K81" s="17" t="inlineStr">
+        <is>
+          <t>2つの入口で更新処理が共通か</t>
+        </is>
+      </c>
+      <c r="L81" s="17" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="M81" s="17" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="N81" s="5" t="inlineStr"/>
+      <c r="O81" s="5" t="inlineStr"/>
+      <c r="P81" s="6" t="inlineStr"/>
+      <c r="Q81" s="5" t="inlineStr"/>
+      <c r="R81" s="5" t="inlineStr"/>
+      <c r="S81" s="17" t="inlineStr">
+        <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S80"/>
+  <autoFilter ref="A2:S81"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3:O80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -1580,7 +1580,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="64" customHeight="1">
+    <row r="16" ht="79" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>一覧</t>
@@ -1599,7 +1599,7 @@
       <c r="D16" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
-【操作】右上「従業員登録」「CSVインポート」「設定・実績エクスポート」、2段目「設定取込データへ」、行の詳細アイコン を順に押す</t>
+【操作】右上「従業員登録」「CSVインポート」「設定・実績エクスポート」、2段目「設定取込データへ」、行の詳細アイコン を順に押す。次に店舗フィルタを「渋谷店」にして「この店舗の人件費実績へ」「この店舗の設定変更履歴へ」を押す</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1610,7 +1610,8 @@
       <c r="F16" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員一覧】
-5経路すべて到達（従業員登録／設定インポート／設定・実績エクスポート／設定取込データ／従業員詳細）。不通=0</t>
+5経路すべて到達（従業員登録／設定インポート／設定・実績エクスポート／設定取込データ／従業員詳細）。不通=0
+店舗で絞った状態から2経路とも到達し、遷移先が渋谷店で絞り込まれている（絞り込みが引き継がれない=0件）</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -1620,7 +1621,7 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>遷移先5画面の到達直後（従業員登録・設定インポート・エクスポート・設定取込データ・従業員詳細）</t>
+          <t>遷移先5画面の到達直後（従業員登録・設定インポート・エクスポート・設定取込データ・従業員詳細）／店舗で絞った従業員一覧と、そこから開いた人件費実績・設定変更履歴（絞り込み条件が見える状態）</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
@@ -1641,7 +1642,7 @@
       </c>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>AC-30</t>
+          <t>AC-30 AC-58</t>
         </is>
       </c>
       <c r="N16" s="5" t="inlineStr"/>
@@ -4581,7 +4582,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="64" customHeight="1">
+    <row r="56" ht="79" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4600,7 +4601,7 @@
       <c r="D56" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
+【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（給与実績差分を含む）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -4611,7 +4612,8 @@
       <c r="F56" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
+実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される
+実績の項目に給与実績差分が選べ、出力値＝実績給与−概算給与と一致する</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
@@ -4642,7 +4644,7 @@
       </c>
       <c r="M56" s="13" t="inlineStr">
         <is>
-          <t>AC-25</t>
+          <t>AC-25 AC-57</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr"/>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -949,7 +949,7 @@
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="4" t="inlineStr"/>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>準備</t>
@@ -978,8 +978,8 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>【確認場所：従業員設定履歴／人件費実績（月別実績タブ）】
-履歴に適用済3・予約中1が入る／人件費実績に5名分が表示される</t>
+          <t>【確認場所：設定変更履歴一覧／給与実績一覧（月別実績タブ）】
+履歴に適用済3・予約中1が入る／給与実績一覧に5名分が表示される</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -989,13 +989,13 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>設定変更履歴（予約中の行が見える）／人件費実績 月別実績の5行</t>
+          <t>設定変更履歴（予約中の行が見える）／給与実績一覧 月別実績の5行</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>従業員設定履歴／人件費実績（月別実績タブ）</t>
+          <t>設定変更履歴一覧／給与実績一覧（月別実績タブ）</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
+          <t>【確認場所：給与実績一覧　→　月別実績タブ】
 ボタンが「2026-05 締め」になっている</t>
         </is>
       </c>
@@ -1194,13 +1194,13 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>人件費実績 月別実績（ボタンが「2026-05 締め」＝未締め）</t>
+          <t>給与実績一覧 月別実績（ボタンが「2026-05 締め」＝未締め）</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 年月2026-05（締め状態の確認）</t>
+          <t>給与実績一覧 → 月別実績タブ → 年月2026-05（締め状態の確認）</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1244,7 +1244,7 @@
       <c r="D11" s="4" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】data/15（突合テンプレート）に、移行前の従業員一覧・直近3か月の人件費実績をCSV出力して記入</t>
+【操作】data/15（突合テンプレート）に、移行前の従業員一覧・直近3か月の給与実績一覧をCSV出力して記入</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>【確認場所：従業員一覧（CSVエクスポート）／人件費実績 月別実績（直近3か月）】
+          <t>【確認場所：従業員一覧（CSVエクスポート）／給与実績一覧 月別実績（直近3か月）】
 突合シート M-01〜M-06 が埋まった状態</t>
         </is>
       </c>
@@ -1265,13 +1265,13 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>移行前の従業員一覧と人件費実績（比較の元になるため必須）</t>
+          <t>移行前の従業員一覧と給与実績一覧（比較の元になるため必須）</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>従業員一覧（CSVエクスポート）／人件費実績 月別実績（直近3か月）</t>
+          <t>従業員一覧（CSVエクスポート）／給与実績一覧 月別実績（直近3か月）</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -1599,7 +1599,7 @@
       <c r="D16" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
-【操作】右上「従業員登録」「CSVインポート」「設定・実績エクスポート」、2段目「設定取込データへ」、行の詳細アイコン を順に押す。次に店舗フィルタを「渋谷店」にして「この店舗の人件費実績へ」「この店舗の設定変更履歴へ」を押す</t>
+【操作】右上「従業員登録」「CSVインポート」「設定・実績エクスポート」、2段目「設定取込データへ」、行の詳細アイコン を順に押す。次に店舗フィルタを「渋谷店」にして「この店舗の給与実績一覧へ」「この店舗の設定変更履歴へ」を押す</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>遷移先5画面の到達直後（従業員登録・設定インポート・エクスポート・設定取込データ・従業員詳細）／店舗で絞った従業員一覧と、そこから開いた人件費実績・設定変更履歴（絞り込み条件が見える状態）</t>
+          <t>遷移先5画面の到達直後（従業員登録・設定インポート・エクスポート・設定取込データ・従業員詳細）／店舗で絞った従業員一覧と、そこから開いた給与実績一覧・設定変更履歴（絞り込み条件が見える状態）</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
@@ -2361,7 +2361,7 @@
       <c r="F26" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員詳細 → 給与実績】
-概算⇄実績で表示列が増減する。直近3か月が表示され、実績データ取込の前でも概算モードで金額が出る（空欄=0件）。絞り込みとCSVエクスポートは無い（残っている数=0件）。「すべての実績」で給与実績一覧が開き、EMP-001で絞り込まれている</t>
+概算⇄実績で表示列が増減する。直近3か月が表示され、実績データ取込の前でも概算モードで金額が出る（空欄=0件）。絞り込みとCSVエクスポートは無い（残っている数=0件）。「すべての実績」で従業員別 給与実績が開き、EMP-001で絞り込まれている</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -2371,13 +2371,13 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>給与実績セクション（月次・日次の両タブ／絞り込みとCSVボタンが無いこと）／「すべての実績」で開いた給与実績一覧</t>
+          <t>給与実績セクション（月次・日次の両タブ／絞り込みとCSVボタンが無いこと）／「すべての実績」で開いた従業員別 給与実績</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 給与実績セクション … 右上「すべての実績」→ 給与実績一覧</t>
+          <t>従業員詳細 → 給与実績セクション … 右上「すべての実績」→ 従業員別 給与実績</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
@@ -2419,13 +2419,13 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>給与実績一覧の絞り込みと出力</t>
+          <t>従業員別 給与実績の絞り込みと出力</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】給与実績一覧で（a）年月を2024-10〜2024-12に指定 →（b）年をまたぐ範囲（2024-10〜2025-01）に変更 →（c）給与計算モードを概算⇄実績で切替 →（d）日次実績タブに切り替え →（e）CSVエクスポート</t>
+【操作】従業員別 給与実績で（a）年月を2024-10〜2024-12に指定 →（b）年をまたぐ範囲（2024-10〜2025-01）に変更 →（c）給与計算モードを概算⇄実績で切替 →（d）日次実績タブに切り替え →（e）CSVエクスポート</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧】
+          <t>【確認場所：従業員別 給与実績】
 （a・b）指定した期間の行だけが表示され、年をまたいでも表示される（またげない=0件）（c）月次では列が増減する（d）日次タブでは給与計算モードが表示されない（e）出力した行数＝画面の行数（差0件）。Excelで開いて文字化け=0件</t>
         </is>
       </c>
@@ -2452,7 +2452,7 @@
       <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧（従業員詳細 →「すべての実績」）… 年月の開始・終了、給与計算モード、月次実績／日次実績タブ、右上CSVエクスポート</t>
+          <t>従業員別 給与実績（従業員詳細 →「すべての実績」）… 年月の開始・終了、給与計算モード、月次実績／日次実績タブ、右上CSVエクスポート</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
@@ -2500,7 +2500,7 @@
       <c r="D28" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】（a）給与実績一覧で給与計算モードを 概算 → 実績 に切り替える →（b）実績モードで 想定給与・給与実績差分 を確認する →（c）実績データ取込を行っていない月（当月）を範囲に含めて概算モードで表示する</t>
+【操作】（a）従業員別 給与実績で給与計算モードを 概算 → 実績 に切り替える →（b）実績モードで 想定給与・給与実績差分 を確認する →（c）実績データ取込を行っていない月（当月）を範囲に含めて概算モードで表示する</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月次実績】
+          <t>【確認場所：従業員別 給与実績 → 月次実績】
 （a）概算モードでは基本列のみ、実績モードで実績列が追加される（b）給与実績差分＝給与−想定給与（計算違い0件）（c）実績がまだ無い月でも概算モードで金額が表示される（空欄=0件）</t>
         </is>
       </c>
@@ -2527,7 +2527,7 @@
       <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月次実績タブ … 給与計算モード（概算／実績）</t>
+          <t>従業員別 給与実績 → 月次実績タブ … 給与計算モード（概算／実績）</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
@@ -2661,7 +2661,7 @@
       <c r="F30" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員詳細 → 設定変更履歴】
-（a）並びは変更反映日時の降順で、予約中が最上部。ステータスは変更反映日時の次（2列目）にあり横スクロールなしで見える。表示は直近3件（b・c）保存した行が最上部に増え、1つ古い行と値が違う項目（単位給与額）だけが強調される。強調の過不足=0件（d）従業員設定履歴が開き、EMP-001で絞り込まれた状態になる（絞り込みなしでの遷移=0件）</t>
+（a）並びは変更反映日時の降順で、予約中が最上部。ステータスは変更反映日時の次（2列目）にあり横スクロールなしで見える。表示は直近3件（b・c）保存した行が最上部に増え、1つ古い行と値が違う項目（単位給与額）だけが強調される。強調の過不足=0件（d）設定変更履歴一覧が開き、EMP-001で絞り込まれた状態になる（絞り込みなしでの遷移=0件）</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -2671,13 +2671,13 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>保存前後の履歴セクション2枚（並び順とステータス列の位置が分かる範囲）／強調された項目／「すべての履歴」で開いた従業員設定履歴（絞り込み条件が見える状態）</t>
+          <t>保存前後の履歴セクション2枚（並び順とステータス列の位置が分かる範囲）／強調された項目／「すべての履歴」で開いた設定変更履歴一覧（絞り込み条件が見える状態）</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 設定変更履歴セクション … 右上「すべての履歴」→ 従業員設定履歴（EMP-001で絞り込み済み）</t>
+          <t>従業員詳細 → 設定変更履歴セクション … 右上「すべての履歴」→ 設定変更履歴一覧（EMP-001で絞り込み済み）</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員設定履歴】
+          <t>【確認場所：設定変更履歴一覧】
 履歴が1行増える。既存行の値の差分＝0</t>
         </is>
       </c>
@@ -2752,7 +2752,7 @@
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>従業員設定履歴 … 変更前後の行（既存行が書き換わらないこと）</t>
+          <t>設定変更履歴一覧 … 変更前後の行（既存行が書き換わらないこと）</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員設定履歴】
+          <t>【確認場所：設定変更履歴一覧】
 ①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
         </is>
       </c>
@@ -2827,7 +2827,7 @@
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>従業員設定履歴 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
+          <t>設定変更履歴一覧 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員設定履歴】
+          <t>【確認場所：設定変更履歴一覧】
 店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
         </is>
       </c>
@@ -2902,7 +2902,7 @@
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>従業員設定履歴 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
+          <t>設定変更履歴一覧 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
 全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない
 実績モードでは 想定給与・給与・給与実績差分 が表示され、差分＝給与−想定給与 と一致する</t>
         </is>
@@ -2978,7 +2978,7 @@
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
+          <t>給与実績一覧 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
@@ -3020,13 +3020,13 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>人件費実績からの設定編集</t>
+          <t>給与実績一覧からの設定編集</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】人件費実績で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
+【操作】給与実績一覧で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -3036,8 +3036,8 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　行の「従業員設定」】
-モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
+          <t>【確認場所：給与実績一覧　→　行の「従業員設定」】
+モーダルに14項目が表示される。更新保存で給与実績一覧に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -3047,13 +3047,13 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>設定編集モーダル（項目が見える状態）／更新保存後の人件費実績／従業員詳細の設定変更履歴に行が増えたこと</t>
+          <t>設定編集モーダル（項目が見える状態）／更新保存後の給与実績一覧／従業員詳細の設定変更履歴に行が増えたこと</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 人件費実績／確認は従業員詳細の設定変更履歴</t>
+          <t>給与実績一覧 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 給与実績一覧／確認は従業員詳細の設定変更履歴</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 日別実績タブ】
+          <t>【確認場所：給与実績一覧 → 日別実績タブ】
 全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
         </is>
       </c>
@@ -3128,7 +3128,7 @@
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
+          <t>給与実績一覧 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績】
+          <t>【確認場所：給与実績一覧】
 出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
         </is>
       </c>
@@ -3203,7 +3203,7 @@
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
+          <t>給与実績一覧 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
@@ -3251,7 +3251,7 @@
       <c r="D38" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05 S-08
-【操作】人件費実績の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
+【操作】給与実績一覧の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
 「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
         </is>
       </c>
@@ -3278,7 +3278,7 @@
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
+          <t>給与実績一覧 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績】
+          <t>【確認場所：給与実績一覧】
 月別のみ「2026-05 締め」が表示。日別には表示されない</t>
         </is>
       </c>
@@ -3353,7 +3353,7 @@
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
+          <t>給与実績一覧 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
+          <t>【確認場所：給与実績一覧　→　月別実績タブ】
 「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
         </is>
       </c>
@@ -3428,7 +3428,7 @@
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
+          <t>給与実績一覧 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績】
+          <t>【確認場所：給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績】
 編集できない（または反映されない）</t>
         </is>
       </c>
@@ -3503,7 +3503,7 @@
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>人件費実績（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
+          <t>給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
+          <t>【確認場所：給与実績一覧　→　月別実績タブ】
 「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
         </is>
       </c>
@@ -3653,7 +3653,7 @@
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
+          <t>給与実績一覧 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
@@ -3701,7 +3701,7 @@
       <c r="D44" s="8" t="inlineStr">
         <is>
           <t>【前提】S-10 S-08
-【操作】店長スコープのアカウントでログインし、人件費実績を開いて締めを試みる</t>
+【操作】店長スコープのアカウントでログインし、給与実績一覧を開いて締めを試みる</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ（店長スコープでログイン）】
+          <t>【確認場所：給与実績一覧 → 月別実績タブ（店長スコープでログイン）】
 締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
         </is>
       </c>
@@ -3722,13 +3722,13 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>店長スコープでの人件費実績（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
+          <t>店長スコープでの給与実績一覧（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
+          <t>給与実績一覧 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録】
+          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録】
 中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
         </is>
       </c>
@@ -4253,7 +4253,7 @@
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>設定インポート（全行エラー）→ 従業員一覧と従業員設定履歴（部分登録されていないこと）</t>
+          <t>設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録されていないこと）</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
@@ -4971,13 +4971,13 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>取込データと人件費実績の相互導線</t>
+          <t>取込データと給与実績一覧の相互導線</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
+【操作】給与実績一覧の「実績取込データへ」→ 実績取込データの「給与実績一覧へ」を押す</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　「実績取込データへ」／実績取込データ】
+          <t>【確認場所：給与実績一覧　→　「実績取込データへ」／実績取込データ】
 2経路とも到達する（不通=0）</t>
         </is>
       </c>
@@ -4998,13 +4998,13 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>人件費実績→実績取込データ／実績取込データ→人件費実績 の到達直後（2枚）</t>
+          <t>給与実績一覧→実績取込データ／実績取込データ→給与実績一覧 の到達直後（2枚）</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 「実績取込データへ」／実績取込データ → 「人件費実績へ」（相互導線）</t>
+          <t>給与実績一覧 → 「実績取込データへ」／実績取込データ → 「給与実績一覧へ」（相互導線）</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
@@ -5108,7 +5108,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="79" customHeight="1">
+    <row r="63" ht="94" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
           <t>横断</t>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細 → 設定変更履歴／従業員設定履歴】
+          <t>【確認場所：従業員詳細 → 設定変更履歴／設定変更履歴一覧】
 適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている
 あわせて、すべての従業員に従業員IDが付番されている（未付番=0件）。外部IDは対応表に移されている</t>
         </is>
@@ -5155,7 +5155,7 @@
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 設定変更履歴／従業員設定履歴 … 適用日付の空欄</t>
+          <t>従業員詳細 → 設定変更履歴／設定変更履歴一覧 … 適用日付の空欄</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr">
@@ -5203,7 +5203,7 @@
       <c r="D64" s="8" t="inlineStr">
         <is>
           <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行前に出力しておいた直近3か月の人件費実績と、移行後の同3か月を突合する</t>
+【操作】移行前に出力しておいた直近3か月の給与実績一覧と、移行後の同3か月を突合する</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
 3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
@@ -5224,13 +5224,13 @@
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>移行前後の人件費実績 月別実績（直近3か月・金額が同じであること）</t>
+          <t>移行前後の給与実績一覧 月別実績（直近3か月・金額が同じであること）</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ … 移行前後の直近3か月</t>
+          <t>給与実績一覧 → 月別実績タブ … 移行前後の直近3か月</t>
         </is>
       </c>
       <c r="K64" s="8" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未】
+          <t>【確認場所：従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未】
 従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
@@ -5449,13 +5449,13 @@
       </c>
       <c r="H67" s="15" t="inlineStr">
         <is>
-          <t>初期化後の従業員一覧（12名）と人件費実績（未締め・S-05時点の金額）</t>
+          <t>初期化後の従業員一覧（12名）と給与実績一覧（未締め・S-05時点の金額）</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="15" t="inlineStr">
         <is>
-          <t>従業員一覧（12名に戻す）／人件費実績 月別実績（2026-05を未締めに戻す）</t>
+          <t>従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未締めに戻す）</t>
         </is>
       </c>
       <c r="K67" s="15" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
+          <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
 EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
         </is>
       </c>
@@ -5530,7 +5530,7 @@
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
         </is>
       </c>
       <c r="K68" s="15" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="F69" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
+          <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
 EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算＋深夜＋みなし超過＋交通費）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
         </is>
       </c>
@@ -5605,7 +5605,7 @@
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
         </is>
       </c>
       <c r="K69" s="15" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ → 実績モード】
+          <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
 店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
         </is>
       </c>
@@ -5680,7 +5680,7 @@
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
         </is>
       </c>
       <c r="K70" s="15" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従】
+          <t>【確認場所：給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従】
 6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
@@ -5755,7 +5755,7 @@
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
+          <t>給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績　→　月別実績タブ】
+          <t>【確認場所：給与実績一覧　→　月別実績タブ】
 5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
@@ -5830,7 +5830,7 @@
       <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
+          <t>給与実績一覧 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
         </is>
       </c>
       <c r="K72" s="15" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
+          <t>【確認場所：給与実績一覧 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
 判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
         </is>
       </c>
@@ -5905,7 +5905,7 @@
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
+          <t>給与実績一覧 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績・日別実績】
+          <t>【確認場所：給与実績一覧 → 月別実績・日別実績】
 交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
         </is>
       </c>
@@ -5980,7 +5980,7 @@
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+          <t>給与実績一覧 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
         </is>
       </c>
       <c r="K74" s="15" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：人件費実績 → 月別実績タブ】
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
 （a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
         </is>
       </c>
@@ -6055,7 +6055,7 @@
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="15" t="inlineStr">
         <is>
-          <t>人件費実績 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+          <t>給与実績一覧 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
         </is>
       </c>
       <c r="K75" s="15" t="inlineStr">
@@ -6328,7 +6328,7 @@
       <c r="D79" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+【操作】給与実績一覧・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
       <c r="E79" s="17" t="inlineStr">

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -2481,7 +2481,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="79" customHeight="1">
+    <row r="28" ht="109" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -2500,7 +2500,7 @@
       <c r="D28" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】（a）従業員別 給与実績で給与計算モードを 概算 → 実績 に切り替える →（b）実績モードで 想定給与・給与実績差分 を確認する →（c）実績データ取込を行っていない月（当月）を範囲に含めて概算モードで表示する</t>
+【操作】（a）従業員別 給与実績で給与計算モードを 概算 → 実績 に切り替える →（b）実績モードで 想定給与・給与実績差分 を確認する →（c）実績データ取込を行っていない月（当月）を範囲に含めて概算モードで表示する →（d）日次実績タブに切り替え、想定給与・給与実績差分が表示されることを確認する</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -2511,7 +2511,7 @@
       <c r="F28" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員別 給与実績 → 月次実績】
-（a）概算モードでは基本列のみ、実績モードで実績列が追加される（b）給与実績差分＝給与−想定給与（計算違い0件）（c）実績がまだ無い月でも概算モードで金額が表示される（空欄=0件）</t>
+（a）概算モードでは基本列のみ、実績モードで実績列が追加される（b）給与実績差分＝給与−想定給与（計算違い0件）（c）実績がまだ無い月でも概算モードで金額が表示される（空欄=0件）（d）日次はモード切替を持たないが、想定給与・給与実績差分が表示される（欠落=0件）</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -3082,7 +3082,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="109" customHeight="1">
+    <row r="36" ht="139" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -3112,7 +3112,8 @@
       <c r="F36" s="8" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 日別実績タブ】
-全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
+全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない
+日別にモード切替は無いが、想定給与・給与実績差分は表示される</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -3143,7 +3144,7 @@
       </c>
       <c r="M36" s="13" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>AC-10 AC-57</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr"/>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S81"/>
+  <dimension ref="A1:S82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証68ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
+          <t>確かめる手順（準備11行＋検証69ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
 実施順を変えてはいけない箇所：①T-A08（勤怠取込）→T-S03（締め）　②T-S03→T-S04・T-D07→T-S05（この3件は締め済みでしか確認できない）　③C-000（初期化）は計算の先頭　④C-008は計算の最後（2026-05のEMP-001を352,286円に変えるためC-013・C-017が合わなくなる）　⑤T-N02の前にdata/02を再投入　⑥削除はEMP-012（T-L10）とEMP-004（T-D08）だけ
 列の使い方：使用する検証データ＝この検証で投入・使用するdataファイル／期待値＝先頭の【確認場所】でどの画面を見て合否を出すかを示し、続けて合格の基準を書いている／スクショ（撮るもの）＝何が写っていれば証拠になるか／スクショ貼付欄＝撮った画像をこの列に貼る／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めて合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを決める
 色：緑＝使う検証データ　青＝画面　橙＝スクショの指示　紫＝ヘルプ・受入条件との対応　黄＝当日の記入欄。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
@@ -5868,60 +5868,60 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-018</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>想定労働日数と日次の想定給与</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>【前提】C-000 S-05
+【操作】（a）EMP-001（想定労働日数が未入力・月給350,000）と EMP-003（想定労働日数15・パート）の日次の想定給与を検算 →（b）EMP-001に想定労働日数22を入力して保存し、再計算する</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ・05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
-判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
+          <t>【確認場所：給与実績一覧 → 日別実績／従業員詳細（想定労働日数の欄）】
+（a）EMP-001は未入力のため月次予算設定の営業日数20日が使われ、日次の想定給与＝350,000÷20＝17,500円。EMP-003は時給のため 1,200×実働時間（b）22を入力すると 350,000÷22＝15,909円に変わる。解決できない従業員=0件</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>C-013.png</t>
+          <t>C-018.png</t>
         </is>
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
+          <t>従業員詳細の想定労働日数の欄（未入力の状態と入力後）／日別実績の想定給与が変わったこと</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
+          <t>従業員詳細（想定労働日数）→ 給与実績一覧 日別実績（想定給与）</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>深夜1.5倍とヘルプの按分単価</t>
+          <t>未入力なら営業日数が使われるか</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M73" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-59</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr"/>
@@ -5931,11 +5931,11 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="79" customHeight="1">
+          <t>日次の想定給与＝単位給与額÷想定労働日数（月給者）。想定労働日数は 従業員設定の入力値 → 無ければ月次予算設定の営業日数</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="94" customHeight="1">
       <c r="A74" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5943,60 +5943,60 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-013</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績・日別実績】
-交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
+          <t>【確認場所：給与実績一覧 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
+判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>C-017.png</t>
+          <t>C-013.png</t>
         </is>
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
+          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+          <t>給与実績一覧 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
         </is>
       </c>
       <c r="K74" s="15" t="inlineStr">
         <is>
-          <t>交通費が給与と別費目か</t>
+          <t>深夜1.5倍とヘルプの按分単価</t>
         </is>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr"/>
@@ -6006,11 +6006,11 @@
       <c r="R74" s="5" t="inlineStr"/>
       <c r="S74" s="15" t="inlineStr">
         <is>
-          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="94" customHeight="1">
+          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="79" customHeight="1">
       <c r="A75" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6018,60 +6018,60 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-017</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>交通費の計上先</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07
-【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績・日別実績】
+交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>C-008.png</t>
+          <t>C-017.png</t>
         </is>
       </c>
       <c r="H75" s="15" t="inlineStr">
         <is>
-          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
+          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+          <t>給与実績一覧 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
         </is>
       </c>
       <c r="K75" s="15" t="inlineStr">
         <is>
-          <t>締め前後で差0円・解除後に再計算</t>
+          <t>交通費が給与と別費目か</t>
         </is>
       </c>
       <c r="L75" s="15" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M75" s="15" t="inlineStr">
         <is>
-          <t>AC-16 AC-17</t>
+          <t>AC-15</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
@@ -6081,72 +6081,72 @@
       <c r="R75" s="5" t="inlineStr"/>
       <c r="S75" s="15" t="inlineStr">
         <is>
-          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="124" customHeight="1">
-      <c r="A76" s="16" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B76" s="16" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C76" s="17" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="D76" s="17" t="inlineStr">
-        <is>
-          <t>【前提】S-01
-【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
-        </is>
-      </c>
-      <c r="E76" s="17" t="inlineStr">
-        <is>
-          <t>（追加のデータ投入なし）</t>
-        </is>
-      </c>
-      <c r="F76" s="17" t="inlineStr">
-        <is>
-          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
-①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）</t>
-        </is>
-      </c>
-      <c r="G76" s="16" t="inlineStr">
-        <is>
-          <t>R-01.png</t>
-        </is>
-      </c>
-      <c r="H76" s="17" t="inlineStr">
-        <is>
-          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
+          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="94" customHeight="1">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>締めの前後で数字が動かないこと</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-07
+【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+        </is>
+      </c>
+      <c r="F76" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>C-008.png</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="inlineStr">
+        <is>
+          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
-      <c r="J76" s="17" t="inlineStr">
-        <is>
-          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
-        </is>
-      </c>
-      <c r="K76" s="17" t="inlineStr">
-        <is>
-          <t>適用日付と履歴がテーブルにあるか</t>
-        </is>
-      </c>
-      <c r="L76" s="17" t="inlineStr">
-        <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
-        </is>
-      </c>
-      <c r="M76" s="17" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47 AC-55</t>
+      <c r="J76" s="15" t="inlineStr">
+        <is>
+          <t>給与実績一覧 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+        </is>
+      </c>
+      <c r="K76" s="15" t="inlineStr">
+        <is>
+          <t>締め前後で差0円・解除後に再計算</t>
+        </is>
+      </c>
+      <c r="L76" s="15" t="inlineStr">
+        <is>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
+        </is>
+      </c>
+      <c r="M76" s="15" t="inlineStr">
+        <is>
+          <t>AC-16 AC-17</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr"/>
@@ -6154,13 +6154,13 @@
       <c r="P76" s="6" t="inlineStr"/>
       <c r="Q76" s="5" t="inlineStr"/>
       <c r="R76" s="5" t="inlineStr"/>
-      <c r="S76" s="17" t="inlineStr">
-        <is>
-          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="79" customHeight="1">
+      <c r="S76" s="15" t="inlineStr">
+        <is>
+          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="124" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6168,18 +6168,18 @@
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>締めの実装レビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="D77" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
+【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
         </is>
       </c>
       <c r="E77" s="17" t="inlineStr">
@@ -6189,39 +6189,39 @@
       </c>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
-①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
+          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
+①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）</t>
         </is>
       </c>
       <c r="G77" s="16" t="inlineStr">
         <is>
-          <t>R-02.png</t>
+          <t>R-01.png</t>
         </is>
       </c>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>締めAPIのコードとスコープ判定箇所</t>
+          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
+          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
       </c>
       <c r="K77" s="17" t="inlineStr">
         <is>
-          <t>APIでも店長が締められないか</t>
+          <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
       <c r="L77" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M77" s="17" t="inlineStr">
         <is>
-          <t>AC-16 AC-41</t>
+          <t>AC-07 AC-40 AC-47 AC-55</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
@@ -6231,11 +6231,11 @@
       <c r="R77" s="5" t="inlineStr"/>
       <c r="S77" s="17" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="109" customHeight="1">
+          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="79" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6243,18 +6243,18 @@
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>入力検証とトランザクションのレビュー</t>
+          <t>締めの実装レビュー</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
+【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
@@ -6264,39 +6264,39 @@
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
-①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
+          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
+①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
         </is>
       </c>
       <c r="G78" s="16" t="inlineStr">
         <is>
-          <t>R-03.png</t>
+          <t>R-02.png</t>
         </is>
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
+          <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
+          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
       </c>
       <c r="K78" s="17" t="inlineStr">
         <is>
-          <t>APIを直接呼んでも弾かれるか</t>
+          <t>APIでも店長が締められないか</t>
         </is>
       </c>
       <c r="L78" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 設定が保存できません</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>AC-23 AC-42 AC-43</t>
+          <t>AC-16 AC-41</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
@@ -6306,11 +6306,11 @@
       <c r="R78" s="5" t="inlineStr"/>
       <c r="S78" s="17" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="79" customHeight="1">
+          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="109" customHeight="1">
       <c r="A79" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6318,18 +6318,18 @@
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの共有レビュー</t>
+          <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】給与実績一覧・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
       <c r="E79" s="17" t="inlineStr">
@@ -6339,39 +6339,39 @@
       </c>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
-同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
+          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
+①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
         </is>
       </c>
       <c r="G79" s="16" t="inlineStr">
         <is>
-          <t>R-04.png</t>
+          <t>R-03.png</t>
         </is>
       </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
+          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
+          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
       </c>
       <c r="K79" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックが1箇所か</t>
+          <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
       <c r="L79" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
       <c r="M79" s="17" t="inlineStr">
         <is>
-          <t>AC-35 AC-11</t>
+          <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr"/>
@@ -6381,11 +6381,11 @@
       <c r="R79" s="5" t="inlineStr"/>
       <c r="S79" s="17" t="inlineStr">
         <is>
-          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="64" customHeight="1">
+          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="79" customHeight="1">
       <c r="A80" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6393,18 +6393,18 @@
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>計算ロジックの共有レビュー</t>
         </is>
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込の列解決の実装を提示してもらう</t>
+【操作】給与実績一覧・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
-CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
+          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
+同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
         </is>
       </c>
       <c r="G80" s="16" t="inlineStr">
         <is>
-          <t>R-05.png</t>
+          <t>R-04.png</t>
         </is>
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
+          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
+          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
         </is>
       </c>
       <c r="K80" s="17" t="inlineStr">
         <is>
-          <t>列名がコードに埋まっていないか</t>
+          <t>計算ロジックが1箇所か</t>
         </is>
       </c>
       <c r="L80" s="17" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M80" s="17" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-35 AC-11</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr"/>
@@ -6456,11 +6456,11 @@
       <c r="R80" s="5" t="inlineStr"/>
       <c r="S80" s="17" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="79" customHeight="1">
+          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="64" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6468,18 +6468,18 @@
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>設定更新処理の共通化レビュー</t>
+          <t>列マッピングの実装レビュー</t>
         </is>
       </c>
       <c r="D81" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+【操作】取込の列解決の実装を提示してもらう</t>
         </is>
       </c>
       <c r="E81" s="17" t="inlineStr">
@@ -6489,39 +6489,39 @@
       </c>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
-設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
+CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
       <c r="G81" s="16" t="inlineStr">
         <is>
-          <t>R-06.png</t>
+          <t>R-05.png</t>
         </is>
       </c>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
         </is>
       </c>
       <c r="K81" s="17" t="inlineStr">
         <is>
-          <t>2つの入口で更新処理が共通か</t>
+          <t>列名がコードに埋まっていないか</t>
         </is>
       </c>
       <c r="L81" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M81" s="17" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-22 AC-24</t>
         </is>
       </c>
       <c r="N81" s="5" t="inlineStr"/>
@@ -6531,17 +6531,92 @@
       <c r="R81" s="5" t="inlineStr"/>
       <c r="S81" s="17" t="inlineStr">
         <is>
+          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="79" customHeight="1">
+      <c r="A82" s="16" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
+設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="G82" s="16" t="inlineStr">
+        <is>
+          <t>R-06.png</t>
+        </is>
+      </c>
+      <c r="H82" s="17" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="17" t="inlineStr">
+        <is>
+          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+        </is>
+      </c>
+      <c r="K82" s="17" t="inlineStr">
+        <is>
+          <t>2つの入口で更新処理が共通か</t>
+        </is>
+      </c>
+      <c r="L82" s="17" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="M82" s="17" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="N82" s="5" t="inlineStr"/>
+      <c r="O82" s="5" t="inlineStr"/>
+      <c r="P82" s="6" t="inlineStr"/>
+      <c r="Q82" s="5" t="inlineStr"/>
+      <c r="R82" s="5" t="inlineStr"/>
+      <c r="S82" s="17" t="inlineStr">
+        <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S81"/>
+  <autoFilter ref="A2:S82"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3:O81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S82"/>
+  <dimension ref="A1:S83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証69ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
+          <t>確かめる手順（準備11行＋検証70ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
 実施順を変えてはいけない箇所：①T-A08（勤怠取込）→T-S03（締め）　②T-S03→T-S04・T-D07→T-S05（この3件は締め済みでしか確認できない）　③C-000（初期化）は計算の先頭　④C-008は計算の最後（2026-05のEMP-001を352,286円に変えるためC-013・C-017が合わなくなる）　⑤T-N02の前にdata/02を再投入　⑥削除はEMP-012（T-L10）とEMP-004（T-D08）だけ
 列の使い方：使用する検証データ＝この検証で投入・使用するdataファイル／期待値＝先頭の【確認場所】でどの画面を見て合否を出すかを示し、続けて合格の基準を書いている／スクショ（撮るもの）＝何が写っていれば証拠になるか／スクショ貼付欄＝撮った画像をこの列に貼る／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めて合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを決める
 色：緑＝使う検証データ　青＝画面　橙＝スクショの指示　紫＝ヘルプ・受入条件との対応　黄＝当日の記入欄。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
@@ -5935,7 +5935,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="94" customHeight="1">
+    <row r="74" ht="109" customHeight="1">
       <c r="A74" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5943,60 +5943,60 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-019</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>日別の概算モード（営業日でならした見込み）</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>【前提】C-000 S-05
+【操作】給与実績一覧 → 日別実績タブ → 給与計算モードを「概算」に切り替える → 当月の全営業日ぶんの行が出ることと、日別の合計を確認する</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
-判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
+          <t>【確認場所：給与実績一覧 → 日別実績タブ → 給与計算モード＝概算】
+実績が無い日も含めて当月の全営業日に行が出る。1日あたり＝月次の概算給与÷当月の営業日数。日別を全部足すと月次の概算給与と一致する（差 0円）。実績モードに戻すと想定給与列は月次概算÷想定労働日数の額に変わる（同じ日でも額が違う）</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>C-013.png</t>
+          <t>C-019.png</t>
         </is>
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
+          <t>概算モードの日別（全営業日に行が出ている）／合計が月次の概算給与と一致していること／実績モードに戻したときの想定給与列</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
+          <t>給与実績一覧 日別実績（概算モード ↔ 実績モード）</t>
         </is>
       </c>
       <c r="K74" s="15" t="inlineStr">
         <is>
-          <t>深夜1.5倍とヘルプの按分単価</t>
+          <t>日別の合計が月次の概算給与と一致するか</t>
         </is>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-60</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr"/>
@@ -6006,11 +6006,11 @@
       <c r="R74" s="5" t="inlineStr"/>
       <c r="S74" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="79" customHeight="1">
+          <t>概算の日別＝月次の概算給与÷当月の営業日数、当月の全営業日に配分。端数は最大剰余で月次と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="94" customHeight="1">
       <c r="A75" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6018,60 +6018,60 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-013</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績・日別実績】
-交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
+          <t>【確認場所：給与実績一覧 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
+判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>C-017.png</t>
+          <t>C-013.png</t>
         </is>
       </c>
       <c r="H75" s="15" t="inlineStr">
         <is>
-          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
+          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+          <t>給与実績一覧 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
         </is>
       </c>
       <c r="K75" s="15" t="inlineStr">
         <is>
-          <t>交通費が給与と別費目か</t>
+          <t>深夜1.5倍とヘルプの按分単価</t>
         </is>
       </c>
       <c r="L75" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M75" s="15" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
@@ -6081,11 +6081,11 @@
       <c r="R75" s="5" t="inlineStr"/>
       <c r="S75" s="15" t="inlineStr">
         <is>
-          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="94" customHeight="1">
+          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="79" customHeight="1">
       <c r="A76" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6093,60 +6093,60 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-017</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>交通費の計上先</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07
-【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績・日別実績】
+交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>C-008.png</t>
+          <t>C-017.png</t>
         </is>
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
+          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+          <t>給与実績一覧 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
         </is>
       </c>
       <c r="K76" s="15" t="inlineStr">
         <is>
-          <t>締め前後で差0円・解除後に再計算</t>
+          <t>交通費が給与と別費目か</t>
         </is>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>AC-16 AC-17</t>
+          <t>AC-15</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr"/>
@@ -6156,72 +6156,72 @@
       <c r="R76" s="5" t="inlineStr"/>
       <c r="S76" s="15" t="inlineStr">
         <is>
-          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="124" customHeight="1">
-      <c r="A77" s="16" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B77" s="16" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C77" s="17" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="D77" s="17" t="inlineStr">
-        <is>
-          <t>【前提】S-01
-【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
-        </is>
-      </c>
-      <c r="E77" s="17" t="inlineStr">
-        <is>
-          <t>（追加のデータ投入なし）</t>
-        </is>
-      </c>
-      <c r="F77" s="17" t="inlineStr">
-        <is>
-          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
-①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）</t>
-        </is>
-      </c>
-      <c r="G77" s="16" t="inlineStr">
-        <is>
-          <t>R-01.png</t>
-        </is>
-      </c>
-      <c r="H77" s="17" t="inlineStr">
-        <is>
-          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
+          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="94" customHeight="1">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>締めの前後で数字が動かないこと</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-07
+【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>C-008.png</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="inlineStr">
+        <is>
+          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
-      <c r="J77" s="17" t="inlineStr">
-        <is>
-          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
-        </is>
-      </c>
-      <c r="K77" s="17" t="inlineStr">
-        <is>
-          <t>適用日付と履歴がテーブルにあるか</t>
-        </is>
-      </c>
-      <c r="L77" s="17" t="inlineStr">
-        <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
-        </is>
-      </c>
-      <c r="M77" s="17" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47 AC-55</t>
+      <c r="J77" s="15" t="inlineStr">
+        <is>
+          <t>給与実績一覧 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+        </is>
+      </c>
+      <c r="K77" s="15" t="inlineStr">
+        <is>
+          <t>締め前後で差0円・解除後に再計算</t>
+        </is>
+      </c>
+      <c r="L77" s="15" t="inlineStr">
+        <is>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
+        </is>
+      </c>
+      <c r="M77" s="15" t="inlineStr">
+        <is>
+          <t>AC-16 AC-17</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
@@ -6229,13 +6229,13 @@
       <c r="P77" s="6" t="inlineStr"/>
       <c r="Q77" s="5" t="inlineStr"/>
       <c r="R77" s="5" t="inlineStr"/>
-      <c r="S77" s="17" t="inlineStr">
-        <is>
-          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="79" customHeight="1">
+      <c r="S77" s="15" t="inlineStr">
+        <is>
+          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="124" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6243,18 +6243,18 @@
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>締めの実装レビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="D78" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
+【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
         </is>
       </c>
       <c r="E78" s="17" t="inlineStr">
@@ -6264,39 +6264,39 @@
       </c>
       <c r="F78" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
-①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
+          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
+①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）</t>
         </is>
       </c>
       <c r="G78" s="16" t="inlineStr">
         <is>
-          <t>R-02.png</t>
+          <t>R-01.png</t>
         </is>
       </c>
       <c r="H78" s="17" t="inlineStr">
         <is>
-          <t>締めAPIのコードとスコープ判定箇所</t>
+          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
+          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
       </c>
       <c r="K78" s="17" t="inlineStr">
         <is>
-          <t>APIでも店長が締められないか</t>
+          <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
       <c r="L78" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>AC-16 AC-41</t>
+          <t>AC-07 AC-40 AC-47 AC-55</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
@@ -6306,11 +6306,11 @@
       <c r="R78" s="5" t="inlineStr"/>
       <c r="S78" s="17" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="109" customHeight="1">
+          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="79" customHeight="1">
       <c r="A79" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6318,18 +6318,18 @@
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>入力検証とトランザクションのレビュー</t>
+          <t>締めの実装レビュー</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
+【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
       <c r="E79" s="17" t="inlineStr">
@@ -6339,39 +6339,39 @@
       </c>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
-①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
+          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
+①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
         </is>
       </c>
       <c r="G79" s="16" t="inlineStr">
         <is>
-          <t>R-03.png</t>
+          <t>R-02.png</t>
         </is>
       </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
-          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
+          <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
+          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
       </c>
       <c r="K79" s="17" t="inlineStr">
         <is>
-          <t>APIを直接呼んでも弾かれるか</t>
+          <t>APIでも店長が締められないか</t>
         </is>
       </c>
       <c r="L79" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 設定が保存できません</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M79" s="17" t="inlineStr">
         <is>
-          <t>AC-23 AC-42 AC-43</t>
+          <t>AC-16 AC-41</t>
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr"/>
@@ -6381,11 +6381,11 @@
       <c r="R79" s="5" t="inlineStr"/>
       <c r="S79" s="17" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="79" customHeight="1">
+          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="109" customHeight="1">
       <c r="A80" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6393,18 +6393,18 @@
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの共有レビュー</t>
+          <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】給与実績一覧・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
-同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
+          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
+①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
         </is>
       </c>
       <c r="G80" s="16" t="inlineStr">
         <is>
-          <t>R-04.png</t>
+          <t>R-03.png</t>
         </is>
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
+          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
+          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
       </c>
       <c r="K80" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックが1箇所か</t>
+          <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
       <c r="L80" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
       <c r="M80" s="17" t="inlineStr">
         <is>
-          <t>AC-35 AC-11</t>
+          <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr"/>
@@ -6456,11 +6456,11 @@
       <c r="R80" s="5" t="inlineStr"/>
       <c r="S80" s="17" t="inlineStr">
         <is>
-          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="64" customHeight="1">
+          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="79" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6468,18 +6468,18 @@
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>計算ロジックの共有レビュー</t>
         </is>
       </c>
       <c r="D81" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込の列解決の実装を提示してもらう</t>
+【操作】給与実績一覧・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
       <c r="E81" s="17" t="inlineStr">
@@ -6489,39 +6489,39 @@
       </c>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
-CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
+          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
+同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
         </is>
       </c>
       <c r="G81" s="16" t="inlineStr">
         <is>
-          <t>R-05.png</t>
+          <t>R-04.png</t>
         </is>
       </c>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
+          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
+          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
         </is>
       </c>
       <c r="K81" s="17" t="inlineStr">
         <is>
-          <t>列名がコードに埋まっていないか</t>
+          <t>計算ロジックが1箇所か</t>
         </is>
       </c>
       <c r="L81" s="17" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M81" s="17" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-35 AC-11</t>
         </is>
       </c>
       <c r="N81" s="5" t="inlineStr"/>
@@ -6531,11 +6531,11 @@
       <c r="R81" s="5" t="inlineStr"/>
       <c r="S81" s="17" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="79" customHeight="1">
+          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="64" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6543,18 +6543,18 @@
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>設定更新処理の共通化レビュー</t>
+          <t>列マッピングの実装レビュー</t>
         </is>
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+【操作】取込の列解決の実装を提示してもらう</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
@@ -6564,39 +6564,39 @@
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
-設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
+CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
       <c r="G82" s="16" t="inlineStr">
         <is>
-          <t>R-06.png</t>
+          <t>R-05.png</t>
         </is>
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
         </is>
       </c>
       <c r="K82" s="17" t="inlineStr">
         <is>
-          <t>2つの入口で更新処理が共通か</t>
+          <t>列名がコードに埋まっていないか</t>
         </is>
       </c>
       <c r="L82" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M82" s="17" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-22 AC-24</t>
         </is>
       </c>
       <c r="N82" s="5" t="inlineStr"/>
@@ -6606,17 +6606,92 @@
       <c r="R82" s="5" t="inlineStr"/>
       <c r="S82" s="17" t="inlineStr">
         <is>
+          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="79" customHeight="1">
+      <c r="A83" s="16" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B83" s="16" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C83" s="17" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="D83" s="17" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="E83" s="17" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
+設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="G83" s="16" t="inlineStr">
+        <is>
+          <t>R-06.png</t>
+        </is>
+      </c>
+      <c r="H83" s="17" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr"/>
+      <c r="J83" s="17" t="inlineStr">
+        <is>
+          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+        </is>
+      </c>
+      <c r="K83" s="17" t="inlineStr">
+        <is>
+          <t>2つの入口で更新処理が共通か</t>
+        </is>
+      </c>
+      <c r="L83" s="17" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="M83" s="17" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="N83" s="5" t="inlineStr"/>
+      <c r="O83" s="5" t="inlineStr"/>
+      <c r="P83" s="6" t="inlineStr"/>
+      <c r="Q83" s="5" t="inlineStr"/>
+      <c r="R83" s="5" t="inlineStr"/>
+      <c r="S83" s="17" t="inlineStr">
+        <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S82"/>
+  <autoFilter ref="A2:S83"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3:O82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -5860,7 +5860,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="94" customHeight="1">
+    <row r="73" ht="124" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5879,7 +5879,7 @@
       <c r="D73" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-05
-【操作】（a）EMP-001（想定労働日数が未入力・月給350,000）と EMP-003（想定労働日数15・パート）の日次の想定給与を検算 →（b）EMP-001に想定労働日数22を入力して保存し、再計算する</t>
+【操作】（a）EMP-001（月給・想定労働日数が未入力）と EMP-003（時給・パート）の日次の想定給与を検算 →（b）EMP-001に想定労働日数22を入力して保存し、再計算する</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
@@ -5890,7 +5890,7 @@
       <c r="F73" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 日別実績／従業員詳細（想定労働日数の欄）】
-（a）EMP-001は未入力のため月次予算設定の営業日数20日が使われ、日次の想定給与＝350,000÷20＝17,500円。EMP-003は時給のため 1,200×実働時間（b）22を入力すると 350,000÷22＝15,909円に変わる。解決できない従業員=0件</t>
+（a）EMP-001は未入力のため所属店舗の休業日設定から求めた営業日数20日が使われ、日次の想定給与＝350,000÷20＝17,500円。EMP-003は時給のため想定労働日数は空欄で、日次の想定給与＝1,200×その日の実働時間（日数を使わない）（b）22を入力すると 350,000÷22＝15,909円に変わる。月給者で解決できない従業員=0件</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>未入力なら営業日数が使われるか</t>
+          <t>未入力なら営業日数が使われるか／時給者は空欄のまま計算できるか</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
@@ -5931,7 +5931,7 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>日次の想定給与＝単位給与額÷想定労働日数（月給者）。想定労働日数は 従業員設定の入力値 → 無ければ月次予算設定の営業日数</t>
+          <t>日次の想定給与＝単位給与額÷想定労働日数（月給者のみ）／単位給与額×実働時間（時給者）。想定労働日数は 従業員設定の入力値 → 無ければ所属店舗の休業日設定から求めた営業日数</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -2406,7 +2406,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="79" customHeight="1">
+    <row r="27" ht="94" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -2436,7 +2436,7 @@
       <c r="F27" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員別 給与実績】
-（a・b）指定した期間の行だけが表示され、年をまたいでも表示される（またげない=0件）（c）月次では列が増減する（d）日次タブでは給与計算モードが表示されない（e）出力した行数＝画面の行数（差0件）。Excelで開いて文字化け=0件</t>
+（a・b）指定した期間の行だけが表示され、年をまたいでも表示される（またげない=0件）（c）月次では列が増減する（d）日次タブでも給与計算モードが使え、概算にすると「営業日でならした額」の注記が出る（判断21）（e）出力した行数＝画面の行数（差0件）。Excelで開いて文字化け=0件</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>年またぎの期間で表示した一覧／概算と実績の両モード／日次タブ（モードが無いこと）／出力したCSVをExcelで開いた画面</t>
+          <t>年またぎの期間で表示した一覧／概算と実績の両モード／日次タブの概算モード（注記が出ていること）／出力したCSVをExcelで開いた画面</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr"/>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -2331,7 +2331,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="94" customHeight="1">
+    <row r="26" ht="124" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
           <t>詳細</t>
@@ -2361,7 +2361,7 @@
       <c r="F26" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員詳細 → 給与実績】
-概算⇄実績で表示列が増減する。直近3か月が表示され、実績データ取込の前でも概算モードで金額が出る（空欄=0件）。絞り込みとCSVエクスポートは無い（残っている数=0件）。「すべての実績」で従業員別 給与実績が開き、EMP-001で絞り込まれている</t>
+概算⇄実績で表示列が増減する（月次18列⇄10列／日次15列⇄8列）。日次でも切り替わる。概算で残るのは実績データが無くても値が決まる列だけ（判断22）。直近3か月が表示され、実績データ取込の前でも概算モードで金額が出る（空欄=0件）。絞り込みとCSVエクスポートは無い（残っている数=0件）。「すべての実績」で従業員別 給与実績が開き、EMP-001で絞り込まれている</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>詳細がダイジェストに絞られているか</t>
+          <t>日次でもモードが効くか／概算に実績由来の列が残らないか</t>
         </is>
       </c>
       <c r="L26" s="13" t="inlineStr">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="154" customHeight="1">
+    <row r="34" ht="199" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -2962,7 +2962,8 @@
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績タブ】
 全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない
-実績モードでは 想定給与・給与・給与実績差分 が表示され、差分＝給与−想定給与 と一致する</t>
+実績モードでは 想定給与・給与・給与実績差分 が表示され、差分＝給与−想定給与 と一致する
+概算モードでは実績由来の列（給与・給与実績差分・ヘルプ人件費・深夜残業代など）が隠れる。残るのは実績データが無くても値が決まる列だけ（判断22。食い違う列=0件）</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -5861,7 +5861,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="124" customHeight="1">
+    <row r="73" ht="94" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5880,7 +5880,7 @@
       <c r="D73" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-05
-【操作】（a）EMP-001（月給・想定労働日数が未入力）と EMP-003（時給・パート）の日次の想定給与を検算 →（b）EMP-001に想定労働日数22を入力して保存し、再計算する</t>
+【操作】（a）EMP-001（月給320,000・月額交通費18,000）と EMP-003（時給1,200・所定120h・日額交通費600・想定労働日数15）の想定給与を検算 →（b）EMP-001に想定労働日数22を入力して保存し、日次を再計算する</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
@@ -5890,8 +5890,8 @@
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 日別実績／従業員詳細（想定労働日数の欄）】
-（a）EMP-001は未入力のため所属店舗の休業日設定から求めた営業日数20日が使われ、日次の想定給与＝350,000÷20＝17,500円。EMP-003は時給のため想定労働日数は空欄で、日次の想定給与＝1,200×その日の実働時間（日数を使わない）（b）22を入力すると 350,000÷22＝15,909円に変わる。月給者で解決できない従業員=0件</t>
+          <t>【確認場所：給与実績一覧 → 月別実績／日別実績】
+（a）EMP-001の想定給与＝320,000＋18,000＝338,000円。給与実績差分＝357,600−338,000＝19,600円。EMP-003の想定給与＝1,200×120＋600×15＝153,000円（日額交通費は想定労働日数を掛ける）。どちらもヘルプ先の交通費は含まれない（b）日次の想定給与＝338,000÷22＝15,364円。計算違い0件</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>未入力なら営業日数が使われるか／時給者は空欄のまま計算できるか</t>
+          <t>想定給与に所属店舗の交通費が入っているか／ヘルプ先の交通費が入っていないか</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
@@ -5932,7 +5932,7 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>日次の想定給与＝単位給与額÷想定労働日数（月給者のみ）／単位給与額×実働時間（時給者）。想定労働日数は 従業員設定の入力値 → 無ければ所属店舗の休業日設定から求めた営業日数</t>
+          <t>想定給与＝基本給の想定＋所属店舗の交通費（日額なら×想定労働日数）。日次＝月次の想定給与÷想定労働日数（判断20・23）</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -5861,7 +5861,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="94" customHeight="1">
+    <row r="73" ht="139" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5880,7 +5880,7 @@
       <c r="D73" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-05
-【操作】（a）EMP-001（月給320,000・月額交通費18,000）と EMP-003（時給1,200・所定120h・日額交通費600・想定労働日数15）の想定給与を検算 →（b）EMP-001に想定労働日数22を入力して保存し、日次を再計算する</t>
+【操作】（a）EMP-001（月給・想定労働日数が未入力）と EMP-003（時給・15日を入力済み）と EMP-006（時給・所定120h・未入力）の想定給与を検算 →（b）EMP-001に想定労働日数22を入力して保存し、日次を再計算する</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
@@ -5890,8 +5890,8 @@
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績／日別実績】
-（a）EMP-001の想定給与＝320,000＋18,000＝338,000円。給与実績差分＝357,600−338,000＝19,600円。EMP-003の想定給与＝1,200×120＋600×15＝153,000円（日額交通費は想定労働日数を掛ける）。どちらもヘルプ先の交通費は含まれない（b）日次の想定給与＝338,000÷22＝15,364円。計算違い0件</t>
+          <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
+（a）EMP-001は未入力のため営業日数20日が使われ、想定給与＝320,000＋18,000＝338,000円。給与実績差分＝19,600円。EMP-003は入力済み15日で 1,200×120＋600×15＝153,000円。EMP-006は未入力のため 切り上げ(120÷8)＝15日 が薄字で出て、その日数で計算される（営業日数20は使わない）。どちらもヘルプ先の交通費は含まれない（b）日次の想定給与＝338,000÷22＝15,364円。計算違い0件</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>従業員詳細の想定労働日数の欄（未入力の状態と入力後）／日別実績の想定給与が変わったこと</t>
+          <t>従業員詳細の想定労働日数の欄（月給者の未入力・時給者の未入力で薄字の既定値が出ていること・入力後）／月別実績の想定給与</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>想定給与に所属店舗の交通費が入っているか／ヘルプ先の交通費が入っていないか</t>
+          <t>時給者の既定値が営業日数でなく所定労働時間÷8になっているか／想定給与に所属店舗の交通費が入っているか</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
@@ -5932,7 +5932,7 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>想定給与＝基本給の想定＋所属店舗の交通費（日額なら×想定労働日数）。日次＝月次の想定給与÷想定労働日数（判断20・23）</t>
+          <t>想定給与＝基本給の想定＋所属店舗の交通費（日額なら×想定労働日数）。日次＝月次÷想定労働日数。既定値は月給者＝営業日数／時給者＝切り上げ(所定労働時間÷8)（判断20・23・24）</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -5861,7 +5861,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="139" customHeight="1">
+    <row r="73" ht="169" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5891,7 +5891,7 @@
       <c r="F73" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
-（a）EMP-001は未入力のため営業日数20日が使われ、想定給与＝320,000＋18,000＝338,000円。給与実績差分＝19,600円。EMP-003は入力済み15日で 1,200×120＋600×15＝153,000円。EMP-006は未入力のため 切り上げ(120÷8)＝15日 が薄字で出て、その日数で計算される（営業日数20は使わない）。どちらもヘルプ先の交通費は含まれない（b）日次の想定給与＝338,000÷22＝15,364円。計算違い0件</t>
+（a）EMP-001は未入力のため営業日数20日が使われ、想定給与＝320,000＋18,000＝338,000円。給与実績差分＝19,600円。EMP-003は入力済み15日で 1,200×120＋600×15＝153,000円。EMP-006は未入力のため 切り上げ(120÷8)＝15日 が薄字で出て、その日数で計算される（営業日数20は使わない）。どちらもヘルプ先の交通費は含まれない（b）日次の想定給与は 月給者のEMP-001＝338,000÷22＝15,364円。時給者のEMP-003は日数で割らず 1,200×その日の想定勤務時間＋600（日額交通費）で出る（判断25）。計算違い0件</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>時給者の既定値が営業日数でなく所定労働時間÷8になっているか／想定給与に所属店舗の交通費が入っているか</t>
+          <t>時給者の既定値が営業日数でなく所定労働時間÷8になっているか／想定給与に所属店舗の交通費が入っているか／時給者の日次が日数割りになっていないか</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
@@ -5932,7 +5932,7 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>想定給与＝基本給の想定＋所属店舗の交通費（日額なら×想定労働日数）。日次＝月次÷想定労働日数。既定値は月給者＝営業日数／時給者＝切り上げ(所定労働時間÷8)（判断20・23・24）</t>
+          <t>想定給与＝基本給の想定＋所属店舗の交通費（日額なら×想定労働日数）。日次＝月給者は月次÷想定労働日数、時給者は単位給与額×その日の想定勤務時間＋その日ぶんの交通費。既定値は月給者＝営業日数／時給者＝切り上げ(所定労働時間÷8)（判断20・23・24）</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -5861,7 +5861,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="169" customHeight="1">
+    <row r="73" ht="154" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5880,7 +5880,7 @@
       <c r="D73" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-05
-【操作】（a）EMP-001（月給・想定労働日数が未入力）と EMP-003（時給・15日を入力済み）と EMP-006（時給・所定120h・未入力）の想定給与を検算 →（b）EMP-001に想定労働日数22を入力して保存し、日次を再計算する</t>
+【操作】（a）EMP-001（月給・未入力）と EMP-003（時給・15日を入力済み）と EMP-006（時給・所定120h・未入力）の月次と日次の想定給与を見る →（b）EMP-006に想定労働日数15を入力して保存し、日次が出るようになるか見る</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
@@ -5891,7 +5891,7 @@
       <c r="F73" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
-（a）EMP-001は未入力のため営業日数20日が使われ、想定給与＝320,000＋18,000＝338,000円。給与実績差分＝19,600円。EMP-003は入力済み15日で 1,200×120＋600×15＝153,000円。EMP-006は未入力のため 切り上げ(120÷8)＝15日 が薄字で出て、その日数で計算される（営業日数20は使わない）。どちらもヘルプ先の交通費は含まれない（b）日次の想定給与は 月給者のEMP-001＝338,000÷22＝15,364円。時給者のEMP-003は日数で割らず 1,200×その日の想定勤務時間＋600（日額交通費）で出る（判断25）。計算違い0件</t>
+（a）EMP-001は未入力のため営業日数20日が使われ、月次の想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003は15日が入っているので 月次＝1,200×120＋600×15＝153,000円、1日の想定勤務時間＝120÷15＝8時間、日次＝1,200×8＋600＝10,200円（×15日＝153,000円で月次と一致）。EMP-006は未入力のため月次は出るが日次は「—」で、理由（想定労働日数が未入力）が添えられる（b）15を入力すると日次が 10,200円 になる。計算違い0件</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>従業員詳細の想定労働日数の欄（月給者の未入力・時給者の未入力で薄字の既定値が出ていること・入力後）／月別実績の想定給与</t>
+          <t>従業員詳細の想定労働日数の欄／日別実績でEMP-006が「—」になっていること／入力後に日次が出ること</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>時給者の既定値が営業日数でなく所定労働時間÷8になっているか／想定給与に所属店舗の交通費が入っているか／時給者の日次が日数割りになっていないか</t>
+          <t>時給者で未入力のとき日次が「—」になり月次は出るか／1日の想定勤務時間が 所定÷想定労働日数 か</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
@@ -5932,7 +5932,7 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>想定給与＝基本給の想定＋所属店舗の交通費（日額なら×想定労働日数）。日次＝月給者は月次÷想定労働日数、時給者は単位給与額×その日の想定勤務時間＋その日ぶんの交通費。既定値は月給者＝営業日数／時給者＝切り上げ(所定労働時間÷8)（判断20・23・24）</t>
+          <t>1日の想定勤務時間＝所定労働時間÷想定労働日数。日次の想定給与＝月給者は月次÷想定労働日数／時給者は単位給与額×（所定÷想定労働日数）＋交通費÷想定労働日数。日次×想定労働日数＝月次（判断23・25・26）</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -5861,7 +5861,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="154" customHeight="1">
+    <row r="73" ht="184" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5891,7 +5891,7 @@
       <c r="F73" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
-（a）EMP-001は未入力のため営業日数20日が使われ、月次の想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003は15日が入っているので 月次＝1,200×120＋600×15＝153,000円、1日の想定勤務時間＝120÷15＝8時間、日次＝1,200×8＋600＝10,200円（×15日＝153,000円で月次と一致）。EMP-006は未入力のため月次は出るが日次は「—」で、理由（想定労働日数が未入力）が添えられる（b）15を入力すると日次が 10,200円 になる。計算違い0件</t>
+（a）EMP-001は未入力のため営業日数20日が使われ、月次の想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003は15日が入っているので 月次＝1,200×120＋600×15＝153,000円、1日の想定勤務時間＝120÷15＝8時間、日次＝1,200×8＋600＝10,200円（×15日＝153,000円で月次と一致）。EMP-006は未入力のため月次は出るが、日次の想定給与と給与実績差分は「—」で理由が添えられる。ただし日次の給与は勤怠実績から 1,200×実働時間＋交通費＋深夜残業代＋ヘルプ人件費 で表示される（空欄=0件）（b）15を入力すると日次が 10,200円 になる。計算違い0件</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>時給者で未入力のとき日次が「—」になり月次は出るか／1日の想定勤務時間が 所定÷想定労働日数 か</t>
+          <t>時給者で未入力のとき日次の想定給与だけ「—」になり、給与は出るか／1日の想定勤務時間が 所定÷想定労働日数 か</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -5861,7 +5861,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="184" customHeight="1">
+    <row r="73" ht="139" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5880,7 +5880,7 @@
       <c r="D73" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-05
-【操作】（a）EMP-001（月給・未入力）と EMP-003（時給・15日を入力済み）と EMP-006（時給・所定120h・未入力）の月次と日次の想定給与を見る →（b）EMP-006に想定労働日数15を入力して保存し、日次が出るようになるか見る</t>
+【操作】（a）EMP-001（月給・想定労働日数が未入力）と EMP-003（時給・15日を入力済み・日額交通費600）の月次の想定給与を検算 →（b）日別実績タブで EMP-003 の行を見る</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
@@ -5891,7 +5891,7 @@
       <c r="F73" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
-（a）EMP-001は未入力のため営業日数20日が使われ、月次の想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003は15日が入っているので 月次＝1,200×120＋600×15＝153,000円、1日の想定勤務時間＝120÷15＝8時間、日次＝1,200×8＋600＝10,200円（×15日＝153,000円で月次と一致）。EMP-006は未入力のため月次は出るが、日次の想定給与と給与実績差分は「—」で理由が添えられる。ただし日次の給与は勤怠実績から 1,200×実働時間＋交通費＋深夜残業代＋ヘルプ人件費 で表示される（空欄=0件）（b）15を入力すると日次が 10,200円 になる。計算違い0件</t>
+（a）EMP-001は未入力のため営業日数20日が使われ、月次の想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003は 1,200×120＋600×15＝153,000円（日額交通費に想定労働日数を掛ける）（b）EMP-003の日次は 想定勤務時間・想定給与・給与実績差分が「—」。給与は 1,200×実働時間＋600＋深夜残業代＋ヘルプ人件費 で表示される（空欄=0件）。計算違い0件</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>従業員詳細の想定労働日数の欄／日別実績でEMP-006が「—」になっていること／入力後に日次が出ること</t>
+          <t>従業員詳細の想定労働日数の欄／月別実績の想定給与／日別実績で時給者の想定給与が「—」・給与は出ていること</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>時給者で未入力のとき日次の想定給与だけ「—」になり、給与は出るか／1日の想定勤務時間が 所定÷想定労働日数 か</t>
+          <t>日額交通費が想定労働日数ぶん月次に入るか／時給者の日次に想定給与を出していないか</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
@@ -5932,7 +5932,7 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>1日の想定勤務時間＝所定労働時間÷想定労働日数。日次の想定給与＝月給者は月次÷想定労働日数／時給者は単位給与額×（所定÷想定労働日数）＋交通費÷想定労働日数。日次×想定労働日数＝月次（判断23・25・26）</t>
+          <t>想定労働日数の用途は日額交通費の月次換算（単位交通費×想定労働日数）と月給者の日次按分。時給者の日次に想定給与は出さない（判断23・26・27）</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -1599,7 +1599,7 @@
       <c r="D16" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
-【操作】右上「従業員登録」「CSVインポート」「設定・実績エクスポート」、2段目「設定取込データへ」、行の詳細アイコン を順に押す。次に店舗フィルタを「渋谷店」にして「この店舗の給与実績一覧へ」「この店舗の設定変更履歴へ」を押す</t>
+【操作】右上「従業員登録」「CSVインポート」「設定・実績エクスポート」、2段目「設定の取込結果」、行の詳細アイコン を順に押す。次に店舗フィルタを「渋谷店」にして「この店舗の給与実績一覧」「この店舗の設定変更履歴へ」を押す</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1610,7 +1610,7 @@
       <c r="F16" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員一覧】
-5経路すべて到達（従業員登録／設定インポート／設定・実績エクスポート／設定取込データ／従業員詳細）。不通=0
+5経路すべて到達（従業員登録／設定インポート／設定・実績エクスポート／設定の取込結果／従業員詳細）。不通=0
 店舗で絞った状態から2経路とも到達し、遷移先が渋谷店で絞り込まれている（絞り込みが引き継がれない=0件）</t>
         </is>
       </c>
@@ -1621,13 +1621,13 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>遷移先5画面の到達直後（従業員登録・設定インポート・エクスポート・設定取込データ・従業員詳細）／店舗で絞った従業員一覧と、そこから開いた給与実績一覧・設定変更履歴（絞り込み条件が見える状態）</t>
+          <t>遷移先5画面の到達直後（従業員登録・設定インポート・エクスポート・設定の取込結果・従業員詳細）／店舗で絞った従業員一覧と、そこから開いた給与実績一覧・設定変更履歴（絞り込み条件が見える状態）</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>従業員一覧 … 右上ツールバー「従業員登録」「CSVインポート」「設定・実績エクスポート」／2段目「設定取込データへ」／行末の詳細アイコン</t>
+          <t>従業員一覧 … 右上ツールバー「従業員登録」「CSVインポート」「設定・実績エクスポート」／2段目「設定の取込結果」／行末の詳細アイコン</t>
         </is>
       </c>
       <c r="K16" s="8" t="inlineStr">
@@ -1900,7 +1900,7 @@
       <c r="D20" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
-【操作】（a）必須を埋めて「登録」（適用日付＝当日）（b）入力途中で「キャンセル」（c）ツールバー「従業員一覧へ」「CSVインポート」</t>
+【操作】（a）必須を埋めて「登録」（適用日付＝当日）（b）入力途中で「キャンセル」（c）ツールバー「従業員一覧」「CSVインポート」</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1927,7 +1927,7 @@
       <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>従業員登録 … 下部「登録」「キャンセル」／ツールバー「従業員一覧へ」「CSVインポート」→ 従業員一覧</t>
+          <t>従業員登録 … 下部「登録」「キャンセル」／ツールバー「従業員一覧」「CSVインポート」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="94" customHeight="1">
+    <row r="53" ht="139" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4378,7 +4378,7 @@
       <c r="D53" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】「列マッピングテンプレート管理」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
+【操作】「列マッピングテンプレート」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -4388,8 +4388,9 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート管理」】
-テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
+          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート」】
+テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる
+リンクのラベルが遷移先の画面名と一字一句そろっている（「〜へ」が付いていない・旧名「従業員設定インポート」が残っていない。食い違い=0件。判断4）</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -4405,12 +4406,12 @@
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>設定インポート → ツールバー「列マッピングテンプレート管理」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
+          <t>設定インポート → ツールバー「列マッピングテンプレート」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>テンプレの登録・編集・削除と往復</t>
+          <t>テンプレの登録・編集・削除と往復／リンク名が画面名と一致しているか</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
@@ -4829,7 +4830,7 @@
       <c r="D59" s="8" t="inlineStr">
         <is>
           <t>【前提】T-I03実施済み
-【操作】サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
+【操作】サイドバー「設定の取込結果」→ 取り込んだファイル・行を確認。次に「実績の取込結果」を開く</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -4839,8 +4840,8 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定取込データ（サイドバー）】
-設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ10列／日別データ10列。交通費・総支給額は表示しない（判断14））</t>
+          <t>【確認場所：設定の取込結果（サイドバー）】
+設定の取込結果＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績の取込結果＝一覧→タブ（月別データ10列／日別データ10列。交通費・総支給額は表示しない（判断14））</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
@@ -4850,13 +4851,13 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>設定取込データと実績取込データの一覧＋各タブ（計4枚）</t>
+          <t>設定の取込結果と実績の取込結果の一覧＋各タブ（計4枚）</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>設定取込データ（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績取込データ … 月別データ／日別データタブ</t>
+          <t>設定の取込結果（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績の取込結果 … 月別データ／日別データタブ</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
@@ -4904,7 +4905,7 @@
       <c r="D60" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05 S-06
-【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
+【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定の取込結果と実績の取込結果で、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -4914,7 +4915,7 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定取込データ／実績取込データ】
+          <t>【確認場所：設定の取込結果／実績の取込結果】
 プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
@@ -4931,7 +4932,7 @@
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>設定取込データ／実績取込データ … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
+          <t>設定の取込結果／実績の取込結果 … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
@@ -4979,7 +4980,7 @@
       <c r="D61" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】給与実績一覧の「実績取込データへ」→ 実績取込データの「給与実績一覧へ」を押す</t>
+【操作】給与実績一覧の「実績の取込結果」→ 実績の取込結果の「給与実績一覧」を押す</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -4989,7 +4990,7 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　「実績取込データへ」／実績取込データ】
+          <t>【確認場所：給与実績一覧　→　「実績の取込結果」／実績の取込結果】
 2経路とも到達する（不通=0）</t>
         </is>
       </c>
@@ -5000,13 +5001,13 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>給与実績一覧→実績取込データ／実績取込データ→給与実績一覧 の到達直後（2枚）</t>
+          <t>給与実績一覧→実績の取込結果／実績の取込結果→給与実績一覧 の到達直後（2枚）</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 「実績取込データへ」／実績取込データ → 「給与実績一覧へ」（相互導線）</t>
+          <t>給与実績一覧 → 「実績の取込結果」／実績の取込結果 → 「給与実績一覧」（相互導線）</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -5862,7 +5862,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="139" customHeight="1">
+    <row r="73" ht="124" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5881,7 +5881,7 @@
       <c r="D73" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-05
-【操作】（a）EMP-001（月給・想定労働日数が未入力）と EMP-003（時給・15日を入力済み・日額交通費600）の月次の想定給与を検算 →（b）日別実績タブで EMP-003 の行を見る</t>
+【操作】（a）EMP-003（時給・想定労働日数15を入力済み）の月次の想定給与を検算 →（b）EMP-003の想定労働日数を空欄にして保存し、打刻から求めた日数が使われるか見る →（c）EMP-001（月給・未入力）の月次と日次を検算</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
@@ -5892,7 +5892,7 @@
       <c r="F73" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
-（a）EMP-001は未入力のため営業日数20日が使われ、月次の想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003は 1,200×120＋600×15＝153,000円（日額交通費に想定労働日数を掛ける）（b）EMP-003の日次は 想定勤務時間・想定給与・給与実績差分が「—」。給与は 1,200×実働時間＋600＋深夜残業代＋ヘルプ人件費 で表示される（空欄=0件）。計算違い0件</t>
+（a）EMP-003の想定給与＝1,200×120＋600×15＝153,000円（b）空欄にしても打刻の出勤日数15日（data/06で2026-05は15日）が使われ、153,000円のまま変わらない（c）EMP-001は打刻20日が使われ、想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003の日次は想定給与・給与実績差分が「—」（判断27）。計算違い0件</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>従業員詳細の想定労働日数の欄／月別実績の想定給与／日別実績で時給者の想定給与が「—」・給与は出ていること</t>
+          <t>従業員詳細の想定労働日数の欄（空欄でも金額が変わらないこと）／月別実績の想定給与／日別実績で時給者の想定給与が「—」であること</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>日額交通費が想定労働日数ぶん月次に入るか／時給者の日次に想定給与を出していないか</t>
+          <t>未入力でも打刻から日数が取れるか／日額交通費が日数ぶん月次に入るか</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
@@ -5933,7 +5933,7 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>想定労働日数の用途は日額交通費の月次換算（単位交通費×想定労働日数）と月給者の日次按分。時給者の日次に想定給与は出さない（判断23・26・27）</t>
+          <t>想定労働日数＝入力値 → 無ければ直近3か月の平均出勤日数（打刻）→ 打刻が無ければ月給者は営業日数。日額交通費の月次換算と月給者の日次按分に使う（判断26・27・28）</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S83"/>
+  <dimension ref="A1:S84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証70ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
+          <t>確かめる手順（準備11行＋検証71ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
 実施順を変えてはいけない箇所：①T-A08（勤怠取込）→T-S03（締め）　②T-S03→T-S04・T-D07→T-S05（この3件は締め済みでしか確認できない）　③C-000（初期化）は計算の先頭　④C-008は計算の最後（2026-05のEMP-001を352,286円に変えるためC-013・C-017が合わなくなる）　⑤T-N02の前にdata/02を再投入　⑥削除はEMP-012（T-L10）とEMP-004（T-D08）だけ
 列の使い方：使用する検証データ＝この検証で投入・使用するdataファイル／期待値＝先頭の【確認場所】でどの画面を見て合否を出すかを示し、続けて合格の基準を書いている／スクショ（撮るもの）＝何が写っていれば証拠になるか／スクショ貼付欄＝撮った画像をこの列に貼る／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めて合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを決める
 色：緑＝使う検証データ　青＝画面　橙＝スクショの指示　紫＝ヘルプ・受入条件との対応　黄＝当日の記入欄。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
@@ -2706,68 +2706,68 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
+    <row r="31" ht="124" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>詳細</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>T-H01</t>
+          <t>T-D12</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>履歴の追記と過去行の不変</t>
+          <t>設定変更履歴の操作がステータスで変わる</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 ／ 変更前の履歴をCSV出力しておく
-【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
+          <t>【前提】S-05
+【操作】（a）従業員詳細（EMP-001）の設定変更履歴で、予約中・適用中・過去の各行の操作ボタンを見る →（b）適用中の行の表示ボタンを押す →（c）設定変更履歴一覧でも同じ規則か見る</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）04 設定変更履歴（適用済3・予約中1）</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定変更履歴一覧】
-履歴が1行増える。既存行の値の差分＝0</t>
+          <t>【確認場所：従業員詳細 → 設定変更履歴／設定変更履歴一覧】
+（a）予約中の行だけに編集・削除ボタンが出る。適用中・過去の行は表示ボタンのみ（編集・削除=0件）（b）読み取り専用のモーダルが開き、「すでに適用された設定のため編集・削除はできません」と出る（c）設定変更履歴一覧にも操作列があり、予約中は編集・削除、適用中・過去は従業員詳細へのリンク</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>T-H01.png</t>
+          <t>T-D12.png</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
+          <t>設定変更履歴の3行（ボタンの違いが分かる状態）／適用中の表示モーダル／設定変更履歴一覧の操作列</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧 … 変更前後の行（既存行が書き換わらないこと）</t>
+          <t>従業員詳細（設定変更履歴）→ 表示モーダル → 設定変更履歴一覧</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>既存行が書き換わらないか</t>
+          <t>適用済みの行に編集・削除が出ていないか</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
+          <t>ケース別 ＞ 適用済みの設定を直したいとき</t>
         </is>
       </c>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>AC-07</t>
+          <t>AC-61</t>
         </is>
       </c>
       <c r="N31" s="5" t="inlineStr"/>
@@ -2777,11 +2777,11 @@
       <c r="R31" s="5" t="inlineStr"/>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t>原則①：過去は不変</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="79" customHeight="1">
+          <t>（金額計算なし）適用済みの履歴を消すと過去の金額が変わるため、編集・削除を出さない（原則②・AC-16）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2789,18 +2789,18 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>T-H02</t>
+          <t>T-H01</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>記録の内容</t>
+          <t>履歴の追記と過去行の不変</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 T-D04実施済み
-【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
+          <t>【前提】S-05 ／ 変更前の履歴をCSV出力しておく
+【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2811,28 +2811,28 @@
       <c r="F32" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定変更履歴一覧】
-①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
+履歴が1行増える。既存行の値の差分＝0</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>T-H02.png</t>
+          <t>T-H01.png</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
+          <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
+          <t>設定変更履歴一覧 … 変更前後の行（既存行が書き換わらないこと）</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>2つの日時が別で記録されるか</t>
+          <t>既存行が書き換わらないか</t>
         </is>
       </c>
       <c r="L32" s="13" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="M32" s="13" t="inlineStr">
         <is>
-          <t>AC-08 AC-09</t>
+          <t>AC-07</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr"/>
@@ -2852,11 +2852,11 @@
       <c r="R32" s="5" t="inlineStr"/>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="94" customHeight="1">
+          <t>原則①：過去は不変</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="79" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2864,18 +2864,18 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>T-H04</t>
+          <t>T-H02</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>履歴の絞り込み・出力・遷移</t>
+          <t>記録の内容</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
+          <t>【前提】S-05 T-D04実施済み
+【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2886,28 +2886,28 @@
       <c r="F33" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定変更履歴一覧】
-店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
+①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>T-H04.png</t>
+          <t>T-H02.png</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
+          <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
+          <t>設定変更履歴一覧 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>絞り込み後の行だけ出力されるか</t>
+          <t>2つの日時が別で記録されるか</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="M33" s="13" t="inlineStr">
         <is>
-          <t>AC-33 AC-36 AC-30</t>
+          <t>AC-08 AC-09</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
@@ -2927,30 +2927,30 @@
       <c r="R33" s="5" t="inlineStr"/>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="199" customHeight="1">
+          <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="94" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>履歴</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>T-A02</t>
+          <t>T-H04</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>月別実績の表示と切替</t>
+          <t>履歴の絞り込み・出力・遷移</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
+【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2960,41 +2960,39 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない
-実績モードでは 想定給与・給与・給与実績差分 が表示され、差分＝給与−想定給与 と一致する
-概算モードでは実績由来の列（給与・給与実績差分・ヘルプ人件費・深夜残業代など）が隠れる。残るのは実績データが無くても値が決まる列だけ（判断22。食い違う列=0件）</t>
+          <t>【確認場所：設定変更履歴一覧】
+店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>T-A02.png</t>
+          <t>T-H04.png</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
+          <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
+          <t>設定変更履歴一覧 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>モード切替で列が増減するか</t>
+          <t>絞り込み後の行だけ出力されるか</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M34" s="13" t="inlineStr">
         <is>
-          <t>AC-10 AC-31 AC-57</t>
+          <t>AC-33 AC-36 AC-30</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr"/>
@@ -3004,11 +3002,11 @@
       <c r="R34" s="5" t="inlineStr"/>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>計算：算式どおりの金額／画面：状態が漏れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="64" customHeight="1">
+          <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="199" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -3016,18 +3014,18 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>T-A09</t>
+          <t>T-A02</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>給与実績一覧からの設定編集</t>
+          <t>月別実績の表示と切替</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】給与実績一覧で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
+【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -3037,39 +3035,41 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　行の「従業員設定」】
-モーダルに14項目が表示される。更新保存で給与実績一覧に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない
+実績モードでは 想定給与・給与・給与実績差分 が表示され、差分＝給与−想定給与 と一致する
+概算モードでは実績由来の列（給与・給与実績差分・ヘルプ人件費・深夜残業代など）が隠れる。残るのは実績データが無くても値が決まる列だけ（判断22。食い違う列=0件）</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>T-A09.png</t>
+          <t>T-A02.png</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>設定編集モーダル（項目が見える状態）／更新保存後の給与実績一覧／従業員詳細の設定変更履歴に行が増えたこと</t>
+          <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 給与実績一覧／確認は従業員詳細の設定変更履歴</t>
+          <t>給与実績一覧 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>モーダル編集でも履歴が残るか</t>
+          <t>モード切替で列が増減するか</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-10 AC-31 AC-57</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr"/>
@@ -3079,11 +3079,11 @@
       <c r="R35" s="5" t="inlineStr"/>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>原則①：どの入口から編集しても履歴が残る</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="139" customHeight="1">
+          <t>計算：算式どおりの金額／画面：状態が漏れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="64" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -3091,18 +3091,18 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>T-A05</t>
+          <t>T-A09</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>日別実績の表示</t>
+          <t>給与実績一覧からの設定編集</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
+【操作】給与実績一覧で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -3112,40 +3112,39 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 日別実績タブ】
-全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない
-日別にモード切替は無いが、想定給与・給与実績差分は表示される</t>
+          <t>【確認場所：給与実績一覧　→　行の「従業員設定」】
+モーダルに14項目が表示される。更新保存で給与実績一覧に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>T-A05.png</t>
+          <t>T-A09.png</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
+          <t>設定編集モーダル（項目が見える状態）／更新保存後の給与実績一覧／従業員詳細の設定変更履歴に行が増えたこと</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
+          <t>給与実績一覧 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 給与実績一覧／確認は従業員詳細の設定変更履歴</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>日別に概算モードが無いか</t>
+          <t>モーダル編集でも履歴が残るか</t>
         </is>
       </c>
       <c r="L36" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
       <c r="M36" s="13" t="inlineStr">
         <is>
-          <t>AC-10 AC-57</t>
+          <t>AC-49</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr"/>
@@ -3155,11 +3154,11 @@
       <c r="R36" s="5" t="inlineStr"/>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>計算：算式どおりの金額</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="64" customHeight="1">
+          <t>原則①：どの入口から編集しても履歴が残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="139" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -3167,18 +3166,18 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>T-A07</t>
+          <t>T-A05</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>実績のCSVエクスポート</t>
+          <t>日別実績の表示</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
+【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -3188,39 +3187,40 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧】
-出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
+          <t>【確認場所：給与実績一覧 → 日別実績タブ】
+全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない
+日別にモード切替は無いが、想定給与・給与実績差分は表示される</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>T-A07.png</t>
+          <t>T-A05.png</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
+          <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
+          <t>給与実績一覧 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>表示中の内容が出力されるか</t>
+          <t>日別に概算モードが無いか</t>
         </is>
       </c>
       <c r="L37" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M37" s="13" t="inlineStr">
         <is>
-          <t>AC-36</t>
+          <t>AC-10 AC-57</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
       <c r="R37" s="5" t="inlineStr"/>
       <c r="S37" s="8" t="inlineStr">
         <is>
-          <t>入出力：画面の内容と一致</t>
+          <t>計算：算式どおりの金額</t>
         </is>
       </c>
     </row>
@@ -3242,18 +3242,18 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>T-A08</t>
+          <t>T-A07</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>勤怠実績の取込</t>
+          <t>実績のCSVエクスポート</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-08
-【操作】給与実績一覧の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
+          <t>【前提】S-05
+【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -3263,39 +3263,39 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
+          <t>【確認場所：給与実績一覧】
+出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>T-A08.png</t>
+          <t>T-A07.png</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
+          <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
+          <t>給与実績一覧 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>進捗が出て他操作を受け付けないか</t>
+          <t>表示中の内容が出力されるか</t>
         </is>
       </c>
       <c r="L38" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M38" s="13" t="inlineStr">
         <is>
-          <t>AC-48</t>
+          <t>AC-36</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr"/>
@@ -3305,62 +3305,62 @@
       <c r="R38" s="5" t="inlineStr"/>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>入出力：勤怠実績を取り込める</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="60" customHeight="1">
+          <t>入出力：画面の内容と一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="64" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>締め</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>T-S01</t>
+          <t>T-A08</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>締めボタンの表示条件</t>
+          <t>勤怠実績の取込</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-08
-【操作】月別実績タブと日別実績タブを順に開く</t>
+          <t>【前提】S-05 S-08
+【操作】給与実績一覧の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧】
-月別のみ「2026-05 締め」が表示。日別には表示されない</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>T-S01.png</t>
+          <t>T-A08.png</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
+          <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
+          <t>給与実績一覧 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>締めが月別タブにだけ出るか</t>
+          <t>進捗が出て他操作を受け付けないか</t>
         </is>
       </c>
       <c r="L39" s="13" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="M39" s="13" t="inlineStr">
         <is>
-          <t>AC-18</t>
+          <t>AC-48</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr"/>
@@ -3380,11 +3380,11 @@
       <c r="R39" s="5" t="inlineStr"/>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めの単位は月</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="64" customHeight="1">
+          <t>入出力：勤怠実績を取り込める</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3392,18 +3392,18 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>T-S03</t>
+          <t>T-S01</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>締めの実行</t>
+          <t>締めボタンの表示条件</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06 S-08
-【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
+          <t>【前提】S-08
+【操作】月別実績タブと日別実績タブを順に開く</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -3413,29 +3413,29 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　月別実績タブ】
-「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
+          <t>【確認場所：給与実績一覧】
+月別のみ「2026-05 締め」が表示。日別には表示されない</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>T-S03.png</t>
+          <t>T-S01.png</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
+          <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
+          <t>給与実績一覧 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>確認モーダルを経て締まるか</t>
+          <t>締めが月別タブにだけ出るか</t>
         </is>
       </c>
       <c r="L40" s="13" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="M40" s="13" t="inlineStr">
         <is>
-          <t>AC-16 AC-19 AC-32</t>
+          <t>AC-18</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr"/>
@@ -3455,11 +3455,11 @@
       <c r="R40" s="5" t="inlineStr"/>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="60" customHeight="1">
+          <t>原則②：締めの単位は月</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="64" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3467,18 +3467,18 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>T-S04</t>
+          <t>T-S03</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>締め後は編集できない</t>
+          <t>締めの実行</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み
-【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
+          <t>【前提】S-06 S-08
+【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -3488,39 +3488,39 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績】
-編集できない（または反映されない）</t>
+          <t>【確認場所：給与実績一覧　→　月別実績タブ】
+「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>T-S04.png</t>
+          <t>T-S03.png</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
+          <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
+          <t>給与実績一覧 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>締め後に金額が動かないか</t>
+          <t>確認モーダルを経て締まるか</t>
         </is>
       </c>
       <c r="L41" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M41" s="13" t="inlineStr">
         <is>
-          <t>AC-16</t>
+          <t>AC-16 AC-19 AC-32</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr"/>
@@ -3530,7 +3530,7 @@
       <c r="R41" s="5" t="inlineStr"/>
       <c r="S41" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない</t>
+          <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
         </is>
       </c>
     </row>
@@ -3542,18 +3542,18 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>T-D07</t>
+          <t>T-S04</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>締め済み期間への遡及</t>
+          <t>締め後は編集できない</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み S-07
-【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
+          <t>【前提】T-S03実施済み
+【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細】
-締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
+          <t>【確認場所：給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績】
+編集できない（または反映されない）</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>T-D07.png</t>
+          <t>T-S04.png</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
+          <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
+          <t>給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
         </is>
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>警告が出て反映されないか</t>
+          <t>締め後に金額が動かないか</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="M42" s="13" t="inlineStr">
         <is>
-          <t>AC-20</t>
+          <t>AC-16</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr"/>
@@ -3605,11 +3605,11 @@
       <c r="R42" s="5" t="inlineStr"/>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t>原則②：遡及は黙って捨てない</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="64" customHeight="1">
+          <t>原則②：締めたら動かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3617,18 +3617,18 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>T-S05</t>
+          <t>T-D07</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>締めの解除</t>
+          <t>締め済み期間への遡及</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み
-【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
+          <t>【前提】T-S03実施済み S-07
+【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -3638,39 +3638,39 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　月別実績タブ】
-「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
+          <t>【確認場所：従業員詳細】
+締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>T-S05.png</t>
+          <t>T-D07.png</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
+          <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
+          <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>解除で再計算されるか</t>
+          <t>警告が出て反映されないか</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
       <c r="M43" s="13" t="inlineStr">
         <is>
-          <t>AC-19</t>
+          <t>AC-20</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr"/>
@@ -3680,7 +3680,7 @@
       <c r="R43" s="5" t="inlineStr"/>
       <c r="S43" s="8" t="inlineStr">
         <is>
-          <t>原則②：確定操作は確認を経る</t>
+          <t>原則②：遡及は黙って捨てない</t>
         </is>
       </c>
     </row>
@@ -3692,18 +3692,18 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>T-S07</t>
+          <t>T-S05</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>締めの実行権限</t>
+          <t>締めの解除</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-10 S-08
-【操作】店長スコープのアカウントでログインし、給与実績一覧を開いて締めを試みる</t>
+          <t>【前提】T-S03実施済み
+【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -3713,39 +3713,39 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ（店長スコープでログイン）】
-締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
+          <t>【確認場所：給与実績一覧　→　月別実績タブ】
+「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>T-S07.png</t>
+          <t>T-S05.png</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>店長スコープでの給与実績一覧（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
+          <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
+          <t>給与実績一覧 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>店長が締められないか</t>
+          <t>解除で再計算されるか</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>AC-41</t>
+          <t>AC-19</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr"/>
@@ -3755,30 +3755,30 @@
       <c r="R44" s="5" t="inlineStr"/>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="79" customHeight="1">
+          <t>原則②：確定操作は確認を経る</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="64" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>取込</t>
+          <t>締め</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>T-I02</t>
+          <t>T-S07</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>テンプレートのDLと画面</t>
+          <t>締めの実行権限</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
+          <t>【前提】S-10 S-08
+【操作】店長スコープのアカウントでログインし、給与実績一覧を開いて締めを試みる</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -3788,39 +3788,39 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ（店長スコープでログイン）】
+締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>T-I02.png</t>
+          <t>T-S07.png</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
+          <t>店長スコープでの給与実績一覧（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
+          <t>給与実績一覧 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>テンプレートの列とBOM</t>
+          <t>店長が締められないか</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ はじめて設定する</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M45" s="13" t="inlineStr">
         <is>
-          <t>AC-21 AC-30</t>
+          <t>AC-41</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr"/>
@@ -3830,7 +3830,7 @@
       <c r="R45" s="5" t="inlineStr"/>
       <c r="S45" s="8" t="inlineStr">
         <is>
-          <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
+          <t>原則②：締めは会社スコープのみ</t>
         </is>
       </c>
     </row>
@@ -3842,50 +3842,50 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>T-I03</t>
+          <t>T-I02</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>King of Time形式の取込</t>
+          <t>テンプレートのDLと画面</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-06
-【操作】データ種類＝King of Time を選び data/07（従業員設定・3行／外部ID 1001・1005・1013）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
+          <t>【前提】S-01
+【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート → 従業員一覧】
-外部ID 1001・1005 は対応表で E0001・E0005 に解決され、既存の従業員が更新される（単位給与額 340,000／360,000）。対応表に無い 1013 は新規として扱われ、従業員IDが自動で付番される。件数は3行</t>
+          <t>【確認場所：設定インポート】
+従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>T-I03.png</t>
+          <t>T-I02.png</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
+          <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
+          <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>3行が更新・追加されるか</t>
+          <t>テンプレートの列とBOM</t>
         </is>
       </c>
       <c r="L46" s="13" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="M46" s="13" t="inlineStr">
         <is>
-          <t>AC-21</t>
+          <t>AC-21 AC-30</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr"/>
@@ -3905,11 +3905,11 @@
       <c r="R46" s="5" t="inlineStr"/>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>入出力：導入を止めない</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="60" customHeight="1">
+          <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="79" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3917,50 +3917,50 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>T-I04</t>
+          <t>T-I03</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>ジョブカン形式（表記ゆれ）の取込</t>
+          <t>King of Time形式の取込</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】データ種類＝ジョブカン を選び data/08（3行／外部ID JB-003・JB-010・JB-014）をD&amp;D → 登録</t>
+【操作】データ種類＝King of Time を選び data/07（従業員設定・3行／外部ID 1001・1005・1013）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>08 取込CSV ジョブカン</t>
+          <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート → 従業員一覧】
-スタッフコード等の表記ゆれを吸収し、外部ID JB-003・JB-010 が E0003・E0010 に解決される。取込成功=3行</t>
+外部ID 1001・1005 は対応表で E0001・E0005 に解決され、既存の従業員が更新される（単位給与額 340,000／360,000）。対応表に無い 1013 は新規として扱われ、従業員IDが自動で付番される。件数は3行</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>T-I04.png</t>
+          <t>T-I03.png</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
+          <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
+          <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>表記ゆれを吸収できるか</t>
+          <t>3行が更新・追加されるか</t>
         </is>
       </c>
       <c r="L47" s="13" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="M47" s="13" t="inlineStr">
         <is>
-          <t>AC-22</t>
+          <t>AC-21</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr"/>
@@ -3980,7 +3980,7 @@
       <c r="R47" s="5" t="inlineStr"/>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収</t>
+          <t>入出力：導入を止めない</t>
         </is>
       </c>
     </row>
@@ -3992,60 +3992,60 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>T-I05</t>
+          <t>T-I04</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>異常系データの検出</t>
+          <t>ジョブカン形式（表記ゆれ）の取込</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】data/09（4行）をD&amp;D → 登録</t>
+【操作】データ種類＝ジョブカン を選び data/08（3行／外部ID JB-003・JB-010・JB-014）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>08 取込CSV ジョブカン</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
+          <t>【確認場所：設定インポート → 従業員一覧】
+スタッフコード等の表記ゆれを吸収し、外部ID JB-003・JB-010 が E0003・E0010 に解決される。取込成功=3行</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>T-I05.png</t>
+          <t>T-I04.png</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
+          <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
+          <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>4種の異常を行ごとに検出するか</t>
+          <t>表記ゆれを吸収できるか</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
+          <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
       <c r="M48" s="13" t="inlineStr">
         <is>
-          <t>AC-23</t>
+          <t>AC-22</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr"/>
@@ -4055,11 +4055,11 @@
       <c r="R48" s="5" t="inlineStr"/>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="64" customHeight="1">
+          <t>入出力：表記ゆれを吸収</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4067,50 +4067,50 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>T-I17</t>
+          <t>T-I05</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>二重登録の防止</t>
+          <t>異常系データの検出</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】（a）data/07を2回続けて取り込む （b）data/19（外部ID 1002 が2行・単位給与額が異なる）を取り込む</t>
+【操作】data/09（4行）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート】
-（a）2回目は更新となり件数が増えない（二重登録=0件）（b）同じ外部IDが2行あるためエラーとして検出され、両方とも登録されない。1つの外部IDが2つの従業員IDに紐づく=0件</t>
+4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>T-I17.png</t>
+          <t>T-I05.png</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
+          <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
+          <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>二重登録されないか</t>
+          <t>4種の異常を行ごとに検出するか</t>
         </is>
       </c>
       <c r="L49" s="13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>AC-40 AC-56</t>
+          <t>AC-23</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
@@ -4130,11 +4130,11 @@
       <c r="R49" s="5" t="inlineStr"/>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>データ保全：二重登録を防ぐ</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="94" customHeight="1">
+          <t>データ保全：不正値を入れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="64" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4142,60 +4142,60 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>T-I20</t>
+          <t>T-I17</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>外部IDの対応と付番</t>
+          <t>二重登録の防止</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】（a）data/20 の対応表を開き、EMP-001 が King of Time 1001 とジョブカン JB-001 の2件を持つことを確認 →（b）対応表に無い外部ID（例 9999）を含むCSVを取り込む →（c）取り込んだ従業員の従業員IDを従業員一覧で確認する</t>
+【操作】（a）data/07を2回続けて取り込む （b）data/19（外部ID 1002 が2行・単位給与額が異なる）を取り込む</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>20 外部ID対応表／07 取込CSV KingOfTime</t>
+          <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：列マッピングテンプレート（外部ID対応）→ 設定インポート → 従業員一覧】
-（a）1名が複数の勤怠システムの外部IDを持てる（E0001＝1001／JB-001）（b）対応表に無い外部IDは取り込まれず、件数と理由が表示される（黙って登録=0件）（c）すべての従業員に従業員IDが付いている（未付番=0件）</t>
+          <t>【確認場所：設定インポート】
+（a）2回目は更新となり件数が増えない（二重登録=0件）（b）同じ外部IDが2行あるためエラーとして検出され、両方とも登録されない。1つの外部IDが2つの従業員IDに紐づく=0件</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>T-I20.png</t>
+          <t>T-I17.png</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>外部ID対応表（EMP-001が2システム分ある状態）／対応表に無い外部IDのエラー表示／従業員一覧の従業員ID列</t>
+          <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート（外部IDの対応）→ 設定インポート → 従業員一覧</t>
+          <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>外部IDが従業員IDに解決されるか／未登録は弾かれるか</t>
+          <t>二重登録されないか</t>
         </is>
       </c>
       <c r="L50" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="M50" s="13" t="inlineStr">
         <is>
-          <t>AC-55 AC-56</t>
+          <t>AC-40 AC-56</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr"/>
@@ -4205,7 +4205,7 @@
       <c r="R50" s="5" t="inlineStr"/>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>データ保全：従業員の同一性を保つ／入出力：ID体系の違いを吸収</t>
+          <t>データ保全：二重登録を防ぐ</t>
         </is>
       </c>
     </row>
@@ -4217,60 +4217,60 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>T-I18</t>
+          <t>T-I20</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>取込が途中で失敗したときの扱い</t>
+          <t>外部IDの対応と付番</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
+【操作】（a）data/20 の対応表を開き、EMP-001 が King of Time 1001 とジョブカン JB-001 の2件を持つことを確認 →（b）対応表に無い外部ID（例 9999）を含むCSVを取り込む →（c）取り込んだ従業員の従業員IDを従業員一覧で確認する</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>20 外部ID対応表／07 取込CSV KingOfTime</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録】
-中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
+          <t>【確認場所：列マッピングテンプレート（外部ID対応）→ 設定インポート → 従業員一覧】
+（a）1名が複数の勤怠システムの外部IDを持てる（E0001＝1001／JB-001）（b）対応表に無い外部IDは取り込まれず、件数と理由が表示される（黙って登録=0件）（c）すべての従業員に従業員IDが付いている（未付番=0件）</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>T-I18.png</t>
+          <t>T-I20.png</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
+          <t>外部ID対応表（EMP-001が2システム分ある状態）／対応表に無い外部IDのエラー表示／従業員一覧の従業員ID列</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録されていないこと）</t>
+          <t>列マッピングテンプレート（外部IDの対応）→ 設定インポート → 従業員一覧</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>部分登録が残らないか</t>
+          <t>外部IDが従業員IDに解決されるか／未登録は弾かれるか</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M51" s="13" t="inlineStr">
         <is>
-          <t>AC-42</t>
+          <t>AC-55 AC-56</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr"/>
@@ -4280,11 +4280,11 @@
       <c r="R51" s="5" t="inlineStr"/>
       <c r="S51" s="8" t="inlineStr">
         <is>
-          <t>データ保全：中途半端に残さない</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="64" customHeight="1">
+          <t>データ保全：従業員の同一性を保つ／入出力：ID体系の違いを吸収</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="94" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4292,60 +4292,60 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>T-I11</t>
+          <t>T-I18</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>CSV位置合わせ設定</t>
+          <t>取込が途中で失敗したときの扱い</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06
-【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
+          <t>【前提】S-04 S-06
+【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>11 取込CSV 説明行あり</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-余計な行が無視され、3行が正しく取り込まれる</t>
+          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録】
+中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>T-I11.png</t>
+          <t>T-I18.png</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
+          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
+          <t>設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録されていないこと）</t>
         </is>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>説明行を飛ばして取り込めるか</t>
+          <t>部分登録が残らないか</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="M52" s="13" t="inlineStr">
         <is>
-          <t>AC-37</t>
+          <t>AC-42</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr"/>
@@ -4355,11 +4355,11 @@
       <c r="R52" s="5" t="inlineStr"/>
       <c r="S52" s="8" t="inlineStr">
         <is>
-          <t>入出力：現場のCSVをそのまま使える</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="139" customHeight="1">
+          <t>データ保全：中途半端に残さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="64" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4367,51 +4367,50 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>T-I09</t>
+          <t>T-I11</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>CSV位置合わせ設定</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】「列マッピングテンプレート」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
+【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>11 取込CSV 説明行あり</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート」】
-テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる
-リンクのラベルが遷移先の画面名と一字一句そろっている（「〜へ」が付いていない・旧名「従業員設定インポート」が残っていない。食い違い=0件。判断4）</t>
+          <t>【確認場所：設定インポート】
+余計な行が無視され、3行が正しく取り込まれる</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>T-I09.png</t>
+          <t>T-I11.png</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
+          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>設定インポート → ツールバー「列マッピングテンプレート」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
+          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>テンプレの登録・編集・削除と往復／リンク名が画面名と一致しているか</t>
+          <t>説明行を飛ばして取り込めるか</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
@@ -4421,7 +4420,7 @@
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>AC-24 AC-38 AC-30</t>
+          <t>AC-37</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr"/>
@@ -4431,11 +4430,11 @@
       <c r="R53" s="5" t="inlineStr"/>
       <c r="S53" s="8" t="inlineStr">
         <is>
-          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="79" customHeight="1">
+          <t>入出力：現場のCSVをそのまま使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="139" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4443,50 +4442,51 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>T-I19</t>
+          <t>T-I09</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>マッピング表の一括登録</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
+【操作】「列マッピングテンプレート」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>18 列マッピング表テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：列マッピングテンプレート】
-テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
+          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート」】
+テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる
+リンクのラベルが遷移先の画面名と一字一句そろっている（「〜へ」が付いていない・旧名「従業員設定インポート」が残っていない。食い違い=0件。判断4）</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>T-I19.png</t>
+          <t>T-I09.png</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
+          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
+          <t>設定インポート → ツールバー「列マッピングテンプレート」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>一括登録と10MB超の扱い</t>
+          <t>テンプレの登録・編集・削除と往復／リンク名が画面名と一致しているか</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="M54" s="13" t="inlineStr">
         <is>
-          <t>AC-51</t>
+          <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr"/>
@@ -4506,72 +4506,72 @@
       <c r="R54" s="5" t="inlineStr"/>
       <c r="S54" s="8" t="inlineStr">
         <is>
-          <t>入出力：マッピングの一括運用</t>
+          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="55" ht="79" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>取込</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>T-E04</t>
+          <t>T-I19</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>設定のエクスポート</t>
+          <t>マッピング表の一括登録</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
+          <t>【前提】S-06
+【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>18 列マッピング表テンプレ</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
-専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
+          <t>【確認場所：列マッピングテンプレート】
+テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>T-E04.png</t>
+          <t>T-I19.png</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
+          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
+          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>選んだ項目だけ・対象数だけ出るか</t>
+          <t>一括登録と10MB超の扱い</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M55" s="13" t="inlineStr">
         <is>
-          <t>AC-25 AC-26 AC-30</t>
+          <t>AC-51</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
@@ -4581,7 +4581,7 @@
       <c r="R55" s="5" t="inlineStr"/>
       <c r="S55" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
+          <t>入出力：マッピングの一括運用</t>
         </is>
       </c>
     </row>
@@ -4593,51 +4593,50 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>T-E09</t>
+          <t>T-E04</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>実績・同時のエクスポート</t>
+          <t>設定のエクスポート</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（給与実績差分を含む）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
+          <t>【前提】S-04
+【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート】
-実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される
-実績の項目に給与実績差分が選べ、出力値＝実績給与−概算給与と一致する</t>
+          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
+専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>T-E09.png</t>
+          <t>T-E04.png</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
+          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
+          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>実績と同時選択のファイル数</t>
+          <t>選んだ項目だけ・対象数だけ出るか</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
@@ -4647,7 +4646,7 @@
       </c>
       <c r="M56" s="13" t="inlineStr">
         <is>
-          <t>AC-25 AC-57</t>
+          <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr"/>
@@ -4657,11 +4656,11 @@
       <c r="R56" s="5" t="inlineStr"/>
       <c r="S56" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="60" customHeight="1">
+          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="79" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4669,50 +4668,51 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>T-E07</t>
+          <t>T-E09</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>未選択でのエクスポート防止</t>
+          <t>実績・同時のエクスポート</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
+          <t>【前提】S-05
+【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（給与実績差分を含む）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
+実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される
+実績の項目に給与実績差分が選べ、出力値＝実績給与−概算給与と一致する</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>T-E07.png</t>
+          <t>T-E09.png</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
+          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
+          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>未選択で出力されないか</t>
+          <t>実績と同時選択のファイル数</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="M57" s="13" t="inlineStr">
         <is>
-          <t>AC-27</t>
+          <t>AC-25 AC-57</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr"/>
@@ -4732,7 +4732,7 @@
       <c r="R57" s="5" t="inlineStr"/>
       <c r="S57" s="8" t="inlineStr">
         <is>
-          <t>入出力：空振りを防ぐ</t>
+          <t>入出力：渡し先に合わせて出せる</t>
         </is>
       </c>
     </row>
@@ -4744,18 +4744,18 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>T-E08</t>
+          <t>T-E07</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>出力CSVの文字化け</t>
+          <t>未選択でのエクスポート防止</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 ／ T-E04で出力済み
-【操作】T-E04で出力したCSVをExcelで開く</t>
+          <t>【前提】S-04
+【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -4766,28 +4766,28 @@
       <c r="F58" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
+警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>T-E08.png</t>
+          <t>T-E07.png</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
+          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
+          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
         </is>
       </c>
       <c r="K58" s="8" t="inlineStr">
         <is>
-          <t>Excelで文字化けしないか</t>
+          <t>未選択で出力されないか</t>
         </is>
       </c>
       <c r="L58" s="13" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>AC-28</t>
+          <t>AC-27</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr"/>
@@ -4807,72 +4807,72 @@
       <c r="R58" s="5" t="inlineStr"/>
       <c r="S58" s="8" t="inlineStr">
         <is>
-          <t>入出力：そのまま提出できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="79" customHeight="1">
+          <t>入出力：空振りを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>取込データ</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>T-N01</t>
+          <t>T-E08</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>取込元データの確認</t>
+          <t>出力CSVの文字化け</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-I03実施済み
-【操作】サイドバー「設定の取込結果」→ 取り込んだファイル・行を確認。次に「実績の取込結果」を開く</t>
+          <t>【前提】S-04 ／ T-E04で出力済み
+【操作】T-E04で出力したCSVをExcelで開く</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定の取込結果（サイドバー）】
-設定の取込結果＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績の取込結果＝一覧→タブ（月別データ10列／日別データ10列。交通費・総支給額は表示しない（判断14））</t>
+          <t>【確認場所：設定・実績エクスポート】
+日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>T-N01.png</t>
+          <t>T-E08.png</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>設定の取込結果と実績の取込結果の一覧＋各タブ（計4枚）</t>
+          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>設定の取込結果（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績の取込結果 … 月別データ／日別データタブ</t>
+          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>元データとタブの構成</t>
+          <t>Excelで文字化けしないか</t>
         </is>
       </c>
       <c r="L59" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M59" s="13" t="inlineStr">
         <is>
-          <t>AC-39</t>
+          <t>AC-28</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr"/>
@@ -4882,11 +4882,11 @@
       <c r="R59" s="5" t="inlineStr"/>
       <c r="S59" s="8" t="inlineStr">
         <is>
-          <t>入出力：原因を追える</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="94" customHeight="1">
+          <t>入出力：そのまま提出できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="79" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -4894,50 +4894,50 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>T-N02</t>
+          <t>T-N01</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>取込前のプレビューと前回差分</t>
+          <t>取込元データの確認</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-06
-【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定の取込結果と実績の取込結果で、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
+          <t>【前提】T-I03実施済み
+【操作】サイドバー「設定の取込結果」→ 取り込んだファイル・行を確認。次に「実績の取込結果」を開く</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定の取込結果／実績の取込結果】
-プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
+          <t>【確認場所：設定の取込結果（サイドバー）】
+設定の取込結果＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績の取込結果＝一覧→タブ（月別データ10列／日別データ10列。交通費・総支給額は表示しない（判断14））</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>T-N02.png</t>
+          <t>T-N01.png</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
+          <t>設定の取込結果と実績の取込結果の一覧＋各タブ（計4枚）</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>設定の取込結果／実績の取込結果 … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
+          <t>設定の取込結果（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績の取込結果 … 月別データ／日別データタブ</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>差分がdata/16・17と一致するか</t>
+          <t>元データとタブの構成</t>
         </is>
       </c>
       <c r="L60" s="13" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="M60" s="13" t="inlineStr">
         <is>
-          <t>AC-50</t>
+          <t>AC-39</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr"/>
@@ -4957,11 +4957,11 @@
       <c r="R60" s="5" t="inlineStr"/>
       <c r="S60" s="8" t="inlineStr">
         <is>
-          <t>データ保全：取り込む前に気づける</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="60" customHeight="1">
+          <t>入出力：原因を追える</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="94" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -4969,50 +4969,50 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>T-N03</t>
+          <t>T-N02</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>取込データと給与実績一覧の相互導線</t>
+          <t>取込前のプレビューと前回差分</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】給与実績一覧の「実績の取込結果」→ 実績の取込結果の「給与実績一覧」を押す</t>
+          <t>【前提】S-05 S-06
+【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定の取込結果と実績の取込結果で、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　「実績の取込結果」／実績の取込結果】
-2経路とも到達する（不通=0）</t>
+          <t>【確認場所：設定の取込結果／実績の取込結果】
+プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>T-N03.png</t>
+          <t>T-N02.png</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>給与実績一覧→実績の取込結果／実績の取込結果→給与実績一覧 の到達直後（2枚）</t>
+          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 「実績の取込結果」／実績の取込結果 → 「給与実績一覧」（相互導線）</t>
+          <t>設定の取込結果／実績の取込結果 … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>2経路とも到達するか</t>
+          <t>差分がdata/16・17と一致するか</t>
         </is>
       </c>
       <c r="L61" s="13" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>AC-30</t>
+          <t>AC-50</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr"/>
@@ -5032,72 +5032,72 @@
       <c r="R61" s="5" t="inlineStr"/>
       <c r="S61" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る</t>
+          <t>データ保全：取り込む前に気づける</t>
         </is>
       </c>
     </row>
     <row r="62" ht="60" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>T-Z01</t>
+          <t>T-N03</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>移行前後の突合（既存データ）</t>
+          <t>取込データと給与実績一覧の相互導線</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 S-11
-【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
+          <t>【前提】S-05
+【操作】給与実績一覧の「実績の取込結果」→ 実績の取込結果の「給与実績一覧」を押す</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員一覧】
-件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
+          <t>【確認場所：給与実績一覧　→　「実績の取込結果」／実績の取込結果】
+2経路とも到達する（不通=0）</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>T-Z01.png</t>
+          <t>T-N03.png</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
+          <t>給与実績一覧→実績の取込結果／実績の取込結果→給与実績一覧 の到達直後（2枚）</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
+          <t>給与実績一覧 → 「実績の取込結果」／実績の取込結果 → 「給与実績一覧」（相互導線）</t>
         </is>
       </c>
       <c r="K62" s="8" t="inlineStr">
         <is>
-          <t>移行前後で差分0件か</t>
+          <t>2経路とも到達するか</t>
         </is>
       </c>
       <c r="L62" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ すでにご利用中のお客様</t>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
       <c r="M62" s="13" t="inlineStr">
         <is>
-          <t>AC-01</t>
+          <t>AC-30</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr"/>
@@ -5107,11 +5107,11 @@
       <c r="R62" s="5" t="inlineStr"/>
       <c r="S62" s="8" t="inlineStr">
         <is>
-          <t>移行：既存顧客が壊れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="94" customHeight="1">
+          <t>画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
           <t>横断</t>
@@ -5119,51 +5119,50 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>T-Z02</t>
+          <t>T-Z01</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>移行後の適用日付の付与</t>
+          <t>移行前後の突合（既存データ）</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
+          <t>【前提】S-09 S-11
+【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細 → 設定変更履歴／設定変更履歴一覧】
-適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている
-あわせて、すべての従業員に従業員IDが付番されている（未付番=0件）。外部IDは対応表に移されている</t>
+          <t>【確認場所：従業員一覧】
+件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>T-Z02.png</t>
+          <t>T-Z01.png</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
+          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 設定変更履歴／設定変更履歴一覧 … 適用日付の空欄</t>
+          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr">
         <is>
-          <t>適用日付の空欄が0件か</t>
+          <t>移行前後で差分0件か</t>
         </is>
       </c>
       <c r="L63" s="13" t="inlineStr">
@@ -5173,7 +5172,7 @@
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>AC-02 AC-55</t>
+          <t>AC-01</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr"/>
@@ -5183,11 +5182,11 @@
       <c r="R63" s="5" t="inlineStr"/>
       <c r="S63" s="8" t="inlineStr">
         <is>
-          <t>移行：履歴の起点を作る</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="60" customHeight="1">
+          <t>移行：既存顧客が壊れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="94" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
           <t>横断</t>
@@ -5195,50 +5194,51 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>T-Z03</t>
+          <t>T-Z02</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>移行前後の過去月の人件費</t>
+          <t>移行後の適用日付の付与</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
           <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行前に出力しておいた直近3か月の給与実績一覧と、移行後の同3か月を突合する</t>
+【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
+          <t>【確認場所：従業員詳細 → 設定変更履歴／設定変更履歴一覧】
+適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている
+あわせて、すべての従業員に従業員IDが付番されている（未付番=0件）。外部IDは対応表に移されている</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>T-Z03.png</t>
+          <t>T-Z02.png</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>移行前後の給与実績一覧 月別実績（直近3か月・金額が同じであること）</t>
+          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ … 移行前後の直近3か月</t>
+          <t>従業員詳細 → 設定変更履歴／設定変更履歴一覧 … 適用日付の空欄</t>
         </is>
       </c>
       <c r="K64" s="8" t="inlineStr">
         <is>
-          <t>過去3か月の金額が変わらないか</t>
+          <t>適用日付の空欄が0件か</t>
         </is>
       </c>
       <c r="L64" s="13" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="M64" s="13" t="inlineStr">
         <is>
-          <t>AC-03</t>
+          <t>AC-02 AC-55</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr"/>
@@ -5258,7 +5258,7 @@
       <c r="R64" s="5" t="inlineStr"/>
       <c r="S64" s="8" t="inlineStr">
         <is>
-          <t>移行：過去が動かない</t>
+          <t>移行：履歴の起点を作る</t>
         </is>
       </c>
     </row>
@@ -5270,60 +5270,60 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>T-Z04</t>
+          <t>T-Z03</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>サイドバーの構成</t>
+          <t>移行前後の過去月の人件費</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
+          <t>【前提】S-09 ／ T-Z01実施済み
+【操作】移行前に出力しておいた直近3か月の給与実績一覧と、移行後の同3か月を突合する</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：サイドバー「従業員管理」】
-閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>T-Z04.png</t>
+          <t>T-Z03.png</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
+          <t>移行前後の給与実績一覧 月別実績（直近3か月・金額が同じであること）</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="12" t="inlineStr">
         <is>
-          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
+          <t>給与実績一覧 → 月別実績タブ … 移行前後の直近3か月</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>PC・モバイルとも開くか</t>
+          <t>過去3か月の金額が変わらないか</t>
         </is>
       </c>
       <c r="L65" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・画面構成）</t>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
       <c r="M65" s="13" t="inlineStr">
         <is>
-          <t>AC-29</t>
+          <t>AC-03</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr"/>
@@ -5333,7 +5333,7 @@
       <c r="R65" s="5" t="inlineStr"/>
       <c r="S65" s="8" t="inlineStr">
         <is>
-          <t>画面：たどり着ける</t>
+          <t>移行：過去が動かない</t>
         </is>
       </c>
     </row>
@@ -5345,60 +5345,60 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>T-Z05</t>
+          <t>T-Z04</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>遷移と表示規則の網羅</t>
+          <t>サイドバーの構成</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-05
-【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+          <t>【前提】S-01
+【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
-すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+          <t>【確認場所：サイドバー「従業員管理」】
+閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>T-Z05.png</t>
+          <t>T-Z04.png</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
+          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
         </is>
       </c>
       <c r="K66" s="8" t="inlineStr">
         <is>
-          <t>75本の遷移と表示規則</t>
+          <t>PC・モバイルとも開くか</t>
         </is>
       </c>
       <c r="L66" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・遷移網羅）</t>
+          <t>（ヘルプ記載なし・画面構成）</t>
         </is>
       </c>
       <c r="M66" s="13" t="inlineStr">
         <is>
-          <t>AC-30 AC-01</t>
+          <t>AC-29</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr"/>
@@ -5408,72 +5408,72 @@
       <c r="R66" s="5" t="inlineStr"/>
       <c r="S66" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="79" customHeight="1">
-      <c r="A67" s="14" t="inlineStr">
-        <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>C-000</t>
-        </is>
-      </c>
-      <c r="C67" s="15" t="inlineStr">
-        <is>
-          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
-        </is>
-      </c>
-      <c r="D67" s="15" t="inlineStr">
-        <is>
-          <t>【前提】S-03 S-05
-【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
-        </is>
-      </c>
-      <c r="E67" s="15" t="inlineStr">
-        <is>
-          <t>02〜06・13を再投入（初期化）</t>
-        </is>
-      </c>
-      <c r="F67" s="15" t="inlineStr">
-        <is>
-          <t>【確認場所：従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未】
-従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
-        </is>
-      </c>
-      <c r="G67" s="14" t="inlineStr">
-        <is>
-          <t>C-000.png</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="inlineStr">
-        <is>
-          <t>初期化後の従業員一覧（12名）と給与実績一覧（未締め・S-05時点の金額）</t>
+          <t>画面：たどり着ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>T-Z05</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>遷移と表示規則の網羅</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>【前提】S-04 S-05
+【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
+すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>T-Z05.png</t>
+        </is>
+      </c>
+      <c r="H67" s="11" t="inlineStr">
+        <is>
+          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="15" t="inlineStr">
-        <is>
-          <t>従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未締めに戻す）</t>
-        </is>
-      </c>
-      <c r="K67" s="15" t="inlineStr">
-        <is>
-          <t>S-05時点の値に戻ったか</t>
-        </is>
-      </c>
-      <c r="L67" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため対応なし）</t>
-        </is>
-      </c>
-      <c r="M67" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J67" s="12" t="inlineStr">
+        <is>
+          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+        </is>
+      </c>
+      <c r="K67" s="8" t="inlineStr">
+        <is>
+          <t>75本の遷移と表示規則</t>
+        </is>
+      </c>
+      <c r="L67" s="13" t="inlineStr">
+        <is>
+          <t>（ヘルプ記載なし・遷移網羅）</t>
+        </is>
+      </c>
+      <c r="M67" s="13" t="inlineStr">
+        <is>
+          <t>AC-30 AC-01</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr"/>
@@ -5481,13 +5481,13 @@
       <c r="P67" s="6" t="inlineStr"/>
       <c r="Q67" s="5" t="inlineStr"/>
       <c r="R67" s="5" t="inlineStr"/>
-      <c r="S67" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="64" customHeight="1">
+      <c r="S67" s="8" t="inlineStr">
+        <is>
+          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="79" customHeight="1">
       <c r="A68" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5495,60 +5495,60 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>C-001</t>
+          <t>C-000</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプなし）</t>
+          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-002（概算280,000・基礎時給1,750・深夜2h・所属店舗の交通費15,000）と EMP-007（概算300,000・基礎時給1,875・深夜4h・交通費30,000）を検算</t>
+          <t>【前提】S-03 S-05
+【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>02〜06・13を再投入（初期化）</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
-EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
+          <t>【確認場所：従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未】
+従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>C-001.png</t>
+          <t>C-000.png</t>
         </is>
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
+          <t>初期化後の従業員一覧（12名）と給与実績一覧（未締め・S-05時点の金額）</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
+          <t>従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未締めに戻す）</t>
         </is>
       </c>
       <c r="K68" s="15" t="inlineStr">
         <is>
-          <t>概算＋深夜＝実績給与か</t>
+          <t>S-05時点の値に戻ったか</t>
         </is>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>（初期化のため対応なし）</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr"/>
@@ -5558,11 +5558,11 @@
       <c r="R68" s="5" t="inlineStr"/>
       <c r="S68" s="15" t="inlineStr">
         <is>
-          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="79" customHeight="1">
+          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="64" customHeight="1">
       <c r="A69" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5570,60 +5570,60 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>C-003</t>
+          <t>C-001</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプあり）</t>
+          <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-001（概算320,000・深夜6h・ヘルプ22h／所属店舗の交通費18,000・ヘルプ先の交通費1,600）／EMP-005（概算350,000・深夜10h・ヘルプ35h／22,000・3,100）／EMP-003（概算144,000・ヘルプ20h／9,000・1,300）を検算</t>
+【操作】2026-05の EMP-002（概算280,000・基礎時給1,750・深夜2h・所属店舗の交通費15,000）と EMP-007（概算300,000・基礎時給1,875・深夜4h・交通費30,000）を検算</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F69" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
-EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算＋深夜＋みなし超過＋交通費）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
+EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
         </is>
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>C-003.png</t>
+          <t>C-001.png</t>
         </is>
       </c>
       <c r="H69" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
+          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
         </is>
       </c>
       <c r="K69" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費が按分で振替されるか</t>
+          <t>概算＋深夜＝実績給与か</t>
         </is>
       </c>
       <c r="L69" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M69" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr"/>
@@ -5633,11 +5633,11 @@
       <c r="R69" s="5" t="inlineStr"/>
       <c r="S69" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="60" customHeight="1">
+          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="79" customHeight="1">
       <c r="A70" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5645,50 +5645,50 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>C-005</t>
+          <t>C-003</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計と全社合計の一致</t>
+          <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】2026-05の EMP-001（概算320,000・深夜6h・ヘルプ22h／所属店舗の交通費18,000・ヘルプ先の交通費1,600）／EMP-005（概算350,000・深夜10h・ヘルプ35h／22,000・3,100）／EMP-003（概算144,000・ヘルプ20h／9,000・1,300）を検算</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
-店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
+EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算＋深夜＋みなし超過＋交通費）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>C-005.png</t>
+          <t>C-003.png</t>
         </is>
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
+          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
         </is>
       </c>
       <c r="K70" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計＝全社（差0円）か</t>
+          <t>ヘルプ人件費が按分で振替されるか</t>
         </is>
       </c>
       <c r="L70" s="15" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>AC-11</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr"/>
@@ -5708,11 +5708,11 @@
       <c r="R70" s="5" t="inlineStr"/>
       <c r="S70" s="15" t="inlineStr">
         <is>
-          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="79" customHeight="1">
+          <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="60" customHeight="1">
       <c r="A71" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5720,60 +5720,60 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>C-006</t>
+          <t>C-005</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>月中改定と予約の日割り</t>
+          <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>14 勤務データ 2026-06</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従】
-6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
+店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>C-006.png</t>
+          <t>C-005.png</t>
         </is>
       </c>
       <c r="H71" s="15" t="inlineStr">
         <is>
-          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
+          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
         <is>
-          <t>所定労働日割になっているか</t>
+          <t>店舗別合計＝全社（差0円）か</t>
         </is>
       </c>
       <c r="L71" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>AC-12 AC-04</t>
+          <t>AC-11</t>
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr"/>
@@ -5783,11 +5783,11 @@
       <c r="R71" s="5" t="inlineStr"/>
       <c r="S71" s="15" t="inlineStr">
         <is>
-          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="64" customHeight="1">
+          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="79" customHeight="1">
       <c r="A72" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5795,60 +5795,60 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>C-011</t>
+          <t>C-006</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>月中改定と予約の日割り</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
+【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・14 勤務データ 2026-06</t>
+          <t>14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　月別実績タブ】
-5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従】
+6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>C-011.png</t>
+          <t>C-006.png</t>
         </is>
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
+          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
+          <t>給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
         </is>
       </c>
       <c r="K72" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>所定労働日割になっているか</t>
         </is>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>AC-13</t>
+          <t>AC-12 AC-04</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr"/>
@@ -5858,11 +5858,11 @@
       <c r="R72" s="5" t="inlineStr"/>
       <c r="S72" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="124" customHeight="1">
+          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="64" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5870,60 +5870,60 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>C-018</t>
+          <t>C-011</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>想定労働日数と日次の想定給与</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-05
-【操作】（a）EMP-003（時給・想定労働日数15を入力済み）の月次の想定給与を検算 →（b）EMP-003の想定労働日数を空欄にして保存し、打刻から求めた日数が使われるか見る →（c）EMP-001（月給・未入力）の月次と日次を検算</t>
+          <t>【前提】C-000 S-07 ／ data/14を投入
+【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ・05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績・14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
-（a）EMP-003の想定給与＝1,200×120＋600×15＝153,000円（b）空欄にしても打刻の出勤日数15日（data/06で2026-05は15日）が使われ、153,000円のまま変わらない（c）EMP-001は打刻20日が使われ、想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003の日次は想定給与・給与実績差分が「—」（判断27）。計算違い0件</t>
+          <t>【確認場所：給与実績一覧　→　月別実績タブ】
+5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>C-018.png</t>
+          <t>C-011.png</t>
         </is>
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>従業員詳細の想定労働日数の欄（空欄でも金額が変わらないこと）／月別実績の想定給与／日別実績で時給者の想定給与が「—」であること</t>
+          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="15" t="inlineStr">
         <is>
-          <t>従業員詳細（想定労働日数）→ 給与実績一覧 日別実績（想定給与）</t>
+          <t>給与実績一覧 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>未入力でも打刻から日数が取れるか／日額交通費が日数ぶん月次に入るか</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M73" s="15" t="inlineStr">
         <is>
-          <t>AC-59</t>
+          <t>AC-13</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr"/>
@@ -5933,11 +5933,11 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>想定労働日数＝入力値 → 無ければ直近3か月の平均出勤日数（打刻）→ 打刻が無ければ月給者は営業日数。日額交通費の月次換算と月給者の日次按分に使う（判断26・27・28）</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="109" customHeight="1">
+          <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="124" customHeight="1">
       <c r="A74" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5945,50 +5945,50 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>C-019</t>
+          <t>C-018</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>日別の概算モード（営業日でならした見込み）</t>
+          <t>想定労働日数と日次の想定給与</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-05
-【操作】給与実績一覧 → 日別実績タブ → 給与計算モードを「概算」に切り替える → 当月の全営業日ぶんの行が出ることと、日別の合計を確認する</t>
+【操作】（a）EMP-003（時給・想定労働日数15を入力済み）の月次の想定給与を検算 →（b）EMP-003の想定労働日数を空欄にして保存し、打刻から求めた日数が使われるか見る →（c）EMP-001（月給・未入力）の月次と日次を検算</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ・05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 日別実績タブ → 給与計算モード＝概算】
-実績が無い日も含めて当月の全営業日に行が出る。1日あたり＝月次の概算給与÷当月の営業日数。日別を全部足すと月次の概算給与と一致する（差 0円）。実績モードに戻すと想定給与列は月次概算÷想定労働日数の額に変わる（同じ日でも額が違う）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
+（a）EMP-003の想定給与＝1,200×120＋600×15＝153,000円（b）空欄にしても打刻の出勤日数15日（data/06で2026-05は15日）が使われ、153,000円のまま変わらない（c）EMP-001は打刻20日が使われ、想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003の日次は想定給与・給与実績差分が「—」（判断27）。計算違い0件</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>C-019.png</t>
+          <t>C-018.png</t>
         </is>
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>概算モードの日別（全営業日に行が出ている）／合計が月次の概算給与と一致していること／実績モードに戻したときの想定給与列</t>
+          <t>従業員詳細の想定労働日数の欄（空欄でも金額が変わらないこと）／月別実績の想定給与／日別実績で時給者の想定給与が「—」であること</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 日別実績（概算モード ↔ 実績モード）</t>
+          <t>従業員詳細（想定労働日数）→ 給与実績一覧 日別実績（想定給与）</t>
         </is>
       </c>
       <c r="K74" s="15" t="inlineStr">
         <is>
-          <t>日別の合計が月次の概算給与と一致するか</t>
+          <t>未入力でも打刻から日数が取れるか／日額交通費が日数ぶん月次に入るか</t>
         </is>
       </c>
       <c r="L74" s="15" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>AC-60</t>
+          <t>AC-59</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr"/>
@@ -6008,11 +6008,11 @@
       <c r="R74" s="5" t="inlineStr"/>
       <c r="S74" s="15" t="inlineStr">
         <is>
-          <t>概算の日別＝月次の概算給与÷当月の営業日数、当月の全営業日に配分。端数は最大剰余で月次と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="94" customHeight="1">
+          <t>想定労働日数＝入力値 → 無ければ直近3か月の平均出勤日数（打刻）→ 打刻が無ければ月給者は営業日数。日額交通費の月次換算と月給者の日次按分に使う（判断26・27・28）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="109" customHeight="1">
       <c r="A75" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6020,60 +6020,60 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-019</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>日別の概算モード（営業日でならした見込み）</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>【前提】C-000 S-05
+【操作】給与実績一覧 → 日別実績タブ → 給与計算モードを「概算」に切り替える → 当月の全営業日ぶんの行が出ることと、日別の合計を確認する</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
-判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
+          <t>【確認場所：給与実績一覧 → 日別実績タブ → 給与計算モード＝概算】
+実績が無い日も含めて当月の全営業日に行が出る。1日あたり＝月次の概算給与÷当月の営業日数。日別を全部足すと月次の概算給与と一致する（差 0円）。実績モードに戻すと想定給与列は月次概算÷想定労働日数の額に変わる（同じ日でも額が違う）</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>C-013.png</t>
+          <t>C-019.png</t>
         </is>
       </c>
       <c r="H75" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
+          <t>概算モードの日別（全営業日に行が出ている）／合計が月次の概算給与と一致していること／実績モードに戻したときの想定給与列</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
+          <t>給与実績一覧 日別実績（概算モード ↔ 実績モード）</t>
         </is>
       </c>
       <c r="K75" s="15" t="inlineStr">
         <is>
-          <t>深夜1.5倍とヘルプの按分単価</t>
+          <t>日別の合計が月次の概算給与と一致するか</t>
         </is>
       </c>
       <c r="L75" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M75" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-60</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
@@ -6083,11 +6083,11 @@
       <c r="R75" s="5" t="inlineStr"/>
       <c r="S75" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="79" customHeight="1">
+          <t>概算の日別＝月次の概算給与÷当月の営業日数、当月の全営業日に配分。端数は最大剰余で月次と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="94" customHeight="1">
       <c r="A76" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6095,60 +6095,60 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-013</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績・日別実績】
-交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
+          <t>【確認場所：給与実績一覧 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
+判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>C-017.png</t>
+          <t>C-013.png</t>
         </is>
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
+          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+          <t>給与実績一覧 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
         </is>
       </c>
       <c r="K76" s="15" t="inlineStr">
         <is>
-          <t>交通費が給与と別費目か</t>
+          <t>深夜1.5倍とヘルプの按分単価</t>
         </is>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr"/>
@@ -6158,11 +6158,11 @@
       <c r="R76" s="5" t="inlineStr"/>
       <c r="S76" s="15" t="inlineStr">
         <is>
-          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="94" customHeight="1">
+          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="79" customHeight="1">
       <c r="A77" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6170,60 +6170,60 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-017</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>交通費の計上先</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07
-【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績・日別実績】
+交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
-          <t>C-008.png</t>
+          <t>C-017.png</t>
         </is>
       </c>
       <c r="H77" s="15" t="inlineStr">
         <is>
-          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
+          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+          <t>給与実績一覧 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
         </is>
       </c>
       <c r="K77" s="15" t="inlineStr">
         <is>
-          <t>締め前後で差0円・解除後に再計算</t>
+          <t>交通費が給与と別費目か</t>
         </is>
       </c>
       <c r="L77" s="15" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M77" s="15" t="inlineStr">
         <is>
-          <t>AC-16 AC-17</t>
+          <t>AC-15</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
@@ -6233,72 +6233,72 @@
       <c r="R77" s="5" t="inlineStr"/>
       <c r="S77" s="15" t="inlineStr">
         <is>
-          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="124" customHeight="1">
-      <c r="A78" s="16" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B78" s="16" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C78" s="17" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="D78" s="17" t="inlineStr">
-        <is>
-          <t>【前提】S-01
-【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
-        </is>
-      </c>
-      <c r="E78" s="17" t="inlineStr">
-        <is>
-          <t>（追加のデータ投入なし）</t>
-        </is>
-      </c>
-      <c r="F78" s="17" t="inlineStr">
-        <is>
-          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
-①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）</t>
-        </is>
-      </c>
-      <c r="G78" s="16" t="inlineStr">
-        <is>
-          <t>R-01.png</t>
-        </is>
-      </c>
-      <c r="H78" s="17" t="inlineStr">
-        <is>
-          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
+          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="94" customHeight="1">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>締めの前後で数字が動かないこと</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-07
+【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>C-008.png</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
-      <c r="J78" s="17" t="inlineStr">
-        <is>
-          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
-        </is>
-      </c>
-      <c r="K78" s="17" t="inlineStr">
-        <is>
-          <t>適用日付と履歴がテーブルにあるか</t>
-        </is>
-      </c>
-      <c r="L78" s="17" t="inlineStr">
-        <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
-        </is>
-      </c>
-      <c r="M78" s="17" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47 AC-55</t>
+      <c r="J78" s="15" t="inlineStr">
+        <is>
+          <t>給与実績一覧 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+        </is>
+      </c>
+      <c r="K78" s="15" t="inlineStr">
+        <is>
+          <t>締め前後で差0円・解除後に再計算</t>
+        </is>
+      </c>
+      <c r="L78" s="15" t="inlineStr">
+        <is>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
+        </is>
+      </c>
+      <c r="M78" s="15" t="inlineStr">
+        <is>
+          <t>AC-16 AC-17</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
@@ -6306,13 +6306,13 @@
       <c r="P78" s="6" t="inlineStr"/>
       <c r="Q78" s="5" t="inlineStr"/>
       <c r="R78" s="5" t="inlineStr"/>
-      <c r="S78" s="17" t="inlineStr">
-        <is>
-          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="79" customHeight="1">
+      <c r="S78" s="15" t="inlineStr">
+        <is>
+          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="124" customHeight="1">
       <c r="A79" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6320,18 +6320,18 @@
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>締めの実装レビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="D79" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
+【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
         </is>
       </c>
       <c r="E79" s="17" t="inlineStr">
@@ -6341,39 +6341,39 @@
       </c>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
-①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所</t>
+          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
+①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）</t>
         </is>
       </c>
       <c r="G79" s="16" t="inlineStr">
         <is>
-          <t>R-02.png</t>
+          <t>R-01.png</t>
         </is>
       </c>
       <c r="H79" s="17" t="inlineStr">
         <is>
-          <t>締めAPIのコードとスコープ判定箇所</t>
+          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
+          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
       </c>
       <c r="K79" s="17" t="inlineStr">
         <is>
-          <t>APIでも店長が締められないか</t>
+          <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
       <c r="L79" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M79" s="17" t="inlineStr">
         <is>
-          <t>AC-16 AC-41</t>
+          <t>AC-07 AC-40 AC-47 AC-55</t>
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr"/>
@@ -6383,7 +6383,7 @@
       <c r="R79" s="5" t="inlineStr"/>
       <c r="S79" s="17" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
+          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
         </is>
       </c>
     </row>
@@ -6395,18 +6395,18 @@
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>入力検証とトランザクションのレビュー</t>
+          <t>締めの実装レビュー</t>
         </is>
       </c>
       <c r="D80" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
+【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
       <c r="E80" s="17" t="inlineStr">
@@ -6416,39 +6416,40 @@
       </c>
       <c r="F80" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
-①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
+          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
+①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所
+適用済みの設定変更履歴は、APIを直接呼んでも更新・削除できない（成功=0件。判断29）</t>
         </is>
       </c>
       <c r="G80" s="16" t="inlineStr">
         <is>
-          <t>R-03.png</t>
+          <t>R-02.png</t>
         </is>
       </c>
       <c r="H80" s="17" t="inlineStr">
         <is>
-          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
+          <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
+          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
       </c>
       <c r="K80" s="17" t="inlineStr">
         <is>
-          <t>APIを直接呼んでも弾かれるか</t>
+          <t>APIでも店長が締められないか／適用済みの履歴が消せないか</t>
         </is>
       </c>
       <c r="L80" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 設定が保存できません</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M80" s="17" t="inlineStr">
         <is>
-          <t>AC-23 AC-42 AC-43</t>
+          <t>AC-16 AC-41 AC-61</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr"/>
@@ -6458,11 +6459,11 @@
       <c r="R80" s="5" t="inlineStr"/>
       <c r="S80" s="17" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="79" customHeight="1">
+          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="109" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6470,18 +6471,18 @@
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの共有レビュー</t>
+          <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
       <c r="D81" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】給与実績一覧・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
       <c r="E81" s="17" t="inlineStr">
@@ -6491,39 +6492,39 @@
       </c>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
-同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
+          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
+①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
         </is>
       </c>
       <c r="G81" s="16" t="inlineStr">
         <is>
-          <t>R-04.png</t>
+          <t>R-03.png</t>
         </is>
       </c>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
+          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
+          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
       </c>
       <c r="K81" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックが1箇所か</t>
+          <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
       <c r="L81" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
       <c r="M81" s="17" t="inlineStr">
         <is>
-          <t>AC-35 AC-11</t>
+          <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
       <c r="N81" s="5" t="inlineStr"/>
@@ -6533,11 +6534,11 @@
       <c r="R81" s="5" t="inlineStr"/>
       <c r="S81" s="17" t="inlineStr">
         <is>
-          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="64" customHeight="1">
+          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="79" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6545,18 +6546,18 @@
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>計算ロジックの共有レビュー</t>
         </is>
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込の列解決の実装を提示してもらう</t>
+【操作】給与実績一覧・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
@@ -6566,39 +6567,39 @@
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
-CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
+          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
+同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
         </is>
       </c>
       <c r="G82" s="16" t="inlineStr">
         <is>
-          <t>R-05.png</t>
+          <t>R-04.png</t>
         </is>
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
+          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
+          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
         </is>
       </c>
       <c r="K82" s="17" t="inlineStr">
         <is>
-          <t>列名がコードに埋まっていないか</t>
+          <t>計算ロジックが1箇所か</t>
         </is>
       </c>
       <c r="L82" s="17" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M82" s="17" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-35 AC-11</t>
         </is>
       </c>
       <c r="N82" s="5" t="inlineStr"/>
@@ -6608,11 +6609,11 @@
       <c r="R82" s="5" t="inlineStr"/>
       <c r="S82" s="17" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="79" customHeight="1">
+          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="64" customHeight="1">
       <c r="A83" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6620,18 +6621,18 @@
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>設定更新処理の共通化レビュー</t>
+          <t>列マッピングの実装レビュー</t>
         </is>
       </c>
       <c r="D83" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+【操作】取込の列解決の実装を提示してもらう</t>
         </is>
       </c>
       <c r="E83" s="17" t="inlineStr">
@@ -6641,39 +6642,39 @@
       </c>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
-設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
+CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
       <c r="G83" s="16" t="inlineStr">
         <is>
-          <t>R-06.png</t>
+          <t>R-05.png</t>
         </is>
       </c>
       <c r="H83" s="17" t="inlineStr">
         <is>
-          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
         </is>
       </c>
       <c r="K83" s="17" t="inlineStr">
         <is>
-          <t>2つの入口で更新処理が共通か</t>
+          <t>列名がコードに埋まっていないか</t>
         </is>
       </c>
       <c r="L83" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M83" s="17" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-22 AC-24</t>
         </is>
       </c>
       <c r="N83" s="5" t="inlineStr"/>
@@ -6683,17 +6684,92 @@
       <c r="R83" s="5" t="inlineStr"/>
       <c r="S83" s="17" t="inlineStr">
         <is>
+          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="79" customHeight="1">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
+設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="G84" s="16" t="inlineStr">
+        <is>
+          <t>R-06.png</t>
+        </is>
+      </c>
+      <c r="H84" s="17" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr"/>
+      <c r="J84" s="17" t="inlineStr">
+        <is>
+          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+        </is>
+      </c>
+      <c r="K84" s="17" t="inlineStr">
+        <is>
+          <t>2つの入口で更新処理が共通か</t>
+        </is>
+      </c>
+      <c r="L84" s="17" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="M84" s="17" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="N84" s="5" t="inlineStr"/>
+      <c r="O84" s="5" t="inlineStr"/>
+      <c r="P84" s="6" t="inlineStr"/>
+      <c r="Q84" s="5" t="inlineStr"/>
+      <c r="R84" s="5" t="inlineStr"/>
+      <c r="S84" s="17" t="inlineStr">
+        <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S83"/>
+  <autoFilter ref="A2:S84"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3:O83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:S86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証71ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
+          <t>確かめる手順（準備11行＋検証73ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
 実施順を変えてはいけない箇所：①T-A08（勤怠取込）→T-S03（締め）　②T-S03→T-S04・T-D07→T-S05（この3件は締め済みでしか確認できない）　③C-000（初期化）は計算の先頭　④C-008は計算の最後（2026-05のEMP-001を352,286円に変えるためC-013・C-017が合わなくなる）　⑤T-N02の前にdata/02を再投入　⑥削除はEMP-012（T-L10）とEMP-004（T-D08）だけ
 列の使い方：使用する検証データ＝この検証で投入・使用するdataファイル／期待値＝先頭の【確認場所】でどの画面を見て合否を出すかを示し、続けて合格の基準を書いている／スクショ（撮るもの）＝何が写っていれば証拠になるか／スクショ貼付欄＝撮った画像をこの列に貼る／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めて合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを決める
 色：緑＝使う検証データ　青＝画面　橙＝スクショの指示　紫＝ヘルプ・受入条件との対応　黄＝当日の記入欄。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
@@ -2781,68 +2781,68 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="94" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>詳細</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>T-H01</t>
+          <t>T-D13</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>履歴の追記と過去行の不変</t>
+          <t>退職にしたときの一覧と過去実績</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 ／ 変更前の履歴をCSV出力しておく
-【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
+          <t>【前提】S-04 S-05
+【操作】（a）EMP-002（2026-05の実績あり）の在籍状態を「退職」にして保存 →（b）従業員一覧を見る →（c）給与実績一覧で2026-05を見る →（d）EMP-002を削除しようとする →（e）実績が無いEMP-012を削除しようとする</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ（12名）・05 月次給与実績</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定変更履歴一覧】
-履歴が1行増える。既存行の値の差分＝0</t>
+          <t>【確認場所：従業員詳細 → 従業員一覧 → 給与実績一覧（月別実績）】
+（b）従業員一覧から外れて11名になる（c）2026-05にはEMP-002が出続け、実績給与300,250円が1円も変わらない。設定変更履歴も残る（d）実績があるため削除できない（削除成功=0件）（e）実績が無いため削除できる</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>T-H01.png</t>
+          <t>T-D13.png</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
+          <t>在籍状態を退職にした従業員詳細／11名になった従業員一覧／2026-05の給与実績一覧にEMP-002が残っていること／削除できない旨の表示</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧 … 変更前後の行（既存行が書き換わらないこと）</t>
+          <t>従業員詳細（在籍状態）→ 従業員一覧 → 給与実績一覧 月別実績</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>既存行が書き換わらないか</t>
+          <t>退職者が一覧から外れ、過去の実績は残るか／実績がある人を削除できないか</t>
         </is>
       </c>
       <c r="L32" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
+          <t>操作手順 ＞ 従業員を探す・削除する</t>
         </is>
       </c>
       <c r="M32" s="13" t="inlineStr">
         <is>
-          <t>AC-07</t>
+          <t>AC-63</t>
         </is>
       </c>
       <c r="N32" s="5" t="inlineStr"/>
@@ -2852,11 +2852,11 @@
       <c r="R32" s="5" t="inlineStr"/>
       <c r="S32" s="8" t="inlineStr">
         <is>
-          <t>原則①：過去は不変</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="79" customHeight="1">
+          <t>（金額計算なし）退職は削除ではない。実績と履歴を物理削除すると締めた月の数字が動く（原則②・AC-16）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2864,18 +2864,18 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>T-H02</t>
+          <t>T-H01</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>記録の内容</t>
+          <t>履歴の追記と過去行の不変</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 T-D04実施済み
-【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
+          <t>【前提】S-05 ／ 変更前の履歴をCSV出力しておく
+【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2886,28 +2886,28 @@
       <c r="F33" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定変更履歴一覧】
-①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
+履歴が1行増える。既存行の値の差分＝0</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>T-H02.png</t>
+          <t>T-H01.png</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
+          <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
+          <t>設定変更履歴一覧 … 変更前後の行（既存行が書き換わらないこと）</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>2つの日時が別で記録されるか</t>
+          <t>既存行が書き換わらないか</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="M33" s="13" t="inlineStr">
         <is>
-          <t>AC-08 AC-09</t>
+          <t>AC-07</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
@@ -2927,11 +2927,11 @@
       <c r="R33" s="5" t="inlineStr"/>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="94" customHeight="1">
+          <t>原則①：過去は不変</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="79" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2939,18 +2939,18 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>T-H04</t>
+          <t>T-H02</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>履歴の絞り込み・出力・遷移</t>
+          <t>記録の内容</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
+          <t>【前提】S-05 T-D04実施済み
+【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2961,28 +2961,28 @@
       <c r="F34" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定変更履歴一覧】
-店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
+①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>T-H04.png</t>
+          <t>T-H02.png</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
+          <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
+          <t>設定変更履歴一覧 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>絞り込み後の行だけ出力されるか</t>
+          <t>2つの日時が別で記録されるか</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="M34" s="13" t="inlineStr">
         <is>
-          <t>AC-33 AC-36 AC-30</t>
+          <t>AC-08 AC-09</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr"/>
@@ -3002,30 +3002,30 @@
       <c r="R34" s="5" t="inlineStr"/>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="199" customHeight="1">
+          <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="94" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>履歴</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>T-A02</t>
+          <t>T-H04</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>月別実績の表示と切替</t>
+          <t>履歴の絞り込み・出力・遷移</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
+【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -3035,41 +3035,39 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない
-実績モードでは 想定給与・給与・給与実績差分 が表示され、差分＝給与−想定給与 と一致する
-概算モードでは実績由来の列（給与・給与実績差分・ヘルプ人件費・深夜残業代など）が隠れる。残るのは実績データが無くても値が決まる列だけ（判断22。食い違う列=0件）</t>
+          <t>【確認場所：設定変更履歴一覧】
+店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>T-A02.png</t>
+          <t>T-H04.png</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
+          <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
+          <t>設定変更履歴一覧 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>モード切替で列が増減するか</t>
+          <t>絞り込み後の行だけ出力されるか</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>AC-10 AC-31 AC-57</t>
+          <t>AC-33 AC-36 AC-30</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr"/>
@@ -3079,11 +3077,11 @@
       <c r="R35" s="5" t="inlineStr"/>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>計算：算式どおりの金額／画面：状態が漏れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="64" customHeight="1">
+          <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="199" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -3091,18 +3089,18 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>T-A09</t>
+          <t>T-A02</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>給与実績一覧からの設定編集</t>
+          <t>月別実績の表示と切替</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】給与実績一覧で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
+【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -3112,39 +3110,41 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　行の「従業員設定」】
-モーダルに14項目が表示される。更新保存で給与実績一覧に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない
+実績モードでは 想定給与・給与・給与実績差分 が表示され、差分＝給与−想定給与 と一致する
+概算モードでは実績由来の列（給与・給与実績差分・ヘルプ人件費・深夜残業代など）が隠れる。残るのは実績データが無くても値が決まる列だけ（判断22。食い違う列=0件）</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>T-A09.png</t>
+          <t>T-A02.png</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>設定編集モーダル（項目が見える状態）／更新保存後の給与実績一覧／従業員詳細の設定変更履歴に行が増えたこと</t>
+          <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 給与実績一覧／確認は従業員詳細の設定変更履歴</t>
+          <t>給与実績一覧 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>モーダル編集でも履歴が残るか</t>
+          <t>モード切替で列が増減するか</t>
         </is>
       </c>
       <c r="L36" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M36" s="13" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-10 AC-31 AC-57</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr"/>
@@ -3154,11 +3154,11 @@
       <c r="R36" s="5" t="inlineStr"/>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>原則①：どの入口から編集しても履歴が残る</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="139" customHeight="1">
+          <t>計算：算式どおりの金額／画面：状態が漏れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="64" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -3166,18 +3166,18 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>T-A05</t>
+          <t>T-A09</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>日別実績の表示</t>
+          <t>給与実績一覧からの設定編集</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
+【操作】給与実績一覧で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -3187,40 +3187,39 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 日別実績タブ】
-全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない
-日別にモード切替は無いが、想定給与・給与実績差分は表示される</t>
+          <t>【確認場所：給与実績一覧　→　行の「従業員設定」】
+モーダルに14項目が表示される。更新保存で給与実績一覧に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>T-A05.png</t>
+          <t>T-A09.png</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
+          <t>設定編集モーダル（項目が見える状態）／更新保存後の給与実績一覧／従業員詳細の設定変更履歴に行が増えたこと</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
+          <t>給与実績一覧 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 給与実績一覧／確認は従業員詳細の設定変更履歴</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>日別に概算モードが無いか</t>
+          <t>モーダル編集でも履歴が残るか</t>
         </is>
       </c>
       <c r="L37" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
       <c r="M37" s="13" t="inlineStr">
         <is>
-          <t>AC-10 AC-57</t>
+          <t>AC-49</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr"/>
@@ -3230,72 +3229,72 @@
       <c r="R37" s="5" t="inlineStr"/>
       <c r="S37" s="8" t="inlineStr">
         <is>
-          <t>計算：算式どおりの金額</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="64" customHeight="1">
+          <t>原則①：どの入口から編集しても履歴が残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="94" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>詳細</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>T-A07</t>
+          <t>T-A10</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>実績のCSVエクスポート</t>
+          <t>取込エラーがある行の金額</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
+          <t>【前提】S-05 S-06
+【操作】（a）data/12（設定未入力のEMP-015）を投入した状態で給与実績一覧の月別を見る →（b）エラーの絞り込みで「交通費欠損」「出退勤打刻漏れ」を順に選ぶ →（c）日別で打刻漏れの日を探す</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）12 従業員マスタ_設定未入力・05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧】
-出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
+          <t>【確認場所：給与実績一覧 → 月別実績／日別実績（エラーの絞り込み）】
+（a）交通費が無い従業員も金額が出る（交通費0円として計算。空欄=0件）（b）絞り込みでその行だけが残る（c）打刻漏れの日は日別に行が無く、出勤日にも数えられていない（想定労働日数に含まれない）</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>T-A07.png</t>
+          <t>T-A10.png</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
+          <t>エラー絞り込みで抽出した行（金額が出ていること）／日別で打刻漏れの日に行が無いこと</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
+          <t>給与実績一覧 月別実績・日別実績（エラーの絞り込み）</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>表示中の内容が出力されるか</t>
+          <t>交通費0で金額が出るか／打刻漏れの日を出勤日に数えていないか</t>
         </is>
       </c>
       <c r="L38" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M38" s="13" t="inlineStr">
         <is>
-          <t>AC-36</t>
+          <t>AC-62</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr"/>
@@ -3305,11 +3304,11 @@
       <c r="R38" s="5" t="inlineStr"/>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>入出力：画面の内容と一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="64" customHeight="1">
+          <t>交通費が無ければ0円として計算。打刻漏れの日は出勤日に数えない（想定労働日数＝直近3か月の平均出勤日数に効く。判断28・30）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="139" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -3317,18 +3316,18 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>T-A08</t>
+          <t>T-A05</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>勤怠実績の取込</t>
+          <t>日別実績の表示</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-08
-【操作】給与実績一覧の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
+          <t>【前提】S-05
+【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -3338,29 +3337,30 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
+          <t>【確認場所：給与実績一覧 → 日別実績タブ】
+全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない
+日別にモード切替は無いが、想定給与・給与実績差分は表示される</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>T-A08.png</t>
+          <t>T-A05.png</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
+          <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
+          <t>給与実績一覧 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>進捗が出て他操作を受け付けないか</t>
+          <t>日別に概算モードが無いか</t>
         </is>
       </c>
       <c r="L39" s="13" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="M39" s="13" t="inlineStr">
         <is>
-          <t>AC-48</t>
+          <t>AC-10 AC-57</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr"/>
@@ -3380,72 +3380,72 @@
       <c r="R39" s="5" t="inlineStr"/>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t>入出力：勤怠実績を取り込める</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1">
+          <t>計算：算式どおりの金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="64" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>締め</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>T-S01</t>
+          <t>T-A07</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>締めボタンの表示条件</t>
+          <t>実績のCSVエクスポート</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-08
-【操作】月別実績タブと日別実績タブを順に開く</t>
+          <t>【前提】S-05
+【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧】
-月別のみ「2026-05 締め」が表示。日別には表示されない</t>
+出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>T-S01.png</t>
+          <t>T-A07.png</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
+          <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
+          <t>給与実績一覧 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>締めが月別タブにだけ出るか</t>
+          <t>表示中の内容が出力されるか</t>
         </is>
       </c>
       <c r="L40" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M40" s="13" t="inlineStr">
         <is>
-          <t>AC-18</t>
+          <t>AC-36</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr"/>
@@ -3455,62 +3455,62 @@
       <c r="R40" s="5" t="inlineStr"/>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めの単位は月</t>
+          <t>入出力：画面の内容と一致</t>
         </is>
       </c>
     </row>
     <row r="41" ht="64" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>締め</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>T-S03</t>
+          <t>T-A08</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>締めの実行</t>
+          <t>勤怠実績の取込</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06 S-08
-【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
+          <t>【前提】S-05 S-08
+【操作】給与実績一覧の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　月別実績タブ】
-「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>T-S03.png</t>
+          <t>T-A08.png</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
+          <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
+          <t>給与実績一覧 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>確認モーダルを経て締まるか</t>
+          <t>進捗が出て他操作を受け付けないか</t>
         </is>
       </c>
       <c r="L41" s="13" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="M41" s="13" t="inlineStr">
         <is>
-          <t>AC-16 AC-19 AC-32</t>
+          <t>AC-48</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr"/>
@@ -3530,7 +3530,7 @@
       <c r="R41" s="5" t="inlineStr"/>
       <c r="S41" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
+          <t>入出力：勤怠実績を取り込める</t>
         </is>
       </c>
     </row>
@@ -3542,18 +3542,18 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>T-S04</t>
+          <t>T-S01</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>締め後は編集できない</t>
+          <t>締めボタンの表示条件</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み
-【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
+          <t>【前提】S-08
+【操作】月別実績タブと日別実績タブを順に開く</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績】
-編集できない（または反映されない）</t>
+          <t>【確認場所：給与実績一覧】
+月別のみ「2026-05 締め」が表示。日別には表示されない</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>T-S04.png</t>
+          <t>T-S01.png</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
+          <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
+          <t>給与実績一覧 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
         </is>
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>締め後に金額が動かないか</t>
+          <t>締めが月別タブにだけ出るか</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M42" s="13" t="inlineStr">
         <is>
-          <t>AC-16</t>
+          <t>AC-18</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr"/>
@@ -3605,11 +3605,11 @@
       <c r="R42" s="5" t="inlineStr"/>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="60" customHeight="1">
+          <t>原則②：締めの単位は月</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="64" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3617,18 +3617,18 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>T-D07</t>
+          <t>T-S03</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>締め済み期間への遡及</t>
+          <t>締めの実行</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み S-07
-【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
+          <t>【前提】S-06 S-08
+【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -3638,39 +3638,39 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細】
-締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
+          <t>【確認場所：給与実績一覧　→　月別実績タブ】
+「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>T-D07.png</t>
+          <t>T-S03.png</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
+          <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
+          <t>給与実績一覧 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>警告が出て反映されないか</t>
+          <t>確認モーダルを経て締まるか</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M43" s="13" t="inlineStr">
         <is>
-          <t>AC-20</t>
+          <t>AC-16 AC-19 AC-32</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr"/>
@@ -3680,11 +3680,11 @@
       <c r="R43" s="5" t="inlineStr"/>
       <c r="S43" s="8" t="inlineStr">
         <is>
-          <t>原則②：遡及は黙って捨てない</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="64" customHeight="1">
+          <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3692,18 +3692,18 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>T-S05</t>
+          <t>T-S04</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>締めの解除</t>
+          <t>締め後は編集できない</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
           <t>【前提】T-S03実施済み
-【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
+【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -3713,29 +3713,29 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　月別実績タブ】
-「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
+          <t>【確認場所：給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績】
+編集できない（または反映されない）</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>T-S05.png</t>
+          <t>T-S04.png</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
+          <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
+          <t>給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>解除で再計算されるか</t>
+          <t>締め後に金額が動かないか</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>AC-19</t>
+          <t>AC-16</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr"/>
@@ -3755,11 +3755,11 @@
       <c r="R44" s="5" t="inlineStr"/>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t>原則②：確定操作は確認を経る</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="64" customHeight="1">
+          <t>原則②：締めたら動かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3767,18 +3767,18 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>T-S07</t>
+          <t>T-D07</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>締めの実行権限</t>
+          <t>締め済み期間への遡及</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-10 S-08
-【操作】店長スコープのアカウントでログインし、給与実績一覧を開いて締めを試みる</t>
+          <t>【前提】T-S03実施済み S-07
+【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -3788,39 +3788,39 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ（店長スコープでログイン）】
-締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
+          <t>【確認場所：従業員詳細】
+締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>T-S07.png</t>
+          <t>T-D07.png</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>店長スコープでの給与実績一覧（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
+          <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
+          <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>店長が締められないか</t>
+          <t>警告が出て反映されないか</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
       <c r="M45" s="13" t="inlineStr">
         <is>
-          <t>AC-41</t>
+          <t>AC-20</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr"/>
@@ -3830,30 +3830,30 @@
       <c r="R45" s="5" t="inlineStr"/>
       <c r="S45" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="79" customHeight="1">
+          <t>原則②：遡及は黙って捨てない</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="64" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>取込</t>
+          <t>締め</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>T-I02</t>
+          <t>T-S05</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>テンプレートのDLと画面</t>
+          <t>締めの解除</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
+          <t>【前提】T-S03実施済み
+【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -3863,39 +3863,39 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
+          <t>【確認場所：給与実績一覧　→　月別実績タブ】
+「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>T-I02.png</t>
+          <t>T-S05.png</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
+          <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
+          <t>給与実績一覧 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>テンプレートの列とBOM</t>
+          <t>解除で再計算されるか</t>
         </is>
       </c>
       <c r="L46" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ はじめて設定する</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="M46" s="13" t="inlineStr">
         <is>
-          <t>AC-21 AC-30</t>
+          <t>AC-19</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr"/>
@@ -3905,72 +3905,72 @@
       <c r="R46" s="5" t="inlineStr"/>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="79" customHeight="1">
+          <t>原則②：確定操作は確認を経る</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="64" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>取込</t>
+          <t>締め</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>T-I03</t>
+          <t>T-S07</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>King of Time形式の取込</t>
+          <t>締めの実行権限</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-06
-【操作】データ種類＝King of Time を選び data/07（従業員設定・3行／外部ID 1001・1005・1013）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
+          <t>【前提】S-10 S-08
+【操作】店長スコープのアカウントでログインし、給与実績一覧を開いて締めを試みる</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート → 従業員一覧】
-外部ID 1001・1005 は対応表で E0001・E0005 に解決され、既存の従業員が更新される（単位給与額 340,000／360,000）。対応表に無い 1013 は新規として扱われ、従業員IDが自動で付番される。件数は3行</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ（店長スコープでログイン）】
+締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>T-I03.png</t>
+          <t>T-S07.png</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
+          <t>店長スコープでの給与実績一覧（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
+          <t>給与実績一覧 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>3行が更新・追加されるか</t>
+          <t>店長が締められないか</t>
         </is>
       </c>
       <c r="L47" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ はじめて設定する</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M47" s="13" t="inlineStr">
         <is>
-          <t>AC-21</t>
+          <t>AC-41</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr"/>
@@ -3980,11 +3980,11 @@
       <c r="R47" s="5" t="inlineStr"/>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>入出力：導入を止めない</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="60" customHeight="1">
+          <t>原則②：締めは会社スコープのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="79" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -3992,50 +3992,50 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>T-I04</t>
+          <t>T-I02</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>ジョブカン形式（表記ゆれ）の取込</t>
+          <t>テンプレートのDLと画面</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-06
-【操作】データ種類＝ジョブカン を選び data/08（3行／外部ID JB-003・JB-010・JB-014）をD&amp;D → 登録</t>
+          <t>【前提】S-01
+【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>08 取込CSV ジョブカン</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート → 従業員一覧】
-スタッフコード等の表記ゆれを吸収し、外部ID JB-003・JB-010 が E0003・E0010 に解決される。取込成功=3行</t>
+          <t>【確認場所：設定インポート】
+従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>T-I04.png</t>
+          <t>T-I02.png</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
+          <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
+          <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>表記ゆれを吸収できるか</t>
+          <t>テンプレートの列とBOM</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="M48" s="13" t="inlineStr">
         <is>
-          <t>AC-22</t>
+          <t>AC-21 AC-30</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr"/>
@@ -4055,11 +4055,11 @@
       <c r="R48" s="5" t="inlineStr"/>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="60" customHeight="1">
+          <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="79" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4067,60 +4067,60 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>T-I05</t>
+          <t>T-I03</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>異常系データの検出</t>
+          <t>King of Time形式の取込</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】data/09（4行）をD&amp;D → 登録</t>
+【操作】データ種類＝King of Time を選び data/07（従業員設定・3行／外部ID 1001・1005・1013）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
+          <t>【確認場所：設定インポート → 従業員一覧】
+外部ID 1001・1005 は対応表で E0001・E0005 に解決され、既存の従業員が更新される（単位給与額 340,000／360,000）。対応表に無い 1013 は新規として扱われ、従業員IDが自動で付番される。件数は3行</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>T-I05.png</t>
+          <t>T-I03.png</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
+          <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
+          <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>4種の異常を行ごとに検出するか</t>
+          <t>3行が更新・追加されるか</t>
         </is>
       </c>
       <c r="L49" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
+          <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>AC-23</t>
+          <t>AC-21</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
@@ -4130,11 +4130,11 @@
       <c r="R49" s="5" t="inlineStr"/>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="64" customHeight="1">
+          <t>入出力：導入を止めない</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4142,60 +4142,60 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>T-I17</t>
+          <t>T-I04</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>二重登録の防止</t>
+          <t>ジョブカン形式（表記ゆれ）の取込</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】（a）data/07を2回続けて取り込む （b）data/19（外部ID 1002 が2行・単位給与額が異なる）を取り込む</t>
+【操作】データ種類＝ジョブカン を選び data/08（3行／外部ID JB-003・JB-010・JB-014）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
+          <t>08 取込CSV ジョブカン</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-（a）2回目は更新となり件数が増えない（二重登録=0件）（b）同じ外部IDが2行あるためエラーとして検出され、両方とも登録されない。1つの外部IDが2つの従業員IDに紐づく=0件</t>
+          <t>【確認場所：設定インポート → 従業員一覧】
+スタッフコード等の表記ゆれを吸収し、外部ID JB-003・JB-010 が E0003・E0010 に解決される。取込成功=3行</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>T-I17.png</t>
+          <t>T-I04.png</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
+          <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
+          <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>二重登録されないか</t>
+          <t>表記ゆれを吸収できるか</t>
         </is>
       </c>
       <c r="L50" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
+          <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
       <c r="M50" s="13" t="inlineStr">
         <is>
-          <t>AC-40 AC-56</t>
+          <t>AC-22</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr"/>
@@ -4205,11 +4205,11 @@
       <c r="R50" s="5" t="inlineStr"/>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>データ保全：二重登録を防ぐ</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="94" customHeight="1">
+          <t>入出力：表記ゆれを吸収</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4217,60 +4217,60 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>T-I20</t>
+          <t>T-I05</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>外部IDの対応と付番</t>
+          <t>異常系データの検出</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】（a）data/20 の対応表を開き、EMP-001 が King of Time 1001 とジョブカン JB-001 の2件を持つことを確認 →（b）対応表に無い外部ID（例 9999）を含むCSVを取り込む →（c）取り込んだ従業員の従業員IDを従業員一覧で確認する</t>
+【操作】data/09（4行）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>20 外部ID対応表／07 取込CSV KingOfTime</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：列マッピングテンプレート（外部ID対応）→ 設定インポート → 従業員一覧】
-（a）1名が複数の勤怠システムの外部IDを持てる（E0001＝1001／JB-001）（b）対応表に無い外部IDは取り込まれず、件数と理由が表示される（黙って登録=0件）（c）すべての従業員に従業員IDが付いている（未付番=0件）</t>
+          <t>【確認場所：設定インポート】
+4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>T-I20.png</t>
+          <t>T-I05.png</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>外部ID対応表（EMP-001が2システム分ある状態）／対応表に無い外部IDのエラー表示／従業員一覧の従業員ID列</t>
+          <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート（外部IDの対応）→ 設定インポート → 従業員一覧</t>
+          <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>外部IDが従業員IDに解決されるか／未登録は弾かれるか</t>
+          <t>4種の異常を行ごとに検出するか</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="M51" s="13" t="inlineStr">
         <is>
-          <t>AC-55 AC-56</t>
+          <t>AC-23</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr"/>
@@ -4280,11 +4280,11 @@
       <c r="R51" s="5" t="inlineStr"/>
       <c r="S51" s="8" t="inlineStr">
         <is>
-          <t>データ保全：従業員の同一性を保つ／入出力：ID体系の違いを吸収</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="94" customHeight="1">
+          <t>データ保全：不正値を入れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="64" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4292,50 +4292,50 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>T-I18</t>
+          <t>T-I17</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>取込が途中で失敗したときの扱い</t>
+          <t>二重登録の防止</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
+【操作】（a）data/07を2回続けて取り込む （b）data/19（外部ID 1002 が2行・単位給与額が異なる）を取り込む</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録】
-中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
+          <t>【確認場所：設定インポート】
+（a）2回目は更新となり件数が増えない（二重登録=0件）（b）同じ外部IDが2行あるためエラーとして検出され、両方とも登録されない。1つの外部IDが2つの従業員IDに紐づく=0件</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>T-I18.png</t>
+          <t>T-I17.png</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
+          <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録されていないこと）</t>
+          <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
         </is>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>部分登録が残らないか</t>
+          <t>二重登録されないか</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="M52" s="13" t="inlineStr">
         <is>
-          <t>AC-42</t>
+          <t>AC-40 AC-56</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr"/>
@@ -4355,11 +4355,11 @@
       <c r="R52" s="5" t="inlineStr"/>
       <c r="S52" s="8" t="inlineStr">
         <is>
-          <t>データ保全：中途半端に残さない</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="64" customHeight="1">
+          <t>データ保全：二重登録を防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="94" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4367,50 +4367,50 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>T-I11</t>
+          <t>T-I20</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>CSV位置合わせ設定</t>
+          <t>外部IDの対応と付番</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06
-【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
+          <t>【前提】S-04 S-06
+【操作】（a）data/20 の対応表を開き、EMP-001 が King of Time 1001 とジョブカン JB-001 の2件を持つことを確認 →（b）対応表に無い外部ID（例 9999）を含むCSVを取り込む →（c）取り込んだ従業員の従業員IDを従業員一覧で確認する</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>11 取込CSV 説明行あり</t>
+          <t>20 外部ID対応表／07 取込CSV KingOfTime</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-余計な行が無視され、3行が正しく取り込まれる</t>
+          <t>【確認場所：列マッピングテンプレート（外部ID対応）→ 設定インポート → 従業員一覧】
+（a）1名が複数の勤怠システムの外部IDを持てる（E0001＝1001／JB-001）（b）対応表に無い外部IDは取り込まれず、件数と理由が表示される（黙って登録=0件）（c）すべての従業員に従業員IDが付いている（未付番=0件）</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>T-I11.png</t>
+          <t>T-I20.png</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
+          <t>外部ID対応表（EMP-001が2システム分ある状態）／対応表に無い外部IDのエラー表示／従業員一覧の従業員ID列</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
+          <t>列マッピングテンプレート（外部IDの対応）→ 設定インポート → 従業員一覧</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>説明行を飛ばして取り込めるか</t>
+          <t>外部IDが従業員IDに解決されるか／未登録は弾かれるか</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>AC-37</t>
+          <t>AC-55 AC-56</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr"/>
@@ -4430,11 +4430,11 @@
       <c r="R53" s="5" t="inlineStr"/>
       <c r="S53" s="8" t="inlineStr">
         <is>
-          <t>入出力：現場のCSVをそのまま使える</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="139" customHeight="1">
+          <t>データ保全：従業員の同一性を保つ／入出力：ID体系の違いを吸収</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="94" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4442,61 +4442,60 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>T-I09</t>
+          <t>T-I18</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>取込が途中で失敗したときの扱い</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06
-【操作】「列マッピングテンプレート」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
+          <t>【前提】S-04 S-06
+【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート」】
-テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる
-リンクのラベルが遷移先の画面名と一字一句そろっている（「〜へ」が付いていない・旧名「従業員設定インポート」が残っていない。食い違い=0件。判断4）</t>
+          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録】
+中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>T-I09.png</t>
+          <t>T-I18.png</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
+          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>設定インポート → ツールバー「列マッピングテンプレート」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
+          <t>設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録されていないこと）</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>テンプレの登録・編集・削除と往復／リンク名が画面名と一致しているか</t>
+          <t>部分登録が残らないか</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="M54" s="13" t="inlineStr">
         <is>
-          <t>AC-24 AC-38 AC-30</t>
+          <t>AC-42</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr"/>
@@ -4506,11 +4505,11 @@
       <c r="R54" s="5" t="inlineStr"/>
       <c r="S54" s="8" t="inlineStr">
         <is>
-          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="79" customHeight="1">
+          <t>データ保全：中途半端に残さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="64" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4518,50 +4517,50 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>T-I19</t>
+          <t>T-I11</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>マッピング表の一括登録</t>
+          <t>CSV位置合わせ設定</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
+【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>18 列マッピング表テンプレ</t>
+          <t>11 取込CSV 説明行あり</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：列マッピングテンプレート】
-テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
+          <t>【確認場所：設定インポート】
+余計な行が無視され、3行が正しく取り込まれる</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>T-I19.png</t>
+          <t>T-I11.png</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
+          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
+          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>一括登録と10MB超の扱い</t>
+          <t>説明行を飛ばして取り込めるか</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
@@ -4571,7 +4570,7 @@
       </c>
       <c r="M55" s="13" t="inlineStr">
         <is>
-          <t>AC-51</t>
+          <t>AC-37</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
@@ -4581,72 +4580,73 @@
       <c r="R55" s="5" t="inlineStr"/>
       <c r="S55" s="8" t="inlineStr">
         <is>
-          <t>入出力：マッピングの一括運用</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="79" customHeight="1">
+          <t>入出力：現場のCSVをそのまま使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="139" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>取込</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>T-E04</t>
+          <t>T-I09</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>設定のエクスポート</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
+          <t>【前提】S-06
+【操作】「列マッピングテンプレート」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
-専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
+          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート」】
+テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる
+リンクのラベルが遷移先の画面名と一字一句そろっている（「〜へ」が付いていない・旧名「従業員設定インポート」が残っていない。食い違い=0件。判断4）</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>T-E04.png</t>
+          <t>T-I09.png</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
+          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
+          <t>設定インポート → ツールバー「列マッピングテンプレート」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>選んだ項目だけ・対象数だけ出るか</t>
+          <t>テンプレの登録・編集・削除と往復／リンク名が画面名と一致しているか</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M56" s="13" t="inlineStr">
         <is>
-          <t>AC-25 AC-26 AC-30</t>
+          <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr"/>
@@ -4656,73 +4656,72 @@
       <c r="R56" s="5" t="inlineStr"/>
       <c r="S56" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
+          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="57" ht="79" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>取込</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>T-E09</t>
+          <t>T-I19</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>実績・同時のエクスポート</t>
+          <t>マッピング表の一括登録</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（給与実績差分を含む）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
+          <t>【前提】S-06
+【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>18 列マッピング表テンプレ</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート】
-実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される
-実績の項目に給与実績差分が選べ、出力値＝実績給与−概算給与と一致する</t>
+          <t>【確認場所：列マッピングテンプレート】
+テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>T-E09.png</t>
+          <t>T-I19.png</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
+          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
+          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>実績と同時選択のファイル数</t>
+          <t>一括登録と10MB超の扱い</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M57" s="13" t="inlineStr">
         <is>
-          <t>AC-25 AC-57</t>
+          <t>AC-51</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr"/>
@@ -4732,11 +4731,11 @@
       <c r="R57" s="5" t="inlineStr"/>
       <c r="S57" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="60" customHeight="1">
+          <t>入出力：マッピングの一括運用</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="79" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4744,18 +4743,18 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>T-E07</t>
+          <t>T-E04</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>未選択でのエクスポート防止</t>
+          <t>設定のエクスポート</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04
-【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
+【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -4765,29 +4764,29 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート】
-警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
+          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
+専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>T-E07.png</t>
+          <t>T-E04.png</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
+          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
+          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
         </is>
       </c>
       <c r="K58" s="8" t="inlineStr">
         <is>
-          <t>未選択で出力されないか</t>
+          <t>選んだ項目だけ・対象数だけ出るか</t>
         </is>
       </c>
       <c r="L58" s="13" t="inlineStr">
@@ -4797,7 +4796,7 @@
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>AC-27</t>
+          <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr"/>
@@ -4807,11 +4806,11 @@
       <c r="R58" s="5" t="inlineStr"/>
       <c r="S58" s="8" t="inlineStr">
         <is>
-          <t>入出力：空振りを防ぐ</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="60" customHeight="1">
+          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="79" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4819,50 +4818,51 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>T-E08</t>
+          <t>T-E09</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>出力CSVの文字化け</t>
+          <t>実績・同時のエクスポート</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 ／ T-E04で出力済み
-【操作】T-E04で出力したCSVをExcelで開く</t>
+          <t>【前提】S-05
+【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（給与実績差分を含む）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
+実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される
+実績の項目に給与実績差分が選べ、出力値＝実績給与−概算給与と一致する</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>T-E08.png</t>
+          <t>T-E09.png</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
+          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
+          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>Excelで文字化けしないか</t>
+          <t>実績と同時選択のファイル数</t>
         </is>
       </c>
       <c r="L59" s="13" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="M59" s="13" t="inlineStr">
         <is>
-          <t>AC-28</t>
+          <t>AC-25 AC-57</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr"/>
@@ -4882,72 +4882,72 @@
       <c r="R59" s="5" t="inlineStr"/>
       <c r="S59" s="8" t="inlineStr">
         <is>
-          <t>入出力：そのまま提出できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="79" customHeight="1">
+          <t>入出力：渡し先に合わせて出せる</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="60" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>取込データ</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>T-N01</t>
+          <t>T-E07</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>取込元データの確認</t>
+          <t>未選択でのエクスポート防止</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-I03実施済み
-【操作】サイドバー「設定の取込結果」→ 取り込んだファイル・行を確認。次に「実績の取込結果」を開く</t>
+          <t>【前提】S-04
+【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定の取込結果（サイドバー）】
-設定の取込結果＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績の取込結果＝一覧→タブ（月別データ10列／日別データ10列。交通費・総支給額は表示しない（判断14））</t>
+          <t>【確認場所：設定・実績エクスポート】
+警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>T-N01.png</t>
+          <t>T-E07.png</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>設定の取込結果と実績の取込結果の一覧＋各タブ（計4枚）</t>
+          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>設定の取込結果（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績の取込結果 … 月別データ／日別データタブ</t>
+          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>元データとタブの構成</t>
+          <t>未選択で出力されないか</t>
         </is>
       </c>
       <c r="L60" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M60" s="13" t="inlineStr">
         <is>
-          <t>AC-39</t>
+          <t>AC-27</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr"/>
@@ -4957,72 +4957,72 @@
       <c r="R60" s="5" t="inlineStr"/>
       <c r="S60" s="8" t="inlineStr">
         <is>
-          <t>入出力：原因を追える</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="94" customHeight="1">
+          <t>入出力：空振りを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="60" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>取込データ</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>T-N02</t>
+          <t>T-E08</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>取込前のプレビューと前回差分</t>
+          <t>出力CSVの文字化け</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-06
-【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定の取込結果と実績の取込結果で、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
+          <t>【前提】S-04 ／ T-E04で出力済み
+【操作】T-E04で出力したCSVをExcelで開く</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定の取込結果／実績の取込結果】
-プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
+          <t>【確認場所：設定・実績エクスポート】
+日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>T-N02.png</t>
+          <t>T-E08.png</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
+          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>設定の取込結果／実績の取込結果 … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
+          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>差分がdata/16・17と一致するか</t>
+          <t>Excelで文字化けしないか</t>
         </is>
       </c>
       <c r="L61" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>AC-50</t>
+          <t>AC-28</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr"/>
@@ -5032,11 +5032,11 @@
       <c r="R61" s="5" t="inlineStr"/>
       <c r="S61" s="8" t="inlineStr">
         <is>
-          <t>データ保全：取り込む前に気づける</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="60" customHeight="1">
+          <t>入出力：そのまま提出できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="79" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -5044,50 +5044,50 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>T-N03</t>
+          <t>T-N01</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>取込データと給与実績一覧の相互導線</t>
+          <t>取込元データの確認</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】給与実績一覧の「実績の取込結果」→ 実績の取込結果の「給与実績一覧」を押す</t>
+          <t>【前提】T-I03実施済み
+【操作】サイドバー「設定の取込結果」→ 取り込んだファイル・行を確認。次に「実績の取込結果」を開く</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　「実績の取込結果」／実績の取込結果】
-2経路とも到達する（不通=0）</t>
+          <t>【確認場所：設定の取込結果（サイドバー）】
+設定の取込結果＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績の取込結果＝一覧→タブ（月別データ10列／日別データ10列。交通費・総支給額は表示しない（判断14））</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>T-N03.png</t>
+          <t>T-N01.png</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>給与実績一覧→実績の取込結果／実績の取込結果→給与実績一覧 の到達直後（2枚）</t>
+          <t>設定の取込結果と実績の取込結果の一覧＋各タブ（計4枚）</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 「実績の取込結果」／実績の取込結果 → 「給与実績一覧」（相互導線）</t>
+          <t>設定の取込結果（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績の取込結果 … 月別データ／日別データタブ</t>
         </is>
       </c>
       <c r="K62" s="8" t="inlineStr">
         <is>
-          <t>2経路とも到達するか</t>
+          <t>元データとタブの構成</t>
         </is>
       </c>
       <c r="L62" s="13" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="M62" s="13" t="inlineStr">
         <is>
-          <t>AC-30</t>
+          <t>AC-39</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr"/>
@@ -5107,72 +5107,72 @@
       <c r="R62" s="5" t="inlineStr"/>
       <c r="S62" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="60" customHeight="1">
+          <t>入出力：原因を追える</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="94" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>T-Z01</t>
+          <t>T-N02</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>移行前後の突合（既存データ）</t>
+          <t>取込前のプレビューと前回差分</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 S-11
-【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
+          <t>【前提】S-05 S-06
+【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定の取込結果と実績の取込結果で、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員一覧】
-件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
+          <t>【確認場所：設定の取込結果／実績の取込結果】
+プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>T-Z01.png</t>
+          <t>T-N02.png</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
+          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
+          <t>設定の取込結果／実績の取込結果 … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr">
         <is>
-          <t>移行前後で差分0件か</t>
+          <t>差分がdata/16・17と一致するか</t>
         </is>
       </c>
       <c r="L63" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ すでにご利用中のお客様</t>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>AC-01</t>
+          <t>AC-50</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr"/>
@@ -5182,73 +5182,72 @@
       <c r="R63" s="5" t="inlineStr"/>
       <c r="S63" s="8" t="inlineStr">
         <is>
-          <t>移行：既存顧客が壊れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="94" customHeight="1">
+          <t>データ保全：取り込む前に気づける</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="60" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>T-Z02</t>
+          <t>T-N03</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>移行後の適用日付の付与</t>
+          <t>取込データと給与実績一覧の相互導線</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
+          <t>【前提】S-05
+【操作】給与実績一覧の「実績の取込結果」→ 実績の取込結果の「給与実績一覧」を押す</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細 → 設定変更履歴／設定変更履歴一覧】
-適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている
-あわせて、すべての従業員に従業員IDが付番されている（未付番=0件）。外部IDは対応表に移されている</t>
+          <t>【確認場所：給与実績一覧　→　「実績の取込結果」／実績の取込結果】
+2経路とも到達する（不通=0）</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>T-Z02.png</t>
+          <t>T-N03.png</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
+          <t>給与実績一覧→実績の取込結果／実績の取込結果→給与実績一覧 の到達直後（2枚）</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 設定変更履歴／設定変更履歴一覧 … 適用日付の空欄</t>
+          <t>給与実績一覧 → 「実績の取込結果」／実績の取込結果 → 「給与実績一覧」（相互導線）</t>
         </is>
       </c>
       <c r="K64" s="8" t="inlineStr">
         <is>
-          <t>適用日付の空欄が0件か</t>
+          <t>2経路とも到達するか</t>
         </is>
       </c>
       <c r="L64" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ すでにご利用中のお客様</t>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
       <c r="M64" s="13" t="inlineStr">
         <is>
-          <t>AC-02 AC-55</t>
+          <t>AC-30</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr"/>
@@ -5258,7 +5257,7 @@
       <c r="R64" s="5" t="inlineStr"/>
       <c r="S64" s="8" t="inlineStr">
         <is>
-          <t>移行：履歴の起点を作る</t>
+          <t>画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
@@ -5270,18 +5269,18 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>T-Z03</t>
+          <t>T-Z01</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>移行前後の過去月の人件費</t>
+          <t>移行前後の突合（既存データ）</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行前に出力しておいた直近3か月の給与実績一覧と、移行後の同3か月を突合する</t>
+          <t>【前提】S-09 S-11
+【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
@@ -5291,29 +5290,29 @@
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
+          <t>【確認場所：従業員一覧】
+件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>T-Z03.png</t>
+          <t>T-Z01.png</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>移行前後の給与実績一覧 月別実績（直近3か月・金額が同じであること）</t>
+          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ … 移行前後の直近3か月</t>
+          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>過去3か月の金額が変わらないか</t>
+          <t>移行前後で差分0件か</t>
         </is>
       </c>
       <c r="L65" s="13" t="inlineStr">
@@ -5323,7 +5322,7 @@
       </c>
       <c r="M65" s="13" t="inlineStr">
         <is>
-          <t>AC-03</t>
+          <t>AC-01</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr"/>
@@ -5333,11 +5332,11 @@
       <c r="R65" s="5" t="inlineStr"/>
       <c r="S65" s="8" t="inlineStr">
         <is>
-          <t>移行：過去が動かない</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="60" customHeight="1">
+          <t>移行：既存顧客が壊れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="94" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
           <t>横断</t>
@@ -5345,18 +5344,18 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>T-Z04</t>
+          <t>T-Z02</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>サイドバーの構成</t>
+          <t>移行後の適用日付の付与</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
+          <t>【前提】S-09 ／ T-Z01実施済み
+【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
@@ -5366,39 +5365,40 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：サイドバー「従業員管理」】
-閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
+          <t>【確認場所：従業員詳細 → 設定変更履歴／設定変更履歴一覧】
+適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている
+あわせて、すべての従業員に従業員IDが付番されている（未付番=0件）。外部IDは対応表に移されている</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>T-Z04.png</t>
+          <t>T-Z02.png</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
+          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
+          <t>従業員詳細 → 設定変更履歴／設定変更履歴一覧 … 適用日付の空欄</t>
         </is>
       </c>
       <c r="K66" s="8" t="inlineStr">
         <is>
-          <t>PC・モバイルとも開くか</t>
+          <t>適用日付の空欄が0件か</t>
         </is>
       </c>
       <c r="L66" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・画面構成）</t>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
       <c r="M66" s="13" t="inlineStr">
         <is>
-          <t>AC-29</t>
+          <t>AC-02 AC-55</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr"/>
@@ -5408,7 +5408,7 @@
       <c r="R66" s="5" t="inlineStr"/>
       <c r="S66" s="8" t="inlineStr">
         <is>
-          <t>画面：たどり着ける</t>
+          <t>移行：履歴の起点を作る</t>
         </is>
       </c>
     </row>
@@ -5420,60 +5420,60 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>T-Z05</t>
+          <t>T-Z03</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>遷移と表示規則の網羅</t>
+          <t>移行前後の過去月の人件費</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-05
-【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+          <t>【前提】S-09 ／ T-Z01実施済み
+【操作】移行前に出力しておいた直近3か月の給与実績一覧と、移行後の同3か月を突合する</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
-すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>T-Z05.png</t>
+          <t>T-Z03.png</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
+          <t>移行前後の給与実績一覧 月別実績（直近3か月・金額が同じであること）</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="12" t="inlineStr">
         <is>
-          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+          <t>給与実績一覧 → 月別実績タブ … 移行前後の直近3か月</t>
         </is>
       </c>
       <c r="K67" s="8" t="inlineStr">
         <is>
-          <t>75本の遷移と表示規則</t>
+          <t>過去3か月の金額が変わらないか</t>
         </is>
       </c>
       <c r="L67" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・遷移網羅）</t>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
       <c r="M67" s="13" t="inlineStr">
         <is>
-          <t>AC-30 AC-01</t>
+          <t>AC-03</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr"/>
@@ -5483,72 +5483,72 @@
       <c r="R67" s="5" t="inlineStr"/>
       <c r="S67" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="79" customHeight="1">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>C-000</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr">
-        <is>
-          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
-        </is>
-      </c>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>【前提】S-03 S-05
-【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
-        </is>
-      </c>
-      <c r="E68" s="15" t="inlineStr">
-        <is>
-          <t>02〜06・13を再投入（初期化）</t>
-        </is>
-      </c>
-      <c r="F68" s="15" t="inlineStr">
-        <is>
-          <t>【確認場所：従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未】
-従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
-        </is>
-      </c>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>C-000.png</t>
-        </is>
-      </c>
-      <c r="H68" s="15" t="inlineStr">
-        <is>
-          <t>初期化後の従業員一覧（12名）と給与実績一覧（未締め・S-05時点の金額）</t>
+          <t>移行：過去が動かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>T-Z04</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>サイドバーの構成</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：サイドバー「従業員管理」】
+閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>T-Z04.png</t>
+        </is>
+      </c>
+      <c r="H68" s="11" t="inlineStr">
+        <is>
+          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
-      <c r="J68" s="15" t="inlineStr">
-        <is>
-          <t>従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未締めに戻す）</t>
-        </is>
-      </c>
-      <c r="K68" s="15" t="inlineStr">
-        <is>
-          <t>S-05時点の値に戻ったか</t>
-        </is>
-      </c>
-      <c r="L68" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため対応なし）</t>
-        </is>
-      </c>
-      <c r="M68" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J68" s="12" t="inlineStr">
+        <is>
+          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>PC・モバイルとも開くか</t>
+        </is>
+      </c>
+      <c r="L68" s="13" t="inlineStr">
+        <is>
+          <t>（ヘルプ記載なし・画面構成）</t>
+        </is>
+      </c>
+      <c r="M68" s="13" t="inlineStr">
+        <is>
+          <t>AC-29</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr"/>
@@ -5556,74 +5556,74 @@
       <c r="P68" s="6" t="inlineStr"/>
       <c r="Q68" s="5" t="inlineStr"/>
       <c r="R68" s="5" t="inlineStr"/>
-      <c r="S68" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="64" customHeight="1">
-      <c r="A69" s="14" t="inlineStr">
-        <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>C-001</t>
-        </is>
-      </c>
-      <c r="C69" s="15" t="inlineStr">
-        <is>
-          <t>実績給与の内訳整合（ヘルプなし）</t>
-        </is>
-      </c>
-      <c r="D69" s="15" t="inlineStr">
-        <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-002（概算280,000・基礎時給1,750・深夜2h・所属店舗の交通費15,000）と EMP-007（概算300,000・基礎時給1,875・深夜4h・交通費30,000）を検算</t>
-        </is>
-      </c>
-      <c r="E69" s="15" t="inlineStr">
-        <is>
-          <t>05 月次給与実績</t>
-        </is>
-      </c>
-      <c r="F69" s="15" t="inlineStr">
-        <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
-EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
-        </is>
-      </c>
-      <c r="G69" s="14" t="inlineStr">
-        <is>
-          <t>C-001.png</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="inlineStr">
-        <is>
-          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
+      <c r="S68" s="8" t="inlineStr">
+        <is>
+          <t>画面：たどり着ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>T-Z05</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>遷移と表示規則の網羅</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>【前提】S-04 S-05
+【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
+すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>T-Z05.png</t>
+        </is>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
-      <c r="J69" s="15" t="inlineStr">
-        <is>
-          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
-        </is>
-      </c>
-      <c r="K69" s="15" t="inlineStr">
-        <is>
-          <t>概算＋深夜＝実績給与か</t>
-        </is>
-      </c>
-      <c r="L69" s="15" t="inlineStr">
-        <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
-        </is>
-      </c>
-      <c r="M69" s="15" t="inlineStr">
-        <is>
-          <t>AC-10</t>
+      <c r="J69" s="12" t="inlineStr">
+        <is>
+          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+        </is>
+      </c>
+      <c r="K69" s="8" t="inlineStr">
+        <is>
+          <t>75本の遷移と表示規則</t>
+        </is>
+      </c>
+      <c r="L69" s="13" t="inlineStr">
+        <is>
+          <t>（ヘルプ記載なし・遷移網羅）</t>
+        </is>
+      </c>
+      <c r="M69" s="13" t="inlineStr">
+        <is>
+          <t>AC-30 AC-01</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr"/>
@@ -5631,9 +5631,9 @@
       <c r="P69" s="6" t="inlineStr"/>
       <c r="Q69" s="5" t="inlineStr"/>
       <c r="R69" s="5" t="inlineStr"/>
-      <c r="S69" s="15" t="inlineStr">
-        <is>
-          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
+      <c r="S69" s="8" t="inlineStr">
+        <is>
+          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
         </is>
       </c>
     </row>
@@ -5645,60 +5645,60 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>C-003</t>
+          <t>C-000</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプあり）</t>
+          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-001（概算320,000・深夜6h・ヘルプ22h／所属店舗の交通費18,000・ヘルプ先の交通費1,600）／EMP-005（概算350,000・深夜10h・ヘルプ35h／22,000・3,100）／EMP-003（概算144,000・ヘルプ20h／9,000・1,300）を検算</t>
+          <t>【前提】S-03 S-05
+【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>02〜06・13を再投入（初期化）</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
-EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算＋深夜＋みなし超過＋交通費）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
+          <t>【確認場所：従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未】
+従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>C-003.png</t>
+          <t>C-000.png</t>
         </is>
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
+          <t>初期化後の従業員一覧（12名）と給与実績一覧（未締め・S-05時点の金額）</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
+          <t>従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未締めに戻す）</t>
         </is>
       </c>
       <c r="K70" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費が按分で振替されるか</t>
+          <t>S-05時点の値に戻ったか</t>
         </is>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>（初期化のため対応なし）</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr"/>
@@ -5708,11 +5708,11 @@
       <c r="R70" s="5" t="inlineStr"/>
       <c r="S70" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="60" customHeight="1">
+          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="64" customHeight="1">
       <c r="A71" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5720,18 +5720,18 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>C-005</t>
+          <t>C-001</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計と全社合計の一致</t>
+          <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】2026-05の EMP-002（概算280,000・基礎時給1,750・深夜2h・所属店舗の交通費15,000）と EMP-007（概算300,000・基礎時給1,875・深夜4h・交通費30,000）を検算</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
@@ -5742,38 +5742,38 @@
       <c r="F71" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
-店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
+EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>C-005.png</t>
+          <t>C-001.png</t>
         </is>
       </c>
       <c r="H71" s="15" t="inlineStr">
         <is>
-          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
+          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計＝全社（差0円）か</t>
+          <t>概算＋深夜＝実績給与か</t>
         </is>
       </c>
       <c r="L71" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>AC-11</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr"/>
@@ -5783,7 +5783,7 @@
       <c r="R71" s="5" t="inlineStr"/>
       <c r="S71" s="15" t="inlineStr">
         <is>
-          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
+          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
         </is>
       </c>
     </row>
@@ -5795,60 +5795,60 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>C-006</t>
+          <t>C-003</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>月中改定と予約の日割り</t>
+          <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】2026-05の EMP-001（概算320,000・深夜6h・ヘルプ22h／所属店舗の交通費18,000・ヘルプ先の交通費1,600）／EMP-005（概算350,000・深夜10h・ヘルプ35h／22,000・3,100）／EMP-003（概算144,000・ヘルプ20h／9,000・1,300）を検算</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>14 勤務データ 2026-06</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従】
-6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
+EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算＋深夜＋みなし超過＋交通費）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>C-006.png</t>
+          <t>C-003.png</t>
         </is>
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
+          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
         </is>
       </c>
       <c r="K72" s="15" t="inlineStr">
         <is>
-          <t>所定労働日割になっているか</t>
+          <t>ヘルプ人件費が按分で振替されるか</t>
         </is>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>AC-12 AC-04</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr"/>
@@ -5858,11 +5858,11 @@
       <c r="R72" s="5" t="inlineStr"/>
       <c r="S72" s="15" t="inlineStr">
         <is>
-          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="64" customHeight="1">
+          <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="60" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5870,60 +5870,60 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>C-011</t>
+          <t>C-005</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・14 勤務データ 2026-06</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　月別実績タブ】
-5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
+店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>C-011.png</t>
+          <t>C-005.png</t>
         </is>
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
+          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>店舗別合計＝全社（差0円）か</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M73" s="15" t="inlineStr">
         <is>
-          <t>AC-13</t>
+          <t>AC-11</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr"/>
@@ -5933,11 +5933,11 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="124" customHeight="1">
+          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="79" customHeight="1">
       <c r="A74" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5945,60 +5945,60 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>C-018</t>
+          <t>C-006</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>想定労働日数と日次の想定給与</t>
+          <t>月中改定と予約の日割り</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-05
-【操作】（a）EMP-003（時給・想定労働日数15を入力済み）の月次の想定給与を検算 →（b）EMP-003の想定労働日数を空欄にして保存し、打刻から求めた日数が使われるか見る →（c）EMP-001（月給・未入力）の月次と日次を検算</t>
+          <t>【前提】C-000 S-07 ／ data/14を投入
+【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ・05 月次給与実績・06 日次給与実績</t>
+          <t>14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
-（a）EMP-003の想定給与＝1,200×120＋600×15＝153,000円（b）空欄にしても打刻の出勤日数15日（data/06で2026-05は15日）が使われ、153,000円のまま変わらない（c）EMP-001は打刻20日が使われ、想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003の日次は想定給与・給与実績差分が「—」（判断27）。計算違い0件</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従】
+6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>C-018.png</t>
+          <t>C-006.png</t>
         </is>
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>従業員詳細の想定労働日数の欄（空欄でも金額が変わらないこと）／月別実績の想定給与／日別実績で時給者の想定給与が「—」であること</t>
+          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="15" t="inlineStr">
         <is>
-          <t>従業員詳細（想定労働日数）→ 給与実績一覧 日別実績（想定給与）</t>
+          <t>給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
         </is>
       </c>
       <c r="K74" s="15" t="inlineStr">
         <is>
-          <t>未入力でも打刻から日数が取れるか／日額交通費が日数ぶん月次に入るか</t>
+          <t>所定労働日割になっているか</t>
         </is>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>AC-59</t>
+          <t>AC-12 AC-04</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr"/>
@@ -6008,11 +6008,11 @@
       <c r="R74" s="5" t="inlineStr"/>
       <c r="S74" s="15" t="inlineStr">
         <is>
-          <t>想定労働日数＝入力値 → 無ければ直近3か月の平均出勤日数（打刻）→ 打刻が無ければ月給者は営業日数。日額交通費の月次換算と月給者の日次按分に使う（判断26・27・28）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="109" customHeight="1">
+          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="64" customHeight="1">
       <c r="A75" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6020,60 +6020,60 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>C-019</t>
+          <t>C-011</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>日別の概算モード（営業日でならした見込み）</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-05
-【操作】給与実績一覧 → 日別実績タブ → 給与計算モードを「概算」に切り替える → 当月の全営業日ぶんの行が出ることと、日別の合計を確認する</t>
+          <t>【前提】C-000 S-07 ／ data/14を投入
+【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績・14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 日別実績タブ → 給与計算モード＝概算】
-実績が無い日も含めて当月の全営業日に行が出る。1日あたり＝月次の概算給与÷当月の営業日数。日別を全部足すと月次の概算給与と一致する（差 0円）。実績モードに戻すと想定給与列は月次概算÷想定労働日数の額に変わる（同じ日でも額が違う）</t>
+          <t>【確認場所：給与実績一覧　→　月別実績タブ】
+5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>C-019.png</t>
+          <t>C-011.png</t>
         </is>
       </c>
       <c r="H75" s="15" t="inlineStr">
         <is>
-          <t>概算モードの日別（全営業日に行が出ている）／合計が月次の概算給与と一致していること／実績モードに戻したときの想定給与列</t>
+          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 日別実績（概算モード ↔ 実績モード）</t>
+          <t>給与実績一覧 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
         </is>
       </c>
       <c r="K75" s="15" t="inlineStr">
         <is>
-          <t>日別の合計が月次の概算給与と一致するか</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="L75" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M75" s="15" t="inlineStr">
         <is>
-          <t>AC-60</t>
+          <t>AC-13</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
@@ -6083,11 +6083,11 @@
       <c r="R75" s="5" t="inlineStr"/>
       <c r="S75" s="15" t="inlineStr">
         <is>
-          <t>概算の日別＝月次の概算給与÷当月の営業日数、当月の全営業日に配分。端数は最大剰余で月次と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="94" customHeight="1">
+          <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="124" customHeight="1">
       <c r="A76" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6095,60 +6095,60 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-018</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>想定労働日数と日次の想定給与</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>【前提】C-000 S-05
+【操作】（a）EMP-003（時給・想定労働日数15を入力済み）の月次の想定給与を検算 →（b）EMP-003の想定労働日数を空欄にして保存し、打刻から求めた日数が使われるか見る →（c）EMP-001（月給・未入力）の月次と日次を検算</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ・05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
-判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
+          <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
+（a）EMP-003の想定給与＝1,200×120＋600×15＝153,000円（b）空欄にしても打刻の出勤日数15日（data/06で2026-05は15日）が使われ、153,000円のまま変わらない（c）EMP-001は打刻20日が使われ、想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003の日次は想定給与・給与実績差分が「—」（判断27）。計算違い0件</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>C-013.png</t>
+          <t>C-018.png</t>
         </is>
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
+          <t>従業員詳細の想定労働日数の欄（空欄でも金額が変わらないこと）／月別実績の想定給与／日別実績で時給者の想定給与が「—」であること</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
+          <t>従業員詳細（想定労働日数）→ 給与実績一覧 日別実績（想定給与）</t>
         </is>
       </c>
       <c r="K76" s="15" t="inlineStr">
         <is>
-          <t>深夜1.5倍とヘルプの按分単価</t>
+          <t>未入力でも打刻から日数が取れるか／日額交通費が日数ぶん月次に入るか</t>
         </is>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-59</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr"/>
@@ -6158,11 +6158,11 @@
       <c r="R76" s="5" t="inlineStr"/>
       <c r="S76" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="79" customHeight="1">
+          <t>想定労働日数＝入力値 → 無ければ直近3か月の平均出勤日数（打刻）→ 打刻が無ければ月給者は営業日数。日額交通費の月次換算と月給者の日次按分に使う（判断26・27・28）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="109" customHeight="1">
       <c r="A77" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6170,60 +6170,60 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-019</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>日別の概算モード（営業日でならした見込み）</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>【前提】C-000 S-05
+【操作】給与実績一覧 → 日別実績タブ → 給与計算モードを「概算」に切り替える → 当月の全営業日ぶんの行が出ることと、日別の合計を確認する</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績・日別実績】
-交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
+          <t>【確認場所：給与実績一覧 → 日別実績タブ → 給与計算モード＝概算】
+実績が無い日も含めて当月の全営業日に行が出る。1日あたり＝月次の概算給与÷当月の営業日数。日別を全部足すと月次の概算給与と一致する（差 0円）。実績モードに戻すと想定給与列は月次概算÷想定労働日数の額に変わる（同じ日でも額が違う）</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
-          <t>C-017.png</t>
+          <t>C-019.png</t>
         </is>
       </c>
       <c r="H77" s="15" t="inlineStr">
         <is>
-          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
+          <t>概算モードの日別（全営業日に行が出ている）／合計が月次の概算給与と一致していること／実績モードに戻したときの想定給与列</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+          <t>給与実績一覧 日別実績（概算モード ↔ 実績モード）</t>
         </is>
       </c>
       <c r="K77" s="15" t="inlineStr">
         <is>
-          <t>交通費が給与と別費目か</t>
+          <t>日別の合計が月次の概算給与と一致するか</t>
         </is>
       </c>
       <c r="L77" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M77" s="15" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-60</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
@@ -6233,7 +6233,7 @@
       <c r="R77" s="5" t="inlineStr"/>
       <c r="S77" s="15" t="inlineStr">
         <is>
-          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
+          <t>概算の日別＝月次の概算給与÷当月の営業日数、当月の全営業日に配分。端数は最大剰余で月次と一致させる</t>
         </is>
       </c>
     </row>
@@ -6245,60 +6245,60 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-013</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07
-【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
+判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
-          <t>C-008.png</t>
+          <t>C-013.png</t>
         </is>
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
+          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+          <t>給与実績一覧 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
         </is>
       </c>
       <c r="K78" s="15" t="inlineStr">
         <is>
-          <t>締め前後で差0円・解除後に再計算</t>
+          <t>深夜1.5倍とヘルプの按分単価</t>
         </is>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>AC-16 AC-17</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
@@ -6308,72 +6308,72 @@
       <c r="R78" s="5" t="inlineStr"/>
       <c r="S78" s="15" t="inlineStr">
         <is>
-          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="124" customHeight="1">
-      <c r="A79" s="16" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B79" s="16" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C79" s="17" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="D79" s="17" t="inlineStr">
-        <is>
-          <t>【前提】S-01
-【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
-        </is>
-      </c>
-      <c r="E79" s="17" t="inlineStr">
-        <is>
-          <t>（追加のデータ投入なし）</t>
-        </is>
-      </c>
-      <c r="F79" s="17" t="inlineStr">
-        <is>
-          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
-①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）</t>
-        </is>
-      </c>
-      <c r="G79" s="16" t="inlineStr">
-        <is>
-          <t>R-01.png</t>
-        </is>
-      </c>
-      <c r="H79" s="17" t="inlineStr">
-        <is>
-          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
+          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="79" customHeight="1">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>C-017</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>交通費の計上先</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-03 S-04
+【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：給与実績一覧 → 月別実績・日別実績】
+交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
+        </is>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>C-017.png</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="inlineStr">
+        <is>
+          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
-      <c r="J79" s="17" t="inlineStr">
-        <is>
-          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
-        </is>
-      </c>
-      <c r="K79" s="17" t="inlineStr">
-        <is>
-          <t>適用日付と履歴がテーブルにあるか</t>
-        </is>
-      </c>
-      <c r="L79" s="17" t="inlineStr">
-        <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
-        </is>
-      </c>
-      <c r="M79" s="17" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47 AC-55</t>
+      <c r="J79" s="15" t="inlineStr">
+        <is>
+          <t>給与実績一覧 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+        </is>
+      </c>
+      <c r="K79" s="15" t="inlineStr">
+        <is>
+          <t>交通費が給与と別費目か</t>
+        </is>
+      </c>
+      <c r="L79" s="15" t="inlineStr">
+        <is>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+        </is>
+      </c>
+      <c r="M79" s="15" t="inlineStr">
+        <is>
+          <t>AC-15</t>
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr"/>
@@ -6381,75 +6381,74 @@
       <c r="P79" s="6" t="inlineStr"/>
       <c r="Q79" s="5" t="inlineStr"/>
       <c r="R79" s="5" t="inlineStr"/>
-      <c r="S79" s="17" t="inlineStr">
-        <is>
-          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="109" customHeight="1">
-      <c r="A80" s="16" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B80" s="16" t="inlineStr">
-        <is>
-          <t>R-02</t>
-        </is>
-      </c>
-      <c r="C80" s="17" t="inlineStr">
-        <is>
-          <t>締めの実装レビュー</t>
-        </is>
-      </c>
-      <c r="D80" s="17" t="inlineStr">
-        <is>
-          <t>【前提】S-01
-【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
-        </is>
-      </c>
-      <c r="E80" s="17" t="inlineStr">
-        <is>
-          <t>（追加のデータ投入なし）</t>
-        </is>
-      </c>
-      <c r="F80" s="17" t="inlineStr">
-        <is>
-          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
-①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所
-適用済みの設定変更履歴は、APIを直接呼んでも更新・削除できない（成功=0件。判断29）</t>
-        </is>
-      </c>
-      <c r="G80" s="16" t="inlineStr">
-        <is>
-          <t>R-02.png</t>
-        </is>
-      </c>
-      <c r="H80" s="17" t="inlineStr">
-        <is>
-          <t>締めAPIのコードとスコープ判定箇所</t>
+      <c r="S79" s="15" t="inlineStr">
+        <is>
+          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="94" customHeight="1">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>締めの前後で数字が動かないこと</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-07
+【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>C-008.png</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="inlineStr">
+        <is>
+          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr"/>
-      <c r="J80" s="17" t="inlineStr">
-        <is>
-          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
-        </is>
-      </c>
-      <c r="K80" s="17" t="inlineStr">
-        <is>
-          <t>APIでも店長が締められないか／適用済みの履歴が消せないか</t>
-        </is>
-      </c>
-      <c r="L80" s="17" t="inlineStr">
-        <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
-        </is>
-      </c>
-      <c r="M80" s="17" t="inlineStr">
-        <is>
-          <t>AC-16 AC-41 AC-61</t>
+      <c r="J80" s="15" t="inlineStr">
+        <is>
+          <t>給与実績一覧 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+        </is>
+      </c>
+      <c r="K80" s="15" t="inlineStr">
+        <is>
+          <t>締め前後で差0円・解除後に再計算</t>
+        </is>
+      </c>
+      <c r="L80" s="15" t="inlineStr">
+        <is>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
+        </is>
+      </c>
+      <c r="M80" s="15" t="inlineStr">
+        <is>
+          <t>AC-16 AC-17</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr"/>
@@ -6457,13 +6456,13 @@
       <c r="P80" s="6" t="inlineStr"/>
       <c r="Q80" s="5" t="inlineStr"/>
       <c r="R80" s="5" t="inlineStr"/>
-      <c r="S80" s="17" t="inlineStr">
-        <is>
-          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="109" customHeight="1">
+      <c r="S80" s="15" t="inlineStr">
+        <is>
+          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="124" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6471,18 +6470,18 @@
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>入力検証とトランザクションのレビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="D81" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
+【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
         </is>
       </c>
       <c r="E81" s="17" t="inlineStr">
@@ -6492,39 +6491,39 @@
       </c>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
-①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）</t>
+          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
+①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）</t>
         </is>
       </c>
       <c r="G81" s="16" t="inlineStr">
         <is>
-          <t>R-03.png</t>
+          <t>R-01.png</t>
         </is>
       </c>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
+          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
+          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
       </c>
       <c r="K81" s="17" t="inlineStr">
         <is>
-          <t>APIを直接呼んでも弾かれるか</t>
+          <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
       <c r="L81" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 設定が保存できません</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M81" s="17" t="inlineStr">
         <is>
-          <t>AC-23 AC-42 AC-43</t>
+          <t>AC-07 AC-40 AC-47 AC-55</t>
         </is>
       </c>
       <c r="N81" s="5" t="inlineStr"/>
@@ -6534,11 +6533,11 @@
       <c r="R81" s="5" t="inlineStr"/>
       <c r="S81" s="17" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="79" customHeight="1">
+          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="109" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6546,18 +6545,18 @@
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの共有レビュー</t>
+          <t>締めの実装レビュー</t>
         </is>
       </c>
       <c r="D82" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】給与実績一覧・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
       <c r="E82" s="17" t="inlineStr">
@@ -6567,39 +6566,40 @@
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
-同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
+          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
+①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所
+適用済みの設定変更履歴は、APIを直接呼んでも更新・削除できない（成功=0件。判断29）</t>
         </is>
       </c>
       <c r="G82" s="16" t="inlineStr">
         <is>
-          <t>R-04.png</t>
+          <t>R-02.png</t>
         </is>
       </c>
       <c r="H82" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
+          <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
+          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
       </c>
       <c r="K82" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックが1箇所か</t>
+          <t>APIでも店長が締められないか／適用済みの履歴が消せないか</t>
         </is>
       </c>
       <c r="L82" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M82" s="17" t="inlineStr">
         <is>
-          <t>AC-35 AC-11</t>
+          <t>AC-16 AC-41 AC-61</t>
         </is>
       </c>
       <c r="N82" s="5" t="inlineStr"/>
@@ -6609,11 +6609,11 @@
       <c r="R82" s="5" t="inlineStr"/>
       <c r="S82" s="17" t="inlineStr">
         <is>
-          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="64" customHeight="1">
+          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="139" customHeight="1">
       <c r="A83" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6621,18 +6621,18 @@
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
       <c r="D83" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込の列解決の実装を提示してもらう</t>
+【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
       <c r="E83" s="17" t="inlineStr">
@@ -6642,39 +6642,40 @@
       </c>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
-CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
+          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
+①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）
+実績がある従業員は、APIを直接呼んでも削除できない（成功=0件。判断31）</t>
         </is>
       </c>
       <c r="G83" s="16" t="inlineStr">
         <is>
-          <t>R-05.png</t>
+          <t>R-03.png</t>
         </is>
       </c>
       <c r="H83" s="17" t="inlineStr">
         <is>
-          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
+          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
+          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
       </c>
       <c r="K83" s="17" t="inlineStr">
         <is>
-          <t>列名がコードに埋まっていないか</t>
+          <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
       <c r="L83" s="17" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
       <c r="M83" s="17" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-23 AC-42 AC-43 AC-63</t>
         </is>
       </c>
       <c r="N83" s="5" t="inlineStr"/>
@@ -6684,7 +6685,7 @@
       <c r="R83" s="5" t="inlineStr"/>
       <c r="S83" s="17" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
+          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
         </is>
       </c>
     </row>
@@ -6696,18 +6697,18 @@
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>設定更新処理の共通化レビュー</t>
+          <t>計算ロジックの共有レビュー</t>
         </is>
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+【操作】給与実績一覧・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
@@ -6717,39 +6718,39 @@
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
-設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
+同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
         </is>
       </c>
       <c r="G84" s="16" t="inlineStr">
         <is>
-          <t>R-06.png</t>
+          <t>R-04.png</t>
         </is>
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
         </is>
       </c>
       <c r="K84" s="17" t="inlineStr">
         <is>
-          <t>2つの入口で更新処理が共通か</t>
+          <t>計算ロジックが1箇所か</t>
         </is>
       </c>
       <c r="L84" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M84" s="17" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-35 AC-11</t>
         </is>
       </c>
       <c r="N84" s="5" t="inlineStr"/>
@@ -6759,17 +6760,167 @@
       <c r="R84" s="5" t="inlineStr"/>
       <c r="S84" s="17" t="inlineStr">
         <is>
+          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="64" customHeight="1">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>R-05</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>列マッピングの実装レビュー</t>
+        </is>
+      </c>
+      <c r="D85" s="17" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】取込の列解決の実装を提示してもらう</t>
+        </is>
+      </c>
+      <c r="E85" s="17" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F85" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
+CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
+        </is>
+      </c>
+      <c r="G85" s="16" t="inlineStr">
+        <is>
+          <t>R-05.png</t>
+        </is>
+      </c>
+      <c r="H85" s="17" t="inlineStr">
+        <is>
+          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr"/>
+      <c r="J85" s="17" t="inlineStr">
+        <is>
+          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
+        </is>
+      </c>
+      <c r="K85" s="17" t="inlineStr">
+        <is>
+          <t>列名がコードに埋まっていないか</t>
+        </is>
+      </c>
+      <c r="L85" s="17" t="inlineStr">
+        <is>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+      <c r="M85" s="17" t="inlineStr">
+        <is>
+          <t>AC-22 AC-24</t>
+        </is>
+      </c>
+      <c r="N85" s="5" t="inlineStr"/>
+      <c r="O85" s="5" t="inlineStr"/>
+      <c r="P85" s="6" t="inlineStr"/>
+      <c r="Q85" s="5" t="inlineStr"/>
+      <c r="R85" s="5" t="inlineStr"/>
+      <c r="S85" s="17" t="inlineStr">
+        <is>
+          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="79" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="E86" s="17" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
+設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="G86" s="16" t="inlineStr">
+        <is>
+          <t>R-06.png</t>
+        </is>
+      </c>
+      <c r="H86" s="17" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr"/>
+      <c r="J86" s="17" t="inlineStr">
+        <is>
+          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+        </is>
+      </c>
+      <c r="K86" s="17" t="inlineStr">
+        <is>
+          <t>2つの入口で更新処理が共通か</t>
+        </is>
+      </c>
+      <c r="L86" s="17" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="M86" s="17" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="N86" s="5" t="inlineStr"/>
+      <c r="O86" s="5" t="inlineStr"/>
+      <c r="P86" s="6" t="inlineStr"/>
+      <c r="Q86" s="5" t="inlineStr"/>
+      <c r="R86" s="5" t="inlineStr"/>
+      <c r="S86" s="17" t="inlineStr">
+        <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S84"/>
+  <autoFilter ref="A2:S86"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3:O84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -5787,7 +5787,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="79" customHeight="1">
+    <row r="72" ht="94" customHeight="1">
       <c r="A72" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5806,7 +5806,7 @@
       <c r="D72" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-001（概算320,000・深夜6h・ヘルプ22h／所属店舗の交通費18,000・ヘルプ先の交通費1,600）／EMP-005（概算350,000・深夜10h・ヘルプ35h／22,000・3,100）／EMP-003（概算144,000・ヘルプ20h／9,000・1,300）を検算</t>
+【操作】2026-05の EMP-001（概算338,000＝320,000＋交通費18,000・深夜6h・ヘルプ22h／ヘルプ先の交通費1,600）／EMP-005（概算372,000＝350,000＋22,000・深夜10h・ヘルプ35h／3,100）／EMP-003（概算153,000＝1,200×120h＋600×15日・ヘルプ20h／1,300）を検算</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
@@ -5817,7 +5817,7 @@
       <c r="F72" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
-EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算＋深夜＋みなし超過＋交通費）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
+EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算給与＋深夜残業代＋みなし超過残業代＋ヘルプ先の交通費。所属店舗の交通費は概算給与に含む）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -5858,7 +5858,7 @@
       <c r="R72" s="5" t="inlineStr"/>
       <c r="S72" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費＝実績給与×ヘルプ時間÷総労働時間（判断5・確定）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
+          <t>ヘルプ人件費＝（概算給与−所属店舗の交通費＋深夜残業代＋みなし超過残業代）×ヘルプ時間÷総労働時間 ＋ ヘルプ先の交通費（判断5・14・23）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="79" customHeight="1">
+    <row r="74" ht="94" customHeight="1">
       <c r="A74" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5967,7 +5967,7 @@
       <c r="F74" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従】
-6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+6月＝350,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -6008,11 +6008,11 @@
       <c r="R74" s="5" t="inlineStr"/>
       <c r="S74" s="15" t="inlineStr">
         <is>
-          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="64" customHeight="1">
+          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし。概算給与には所属店舗の交通費（月額18,000円）を足す（判断23）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="79" customHeight="1">
       <c r="A75" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6041,8 +6041,8 @@
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　月別実績タブ】
-5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
+          <t>【確認場所：給与実績一覧　→　月別実績タブ（概算モード）】
+5月＝1,200×120h ＋ 日額交通費600×想定労働日数15 ＝ 153,000円／6月＝1,200×60h ＋ 1,250×60h ＝ 147,000 ＋ 日額交通費600×15 ＝ 156,000円。計算違い0件</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
@@ -6083,7 +6083,7 @@
       <c r="R75" s="5" t="inlineStr"/>
       <c r="S75" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算給与＝単位給与額×所定労働時間。月中改定は期間ごとの実働時間×各単価の合計</t>
+          <t>時給者の概算給与＝単位給与額×所定労働時間＋所属店舗の交通費（日額なら×想定労働日数）。月中改定は期間ごとの実働時間×各単価の合計に交通費を足す（判断1・23）</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -2631,7 +2631,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="109" customHeight="1">
+    <row r="30" ht="169" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>詳細</t>
@@ -2650,7 +2650,7 @@
       <c r="D30" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-05
-【操作】EMP-001の詳細を開き、（a）並び順とステータス列の位置を確認 →（b）単位給与額を380,000に変更し適用日付＝翌々月1日で保存 →（c）保存後の履歴の最上部と強調を確認 →（d）右上「すべての履歴」を押す</t>
+【操作】EMP-001の詳細を開き、（a）並び順とステータス列の位置を確認 →（b）単位給与額を380,000に変更し適用日付＝翌々月1日で保存 →（c）保存後の履歴の最上部と強調を確認 →（d）右上「すべての履歴」を押す。あわせてモーダルの適用日付に（a）未来日（b）締め済み期間内の日付 を入れる</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -2661,7 +2661,8 @@
       <c r="F30" s="8" t="inlineStr">
         <is>
           <t>【確認場所：従業員詳細 → 設定変更履歴】
-（a）並びは変更反映日時の降順で、予約中が最上部。ステータスは変更反映日時の次（2列目）にあり横スクロールなしで見える。表示は直近3件（b・c）保存した行が最上部に増え、1つ古い行と値が違う項目（単位給与額）だけが強調される。強調の過不足=0件（d）設定変更履歴一覧が開き、EMP-001で絞り込まれた状態になる（絞り込みなしでの遷移=0件）</t>
+（a）並びは変更反映日時の降順で、予約中が最上部。ステータスは変更反映日時の次（2列目）にあり横スクロールなしで見える。表示は直近3件（b・c）保存した行が最上部に増え、1つ古い行と値が違う項目（単位給与額）だけが強調される。強調の過不足=0件（d）設定変更履歴一覧が開き、EMP-001で絞り込まれた状態になる（絞り込みなしでの遷移=0件）
+モーダルに適用日付の入力欄がある（a）未来日なら予約になり、設定変更履歴のステータスが「予約中」（b）締め済み期間内なら警告が出て反映されない（反映=0件）。従業員詳細から直した場合と履歴の記録が同じ（判断32）</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -2682,7 +2683,7 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>保存した行が最上部に来るか／変更点だけ強調されるか</t>
+          <t>保存した行が最上部に来るか／変更点だけ強調されるか／モーダルでも適用日付が効くか</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">
@@ -2692,7 +2693,7 @@
       </c>
       <c r="M30" s="13" t="inlineStr">
         <is>
-          <t>AC-52 AC-53</t>
+          <t>AC-52 AC-53 AC-49</t>
         </is>
       </c>
       <c r="N30" s="5" t="inlineStr"/>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -2631,7 +2631,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="169" customHeight="1">
+    <row r="30" ht="79" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>詳細</t>
@@ -2644,13 +2644,13 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>設定変更履歴の表示ルール</t>
+          <t>給与実績一覧から従業員詳細へ遷移する</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-05
-【操作】EMP-001の詳細を開き、（a）並び順とステータス列の位置を確認 →（b）単位給与額を380,000に変更し適用日付＝翌々月1日で保存 →（c）保存後の履歴の最上部と強調を確認 →（d）右上「すべての履歴」を押す。あわせてモーダルの適用日付に（a）未来日（b）締め済み期間内の日付 を入れる</t>
+【操作】給与実績一覧の月別実績で「従業員詳細」列のアイコンを押し、その従業員の詳細へ遷移することを確認する。設定を編集できる要素が無いことも確認する</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -2660,9 +2660,8 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細 → 設定変更履歴】
-（a）並びは変更反映日時の降順で、予約中が最上部。ステータスは変更反映日時の次（2列目）にあり横スクロールなしで見える。表示は直近3件（b・c）保存した行が最上部に増え、1つ古い行と値が違う項目（単位給与額）だけが強調される。強調の過不足=0件（d）設定変更履歴一覧が開き、EMP-001で絞り込まれた状態になる（絞り込みなしでの遷移=0件）
-モーダルに適用日付の入力欄がある（a）未来日なら予約になり、設定変更履歴のステータスが「予約中」（b）締め済み期間内なら警告が出て反映されない（反映=0件）。従業員詳細から直した場合と履歴の記録が同じ（判断32）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績】
+「従業員詳細」列からその従業員の詳細へ遷移する。給与実績一覧に設定を編集できる要素が無い（編集ボタン・保存ボタン=0件）。月別実績は23列で「従業員設定」の列が無い。設定を直すのは従業員詳細だけ（判断33）</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -2672,18 +2671,18 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>保存前後の履歴セクション2枚（並び順とステータス列の位置が分かる範囲）／強調された項目／「すべての履歴」で開いた設定変更履歴一覧（絞り込み条件が見える状態）</t>
+          <t>月別実績の左端（名前・従業員詳細・従業員コード）と、遷移先の従業員詳細</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 設定変更履歴セクション … 右上「すべての履歴」→ 設定変更履歴一覧（EMP-001で絞り込み済み）</t>
+          <t>給与実績一覧 月別実績 → 従業員詳細</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>保存した行が最上部に来るか／変更点だけ強調されるか／モーダルでも適用日付が効くか</t>
+          <t>給与実績一覧で設定を編集できないか／従業員詳細へ遷移できるか</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">
@@ -2703,7 +2702,7 @@
       <c r="R30" s="5" t="inlineStr"/>
       <c r="S30" s="8" t="inlineStr">
         <is>
-          <t>画面：保存できたか確かめられる／画面：変更点が読み取れる</t>
+          <t>（金額計算なし）設定を変えられる場所を従業員詳細だけにする（判断33。判断10の見直し）</t>
         </is>
       </c>
     </row>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -2631,7 +2631,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="79" customHeight="1">
+    <row r="30" ht="109" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
           <t>詳細</t>
@@ -2644,13 +2644,13 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>給与実績一覧から従業員詳細へ遷移する</t>
+          <t>給与実績一覧から設定を確認する</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-05
-【操作】給与実績一覧の月別実績で「従業員詳細」列のアイコンを押し、その従業員の詳細へ遷移することを確認する。設定を編集できる要素が無いことも確認する</t>
+【操作】給与実績一覧の月別実績で（a）絞り込みを設定した状態で「従業員設定」のアイコンを押す →（b）閉じて絞り込みが残っているか見る →（c）モーダルの「従業員詳細」ボタンを押す</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -2660,8 +2660,8 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績】
-「従業員詳細」列からその従業員の詳細へ遷移する。給与実績一覧に設定を編集できる要素が無い（編集ボタン・保存ボタン=0件）。月別実績は23列で「従業員設定」の列が無い。設定を直すのは従業員詳細だけ（判断33）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績 → 従業員設定】
+（a）設定内容が表示のみで開く。入力できず保存ボタンが無い（保存ボタン=0件）。「表示のみです」の注記が出る（b）閉じると絞り込み・年月・給与計算モードがそのまま残っている（やり直し=0件）（c）その従業員の詳細へ遷移し、適用日付を指定して直せる。月別実績は23列で「従業員ページ」の列が無い（判断33）</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -2671,18 +2671,18 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>月別実績の左端（名前・従業員詳細・従業員コード）と、遷移先の従業員詳細</t>
+          <t>表示のみの従業員設定モーダル（注記と「従業員詳細」ボタンが見える状態）／閉じたあと絞り込みが残っていること</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 月別実績 → 従業員詳細</t>
+          <t>給与実績一覧 月別実績 → 従業員設定（表示のみ）→ 従業員詳細</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>給与実績一覧で設定を編集できないか／従業員詳細へ遷移できるか</t>
+          <t>モーダルで編集できないか／閉じても絞り込みが残るか</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S86"/>
+  <dimension ref="A1:S89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証73ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
+          <t>確かめる手順（準備11行＋検証76ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
 実施順を変えてはいけない箇所：①T-A08（勤怠取込）→T-S03（締め）　②T-S03→T-S04・T-D07→T-S05（この3件は締め済みでしか確認できない）　③C-000（初期化）は計算の先頭　④C-008は計算の最後（2026-05のEMP-001を352,286円に変えるためC-013・C-017が合わなくなる）　⑤T-N02の前にdata/02を再投入　⑥削除はEMP-012（T-L10）とEMP-004（T-D08）だけ
 列の使い方：使用する検証データ＝この検証で投入・使用するdataファイル／期待値＝先頭の【確認場所】でどの画面を見て合否を出すかを示し、続けて合格の基準を書いている／スクショ（撮るもの）＝何が写っていれば証拠になるか／スクショ貼付欄＝撮った画像をこの列に貼る／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めて合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを決める
 色：緑＝使う検証データ　青＝画面　橙＝スクショの指示　紫＝ヘルプ・受入条件との対応　黄＝当日の記入欄。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
@@ -2856,68 +2856,68 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
+    <row r="33" ht="109" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>履歴</t>
+          <t>詳細</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>T-H01</t>
+          <t>T-D14</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>履歴の追記と過去行の不変</t>
+          <t>退職者と、同じ適用日付が複数あるとき</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 ／ 変更前の履歴をCSV出力しておく
-【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
+          <t>【前提】S-04 S-05
+【操作】（a）EMP-002を退職にして給与実績一覧を概算モードと実績モードで見る →（b）EMP-001に同じ適用日付（2026-07-01）で設定を2回保存する →（c）2026-09-01と2026-10-01の予約を入れる</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ・04 設定変更履歴・05 月次給与実績</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定変更履歴一覧】
-履歴が1行増える。既存行の値の差分＝0</t>
+          <t>【確認場所：給与実績一覧（概算／実績）／従業員詳細 → 設定変更履歴】
+（a）概算モードにEMP-002が出ない（出現=0件）。実績モードには出て金額が変わらない（判断35）（b）2件とも履歴に残り、編集日時が新しいほうにステータスが付く。古いほうは残るがステータスなし（消失=0件。判断36）（c）予約が2件とも「予約中」で残り、適用日付の順に並ぶ</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>T-H01.png</t>
+          <t>T-D14.png</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
+          <t>概算モードでEMP-002が居ないこと／実績モードで居ること／同じ適用日付が2行並びステータスが片方だけに付いている状態／予約2件</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧 … 変更前後の行（既存行が書き換わらないこと）</t>
+          <t>給与実績一覧（概算⇄実績）／従業員詳細 設定変更履歴</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>既存行が書き換わらないか</t>
+          <t>退職者が概算から外れるか／同じ適用日付で後勝ちになり古い行も残るか</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr">
         <is>
-          <t>AC-07</t>
+          <t>AC-65 AC-66</t>
         </is>
       </c>
       <c r="N33" s="5" t="inlineStr"/>
@@ -2927,11 +2927,11 @@
       <c r="R33" s="5" t="inlineStr"/>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>原則①：過去は不変</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="79" customHeight="1">
+          <t>（金額計算なし）概算は在籍者だけ（判断35）。同じ適用日付は編集日時が新しいほうが有効で、古いほうも履歴に残す（判断36）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -2939,18 +2939,18 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>T-H02</t>
+          <t>T-H01</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>記録の内容</t>
+          <t>履歴の追記と過去行の不変</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 T-D04実施済み
-【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
+          <t>【前提】S-05 ／ 変更前の履歴をCSV出力しておく
+【操作】EMP-001の設定を1回変更して保存し、変更前後の履歴を突合</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2961,28 +2961,28 @@
       <c r="F34" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定変更履歴一覧】
-①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
+履歴が1行増える。既存行の値の差分＝0</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>T-H02.png</t>
+          <t>T-H01.png</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
+          <t>変更前の履歴と変更後の履歴（既存行が同じであることが並べて分かること）</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
+          <t>設定変更履歴一覧 … 変更前後の行（既存行が書き換わらないこと）</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>2つの日時が別で記録されるか</t>
+          <t>既存行が書き換わらないか</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="M34" s="13" t="inlineStr">
         <is>
-          <t>AC-08 AC-09</t>
+          <t>AC-07</t>
         </is>
       </c>
       <c r="N34" s="5" t="inlineStr"/>
@@ -3002,11 +3002,11 @@
       <c r="R34" s="5" t="inlineStr"/>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="94" customHeight="1">
+          <t>原則①：過去は不変</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="79" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
           <t>履歴</t>
@@ -3014,18 +3014,18 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>T-H04</t>
+          <t>T-H02</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>履歴の絞り込み・出力・遷移</t>
+          <t>記録の内容</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
+          <t>【前提】S-05 T-D04実施済み
+【操作】予約した行の「変更反映日時」と「編集日時」を比較し、変更ソースを4種で絞り込む</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -3036,28 +3036,28 @@
       <c r="F35" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定変更履歴一覧】
-店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
+①変更反映日時と編集日時が異なる（例：反映8/1・編集6/25）　②変更ソースが4種すべて記録・絞り込みできる（手動編集／更新予約／CSVインポート(KOT)／CSVインポート(ジョブカン)）</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>T-H04.png</t>
+          <t>T-H02.png</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
+          <t>「変更反映日時」と「編集日時」が異なる行／変更ソース4種で絞り込んだ結果</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>設定変更履歴一覧 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
+          <t>設定変更履歴一覧 … 「変更反映日時」と「編集日時」の2列／変更ソースのフィルタ（4種）</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>絞り込み後の行だけ出力されるか</t>
+          <t>2つの日時が別で記録されるか</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>AC-33 AC-36 AC-30</t>
+          <t>AC-08 AC-09</t>
         </is>
       </c>
       <c r="N35" s="5" t="inlineStr"/>
@@ -3077,30 +3077,30 @@
       <c r="R35" s="5" t="inlineStr"/>
       <c r="S35" s="8" t="inlineStr">
         <is>
-          <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="199" customHeight="1">
+          <t>原則①：原因を追える（変更ソース）／原則①：適用日と操作日を分ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="94" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>履歴</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>T-A02</t>
+          <t>T-H04</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>月別実績の表示と切替</t>
+          <t>履歴の絞り込み・出力・遷移</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
+【操作】店舗／雇用区分／名前／編集日時の範囲（2026-05-01〜05-31）で絞り込み → CSVエクスポート → 名前をクリック → ツールバー「CSVインポート」</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -3110,41 +3110,39 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない
-実績モードでは 想定給与・給与・給与実績差分 が表示され、差分＝給与−想定給与 と一致する
-概算モードでは実績由来の列（給与・給与実績差分・ヘルプ人件費・深夜残業代など）が隠れる。残るのは実績データが無くても値が決まる列だけ（判断22。食い違う列=0件）</t>
+          <t>【確認場所：設定変更履歴一覧】
+店舗・雇用区分・名前の各条件で行が絞られる。編集日時2026-05-01〜05-31では2行（EMP-001 5/18・EMP-003 5/28）。CSVは絞り込み後の2行のみ出力（全5行にならない）。名前から従業員詳細へ、ツールバーから設定インポートへ遷移（2経路とも到達）</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>T-A02.png</t>
+          <t>T-H04.png</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
+          <t>絞り込み条件を適用した一覧と、出力したCSV（行数が一致すること）</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
+          <t>設定変更履歴一覧 … 店舗/雇用区分/名前/編集日時範囲のフィルタ → CSVエクスポート → 名前クリックで従業員詳細 → ツールバー「CSVインポート」</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>モード切替で列が増減するか</t>
+          <t>絞り込み後の行だけ出力されるか</t>
         </is>
       </c>
       <c r="L36" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M36" s="13" t="inlineStr">
         <is>
-          <t>AC-10 AC-31 AC-57</t>
+          <t>AC-33 AC-36 AC-30</t>
         </is>
       </c>
       <c r="N36" s="5" t="inlineStr"/>
@@ -3154,11 +3152,11 @@
       <c r="R36" s="5" t="inlineStr"/>
       <c r="S36" s="8" t="inlineStr">
         <is>
-          <t>計算：算式どおりの金額／画面：状態が漏れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="64" customHeight="1">
+          <t>画面：対象を探せる／入出力：画面の内容と一致／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="199" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -3166,18 +3164,18 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>T-A09</t>
+          <t>T-A02</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>給与実績一覧からの設定編集</t>
+          <t>月別実績の表示と切替</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】給与実績一覧で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
+【操作】月別実績タブで 概算 → 実績 に切り替え、年月／店舗／雇用区分／検索で絞り込む。その後ほかの画面を開いて戻る</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -3187,39 +3185,41 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　行の「従業員設定」】
-モーダルに14項目が表示される。更新保存で給与実績一覧に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+全26列。常時表示11列（名前/従業員ページ/従業員設定/従業員コード/雇用区分/給与単位/単位給与額/勤務日数/所属店舗/交通費/総支給額）＋実績モードで15列追加（想定労働日数/想定労働時間/総労働時間/労働時間差分/みなし労働時間/みなし労働時間差分/想定給与/給与/給与実績差分/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代）。各フィルタが効く。他画面に切替状態が漏れない
+実績モードでは 想定給与・給与・給与実績差分 が表示され、差分＝給与−想定給与 と一致する
+概算モードでは実績由来の列（給与・給与実績差分・ヘルプ人件費・深夜残業代など）が隠れる。残るのは実績データが無くても値が決まる列だけ（判断22。食い違う列=0件）</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>T-A09.png</t>
+          <t>T-A02.png</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>設定編集モーダル（項目が見える状態）／更新保存後の給与実績一覧／従業員詳細の設定変更履歴に行が増えたこと</t>
+          <t>概算モードと実績モードの両方（列の増減が比較できること）</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 給与実績一覧／確認は従業員詳細の設定変更履歴</t>
+          <t>給与実績一覧 → 月別実績タブ … 給与計算モード（概算⇄実績）の切替と、年月/店舗/雇用区分/検索のフィルタ</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>モーダル編集でも履歴が残るか</t>
+          <t>モード切替で列が増減するか</t>
         </is>
       </c>
       <c r="L37" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M37" s="13" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-10 AC-31 AC-57</t>
         </is>
       </c>
       <c r="N37" s="5" t="inlineStr"/>
@@ -3229,72 +3229,72 @@
       <c r="R37" s="5" t="inlineStr"/>
       <c r="S37" s="8" t="inlineStr">
         <is>
-          <t>原則①：どの入口から編集しても履歴が残る</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="94" customHeight="1">
+          <t>計算：算式どおりの金額／画面：状態が漏れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="64" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>詳細</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>T-A10</t>
+          <t>T-A09</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>取込エラーがある行の金額</t>
+          <t>給与実績一覧からの設定編集</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-06
-【操作】（a）data/12（設定未入力のEMP-015）を投入した状態で給与実績一覧の月別を見る →（b）エラーの絞り込みで「交通費欠損」「出退勤打刻漏れ」を順に選ぶ →（c）日別で打刻漏れの日を探す</t>
+          <t>【前提】S-05
+【操作】給与実績一覧で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）12 従業員マスタ_設定未入力・05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績／日別実績（エラーの絞り込み）】
-（a）交通費が無い従業員も金額が出る（交通費0円として計算。空欄=0件）（b）絞り込みでその行だけが残る（c）打刻漏れの日は日別に行が無く、出勤日にも数えられていない（想定労働日数に含まれない）</t>
+          <t>【確認場所：給与実績一覧　→　行の「従業員設定」】
+モーダルに14項目が表示される。更新保存で給与実績一覧に戻り数字が再計算される。従業員詳細の履歴が1行増え、変更ソースが記録される（詳細から編集した場合と同じ形式）</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>T-A10.png</t>
+          <t>T-A09.png</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>エラー絞り込みで抽出した行（金額が出ていること）／日別で打刻漏れの日に行が無いこと</t>
+          <t>設定編集モーダル（項目が見える状態）／更新保存後の給与実績一覧／従業員詳細の設定変更履歴に行が増えたこと</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 月別実績・日別実績（エラーの絞り込み）</t>
+          <t>給与実績一覧 → 行の「従業員設定」→ 設定編集モーダル →「更新保存」→ 給与実績一覧／確認は従業員詳細の設定変更履歴</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>交通費0で金額が出るか／打刻漏れの日を出勤日に数えていないか</t>
+          <t>モーダル編集でも履歴が残るか</t>
         </is>
       </c>
       <c r="L38" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
         </is>
       </c>
       <c r="M38" s="13" t="inlineStr">
         <is>
-          <t>AC-62</t>
+          <t>AC-49</t>
         </is>
       </c>
       <c r="N38" s="5" t="inlineStr"/>
@@ -3304,73 +3304,72 @@
       <c r="R38" s="5" t="inlineStr"/>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t>交通費が無ければ0円として計算。打刻漏れの日は出勤日に数えない（想定労働日数＝直近3か月の平均出勤日数に効く。判断28・30）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="139" customHeight="1">
+          <t>原則①：どの入口から編集しても履歴が残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="94" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>実績</t>
+          <t>詳細</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>T-A05</t>
+          <t>T-A10</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>日別実績の表示</t>
+          <t>取込エラーがある行の金額</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
+          <t>【前提】S-05 S-06
+【操作】（a）data/12（設定未入力のEMP-015）を投入した状態で給与実績一覧の月別を見る →（b）エラーの絞り込みで「交通費欠損」「出退勤打刻漏れ」を順に選ぶ →（c）日別で打刻漏れの日を探す</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）12 従業員マスタ_設定未入力・05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 日別実績タブ】
-全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない
-日別にモード切替は無いが、想定給与・給与実績差分は表示される</t>
+          <t>【確認場所：給与実績一覧 → 月別実績／日別実績（エラーの絞り込み）】
+（a）交通費が無い従業員も金額が出る（交通費0円として計算。空欄=0件）（b）絞り込みでその行だけが残る（c）打刻漏れの日は日別に行が無く、出勤日にも数えられていない（想定労働日数に含まれない）</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>T-A05.png</t>
+          <t>T-A10.png</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
+          <t>エラー絞り込みで抽出した行（金額が出ていること）／日別で打刻漏れの日に行が無いこと</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
+          <t>給与実績一覧 月別実績・日別実績（エラーの絞り込み）</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>日別に概算モードが無いか</t>
+          <t>交通費0で金額が出るか／打刻漏れの日を出勤日に数えていないか</t>
         </is>
       </c>
       <c r="L39" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M39" s="13" t="inlineStr">
         <is>
-          <t>AC-10 AC-57</t>
+          <t>AC-62</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr"/>
@@ -3380,11 +3379,11 @@
       <c r="R39" s="5" t="inlineStr"/>
       <c r="S39" s="8" t="inlineStr">
         <is>
-          <t>計算：算式どおりの金額</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="64" customHeight="1">
+          <t>交通費が無ければ0円として計算。打刻漏れの日は出勤日に数えない（想定労働日数＝直近3か月の平均出勤日数に効く。判断28・30）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="139" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>実績</t>
@@ -3392,18 +3391,18 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>T-A07</t>
+          <t>T-A05</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>実績のCSVエクスポート</t>
+          <t>日別実績の表示</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
           <t>【前提】S-05
-【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
+【操作】日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -3413,39 +3412,40 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧】
-出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
+          <t>【確認場所：給与実績一覧 → 日別実績タブ】
+全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない
+日別にモード切替は無いが、想定給与・給与実績差分は表示される</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>T-A07.png</t>
+          <t>T-A05.png</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
+          <t>日別実績の全体（モード切替が無いことが分かる範囲）</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
+          <t>給与実績一覧 → 日別実績タブ … 日付/店舗/雇用区分/検索のフィルタ（概算モードが無いこと）</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>表示中の内容が出力されるか</t>
+          <t>日別に概算モードが無いか</t>
         </is>
       </c>
       <c r="L40" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M40" s="13" t="inlineStr">
         <is>
-          <t>AC-36</t>
+          <t>AC-10 AC-57</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr"/>
@@ -3455,7 +3455,7 @@
       <c r="R40" s="5" t="inlineStr"/>
       <c r="S40" s="8" t="inlineStr">
         <is>
-          <t>入出力：画面の内容と一致</t>
+          <t>計算：算式どおりの金額</t>
         </is>
       </c>
     </row>
@@ -3467,18 +3467,18 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>T-A08</t>
+          <t>T-A07</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>勤怠実績の取込</t>
+          <t>実績のCSVエクスポート</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-08
-【操作】給与実績一覧の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
+          <t>【前提】S-05
+【操作】月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -3488,39 +3488,39 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
+          <t>【確認場所：給与実績一覧】
+出力した行数＝画面に表示されていた行数（差0件）。列も画面と一致（月別・実績モードなら実績列を含む／日別なら日別の列）。Excelで開いて文字化け=0件</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>T-A08.png</t>
+          <t>T-A07.png</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
+          <t>出力したCSVをExcelで開いた画面（月別・日別の2枚）</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
+          <t>給与実績一覧 … 月別実績（実績モード）と日別実績で、それぞれ右上のCSVエクスポート</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>進捗が出て他操作を受け付けないか</t>
+          <t>表示中の内容が出力されるか</t>
         </is>
       </c>
       <c r="L41" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M41" s="13" t="inlineStr">
         <is>
-          <t>AC-48</t>
+          <t>AC-36</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr"/>
@@ -3530,62 +3530,62 @@
       <c r="R41" s="5" t="inlineStr"/>
       <c r="S41" s="8" t="inlineStr">
         <is>
-          <t>入出力：勤怠実績を取り込める</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="60" customHeight="1">
+          <t>入出力：画面の内容と一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="64" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>締め</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>T-S01</t>
+          <t>T-A08</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>締めボタンの表示条件</t>
+          <t>勤怠実績の取込</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-08
-【操作】月別実績タブと日別実績タブを順に開く</t>
+          <t>【前提】S-05 S-08
+【操作】給与実績一覧の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧】
-月別のみ「2026-05 締め」が表示。日別には表示されない</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>T-S01.png</t>
+          <t>T-A08.png</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
+          <t>取込中モーダル（進捗%が出ている瞬間）と、完了後に金額が入った実績モード</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
+          <t>給与実績一覧 → 月別実績タブ … 右上「実績データ取込」→ 取込中モーダル（進捗%・閉じられない）</t>
         </is>
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>締めが月別タブにだけ出るか</t>
+          <t>進捗が出て他操作を受け付けないか</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="M42" s="13" t="inlineStr">
         <is>
-          <t>AC-18</t>
+          <t>AC-48</t>
         </is>
       </c>
       <c r="N42" s="5" t="inlineStr"/>
@@ -3605,11 +3605,11 @@
       <c r="R42" s="5" t="inlineStr"/>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めの単位は月</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="64" customHeight="1">
+          <t>入出力：勤怠実績を取り込める</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3617,18 +3617,18 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>T-S03</t>
+          <t>T-S01</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>締めの実行</t>
+          <t>締めボタンの表示条件</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06 S-08
-【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
+          <t>【前提】S-08
+【操作】月別実績タブと日別実績タブを順に開く</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -3638,29 +3638,29 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　月別実績タブ】
-「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
+          <t>【確認場所：給与実績一覧】
+月別のみ「2026-05 締め」が表示。日別には表示されない</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>T-S03.png</t>
+          <t>T-S01.png</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
+          <t>月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）の2枚</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
+          <t>給与実績一覧 … 月別実績タブ（締めボタンあり）と日別実績タブ（締めボタンなし）</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>確認モーダルを経て締まるか</t>
+          <t>締めが月別タブにだけ出るか</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="M43" s="13" t="inlineStr">
         <is>
-          <t>AC-16 AC-19 AC-32</t>
+          <t>AC-18</t>
         </is>
       </c>
       <c r="N43" s="5" t="inlineStr"/>
@@ -3680,11 +3680,11 @@
       <c r="R43" s="5" t="inlineStr"/>
       <c r="S43" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="60" customHeight="1">
+          <t>原則②：締めの単位は月</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="64" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3692,18 +3692,18 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>T-S04</t>
+          <t>T-S03</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>締め後は編集できない</t>
+          <t>締めの実行</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み
-【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
+          <t>【前提】S-06 S-08
+【操作】年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -3713,39 +3713,39 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績】
-編集できない（または反映されない）</t>
+          <t>【確認場所：給与実績一覧　→　月別実績タブ】
+「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>T-S04.png</t>
+          <t>T-S03.png</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
+          <t>確認モーダル「月別実績締め処理の確認」の全文／締め実行後にボタンが「締め解除」に変わった状態</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
+          <t>給与実績一覧 → 月別実績タブ → 年月2026-05 → 右上「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>締め後に金額が動かないか</t>
+          <t>確認モーダルを経て締まるか</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>AC-16</t>
+          <t>AC-16 AC-19 AC-32</t>
         </is>
       </c>
       <c r="N44" s="5" t="inlineStr"/>
@@ -3755,7 +3755,7 @@
       <c r="R44" s="5" t="inlineStr"/>
       <c r="S44" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない</t>
+          <t>原則②：締めたら動かない／原則②：確定操作は確認を経る／原則②：締め前の事前チェック</t>
         </is>
       </c>
     </row>
@@ -3767,18 +3767,18 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>T-D07</t>
+          <t>T-S04</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>締め済み期間への遡及</t>
+          <t>締め後は編集できない</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み S-07
-【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
+          <t>【前提】T-S03実施済み
+【操作】2026-05の実績を編集／勤怠を再取込しようとする</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -3788,39 +3788,39 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細】
-締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
+          <t>【確認場所：給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績】
+編集できない（または反映されない）</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>T-D07.png</t>
+          <t>T-S04.png</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
+          <t>締め後に編集・再取込を試みたときの表示と、金額が変わっていない実績画面</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
+          <t>給与実績一覧（締め済み2026-05）／従業員詳細での過去日編集／実績データ取込の再実行</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>警告が出て反映されないか</t>
+          <t>締め後に金額が動かないか</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="M45" s="13" t="inlineStr">
         <is>
-          <t>AC-20</t>
+          <t>AC-16</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr"/>
@@ -3830,11 +3830,11 @@
       <c r="R45" s="5" t="inlineStr"/>
       <c r="S45" s="8" t="inlineStr">
         <is>
-          <t>原則②：遡及は黙って捨てない</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="64" customHeight="1">
+          <t>原則②：締めたら動かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
           <t>締め</t>
@@ -3842,18 +3842,18 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>T-S05</t>
+          <t>T-D07</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>締めの解除</t>
+          <t>締め済み期間への遡及</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-S03実施済み
-【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
+          <t>【前提】T-S03実施済み S-07
+【操作】EMP-001に適用日付＝2026-05-10で保存を試行</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -3863,39 +3863,39 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　月別実績タブ】
-「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
+          <t>【確認場所：従業員詳細】
+締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>T-S05.png</t>
+          <t>T-D07.png</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
+          <t>締め済み期間の適用日付で保存したときの警告表示（メッセージ全文が読めること）</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
+          <t>従業員詳細 … 適用日付＝2026-05-10（締め済み期間内）で「保存」→ 警告表示</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>解除で再計算されるか</t>
+          <t>警告が出て反映されないか</t>
         </is>
       </c>
       <c r="L46" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>ケース別 ＞ 締めたあとに給与改定が決まったとき</t>
         </is>
       </c>
       <c r="M46" s="13" t="inlineStr">
         <is>
-          <t>AC-19</t>
+          <t>AC-20</t>
         </is>
       </c>
       <c r="N46" s="5" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
       <c r="R46" s="5" t="inlineStr"/>
       <c r="S46" s="8" t="inlineStr">
         <is>
-          <t>原則②：確定操作は確認を経る</t>
+          <t>原則②：遡及は黙って捨てない</t>
         </is>
       </c>
     </row>
@@ -3917,18 +3917,18 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>T-S07</t>
+          <t>T-S05</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>締めの実行権限</t>
+          <t>締めの解除</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-10 S-08
-【操作】店長スコープのアカウントでログインし、給与実績一覧を開いて締めを試みる</t>
+          <t>【前提】T-S03実施済み
+【操作】「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -3938,39 +3938,39 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ（店長スコープでログイン）】
-締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
+          <t>【確認場所：給与実績一覧　→　月別実績タブ】
+「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻る（ボタンが「2026-05 締め」に戻る）</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>T-S07.png</t>
+          <t>T-S05.png</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>店長スコープでの給与実績一覧（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
+          <t>確認モーダル「月別実績締め解除の確認」／解除後に再計算された金額</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
+          <t>給与実績一覧 → 月別実績タブ → 右上「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>店長が締められないか</t>
+          <t>解除で再計算されるか</t>
         </is>
       </c>
       <c r="L47" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
         </is>
       </c>
       <c r="M47" s="13" t="inlineStr">
         <is>
-          <t>AC-41</t>
+          <t>AC-19</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr"/>
@@ -3980,30 +3980,30 @@
       <c r="R47" s="5" t="inlineStr"/>
       <c r="S47" s="8" t="inlineStr">
         <is>
-          <t>原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="79" customHeight="1">
+          <t>原則②：確定操作は確認を経る</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="64" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>取込</t>
+          <t>締め</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>T-I02</t>
+          <t>T-S07</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>テンプレートのDLと画面</t>
+          <t>締めの実行権限</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
+          <t>【前提】S-10 S-08
+【操作】店長スコープのアカウントでログインし、給与実績一覧を開いて締めを試みる</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -4013,39 +4013,39 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ（店長スコープでログイン）】
+締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>T-I02.png</t>
+          <t>T-S07.png</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
         <is>
-          <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
+          <t>店長スコープでの給与実績一覧（締めボタンが無いこと）。APIを直接呼んだ場合の応答も残す</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
+          <t>給与実績一覧 → 月別実績タブ（店長スコープでログイン）… 締めボタンの表示有無とAPI拒否</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>テンプレートの列とBOM</t>
+          <t>店長が締められないか</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ はじめて設定する</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M48" s="13" t="inlineStr">
         <is>
-          <t>AC-21 AC-30</t>
+          <t>AC-41</t>
         </is>
       </c>
       <c r="N48" s="5" t="inlineStr"/>
@@ -4055,7 +4055,7 @@
       <c r="R48" s="5" t="inlineStr"/>
       <c r="S48" s="8" t="inlineStr">
         <is>
-          <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
+          <t>原則②：締めは会社スコープのみ</t>
         </is>
       </c>
     </row>
@@ -4067,50 +4067,50 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>T-I03</t>
+          <t>T-I02</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>King of Time形式の取込</t>
+          <t>テンプレートのDLと画面</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-06
-【操作】データ種類＝King of Time を選び data/07（従業員設定・3行／外部ID 1001・1005・1013）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
+          <t>【前提】S-01
+【操作】設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート → 従業員一覧】
-外部ID 1001・1005 は対応表で E0001・E0005 に解決され、既存の従業員が更新される（単位給与額 340,000／360,000）。対応表に無い 1013 は新規として扱われ、従業員IDが自動で付番される。件数は3行</t>
+          <t>【確認場所：設定インポート】
+従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>T-I03.png</t>
+          <t>T-I02.png</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
+          <t>ダウンロードしたテンプレートをExcelで開いた画面（列名と文字化けが無いこと）</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
+          <t>設定インポート … 右上「従業員設定CSVテンプレート」「給与設定CSVテンプレート」のダウンロード</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
         <is>
-          <t>3行が更新・追加されるか</t>
+          <t>テンプレートの列とBOM</t>
         </is>
       </c>
       <c r="L49" s="13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="M49" s="13" t="inlineStr">
         <is>
-          <t>AC-21</t>
+          <t>AC-21 AC-30</t>
         </is>
       </c>
       <c r="N49" s="5" t="inlineStr"/>
@@ -4130,11 +4130,11 @@
       <c r="R49" s="5" t="inlineStr"/>
       <c r="S49" s="8" t="inlineStr">
         <is>
-          <t>入出力：導入を止めない</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="60" customHeight="1">
+          <t>入出力：導入を止めない／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="79" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4142,50 +4142,50 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>T-I04</t>
+          <t>T-I03</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>ジョブカン形式（表記ゆれ）の取込</t>
+          <t>King of Time形式の取込</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】データ種類＝ジョブカン を選び data/08（3行／外部ID JB-003・JB-010・JB-014）をD&amp;D → 登録</t>
+【操作】データ種類＝King of Time を選び data/07（従業員設定・3行／外部ID 1001・1005・1013）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>08 取込CSV ジョブカン</t>
+          <t>07 取込CSV KingOfTime／10 取込CSV 給与設定</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート → 従業員一覧】
-スタッフコード等の表記ゆれを吸収し、外部ID JB-003・JB-010 が E0003・E0010 に解決される。取込成功=3行</t>
+外部ID 1001・1005 は対応表で E0001・E0005 に解決され、既存の従業員が更新される（単位給与額 340,000／360,000）。対応表に無い 1013 は新規として扱われ、従業員IDが自動で付番される。件数は3行</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>T-I04.png</t>
+          <t>T-I03.png</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
+          <t>取込後の従業員一覧（EMP-001=340,000・EMP-005=360,000・EMP-013が追加されていること）</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
+          <t>設定インポート … データ種類＝King of Time → ファイルのドラッグ領域 → 取り込み列設定 → 下部「登録」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>表記ゆれを吸収できるか</t>
+          <t>3行が更新・追加されるか</t>
         </is>
       </c>
       <c r="L50" s="13" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="M50" s="13" t="inlineStr">
         <is>
-          <t>AC-22</t>
+          <t>AC-21</t>
         </is>
       </c>
       <c r="N50" s="5" t="inlineStr"/>
@@ -4205,7 +4205,7 @@
       <c r="R50" s="5" t="inlineStr"/>
       <c r="S50" s="8" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収</t>
+          <t>入出力：導入を止めない</t>
         </is>
       </c>
     </row>
@@ -4217,60 +4217,60 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>T-I05</t>
+          <t>T-I04</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>異常系データの検出</t>
+          <t>ジョブカン形式（表記ゆれ）の取込</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】data/09（4行）をD&amp;D → 登録</t>
+【操作】データ種類＝ジョブカン を選び data/08（3行／外部ID JB-003・JB-010・JB-014）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>08 取込CSV ジョブカン</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
+          <t>【確認場所：設定インポート → 従業員一覧】
+スタッフコード等の表記ゆれを吸収し、外部ID JB-003・JB-010 が E0003・E0010 に解決される。取込成功=3行</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>T-I05.png</t>
+          <t>T-I04.png</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
+          <t>ジョブカン形式の取込結果（スタッフコード等が正しく対応づいたこと）</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
+          <t>設定インポート … データ種類＝ジョブカン（スタッフコード等の表記ゆれ）→「登録」→ 従業員一覧</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>4種の異常を行ごとに検出するか</t>
+          <t>表記ゆれを吸収できるか</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
+          <t>操作手順 ＞ はじめて設定する</t>
         </is>
       </c>
       <c r="M51" s="13" t="inlineStr">
         <is>
-          <t>AC-23</t>
+          <t>AC-22</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr"/>
@@ -4280,11 +4280,11 @@
       <c r="R51" s="5" t="inlineStr"/>
       <c r="S51" s="8" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="64" customHeight="1">
+          <t>入出力：表記ゆれを吸収</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4292,50 +4292,50 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>T-I17</t>
+          <t>T-I05</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>二重登録の防止</t>
+          <t>異常系データの検出</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】（a）data/07を2回続けて取り込む （b）data/19（外部ID 1002 が2行・単位給与額が異なる）を取り込む</t>
+【操作】data/09（4行）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定インポート】
-（a）2回目は更新となり件数が増えない（二重登録=0件）（b）同じ外部IDが2行あるためエラーとして検出され、両方とも登録されない。1つの外部IDが2つの従業員IDに紐づく=0件</t>
+4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>T-I17.png</t>
+          <t>T-I05.png</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
         <is>
-          <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
+          <t>エラー表示の全体（4行それぞれの理由が読めること）</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
+          <t>設定インポート … data/09 取込時のエラー表示（行ごとの理由）</t>
         </is>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>二重登録されないか</t>
+          <t>4種の異常を行ごとに検出するか</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="M52" s="13" t="inlineStr">
         <is>
-          <t>AC-40 AC-56</t>
+          <t>AC-23</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr"/>
@@ -4355,11 +4355,11 @@
       <c r="R52" s="5" t="inlineStr"/>
       <c r="S52" s="8" t="inlineStr">
         <is>
-          <t>データ保全：二重登録を防ぐ</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="94" customHeight="1">
+          <t>データ保全：不正値を入れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="64" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4367,60 +4367,60 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>T-I20</t>
+          <t>T-I17</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>外部IDの対応と付番</t>
+          <t>二重登録の防止</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】（a）data/20 の対応表を開き、EMP-001 が King of Time 1001 とジョブカン JB-001 の2件を持つことを確認 →（b）対応表に無い外部ID（例 9999）を含むCSVを取り込む →（c）取り込んだ従業員の従業員IDを従業員一覧で確認する</t>
+【操作】（a）data/07を2回続けて取り込む （b）data/19（外部ID 1002 が2行・単位給与額が異なる）を取り込む</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>20 外部ID対応表／07 取込CSV KingOfTime</t>
+          <t>07 取込CSV KingOfTime／19 取込CSV 重複コード</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：列マッピングテンプレート（外部ID対応）→ 設定インポート → 従業員一覧】
-（a）1名が複数の勤怠システムの外部IDを持てる（E0001＝1001／JB-001）（b）対応表に無い外部IDは取り込まれず、件数と理由が表示される（黙って登録=0件）（c）すべての従業員に従業員IDが付いている（未付番=0件）</t>
+          <t>【確認場所：設定インポート】
+（a）2回目は更新となり件数が増えない（二重登録=0件）（b）同じ外部IDが2行あるためエラーとして検出され、両方とも登録されない。1つの外部IDが2つの従業員IDに紐づく=0件</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>T-I20.png</t>
+          <t>T-I17.png</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>外部ID対応表（EMP-001が2システム分ある状態）／対応表に無い外部IDのエラー表示／従業員一覧の従業員ID列</t>
+          <t>2回目の取込結果（件数が増えていないこと）／重複ファイルのエラー表示</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="12" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート（外部IDの対応）→ 設定インポート → 従業員一覧</t>
+          <t>設定インポート … 同一ファイルの2回取込／重複コードを含むファイルのエラー表示</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>外部IDが従業員IDに解決されるか／未登録は弾かれるか</t>
+          <t>二重登録されないか</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="M53" s="13" t="inlineStr">
         <is>
-          <t>AC-55 AC-56</t>
+          <t>AC-40 AC-56</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr"/>
@@ -4430,7 +4430,7 @@
       <c r="R53" s="5" t="inlineStr"/>
       <c r="S53" s="8" t="inlineStr">
         <is>
-          <t>データ保全：従業員の同一性を保つ／入出力：ID体系の違いを吸収</t>
+          <t>データ保全：二重登録を防ぐ</t>
         </is>
       </c>
     </row>
@@ -4442,60 +4442,60 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>T-I18</t>
+          <t>T-I20</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>取込が途中で失敗したときの扱い</t>
+          <t>外部IDの対応と付番</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
           <t>【前提】S-04 S-06
-【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
+【操作】（a）data/20 の対応表を開き、EMP-001 が King of Time 1001 とジョブカン JB-001 の2件を持つことを確認 →（b）対応表に無い外部ID（例 9999）を含むCSVを取り込む →（c）取り込んだ従業員の従業員IDを従業員一覧で確認する</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>20 外部ID対応表／07 取込CSV KingOfTime</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録】
-中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
+          <t>【確認場所：列マッピングテンプレート（外部ID対応）→ 設定インポート → 従業員一覧】
+（a）1名が複数の勤怠システムの外部IDを持てる（E0001＝1001／JB-001）（b）対応表に無い外部IDは取り込まれず、件数と理由が表示される（黙って登録=0件）（c）すべての従業員に従業員IDが付いている（未付番=0件）</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>T-I18.png</t>
+          <t>T-I20.png</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
+          <t>外部ID対応表（EMP-001が2システム分ある状態）／対応表に無い外部IDのエラー表示／従業員一覧の従業員ID列</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録されていないこと）</t>
+          <t>列マッピングテンプレート（外部IDの対応）→ 設定インポート → 従業員一覧</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>部分登録が残らないか</t>
+          <t>外部IDが従業員IDに解決されるか／未登録は弾かれるか</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M54" s="13" t="inlineStr">
         <is>
-          <t>AC-42</t>
+          <t>AC-55 AC-56</t>
         </is>
       </c>
       <c r="N54" s="5" t="inlineStr"/>
@@ -4505,11 +4505,11 @@
       <c r="R54" s="5" t="inlineStr"/>
       <c r="S54" s="8" t="inlineStr">
         <is>
-          <t>データ保全：中途半端に残さない</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="64" customHeight="1">
+          <t>データ保全：従業員の同一性を保つ／入出力：ID体系の違いを吸収</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="94" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4517,60 +4517,60 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>T-I11</t>
+          <t>T-I18</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>CSV位置合わせ設定</t>
+          <t>取込が途中で失敗したときの扱い</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06
-【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
+          <t>【前提】S-04 S-06
+【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>11 取込CSV 説明行あり</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-余計な行が無視され、3行が正しく取り込まれる</t>
+          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録】
+中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>T-I11.png</t>
+          <t>T-I18.png</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
+          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
+          <t>設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録されていないこと）</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>説明行を飛ばして取り込めるか</t>
+          <t>部分登録が残らないか</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="M55" s="13" t="inlineStr">
         <is>
-          <t>AC-37</t>
+          <t>AC-42</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
@@ -4580,11 +4580,11 @@
       <c r="R55" s="5" t="inlineStr"/>
       <c r="S55" s="8" t="inlineStr">
         <is>
-          <t>入出力：現場のCSVをそのまま使える</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="139" customHeight="1">
+          <t>データ保全：中途半端に残さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="64" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4592,51 +4592,50 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>T-I09</t>
+          <t>T-I11</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>CSV位置合わせ設定</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】「列マッピングテンプレート」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
+【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>11 取込CSV 説明行あり</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート」】
-テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる
-リンクのラベルが遷移先の画面名と一字一句そろっている（「〜へ」が付いていない・旧名「従業員設定インポート」が残っていない。食い違い=0件。判断4）</t>
+          <t>【確認場所：設定インポート】
+余計な行が無視され、3行が正しく取り込まれる</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>T-I09.png</t>
+          <t>T-I11.png</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
+          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>設定インポート → ツールバー「列マッピングテンプレート」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
+          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>テンプレの登録・編集・削除と往復／リンク名が画面名と一致しているか</t>
+          <t>説明行を飛ばして取り込めるか</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
@@ -4646,7 +4645,7 @@
       </c>
       <c r="M56" s="13" t="inlineStr">
         <is>
-          <t>AC-24 AC-38 AC-30</t>
+          <t>AC-37</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr"/>
@@ -4656,11 +4655,11 @@
       <c r="R56" s="5" t="inlineStr"/>
       <c r="S56" s="8" t="inlineStr">
         <is>
-          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="79" customHeight="1">
+          <t>入出力：現場のCSVをそのまま使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="139" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4668,50 +4667,51 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>T-I19</t>
+          <t>T-I09</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>マッピング表の一括登録</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
+【操作】「列マッピングテンプレート」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>18 列マッピング表テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：列マッピングテンプレート】
-テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
+          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート」】
+テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる
+リンクのラベルが遷移先の画面名と一字一句そろっている（「〜へ」が付いていない・旧名「従業員設定インポート」が残っていない。食い違い=0件。判断4）</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>T-I19.png</t>
+          <t>T-I09.png</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
+          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
+          <t>設定インポート → ツールバー「列マッピングテンプレート」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>一括登録と10MB超の扱い</t>
+          <t>テンプレの登録・編集・削除と往復／リンク名が画面名と一致しているか</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="M57" s="13" t="inlineStr">
         <is>
-          <t>AC-51</t>
+          <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr"/>
@@ -4731,72 +4731,72 @@
       <c r="R57" s="5" t="inlineStr"/>
       <c r="S57" s="8" t="inlineStr">
         <is>
-          <t>入出力：マッピングの一括運用</t>
+          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="58" ht="79" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>取込</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>T-E04</t>
+          <t>T-I19</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>設定のエクスポート</t>
+          <t>マッピング表の一括登録</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
+          <t>【前提】S-06
+【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>18 列マッピング表テンプレ</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
-専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
+          <t>【確認場所：列マッピングテンプレート】
+テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>T-E04.png</t>
+          <t>T-I19.png</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
+          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
+          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
         </is>
       </c>
       <c r="K58" s="8" t="inlineStr">
         <is>
-          <t>選んだ項目だけ・対象数だけ出るか</t>
+          <t>一括登録と10MB超の扱い</t>
         </is>
       </c>
       <c r="L58" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>AC-25 AC-26 AC-30</t>
+          <t>AC-51</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr"/>
@@ -4806,7 +4806,7 @@
       <c r="R58" s="5" t="inlineStr"/>
       <c r="S58" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
+          <t>入出力：マッピングの一括運用</t>
         </is>
       </c>
     </row>
@@ -4818,51 +4818,50 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>T-E09</t>
+          <t>T-E04</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>実績・同時のエクスポート</t>
+          <t>設定のエクスポート</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（給与実績差分を含む）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
+          <t>【前提】S-04
+【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート】
-実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される
-実績の項目に給与実績差分が選べ、出力値＝実績給与−概算給与と一致する</t>
+          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
+専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>T-E09.png</t>
+          <t>T-E04.png</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
+          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
+          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>実績と同時選択のファイル数</t>
+          <t>選んだ項目だけ・対象数だけ出るか</t>
         </is>
       </c>
       <c r="L59" s="13" t="inlineStr">
@@ -4872,7 +4871,7 @@
       </c>
       <c r="M59" s="13" t="inlineStr">
         <is>
-          <t>AC-25 AC-57</t>
+          <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr"/>
@@ -4882,11 +4881,11 @@
       <c r="R59" s="5" t="inlineStr"/>
       <c r="S59" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="60" customHeight="1">
+          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="79" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4894,50 +4893,51 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>T-E07</t>
+          <t>T-E09</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>未選択でのエクスポート防止</t>
+          <t>実績・同時のエクスポート</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
+          <t>【前提】S-05
+【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（給与実績差分を含む）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
+実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される
+実績の項目に給与実績差分が選べ、出力値＝実績給与−概算給与と一致する</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>T-E07.png</t>
+          <t>T-E09.png</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
+          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
+          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>未選択で出力されないか</t>
+          <t>実績と同時選択のファイル数</t>
         </is>
       </c>
       <c r="L60" s="13" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="M60" s="13" t="inlineStr">
         <is>
-          <t>AC-27</t>
+          <t>AC-25 AC-57</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr"/>
@@ -4957,7 +4957,7 @@
       <c r="R60" s="5" t="inlineStr"/>
       <c r="S60" s="8" t="inlineStr">
         <is>
-          <t>入出力：空振りを防ぐ</t>
+          <t>入出力：渡し先に合わせて出せる</t>
         </is>
       </c>
     </row>
@@ -4969,18 +4969,18 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>T-E08</t>
+          <t>T-E07</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>出力CSVの文字化け</t>
+          <t>未選択でのエクスポート防止</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 ／ T-E04で出力済み
-【操作】T-E04で出力したCSVをExcelで開く</t>
+          <t>【前提】S-04
+【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -4991,28 +4991,28 @@
       <c r="F61" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
+警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>T-E08.png</t>
+          <t>T-E07.png</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
+          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
+          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>Excelで文字化けしないか</t>
+          <t>未選択で出力されないか</t>
         </is>
       </c>
       <c r="L61" s="13" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>AC-28</t>
+          <t>AC-27</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr"/>
@@ -5032,72 +5032,72 @@
       <c r="R61" s="5" t="inlineStr"/>
       <c r="S61" s="8" t="inlineStr">
         <is>
-          <t>入出力：そのまま提出できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="79" customHeight="1">
+          <t>入出力：空振りを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="60" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>取込データ</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>T-N01</t>
+          <t>T-E08</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>取込元データの確認</t>
+          <t>出力CSVの文字化け</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-I03実施済み
-【操作】サイドバー「設定の取込結果」→ 取り込んだファイル・行を確認。次に「実績の取込結果」を開く</t>
+          <t>【前提】S-04 ／ T-E04で出力済み
+【操作】T-E04で出力したCSVをExcelで開く</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定の取込結果（サイドバー）】
-設定の取込結果＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績の取込結果＝一覧→タブ（月別データ10列／日別データ10列。交通費・総支給額は表示しない（判断14））</t>
+          <t>【確認場所：設定・実績エクスポート】
+日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>T-N01.png</t>
+          <t>T-E08.png</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>設定の取込結果と実績の取込結果の一覧＋各タブ（計4枚）</t>
+          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>設定の取込結果（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績の取込結果 … 月別データ／日別データタブ</t>
+          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
         </is>
       </c>
       <c r="K62" s="8" t="inlineStr">
         <is>
-          <t>元データとタブの構成</t>
+          <t>Excelで文字化けしないか</t>
         </is>
       </c>
       <c r="L62" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M62" s="13" t="inlineStr">
         <is>
-          <t>AC-39</t>
+          <t>AC-28</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr"/>
@@ -5107,11 +5107,11 @@
       <c r="R62" s="5" t="inlineStr"/>
       <c r="S62" s="8" t="inlineStr">
         <is>
-          <t>入出力：原因を追える</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="94" customHeight="1">
+          <t>入出力：そのまま提出できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="79" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -5119,50 +5119,50 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>T-N02</t>
+          <t>T-N01</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>取込前のプレビューと前回差分</t>
+          <t>取込元データの確認</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-06
-【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定の取込結果と実績の取込結果で、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
+          <t>【前提】T-I03実施済み
+【操作】サイドバー「設定の取込結果」→ 取り込んだファイル・行を確認。次に「実績の取込結果」を開く</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定の取込結果／実績の取込結果】
-プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
+          <t>【確認場所：設定の取込結果（サイドバー）】
+設定の取込結果＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績の取込結果＝一覧→タブ（月別データ10列／日別データ10列。交通費・総支給額は表示しない（判断14））</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>T-N02.png</t>
+          <t>T-N01.png</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
+          <t>設定の取込結果と実績の取込結果の一覧＋各タブ（計4枚）</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>設定の取込結果／実績の取込結果 … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
+          <t>設定の取込結果（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績の取込結果 … 月別データ／日別データタブ</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr">
         <is>
-          <t>差分がdata/16・17と一致するか</t>
+          <t>元データとタブの構成</t>
         </is>
       </c>
       <c r="L63" s="13" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>AC-50</t>
+          <t>AC-39</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr"/>
@@ -5182,11 +5182,11 @@
       <c r="R63" s="5" t="inlineStr"/>
       <c r="S63" s="8" t="inlineStr">
         <is>
-          <t>データ保全：取り込む前に気づける</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="60" customHeight="1">
+          <t>入出力：原因を追える</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="94" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -5194,50 +5194,50 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>T-N03</t>
+          <t>T-N02</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>取込データと給与実績一覧の相互導線</t>
+          <t>取込前のプレビューと前回差分</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】給与実績一覧の「実績の取込結果」→ 実績の取込結果の「給与実績一覧」を押す</t>
+          <t>【前提】S-05 S-06
+【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定の取込結果と実績の取込結果で、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　「実績の取込結果」／実績の取込結果】
-2経路とも到達する（不通=0）</t>
+          <t>【確認場所：設定の取込結果／実績の取込結果】
+プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>T-N03.png</t>
+          <t>T-N02.png</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>給与実績一覧→実績の取込結果／実績の取込結果→給与実績一覧 の到達直後（2枚）</t>
+          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 「実績の取込結果」／実績の取込結果 → 「給与実績一覧」（相互導線）</t>
+          <t>設定の取込結果／実績の取込結果 … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
         </is>
       </c>
       <c r="K64" s="8" t="inlineStr">
         <is>
-          <t>2経路とも到達するか</t>
+          <t>差分がdata/16・17と一致するか</t>
         </is>
       </c>
       <c r="L64" s="13" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="M64" s="13" t="inlineStr">
         <is>
-          <t>AC-30</t>
+          <t>AC-50</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr"/>
@@ -5257,72 +5257,72 @@
       <c r="R64" s="5" t="inlineStr"/>
       <c r="S64" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る</t>
+          <t>データ保全：取り込む前に気づける</t>
         </is>
       </c>
     </row>
     <row r="65" ht="60" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>T-Z01</t>
+          <t>T-N03</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>移行前後の突合（既存データ）</t>
+          <t>取込データと給与実績一覧の相互導線</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 S-11
-【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
+          <t>【前提】S-05
+【操作】給与実績一覧の「実績の取込結果」→ 実績の取込結果の「給与実績一覧」を押す</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員一覧】
-件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
+          <t>【確認場所：給与実績一覧　→　「実績の取込結果」／実績の取込結果】
+2経路とも到達する（不通=0）</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>T-Z01.png</t>
+          <t>T-N03.png</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
+          <t>給与実績一覧→実績の取込結果／実績の取込結果→給与実績一覧 の到達直後（2枚）</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="12" t="inlineStr">
         <is>
-          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
+          <t>給与実績一覧 → 「実績の取込結果」／実績の取込結果 → 「給与実績一覧」（相互導線）</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>移行前後で差分0件か</t>
+          <t>2経路とも到達するか</t>
         </is>
       </c>
       <c r="L65" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ すでにご利用中のお客様</t>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
       <c r="M65" s="13" t="inlineStr">
         <is>
-          <t>AC-01</t>
+          <t>AC-30</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr"/>
@@ -5332,11 +5332,11 @@
       <c r="R65" s="5" t="inlineStr"/>
       <c r="S65" s="8" t="inlineStr">
         <is>
-          <t>移行：既存顧客が壊れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="94" customHeight="1">
+          <t>画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="60" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
           <t>横断</t>
@@ -5344,51 +5344,50 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>T-Z02</t>
+          <t>T-Z01</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>移行後の適用日付の付与</t>
+          <t>移行前後の突合（既存データ）</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
+          <t>【前提】S-09 S-11
+【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細 → 設定変更履歴／設定変更履歴一覧】
-適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている
-あわせて、すべての従業員に従業員IDが付番されている（未付番=0件）。外部IDは対応表に移されている</t>
+          <t>【確認場所：従業員一覧】
+件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>T-Z02.png</t>
+          <t>T-Z01.png</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
+          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 設定変更履歴／設定変更履歴一覧 … 適用日付の空欄</t>
+          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
         </is>
       </c>
       <c r="K66" s="8" t="inlineStr">
         <is>
-          <t>適用日付の空欄が0件か</t>
+          <t>移行前後で差分0件か</t>
         </is>
       </c>
       <c r="L66" s="13" t="inlineStr">
@@ -5398,7 +5397,7 @@
       </c>
       <c r="M66" s="13" t="inlineStr">
         <is>
-          <t>AC-02 AC-55</t>
+          <t>AC-01</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr"/>
@@ -5408,11 +5407,11 @@
       <c r="R66" s="5" t="inlineStr"/>
       <c r="S66" s="8" t="inlineStr">
         <is>
-          <t>移行：履歴の起点を作る</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="60" customHeight="1">
+          <t>移行：既存顧客が壊れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="94" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
           <t>横断</t>
@@ -5420,50 +5419,51 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>T-Z03</t>
+          <t>T-Z02</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>移行前後の過去月の人件費</t>
+          <t>移行後の適用日付の付与</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
           <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行前に出力しておいた直近3か月の給与実績一覧と、移行後の同3か月を突合する</t>
+【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
+          <t>【確認場所：従業員詳細 → 設定変更履歴／設定変更履歴一覧】
+適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている
+あわせて、すべての従業員に従業員IDが付番されている（未付番=0件）。外部IDは対応表に移されている</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>T-Z03.png</t>
+          <t>T-Z02.png</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>移行前後の給与実績一覧 月別実績（直近3か月・金額が同じであること）</t>
+          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ … 移行前後の直近3か月</t>
+          <t>従業員詳細 → 設定変更履歴／設定変更履歴一覧 … 適用日付の空欄</t>
         </is>
       </c>
       <c r="K67" s="8" t="inlineStr">
         <is>
-          <t>過去3か月の金額が変わらないか</t>
+          <t>適用日付の空欄が0件か</t>
         </is>
       </c>
       <c r="L67" s="13" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="M67" s="13" t="inlineStr">
         <is>
-          <t>AC-03</t>
+          <t>AC-02 AC-55</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr"/>
@@ -5483,7 +5483,7 @@
       <c r="R67" s="5" t="inlineStr"/>
       <c r="S67" s="8" t="inlineStr">
         <is>
-          <t>移行：過去が動かない</t>
+          <t>移行：履歴の起点を作る</t>
         </is>
       </c>
     </row>
@@ -5495,60 +5495,60 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>T-Z04</t>
+          <t>T-Z03</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>サイドバーの構成</t>
+          <t>移行前後の過去月の人件費</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
+          <t>【前提】S-09 ／ T-Z01実施済み
+【操作】移行前に出力しておいた直近3か月の給与実績一覧と、移行後の同3か月を突合する</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：サイドバー「従業員管理」】
-閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>T-Z04.png</t>
+          <t>T-Z03.png</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
+          <t>移行前後の給与実績一覧 月別実績（直近3か月・金額が同じであること）</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="12" t="inlineStr">
         <is>
-          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
+          <t>給与実績一覧 → 月別実績タブ … 移行前後の直近3か月</t>
         </is>
       </c>
       <c r="K68" s="8" t="inlineStr">
         <is>
-          <t>PC・モバイルとも開くか</t>
+          <t>過去3か月の金額が変わらないか</t>
         </is>
       </c>
       <c r="L68" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・画面構成）</t>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
       <c r="M68" s="13" t="inlineStr">
         <is>
-          <t>AC-29</t>
+          <t>AC-03</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       <c r="R68" s="5" t="inlineStr"/>
       <c r="S68" s="8" t="inlineStr">
         <is>
-          <t>画面：たどり着ける</t>
+          <t>移行：過去が動かない</t>
         </is>
       </c>
     </row>
@@ -5570,60 +5570,60 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>T-Z05</t>
+          <t>T-Z04</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>遷移と表示規則の網羅</t>
+          <t>サイドバーの構成</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-05
-【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+          <t>【前提】S-01
+【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
-すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+          <t>【確認場所：サイドバー「従業員管理」】
+閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>T-Z05.png</t>
+          <t>T-Z04.png</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
+          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="12" t="inlineStr">
         <is>
-          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
         </is>
       </c>
       <c r="K69" s="8" t="inlineStr">
         <is>
-          <t>75本の遷移と表示規則</t>
+          <t>PC・モバイルとも開くか</t>
         </is>
       </c>
       <c r="L69" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・遷移網羅）</t>
+          <t>（ヘルプ記載なし・画面構成）</t>
         </is>
       </c>
       <c r="M69" s="13" t="inlineStr">
         <is>
-          <t>AC-30 AC-01</t>
+          <t>AC-29</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr"/>
@@ -5633,72 +5633,72 @@
       <c r="R69" s="5" t="inlineStr"/>
       <c r="S69" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="79" customHeight="1">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="B70" s="14" t="inlineStr">
-        <is>
-          <t>C-000</t>
-        </is>
-      </c>
-      <c r="C70" s="15" t="inlineStr">
-        <is>
-          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
-        </is>
-      </c>
-      <c r="D70" s="15" t="inlineStr">
-        <is>
-          <t>【前提】S-03 S-05
-【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
-        </is>
-      </c>
-      <c r="E70" s="15" t="inlineStr">
-        <is>
-          <t>02〜06・13を再投入（初期化）</t>
-        </is>
-      </c>
-      <c r="F70" s="15" t="inlineStr">
-        <is>
-          <t>【確認場所：従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未】
-従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
-        </is>
-      </c>
-      <c r="G70" s="14" t="inlineStr">
-        <is>
-          <t>C-000.png</t>
-        </is>
-      </c>
-      <c r="H70" s="15" t="inlineStr">
-        <is>
-          <t>初期化後の従業員一覧（12名）と給与実績一覧（未締め・S-05時点の金額）</t>
+          <t>画面：たどり着ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>T-Z05</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>遷移と表示規則の網羅</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>【前提】S-04 S-05
+【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
+すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>T-Z05.png</t>
+        </is>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
-      <c r="J70" s="15" t="inlineStr">
-        <is>
-          <t>従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未締めに戻す）</t>
-        </is>
-      </c>
-      <c r="K70" s="15" t="inlineStr">
-        <is>
-          <t>S-05時点の値に戻ったか</t>
-        </is>
-      </c>
-      <c r="L70" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため対応なし）</t>
-        </is>
-      </c>
-      <c r="M70" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J70" s="12" t="inlineStr">
+        <is>
+          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+        </is>
+      </c>
+      <c r="K70" s="8" t="inlineStr">
+        <is>
+          <t>75本の遷移と表示規則</t>
+        </is>
+      </c>
+      <c r="L70" s="13" t="inlineStr">
+        <is>
+          <t>（ヘルプ記載なし・遷移網羅）</t>
+        </is>
+      </c>
+      <c r="M70" s="13" t="inlineStr">
+        <is>
+          <t>AC-30 AC-01</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr"/>
@@ -5706,13 +5706,13 @@
       <c r="P70" s="6" t="inlineStr"/>
       <c r="Q70" s="5" t="inlineStr"/>
       <c r="R70" s="5" t="inlineStr"/>
-      <c r="S70" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="64" customHeight="1">
+      <c r="S70" s="8" t="inlineStr">
+        <is>
+          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="79" customHeight="1">
       <c r="A71" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5720,60 +5720,60 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>C-001</t>
+          <t>C-000</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプなし）</t>
+          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-002（概算280,000・基礎時給1,750・深夜2h・所属店舗の交通費15,000）と EMP-007（概算300,000・基礎時給1,875・深夜4h・交通費30,000）を検算</t>
+          <t>【前提】S-03 S-05
+【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>02〜06・13を再投入（初期化）</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
-EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
+          <t>【確認場所：従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未】
+従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>C-001.png</t>
+          <t>C-000.png</t>
         </is>
       </c>
       <c r="H71" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
+          <t>初期化後の従業員一覧（12名）と給与実績一覧（未締め・S-05時点の金額）</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
+          <t>従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未締めに戻す）</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
         <is>
-          <t>概算＋深夜＝実績給与か</t>
+          <t>S-05時点の値に戻ったか</t>
         </is>
       </c>
       <c r="L71" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>（初期化のため対応なし）</t>
         </is>
       </c>
       <c r="M71" s="15" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr"/>
@@ -5783,11 +5783,11 @@
       <c r="R71" s="5" t="inlineStr"/>
       <c r="S71" s="15" t="inlineStr">
         <is>
-          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="94" customHeight="1">
+          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="64" customHeight="1">
       <c r="A72" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5795,60 +5795,60 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>C-003</t>
+          <t>C-001</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプあり）</t>
+          <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-001（概算338,000＝320,000＋交通費18,000・深夜6h・ヘルプ22h／ヘルプ先の交通費1,600）／EMP-005（概算372,000＝350,000＋22,000・深夜10h・ヘルプ35h／3,100）／EMP-003（概算153,000＝1,200×120h＋600×15日・ヘルプ20h／1,300）を検算</t>
+【操作】2026-05の EMP-002（概算280,000・基礎時給1,750・深夜2h・所属店舗の交通費15,000）と EMP-007（概算300,000・基礎時給1,875・深夜4h・交通費30,000）を検算</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
-EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算給与＋深夜残業代＋みなし超過残業代＋ヘルプ先の交通費。所属店舗の交通費は概算給与に含む）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
+EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>C-003.png</t>
+          <t>C-001.png</t>
         </is>
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
+          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
         </is>
       </c>
       <c r="K72" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費が按分で振替されるか</t>
+          <t>概算＋深夜＝実績給与か</t>
         </is>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr"/>
@@ -5858,11 +5858,11 @@
       <c r="R72" s="5" t="inlineStr"/>
       <c r="S72" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費＝（概算給与−所属店舗の交通費＋深夜残業代＋みなし超過残業代）×ヘルプ時間÷総労働時間 ＋ ヘルプ先の交通費（判断5・14・23）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="60" customHeight="1">
+          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="94" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5870,50 +5870,50 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>C-005</t>
+          <t>C-003</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計と全社合計の一致</t>
+          <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】2026-05の EMP-001（概算338,000＝320,000＋交通費18,000・深夜6h・ヘルプ22h／ヘルプ先の交通費1,600）／EMP-005（概算372,000＝350,000＋22,000・深夜10h・ヘルプ35h／3,100）／EMP-003（概算153,000＝1,200×120h＋600×15日・ヘルプ20h／1,300）を検算</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
-店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
+EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算給与＋深夜残業代＋みなし超過残業代＋ヘルプ先の交通費。所属店舗の交通費は概算給与に含む）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>C-005.png</t>
+          <t>C-003.png</t>
         </is>
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
+          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計＝全社（差0円）か</t>
+          <t>ヘルプ人件費が按分で振替されるか</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="M73" s="15" t="inlineStr">
         <is>
-          <t>AC-11</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr"/>
@@ -5933,11 +5933,11 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="94" customHeight="1">
+          <t>ヘルプ人件費＝（概算給与−所属店舗の交通費＋深夜残業代＋みなし超過残業代）×ヘルプ時間÷総労働時間 ＋ ヘルプ先の交通費（判断5・14・23）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="60" customHeight="1">
       <c r="A74" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5945,60 +5945,60 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>C-006</t>
+          <t>C-005</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>月中改定と予約の日割り</t>
+          <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>14 勤務データ 2026-06</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従】
-6月＝350,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
+店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>C-006.png</t>
+          <t>C-005.png</t>
         </is>
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
+          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
         </is>
       </c>
       <c r="K74" s="15" t="inlineStr">
         <is>
-          <t>所定労働日割になっているか</t>
+          <t>店舗別合計＝全社（差0円）か</t>
         </is>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>AC-12 AC-04</t>
+          <t>AC-11</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr"/>
@@ -6008,11 +6008,11 @@
       <c r="R74" s="5" t="inlineStr"/>
       <c r="S74" s="15" t="inlineStr">
         <is>
-          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし。概算給与には所属店舗の交通費（月額18,000円）を足す（判断23）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="79" customHeight="1">
+          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="94" customHeight="1">
       <c r="A75" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6020,60 +6020,60 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>C-011</t>
+          <t>C-006</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>月中改定と予約の日割り</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
+【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・14 勤務データ 2026-06</t>
+          <t>14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　月別実績タブ（概算モード）】
-5月＝1,200×120h ＋ 日額交通費600×想定労働日数15 ＝ 153,000円／6月＝1,200×60h ＋ 1,250×60h ＝ 147,000 ＋ 日額交通費600×15 ＝ 156,000円。計算違い0件</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従】
+6月＝350,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>C-011.png</t>
+          <t>C-006.png</t>
         </is>
       </c>
       <c r="H75" s="15" t="inlineStr">
         <is>
-          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
+          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
+          <t>給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
         </is>
       </c>
       <c r="K75" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>所定労働日割になっているか</t>
         </is>
       </c>
       <c r="L75" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="M75" s="15" t="inlineStr">
         <is>
-          <t>AC-13</t>
+          <t>AC-12 AC-04</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
@@ -6083,11 +6083,11 @@
       <c r="R75" s="5" t="inlineStr"/>
       <c r="S75" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算給与＝単位給与額×所定労働時間＋所属店舗の交通費（日額なら×想定労働日数）。月中改定は期間ごとの実働時間×各単価の合計に交通費を足す（判断1・23）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="124" customHeight="1">
+          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし。概算給与には所属店舗の交通費（月額18,000円）を足す（判断23）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="94" customHeight="1">
       <c r="A76" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6095,60 +6095,60 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>C-018</t>
+          <t>C-021</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>想定労働日数と日次の想定給与</t>
+          <t>月の途中で交通費を改定したとき</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-05
-【操作】（a）EMP-003（時給・想定労働日数15を入力済み）の月次の想定給与を検算 →（b）EMP-003の想定労働日数を空欄にして保存し、打刻から求めた日数が使われるか見る →（c）EMP-001（月給・未入力）の月次と日次を検算</t>
+          <t>【前提】C-000 S-07
+【操作】（a）EMP-001（月額交通費18,000）を2026-06-11適用で20,000に改定し、6月と7月の概算給与を見る →（b）EMP-003（日額交通費600）を2026-06-16適用で700に改定し、6月の日別を見る</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ・05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ／14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
-（a）EMP-003の想定給与＝1,200×120＋600×15＝153,000円（b）空欄にしても打刻の出勤日数15日（data/06で2026-05は15日）が使われ、153,000円のまま変わらない（c）EMP-001は打刻20日が使われ、想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003の日次は想定給与・給与実績差分が「—」（判断27）。計算違い0件</t>
+          <t>【確認場所：給与実績一覧 → 月別実績（概算モード）／日別実績】
+（a）6月の概算給与に含まれる交通費は旧額18,000のまま（日割り=0件）。7月から20,000になる（b）EMP-003の6月は、6/15までの出勤日が600円・6/16以降の出勤日が700円で計算される（判断37）</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>C-018.png</t>
+          <t>C-021.png</t>
         </is>
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>従業員詳細の想定労働日数の欄（空欄でも金額が変わらないこと）／月別実績の想定給与／日別実績で時給者の想定給与が「—」であること</t>
+          <t>2026-06と07の月別実績（概算）／EMP-003の6月の日別（交通費が切り替わる前後の日）</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="15" t="inlineStr">
         <is>
-          <t>従業員詳細（想定労働日数）→ 給与実績一覧 日別実績（想定給与）</t>
+          <t>給与実績一覧 月別実績（概算モード）・日別実績</t>
         </is>
       </c>
       <c r="K76" s="15" t="inlineStr">
         <is>
-          <t>未入力でも打刻から日数が取れるか／日額交通費が日数ぶん月次に入るか</t>
+          <t>月額交通費を日割りしていないか／日額が出勤日単位で切り替わるか</t>
         </is>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>AC-59</t>
+          <t>AC-67</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr"/>
@@ -6158,11 +6158,11 @@
       <c r="R76" s="5" t="inlineStr"/>
       <c r="S76" s="15" t="inlineStr">
         <is>
-          <t>想定労働日数＝入力値 → 無ければ直近3か月の平均出勤日数（打刻）→ 打刻が無ければ月給者は営業日数。日額交通費の月次換算と月給者の日次按分に使う（判断26・27・28）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="109" customHeight="1">
+          <t>交通費は按分しない。月額はその月は旧額・翌月から新額／日額は適用日付以降の出勤日から新額（判断37）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="79" customHeight="1">
       <c r="A77" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6170,60 +6170,60 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>C-019</t>
+          <t>C-011</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>日別の概算モード（営業日でならした見込み）</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-05
-【操作】給与実績一覧 → 日別実績タブ → 給与計算モードを「概算」に切り替える → 当月の全営業日ぶんの行が出ることと、日別の合計を確認する</t>
+          <t>【前提】C-000 S-07 ／ data/14を投入
+【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績・14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 日別実績タブ → 給与計算モード＝概算】
-実績が無い日も含めて当月の全営業日に行が出る。1日あたり＝月次の概算給与÷当月の営業日数。日別を全部足すと月次の概算給与と一致する（差 0円）。実績モードに戻すと想定給与列は月次概算÷想定労働日数の額に変わる（同じ日でも額が違う）</t>
+          <t>【確認場所：給与実績一覧　→　月別実績タブ（概算モード）】
+5月＝1,200×120h ＋ 日額交通費600×想定労働日数15 ＝ 153,000円／6月＝1,200×60h ＋ 1,250×60h ＝ 147,000 ＋ 日額交通費600×15 ＝ 156,000円。計算違い0件</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
-          <t>C-019.png</t>
+          <t>C-011.png</t>
         </is>
       </c>
       <c r="H77" s="15" t="inlineStr">
         <is>
-          <t>概算モードの日別（全営業日に行が出ている）／合計が月次の概算給与と一致していること／実績モードに戻したときの想定給与列</t>
+          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 日別実績（概算モード ↔ 実績モード）</t>
+          <t>給与実績一覧 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
         </is>
       </c>
       <c r="K77" s="15" t="inlineStr">
         <is>
-          <t>日別の合計が月次の概算給与と一致するか</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="L77" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M77" s="15" t="inlineStr">
         <is>
-          <t>AC-60</t>
+          <t>AC-13</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
@@ -6233,11 +6233,11 @@
       <c r="R77" s="5" t="inlineStr"/>
       <c r="S77" s="15" t="inlineStr">
         <is>
-          <t>概算の日別＝月次の概算給与÷当月の営業日数、当月の全営業日に配分。端数は最大剰余で月次と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="94" customHeight="1">
+          <t>時給者の概算給与＝単位給与額×所定労働時間＋所属店舗の交通費（日額なら×想定労働日数）。月中改定は期間ごとの実働時間×各単価の合計に交通費を足す（判断1・23）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="124" customHeight="1">
       <c r="A78" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6245,60 +6245,60 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-018</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>想定労働日数と日次の想定給与</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>【前提】C-000 S-05
+【操作】（a）EMP-003（時給・想定労働日数15を入力済み）の月次の想定給与を検算 →（b）EMP-003の想定労働日数を空欄にして保存し、打刻から求めた日数が使われるか見る →（c）EMP-001（月給・未入力）の月次と日次を検算</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ・05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
-判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
+          <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
+（a）EMP-003の想定給与＝1,200×120＋600×15＝153,000円（b）空欄にしても打刻の出勤日数15日（data/06で2026-05は15日）が使われ、153,000円のまま変わらない（c）EMP-001は打刻20日が使われ、想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003の日次は想定給与・給与実績差分が「—」（判断27）。計算違い0件</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
-          <t>C-013.png</t>
+          <t>C-018.png</t>
         </is>
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
+          <t>従業員詳細の想定労働日数の欄（空欄でも金額が変わらないこと）／月別実績の想定給与／日別実績で時給者の想定給与が「—」であること</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
+          <t>従業員詳細（想定労働日数）→ 給与実績一覧 日別実績（想定給与）</t>
         </is>
       </c>
       <c r="K78" s="15" t="inlineStr">
         <is>
-          <t>深夜1.5倍とヘルプの按分単価</t>
+          <t>未入力でも打刻から日数が取れるか／日額交通費が日数ぶん月次に入るか</t>
         </is>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-59</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
@@ -6308,7 +6308,7 @@
       <c r="R78" s="5" t="inlineStr"/>
       <c r="S78" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
+          <t>想定労働日数＝入力値 → 無ければ直近3か月の平均出勤日数（打刻）→ 打刻が無ければ月給者は営業日数。日額交通費の月次換算と月給者の日次按分に使う（判断26・27・28）</t>
         </is>
       </c>
     </row>
@@ -6320,60 +6320,60 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-020</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>過去月の概算が後から変わらない</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>【前提】C-000 S-05
+【操作】（a）2026-05（未締め）の概算給与を控える →（b）data/14（2026-06の勤務データ）を取り込む →（c）2026-05の概算給与をもう一度見る</t>
         </is>
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績／14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F79" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績・日別実績】
-交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ（概算モード）】
+（c）2026-05の概算給与が（a）と1円も変わらない（差分=0円）。2026-05には打刻があるので、その月の実出勤日数（EMP-001は20日・EMP-003は15日）が想定労働日数として使われ、直近3か月の平均には切り替わらない（判断34）</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr">
         <is>
-          <t>C-017.png</t>
+          <t>C-020.png</t>
         </is>
       </c>
       <c r="H79" s="15" t="inlineStr">
         <is>
-          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
+          <t>取込前と取込後の2026-05 月別実績（概算モード）を2枚</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+          <t>給与実績一覧 月別実績（概算モード）／実績データ取込</t>
         </is>
       </c>
       <c r="K79" s="15" t="inlineStr">
         <is>
-          <t>交通費が給与と別費目か</t>
+          <t>新しい月を取り込んでも過去月の概算が動かないか</t>
         </is>
       </c>
       <c r="L79" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M79" s="15" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-64</t>
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr"/>
@@ -6383,11 +6383,11 @@
       <c r="R79" s="5" t="inlineStr"/>
       <c r="S79" s="15" t="inlineStr">
         <is>
-          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="94" customHeight="1">
+          <t>打刻がある月は その月の実出勤日数 を想定労働日数に使う。直近3か月の平均は打刻が無い月だけ（判断28・34）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="109" customHeight="1">
       <c r="A80" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6395,60 +6395,60 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-019</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>日別の概算モード（営業日でならした見込み）</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07
-【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+          <t>【前提】C-000 S-05
+【操作】給与実績一覧 → 日別実績タブ → 給与計算モードを「概算」に切り替える → 当月の全営業日ぶんの行が出ることと、日別の合計を確認する</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+          <t>【確認場所：給与実績一覧 → 日別実績タブ → 給与計算モード＝概算】
+実績が無い日も含めて当月の全営業日に行が出る。1日あたり＝月次の概算給与÷当月の営業日数。日別を全部足すと月次の概算給与と一致する（差 0円）。実績モードに戻すと想定給与列は月次概算÷想定労働日数の額に変わる（同じ日でも額が違う）</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>C-008.png</t>
+          <t>C-019.png</t>
         </is>
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
+          <t>概算モードの日別（全営業日に行が出ている）／合計が月次の概算給与と一致していること／実績モードに戻したときの想定給与列</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+          <t>給与実績一覧 日別実績（概算モード ↔ 実績モード）</t>
         </is>
       </c>
       <c r="K80" s="15" t="inlineStr">
         <is>
-          <t>締め前後で差0円・解除後に再計算</t>
+          <t>日別の合計が月次の概算給与と一致するか</t>
         </is>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>AC-16 AC-17</t>
+          <t>AC-60</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr"/>
@@ -6458,72 +6458,72 @@
       <c r="R80" s="5" t="inlineStr"/>
       <c r="S80" s="15" t="inlineStr">
         <is>
-          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="124" customHeight="1">
-      <c r="A81" s="16" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B81" s="16" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C81" s="17" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="D81" s="17" t="inlineStr">
-        <is>
-          <t>【前提】S-01
-【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
-        </is>
-      </c>
-      <c r="E81" s="17" t="inlineStr">
-        <is>
-          <t>（追加のデータ投入なし）</t>
-        </is>
-      </c>
-      <c r="F81" s="17" t="inlineStr">
-        <is>
-          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
-①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）</t>
-        </is>
-      </c>
-      <c r="G81" s="16" t="inlineStr">
-        <is>
-          <t>R-01.png</t>
-        </is>
-      </c>
-      <c r="H81" s="17" t="inlineStr">
-        <is>
-          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
+          <t>概算の日別＝月次の概算給与÷当月の営業日数、当月の全営業日に配分。端数は最大剰余で月次と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="94" customHeight="1">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>C-013</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-03 S-07
+【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：給与実績一覧 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
+判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
+        </is>
+      </c>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>C-013.png</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr"/>
-      <c r="J81" s="17" t="inlineStr">
-        <is>
-          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
-        </is>
-      </c>
-      <c r="K81" s="17" t="inlineStr">
-        <is>
-          <t>適用日付と履歴がテーブルにあるか</t>
-        </is>
-      </c>
-      <c r="L81" s="17" t="inlineStr">
-        <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
-        </is>
-      </c>
-      <c r="M81" s="17" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47 AC-55</t>
+      <c r="J81" s="15" t="inlineStr">
+        <is>
+          <t>給与実績一覧 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
+        </is>
+      </c>
+      <c r="K81" s="15" t="inlineStr">
+        <is>
+          <t>深夜1.5倍とヘルプの按分単価</t>
+        </is>
+      </c>
+      <c r="L81" s="15" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 人件費の計算方法</t>
+        </is>
+      </c>
+      <c r="M81" s="15" t="inlineStr">
+        <is>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N81" s="5" t="inlineStr"/>
@@ -6531,75 +6531,74 @@
       <c r="P81" s="6" t="inlineStr"/>
       <c r="Q81" s="5" t="inlineStr"/>
       <c r="R81" s="5" t="inlineStr"/>
-      <c r="S81" s="17" t="inlineStr">
-        <is>
-          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="109" customHeight="1">
-      <c r="A82" s="16" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B82" s="16" t="inlineStr">
-        <is>
-          <t>R-02</t>
-        </is>
-      </c>
-      <c r="C82" s="17" t="inlineStr">
-        <is>
-          <t>締めの実装レビュー</t>
-        </is>
-      </c>
-      <c r="D82" s="17" t="inlineStr">
-        <is>
-          <t>【前提】S-01
-【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
-        </is>
-      </c>
-      <c r="E82" s="17" t="inlineStr">
-        <is>
-          <t>（追加のデータ投入なし）</t>
-        </is>
-      </c>
-      <c r="F82" s="17" t="inlineStr">
-        <is>
-          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
-①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所
-適用済みの設定変更履歴は、APIを直接呼んでも更新・削除できない（成功=0件。判断29）</t>
-        </is>
-      </c>
-      <c r="G82" s="16" t="inlineStr">
-        <is>
-          <t>R-02.png</t>
-        </is>
-      </c>
-      <c r="H82" s="17" t="inlineStr">
-        <is>
-          <t>締めAPIのコードとスコープ判定箇所</t>
+      <c r="S81" s="15" t="inlineStr">
+        <is>
+          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="79" customHeight="1">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>C-017</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>交通費の計上先</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-03 S-04
+【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：給与実績一覧 → 月別実績・日別実績】
+交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
+        </is>
+      </c>
+      <c r="G82" s="14" t="inlineStr">
+        <is>
+          <t>C-017.png</t>
+        </is>
+      </c>
+      <c r="H82" s="15" t="inlineStr">
+        <is>
+          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr"/>
-      <c r="J82" s="17" t="inlineStr">
-        <is>
-          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
-        </is>
-      </c>
-      <c r="K82" s="17" t="inlineStr">
-        <is>
-          <t>APIでも店長が締められないか／適用済みの履歴が消せないか</t>
-        </is>
-      </c>
-      <c r="L82" s="17" t="inlineStr">
-        <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
-        </is>
-      </c>
-      <c r="M82" s="17" t="inlineStr">
-        <is>
-          <t>AC-16 AC-41 AC-61</t>
+      <c r="J82" s="15" t="inlineStr">
+        <is>
+          <t>給与実績一覧 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+        </is>
+      </c>
+      <c r="K82" s="15" t="inlineStr">
+        <is>
+          <t>交通費が給与と別費目か</t>
+        </is>
+      </c>
+      <c r="L82" s="15" t="inlineStr">
+        <is>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+        </is>
+      </c>
+      <c r="M82" s="15" t="inlineStr">
+        <is>
+          <t>AC-15</t>
         </is>
       </c>
       <c r="N82" s="5" t="inlineStr"/>
@@ -6607,75 +6606,74 @@
       <c r="P82" s="6" t="inlineStr"/>
       <c r="Q82" s="5" t="inlineStr"/>
       <c r="R82" s="5" t="inlineStr"/>
-      <c r="S82" s="17" t="inlineStr">
-        <is>
-          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="139" customHeight="1">
-      <c r="A83" s="16" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B83" s="16" t="inlineStr">
-        <is>
-          <t>R-03</t>
-        </is>
-      </c>
-      <c r="C83" s="17" t="inlineStr">
-        <is>
-          <t>入力検証とトランザクションのレビュー</t>
-        </is>
-      </c>
-      <c r="D83" s="17" t="inlineStr">
-        <is>
-          <t>【前提】S-01
-【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
-        </is>
-      </c>
-      <c r="E83" s="17" t="inlineStr">
-        <is>
-          <t>（追加のデータ投入なし）</t>
-        </is>
-      </c>
-      <c r="F83" s="17" t="inlineStr">
-        <is>
-          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
-①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）
-実績がある従業員は、APIを直接呼んでも削除できない（成功=0件。判断31）</t>
-        </is>
-      </c>
-      <c r="G83" s="16" t="inlineStr">
-        <is>
-          <t>R-03.png</t>
-        </is>
-      </c>
-      <c r="H83" s="17" t="inlineStr">
-        <is>
-          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
+      <c r="S82" s="15" t="inlineStr">
+        <is>
+          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="94" customHeight="1">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>締めの前後で数字が動かないこと</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-07
+【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+        </is>
+      </c>
+      <c r="F83" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+        </is>
+      </c>
+      <c r="G83" s="14" t="inlineStr">
+        <is>
+          <t>C-008.png</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="inlineStr">
+        <is>
+          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr"/>
-      <c r="J83" s="17" t="inlineStr">
-        <is>
-          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
-        </is>
-      </c>
-      <c r="K83" s="17" t="inlineStr">
-        <is>
-          <t>APIを直接呼んでも弾かれるか</t>
-        </is>
-      </c>
-      <c r="L83" s="17" t="inlineStr">
-        <is>
-          <t>よくあるご質問 ＞ 設定が保存できません</t>
-        </is>
-      </c>
-      <c r="M83" s="17" t="inlineStr">
-        <is>
-          <t>AC-23 AC-42 AC-43 AC-63</t>
+      <c r="J83" s="15" t="inlineStr">
+        <is>
+          <t>給与実績一覧 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+        </is>
+      </c>
+      <c r="K83" s="15" t="inlineStr">
+        <is>
+          <t>締め前後で差0円・解除後に再計算</t>
+        </is>
+      </c>
+      <c r="L83" s="15" t="inlineStr">
+        <is>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
+        </is>
+      </c>
+      <c r="M83" s="15" t="inlineStr">
+        <is>
+          <t>AC-16 AC-17</t>
         </is>
       </c>
       <c r="N83" s="5" t="inlineStr"/>
@@ -6683,13 +6681,13 @@
       <c r="P83" s="6" t="inlineStr"/>
       <c r="Q83" s="5" t="inlineStr"/>
       <c r="R83" s="5" t="inlineStr"/>
-      <c r="S83" s="17" t="inlineStr">
-        <is>
-          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="79" customHeight="1">
+      <c r="S83" s="15" t="inlineStr">
+        <is>
+          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="154" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6697,18 +6695,18 @@
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの共有レビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="D84" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】給与実績一覧・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
         </is>
       </c>
       <c r="E84" s="17" t="inlineStr">
@@ -6718,39 +6716,40 @@
       </c>
       <c r="F84" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
-同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
+          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
+①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）
+同じ適用日付の設定が2件あっても両方保存され、編集日時で有効な行が決まる（上書き削除=0件。判断36）</t>
         </is>
       </c>
       <c r="G84" s="16" t="inlineStr">
         <is>
-          <t>R-04.png</t>
+          <t>R-01.png</t>
         </is>
       </c>
       <c r="H84" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
+          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
+          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
       </c>
       <c r="K84" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックが1箇所か</t>
+          <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
       <c r="L84" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M84" s="17" t="inlineStr">
         <is>
-          <t>AC-35 AC-11</t>
+          <t>AC-07 AC-40 AC-47 AC-55 AC-66</t>
         </is>
       </c>
       <c r="N84" s="5" t="inlineStr"/>
@@ -6760,11 +6759,11 @@
       <c r="R84" s="5" t="inlineStr"/>
       <c r="S84" s="17" t="inlineStr">
         <is>
-          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="64" customHeight="1">
+          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="109" customHeight="1">
       <c r="A85" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6772,18 +6771,18 @@
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>締めの実装レビュー</t>
         </is>
       </c>
       <c r="D85" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込の列解決の実装を提示してもらう</t>
+【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
       <c r="E85" s="17" t="inlineStr">
@@ -6793,39 +6792,40 @@
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
-CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
+          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
+①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所
+適用済みの設定変更履歴は、APIを直接呼んでも更新・削除できない（成功=0件。判断29）</t>
         </is>
       </c>
       <c r="G85" s="16" t="inlineStr">
         <is>
-          <t>R-05.png</t>
+          <t>R-02.png</t>
         </is>
       </c>
       <c r="H85" s="17" t="inlineStr">
         <is>
-          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
+          <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr"/>
       <c r="J85" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
+          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
       </c>
       <c r="K85" s="17" t="inlineStr">
         <is>
-          <t>列名がコードに埋まっていないか</t>
+          <t>APIでも店長が締められないか／適用済みの履歴が消せないか</t>
         </is>
       </c>
       <c r="L85" s="17" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M85" s="17" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-16 AC-41 AC-61</t>
         </is>
       </c>
       <c r="N85" s="5" t="inlineStr"/>
@@ -6835,11 +6835,11 @@
       <c r="R85" s="5" t="inlineStr"/>
       <c r="S85" s="17" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="79" customHeight="1">
+          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="139" customHeight="1">
       <c r="A86" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6847,18 +6847,18 @@
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>設定更新処理の共通化レビュー</t>
+          <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
@@ -6868,39 +6868,40 @@
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
-設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
+①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）
+実績がある従業員は、APIを直接呼んでも削除できない（成功=0件。判断31）</t>
         </is>
       </c>
       <c r="G86" s="16" t="inlineStr">
         <is>
-          <t>R-06.png</t>
+          <t>R-03.png</t>
         </is>
       </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
       </c>
       <c r="K86" s="17" t="inlineStr">
         <is>
-          <t>2つの入口で更新処理が共通か</t>
+          <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
       <c r="L86" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
       <c r="M86" s="17" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-23 AC-42 AC-43 AC-63</t>
         </is>
       </c>
       <c r="N86" s="5" t="inlineStr"/>
@@ -6910,17 +6911,242 @@
       <c r="R86" s="5" t="inlineStr"/>
       <c r="S86" s="17" t="inlineStr">
         <is>
+          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="79" customHeight="1">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>R-04</t>
+        </is>
+      </c>
+      <c r="C87" s="17" t="inlineStr">
+        <is>
+          <t>計算ロジックの共有レビュー</t>
+        </is>
+      </c>
+      <c r="D87" s="17" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】給与実績一覧・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+        </is>
+      </c>
+      <c r="E87" s="17" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
+同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
+        </is>
+      </c>
+      <c r="G87" s="16" t="inlineStr">
+        <is>
+          <t>R-04.png</t>
+        </is>
+      </c>
+      <c r="H87" s="17" t="inlineStr">
+        <is>
+          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr"/>
+      <c r="J87" s="17" t="inlineStr">
+        <is>
+          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
+        </is>
+      </c>
+      <c r="K87" s="17" t="inlineStr">
+        <is>
+          <t>計算ロジックが1箇所か</t>
+        </is>
+      </c>
+      <c r="L87" s="17" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 人件費の計算方法</t>
+        </is>
+      </c>
+      <c r="M87" s="17" t="inlineStr">
+        <is>
+          <t>AC-35 AC-11</t>
+        </is>
+      </c>
+      <c r="N87" s="5" t="inlineStr"/>
+      <c r="O87" s="5" t="inlineStr"/>
+      <c r="P87" s="6" t="inlineStr"/>
+      <c r="Q87" s="5" t="inlineStr"/>
+      <c r="R87" s="5" t="inlineStr"/>
+      <c r="S87" s="17" t="inlineStr">
+        <is>
+          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="64" customHeight="1">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>R-05</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>列マッピングの実装レビュー</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】取込の列解決の実装を提示してもらう</t>
+        </is>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
+CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
+        </is>
+      </c>
+      <c r="G88" s="16" t="inlineStr">
+        <is>
+          <t>R-05.png</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr">
+        <is>
+          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr"/>
+      <c r="J88" s="17" t="inlineStr">
+        <is>
+          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
+        </is>
+      </c>
+      <c r="K88" s="17" t="inlineStr">
+        <is>
+          <t>列名がコードに埋まっていないか</t>
+        </is>
+      </c>
+      <c r="L88" s="17" t="inlineStr">
+        <is>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+        </is>
+      </c>
+      <c r="M88" s="17" t="inlineStr">
+        <is>
+          <t>AC-22 AC-24</t>
+        </is>
+      </c>
+      <c r="N88" s="5" t="inlineStr"/>
+      <c r="O88" s="5" t="inlineStr"/>
+      <c r="P88" s="6" t="inlineStr"/>
+      <c r="Q88" s="5" t="inlineStr"/>
+      <c r="R88" s="5" t="inlineStr"/>
+      <c r="S88" s="17" t="inlineStr">
+        <is>
+          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="79" customHeight="1">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B89" s="16" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C89" s="17" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="D89" s="17" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="E89" s="17" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F89" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
+設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="G89" s="16" t="inlineStr">
+        <is>
+          <t>R-06.png</t>
+        </is>
+      </c>
+      <c r="H89" s="17" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr"/>
+      <c r="J89" s="17" t="inlineStr">
+        <is>
+          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+        </is>
+      </c>
+      <c r="K89" s="17" t="inlineStr">
+        <is>
+          <t>2つの入口で更新処理が共通か</t>
+        </is>
+      </c>
+      <c r="L89" s="17" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="M89" s="17" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="N89" s="5" t="inlineStr"/>
+      <c r="O89" s="5" t="inlineStr"/>
+      <c r="P89" s="6" t="inlineStr"/>
+      <c r="Q89" s="5" t="inlineStr"/>
+      <c r="R89" s="5" t="inlineStr"/>
+      <c r="S89" s="17" t="inlineStr">
+        <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S86"/>
+  <autoFilter ref="A2:S89"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3:O86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$2:$S$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S89"/>
+  <dimension ref="A1:S90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="1" ht="68" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（準備11行＋検証76ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
+          <t>確かめる手順（準備11行＋検証77ケース）。上から順に実施する。段階でフィルタすると 一覧／登録／詳細／履歴／実績／締め／取込／出力／取込データ／横断／計算／実装レビュー に絞り込める。
 実施順を変えてはいけない箇所：①T-A08（勤怠取込）→T-S03（締め）　②T-S03→T-S04・T-D07→T-S05（この3件は締め済みでしか確認できない）　③C-000（初期化）は計算の先頭　④C-008は計算の最後（2026-05のEMP-001を352,286円に変えるためC-013・C-017が合わなくなる）　⑤T-N02の前にdata/02を再投入　⑥削除はEMP-012（T-L10）とEMP-004（T-D08）だけ
 列の使い方：使用する検証データ＝この検証で投入・使用するdataファイル／期待値＝先頭の【確認場所】でどの画面を見て合否を出すかを示し、続けて合格の基準を書いている／スクショ（撮るもの）＝何が写っていれば証拠になるか／スクショ貼付欄＝撮った画像をこの列に貼る／対応受入条件＝IDで受入条件表を引くと合格基準（定量）がある。検証後はIDごとに確認表へ集約し、紐づく検証がすべてOKで初めて合格／ヘルプページ該当箇所＝顧客への約束。NGのとき実装を直すのかヘルプを直すのかを決める
 色：緑＝使う検証データ　青＝画面　橙＝スクショの指示　紫＝ヘルプ・受入条件との対応　黄＝当日の記入欄。行の地色は 薄黄＝準備　薄緑＝計算　薄紫＝実装レビュー</t>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="94" customHeight="1">
+    <row r="55" ht="109" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4517,60 +4517,60 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>T-I18</t>
+          <t>T-I21</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>取込が途中で失敗したときの扱い</t>
+          <t>外部勤怠の新しい従業員の自動追加</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-06
-【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
+          <t>【前提】S-06
+【操作】（a）連携設定の「新しい従業員を自動で追加する」がOFFの状態で、対応表に無い外部IDを含む勤怠データを取り込む →（b）ONにして同じデータを取り込む →（c）従業員一覧と給与実績一覧のエラーの絞り込みを見る</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>09 取込CSV 異常系</t>
+          <t>（投入済み）20 外部ID対応表／07 インポートCSV_KingOfTime（対応表に無い外部IDを1件含める）</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録】
-中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
+          <t>【確認場所：連携設定／実績の取込結果 → 従業員一覧 → 給与実績一覧】
+（a）取り込まれず、件数と理由が実績の取込結果に出る（黙って登録=0件）（b）従業員が1名追加され、従業員IDが付番され、在籍状態=在籍、適用日付=取込対象月の初日、給与設定は空。外部ID対応表が1行増える（c）給与実績一覧のエラーの絞り込み「給与設定が未入力」でその従業員だけを抽出できる</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>T-I18.png</t>
+          <t>T-I21.png</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
+          <t>連携設定のチェックボックス（OFFとON）／OFFのときの取込結果の件数と理由／ONのあとの従業員一覧（1名増えた状態）／エラーの絞り込みで抽出した状態</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="12" t="inlineStr">
         <is>
-          <t>設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録されていないこと）</t>
+          <t>連携設定 → 実績の取込結果 → 従業員一覧 → 給与実績一覧（エラーの絞り込み）</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
         <is>
-          <t>部分登録が残らないか</t>
+          <t>既定がOFFか／自動追加された従業員の設定漏れが見えるか</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M55" s="13" t="inlineStr">
         <is>
-          <t>AC-42</t>
+          <t>AC-68</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr"/>
@@ -4580,11 +4580,11 @@
       <c r="R55" s="5" t="inlineStr"/>
       <c r="S55" s="8" t="inlineStr">
         <is>
-          <t>データ保全：中途半端に残さない</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="64" customHeight="1">
+          <t>（金額計算なし）自動追加された従業員は給与設定が空なので人件費が計算できない。エラーの絞り込みで見つけて設定を埋める運用（判断30・38）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="94" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4592,60 +4592,60 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>T-I11</t>
+          <t>T-I18</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>CSV位置合わせ設定</t>
+          <t>取込が途中で失敗したときの扱い</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-06
-【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
+          <t>【前提】S-04 S-06
+【操作】data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>11 取込CSV 説明行あり</t>
+          <t>09 取込CSV 異常系</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート】
-余計な行が無視され、3行が正しく取り込まれる</t>
+          <t>【確認場所：設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録】
+中途半端な状態が残らないこと。(a)全体拒否なら 登録=0件・履歴の追加=0件。(b)行単位なら 正常行のみ登録され、異常行はエラーとして件数と理由が表示される。いずれの実装でも「登録されたのに履歴が無い行」=0件</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>T-I11.png</t>
+          <t>T-I18.png</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
         <is>
-          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
+          <t>取込後の従業員一覧と設定変更履歴（1件も登録されていないこと）</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
+          <t>設定インポート（全行エラー）→ 従業員一覧と設定変更履歴一覧（部分登録されていないこと）</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>説明行を飛ばして取り込めるか</t>
+          <t>部分登録が残らないか</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>よくあるご質問 ＞ CSVの取り込みでエラーになります</t>
         </is>
       </c>
       <c r="M56" s="13" t="inlineStr">
         <is>
-          <t>AC-37</t>
+          <t>AC-42</t>
         </is>
       </c>
       <c r="N56" s="5" t="inlineStr"/>
@@ -4655,11 +4655,11 @@
       <c r="R56" s="5" t="inlineStr"/>
       <c r="S56" s="8" t="inlineStr">
         <is>
-          <t>入出力：現場のCSVをそのまま使える</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="139" customHeight="1">
+          <t>データ保全：中途半端に残さない</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="64" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4667,51 +4667,50 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>T-I09</t>
+          <t>T-I11</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>CSV位置合わせ設定</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】「列マッピングテンプレート」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
+【操作】data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>11 取込CSV 説明行あり</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート」】
-テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる
-リンクのラベルが遷移先の画面名と一字一句そろっている（「〜へ」が付いていない・旧名「従業員設定インポート」が残っていない。食い違い=0件。判断4）</t>
+          <t>【確認場所：設定インポート】
+余計な行が無視され、3行が正しく取り込まれる</t>
         </is>
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>T-I09.png</t>
+          <t>T-I11.png</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
+          <t>位置合わせ設定を入れた画面と、正しく列が対応づいたプレビュー</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="12" t="inlineStr">
         <is>
-          <t>設定インポート → ツールバー「列マッピングテンプレート」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
+          <t>設定インポート … CSV位置合わせ設定（ヘッダー行3／データ開始行4／開始列1）→ 取り込み列設定</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>テンプレの登録・編集・削除と往復／リンク名が画面名と一致しているか</t>
+          <t>説明行を飛ばして取り込めるか</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
@@ -4721,7 +4720,7 @@
       </c>
       <c r="M57" s="13" t="inlineStr">
         <is>
-          <t>AC-24 AC-38 AC-30</t>
+          <t>AC-37</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr"/>
@@ -4731,11 +4730,11 @@
       <c r="R57" s="5" t="inlineStr"/>
       <c r="S57" s="8" t="inlineStr">
         <is>
-          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="79" customHeight="1">
+          <t>入出力：現場のCSVをそのまま使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="139" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4743,50 +4742,51 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>T-I19</t>
+          <t>T-I09</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>マッピング表の一括登録</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
+【操作】「列マッピングテンプレート」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>18 列マッピング表テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：列マッピングテンプレート】
-テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
+          <t>【確認場所：設定インポート　→　ツールバー「列マッピングテンプレート」】
+テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる
+リンクのラベルが遷移先の画面名と一字一句そろっている（「〜へ」が付いていない・旧名「従業員設定インポート」が残っていない。食い違い=0件。判断4）</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>T-I19.png</t>
+          <t>T-I09.png</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
         <is>
-          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
+          <t>テンプレート登録モーダル／一覧／編集・削除後の一覧／「設定インポートへ」で戻った画面</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
+          <t>設定インポート → ツールバー「列マッピングテンプレート」→ 列マッピングテンプレート（登録モーダル・行を追加・編集/削除・データ種類フィルタ）→「設定インポートへ」で往復</t>
         </is>
       </c>
       <c r="K58" s="8" t="inlineStr">
         <is>
-          <t>一括登録と10MB超の扱い</t>
+          <t>テンプレの登録・編集・削除と往復／リンク名が画面名と一致しているか</t>
         </is>
       </c>
       <c r="L58" s="13" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="M58" s="13" t="inlineStr">
         <is>
-          <t>AC-51</t>
+          <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
       <c r="N58" s="5" t="inlineStr"/>
@@ -4806,72 +4806,72 @@
       <c r="R58" s="5" t="inlineStr"/>
       <c r="S58" s="8" t="inlineStr">
         <is>
-          <t>入出力：マッピングの一括運用</t>
+          <t>入出力：CSが自走できる／入出力：テンプレートの運用／画面：操作が最後まで通る</t>
         </is>
       </c>
     </row>
     <row r="59" ht="79" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>取込</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>T-E04</t>
+          <t>T-I19</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>設定のエクスポート</t>
+          <t>マッピング表の一括登録</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
+          <t>【前提】S-06
+【操作】列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>18 列マッピング表テンプレ</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
-専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
+          <t>【確認場所：列マッピングテンプレート】
+テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
         </is>
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>T-E04.png</t>
+          <t>T-I19.png</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
+          <t>アップロード後のマッピング結果／10MB超を選んだときの表示</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
+          <t>列マッピングテンプレート … 「テンプレートダウンロード」／「マッピングテンプレートファイル」のアップロード（10MB上限）</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>選んだ項目だけ・対象数だけ出るか</t>
+          <t>一括登録と10MB超の扱い</t>
         </is>
       </c>
       <c r="L59" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ データを出力する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M59" s="13" t="inlineStr">
         <is>
-          <t>AC-25 AC-26 AC-30</t>
+          <t>AC-51</t>
         </is>
       </c>
       <c r="N59" s="5" t="inlineStr"/>
@@ -4881,7 +4881,7 @@
       <c r="R59" s="5" t="inlineStr"/>
       <c r="S59" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
+          <t>入出力：マッピングの一括運用</t>
         </is>
       </c>
     </row>
@@ -4893,51 +4893,50 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>T-E09</t>
+          <t>T-E04</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>実績・同時のエクスポート</t>
+          <t>設定のエクスポート</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（給与実績差分を含む）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
+          <t>【前提】S-04
+【操作】従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定・実績エクスポート】
-実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される
-実績の項目に給与実績差分が選べ、出力値＝実績給与−概算給与と一致する</t>
+          <t>【確認場所：設定・実績エクスポート（従業員一覧 右上から遷移）】
+専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>T-E09.png</t>
+          <t>T-E04.png</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
+          <t>選択画面（種別・対象・項目のチェック状態）と、出力されたファイル数が分かる状態</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
+          <t>設定・実績エクスポート（従業員一覧 右上から遷移）… ①エクスポート種別＝設定 → ②対象（複数選択可）→ データ項目のチェック → 「出力」</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>実績と同時選択のファイル数</t>
+          <t>選んだ項目だけ・対象数だけ出るか</t>
         </is>
       </c>
       <c r="L60" s="13" t="inlineStr">
@@ -4947,7 +4946,7 @@
       </c>
       <c r="M60" s="13" t="inlineStr">
         <is>
-          <t>AC-25 AC-57</t>
+          <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
       <c r="N60" s="5" t="inlineStr"/>
@@ -4957,11 +4956,11 @@
       <c r="R60" s="5" t="inlineStr"/>
       <c r="S60" s="8" t="inlineStr">
         <is>
-          <t>入出力：渡し先に合わせて出せる</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="60" customHeight="1">
+          <t>入出力：渡し先に合わせて出せる／入出力：対象ごとに分ける／画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="79" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
           <t>出力</t>
@@ -4969,50 +4968,51 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>T-E07</t>
+          <t>T-E09</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>未選択でのエクスポート防止</t>
+          <t>実績・同時のエクスポート</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04
-【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
+          <t>【前提】S-05
+【操作】①実績 → ②月＝2026-05 → 実績のデータ項目（給与実績差分を含む）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
+実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される
+実績の項目に給与実績差分が選べ、出力値＝実績給与−概算給与と一致する</t>
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>T-E07.png</t>
+          <t>T-E09.png</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
+          <t>設定＋実績を同時選択した画面と、2ファイル出力されたこと</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
+          <t>設定・実績エクスポート … ①実績（月＝2026-05）／①設定＋実績の同時選択 → データ項目 →「出力」</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>未選択で出力されないか</t>
+          <t>実績と同時選択のファイル数</t>
         </is>
       </c>
       <c r="L61" s="13" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="M61" s="13" t="inlineStr">
         <is>
-          <t>AC-27</t>
+          <t>AC-25 AC-57</t>
         </is>
       </c>
       <c r="N61" s="5" t="inlineStr"/>
@@ -5032,7 +5032,7 @@
       <c r="R61" s="5" t="inlineStr"/>
       <c r="S61" s="8" t="inlineStr">
         <is>
-          <t>入出力：空振りを防ぐ</t>
+          <t>入出力：渡し先に合わせて出せる</t>
         </is>
       </c>
     </row>
@@ -5044,18 +5044,18 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>T-E08</t>
+          <t>T-E07</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>出力CSVの文字化け</t>
+          <t>未選択でのエクスポート防止</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 ／ T-E04で出力済み
-【操作】T-E04で出力したCSVをExcelで開く</t>
+          <t>【前提】S-04
+【操作】種別／対象／項目のいずれかを未選択のまま「エクスポート」を押す</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -5066,28 +5066,28 @@
       <c r="F62" s="8" t="inlineStr">
         <is>
           <t>【確認場所：設定・実績エクスポート】
-日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
+警告が出て出力されない（未選択での出力＝0件・空ファイルが落ちてこない）</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>T-E08.png</t>
+          <t>T-E07.png</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
+          <t>未選択で「出力」を押したときの警告（画面が変わっていないこと）</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
+          <t>設定・実績エクスポート … 種別/対象/項目が未選択のまま「出力」→ 警告（同画面に留まる）</t>
         </is>
       </c>
       <c r="K62" s="8" t="inlineStr">
         <is>
-          <t>Excelで文字化けしないか</t>
+          <t>未選択で出力されないか</t>
         </is>
       </c>
       <c r="L62" s="13" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="M62" s="13" t="inlineStr">
         <is>
-          <t>AC-28</t>
+          <t>AC-27</t>
         </is>
       </c>
       <c r="N62" s="5" t="inlineStr"/>
@@ -5107,72 +5107,72 @@
       <c r="R62" s="5" t="inlineStr"/>
       <c r="S62" s="8" t="inlineStr">
         <is>
-          <t>入出力：そのまま提出できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="79" customHeight="1">
+          <t>入出力：空振りを防ぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>取込データ</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>T-N01</t>
+          <t>T-E08</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>取込元データの確認</t>
+          <t>出力CSVの文字化け</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>【前提】T-I03実施済み
-【操作】サイドバー「設定の取込結果」→ 取り込んだファイル・行を確認。次に「実績の取込結果」を開く</t>
+          <t>【前提】S-04 ／ T-E04で出力済み
+【操作】T-E04で出力したCSVをExcelで開く</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定の取込結果（サイドバー）】
-設定の取込結果＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績の取込結果＝一覧→タブ（月別データ10列／日別データ10列。交通費・総支給額は表示しない（判断14））</t>
+          <t>【確認場所：設定・実績エクスポート】
+日本語（氏名・店舗名・列名）が文字化けしない（文字化け＝0箇所）。BOM付きUTF-8</t>
         </is>
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>T-N01.png</t>
+          <t>T-E08.png</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>設定の取込結果と実績の取込結果の一覧＋各タブ（計4枚）</t>
+          <t>出力CSVをExcelで開いた画面（日本語が文字化けしていないこと）</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="12" t="inlineStr">
         <is>
-          <t>設定の取込結果（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績の取込結果 … 月別データ／日別データタブ</t>
+          <t>設定・実績エクスポート … 出力したCSVをExcelで開く（画面外の確認）</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr">
         <is>
-          <t>元データとタブの構成</t>
+          <t>Excelで文字化けしないか</t>
         </is>
       </c>
       <c r="L63" s="13" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
+          <t>操作手順 ＞ データを出力する</t>
         </is>
       </c>
       <c r="M63" s="13" t="inlineStr">
         <is>
-          <t>AC-39</t>
+          <t>AC-28</t>
         </is>
       </c>
       <c r="N63" s="5" t="inlineStr"/>
@@ -5182,11 +5182,11 @@
       <c r="R63" s="5" t="inlineStr"/>
       <c r="S63" s="8" t="inlineStr">
         <is>
-          <t>入出力：原因を追える</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="94" customHeight="1">
+          <t>入出力：そのまま提出できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="79" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -5194,50 +5194,50 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>T-N02</t>
+          <t>T-N01</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>取込前のプレビューと前回差分</t>
+          <t>取込元データの確認</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05 S-06
-【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定の取込結果と実績の取込結果で、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
+          <t>【前提】T-I03実施済み
+【操作】サイドバー「設定の取込結果」→ 取り込んだファイル・行を確認。次に「実績の取込結果」を開く</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：設定の取込結果／実績の取込結果】
-プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
+          <t>【確認場所：設定の取込結果（サイドバー）】
+設定の取込結果＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績の取込結果＝一覧→タブ（月別データ10列／日別データ10列。交通費・総支給額は表示しない（判断14））</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>T-N02.png</t>
+          <t>T-N01.png</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
+          <t>設定の取込結果と実績の取込結果の一覧＋各タブ（計4枚）</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>設定の取込結果／実績の取込結果 … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
+          <t>設定の取込結果（サイドバー）… 取込データ名の一覧 → 従業員設定／給与設定タブ　実績の取込結果 … 月別データ／日別データタブ</t>
         </is>
       </c>
       <c r="K64" s="8" t="inlineStr">
         <is>
-          <t>差分がdata/16・17と一致するか</t>
+          <t>元データとタブの構成</t>
         </is>
       </c>
       <c r="L64" s="13" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="M64" s="13" t="inlineStr">
         <is>
-          <t>AC-50</t>
+          <t>AC-39</t>
         </is>
       </c>
       <c r="N64" s="5" t="inlineStr"/>
@@ -5257,11 +5257,11 @@
       <c r="R64" s="5" t="inlineStr"/>
       <c r="S64" s="8" t="inlineStr">
         <is>
-          <t>データ保全：取り込む前に気づける</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="60" customHeight="1">
+          <t>入出力：原因を追える</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="94" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
           <t>取込データ</t>
@@ -5269,50 +5269,50 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>T-N03</t>
+          <t>T-N02</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>取込データと給与実績一覧の相互導線</t>
+          <t>取込前のプレビューと前回差分</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-05
-【操作】給与実績一覧の「実績の取込結果」→ 実績の取込結果の「給与実績一覧」を押す</t>
+          <t>【前提】S-05 S-06
+【操作】先に data/02（従業員マスタ）を再投入して設定を取込前の値に戻す。そのうえで設定の取込結果と実績の取込結果で、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す。差分の期待値は data/16（設定）・data/17（実績）と突合する</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>02 従業員マスタ／16 前回取込 設定差分／17 前回取込 実績差分</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　「実績の取込結果」／実績の取込結果】
-2経路とも到達する（不通=0）</t>
+          <t>【確認場所：設定の取込結果／実績の取込結果】
+プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回320,000円→新規340,000円」の形式で差だけが表示され、data/16の5行・data/17の9行と一致する。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>T-N03.png</t>
+          <t>T-N02.png</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>給与実績一覧→実績の取込結果／実績の取込結果→給与実績一覧 の到達直後（2枚）</t>
+          <t>前回差分表示の画面（「前回320,000円→新規340,000円」の形式が読めること）</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 「実績の取込結果」／実績の取込結果 → 「給与実績一覧」（相互導線）</t>
+          <t>設定の取込結果／実績の取込結果 … 各行の「プレビュー」「前回差分表示」「読み込み」ボタン</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>2経路とも到達するか</t>
+          <t>差分がdata/16・17と一致するか</t>
         </is>
       </c>
       <c r="L65" s="13" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="M65" s="13" t="inlineStr">
         <is>
-          <t>AC-30</t>
+          <t>AC-50</t>
         </is>
       </c>
       <c r="N65" s="5" t="inlineStr"/>
@@ -5332,72 +5332,72 @@
       <c r="R65" s="5" t="inlineStr"/>
       <c r="S65" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る</t>
+          <t>データ保全：取り込む前に気づける</t>
         </is>
       </c>
     </row>
     <row r="66" ht="60" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>T-Z01</t>
+          <t>T-N03</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>移行前後の突合（既存データ）</t>
+          <t>取込データと給与実績一覧の相互導線</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 S-11
-【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
+          <t>【前提】S-05
+【操作】給与実績一覧の「実績の取込結果」→ 実績の取込結果の「給与実績一覧」を押す</t>
         </is>
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員一覧】
-件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
+          <t>【確認場所：給与実績一覧　→　「実績の取込結果」／実績の取込結果】
+2経路とも到達する（不通=0）</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>T-Z01.png</t>
+          <t>T-N03.png</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
+          <t>給与実績一覧→実績の取込結果／実績の取込結果→給与実績一覧 の到達直後（2枚）</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
+          <t>給与実績一覧 → 「実績の取込結果」／実績の取込結果 → 「給与実績一覧」（相互導線）</t>
         </is>
       </c>
       <c r="K66" s="8" t="inlineStr">
         <is>
-          <t>移行前後で差分0件か</t>
+          <t>2経路とも到達するか</t>
         </is>
       </c>
       <c r="L66" s="13" t="inlineStr">
         <is>
-          <t>ケース別 ＞ すでにご利用中のお客様</t>
+          <t>操作手順 ＞ 取り込んだ元データを確認する</t>
         </is>
       </c>
       <c r="M66" s="13" t="inlineStr">
         <is>
-          <t>AC-01</t>
+          <t>AC-30</t>
         </is>
       </c>
       <c r="N66" s="5" t="inlineStr"/>
@@ -5407,11 +5407,11 @@
       <c r="R66" s="5" t="inlineStr"/>
       <c r="S66" s="8" t="inlineStr">
         <is>
-          <t>移行：既存顧客が壊れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="94" customHeight="1">
+          <t>画面：操作が最後まで通る</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="60" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
           <t>横断</t>
@@ -5419,51 +5419,50 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>T-Z02</t>
+          <t>T-Z01</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>移行後の適用日付の付与</t>
+          <t>移行前後の突合（既存データ）</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
+          <t>【前提】S-09 S-11
+【操作】移行を実施し、移行前後の従業員一覧をCSV出力して data/15 で突合する</t>
         </is>
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：従業員詳細 → 設定変更履歴／設定変更履歴一覧】
-適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている
-あわせて、すべての従業員に従業員IDが付番されている（未付番=0件）。外部IDは対応表に移されている</t>
+          <t>【確認場所：従業員一覧】
+件数の増減＝0（12名のまま）／12項目すべての値の差分＝0</t>
         </is>
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>T-Z02.png</t>
+          <t>T-Z01.png</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
+          <t>移行前後の従業員一覧と、突合表（data/15）の差分結果</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="12" t="inlineStr">
         <is>
-          <t>従業員詳細 → 設定変更履歴／設定変更履歴一覧 … 適用日付の空欄</t>
+          <t>従業員一覧 … 移行前後のCSVエクスポートを突合（画面外での比較）</t>
         </is>
       </c>
       <c r="K67" s="8" t="inlineStr">
         <is>
-          <t>適用日付の空欄が0件か</t>
+          <t>移行前後で差分0件か</t>
         </is>
       </c>
       <c r="L67" s="13" t="inlineStr">
@@ -5473,7 +5472,7 @@
       </c>
       <c r="M67" s="13" t="inlineStr">
         <is>
-          <t>AC-02 AC-55</t>
+          <t>AC-01</t>
         </is>
       </c>
       <c r="N67" s="5" t="inlineStr"/>
@@ -5483,11 +5482,11 @@
       <c r="R67" s="5" t="inlineStr"/>
       <c r="S67" s="8" t="inlineStr">
         <is>
-          <t>移行：履歴の起点を作る</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="60" customHeight="1">
+          <t>移行：既存顧客が壊れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="94" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
         <is>
           <t>横断</t>
@@ -5495,50 +5494,51 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>T-Z03</t>
+          <t>T-Z02</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>移行前後の過去月の人件費</t>
+          <t>移行後の適用日付の付与</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
           <t>【前提】S-09 ／ T-Z01実施済み
-【操作】移行前に出力しておいた直近3か月の給与実績一覧と、移行後の同3か月を突合する</t>
+【操作】移行後の設定履歴を全件CSV出力し、適用日付の空欄を数える</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>15 移行前後 突合テンプレ</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
+          <t>【確認場所：従業員詳細 → 設定変更履歴／設定変更履歴一覧】
+適用日付がNULLの行＝0件。全12名に初回レコードが過去日で付与されている
+あわせて、すべての従業員に従業員IDが付番されている（未付番=0件）。外部IDは対応表に移されている</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>T-Z03.png</t>
+          <t>T-Z02.png</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>移行前後の給与実績一覧 月別実績（直近3か月・金額が同じであること）</t>
+          <t>移行後の設定変更履歴（適用日付が全行に入っていること）</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="12" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ … 移行前後の直近3か月</t>
+          <t>従業員詳細 → 設定変更履歴／設定変更履歴一覧 … 適用日付の空欄</t>
         </is>
       </c>
       <c r="K68" s="8" t="inlineStr">
         <is>
-          <t>過去3か月の金額が変わらないか</t>
+          <t>適用日付の空欄が0件か</t>
         </is>
       </c>
       <c r="L68" s="13" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M68" s="13" t="inlineStr">
         <is>
-          <t>AC-03</t>
+          <t>AC-02 AC-55</t>
         </is>
       </c>
       <c r="N68" s="5" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       <c r="R68" s="5" t="inlineStr"/>
       <c r="S68" s="8" t="inlineStr">
         <is>
-          <t>移行：過去が動かない</t>
+          <t>移行：履歴の起点を作る</t>
         </is>
       </c>
     </row>
@@ -5570,60 +5570,60 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>T-Z04</t>
+          <t>T-Z03</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>サイドバーの構成</t>
+          <t>移行前後の過去月の人件費</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-01
-【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
+          <t>【前提】S-09 ／ T-Z01実施済み
+【操作】移行前に出力しておいた直近3か月の給与実績一覧と、移行後の同3か月を突合する</t>
         </is>
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>（追加のデータ投入なし）</t>
+          <t>15 移行前後 突合テンプレ</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：サイドバー「従業員管理」】
-閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+3か月とも実績給与の差分＝0円（1円でも動けばリリース中止）</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>T-Z04.png</t>
+          <t>T-Z03.png</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
+          <t>移行前後の給与実績一覧 月別実績（直近3か月・金額が同じであること）</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="12" t="inlineStr">
         <is>
-          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
+          <t>給与実績一覧 → 月別実績タブ … 移行前後の直近3か月</t>
         </is>
       </c>
       <c r="K69" s="8" t="inlineStr">
         <is>
-          <t>PC・モバイルとも開くか</t>
+          <t>過去3か月の金額が変わらないか</t>
         </is>
       </c>
       <c r="L69" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・画面構成）</t>
+          <t>ケース別 ＞ すでにご利用中のお客様</t>
         </is>
       </c>
       <c r="M69" s="13" t="inlineStr">
         <is>
-          <t>AC-29</t>
+          <t>AC-03</t>
         </is>
       </c>
       <c r="N69" s="5" t="inlineStr"/>
@@ -5633,7 +5633,7 @@
       <c r="R69" s="5" t="inlineStr"/>
       <c r="S69" s="8" t="inlineStr">
         <is>
-          <t>画面：たどり着ける</t>
+          <t>移行：過去が動かない</t>
         </is>
       </c>
     </row>
@@ -5645,60 +5645,60 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>T-Z05</t>
+          <t>T-Z04</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>遷移と表示規則の網羅</t>
+          <t>サイドバーの構成</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>【前提】S-04 S-05
-【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+          <t>【前提】S-01
+【操作】PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+          <t>（追加のデータ投入なし）</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
-すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+          <t>【確認場所：サイドバー「従業員管理」】
+閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>T-Z05.png</t>
+          <t>T-Z04.png</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
+          <t>PCのホバー展開とモバイルのアコーディオン（2枚）</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="12" t="inlineStr">
         <is>
-          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+          <t>サイドバー「従業員管理」… PCはホバー展開、モバイルはアコーディオン</t>
         </is>
       </c>
       <c r="K70" s="8" t="inlineStr">
         <is>
-          <t>75本の遷移と表示規則</t>
+          <t>PC・モバイルとも開くか</t>
         </is>
       </c>
       <c r="L70" s="13" t="inlineStr">
         <is>
-          <t>（ヘルプ記載なし・遷移網羅）</t>
+          <t>（ヘルプ記載なし・画面構成）</t>
         </is>
       </c>
       <c r="M70" s="13" t="inlineStr">
         <is>
-          <t>AC-30 AC-01</t>
+          <t>AC-29</t>
         </is>
       </c>
       <c r="N70" s="5" t="inlineStr"/>
@@ -5708,72 +5708,72 @@
       <c r="R70" s="5" t="inlineStr"/>
       <c r="S70" s="8" t="inlineStr">
         <is>
-          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="79" customHeight="1">
-      <c r="A71" s="14" t="inlineStr">
-        <is>
-          <t>計算</t>
-        </is>
-      </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>C-000</t>
-        </is>
-      </c>
-      <c r="C71" s="15" t="inlineStr">
-        <is>
-          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
-        </is>
-      </c>
-      <c r="D71" s="15" t="inlineStr">
-        <is>
-          <t>【前提】S-03 S-05
-【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
-        </is>
-      </c>
-      <c r="E71" s="15" t="inlineStr">
-        <is>
-          <t>02〜06・13を再投入（初期化）</t>
-        </is>
-      </c>
-      <c r="F71" s="15" t="inlineStr">
-        <is>
-          <t>【確認場所：従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未】
-従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
-        </is>
-      </c>
-      <c r="G71" s="14" t="inlineStr">
-        <is>
-          <t>C-000.png</t>
-        </is>
-      </c>
-      <c r="H71" s="15" t="inlineStr">
-        <is>
-          <t>初期化後の従業員一覧（12名）と給与実績一覧（未締め・S-05時点の金額）</t>
+          <t>画面：たどり着ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>横断</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>T-Z05</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>遷移と表示規則の網羅</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>【前提】S-04 S-05
+【操作】仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>（投入済み）02 従業員マスタ（一覧の12名）／05 月次給与実績・06 日次給与実績</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>【確認場所：全画面（仕様書 第2部の遷移フロー75本）】
+すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>T-Z05.png</t>
+        </is>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>差異が出た画面のみ（全75本は不要。想定と違った箇所を記録する）</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="15" t="inlineStr">
-        <is>
-          <t>従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未締めに戻す）</t>
-        </is>
-      </c>
-      <c r="K71" s="15" t="inlineStr">
-        <is>
-          <t>S-05時点の値に戻ったか</t>
-        </is>
-      </c>
-      <c r="L71" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため対応なし）</t>
-        </is>
-      </c>
-      <c r="M71" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J71" s="12" t="inlineStr">
+        <is>
+          <t>全画面（仕様書 第2部の遷移フロー75本）… 通貨の桁区切り・バッジ・0件表示</t>
+        </is>
+      </c>
+      <c r="K71" s="8" t="inlineStr">
+        <is>
+          <t>75本の遷移と表示規則</t>
+        </is>
+      </c>
+      <c r="L71" s="13" t="inlineStr">
+        <is>
+          <t>（ヘルプ記載なし・遷移網羅）</t>
+        </is>
+      </c>
+      <c r="M71" s="13" t="inlineStr">
+        <is>
+          <t>AC-30 AC-01</t>
         </is>
       </c>
       <c r="N71" s="5" t="inlineStr"/>
@@ -5781,13 +5781,13 @@
       <c r="P71" s="6" t="inlineStr"/>
       <c r="Q71" s="5" t="inlineStr"/>
       <c r="R71" s="5" t="inlineStr"/>
-      <c r="S71" s="15" t="inlineStr">
-        <is>
-          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="64" customHeight="1">
+      <c r="S71" s="8" t="inlineStr">
+        <is>
+          <t>画面：操作が最後まで通る／移行：既存顧客が壊れない</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="79" customHeight="1">
       <c r="A72" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5795,60 +5795,60 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>C-001</t>
+          <t>C-000</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプなし）</t>
+          <t>データの初期化（計算の検証に入る前に必ず実施）</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-002（概算280,000・基礎時給1,750・深夜2h・所属店舗の交通費15,000）と EMP-007（概算300,000・基礎時給1,875・深夜4h・交通費30,000）を検算</t>
+          <t>【前提】S-03 S-05
+【操作】操作の検証（T-）でデータが変わっているため、data/02〜06・13 を再投入し、2026-05を未締めに戻す。EMP-013・014（取込で追加された分）は削除する</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>02〜06・13を再投入（初期化）</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
-EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
+          <t>【確認場所：従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未】
+従業員12名・data/05の5名がS-05時点の値に戻る（EMP-001=320,000／EMP-002=280,000／EMP-003=時給1,200／EMP-005=350,000）。2026-05は未締め</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>C-001.png</t>
+          <t>C-000.png</t>
         </is>
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
+          <t>初期化後の従業員一覧（12名）と給与実績一覧（未締め・S-05時点の金額）</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
+          <t>従業員一覧（12名に戻す）／給与実績一覧 月別実績（2026-05を未締めに戻す）</t>
         </is>
       </c>
       <c r="K72" s="15" t="inlineStr">
         <is>
-          <t>概算＋深夜＝実績給与か</t>
+          <t>S-05時点の値に戻ったか</t>
         </is>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>（初期化のため対応なし）</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N72" s="5" t="inlineStr"/>
@@ -5858,11 +5858,11 @@
       <c r="R72" s="5" t="inlineStr"/>
       <c r="S72" s="15" t="inlineStr">
         <is>
-          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="94" customHeight="1">
+          <t>（初期化のため算式なし）S-05時点の値へ戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="64" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5870,60 +5870,60 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>C-003</t>
+          <t>C-001</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプあり）</t>
+          <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-03 S-07
-【操作】2026-05の EMP-001（概算338,000＝320,000＋交通費18,000・深夜6h・ヘルプ22h／ヘルプ先の交通費1,600）／EMP-005（概算372,000＝350,000＋22,000・深夜10h・ヘルプ35h／3,100）／EMP-003（概算153,000＝1,200×120h＋600×15日・ヘルプ20h／1,300）を検算</t>
+【操作】2026-05の EMP-002（概算280,000・基礎時給1,750・深夜2h・所属店舗の交通費15,000）と EMP-007（概算300,000・基礎時給1,875・深夜4h・交通費30,000）を検算</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
-EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算給与＋深夜残業代＋みなし超過残業代＋ヘルプ先の交通費。所属店舗の交通費は概算給与に含む）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
+EMP-002＝300,250（概算280,000＋深夜5,250＋交通費15,000）／EMP-007＝341,250（概算300,000＋深夜11,250＋交通費30,000）。いずれも差分0円。交通費の列は表示されない</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>C-003.png</t>
+          <t>C-001.png</t>
         </is>
       </c>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
+          <t>月別実績（実績モード）でEMP-002・EMP-007の行が読める範囲</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・実績給与の列</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費が按分で振替されるか</t>
+          <t>概算＋深夜＝実績給与か</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M73" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="N73" s="5" t="inlineStr"/>
@@ -5933,11 +5933,11 @@
       <c r="R73" s="5" t="inlineStr"/>
       <c r="S73" s="15" t="inlineStr">
         <is>
-          <t>ヘルプ人件費＝（概算給与−所属店舗の交通費＋深夜残業代＋みなし超過残業代）×ヘルプ時間÷総労働時間 ＋ ヘルプ先の交通費（判断5・14・23）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="60" customHeight="1">
+          <t>基礎時給＝単位給与額÷所定労働時間／深夜残業代＝基礎時給×1.5×深夜残業時間（判断7・確定）／実績給与＝概算給与＋深夜残業代＋みなし超過残業代</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="94" customHeight="1">
       <c r="A74" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -5945,50 +5945,50 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>C-005</t>
+          <t>C-003</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計と全社合計の一致</t>
+          <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】2026-05の EMP-001（概算338,000＝320,000＋交通費18,000・深夜6h・ヘルプ22h／ヘルプ先の交通費1,600）／EMP-005（概算372,000＝350,000＋22,000・深夜10h・ヘルプ35h／3,100）／EMP-003（概算153,000＝1,200×120h＋600×15日・ヘルプ20h／1,300）を検算</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
-店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
+EMP-001＝357,600／EMP-005＝407,912／EMP-003＝154,300（いずれも概算給与＋深夜残業代＋みなし超過残業代＋ヘルプ先の交通費。所属店舗の交通費は概算給与に含む）。ヘルプ人件費は按分にヘルプ先の交通費を足した額（EMP-001＝44,832／EMP-003＝25,300／EMP-005＝75,524）</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>C-005.png</t>
+          <t>C-003.png</t>
         </is>
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
+          <t>月別実績（実績モード）でEMP-001・003・005の行と、ヘルプ人件費の列が読める範囲</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 概算給与・深夜残業代・ヘルプ人件費・実績給与の列</t>
         </is>
       </c>
       <c r="K74" s="15" t="inlineStr">
         <is>
-          <t>店舗別合計＝全社（差0円）か</t>
+          <t>ヘルプ人件費が按分で振替されるか</t>
         </is>
       </c>
       <c r="L74" s="15" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>AC-11</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N74" s="5" t="inlineStr"/>
@@ -6008,11 +6008,11 @@
       <c r="R74" s="5" t="inlineStr"/>
       <c r="S74" s="15" t="inlineStr">
         <is>
-          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="94" customHeight="1">
+          <t>ヘルプ人件費＝（概算給与−所属店舗の交通費＋深夜残業代＋みなし超過残業代）×ヘルプ時間÷総労働時間 ＋ ヘルプ先の交通費（判断5・14・23）。応援先店舗に加算し所属店舗から差し引く（振替）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="60" customHeight="1">
       <c r="A75" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6020,60 +6020,60 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>C-006</t>
+          <t>C-005</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>月中改定と予約の日割り</t>
+          <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>14 勤務データ 2026-06</t>
+          <t>05 月次給与実績</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従】
-6月＝350,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ → 実績モード】
+店舗5店の合計 − 全社合計 ＝ 0円（1,561,312円）</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>C-006.png</t>
+          <t>C-005.png</t>
         </is>
       </c>
       <c r="H75" s="15" t="inlineStr">
         <is>
-          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
+          <t>店舗フィルタ5店それぞれの合計と全社の合計（計6枚、または合計値が分かる1枚）</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
+          <t>給与実績一覧 → 月別実績タブ → 実績モード … 店舗フィルタを5店それぞれに設定して合計</t>
         </is>
       </c>
       <c r="K75" s="15" t="inlineStr">
         <is>
-          <t>所定労働日割になっているか</t>
+          <t>店舗別合計＝全社（差0円）か</t>
         </is>
       </c>
       <c r="L75" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M75" s="15" t="inlineStr">
         <is>
-          <t>AC-12 AC-04</t>
+          <t>AC-11</t>
         </is>
       </c>
       <c r="N75" s="5" t="inlineStr"/>
@@ -6083,7 +6083,7 @@
       <c r="R75" s="5" t="inlineStr"/>
       <c r="S75" s="15" t="inlineStr">
         <is>
-          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし。概算給与には所属店舗の交通費（月額18,000円）を足す（判断23）</t>
+          <t>店舗別の合計＝全社合計。ヘルプ分は店舗間の振替のため総額は変わらない（原則③）</t>
         </is>
       </c>
     </row>
@@ -6095,50 +6095,50 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>C-021</t>
+          <t>C-006</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>月の途中で交通費を改定したとき</t>
+          <t>月中改定と予約の日割り</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07
-【操作】（a）EMP-001（月額交通費18,000）を2026-06-11適用で20,000に改定し、6月と7月の概算給与を見る →（b）EMP-003（日額交通費600）を2026-06-16適用で700に改定し、6月の日別を見る</t>
+          <t>【前提】C-000 S-07 ／ data/14を投入
+【操作】EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ／14 勤務データ 2026-06</t>
+          <t>14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績（概算モード）／日別実績】
-（a）6月の概算給与に含まれる交通費は旧額18,000のまま（日割り=0件）。7月から20,000になる（b）EMP-003の6月は、6/15までの出勤日が600円・6/16以降の出勤日が700円で計算される（判断37）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従】
+6月＝350,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>C-021.png</t>
+          <t>C-006.png</t>
         </is>
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>2026-06と07の月別実績（概算）／EMP-003の6月の日別（交通費が切り替わる前後の日）</t>
+          <t>2026-06・07・08の月別実績（改定の反映と日割りが分かること）</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 月別実績（概算モード）・日別実績</t>
+          <t>給与実績一覧 → 月別実績タブ（2026-06/07/08）／改定は従業員詳細の適用日付</t>
         </is>
       </c>
       <c r="K76" s="15" t="inlineStr">
         <is>
-          <t>月額交通費を日割りしていないか／日額が出勤日単位で切り替わるか</t>
+          <t>所定労働日割になっているか</t>
         </is>
       </c>
       <c r="L76" s="15" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>AC-67</t>
+          <t>AC-12 AC-04</t>
         </is>
       </c>
       <c r="N76" s="5" t="inlineStr"/>
@@ -6158,11 +6158,11 @@
       <c r="R76" s="5" t="inlineStr"/>
       <c r="S76" s="15" t="inlineStr">
         <is>
-          <t>交通費は按分しない。月額はその月は旧額・翌月から新額／日額は適用日付以降の出勤日から新額（判断37）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="79" customHeight="1">
+          <t>月中改定は所定労働日割（判断1・確定）＝旧単価×改定前の所定労働日数÷所定労働日数＋新単価×改定後の所定労働日数÷所定労働日数。月初適用は日割りなし。概算給与には所属店舗の交通費（月額18,000円）を足す（判断23）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="94" customHeight="1">
       <c r="A77" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6170,60 +6170,60 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>C-011</t>
+          <t>C-021</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>月の途中で交通費を改定したとき</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07 ／ data/14を投入
-【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
+          <t>【前提】C-000 S-07
+【操作】（a）EMP-001（月額交通費18,000）を2026-06-11適用で20,000に改定し、6月と7月の概算給与を見る →（b）EMP-003（日額交通費600）を2026-06-16適用で700に改定し、6月の日別を見る</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・14 勤務データ 2026-06</t>
+          <t>（投入済み）02 従業員マスタ／14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧　→　月別実績タブ（概算モード）】
-5月＝1,200×120h ＋ 日額交通費600×想定労働日数15 ＝ 153,000円／6月＝1,200×60h ＋ 1,250×60h ＝ 147,000 ＋ 日額交通費600×15 ＝ 156,000円。計算違い0件</t>
+          <t>【確認場所：給与実績一覧 → 月別実績（概算モード）／日別実績】
+（a）6月の概算給与に含まれる交通費は旧額18,000のまま（日割り=0件）。7月から20,000になる（b）EMP-003の6月は、6/15までの出勤日が600円・6/16以降の出勤日が700円で計算される（判断37）</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
-          <t>C-011.png</t>
+          <t>C-021.png</t>
         </is>
       </c>
       <c r="H77" s="15" t="inlineStr">
         <is>
-          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
+          <t>2026-06と07の月別実績（概算）／EMP-003の6月の日別（交通費が切り替わる前後の日）</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
+          <t>給与実績一覧 月別実績（概算モード）・日別実績</t>
         </is>
       </c>
       <c r="K77" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>月額交通費を日割りしていないか／日額が出勤日単位で切り替わるか</t>
         </is>
       </c>
       <c r="L77" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>ケース別 ＞ 給与改定を先の日付で予約する</t>
         </is>
       </c>
       <c r="M77" s="15" t="inlineStr">
         <is>
-          <t>AC-13</t>
+          <t>AC-67</t>
         </is>
       </c>
       <c r="N77" s="5" t="inlineStr"/>
@@ -6233,11 +6233,11 @@
       <c r="R77" s="5" t="inlineStr"/>
       <c r="S77" s="15" t="inlineStr">
         <is>
-          <t>時給者の概算給与＝単位給与額×所定労働時間＋所属店舗の交通費（日額なら×想定労働日数）。月中改定は期間ごとの実働時間×各単価の合計に交通費を足す（判断1・23）</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="124" customHeight="1">
+          <t>交通費は按分しない。月額はその月は旧額・翌月から新額／日額は適用日付以降の出勤日から新額（判断37）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="79" customHeight="1">
       <c r="A78" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6245,60 +6245,60 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>C-018</t>
+          <t>C-011</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>想定労働日数と日次の想定給与</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-05
-【操作】（a）EMP-003（時給・想定労働日数15を入力済み）の月次の想定給与を検算 →（b）EMP-003の想定労働日数を空欄にして保存し、打刻から求めた日数が使われるか見る →（c）EMP-001（月給・未入力）の月次と日次を検算</t>
+          <t>【前提】C-000 S-07 ／ data/14を投入
+【操作】EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>（投入済み）02 従業員マスタ・05 月次給与実績・06 日次給与実績</t>
+          <t>05 月次給与実績・14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
-（a）EMP-003の想定給与＝1,200×120＋600×15＝153,000円（b）空欄にしても打刻の出勤日数15日（data/06で2026-05は15日）が使われ、153,000円のまま変わらない（c）EMP-001は打刻20日が使われ、想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003の日次は想定給与・給与実績差分が「—」（判断27）。計算違い0件</t>
+          <t>【確認場所：給与実績一覧　→　月別実績タブ（概算モード）】
+5月＝1,200×120h ＋ 日額交通費600×想定労働日数15 ＝ 153,000円／6月＝1,200×60h ＋ 1,250×60h ＝ 147,000 ＋ 日額交通費600×15 ＝ 156,000円。計算違い0件</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
-          <t>C-018.png</t>
+          <t>C-011.png</t>
         </is>
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>従業員詳細の想定労働日数の欄（空欄でも金額が変わらないこと）／月別実績の想定給与／日別実績で時給者の想定給与が「—」であること</t>
+          <t>2026-05と2026-06の概算モード（EMP-003の行）</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="15" t="inlineStr">
         <is>
-          <t>従業員詳細（想定労働日数）→ 給与実績一覧 日別実績（想定給与）</t>
+          <t>給与実績一覧 → 月別実績タブ → 概算モード（2026-05と2026-06）</t>
         </is>
       </c>
       <c r="K78" s="15" t="inlineStr">
         <is>
-          <t>未入力でも打刻から日数が取れるか／日額交通費が日数ぶん月次に入るか</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 毎月の人件費を確定する</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>AC-59</t>
+          <t>AC-13</t>
         </is>
       </c>
       <c r="N78" s="5" t="inlineStr"/>
@@ -6308,11 +6308,11 @@
       <c r="R78" s="5" t="inlineStr"/>
       <c r="S78" s="15" t="inlineStr">
         <is>
-          <t>想定労働日数＝入力値 → 無ければ直近3か月の平均出勤日数（打刻）→ 打刻が無ければ月給者は営業日数。日額交通費の月次換算と月給者の日次按分に使う（判断26・27・28）</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="79" customHeight="1">
+          <t>時給者の概算給与＝単位給与額×所定労働時間＋所属店舗の交通費（日額なら×想定労働日数）。月中改定は期間ごとの実働時間×各単価の合計に交通費を足す（判断1・23）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="124" customHeight="1">
       <c r="A79" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6320,50 +6320,50 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>C-020</t>
+          <t>C-018</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>過去月の概算が後から変わらない</t>
+          <t>想定労働日数と日次の想定給与</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-05
-【操作】（a）2026-05（未締め）の概算給与を控える →（b）data/14（2026-06の勤務データ）を取り込む →（c）2026-05の概算給与をもう一度見る</t>
+【操作】（a）EMP-003（時給・想定労働日数15を入力済み）の月次の想定給与を検算 →（b）EMP-003の想定労働日数を空欄にして保存し、打刻から求めた日数が使われるか見る →（c）EMP-001（月給・未入力）の月次と日次を検算</t>
         </is>
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績／14 勤務データ 2026-06</t>
+          <t>（投入済み）02 従業員マスタ・05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F79" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ（概算モード）】
-（c）2026-05の概算給与が（a）と1円も変わらない（差分=0円）。2026-05には打刻があるので、その月の実出勤日数（EMP-001は20日・EMP-003は15日）が想定労働日数として使われ、直近3か月の平均には切り替わらない（判断34）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績／日別実績／従業員詳細（想定労働日数の欄）】
+（a）EMP-003の想定給与＝1,200×120＋600×15＝153,000円（b）空欄にしても打刻の出勤日数15日（data/06で2026-05は15日）が使われ、153,000円のまま変わらない（c）EMP-001は打刻20日が使われ、想定給与＝320,000＋18,000＝338,000円、日次＝338,000÷20＝16,900円。EMP-003の日次は想定給与・給与実績差分が「—」（判断27）。計算違い0件</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr">
         <is>
-          <t>C-020.png</t>
+          <t>C-018.png</t>
         </is>
       </c>
       <c r="H79" s="15" t="inlineStr">
         <is>
-          <t>取込前と取込後の2026-05 月別実績（概算モード）を2枚</t>
+          <t>従業員詳細の想定労働日数の欄（空欄でも金額が変わらないこと）／月別実績の想定給与／日別実績で時給者の想定給与が「—」であること</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 月別実績（概算モード）／実績データ取込</t>
+          <t>従業員詳細（想定労働日数）→ 給与実績一覧 日別実績（想定給与）</t>
         </is>
       </c>
       <c r="K79" s="15" t="inlineStr">
         <is>
-          <t>新しい月を取り込んでも過去月の概算が動かないか</t>
+          <t>未入力でも打刻から日数が取れるか／日額交通費が日数ぶん月次に入るか</t>
         </is>
       </c>
       <c r="L79" s="15" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="M79" s="15" t="inlineStr">
         <is>
-          <t>AC-64</t>
+          <t>AC-59</t>
         </is>
       </c>
       <c r="N79" s="5" t="inlineStr"/>
@@ -6383,11 +6383,11 @@
       <c r="R79" s="5" t="inlineStr"/>
       <c r="S79" s="15" t="inlineStr">
         <is>
-          <t>打刻がある月は その月の実出勤日数 を想定労働日数に使う。直近3か月の平均は打刻が無い月だけ（判断28・34）</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="109" customHeight="1">
+          <t>想定労働日数＝入力値 → 無ければ直近3か月の平均出勤日数（打刻）→ 打刻が無ければ月給者は営業日数。日額交通費の月次換算と月給者の日次按分に使う（判断26・27・28）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="79" customHeight="1">
       <c r="A80" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6395,50 +6395,50 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>C-019</t>
+          <t>C-020</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>日別の概算モード（営業日でならした見込み）</t>
+          <t>過去月の概算が後から変わらない</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
           <t>【前提】C-000 S-05
-【操作】給与実績一覧 → 日別実績タブ → 給与計算モードを「概算」に切り替える → 当月の全営業日ぶんの行が出ることと、日別の合計を確認する</t>
+【操作】（a）2026-05（未締め）の概算給与を控える →（b）data/14（2026-06の勤務データ）を取り込む →（c）2026-05の概算給与をもう一度見る</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績／14 勤務データ 2026-06</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 日別実績タブ → 給与計算モード＝概算】
-実績が無い日も含めて当月の全営業日に行が出る。1日あたり＝月次の概算給与÷当月の営業日数。日別を全部足すと月次の概算給与と一致する（差 0円）。実績モードに戻すと想定給与列は月次概算÷想定労働日数の額に変わる（同じ日でも額が違う）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ（概算モード）】
+（c）2026-05の概算給与が（a）と1円も変わらない（差分=0円）。2026-05には打刻があるので、その月の実出勤日数（EMP-001は20日・EMP-003は15日）が想定労働日数として使われ、直近3か月の平均には切り替わらない（判断34）</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>C-019.png</t>
+          <t>C-020.png</t>
         </is>
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>概算モードの日別（全営業日に行が出ている）／合計が月次の概算給与と一致していること／実績モードに戻したときの想定給与列</t>
+          <t>取込前と取込後の2026-05 月別実績（概算モード）を2枚</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 日別実績（概算モード ↔ 実績モード）</t>
+          <t>給与実績一覧 月別実績（概算モード）／実績データ取込</t>
         </is>
       </c>
       <c r="K80" s="15" t="inlineStr">
         <is>
-          <t>日別の合計が月次の概算給与と一致するか</t>
+          <t>新しい月を取り込んでも過去月の概算が動かないか</t>
         </is>
       </c>
       <c r="L80" s="15" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>AC-60</t>
+          <t>AC-64</t>
         </is>
       </c>
       <c r="N80" s="5" t="inlineStr"/>
@@ -6458,11 +6458,11 @@
       <c r="R80" s="5" t="inlineStr"/>
       <c r="S80" s="15" t="inlineStr">
         <is>
-          <t>概算の日別＝月次の概算給与÷当月の営業日数、当月の全営業日に配分。端数は最大剰余で月次と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="94" customHeight="1">
+          <t>打刻がある月は その月の実出勤日数 を想定労働日数に使う。直近3か月の平均は打刻が無い月だけ（判断28・34）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="109" customHeight="1">
       <c r="A81" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6470,60 +6470,60 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-019</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>日別の概算モード（営業日でならした見込み）</t>
         </is>
       </c>
       <c r="D81" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-07
-【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>【前提】C-000 S-05
+【操作】給与実績一覧 → 日別実績タブ → 給与計算モードを「概算」に切り替える → 当月の全営業日ぶんの行が出ることと、日別の合計を確認する</t>
         </is>
       </c>
       <c r="E81" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績</t>
+          <t>（投入済み）05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F81" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
-判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
+          <t>【確認場所：給与実績一覧 → 日別実績タブ → 給与計算モード＝概算】
+実績が無い日も含めて当月の全営業日に行が出る。1日あたり＝月次の概算給与÷当月の営業日数。日別を全部足すと月次の概算給与と一致する（差 0円）。実績モードに戻すと想定給与列は月次概算÷想定労働日数の額に変わる（同じ日でも額が違う）</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
         <is>
-          <t>C-013.png</t>
+          <t>C-019.png</t>
         </is>
       </c>
       <c r="H81" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
+          <t>概算モードの日別（全営業日に行が出ている）／合計が月次の概算給与と一致していること／実績モードに戻したときの想定給与列</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
+          <t>給与実績一覧 日別実績（概算モード ↔ 実績モード）</t>
         </is>
       </c>
       <c r="K81" s="15" t="inlineStr">
         <is>
-          <t>深夜1.5倍とヘルプの按分単価</t>
+          <t>日別の合計が月次の概算給与と一致するか</t>
         </is>
       </c>
       <c r="L81" s="15" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>操作手順 ＞ 毎月の人件費を確定する</t>
         </is>
       </c>
       <c r="M81" s="15" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-60</t>
         </is>
       </c>
       <c r="N81" s="5" t="inlineStr"/>
@@ -6533,11 +6533,11 @@
       <c r="R81" s="5" t="inlineStr"/>
       <c r="S81" s="15" t="inlineStr">
         <is>
-          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="79" customHeight="1">
+          <t>概算の日別＝月次の概算給与÷当月の営業日数、当月の全営業日に配分。端数は最大剰余で月次と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="94" customHeight="1">
       <c r="A82" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6545,60 +6545,60 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-013</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-03 S-04
-【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>【前提】C-000 S-03 S-07
+【操作】深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・実働11h・全時間がヘルプ）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
+          <t>05 月次給与実績・06 日次給与実績</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績・日別実績】
-交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
+          <t>【確認場所：給与実績一覧 → 月別実績（深夜残業代・みなし差分）／日別実績（5/8）】
+判断7（2026-08-07 確定）＝基礎時給×1.5（EMP-001は2,000×1.5＝3,000／h）。ヘルプ人件費＝按分（実績給与×ヘルプ時間÷総労働時間）にヘルプ先の交通費を加えた額。みなし労働時間差分＝172−(160＋20)＝−8h</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
         <is>
-          <t>C-017.png</t>
+          <t>C-013.png</t>
         </is>
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
+          <t>深夜残業代の列と、日別実績の5/8の行（ヘルプ人件費と計上先店舗）</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
+          <t>給与実績一覧 → 月別実績（深夜残業代・みなし労働時間差分）／日別実績（5/8のヘルプ人件費）</t>
         </is>
       </c>
       <c r="K82" s="15" t="inlineStr">
         <is>
-          <t>交通費が給与と別費目か</t>
+          <t>深夜1.5倍とヘルプの按分単価</t>
         </is>
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="N82" s="5" t="inlineStr"/>
@@ -6608,11 +6608,11 @@
       <c r="R82" s="5" t="inlineStr"/>
       <c r="S82" s="15" t="inlineStr">
         <is>
-          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="94" customHeight="1">
+          <t>深夜残業代＝基礎時給×1.5（判断7・確定＝時間外1.25＋深夜0.25）／ヘルプ人件費は月次按分（判断5）／みなし労働時間差分＝総労働−（所定＋みなし）、未達は減額なし（判断8・確定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="79" customHeight="1">
       <c r="A83" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6620,60 +6620,60 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-017</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>交通費の計上先</t>
         </is>
       </c>
       <c r="D83" s="15" t="inlineStr">
         <is>
-          <t>【前提】C-000 S-07
-【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+          <t>【前提】C-000 S-03 S-04
+【操作】EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
         </is>
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+          <t>05 月次給与実績・06 日次給与実績・03 ヘルプ先交通費</t>
         </is>
       </c>
       <c r="F83" s="15" t="inlineStr">
         <is>
-          <t>【確認場所：給与実績一覧 → 月別実績タブ】
-（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+          <t>【確認場所：給与実績一覧 → 月別実績・日別実績】
+交通費の列は表示されない。所属店舗の交通費18,000は人件費（実績給与）に、ヘルプ先の交通費1,600はヘルプ人件費に含まれる。設定側（従業員詳細）では単位交通費・ヘルプ先交通費が入力項目として残っている</t>
         </is>
       </c>
       <c r="G83" s="14" t="inlineStr">
         <is>
-          <t>C-008.png</t>
+          <t>C-017.png</t>
         </is>
       </c>
       <c r="H83" s="15" t="inlineStr">
         <is>
-          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
+          <t>月別実績の交通費・総支給額の列と、日別実績5/8の交通費（所属分と応援先分が別列）</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="15" t="inlineStr">
         <is>
-          <t>給与実績一覧 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+          <t>給与実績一覧 → 月別実績（交通費・総支給額の列）／日別実績（5/8のS02勤務日の交通費）</t>
         </is>
       </c>
       <c r="K83" s="15" t="inlineStr">
         <is>
-          <t>締め前後で差0円・解除後に再計算</t>
+          <t>交通費が給与と別費目か</t>
         </is>
       </c>
       <c r="L83" s="15" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 数字・締めについて</t>
+          <t>ケース別 ＞ 応援（ヘルプ）勤務がある場合</t>
         </is>
       </c>
       <c r="M83" s="15" t="inlineStr">
         <is>
-          <t>AC-16 AC-17</t>
+          <t>AC-15</t>
         </is>
       </c>
       <c r="N83" s="5" t="inlineStr"/>
@@ -6683,73 +6683,72 @@
       <c r="R83" s="5" t="inlineStr"/>
       <c r="S83" s="15" t="inlineStr">
         <is>
-          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="154" customHeight="1">
-      <c r="A84" s="16" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B84" s="16" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C84" s="17" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="D84" s="17" t="inlineStr">
-        <is>
-          <t>【前提】S-01
-【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
-        </is>
-      </c>
-      <c r="E84" s="17" t="inlineStr">
-        <is>
-          <t>（追加のデータ投入なし）</t>
-        </is>
-      </c>
-      <c r="F84" s="17" t="inlineStr">
-        <is>
-          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
-①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）
-同じ適用日付の設定が2件あっても両方保存され、編集日時で有効な行が決まる（上書き削除=0件。判断36）</t>
-        </is>
-      </c>
-      <c r="G84" s="16" t="inlineStr">
-        <is>
-          <t>R-01.png</t>
-        </is>
-      </c>
-      <c r="H84" s="17" t="inlineStr">
-        <is>
-          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
+          <t>交通費は給与と別の独立費目（判断6・確定）。所属店舗交通費は所属店舗、ヘルプ先交通費は応援先店舗に計上。総支給額＝実績給与＋交通費</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="94" customHeight="1">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>締めの前後で数字が動かないこと</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>【前提】C-000 S-07
+【操作】C-000のあと 2026-05を締める →（a）EMP-001に2026-05-10適用で340,000を保存し、勤怠も再取込 →（b）締めを解除する</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>05 月次給与実績・13 勤務データ 2026-05</t>
+        </is>
+      </c>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>【確認場所：給与実績一覧 → 月別実績タブ】
+（a）5月の実績給与・総労働時間の差分＝0円（357,600のまま動かない）　（b）解除後は改定が反映され、所定労働日割で 371,886円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000＋所属店舗の交通費18,000＋ヘルプ先の交通費1,600）</t>
+        </is>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>C-008.png</t>
+        </is>
+      </c>
+      <c r="H84" s="15" t="inlineStr">
+        <is>
+          <t>締め前・締め後・締め解除後の3枚（同じ従業員の同じ月）</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr"/>
-      <c r="J84" s="17" t="inlineStr">
-        <is>
-          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
-        </is>
-      </c>
-      <c r="K84" s="17" t="inlineStr">
-        <is>
-          <t>適用日付と履歴がテーブルにあるか</t>
-        </is>
-      </c>
-      <c r="L84" s="17" t="inlineStr">
-        <is>
-          <t>ケース別 ＞ 数字が合わないとき</t>
-        </is>
-      </c>
-      <c r="M84" s="17" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47 AC-55 AC-66</t>
+      <c r="J84" s="15" t="inlineStr">
+        <is>
+          <t>給与実績一覧 → 月別実績タブ（2026-05の締め前・締め後・締め解除後）</t>
+        </is>
+      </c>
+      <c r="K84" s="15" t="inlineStr">
+        <is>
+          <t>締め前後で差0円・解除後に再計算</t>
+        </is>
+      </c>
+      <c r="L84" s="15" t="inlineStr">
+        <is>
+          <t>よくあるご質問 ＞ 数字・締めについて</t>
+        </is>
+      </c>
+      <c r="M84" s="15" t="inlineStr">
+        <is>
+          <t>AC-16 AC-17</t>
         </is>
       </c>
       <c r="N84" s="5" t="inlineStr"/>
@@ -6757,13 +6756,13 @@
       <c r="P84" s="6" t="inlineStr"/>
       <c r="Q84" s="5" t="inlineStr"/>
       <c r="R84" s="5" t="inlineStr"/>
-      <c r="S84" s="17" t="inlineStr">
-        <is>
-          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="109" customHeight="1">
+      <c r="S84" s="15" t="inlineStr">
+        <is>
+          <t>締め済み期間は再計算しない（原則②）。締め解除後は所定労働日割（判断1）で再計算</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="154" customHeight="1">
       <c r="A85" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6771,18 +6770,18 @@
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>締めの実装レビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="D85" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
+【操作】テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する あわせて、従業員IDが主キーとして付番され、履歴・実績の外部キーが従業員IDになっていること、外部IDが別テーブルで管理されていることを確認する</t>
         </is>
       </c>
       <c r="E85" s="17" t="inlineStr">
@@ -6792,40 +6791,40 @@
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
-①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所
-適用済みの設定変更履歴は、APIを直接呼んでも更新・削除できない（成功=0件。判断29）</t>
+          <t>【確認場所：実装物のレビュー（テーブル定義・適用日付と履歴のスキーマ）】
+①履歴テーブルへのUPDATE/DELETEが0箇所（INSERTのみ） ②従業員コードに一意制約が1件ある ③ヘルプ先交通費が「従業員×店舗」の多対多で保持されている（従業員に1つの値だけを持つ実装ではない） ④従業員IDが自動付番され、履歴・実績が従業員IDに紐づく（従業員コードや外部IDを外部キーにしている箇所=0件）
+同じ適用日付の設定が2件あっても両方保存され、編集日時で有効な行が決まる（上書き削除=0件。判断36）</t>
         </is>
       </c>
       <c r="G85" s="16" t="inlineStr">
         <is>
-          <t>R-02.png</t>
+          <t>R-01.png</t>
         </is>
       </c>
       <c r="H85" s="17" t="inlineStr">
         <is>
-          <t>締めAPIのコードとスコープ判定箇所</t>
+          <t>画面ではなくテーブル定義を残す（スキーマ図またはDDL）</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr"/>
       <c r="J85" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
+          <t>（画面ではなく実装物：テーブル定義・適用日付と履歴のスキーマ）</t>
         </is>
       </c>
       <c r="K85" s="17" t="inlineStr">
         <is>
-          <t>APIでも店長が締められないか／適用済みの履歴が消せないか</t>
+          <t>適用日付と履歴がテーブルにあるか</t>
         </is>
       </c>
       <c r="L85" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ どなたが操作できますか</t>
+          <t>ケース別 ＞ 数字が合わないとき</t>
         </is>
       </c>
       <c r="M85" s="17" t="inlineStr">
         <is>
-          <t>AC-16 AC-41 AC-61</t>
+          <t>AC-07 AC-40 AC-47 AC-55 AC-66</t>
         </is>
       </c>
       <c r="N85" s="5" t="inlineStr"/>
@@ -6835,11 +6834,11 @@
       <c r="R85" s="5" t="inlineStr"/>
       <c r="S85" s="17" t="inlineStr">
         <is>
-          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="139" customHeight="1">
+          <t>原則①：過去は不変／データ保全：二重登録を防ぐ／原則③：交通費も働いた店舗の実費で</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="109" customHeight="1">
       <c r="A86" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6847,18 +6846,18 @@
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>入力検証とトランザクションのレビュー</t>
+          <t>締めの実装レビュー</t>
         </is>
       </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
+【操作】締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
       <c r="E86" s="17" t="inlineStr">
@@ -6868,40 +6867,40 @@
       </c>
       <c r="F86" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
-①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）
-実績がある従業員は、APIを直接呼んでも削除できない（成功=0件。判断31）</t>
+          <t>【確認場所：実装物のレビュー（締めのAPI・スコープ判定）】
+①締め状態を保持する項目が1つある ②締め済み期間で再計算を行う経路が0箇所（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が0箇所
+適用済みの設定変更履歴は、APIを直接呼んでも更新・削除できない（成功=0件。判断29）</t>
         </is>
       </c>
       <c r="G86" s="16" t="inlineStr">
         <is>
-          <t>R-03.png</t>
+          <t>R-02.png</t>
         </is>
       </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
+          <t>締めAPIのコードとスコープ判定箇所</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
+          <t>（画面ではなく実装物：締めのAPI・スコープ判定）</t>
         </is>
       </c>
       <c r="K86" s="17" t="inlineStr">
         <is>
-          <t>APIを直接呼んでも弾かれるか</t>
+          <t>APIでも店長が締められないか／適用済みの履歴が消せないか</t>
         </is>
       </c>
       <c r="L86" s="17" t="inlineStr">
         <is>
-          <t>よくあるご質問 ＞ 設定が保存できません</t>
+          <t>よくあるご質問 ＞ どなたが操作できますか</t>
         </is>
       </c>
       <c r="M86" s="17" t="inlineStr">
         <is>
-          <t>AC-23 AC-42 AC-43 AC-63</t>
+          <t>AC-16 AC-41 AC-61</t>
         </is>
       </c>
       <c r="N86" s="5" t="inlineStr"/>
@@ -6911,11 +6910,11 @@
       <c r="R86" s="5" t="inlineStr"/>
       <c r="S86" s="17" t="inlineStr">
         <is>
-          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="79" customHeight="1">
+          <t>原則②：締めたら動かない／原則②：締めは会社スコープのみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="139" customHeight="1">
       <c r="A87" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6923,18 +6922,18 @@
       </c>
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの共有レビュー</t>
+          <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
       <c r="D87" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】給与実績一覧・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+【操作】取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
       <c r="E87" s="17" t="inlineStr">
@@ -6944,39 +6943,40 @@
       </c>
       <c r="F87" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
-同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
+          <t>【確認場所：実装物のレビュー（サーバ側の入力検証とトランザクション）】
+①必須項目のサーバ側チェックが全項目にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の5種をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が1つに固定されている）
+実績がある従業員は、APIを直接呼んでも削除できない（成功=0件。判断31）</t>
         </is>
       </c>
       <c r="G87" s="16" t="inlineStr">
         <is>
-          <t>R-04.png</t>
+          <t>R-03.png</t>
         </is>
       </c>
       <c r="H87" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
+          <t>サーバ側の検証コードと、APIを直接呼んだときの応答</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr"/>
       <c r="J87" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
+          <t>（画面ではなく実装物：サーバ側の入力検証とトランザクション）</t>
         </is>
       </c>
       <c r="K87" s="17" t="inlineStr">
         <is>
-          <t>計算ロジックが1箇所か</t>
+          <t>APIを直接呼んでも弾かれるか</t>
         </is>
       </c>
       <c r="L87" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 人件費の計算方法</t>
+          <t>よくあるご質問 ＞ 設定が保存できません</t>
         </is>
       </c>
       <c r="M87" s="17" t="inlineStr">
         <is>
-          <t>AC-35 AC-11</t>
+          <t>AC-23 AC-42 AC-43 AC-63</t>
         </is>
       </c>
       <c r="N87" s="5" t="inlineStr"/>
@@ -6986,11 +6986,11 @@
       <c r="R87" s="5" t="inlineStr"/>
       <c r="S87" s="17" t="inlineStr">
         <is>
-          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="64" customHeight="1">
+          <t>データ保全：不正値を入れない／データ保全：中途半端に残さない／データ保全：不完全な登録を作らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="79" customHeight="1">
       <c r="A88" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -6998,18 +6998,18 @@
       </c>
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>計算ロジックの共有レビュー</t>
         </is>
       </c>
       <c r="D88" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】取込の列解決の実装を提示してもらう</t>
+【操作】給与実績一覧・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
       <c r="E88" s="17" t="inlineStr">
@@ -7019,39 +7019,39 @@
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
-CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
+          <t>【確認場所：実装物のレビュー（人件費の計算ロジックが1箇所か）】
+同じ集計ロジックを参照している（画面ごとの独自計算が0箇所）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も1箇所に集約されている</t>
         </is>
       </c>
       <c r="G88" s="16" t="inlineStr">
         <is>
-          <t>R-05.png</t>
+          <t>R-04.png</t>
         </is>
       </c>
       <c r="H88" s="17" t="inlineStr">
         <is>
-          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
+          <t>計算ロジックの実装箇所（呼び出し元が複数でも実体が1つであること）</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
+          <t>（画面ではなく実装物：人件費の計算ロジックが1箇所か）</t>
         </is>
       </c>
       <c r="K88" s="17" t="inlineStr">
         <is>
-          <t>列名がコードに埋まっていないか</t>
+          <t>計算ロジックが1箇所か</t>
         </is>
       </c>
       <c r="L88" s="17" t="inlineStr">
         <is>
-          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
+          <t>操作手順 ＞ 人件費の計算方法</t>
         </is>
       </c>
       <c r="M88" s="17" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-35 AC-11</t>
         </is>
       </c>
       <c r="N88" s="5" t="inlineStr"/>
@@ -7061,11 +7061,11 @@
       <c r="R88" s="5" t="inlineStr"/>
       <c r="S88" s="17" t="inlineStr">
         <is>
-          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="79" customHeight="1">
+          <t>計算：個人単位でも同じ数字／原則③：人件費は働いた店舗に付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="64" customHeight="1">
       <c r="A89" s="16" t="inlineStr">
         <is>
           <t>実装レビュー</t>
@@ -7073,18 +7073,18 @@
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>設定更新処理の共通化レビュー</t>
+          <t>列マッピングの実装レビュー</t>
         </is>
       </c>
       <c r="D89" s="17" t="inlineStr">
         <is>
           <t>【前提】S-01
-【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+【操作】取込の列解決の実装を提示してもらう</t>
         </is>
       </c>
       <c r="E89" s="17" t="inlineStr">
@@ -7094,39 +7094,39 @@
       </c>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
-設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+          <t>【確認場所：実装物のレビュー（列名の対応づけがデータ側にあるか）】
+CSVの列名がコードに直接書かれている箇所が0箇所。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
       <c r="G89" s="16" t="inlineStr">
         <is>
-          <t>R-06.png</t>
+          <t>R-05.png</t>
         </is>
       </c>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+          <t>列名の対応づけを保持している箇所（DBかコードか）</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr"/>
       <c r="J89" s="17" t="inlineStr">
         <is>
-          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+          <t>（画面ではなく実装物：列名の対応づけがデータ側にあるか）</t>
         </is>
       </c>
       <c r="K89" s="17" t="inlineStr">
         <is>
-          <t>2つの入口で更新処理が共通か</t>
+          <t>列名がコードに埋まっていないか</t>
         </is>
       </c>
       <c r="L89" s="17" t="inlineStr">
         <is>
-          <t>操作手順 ＞ 従業員の設定を変更する</t>
+          <t>ケース別 ＞ CSVの列名がラクミーと違うとき</t>
         </is>
       </c>
       <c r="M89" s="17" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-22 AC-24</t>
         </is>
       </c>
       <c r="N89" s="5" t="inlineStr"/>
@@ -7136,17 +7136,92 @@
       <c r="R89" s="5" t="inlineStr"/>
       <c r="S89" s="17" t="inlineStr">
         <is>
+          <t>入出力：表記ゆれを吸収／入出力：CSが自走できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="79" customHeight="1">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="D90" s="17" t="inlineStr">
+        <is>
+          <t>【前提】S-01
+【操作】従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>（追加のデータ投入なし）</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>【確認場所：実装物のレビュー（従業員詳細とモーダルで設定更新処理が共通か）】
+設定更新の処理が1箇所に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="G90" s="16" t="inlineStr">
+        <is>
+          <t>R-06.png</t>
+        </is>
+      </c>
+      <c r="H90" s="17" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの更新処理の呼び出し先</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr"/>
+      <c r="J90" s="17" t="inlineStr">
+        <is>
+          <t>（画面ではなく実装物：従業員詳細とモーダルで設定更新処理が共通か）</t>
+        </is>
+      </c>
+      <c r="K90" s="17" t="inlineStr">
+        <is>
+          <t>2つの入口で更新処理が共通か</t>
+        </is>
+      </c>
+      <c r="L90" s="17" t="inlineStr">
+        <is>
+          <t>操作手順 ＞ 従業員の設定を変更する</t>
+        </is>
+      </c>
+      <c r="M90" s="17" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="N90" s="5" t="inlineStr"/>
+      <c r="O90" s="5" t="inlineStr"/>
+      <c r="P90" s="6" t="inlineStr"/>
+      <c r="Q90" s="5" t="inlineStr"/>
+      <c r="R90" s="5" t="inlineStr"/>
+      <c r="S90" s="17" t="inlineStr">
+        <is>
           <t>原則①：どの入口から編集しても履歴が残る</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S89"/>
+  <autoFilter ref="A2:S90"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3:O89" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -4509,7 +4509,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="109" customHeight="1">
+    <row r="55" ht="139" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
           <t>取込</t>
@@ -4528,7 +4528,7 @@
       <c r="D55" s="8" t="inlineStr">
         <is>
           <t>【前提】S-06
-【操作】（a）連携設定の「新しい従業員を自動で追加する」がOFFの状態で、対応表に無い外部IDを含む勤怠データを取り込む →（b）ONにして同じデータを取り込む →（c）従業員一覧と給与実績一覧のエラーの絞り込みを見る</t>
+【操作】（a）連携設定の「新しい従業員を自動で追加する」がOFFの状態で、対応表に無い外部IDを含む勤怠データを取り込む →（b）ONにして同じデータを取り込む →（c）従業員一覧の絞り込み「設定＝給与設定が未入力」と、給与実績一覧の「エラー＝給与設定が未入力」を見る</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -4539,7 +4539,7 @@
       <c r="F55" s="8" t="inlineStr">
         <is>
           <t>【確認場所：連携設定／実績の取込結果 → 従業員一覧 → 給与実績一覧】
-（a）取り込まれず、件数と理由が実績の取込結果に出る（黙って登録=0件）（b）従業員が1名追加され、従業員IDが付番され、在籍状態=在籍、適用日付=取込対象月の初日、給与設定は空。外部ID対応表が1行増える（c）給与実績一覧のエラーの絞り込み「給与設定が未入力」でその従業員だけを抽出できる</t>
+（a）取り込まれず、件数と理由が実績の取込結果に出る（黙って登録=0件）（b）従業員が1名追加され、従業員IDが付番され、在籍状態=在籍、適用日付=取込対象月の初日、給与設定は空。外部ID対応表が1行増える（c）従業員一覧の「設定＝給与設定が未入力」でその従業員だけが残り、そこから従業員詳細を開いて設定を入れられる。給与実績一覧の「エラー＝給与設定が未入力」でも同じ従業員が抽出できる</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>連携設定のチェックボックス（OFFとON）／OFFのときの取込結果の件数と理由／ONのあとの従業員一覧（1名増えた状態）／エラーの絞り込みで抽出した状態</t>
+          <t>連携設定のチェックボックス（OFFとON）／OFFのときの取込結果の件数と理由／ONのあとの従業員一覧（1名増えた状態）／従業員一覧の「設定」の絞り込みで抽出した状態／給与実績一覧のエラーの絞り込み</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>

--- a/20260805_従業員管理_02_検証プラン.xlsx
+++ b/20260805_従業員管理_02_検証プラン.xlsx
@@ -6387,7 +6387,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="79" customHeight="1">
+    <row r="80" ht="94" customHeight="1">
       <c r="A80" s="14" t="inlineStr">
         <is>
           <t>計算</t>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>過去月の概算が後から変わらない</t>
+          <t>過去月の概算が後から変わらない（想定労働日数の保存）</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
@@ -6417,7 +6417,7 @@
       <c r="F80" s="15" t="inlineStr">
         <is>
           <t>【確認場所：給与実績一覧 → 月別実績タブ（概算モード）】
-（c）2026-05の概算給与が（a）と1円も変わらない（差分=0円）。2026-05には打刻があるので、その月の実出勤日数（EMP-001は20日・EMP-003は15日）が想定労働日数として使われ、直近3か月の平均には切り替わらない（判断34）</t>
+（c）2026-05の概算給与が（a）と1円も変わらない（差分=0円）。2026-05の想定労働日数は最初に計算したときの値が保存されており、新しい月を取り込んでも動かない（EMP-005は20日のまま。打刻の19日には変わらない）。想定労働日数と勤務日数は別の値として表示される（同じ値=0件。判断43）</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="K80" s="15" t="inlineStr">
         <is>
-          <t>新しい月を取り込んでも過去月の概算が動かないか</t>
+          <t>新しい月を取り込んでも過去月の概算が動かないか／想定労働日数が勤務日数と同じになっていないか</t>
         </is>
       </c>
       <c r="L80" s="15" t="inlineStr">
@@ -6458,7 +6458,7 @@
       <c r="R80" s="5" t="inlineStr"/>
       <c r="S80" s="15" t="inlineStr">
         <is>
-          <t>打刻がある月は その月の実出勤日数 を想定労働日数に使う。直近3か月の平均は打刻が無い月だけ（判断28・34）</t>
+          <t>想定労働日数はその月を最初に計算したときの値を保存する。入力値があればその値、無ければ直近3か月の平均出勤日数（判断28・43）</t>
         </is>
       </c>
     </row>
